--- a/Spreadsheets/BasicCalculations.xlsx
+++ b/Spreadsheets/BasicCalculations.xlsx
@@ -1665,9 +1665,6 @@
     <t>RCD Snubber</t>
   </si>
   <si>
-    <t>Regenerative Snummer</t>
-  </si>
-  <si>
     <t>n_s</t>
   </si>
   <si>
@@ -2377,6 +2374,9 @@
   </si>
   <si>
     <t>Maximum composite output current limiting resistor average power</t>
+  </si>
+  <si>
+    <t>Regenerative Snubber</t>
   </si>
 </sst>
 </file>
@@ -2645,9 +2645,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2655,6 +2652,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2673,7 +2673,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="10">
     <dxf>
       <fill>
         <patternFill>
@@ -2741,90 +2741,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2923,16 +2839,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>28013</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>521071</xdr:colOff>
       <xdr:row>305</xdr:row>
-      <xdr:rowOff>172891</xdr:rowOff>
+      <xdr:rowOff>161685</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>36017</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>36016</xdr:colOff>
       <xdr:row>312</xdr:row>
-      <xdr:rowOff>84548</xdr:rowOff>
+      <xdr:rowOff>73342</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2949,7 +2865,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7457513" y="55812498"/>
+          <a:off x="9687483" y="58275391"/>
           <a:ext cx="7247004" cy="1245157"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4376,15 +4292,15 @@
       <c r="C19" s="8"/>
       <c r="D19" s="13"/>
       <c r="E19" s="8"/>
-      <c r="G19" s="46" t="s">
-        <v>591</v>
-      </c>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
+      <c r="G19" s="45" t="s">
+        <v>590</v>
+      </c>
+      <c r="H19" s="45"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="45"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="44" t="s">
+      <c r="A20" s="47" t="s">
         <v>103</v>
       </c>
       <c r="B20" t="s">
@@ -4399,13 +4315,13 @@
       <c r="E20" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="46"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="44"/>
+      <c r="A21" s="47"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6" t="s">
         <v>3</v>
@@ -4417,13 +4333,13 @@
       <c r="E21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G21" s="46"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="44"/>
+      <c r="A22" s="47"/>
       <c r="B22" t="s">
         <v>67</v>
       </c>
@@ -4433,13 +4349,13 @@
       <c r="D22">
         <v>0.1</v>
       </c>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="44"/>
+      <c r="A23" s="47"/>
       <c r="B23" s="6"/>
       <c r="C23" s="12" t="s">
         <v>72</v>
@@ -4451,7 +4367,7 @@
       <c r="E23" s="6"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="44"/>
+      <c r="A24" s="47"/>
       <c r="C24" t="s">
         <v>7</v>
       </c>
@@ -4460,7 +4376,7 @@
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="44"/>
+      <c r="A25" s="47"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6" t="s">
         <v>28</v>
@@ -4469,7 +4385,7 @@
       <c r="E25" s="6"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="44"/>
+      <c r="A26" s="47"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
         <v>12</v>
@@ -4483,7 +4399,7 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="44"/>
+      <c r="A27" s="47"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6" t="s">
         <v>11</v>
@@ -4497,7 +4413,7 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="44"/>
+      <c r="A28" s="47"/>
       <c r="C28" t="s">
         <v>8</v>
       </c>
@@ -4509,7 +4425,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="44"/>
+      <c r="A29" s="47"/>
       <c r="C29" t="s">
         <v>10</v>
       </c>
@@ -4520,41 +4436,41 @@
       <c r="E29" t="s">
         <v>25</v>
       </c>
-      <c r="G29" s="46" t="s">
-        <v>592</v>
-      </c>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
+      <c r="G29" s="45" t="s">
+        <v>591</v>
+      </c>
+      <c r="H29" s="46"/>
+      <c r="I29" s="46"/>
+      <c r="J29" s="46"/>
+      <c r="K29" s="46"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B30" s="8"/>
       <c r="C30" s="10"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="G30" s="47"/>
-      <c r="H30" s="47"/>
-      <c r="I30" s="47"/>
-      <c r="J30" s="47"/>
-      <c r="K30" s="47"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="46"/>
+      <c r="K30" s="46"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="44" t="s">
+      <c r="A31" s="47" t="s">
         <v>132</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="7"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="47"/>
-      <c r="J31" s="47"/>
-      <c r="K31" s="47"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="46"/>
+      <c r="J31" s="46"/>
+      <c r="K31" s="46"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="44"/>
+      <c r="A32" s="47"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6" t="s">
         <v>126</v>
@@ -4566,14 +4482,14 @@
       <c r="E32" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G32" s="47"/>
-      <c r="H32" s="47"/>
-      <c r="I32" s="47"/>
-      <c r="J32" s="47"/>
-      <c r="K32" s="47"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="46"/>
+      <c r="I32" s="46"/>
+      <c r="J32" s="46"/>
+      <c r="K32" s="46"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" s="44"/>
+      <c r="A33" s="47"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8" t="s">
         <v>127</v>
@@ -4584,14 +4500,14 @@
       <c r="E33" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G33" s="47"/>
-      <c r="H33" s="47"/>
-      <c r="I33" s="47"/>
-      <c r="J33" s="47"/>
-      <c r="K33" s="47"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="46"/>
+      <c r="I33" s="46"/>
+      <c r="J33" s="46"/>
+      <c r="K33" s="46"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A34" s="44"/>
+      <c r="A34" s="47"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8" t="s">
         <v>128</v>
@@ -4600,14 +4516,14 @@
         <v>5</v>
       </c>
       <c r="E34" s="9"/>
-      <c r="G34" s="47"/>
-      <c r="H34" s="47"/>
-      <c r="I34" s="47"/>
-      <c r="J34" s="47"/>
-      <c r="K34" s="47"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="46"/>
+      <c r="I34" s="46"/>
+      <c r="J34" s="46"/>
+      <c r="K34" s="46"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A35" s="44"/>
+      <c r="A35" s="47"/>
       <c r="C35" t="s">
         <v>133</v>
       </c>
@@ -4617,7 +4533,7 @@
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A36" s="44"/>
+      <c r="A36" s="47"/>
       <c r="C36" t="s">
         <v>136</v>
       </c>
@@ -4629,7 +4545,7 @@
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A37" s="44"/>
+      <c r="A37" s="47"/>
       <c r="C37" t="s">
         <v>169</v>
       </c>
@@ -4639,7 +4555,7 @@
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A38" s="44"/>
+      <c r="A38" s="47"/>
       <c r="C38" t="s">
         <v>170</v>
       </c>
@@ -4649,7 +4565,7 @@
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A39" s="44"/>
+      <c r="A39" s="47"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6" t="s">
         <v>9</v>
@@ -4663,10 +4579,10 @@
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A40" s="44"/>
+      <c r="A40" s="47"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D40" s="6">
         <f>POWER(D10, 2)*D37</f>
@@ -4677,7 +4593,7 @@
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A41" s="44"/>
+      <c r="A41" s="47"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6" t="s">
         <v>171</v>
@@ -4689,7 +4605,7 @@
       <c r="E41" s="6"/>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A42" s="44"/>
+      <c r="A42" s="47"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
         <v>172</v>
@@ -4701,10 +4617,10 @@
       <c r="E42" s="6"/>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A43" s="44"/>
+      <c r="A43" s="47"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D43" s="6">
         <f>POWER(D11, 2)*D37</f>
@@ -4715,7 +4631,7 @@
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A44" s="44"/>
+      <c r="A44" s="47"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6" t="s">
         <v>27</v>
@@ -4729,10 +4645,10 @@
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A45" s="44"/>
+      <c r="A45" s="47"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D45" s="11">
         <v>3</v>
@@ -4742,10 +4658,10 @@
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A46" s="44"/>
+      <c r="A46" s="47"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D46" t="b">
         <f>D45/D4&gt;=D41</f>
@@ -4754,10 +4670,10 @@
       <c r="E46" s="6"/>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A47" s="44"/>
+      <c r="A47" s="47"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D47" s="11">
         <f>D45*D34/D4</f>
@@ -4778,7 +4694,7 @@
       </c>
     </row>
     <row r="49" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="44" t="s">
+      <c r="A49" s="47" t="s">
         <v>30</v>
       </c>
       <c r="C49" s="8" t="s">
@@ -4802,7 +4718,7 @@
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A50" s="44"/>
+      <c r="A50" s="47"/>
       <c r="C50" s="8" t="s">
         <v>26</v>
       </c>
@@ -4824,7 +4740,7 @@
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A51" s="44"/>
+      <c r="A51" s="47"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6" t="s">
         <v>13</v>
@@ -4848,7 +4764,7 @@
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A52" s="44"/>
+      <c r="A52" s="47"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6" t="s">
         <v>14</v>
@@ -4869,7 +4785,7 @@
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A53" s="44"/>
+      <c r="A53" s="47"/>
       <c r="C53" s="8" t="s">
         <v>16</v>
       </c>
@@ -4892,7 +4808,7 @@
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A54" s="44"/>
+      <c r="A54" s="47"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6" t="s">
         <v>107</v>
@@ -4913,7 +4829,7 @@
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A55" s="44"/>
+      <c r="A55" s="47"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6" t="s">
         <v>15</v>
@@ -4934,7 +4850,7 @@
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A56" s="44"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6" t="s">
         <v>32</v>
@@ -4946,7 +4862,7 @@
       <c r="E56" s="6"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A57" s="44"/>
+      <c r="A57" s="47"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6" t="s">
         <v>108</v>
@@ -4965,7 +4881,7 @@
       <c r="E58" s="8"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A59" s="45" t="s">
+      <c r="A59" s="44" t="s">
         <v>109</v>
       </c>
       <c r="C59" s="6"/>
@@ -4973,7 +4889,7 @@
       <c r="E59" s="6"/>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A60" s="45"/>
+      <c r="A60" s="44"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6" t="s">
         <v>90</v>
@@ -4985,7 +4901,7 @@
       <c r="E60" s="6"/>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A61" s="45"/>
+      <c r="A61" s="44"/>
       <c r="B61" s="6" t="s">
         <v>124</v>
       </c>
@@ -5001,7 +4917,7 @@
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A62" s="45"/>
+      <c r="A62" s="44"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6" t="s">
         <v>135</v>
@@ -5013,7 +4929,7 @@
       <c r="E62" s="6"/>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A63" s="45"/>
+      <c r="A63" s="44"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6" t="s">
         <v>91</v>
@@ -5026,7 +4942,7 @@
       <c r="R63" s="1"/>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A64" s="45"/>
+      <c r="A64" s="44"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6" t="s">
         <v>92</v>
@@ -5038,7 +4954,7 @@
       <c r="E64" s="6"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="45"/>
+      <c r="A65" s="44"/>
       <c r="B65" s="6" t="s">
         <v>123</v>
       </c>
@@ -5052,7 +4968,7 @@
       <c r="E65" s="6"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="45"/>
+      <c r="A66" s="44"/>
       <c r="B66" s="6" t="s">
         <v>119</v>
       </c>
@@ -5066,7 +4982,7 @@
       <c r="E66" s="6"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="45"/>
+      <c r="A67" s="44"/>
       <c r="B67" s="6" t="s">
         <v>122</v>
       </c>
@@ -5080,7 +4996,7 @@
       <c r="E67" s="6"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="45"/>
+      <c r="A68" s="44"/>
       <c r="C68" t="s">
         <v>94</v>
       </c>
@@ -5089,7 +5005,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="45"/>
+      <c r="A69" s="44"/>
       <c r="C69" t="s">
         <v>95</v>
       </c>
@@ -5098,7 +5014,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="45"/>
+      <c r="A70" s="44"/>
       <c r="C70" t="s">
         <v>96</v>
       </c>
@@ -5113,7 +5029,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="45"/>
+      <c r="A71" s="44"/>
       <c r="C71" t="s">
         <v>97</v>
       </c>
@@ -5123,7 +5039,7 @@
       <c r="G71" s="5"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="45"/>
+      <c r="A72" s="44"/>
       <c r="C72" t="s">
         <v>98</v>
       </c>
@@ -5132,7 +5048,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="45"/>
+      <c r="A73" s="44"/>
       <c r="C73" t="s">
         <v>99</v>
       </c>
@@ -5141,7 +5057,7 @@
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="45"/>
+      <c r="A74" s="44"/>
       <c r="C74" t="s">
         <v>100</v>
       </c>
@@ -5150,7 +5066,7 @@
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="45"/>
+      <c r="A75" s="44"/>
       <c r="C75" t="s">
         <v>113</v>
       </c>
@@ -5159,7 +5075,7 @@
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="45"/>
+      <c r="A76" s="44"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6" t="s">
         <v>110</v>
@@ -5171,7 +5087,7 @@
       <c r="E76" s="6"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="45"/>
+      <c r="A77" s="44"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6" t="s">
         <v>111</v>
@@ -5183,7 +5099,7 @@
       <c r="E77" s="6"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="45"/>
+      <c r="A78" s="44"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6" t="s">
         <v>112</v>
@@ -5195,7 +5111,7 @@
       <c r="E78" s="6"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="45"/>
+      <c r="A79" s="44"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6" t="s">
         <v>114</v>
@@ -5207,7 +5123,7 @@
       <c r="E79" s="6"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="45"/>
+      <c r="A80" s="44"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6" t="s">
         <v>115</v>
@@ -5219,7 +5135,7 @@
       <c r="E80" s="6"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="45"/>
+      <c r="A81" s="44"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6" t="s">
         <v>116</v>
@@ -5231,7 +5147,7 @@
       <c r="E81" s="6"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="45"/>
+      <c r="A82" s="44"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6" t="s">
         <v>117</v>
@@ -5243,7 +5159,7 @@
       <c r="E82" s="6"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="45"/>
+      <c r="A83" s="44"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6" t="s">
         <v>118</v>
@@ -5264,7 +5180,7 @@
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="44" t="s">
+      <c r="A86" s="47" t="s">
         <v>125</v>
       </c>
       <c r="B86" s="6" t="s">
@@ -5282,7 +5198,7 @@
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="44"/>
+      <c r="A87" s="47"/>
       <c r="B87" t="s">
         <v>58</v>
       </c>
@@ -5294,7 +5210,7 @@
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="44"/>
+      <c r="A88" s="47"/>
       <c r="B88" t="s">
         <v>57</v>
       </c>
@@ -5303,7 +5219,7 @@
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="44"/>
+      <c r="A89" s="47"/>
       <c r="B89" t="s">
         <v>51</v>
       </c>
@@ -5315,7 +5231,7 @@
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="44"/>
+      <c r="A90" s="47"/>
       <c r="C90" t="s">
         <v>36</v>
       </c>
@@ -5324,7 +5240,7 @@
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="44"/>
+      <c r="A91" s="47"/>
       <c r="B91" t="s">
         <v>39</v>
       </c>
@@ -5336,12 +5252,12 @@
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="44"/>
+      <c r="A92" s="47"/>
       <c r="B92" t="s">
+        <v>579</v>
+      </c>
+      <c r="C92" s="35" t="s">
         <v>580</v>
-      </c>
-      <c r="C92" s="35" t="s">
-        <v>581</v>
       </c>
       <c r="D92" s="1">
         <f>D2/D3</f>
@@ -5349,7 +5265,7 @@
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="44"/>
+      <c r="A93" s="47"/>
       <c r="B93" t="s">
         <v>41</v>
       </c>
@@ -5362,7 +5278,7 @@
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="44"/>
+      <c r="A94" s="47"/>
       <c r="C94" t="s">
         <v>40</v>
       </c>
@@ -5372,7 +5288,7 @@
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="44"/>
+      <c r="A95" s="47"/>
       <c r="B95" t="s">
         <v>45</v>
       </c>
@@ -5385,7 +5301,7 @@
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="44"/>
+      <c r="A96" s="47"/>
       <c r="B96" t="s">
         <v>53</v>
       </c>
@@ -5398,7 +5314,7 @@
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="44"/>
+      <c r="A97" s="47"/>
       <c r="B97" t="s">
         <v>55</v>
       </c>
@@ -5411,7 +5327,7 @@
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="44"/>
+      <c r="A98" s="47"/>
       <c r="C98" t="s">
         <v>60</v>
       </c>
@@ -5421,12 +5337,12 @@
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="44"/>
+      <c r="A99" s="47"/>
       <c r="B99" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C99" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D99">
         <f>D93/D101</f>
@@ -5434,12 +5350,12 @@
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="44"/>
+      <c r="A100" s="47"/>
       <c r="B100" t="s">
+        <v>582</v>
+      </c>
+      <c r="C100" t="s">
         <v>583</v>
-      </c>
-      <c r="C100" t="s">
-        <v>584</v>
       </c>
       <c r="D100">
         <f>1/D99</f>
@@ -5450,7 +5366,7 @@
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="44"/>
+      <c r="A101" s="47"/>
       <c r="B101" t="s">
         <v>64</v>
       </c>
@@ -5463,7 +5379,7 @@
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="44"/>
+      <c r="A102" s="47"/>
       <c r="C102" t="s">
         <v>66</v>
       </c>
@@ -5473,7 +5389,7 @@
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="44"/>
+      <c r="A103" s="47"/>
       <c r="B103" t="s">
         <v>68</v>
       </c>
@@ -5489,7 +5405,7 @@
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="44"/>
+      <c r="A104" s="47"/>
       <c r="B104" t="s">
         <v>68</v>
       </c>
@@ -5502,7 +5418,7 @@
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="44"/>
+      <c r="A105" s="47"/>
       <c r="B105" t="s">
         <v>174</v>
       </c>
@@ -5515,7 +5431,7 @@
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="44"/>
+      <c r="A106" s="47"/>
       <c r="C106" t="s">
         <v>176</v>
       </c>
@@ -5524,7 +5440,7 @@
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="44"/>
+      <c r="A107" s="47"/>
       <c r="C107" t="s">
         <v>227</v>
       </c>
@@ -5534,7 +5450,7 @@
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="44"/>
+      <c r="A108" s="47"/>
       <c r="C108" t="s">
         <v>187</v>
       </c>
@@ -5546,7 +5462,7 @@
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="44"/>
+      <c r="A109" s="47"/>
       <c r="C109" t="s">
         <v>185</v>
       </c>
@@ -5558,7 +5474,7 @@
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="44"/>
+      <c r="A110" s="47"/>
       <c r="C110" t="s">
         <v>184</v>
       </c>
@@ -5567,7 +5483,7 @@
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="44"/>
+      <c r="A111" s="47"/>
       <c r="C111" t="s">
         <v>178</v>
       </c>
@@ -5580,7 +5496,7 @@
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="44"/>
+      <c r="A112" s="47"/>
       <c r="C112" t="s">
         <v>179</v>
       </c>
@@ -5593,7 +5509,7 @@
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="44"/>
+      <c r="A113" s="47"/>
       <c r="C113" t="s">
         <v>180</v>
       </c>
@@ -5605,7 +5521,7 @@
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="44"/>
+      <c r="A114" s="47"/>
       <c r="C114" t="s">
         <v>189</v>
       </c>
@@ -5618,7 +5534,7 @@
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="44"/>
+      <c r="A115" s="47"/>
       <c r="C115" t="s">
         <v>181</v>
       </c>
@@ -5628,7 +5544,7 @@
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="44"/>
+      <c r="A116" s="47"/>
       <c r="C116" t="s">
         <v>182</v>
       </c>
@@ -5638,7 +5554,7 @@
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="44"/>
+      <c r="A117" s="47"/>
       <c r="C117" t="s">
         <v>177</v>
       </c>
@@ -5648,7 +5564,7 @@
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="44"/>
+      <c r="A118" s="47"/>
       <c r="C118" t="s">
         <v>183</v>
       </c>
@@ -5658,7 +5574,7 @@
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="44"/>
+      <c r="A119" s="47"/>
       <c r="C119" t="s">
         <v>195</v>
       </c>
@@ -5668,7 +5584,7 @@
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="44"/>
+      <c r="A120" s="47"/>
       <c r="C120" t="s">
         <v>194</v>
       </c>
@@ -5681,7 +5597,7 @@
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="44"/>
+      <c r="A121" s="47"/>
       <c r="C121" t="s">
         <v>186</v>
       </c>
@@ -5691,7 +5607,7 @@
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="44"/>
+      <c r="A122" s="47"/>
       <c r="C122" t="s">
         <v>188</v>
       </c>
@@ -5701,7 +5617,7 @@
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="44"/>
+      <c r="A123" s="47"/>
       <c r="C123" t="s">
         <v>189</v>
       </c>
@@ -5711,7 +5627,7 @@
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="44"/>
+      <c r="A124" s="47"/>
       <c r="C124" t="s">
         <v>190</v>
       </c>
@@ -5724,7 +5640,7 @@
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="44"/>
+      <c r="A125" s="47"/>
       <c r="C125" t="s">
         <v>191</v>
       </c>
@@ -5733,7 +5649,7 @@
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="44"/>
+      <c r="A126" s="47"/>
       <c r="C126" t="s">
         <v>193</v>
       </c>
@@ -5743,7 +5659,7 @@
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="44"/>
+      <c r="A127" s="47"/>
       <c r="C127" t="s">
         <v>225</v>
       </c>
@@ -5753,7 +5669,7 @@
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="44"/>
+      <c r="A128" s="47"/>
       <c r="C128" t="s">
         <v>201</v>
       </c>
@@ -5762,7 +5678,7 @@
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="44"/>
+      <c r="A129" s="47"/>
       <c r="C129" t="s">
         <v>200</v>
       </c>
@@ -5772,7 +5688,7 @@
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="44"/>
+      <c r="A130" s="47"/>
       <c r="C130" t="s">
         <v>202</v>
       </c>
@@ -5785,19 +5701,19 @@
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="44"/>
+      <c r="A131" s="47"/>
       <c r="C131" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="44"/>
+      <c r="A132" s="47"/>
       <c r="C132" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="44"/>
+      <c r="A133" s="47"/>
       <c r="C133" t="s">
         <v>199</v>
       </c>
@@ -5809,7 +5725,7 @@
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" s="44"/>
+      <c r="A134" s="47"/>
       <c r="C134" t="s">
         <v>209</v>
       </c>
@@ -5819,7 +5735,7 @@
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" s="44"/>
+      <c r="A135" s="47"/>
       <c r="C135" t="s">
         <v>198</v>
       </c>
@@ -5828,7 +5744,7 @@
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="44"/>
+      <c r="A136" s="47"/>
       <c r="C136" t="s">
         <v>203</v>
       </c>
@@ -5837,7 +5753,7 @@
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" s="44"/>
+      <c r="A137" s="47"/>
       <c r="C137" t="s">
         <v>204</v>
       </c>
@@ -5847,7 +5763,7 @@
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" s="44"/>
+      <c r="A138" s="47"/>
       <c r="C138" t="s">
         <v>189</v>
       </c>
@@ -5857,7 +5773,7 @@
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" s="44"/>
+      <c r="A139" s="47"/>
       <c r="C139" t="s">
         <v>190</v>
       </c>
@@ -5867,7 +5783,7 @@
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" s="44"/>
+      <c r="A140" s="47"/>
       <c r="C140" t="s">
         <v>206</v>
       </c>
@@ -5880,7 +5796,7 @@
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A141" s="44"/>
+      <c r="A141" s="47"/>
       <c r="C141" t="s">
         <v>207</v>
       </c>
@@ -5893,7 +5809,7 @@
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" s="44"/>
+      <c r="A142" s="47"/>
       <c r="C142" t="s">
         <v>208</v>
       </c>
@@ -5906,7 +5822,7 @@
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143" s="44"/>
+      <c r="A143" s="47"/>
       <c r="C143" t="s">
         <v>210</v>
       </c>
@@ -5919,7 +5835,7 @@
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A144" s="44"/>
+      <c r="A144" s="47"/>
       <c r="C144" t="s">
         <v>211</v>
       </c>
@@ -5932,7 +5848,7 @@
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" s="44"/>
+      <c r="A145" s="47"/>
       <c r="C145" t="s">
         <v>201</v>
       </c>
@@ -5941,7 +5857,7 @@
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A146" s="44"/>
+      <c r="A146" s="47"/>
       <c r="C146" t="s">
         <v>215</v>
       </c>
@@ -5951,7 +5867,7 @@
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" s="44"/>
+      <c r="A147" s="47"/>
       <c r="C147" t="s">
         <v>216</v>
       </c>
@@ -5961,7 +5877,7 @@
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" s="44"/>
+      <c r="A148" s="47"/>
       <c r="C148" t="s">
         <v>217</v>
       </c>
@@ -5974,7 +5890,7 @@
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149" s="44"/>
+      <c r="A149" s="47"/>
       <c r="C149" t="s">
         <v>218</v>
       </c>
@@ -5984,7 +5900,7 @@
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A150" s="44"/>
+      <c r="A150" s="47"/>
       <c r="C150" t="s">
         <v>219</v>
       </c>
@@ -5994,7 +5910,7 @@
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151" s="44"/>
+      <c r="A151" s="47"/>
       <c r="C151" t="s">
         <v>220</v>
       </c>
@@ -6004,7 +5920,7 @@
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A152" s="44"/>
+      <c r="A152" s="47"/>
       <c r="C152" t="s">
         <v>221</v>
       </c>
@@ -6014,7 +5930,7 @@
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153" s="44"/>
+      <c r="A153" s="47"/>
       <c r="C153" t="s">
         <v>222</v>
       </c>
@@ -6024,7 +5940,7 @@
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A154" s="44"/>
+      <c r="A154" s="47"/>
       <c r="C154" t="s">
         <v>223</v>
       </c>
@@ -6037,7 +5953,7 @@
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" s="44"/>
+      <c r="A155" s="47"/>
       <c r="C155" t="s">
         <v>296</v>
       </c>
@@ -6046,7 +5962,7 @@
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" s="44"/>
+      <c r="A156" s="47"/>
       <c r="C156" t="s">
         <v>229</v>
       </c>
@@ -6056,7 +5972,7 @@
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A157" s="44"/>
+      <c r="A157" s="47"/>
       <c r="C157" t="s">
         <v>232</v>
       </c>
@@ -6069,7 +5985,7 @@
       <c r="A158" s="24"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159" s="45" t="s">
+      <c r="A159" s="44" t="s">
         <v>538</v>
       </c>
       <c r="B159" t="s">
@@ -6081,7 +5997,7 @@
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A160" s="45"/>
+      <c r="A160" s="44"/>
       <c r="B160" t="s">
         <v>50</v>
       </c>
@@ -6094,7 +6010,7 @@
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A161" s="45"/>
+      <c r="A161" s="44"/>
       <c r="B161" t="s">
         <v>48</v>
       </c>
@@ -6104,7 +6020,7 @@
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A162" s="45"/>
+      <c r="A162" s="44"/>
       <c r="B162" t="s">
         <v>76</v>
       </c>
@@ -6114,7 +6030,7 @@
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A163" s="45"/>
+      <c r="A163" s="44"/>
       <c r="B163" t="s">
         <v>532</v>
       </c>
@@ -6126,7 +6042,7 @@
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A164" s="45"/>
+      <c r="A164" s="44"/>
       <c r="B164" t="s">
         <v>241</v>
       </c>
@@ -6136,7 +6052,7 @@
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A165" s="45"/>
+      <c r="A165" s="44"/>
       <c r="B165" t="s">
         <v>242</v>
       </c>
@@ -6146,7 +6062,7 @@
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A166" s="45"/>
+      <c r="A166" s="44"/>
       <c r="B166" t="s">
         <v>537</v>
       </c>
@@ -6156,7 +6072,7 @@
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A167" s="45"/>
+      <c r="A167" s="44"/>
       <c r="B167" t="s">
         <v>239</v>
       </c>
@@ -6165,7 +6081,7 @@
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A168" s="45"/>
+      <c r="A168" s="44"/>
       <c r="B168" t="s">
         <v>228</v>
       </c>
@@ -6178,7 +6094,7 @@
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A169" s="45"/>
+      <c r="A169" s="44"/>
       <c r="B169" t="s">
         <v>39</v>
       </c>
@@ -6188,7 +6104,7 @@
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A170" s="45"/>
+      <c r="A170" s="44"/>
       <c r="B170" t="s">
         <v>301</v>
       </c>
@@ -6198,7 +6114,7 @@
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A171" s="45"/>
+      <c r="A171" s="44"/>
       <c r="B171" t="s">
         <v>230</v>
       </c>
@@ -6208,7 +6124,7 @@
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A172" s="45"/>
+      <c r="A172" s="44"/>
       <c r="B172" t="s">
         <v>231</v>
       </c>
@@ -6218,7 +6134,7 @@
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A173" s="45"/>
+      <c r="A173" s="44"/>
       <c r="B173" t="s">
         <v>243</v>
       </c>
@@ -6228,7 +6144,7 @@
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A174" s="45"/>
+      <c r="A174" s="44"/>
       <c r="B174" t="s">
         <v>236</v>
       </c>
@@ -6238,7 +6154,7 @@
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A175" s="45"/>
+      <c r="A175" s="44"/>
       <c r="B175" t="s">
         <v>234</v>
       </c>
@@ -6247,7 +6163,7 @@
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A176" s="45"/>
+      <c r="A176" s="44"/>
       <c r="B176" t="s">
         <v>534</v>
       </c>
@@ -6257,7 +6173,7 @@
       </c>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A177" s="45"/>
+      <c r="A177" s="44"/>
       <c r="B177" t="s">
         <v>536</v>
       </c>
@@ -6267,7 +6183,7 @@
       </c>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A178" s="45"/>
+      <c r="A178" s="44"/>
       <c r="B178" t="s">
         <v>244</v>
       </c>
@@ -6280,7 +6196,7 @@
       </c>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A179" s="45"/>
+      <c r="A179" s="44"/>
       <c r="B179" t="s">
         <v>233</v>
       </c>
@@ -6292,7 +6208,7 @@
       </c>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A180" s="45"/>
+      <c r="A180" s="44"/>
       <c r="B180" t="s">
         <v>235</v>
       </c>
@@ -6302,7 +6218,7 @@
       </c>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A181" s="45"/>
+      <c r="A181" s="44"/>
       <c r="B181" t="s">
         <v>294</v>
       </c>
@@ -6314,7 +6230,7 @@
       </c>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A182" s="45"/>
+      <c r="A182" s="44"/>
       <c r="B182" t="s">
         <v>535</v>
       </c>
@@ -6323,7 +6239,7 @@
       </c>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A183" s="45"/>
+      <c r="A183" s="44"/>
       <c r="B183" t="s">
         <v>511</v>
       </c>
@@ -6332,7 +6248,7 @@
       </c>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A184" s="45"/>
+      <c r="A184" s="44"/>
       <c r="B184" t="s">
         <v>237</v>
       </c>
@@ -6342,7 +6258,7 @@
       </c>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A185" s="45"/>
+      <c r="A185" s="44"/>
       <c r="B185" t="s">
         <v>512</v>
       </c>
@@ -6352,7 +6268,7 @@
       </c>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A186" s="45"/>
+      <c r="A186" s="44"/>
       <c r="B186" t="s">
         <v>516</v>
       </c>
@@ -6386,7 +6302,7 @@
       </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A187" s="45"/>
+      <c r="A187" s="44"/>
       <c r="B187" t="s">
         <v>517</v>
       </c>
@@ -6426,7 +6342,7 @@
       </c>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A188" s="45"/>
+      <c r="A188" s="44"/>
       <c r="B188" t="s">
         <v>515</v>
       </c>
@@ -6463,7 +6379,7 @@
       </c>
     </row>
     <row r="189" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="45"/>
+      <c r="A189" s="44"/>
       <c r="B189" t="s">
         <v>513</v>
       </c>
@@ -6500,7 +6416,7 @@
       </c>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A190" s="45"/>
+      <c r="A190" s="44"/>
       <c r="B190" t="s">
         <v>514</v>
       </c>
@@ -6537,7 +6453,7 @@
       </c>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A191" s="45"/>
+      <c r="A191" s="44"/>
       <c r="B191" t="s">
         <v>297</v>
       </c>
@@ -6574,7 +6490,7 @@
       </c>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A192" s="45"/>
+      <c r="A192" s="44"/>
       <c r="B192" t="s">
         <v>298</v>
       </c>
@@ -6611,7 +6527,7 @@
       </c>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A193" s="45"/>
+      <c r="A193" s="44"/>
       <c r="B193" t="s">
         <v>299</v>
       </c>
@@ -6644,7 +6560,7 @@
       </c>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A194" s="45"/>
+      <c r="A194" s="44"/>
       <c r="B194" t="s">
         <v>300</v>
       </c>
@@ -6654,7 +6570,7 @@
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A195" s="45"/>
+      <c r="A195" s="44"/>
       <c r="B195" t="s">
         <v>301</v>
       </c>
@@ -6664,14 +6580,14 @@
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A196" s="45"/>
+      <c r="A196" s="44"/>
       <c r="B196" t="s">
         <v>302</v>
       </c>
       <c r="D196" s="1"/>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A197" s="45"/>
+      <c r="A197" s="44"/>
       <c r="B197" t="s">
         <v>303</v>
       </c>
@@ -6681,7 +6597,7 @@
       </c>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A198" s="45"/>
+      <c r="A198" s="44"/>
       <c r="B198" t="s">
         <v>249</v>
       </c>
@@ -6690,7 +6606,7 @@
       </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A199" s="45"/>
+      <c r="A199" s="44"/>
       <c r="C199" t="s">
         <v>250</v>
       </c>
@@ -6699,7 +6615,7 @@
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A200" s="45"/>
+      <c r="A200" s="44"/>
       <c r="C200" t="s">
         <v>251</v>
       </c>
@@ -6709,7 +6625,7 @@
       </c>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A201" s="45"/>
+      <c r="A201" s="44"/>
       <c r="C201" t="s">
         <v>252</v>
       </c>
@@ -6718,10 +6634,10 @@
       </c>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A202" s="45"/>
+      <c r="A202" s="44"/>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A203" s="45"/>
+      <c r="A203" s="44"/>
       <c r="B203" t="s">
         <v>254</v>
       </c>
@@ -6730,7 +6646,7 @@
       </c>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A204" s="45"/>
+      <c r="A204" s="44"/>
       <c r="B204" t="s">
         <v>278</v>
       </c>
@@ -6740,7 +6656,7 @@
       </c>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A205" s="45"/>
+      <c r="A205" s="44"/>
       <c r="B205" t="s">
         <v>255</v>
       </c>
@@ -6749,7 +6665,7 @@
       </c>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A206" s="45"/>
+      <c r="A206" s="44"/>
       <c r="B206" t="s">
         <v>256</v>
       </c>
@@ -6759,7 +6675,7 @@
       </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A207" s="45"/>
+      <c r="A207" s="44"/>
       <c r="B207" t="s">
         <v>257</v>
       </c>
@@ -6772,7 +6688,7 @@
       </c>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A208" s="45"/>
+      <c r="A208" s="44"/>
       <c r="B208" t="s">
         <v>258</v>
       </c>
@@ -6785,7 +6701,7 @@
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A209" s="45"/>
+      <c r="A209" s="44"/>
       <c r="B209" t="s">
         <v>259</v>
       </c>
@@ -6798,7 +6714,7 @@
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A210" s="45"/>
+      <c r="A210" s="44"/>
       <c r="B210" t="s">
         <v>260</v>
       </c>
@@ -6814,7 +6730,7 @@
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A211" s="45"/>
+      <c r="A211" s="44"/>
       <c r="B211" t="s">
         <v>261</v>
       </c>
@@ -6824,7 +6740,7 @@
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A212" s="45"/>
+      <c r="A212" s="44"/>
       <c r="C212" t="s">
         <v>262</v>
       </c>
@@ -6834,7 +6750,7 @@
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A213" s="45"/>
+      <c r="A213" s="44"/>
       <c r="C213" t="s">
         <v>263</v>
       </c>
@@ -6844,7 +6760,7 @@
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A214" s="45"/>
+      <c r="A214" s="44"/>
       <c r="C214" t="s">
         <v>264</v>
       </c>
@@ -6860,24 +6776,24 @@
       <c r="A215" s="29"/>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A216" s="45" t="s">
-        <v>539</v>
+      <c r="A216" s="44" t="s">
+        <v>776</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A217" s="45"/>
+      <c r="A217" s="44"/>
       <c r="B217" t="s">
+        <v>577</v>
+      </c>
+      <c r="C217" t="s">
         <v>578</v>
       </c>
-      <c r="C217" t="s">
-        <v>579</v>
-      </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A218" s="45"/>
+      <c r="A218" s="44"/>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A219" s="45"/>
+      <c r="A219" s="44"/>
       <c r="B219" t="s">
         <v>533</v>
       </c>
@@ -6886,9 +6802,9 @@
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A220" s="45"/>
+      <c r="A220" s="44"/>
       <c r="B220" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C220" s="34"/>
       <c r="D220">
@@ -6925,9 +6841,9 @@
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A221" s="45"/>
+      <c r="A221" s="44"/>
       <c r="B221" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C221" s="34"/>
       <c r="D221">
@@ -6964,9 +6880,9 @@
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A222" s="45"/>
+      <c r="A222" s="44"/>
       <c r="B222" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C222" s="34"/>
       <c r="D222">
@@ -7003,12 +6919,12 @@
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A223" s="45"/>
+      <c r="A223" s="44"/>
       <c r="B223" t="s">
         <v>328</v>
       </c>
       <c r="C223" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D223">
         <f>100</f>
@@ -7044,12 +6960,12 @@
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A224" s="45"/>
+      <c r="A224" s="44"/>
       <c r="B224" t="s">
+        <v>550</v>
+      </c>
+      <c r="C224" t="s">
         <v>551</v>
-      </c>
-      <c r="C224" t="s">
-        <v>552</v>
       </c>
       <c r="D224">
         <f>D7</f>
@@ -7085,12 +7001,12 @@
       </c>
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A225" s="45"/>
+      <c r="A225" s="44"/>
       <c r="B225" t="s">
+        <v>552</v>
+      </c>
+      <c r="C225" t="s">
         <v>553</v>
-      </c>
-      <c r="C225" t="s">
-        <v>554</v>
       </c>
       <c r="D225">
         <f>D162</f>
@@ -7123,9 +7039,9 @@
       </c>
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A226" s="45"/>
+      <c r="A226" s="44"/>
       <c r="B226" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C226" s="34"/>
       <c r="D226">
@@ -7162,7 +7078,7 @@
       </c>
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A227" s="45"/>
+      <c r="A227" s="44"/>
       <c r="B227" t="s">
         <v>48</v>
       </c>
@@ -7200,7 +7116,7 @@
       </c>
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A228" s="45"/>
+      <c r="A228" s="44"/>
       <c r="B228" t="s">
         <v>39</v>
       </c>
@@ -7238,16 +7154,16 @@
       </c>
     </row>
     <row r="229" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A229" s="45"/>
+      <c r="A229" s="44"/>
       <c r="C229" s="34"/>
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A230" s="45"/>
+      <c r="A230" s="44"/>
       <c r="B230" t="s">
+        <v>559</v>
+      </c>
+      <c r="C230" s="34" t="s">
         <v>560</v>
-      </c>
-      <c r="C230" s="34" t="s">
-        <v>561</v>
       </c>
       <c r="D230">
         <v>40</v>
@@ -7279,12 +7195,12 @@
       </c>
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A231" s="45"/>
+      <c r="A231" s="44"/>
       <c r="B231" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C231" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D231">
         <f>D220*POWER(D222, 2)/(2*POWER(D223-D224-(D225*D226), 2))</f>
@@ -7292,12 +7208,12 @@
       </c>
     </row>
     <row r="232" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A232" s="45"/>
+      <c r="A232" s="44"/>
       <c r="B232" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C232" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D232" s="1">
         <f>(0.22*0.000001)*6</f>
@@ -7334,12 +7250,12 @@
       <c r="L232" s="1"/>
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A233" s="45"/>
+      <c r="A233" s="44"/>
       <c r="B233" t="s">
+        <v>555</v>
+      </c>
+      <c r="C233" s="34" t="s">
         <v>556</v>
-      </c>
-      <c r="C233" s="34" t="s">
-        <v>557</v>
       </c>
       <c r="D233">
         <f>POWER(D228/(PI()*D227), 2)/D232</f>
@@ -7375,12 +7291,12 @@
       </c>
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A234" s="45"/>
+      <c r="A234" s="44"/>
       <c r="B234" t="s">
+        <v>557</v>
+      </c>
+      <c r="C234" s="34" t="s">
         <v>558</v>
-      </c>
-      <c r="C234" s="34" t="s">
-        <v>559</v>
       </c>
       <c r="D234">
         <f>(POWER(D230, 2)-POWER(POWER(D230, 4) - POWER(PI()*POWER(D224, 2)*D232/(D221+D220), 2), 0.5))/((D232/2)*POWER(PI()*D224/(D221+D220), 2))</f>
@@ -7416,12 +7332,12 @@
       </c>
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A235" s="45"/>
+      <c r="A235" s="44"/>
       <c r="B235" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C235" s="34" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D235" s="1">
         <v>1.5E-5</v>
@@ -7456,12 +7372,12 @@
       </c>
     </row>
     <row r="236" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A236" s="45"/>
+      <c r="A236" s="44"/>
       <c r="B236" t="s">
+        <v>564</v>
+      </c>
+      <c r="C236" s="34" t="s">
         <v>565</v>
-      </c>
-      <c r="C236" s="34" t="s">
-        <v>566</v>
       </c>
       <c r="D236" t="b">
         <f>AND(D235&gt;D234, D235&lt;D233)</f>
@@ -7497,16 +7413,16 @@
       </c>
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A237" s="45"/>
+      <c r="A237" s="44"/>
       <c r="B237" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D237">
         <v>8.4999999999999995E-4</v>
       </c>
     </row>
     <row r="238" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A238" s="45"/>
+      <c r="A238" s="44"/>
       <c r="B238" t="s">
         <v>301</v>
       </c>
@@ -7516,12 +7432,12 @@
       </c>
     </row>
     <row r="239" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A239" s="45"/>
+      <c r="A239" s="44"/>
       <c r="B239" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C239" s="34" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D239">
         <f>POWER(D222/SQRT(3), 2)*D237</f>
@@ -7529,9 +7445,9 @@
       </c>
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A240" s="45"/>
+      <c r="A240" s="44"/>
       <c r="B240" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D240">
         <f>D220*D235/(D220+D235)</f>
@@ -7560,16 +7476,16 @@
       </c>
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A241" s="45"/>
+      <c r="A241" s="44"/>
       <c r="B241" s="36" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D241" s="1">
         <f>1/POWER(D240*D232, 0.5)</f>
         <v>357610.39006916573</v>
       </c>
       <c r="F241" s="5" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G241">
         <v>2.2000000000000001E-3</v>
@@ -7597,9 +7513,9 @@
       </c>
     </row>
     <row r="242" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A242" s="45"/>
+      <c r="A242" s="44"/>
       <c r="B242" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D242">
         <f>POWER(2*D238/D240, 0.5)</f>
@@ -7607,9 +7523,9 @@
       </c>
     </row>
     <row r="243" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A243" s="45"/>
+      <c r="A243" s="44"/>
       <c r="B243" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D243">
         <f>D242</f>
@@ -7617,9 +7533,9 @@
       </c>
     </row>
     <row r="244" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A244" s="45"/>
+      <c r="A244" s="44"/>
       <c r="B244" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D244" s="1">
         <f>SQRT(D238*2/D232)</f>
@@ -7627,9 +7543,9 @@
       </c>
     </row>
     <row r="245" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A245" s="45"/>
+      <c r="A245" s="44"/>
       <c r="B245" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D245" s="1">
         <f>D244+D7</f>
@@ -7637,9 +7553,9 @@
       </c>
     </row>
     <row r="246" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A246" s="45"/>
+      <c r="A246" s="44"/>
       <c r="B246" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D246" s="1">
         <f>D244</f>
@@ -7647,9 +7563,9 @@
       </c>
     </row>
     <row r="247" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A247" s="45"/>
+      <c r="A247" s="44"/>
       <c r="B247" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D247">
         <f>D219*D243</f>
@@ -7657,9 +7573,9 @@
       </c>
     </row>
     <row r="248" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A248" s="45"/>
+      <c r="A248" s="44"/>
       <c r="B248" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D248">
         <f>D219*D243</f>
@@ -7667,9 +7583,9 @@
       </c>
     </row>
     <row r="249" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A249" s="45"/>
+      <c r="A249" s="44"/>
       <c r="B249" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D249">
         <f>D219*D243</f>
@@ -7677,9 +7593,9 @@
       </c>
     </row>
     <row r="250" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A250" s="45"/>
+      <c r="A250" s="44"/>
       <c r="B250" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D250" s="1">
         <f>D219*D245</f>
@@ -7687,9 +7603,9 @@
       </c>
     </row>
     <row r="251" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A251" s="45"/>
+      <c r="A251" s="44"/>
       <c r="B251" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D251" s="1">
         <f>D219*D246</f>
@@ -7697,9 +7613,9 @@
       </c>
     </row>
     <row r="252" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A252" s="45"/>
+      <c r="A252" s="44"/>
       <c r="B252" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D252" s="1">
         <f>D219*D244</f>
@@ -7707,18 +7623,18 @@
       </c>
     </row>
     <row r="253" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A253" s="45"/>
+      <c r="A253" s="44"/>
       <c r="B253" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D253" s="1">
         <v>0.86</v>
       </c>
     </row>
     <row r="254" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A254" s="45"/>
+      <c r="A254" s="44"/>
       <c r="B254" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D254" s="1">
         <f>0.86</f>
@@ -7726,12 +7642,12 @@
       </c>
     </row>
     <row r="255" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A255" s="45"/>
+      <c r="A255" s="44"/>
       <c r="B255" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C255" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D255" s="1">
         <f>D238*16000/4</f>
@@ -7739,12 +7655,12 @@
       </c>
     </row>
     <row r="256" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A256" s="45"/>
+      <c r="A256" s="44"/>
       <c r="B256" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C256" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D256" s="1">
         <f>D255</f>
@@ -7752,27 +7668,27 @@
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A257" s="45"/>
+      <c r="A257" s="44"/>
       <c r="B257" t="s">
+        <v>604</v>
+      </c>
+      <c r="C257" t="s">
         <v>605</v>
-      </c>
-      <c r="C257" t="s">
-        <v>606</v>
       </c>
       <c r="D257">
         <v>0.5</v>
       </c>
       <c r="E257" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A258" s="45"/>
+      <c r="A258" s="44"/>
       <c r="B258" s="43" t="s">
+        <v>606</v>
+      </c>
+      <c r="C258" s="43" t="s">
         <v>607</v>
-      </c>
-      <c r="C258" s="43" t="s">
-        <v>608</v>
       </c>
       <c r="D258" s="43">
         <f>D238*2/POWER(D257, 2)</f>
@@ -7780,46 +7696,46 @@
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A259" s="45"/>
+      <c r="A259" s="44"/>
       <c r="C259" s="34"/>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A260" s="45"/>
+      <c r="A260" s="44"/>
       <c r="C260" s="34"/>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A261" s="45"/>
+      <c r="A261" s="44"/>
       <c r="C261" s="34"/>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A262" s="45"/>
+      <c r="A262" s="44"/>
       <c r="C262" s="34"/>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A263" s="45"/>
+      <c r="A263" s="44"/>
       <c r="C263" s="34"/>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A264" s="45"/>
+      <c r="A264" s="44"/>
       <c r="C264" s="34"/>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A265" s="45"/>
+      <c r="A265" s="44"/>
       <c r="C265" s="34"/>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A266" s="45"/>
+      <c r="A266" s="44"/>
       <c r="C266" s="34"/>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A267" s="45"/>
+      <c r="A267" s="44"/>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="37"/>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A269" s="45" t="s">
-        <v>610</v>
+      <c r="A269" s="44" t="s">
+        <v>609</v>
       </c>
       <c r="C269" t="s">
         <v>265</v>
@@ -7830,7 +7746,7 @@
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A270" s="45"/>
+      <c r="A270" s="44"/>
       <c r="C270" t="s">
         <v>266</v>
       </c>
@@ -7840,7 +7756,7 @@
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A271" s="45"/>
+      <c r="A271" s="44"/>
       <c r="C271" t="s">
         <v>267</v>
       </c>
@@ -7850,7 +7766,7 @@
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A272" s="45"/>
+      <c r="A272" s="44"/>
       <c r="C272" t="s">
         <v>268</v>
       </c>
@@ -7860,7 +7776,7 @@
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A273" s="45"/>
+      <c r="A273" s="44"/>
       <c r="C273" t="s">
         <v>269</v>
       </c>
@@ -7870,7 +7786,7 @@
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A274" s="45"/>
+      <c r="A274" s="44"/>
       <c r="C274" t="s">
         <v>270</v>
       </c>
@@ -7880,7 +7796,7 @@
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A275" s="45"/>
+      <c r="A275" s="44"/>
       <c r="C275" t="s">
         <v>271</v>
       </c>
@@ -7890,7 +7806,7 @@
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A276" s="45"/>
+      <c r="A276" s="44"/>
       <c r="C276" t="s">
         <v>272</v>
       </c>
@@ -7900,7 +7816,7 @@
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A277" s="45"/>
+      <c r="A277" s="44"/>
       <c r="B277" t="s">
         <v>273</v>
       </c>
@@ -7909,7 +7825,7 @@
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A278" s="45"/>
+      <c r="A278" s="44"/>
       <c r="B278" t="s">
         <v>275</v>
       </c>
@@ -7919,7 +7835,7 @@
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A279" s="45"/>
+      <c r="A279" s="44"/>
       <c r="C279" t="s">
         <v>276</v>
       </c>
@@ -7929,10 +7845,10 @@
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A280" s="45"/>
+      <c r="A280" s="44"/>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A281" s="45"/>
+      <c r="A281" s="44"/>
       <c r="B281" t="s">
         <v>277</v>
       </c>
@@ -7942,7 +7858,7 @@
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A282" s="45"/>
+      <c r="A282" s="44"/>
       <c r="B282" t="s">
         <v>349</v>
       </c>
@@ -7952,7 +7868,7 @@
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A283" s="45"/>
+      <c r="A283" s="44"/>
       <c r="B283" t="s">
         <v>285</v>
       </c>
@@ -7962,7 +7878,7 @@
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A284" s="45"/>
+      <c r="A284" s="44"/>
       <c r="B284" t="s">
         <v>284</v>
       </c>
@@ -7971,10 +7887,10 @@
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A285" s="45"/>
+      <c r="A285" s="44"/>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A286" s="45"/>
+      <c r="A286" s="44"/>
       <c r="B286" t="s">
         <v>282</v>
       </c>
@@ -7984,7 +7900,7 @@
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A287" s="45"/>
+      <c r="A287" s="44"/>
       <c r="B287" t="s">
         <v>281</v>
       </c>
@@ -7996,7 +7912,7 @@
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A288" s="45"/>
+      <c r="A288" s="44"/>
       <c r="C288" t="s">
         <v>279</v>
       </c>
@@ -8006,7 +7922,7 @@
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A289" s="45"/>
+      <c r="A289" s="44"/>
       <c r="C289" t="s">
         <v>283</v>
       </c>
@@ -8016,14 +7932,14 @@
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A290" s="45"/>
+      <c r="A290" s="44"/>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A291" s="44" t="s">
-        <v>609</v>
+      <c r="A291" s="47" t="s">
+        <v>608</v>
       </c>
       <c r="B291" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D291" s="1">
         <f>MAX(D321, 200)</f>
@@ -8031,27 +7947,27 @@
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A292" s="44"/>
+      <c r="A292" s="47"/>
       <c r="B292" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D292">
         <v>500000</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A293" s="44"/>
+      <c r="A293" s="47"/>
       <c r="B293" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D293">
         <v>6800</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A294" s="44"/>
+      <c r="A294" s="47"/>
       <c r="B294" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D294">
         <f>D292+D293</f>
@@ -8059,9 +7975,9 @@
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A295" s="44"/>
+      <c r="A295" s="47"/>
       <c r="B295" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D295" s="1">
         <f>D291/D294</f>
@@ -8069,9 +7985,9 @@
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A296" s="44"/>
+      <c r="A296" s="47"/>
       <c r="B296" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D296" s="1">
         <f>POWER(D295, 2)*D292</f>
@@ -8079,9 +7995,9 @@
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A297" s="44"/>
+      <c r="A297" s="47"/>
       <c r="B297" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D297" s="1">
         <f>POWER(D295, 2)*D293</f>
@@ -8089,9 +8005,9 @@
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A298" s="44"/>
+      <c r="A298" s="47"/>
       <c r="B298" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D298" s="1">
         <f>D296+D297</f>
@@ -8099,18 +8015,18 @@
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A299" s="44"/>
+      <c r="A299" s="47"/>
       <c r="C299" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D299">
         <v>2.7</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A300" s="44"/>
+      <c r="A300" s="47"/>
       <c r="C300" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D300" s="1">
         <f>D291/D299</f>
@@ -8118,9 +8034,9 @@
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A301" s="44"/>
+      <c r="A301" s="47"/>
       <c r="C301" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D301" s="1">
         <f>D294/D293</f>
@@ -8128,9 +8044,9 @@
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A302" s="44"/>
+      <c r="A302" s="47"/>
       <c r="C302" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D302" s="1" t="b">
         <f>MAX(D300, D301)/MIN(D300,D301)&lt;1.04</f>
@@ -8138,11 +8054,11 @@
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A303" s="44"/>
+      <c r="A303" s="47"/>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A304" s="44" t="s">
-        <v>586</v>
+      <c r="A304" s="47" t="s">
+        <v>585</v>
       </c>
       <c r="C304" t="s">
         <v>286</v>
@@ -8152,7 +8068,7 @@
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A305" s="44"/>
+      <c r="A305" s="47"/>
       <c r="B305" t="s">
         <v>38</v>
       </c>
@@ -8162,7 +8078,7 @@
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A306" s="44"/>
+      <c r="A306" s="47"/>
       <c r="B306" t="s">
         <v>287</v>
       </c>
@@ -8174,7 +8090,7 @@
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A307" s="44"/>
+      <c r="A307" s="47"/>
       <c r="C307" t="s">
         <v>290</v>
       </c>
@@ -8184,7 +8100,7 @@
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A308" s="44"/>
+      <c r="A308" s="47"/>
       <c r="B308" t="s">
         <v>291</v>
       </c>
@@ -8197,7 +8113,7 @@
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A309" s="44"/>
+      <c r="A309" s="47"/>
       <c r="C309" t="s">
         <v>289</v>
       </c>
@@ -8206,7 +8122,7 @@
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A310" s="44"/>
+      <c r="A310" s="47"/>
       <c r="B310" t="s">
         <v>288</v>
       </c>
@@ -8215,7 +8131,7 @@
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A311" s="44"/>
+      <c r="A311" s="47"/>
       <c r="B311" t="s">
         <v>292</v>
       </c>
@@ -8227,7 +8143,7 @@
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A312" s="44"/>
+      <c r="A312" s="47"/>
       <c r="B312" t="s">
         <v>293</v>
       </c>
@@ -8240,7 +8156,7 @@
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A313" s="44"/>
+      <c r="A313" s="47"/>
       <c r="B313" t="s">
         <v>350</v>
       </c>
@@ -8257,7 +8173,7 @@
       <c r="E314" s="9"/>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A315" s="45" t="s">
+      <c r="A315" s="44" t="s">
         <v>304</v>
       </c>
       <c r="B315" t="s">
@@ -8272,7 +8188,7 @@
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A316" s="45"/>
+      <c r="A316" s="44"/>
       <c r="B316" t="s">
         <v>41</v>
       </c>
@@ -8285,7 +8201,7 @@
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A317" s="45"/>
+      <c r="A317" s="44"/>
       <c r="B317" t="s">
         <v>39</v>
       </c>
@@ -8294,7 +8210,7 @@
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A318" s="45"/>
+      <c r="A318" s="44"/>
       <c r="B318" t="s">
         <v>306</v>
       </c>
@@ -8306,7 +8222,7 @@
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A319" s="45"/>
+      <c r="A319" s="44"/>
       <c r="B319" t="s">
         <v>305</v>
       </c>
@@ -8316,7 +8232,7 @@
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A320" s="45"/>
+      <c r="A320" s="44"/>
       <c r="B320" t="s">
         <v>308</v>
       </c>
@@ -8329,7 +8245,7 @@
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A321" s="45"/>
+      <c r="A321" s="44"/>
       <c r="B321" t="s">
         <v>309</v>
       </c>
@@ -8342,7 +8258,7 @@
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A322" s="45"/>
+      <c r="A322" s="44"/>
       <c r="B322" t="s">
         <v>327</v>
       </c>
@@ -8354,7 +8270,7 @@
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A323" s="45"/>
+      <c r="A323" s="44"/>
       <c r="C323" t="s">
         <v>345</v>
       </c>
@@ -8364,7 +8280,7 @@
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A324" s="45"/>
+      <c r="A324" s="44"/>
       <c r="B324" t="s">
         <v>310</v>
       </c>
@@ -8373,7 +8289,7 @@
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A325" s="45"/>
+      <c r="A325" s="44"/>
       <c r="B325" t="s">
         <v>311</v>
       </c>
@@ -8382,7 +8298,7 @@
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A326" s="45"/>
+      <c r="A326" s="44"/>
       <c r="B326" t="s">
         <v>312</v>
       </c>
@@ -8397,7 +8313,7 @@
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A327" s="45"/>
+      <c r="A327" s="44"/>
       <c r="B327" t="s">
         <v>314</v>
       </c>
@@ -8410,7 +8326,7 @@
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A328" s="45"/>
+      <c r="A328" s="44"/>
       <c r="B328" t="s">
         <v>316</v>
       </c>
@@ -8425,7 +8341,7 @@
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A329" s="45"/>
+      <c r="A329" s="44"/>
       <c r="B329" t="s">
         <v>317</v>
       </c>
@@ -8437,7 +8353,7 @@
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A330" s="45"/>
+      <c r="A330" s="44"/>
       <c r="B330" t="s">
         <v>230</v>
       </c>
@@ -8453,7 +8369,7 @@
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A331" s="45"/>
+      <c r="A331" s="44"/>
       <c r="B331" t="s">
         <v>323</v>
       </c>
@@ -8469,7 +8385,7 @@
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A332" s="45"/>
+      <c r="A332" s="44"/>
       <c r="B332" t="s">
         <v>324</v>
       </c>
@@ -8485,7 +8401,7 @@
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A333" s="45"/>
+      <c r="A333" s="44"/>
       <c r="C333" t="s">
         <v>318</v>
       </c>
@@ -8498,7 +8414,7 @@
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A334" s="45"/>
+      <c r="A334" s="44"/>
       <c r="C334" t="s">
         <v>320</v>
       </c>
@@ -8510,7 +8426,7 @@
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A335" s="45"/>
+      <c r="A335" s="44"/>
       <c r="C335" t="s">
         <v>321</v>
       </c>
@@ -8523,7 +8439,7 @@
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A336" s="45"/>
+      <c r="A336" s="44"/>
       <c r="C336" t="s">
         <v>319</v>
       </c>
@@ -8533,7 +8449,7 @@
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A337" s="45"/>
+      <c r="A337" s="44"/>
       <c r="B337" t="s">
         <v>347</v>
       </c>
@@ -8549,7 +8465,7 @@
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A338" s="45"/>
+      <c r="A338" s="44"/>
       <c r="B338" t="s">
         <v>328</v>
       </c>
@@ -8562,7 +8478,7 @@
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A339" s="45"/>
+      <c r="A339" s="44"/>
       <c r="B339" t="s">
         <v>329</v>
       </c>
@@ -8575,7 +8491,7 @@
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A340" s="45"/>
+      <c r="A340" s="44"/>
       <c r="B340" t="s">
         <v>322</v>
       </c>
@@ -8588,7 +8504,7 @@
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A341" s="45"/>
+      <c r="A341" s="44"/>
       <c r="B341" t="s">
         <v>342</v>
       </c>
@@ -8601,7 +8517,7 @@
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A342" s="45"/>
+      <c r="A342" s="44"/>
       <c r="B342" t="s">
         <v>331</v>
       </c>
@@ -8613,7 +8529,7 @@
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A343" s="45"/>
+      <c r="A343" s="44"/>
       <c r="B343" t="s">
         <v>334</v>
       </c>
@@ -8625,7 +8541,7 @@
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A344" s="45"/>
+      <c r="A344" s="44"/>
       <c r="B344" t="s">
         <v>335</v>
       </c>
@@ -8640,7 +8556,7 @@
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A345" s="45"/>
+      <c r="A345" s="44"/>
       <c r="B345" t="s">
         <v>332</v>
       </c>
@@ -8656,7 +8572,7 @@
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A346" s="45"/>
+      <c r="A346" s="44"/>
       <c r="C346" t="s">
         <v>346</v>
       </c>
@@ -8669,7 +8585,7 @@
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A347" s="45"/>
+      <c r="A347" s="44"/>
       <c r="B347" t="s">
         <v>337</v>
       </c>
@@ -8681,7 +8597,7 @@
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A348" s="45"/>
+      <c r="A348" s="44"/>
       <c r="C348" t="s">
         <v>339</v>
       </c>
@@ -8691,7 +8607,7 @@
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A349" s="45"/>
+      <c r="A349" s="44"/>
       <c r="C349" t="s">
         <v>338</v>
       </c>
@@ -8701,7 +8617,7 @@
       </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A350" s="45"/>
+      <c r="A350" s="44"/>
       <c r="B350" t="s">
         <v>340</v>
       </c>
@@ -8720,8 +8636,8 @@
       <c r="A351" s="38"/>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A352" s="44" t="s">
-        <v>702</v>
+      <c r="A352" s="47" t="s">
+        <v>701</v>
       </c>
       <c r="B352" t="s">
         <v>342</v>
@@ -8735,21 +8651,21 @@
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A353" s="44"/>
+      <c r="A353" s="47"/>
       <c r="C353" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D353">
         <v>0.9</v>
       </c>
       <c r="E353" s="39" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A354" s="47"/>
+      <c r="C354" t="s">
         <v>704</v>
-      </c>
-    </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A354" s="44"/>
-      <c r="C354" t="s">
-        <v>705</v>
       </c>
       <c r="D354">
         <v>0.15</v>
@@ -8759,9 +8675,9 @@
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A355" s="44"/>
+      <c r="A355" s="47"/>
       <c r="C355" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D355" s="1">
         <v>1.4999999999999999E-4</v>
@@ -8771,12 +8687,12 @@
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A356" s="44"/>
+      <c r="A356" s="47"/>
       <c r="B356" t="s">
+        <v>707</v>
+      </c>
+      <c r="C356" t="s">
         <v>708</v>
-      </c>
-      <c r="C356" t="s">
-        <v>709</v>
       </c>
       <c r="D356">
         <f>D354/(1000*D353*D355)</f>
@@ -8785,12 +8701,12 @@
       <c r="E356" s="40"/>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A357" s="44"/>
+      <c r="A357" s="47"/>
       <c r="B357" t="s">
+        <v>709</v>
+      </c>
+      <c r="C357" t="s">
         <v>710</v>
-      </c>
-      <c r="C357" t="s">
-        <v>711</v>
       </c>
       <c r="D357">
         <f>3.5+0.5</f>
@@ -8799,12 +8715,12 @@
       <c r="E357" s="40"/>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A358" s="44"/>
+      <c r="A358" s="47"/>
       <c r="B358" t="s">
+        <v>711</v>
+      </c>
+      <c r="C358" t="s">
         <v>712</v>
-      </c>
-      <c r="C358" t="s">
-        <v>713</v>
       </c>
       <c r="D358">
         <v>6.6665999999999999</v>
@@ -8812,9 +8728,9 @@
       <c r="E358" s="39"/>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A359" s="44"/>
+      <c r="A359" s="47"/>
       <c r="C359" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D359">
         <f>D356+D357+D358</f>
@@ -8823,12 +8739,12 @@
       <c r="E359" s="39"/>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A360" s="44"/>
+      <c r="A360" s="47"/>
       <c r="B360" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C360" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D360" s="1">
         <f>D359*D352</f>
@@ -8837,9 +8753,9 @@
       <c r="E360" s="39"/>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A361" s="44"/>
+      <c r="A361" s="47"/>
       <c r="C361" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D361">
         <v>35</v>
@@ -8847,9 +8763,9 @@
       <c r="E361" s="39"/>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A362" s="44"/>
+      <c r="A362" s="47"/>
       <c r="C362" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D362" s="1">
         <f>D361+D360</f>
@@ -8858,9 +8774,9 @@
       <c r="E362" s="39"/>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A363" s="44"/>
+      <c r="A363" s="47"/>
       <c r="C363" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D363">
         <v>150</v>
@@ -8868,9 +8784,9 @@
       <c r="E363" s="39"/>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A364" s="44"/>
+      <c r="A364" s="47"/>
       <c r="C364" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D364" t="b">
         <f>D362&lt;D363/D4</f>
@@ -8878,21 +8794,21 @@
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A365" s="44" t="s">
-        <v>720</v>
+      <c r="A365" s="47" t="s">
+        <v>719</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A366" s="44"/>
+      <c r="A366" s="47"/>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A367" s="44"/>
+      <c r="A367" s="47"/>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A368" s="44"/>
+      <c r="A368" s="47"/>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A369" s="45" t="s">
+      <c r="A369" s="44" t="s">
         <v>351</v>
       </c>
       <c r="B369" t="s">
@@ -8907,7 +8823,7 @@
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A370" s="45"/>
+      <c r="A370" s="44"/>
       <c r="B370" t="s">
         <v>48</v>
       </c>
@@ -8917,7 +8833,7 @@
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A371" s="45"/>
+      <c r="A371" s="44"/>
       <c r="B371" t="s">
         <v>241</v>
       </c>
@@ -8927,7 +8843,7 @@
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A372" s="45"/>
+      <c r="A372" s="44"/>
       <c r="C372" t="s">
         <v>355</v>
       </c>
@@ -8936,7 +8852,7 @@
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A373" s="45"/>
+      <c r="A373" s="44"/>
       <c r="C373" t="s">
         <v>357</v>
       </c>
@@ -8946,7 +8862,7 @@
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A374" s="45"/>
+      <c r="A374" s="44"/>
       <c r="B374" t="s">
         <v>352</v>
       </c>
@@ -8958,7 +8874,7 @@
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A375" s="45"/>
+      <c r="A375" s="44"/>
       <c r="B375" t="s">
         <v>354</v>
       </c>
@@ -8971,7 +8887,7 @@
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A376" s="45"/>
+      <c r="A376" s="44"/>
       <c r="B376" t="s">
         <v>404</v>
       </c>
@@ -8984,7 +8900,7 @@
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A377" s="45"/>
+      <c r="A377" s="44"/>
       <c r="B377" t="s">
         <v>359</v>
       </c>
@@ -8997,7 +8913,7 @@
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A378" s="45"/>
+      <c r="A378" s="44"/>
       <c r="B378" t="s">
         <v>360</v>
       </c>
@@ -9010,7 +8926,7 @@
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A379" s="45"/>
+      <c r="A379" s="44"/>
       <c r="B379" t="s">
         <v>361</v>
       </c>
@@ -9023,7 +8939,7 @@
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A380" s="45"/>
+      <c r="A380" s="44"/>
       <c r="C380" t="s">
         <v>363</v>
       </c>
@@ -9033,7 +8949,7 @@
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A381" s="45"/>
+      <c r="A381" s="44"/>
       <c r="B381" t="s">
         <v>394</v>
       </c>
@@ -9045,7 +8961,7 @@
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A382" s="45"/>
+      <c r="A382" s="44"/>
       <c r="B382" t="s">
         <v>368</v>
       </c>
@@ -9057,7 +8973,7 @@
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A383" s="45"/>
+      <c r="A383" s="44"/>
       <c r="B383" t="s">
         <v>369</v>
       </c>
@@ -9069,7 +8985,7 @@
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A384" s="45"/>
+      <c r="A384" s="44"/>
       <c r="B384" t="s">
         <v>372</v>
       </c>
@@ -9084,7 +9000,7 @@
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A385" s="45"/>
+      <c r="A385" s="44"/>
       <c r="B385" t="s">
         <v>373</v>
       </c>
@@ -9099,7 +9015,7 @@
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A386" s="45"/>
+      <c r="A386" s="44"/>
       <c r="B386" t="s">
         <v>375</v>
       </c>
@@ -9115,7 +9031,7 @@
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A387" s="45"/>
+      <c r="A387" s="44"/>
       <c r="B387" s="27" t="s">
         <v>379</v>
       </c>
@@ -9130,7 +9046,7 @@
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A388" s="45"/>
+      <c r="A388" s="44"/>
       <c r="C388" t="s">
         <v>382</v>
       </c>
@@ -9140,7 +9056,7 @@
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A389" s="45"/>
+      <c r="A389" s="44"/>
       <c r="B389" t="s">
         <v>397</v>
       </c>
@@ -9153,7 +9069,7 @@
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A390" s="45"/>
+      <c r="A390" s="44"/>
       <c r="B390" t="s">
         <v>398</v>
       </c>
@@ -9163,7 +9079,7 @@
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A391" s="45"/>
+      <c r="A391" s="44"/>
       <c r="B391" t="s">
         <v>364</v>
       </c>
@@ -9172,7 +9088,7 @@
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A392" s="45"/>
+      <c r="A392" s="44"/>
       <c r="B392" t="s">
         <v>366</v>
       </c>
@@ -9182,7 +9098,7 @@
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A393" s="45"/>
+      <c r="A393" s="44"/>
       <c r="B393" t="s">
         <v>365</v>
       </c>
@@ -9194,7 +9110,7 @@
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A394" s="45"/>
+      <c r="A394" s="44"/>
       <c r="B394" t="s">
         <v>399</v>
       </c>
@@ -9207,7 +9123,7 @@
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A395" s="45"/>
+      <c r="A395" s="44"/>
       <c r="C395" t="s">
         <v>415</v>
       </c>
@@ -9216,7 +9132,7 @@
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A396" s="45"/>
+      <c r="A396" s="44"/>
       <c r="B396" t="s">
         <v>416</v>
       </c>
@@ -9226,7 +9142,7 @@
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A397" s="45"/>
+      <c r="A397" s="44"/>
       <c r="B397" t="s">
         <v>417</v>
       </c>
@@ -9236,7 +9152,7 @@
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A398" s="45"/>
+      <c r="A398" s="44"/>
       <c r="B398" t="s">
         <v>418</v>
       </c>
@@ -9246,7 +9162,7 @@
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A399" s="45"/>
+      <c r="A399" s="44"/>
       <c r="B399" t="s">
         <v>419</v>
       </c>
@@ -9256,7 +9172,7 @@
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A400" s="45"/>
+      <c r="A400" s="44"/>
       <c r="B400" t="s">
         <v>413</v>
       </c>
@@ -9269,7 +9185,7 @@
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A401" s="45"/>
+      <c r="A401" s="44"/>
       <c r="B401" t="s">
         <v>420</v>
       </c>
@@ -9282,7 +9198,7 @@
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A402" s="45"/>
+      <c r="A402" s="44"/>
       <c r="C402" t="s">
         <v>421</v>
       </c>
@@ -9292,7 +9208,7 @@
       </c>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A403" s="45"/>
+      <c r="A403" s="44"/>
       <c r="C403" t="s">
         <v>422</v>
       </c>
@@ -9305,7 +9221,7 @@
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A404" s="45"/>
+      <c r="A404" s="44"/>
       <c r="B404" t="s">
         <v>400</v>
       </c>
@@ -9315,7 +9231,7 @@
       </c>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A405" s="45"/>
+      <c r="A405" s="44"/>
       <c r="C405" t="s">
         <v>389</v>
       </c>
@@ -9325,7 +9241,7 @@
       </c>
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A406" s="45"/>
+      <c r="A406" s="44"/>
       <c r="C406" t="s">
         <v>401</v>
       </c>
@@ -9335,7 +9251,7 @@
       </c>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A407" s="45"/>
+      <c r="A407" s="44"/>
       <c r="B407" t="s">
         <v>387</v>
       </c>
@@ -9348,7 +9264,7 @@
       </c>
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A408" s="45"/>
+      <c r="A408" s="44"/>
       <c r="C408" t="s">
         <v>402</v>
       </c>
@@ -9358,7 +9274,7 @@
       </c>
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A409" s="45"/>
+      <c r="A409" s="44"/>
       <c r="C409" t="s">
         <v>403</v>
       </c>
@@ -9368,7 +9284,7 @@
       </c>
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A410" s="45"/>
+      <c r="A410" s="44"/>
       <c r="B410" t="s">
         <v>388</v>
       </c>
@@ -9378,7 +9294,7 @@
       </c>
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A411" s="45"/>
+      <c r="A411" s="44"/>
       <c r="C411" t="s">
         <v>393</v>
       </c>
@@ -9388,7 +9304,7 @@
       </c>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A412" s="45"/>
+      <c r="A412" s="44"/>
       <c r="C412" t="s">
         <v>390</v>
       </c>
@@ -9398,10 +9314,10 @@
       </c>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A413" s="45"/>
+      <c r="A413" s="44"/>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A414" s="45"/>
+      <c r="A414" s="44"/>
       <c r="C414" t="s">
         <v>391</v>
       </c>
@@ -9414,7 +9330,7 @@
       </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A415" s="45"/>
+      <c r="A415" s="44"/>
       <c r="C415" t="s">
         <v>391</v>
       </c>
@@ -9427,7 +9343,7 @@
       </c>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A416" s="45"/>
+      <c r="A416" s="44"/>
       <c r="C416" t="s">
         <v>392</v>
       </c>
@@ -9437,7 +9353,7 @@
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A417" s="45"/>
+      <c r="A417" s="44"/>
       <c r="B417" t="s">
         <v>406</v>
       </c>
@@ -9447,7 +9363,7 @@
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A418" s="45"/>
+      <c r="A418" s="44"/>
       <c r="B418" t="s">
         <v>407</v>
       </c>
@@ -9457,13 +9373,13 @@
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A419" s="45"/>
+      <c r="A419" s="44"/>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A420" s="45"/>
+      <c r="A420" s="44"/>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A421" s="45"/>
+      <c r="A421" s="44"/>
       <c r="B421" t="s">
         <v>409</v>
       </c>
@@ -9479,7 +9395,7 @@
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A422" s="45"/>
+      <c r="A422" s="44"/>
       <c r="B422" t="s">
         <v>410</v>
       </c>
@@ -9492,7 +9408,7 @@
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A423" s="45"/>
+      <c r="A423" s="44"/>
       <c r="B423" t="s">
         <v>412</v>
       </c>
@@ -9502,7 +9418,7 @@
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A424" s="45"/>
+      <c r="A424" s="44"/>
       <c r="B424" t="s">
         <v>423</v>
       </c>
@@ -9515,7 +9431,7 @@
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A425" s="45"/>
+      <c r="A425" s="44"/>
       <c r="B425" t="s">
         <v>425</v>
       </c>
@@ -9525,7 +9441,7 @@
       </c>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A426" s="45"/>
+      <c r="A426" s="44"/>
       <c r="B426" t="s">
         <v>426</v>
       </c>
@@ -9535,7 +9451,7 @@
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A427" s="45"/>
+      <c r="A427" s="44"/>
       <c r="B427" t="s">
         <v>427</v>
       </c>
@@ -9545,7 +9461,7 @@
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A428" s="45"/>
+      <c r="A428" s="44"/>
       <c r="B428" t="s">
         <v>428</v>
       </c>
@@ -9555,7 +9471,7 @@
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A429" s="45"/>
+      <c r="A429" s="44"/>
       <c r="C429" t="s">
         <v>429</v>
       </c>
@@ -9565,7 +9481,7 @@
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A430" s="45"/>
+      <c r="A430" s="44"/>
       <c r="B430" t="s">
         <v>430</v>
       </c>
@@ -9575,7 +9491,7 @@
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A431" s="45"/>
+      <c r="A431" s="44"/>
       <c r="B431" t="s">
         <v>431</v>
       </c>
@@ -9585,7 +9501,7 @@
       </c>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A432" s="45"/>
+      <c r="A432" s="44"/>
       <c r="B432" t="s">
         <v>432</v>
       </c>
@@ -9595,7 +9511,7 @@
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A433" s="45"/>
+      <c r="A433" s="44"/>
       <c r="B433" t="s">
         <v>430</v>
       </c>
@@ -9608,7 +9524,7 @@
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A434" s="45"/>
+      <c r="A434" s="44"/>
       <c r="B434" t="s">
         <v>431</v>
       </c>
@@ -9621,7 +9537,7 @@
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A435" s="45"/>
+      <c r="A435" s="44"/>
       <c r="B435" t="s">
         <v>432</v>
       </c>
@@ -9634,7 +9550,7 @@
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A437" s="45" t="s">
+      <c r="A437" s="44" t="s">
         <v>452</v>
       </c>
       <c r="B437" t="s">
@@ -9649,7 +9565,7 @@
       </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A438" s="45"/>
+      <c r="A438" s="44"/>
       <c r="B438" t="s">
         <v>41</v>
       </c>
@@ -9662,7 +9578,7 @@
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A439" s="45"/>
+      <c r="A439" s="44"/>
       <c r="B439" t="s">
         <v>39</v>
       </c>
@@ -9675,7 +9591,7 @@
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A440" s="45"/>
+      <c r="A440" s="44"/>
       <c r="B440" t="s">
         <v>433</v>
       </c>
@@ -9688,7 +9604,7 @@
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A441" s="45"/>
+      <c r="A441" s="44"/>
       <c r="B441" t="s">
         <v>437</v>
       </c>
@@ -9697,7 +9613,7 @@
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A442" s="45"/>
+      <c r="A442" s="44"/>
       <c r="B442" t="s">
         <v>443</v>
       </c>
@@ -9707,7 +9623,7 @@
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A443" s="45"/>
+      <c r="A443" s="44"/>
       <c r="C443" t="s">
         <v>438</v>
       </c>
@@ -9716,7 +9632,7 @@
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A444" s="45"/>
+      <c r="A444" s="44"/>
       <c r="B444" t="s">
         <v>442</v>
       </c>
@@ -9726,7 +9642,7 @@
       </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A445" s="45"/>
+      <c r="A445" s="44"/>
       <c r="B445" t="s">
         <v>467</v>
       </c>
@@ -9739,7 +9655,7 @@
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A446" s="45"/>
+      <c r="A446" s="44"/>
       <c r="B446" t="s">
         <v>469</v>
       </c>
@@ -9748,7 +9664,7 @@
       </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A447" s="45"/>
+      <c r="A447" s="44"/>
       <c r="B447" t="s">
         <v>470</v>
       </c>
@@ -9757,7 +9673,7 @@
       </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A448" s="45"/>
+      <c r="A448" s="44"/>
       <c r="B448" t="s">
         <v>473</v>
       </c>
@@ -9769,7 +9685,7 @@
       </c>
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A449" s="45"/>
+      <c r="A449" s="44"/>
       <c r="B449" t="s">
         <v>475</v>
       </c>
@@ -9779,7 +9695,7 @@
       </c>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A450" s="45"/>
+      <c r="A450" s="44"/>
       <c r="B450" t="s">
         <v>448</v>
       </c>
@@ -9792,7 +9708,7 @@
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A451" s="45"/>
+      <c r="A451" s="44"/>
       <c r="C451" t="s">
         <v>471</v>
       </c>
@@ -9802,7 +9718,7 @@
       </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A452" s="45"/>
+      <c r="A452" s="44"/>
       <c r="B452" t="s">
         <v>472</v>
       </c>
@@ -9812,7 +9728,7 @@
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A453" s="45"/>
+      <c r="A453" s="44"/>
       <c r="B453" t="s">
         <v>508</v>
       </c>
@@ -9822,7 +9738,7 @@
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A454" s="45"/>
+      <c r="A454" s="44"/>
       <c r="B454" t="s">
         <v>509</v>
       </c>
@@ -9832,7 +9748,7 @@
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A455" s="45"/>
+      <c r="A455" s="44"/>
       <c r="B455" t="s">
         <v>510</v>
       </c>
@@ -9842,7 +9758,7 @@
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A456" s="45"/>
+      <c r="A456" s="44"/>
       <c r="B456" t="s">
         <v>476</v>
       </c>
@@ -9852,7 +9768,7 @@
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A457" s="45"/>
+      <c r="A457" s="44"/>
       <c r="B457" t="s">
         <v>477</v>
       </c>
@@ -9862,7 +9778,7 @@
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A458" s="45"/>
+      <c r="A458" s="44"/>
       <c r="B458" t="s">
         <v>446</v>
       </c>
@@ -9874,7 +9790,7 @@
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A459" s="45"/>
+      <c r="A459" s="44"/>
       <c r="B459" t="s">
         <v>444</v>
       </c>
@@ -9887,7 +9803,7 @@
       </c>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A460" s="45"/>
+      <c r="A460" s="44"/>
       <c r="B460" t="s">
         <v>441</v>
       </c>
@@ -9899,7 +9815,7 @@
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A461" s="45"/>
+      <c r="A461" s="44"/>
       <c r="B461" t="s">
         <v>479</v>
       </c>
@@ -9909,7 +9825,7 @@
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A462" s="45"/>
+      <c r="A462" s="44"/>
       <c r="B462" t="s">
         <v>480</v>
       </c>
@@ -9919,7 +9835,7 @@
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A463" s="45"/>
+      <c r="A463" s="44"/>
       <c r="B463" t="s">
         <v>439</v>
       </c>
@@ -9932,7 +9848,7 @@
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A464" s="45"/>
+      <c r="A464" s="44"/>
       <c r="B464" t="s">
         <v>450</v>
       </c>
@@ -9942,7 +9858,7 @@
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A465" s="45"/>
+      <c r="A465" s="44"/>
       <c r="C465" t="s">
         <v>451</v>
       </c>
@@ -9952,7 +9868,7 @@
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A466" s="45"/>
+      <c r="A466" s="44"/>
       <c r="B466" t="s">
         <v>453</v>
       </c>
@@ -9964,7 +9880,7 @@
       </c>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A467" s="45"/>
+      <c r="A467" s="44"/>
       <c r="B467" t="s">
         <v>38</v>
       </c>
@@ -9974,10 +9890,10 @@
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A468" s="45"/>
+      <c r="A468" s="44"/>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A469" s="45"/>
+      <c r="A469" s="44"/>
       <c r="B469" t="s">
         <v>456</v>
       </c>
@@ -9987,7 +9903,7 @@
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A470" s="45"/>
+      <c r="A470" s="44"/>
       <c r="B470" t="s">
         <v>457</v>
       </c>
@@ -9997,7 +9913,7 @@
       </c>
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A471" s="45"/>
+      <c r="A471" s="44"/>
       <c r="B471" t="s">
         <v>458</v>
       </c>
@@ -10007,7 +9923,7 @@
       </c>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A472" s="45"/>
+      <c r="A472" s="44"/>
       <c r="B472" t="s">
         <v>241</v>
       </c>
@@ -10017,7 +9933,7 @@
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A473" s="45"/>
+      <c r="A473" s="44"/>
       <c r="B473" t="s">
         <v>459</v>
       </c>
@@ -10027,7 +9943,7 @@
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A474" s="45"/>
+      <c r="A474" s="44"/>
       <c r="C474" t="s">
         <v>455</v>
       </c>
@@ -10037,7 +9953,7 @@
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A475" s="45"/>
+      <c r="A475" s="44"/>
       <c r="B475" t="s">
         <v>461</v>
       </c>
@@ -10050,7 +9966,7 @@
       </c>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A476" s="45"/>
+      <c r="A476" s="44"/>
       <c r="B476" t="s">
         <v>462</v>
       </c>
@@ -10060,7 +9976,7 @@
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A477" s="45"/>
+      <c r="A477" s="44"/>
       <c r="B477" t="s">
         <v>463</v>
       </c>
@@ -10070,7 +9986,7 @@
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A478" s="45"/>
+      <c r="A478" s="44"/>
       <c r="B478" t="s">
         <v>464</v>
       </c>
@@ -10080,7 +9996,7 @@
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A479" s="45"/>
+      <c r="A479" s="44"/>
       <c r="C479" t="s">
         <v>465</v>
       </c>
@@ -10090,7 +10006,7 @@
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A480" s="45"/>
+      <c r="A480" s="44"/>
       <c r="B480" t="s">
         <v>466</v>
       </c>
@@ -10100,7 +10016,7 @@
       </c>
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A481" s="45"/>
+      <c r="A481" s="44"/>
       <c r="B481" t="s">
         <v>484</v>
       </c>
@@ -10112,7 +10028,7 @@
       </c>
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A482" s="45"/>
+      <c r="A482" s="44"/>
       <c r="C482" t="s">
         <v>482</v>
       </c>
@@ -10121,7 +10037,7 @@
       </c>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A483" s="45"/>
+      <c r="A483" s="44"/>
       <c r="B483" t="s">
         <v>483</v>
       </c>
@@ -10131,7 +10047,7 @@
       </c>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A484" s="45"/>
+      <c r="A484" s="44"/>
       <c r="B484" t="s">
         <v>485</v>
       </c>
@@ -10141,7 +10057,7 @@
       </c>
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A485" s="45"/>
+      <c r="A485" s="44"/>
       <c r="B485" t="s">
         <v>486</v>
       </c>
@@ -10150,7 +10066,7 @@
       </c>
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A486" s="45"/>
+      <c r="A486" s="44"/>
       <c r="B486" t="s">
         <v>487</v>
       </c>
@@ -10159,7 +10075,7 @@
       </c>
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A487" s="45"/>
+      <c r="A487" s="44"/>
       <c r="C487" t="s">
         <v>488</v>
       </c>
@@ -10169,7 +10085,7 @@
       </c>
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A488" s="45"/>
+      <c r="A488" s="44"/>
       <c r="B488" t="s">
         <v>489</v>
       </c>
@@ -10182,7 +10098,7 @@
       </c>
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A489" s="45"/>
+      <c r="A489" s="44"/>
       <c r="B489" t="s">
         <v>491</v>
       </c>
@@ -10195,7 +10111,7 @@
       </c>
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A490" s="45"/>
+      <c r="A490" s="44"/>
       <c r="B490" t="s">
         <v>493</v>
       </c>
@@ -10205,7 +10121,7 @@
       </c>
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A491" s="45"/>
+      <c r="A491" s="44"/>
       <c r="B491" t="s">
         <v>494</v>
       </c>
@@ -10215,7 +10131,7 @@
       </c>
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A492" s="45"/>
+      <c r="A492" s="44"/>
       <c r="B492" t="s">
         <v>500</v>
       </c>
@@ -10224,7 +10140,7 @@
       </c>
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A493" s="45"/>
+      <c r="A493" s="44"/>
       <c r="C493" t="s">
         <v>504</v>
       </c>
@@ -10233,7 +10149,7 @@
       </c>
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A494" s="45"/>
+      <c r="A494" s="44"/>
       <c r="B494" t="s">
         <v>505</v>
       </c>
@@ -10243,7 +10159,7 @@
       </c>
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A495" s="45"/>
+      <c r="A495" s="44"/>
       <c r="B495" t="s">
         <v>506</v>
       </c>
@@ -10253,7 +10169,7 @@
       </c>
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A496" s="45"/>
+      <c r="A496" s="44"/>
       <c r="C496" t="s">
         <v>497</v>
       </c>
@@ -10263,7 +10179,7 @@
       </c>
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A497" s="45"/>
+      <c r="A497" s="44"/>
       <c r="C497" t="s">
         <v>498</v>
       </c>
@@ -10273,7 +10189,7 @@
       </c>
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A498" s="45"/>
+      <c r="A498" s="44"/>
       <c r="C498" t="s">
         <v>499</v>
       </c>
@@ -10283,7 +10199,7 @@
       </c>
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A499" s="45"/>
+      <c r="A499" s="44"/>
       <c r="C499" t="s">
         <v>501</v>
       </c>
@@ -10293,10 +10209,10 @@
       </c>
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A500" s="45"/>
+      <c r="A500" s="44"/>
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A501" s="45"/>
+      <c r="A501" s="44"/>
       <c r="B501" t="s">
         <v>502</v>
       </c>
@@ -10306,7 +10222,7 @@
       </c>
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A502" s="45"/>
+      <c r="A502" s="44"/>
       <c r="B502" t="s">
         <v>507</v>
       </c>
@@ -10316,7 +10232,7 @@
       </c>
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A503" s="45"/>
+      <c r="A503" s="44"/>
       <c r="B503" t="s">
         <v>503</v>
       </c>
@@ -10326,9 +10242,9 @@
       </c>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A504" s="45"/>
+      <c r="A504" s="44"/>
       <c r="C504" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D504" s="1">
         <f>0.5*D460*POWER(D505, 2)</f>
@@ -10336,9 +10252,9 @@
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A505" s="45"/>
+      <c r="A505" s="44"/>
       <c r="C505" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D505">
         <f>D2/D6</f>
@@ -10346,9 +10262,9 @@
       </c>
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A506" s="45"/>
+      <c r="A506" s="44"/>
       <c r="C506" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D506">
         <f>D6</f>
@@ -10356,9 +10272,9 @@
       </c>
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A507" s="45"/>
+      <c r="A507" s="44"/>
       <c r="C507" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D507">
         <f>POWER(((0.5*D450*POWER(D506, 2))+D504)*2/D450, 0.5)</f>
@@ -10367,13 +10283,13 @@
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
+        <v>738</v>
+      </c>
+      <c r="B508" t="s">
+        <v>740</v>
+      </c>
+      <c r="C508" t="s">
         <v>739</v>
-      </c>
-      <c r="B508" t="s">
-        <v>741</v>
-      </c>
-      <c r="C508" t="s">
-        <v>740</v>
       </c>
       <c r="D508" s="1">
         <f>0.5*D450*POWER(D7, 2)</f>
@@ -10382,10 +10298,10 @@
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B509" t="s">
+        <v>741</v>
+      </c>
+      <c r="C509" t="s">
         <v>742</v>
-      </c>
-      <c r="C509" t="s">
-        <v>743</v>
       </c>
       <c r="D509">
         <f>(0.06*0.022*0.0018)+(2*(0.06*0.0129*0.001))+(0.06*0.0091*0.0018)</f>
@@ -10394,10 +10310,10 @@
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B510" t="s">
+        <v>743</v>
+      </c>
+      <c r="C510" t="s">
         <v>744</v>
-      </c>
-      <c r="C510" t="s">
-        <v>745</v>
       </c>
       <c r="D510">
         <v>850</v>
@@ -10405,10 +10321,10 @@
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B511" t="s">
+        <v>745</v>
+      </c>
+      <c r="C511" t="s">
         <v>746</v>
-      </c>
-      <c r="C511" t="s">
-        <v>747</v>
       </c>
       <c r="D511">
         <v>2700</v>
@@ -10416,7 +10332,7 @@
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B512" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D512">
         <f>D508/(D511*D509*D510)</f>
@@ -10425,10 +10341,10 @@
     </row>
     <row r="513" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B513" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C513" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D513">
         <v>0.2</v>
@@ -10436,10 +10352,10 @@
     </row>
     <row r="514" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B514" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C514" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D514">
         <f>D510*D509*D511</f>
@@ -10448,10 +10364,10 @@
     </row>
     <row r="515" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B515" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C515" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D515">
         <f>0.022*0.06</f>
@@ -10460,10 +10376,10 @@
     </row>
     <row r="516" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B516" t="s">
+        <v>759</v>
+      </c>
+      <c r="C516" t="s">
         <v>760</v>
-      </c>
-      <c r="C516" t="s">
-        <v>761</v>
       </c>
       <c r="D516">
         <f>0.002</f>
@@ -10472,10 +10388,10 @@
     </row>
     <row r="517" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B517" t="s">
+        <v>748</v>
+      </c>
+      <c r="C517" t="s">
         <v>749</v>
-      </c>
-      <c r="C517" t="s">
-        <v>750</v>
       </c>
       <c r="D517">
         <v>0.5</v>
@@ -10483,10 +10399,10 @@
     </row>
     <row r="518" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B518" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C518" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D518">
         <f>4.605*D514/D517</f>
@@ -10495,10 +10411,10 @@
     </row>
     <row r="519" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B519" t="s">
+        <v>755</v>
+      </c>
+      <c r="C519" t="s">
         <v>756</v>
-      </c>
-      <c r="C519" t="s">
-        <v>757</v>
       </c>
       <c r="D519">
         <f>D516/(D513*D515)</f>
@@ -10507,7 +10423,7 @@
     </row>
     <row r="520" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B520" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D520">
         <f>D514*D512/D518</f>
@@ -10517,7 +10433,7 @@
     <row r="521" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A521" s="42"/>
       <c r="B521" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D521">
         <f>D520*D519</f>
@@ -10525,29 +10441,29 @@
       </c>
     </row>
     <row r="522" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A522" s="45" t="s">
+      <c r="A522" s="44" t="s">
+        <v>631</v>
+      </c>
+      <c r="C522" t="s">
+        <v>635</v>
+      </c>
+      <c r="D522" t="s">
+        <v>636</v>
+      </c>
+      <c r="E522" t="s">
+        <v>638</v>
+      </c>
+      <c r="F522" t="s">
+        <v>637</v>
+      </c>
+      <c r="G522" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="523" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A523" s="44"/>
+      <c r="C523" t="s">
         <v>632</v>
-      </c>
-      <c r="C522" t="s">
-        <v>636</v>
-      </c>
-      <c r="D522" t="s">
-        <v>637</v>
-      </c>
-      <c r="E522" t="s">
-        <v>639</v>
-      </c>
-      <c r="F522" t="s">
-        <v>638</v>
-      </c>
-      <c r="G522" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="523" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A523" s="45"/>
-      <c r="C523" t="s">
-        <v>633</v>
       </c>
       <c r="D523">
         <f>D2/D5</f>
@@ -10574,9 +10490,9 @@
       </c>
     </row>
     <row r="524" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A524" s="45"/>
+      <c r="A524" s="44"/>
       <c r="C524" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D524">
         <v>2</v>
@@ -10601,9 +10517,9 @@
       </c>
     </row>
     <row r="525" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A525" s="45"/>
+      <c r="A525" s="44"/>
       <c r="C525" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D525">
         <v>5</v>
@@ -10628,9 +10544,9 @@
       </c>
     </row>
     <row r="526" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A526" s="45"/>
+      <c r="A526" s="44"/>
       <c r="C526" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D526">
         <f>0.0254*POWER(D523/(0.048*POWER(D525, 0.44)), 1/0.725)/(D524*1.378)</f>
@@ -10662,9 +10578,9 @@
       </c>
     </row>
     <row r="527" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A527" s="45"/>
+      <c r="A527" s="44"/>
       <c r="C527" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D527">
         <f>0.0254*POWER(D523/(0.024*POWER(D525, 0.44)), 1/0.725)/(D524*1.378)</f>
@@ -10692,9 +10608,9 @@
       </c>
     </row>
     <row r="528" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A528" s="45"/>
+      <c r="A528" s="44"/>
       <c r="C528" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D528">
         <v>8</v>
@@ -10713,9 +10629,9 @@
       </c>
     </row>
     <row r="529" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A529" s="45"/>
+      <c r="A529" s="44"/>
       <c r="C529" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D529">
         <f>POWER(D523/POWER(D528*(D524*1.378)/0.0254, 0.725)/0.048, 1/0.44)</f>
@@ -10739,9 +10655,9 @@
       </c>
     </row>
     <row r="530" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A530" s="45"/>
+      <c r="A530" s="44"/>
       <c r="C530" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D530">
         <f>POWER(D523/POWER(D528*(D524*1.378)/0.0254, 0.725)/0.024, 1/0.44)</f>
@@ -10765,9 +10681,9 @@
       </c>
     </row>
     <row r="531" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A531" s="45"/>
+      <c r="A531" s="44"/>
       <c r="C531" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D531">
         <v>100</v>
@@ -10786,7 +10702,7 @@
       </c>
     </row>
     <row r="532" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A532" s="45"/>
+      <c r="A532" s="44"/>
       <c r="C532" t="s">
         <v>200</v>
       </c>
@@ -10812,9 +10728,9 @@
       </c>
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A533" s="45"/>
+      <c r="A533" s="44"/>
       <c r="C533" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D533">
         <f>POWER(D523, 2)*D532</f>
@@ -10838,9 +10754,9 @@
       </c>
     </row>
     <row r="534" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A534" s="45"/>
+      <c r="A534" s="44"/>
       <c r="C534" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D534">
         <f>D523*D532</f>
@@ -10870,30 +10786,30 @@
       <c r="A536" s="42"/>
     </row>
     <row r="541" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A541" s="44" t="s">
+      <c r="A541" s="47" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="542" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A542" s="47"/>
+      <c r="C542" t="s">
         <v>721</v>
-      </c>
-    </row>
-    <row r="542" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A542" s="44"/>
-      <c r="C542" t="s">
-        <v>722</v>
       </c>
       <c r="D542" s="1">
         <v>1000000000</v>
       </c>
     </row>
     <row r="543" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A543" s="44"/>
+      <c r="A543" s="47"/>
       <c r="C543" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D543">
         <v>14</v>
       </c>
     </row>
     <row r="544" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A544" s="44"/>
+      <c r="A544" s="47"/>
       <c r="C544" t="s">
         <v>219</v>
       </c>
@@ -10903,9 +10819,9 @@
       </c>
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A545" s="44"/>
+      <c r="A545" s="47"/>
       <c r="C545" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D545">
         <f>2.5</f>
@@ -10913,9 +10829,9 @@
       </c>
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A546" s="44"/>
+      <c r="A546" s="47"/>
       <c r="C546" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D546">
         <f>D8/D545</f>
@@ -10923,9 +10839,9 @@
       </c>
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A547" s="44"/>
+      <c r="A547" s="47"/>
       <c r="C547" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D547">
         <f>D544/D546</f>
@@ -10933,18 +10849,18 @@
       </c>
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A548" s="44"/>
+      <c r="A548" s="47"/>
       <c r="C548" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D548" s="1">
         <v>130000</v>
       </c>
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A549" s="44"/>
+      <c r="A549" s="47"/>
       <c r="C549" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D549" s="1">
         <f>D8/D544</f>
@@ -10952,9 +10868,9 @@
       </c>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A550" s="44"/>
+      <c r="A550" s="47"/>
       <c r="C550" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D550" s="1">
         <f>D549*D549*D542</f>
@@ -10962,9 +10878,9 @@
       </c>
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A551" s="44"/>
+      <c r="A551" s="47"/>
       <c r="C551" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D551" s="1">
         <f>D550*D543</f>
@@ -10972,9 +10888,9 @@
       </c>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A552" s="44"/>
+      <c r="A552" s="47"/>
       <c r="C552" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D552" s="1">
         <f>POWER(D549, 2)*D548</f>
@@ -10982,27 +10898,27 @@
       </c>
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A555" s="44" t="s">
-        <v>731</v>
+      <c r="A555" s="47" t="s">
+        <v>730</v>
       </c>
       <c r="C555" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D555" s="1">
         <v>100000000</v>
       </c>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A556" s="44"/>
+      <c r="A556" s="47"/>
       <c r="C556" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D556">
         <v>1</v>
       </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A557" s="44"/>
+      <c r="A557" s="47"/>
       <c r="C557" t="s">
         <v>219</v>
       </c>
@@ -11012,18 +10928,18 @@
       </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A558" s="44"/>
+      <c r="A558" s="47"/>
       <c r="C558" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D558">
         <v>2.5</v>
       </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A559" s="44"/>
+      <c r="A559" s="47"/>
       <c r="C559" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D559">
         <f>D12/D558</f>
@@ -11031,9 +10947,9 @@
       </c>
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A560" s="44"/>
+      <c r="A560" s="47"/>
       <c r="C560" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D560">
         <f>D557/D559</f>
@@ -11041,18 +10957,18 @@
       </c>
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A561" s="44"/>
+      <c r="A561" s="47"/>
       <c r="C561" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D561" s="1">
         <v>20000</v>
       </c>
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A562" s="44"/>
+      <c r="A562" s="47"/>
       <c r="C562" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D562" s="1">
         <f>D12/D557</f>
@@ -11060,9 +10976,9 @@
       </c>
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A563" s="44"/>
+      <c r="A563" s="47"/>
       <c r="C563" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D563" s="1">
         <f>D562*D562*D555</f>
@@ -11070,9 +10986,9 @@
       </c>
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A564" s="44"/>
+      <c r="A564" s="47"/>
       <c r="C564" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D564" s="1">
         <f>D563*D556</f>
@@ -11081,7 +10997,7 @@
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C565" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D565" s="1">
         <f>POWER(D562, 2)*D561</f>
@@ -11089,32 +11005,32 @@
       </c>
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A567" s="45" t="s">
+      <c r="A567" s="44" t="s">
+        <v>731</v>
+      </c>
+      <c r="C567" t="s">
         <v>732</v>
-      </c>
-      <c r="C567" t="s">
-        <v>733</v>
       </c>
       <c r="D567">
         <v>3</v>
       </c>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A568" s="45"/>
+      <c r="A568" s="44"/>
       <c r="C568" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D568">
         <v>550</v>
       </c>
       <c r="E568" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A569" s="45"/>
+      <c r="A569" s="44"/>
       <c r="C569" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D569">
         <f>25.4*41.9*0.000001</f>
@@ -11122,22 +11038,22 @@
       </c>
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A570" s="45"/>
+      <c r="A570" s="44"/>
       <c r="C570" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D570">
         <f>D569*D568*0.3048</f>
         <v>0.17841254640000004</v>
       </c>
       <c r="E570" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A571" s="45"/>
+      <c r="A571" s="44"/>
       <c r="C571" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D571">
         <f>D570*50</f>
@@ -11145,35 +11061,35 @@
       </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A572" s="45"/>
+      <c r="A572" s="44"/>
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A573" s="45"/>
+      <c r="A573" s="44"/>
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A574" s="45"/>
+      <c r="A574" s="44"/>
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A575" s="45"/>
+      <c r="A575" s="44"/>
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A576" s="45"/>
+      <c r="A576" s="44"/>
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A577" s="45"/>
+      <c r="A577" s="44"/>
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A578" s="45"/>
+      <c r="A578" s="44"/>
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A579" s="45"/>
+      <c r="A579" s="44"/>
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A581" s="45" t="s">
+      <c r="A581" s="44" t="s">
+        <v>765</v>
+      </c>
+      <c r="C581" t="s">
         <v>766</v>
-      </c>
-      <c r="C581" t="s">
-        <v>767</v>
       </c>
       <c r="E581" s="1">
         <f>D55</f>
@@ -11181,9 +11097,9 @@
       </c>
     </row>
     <row r="582" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A582" s="45"/>
+      <c r="A582" s="44"/>
       <c r="C582" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="E582">
         <f>D27</f>
@@ -11191,9 +11107,9 @@
       </c>
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A583" s="45"/>
+      <c r="A583" s="44"/>
       <c r="C583" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E583" s="1">
         <f>D151+D152</f>
@@ -11201,9 +11117,9 @@
       </c>
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A584" s="45"/>
+      <c r="A584" s="44"/>
       <c r="C584" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E584" s="1">
         <f>E581+E582+E583</f>
@@ -11211,13 +11127,13 @@
       </c>
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A585" s="45"/>
+      <c r="A585" s="44"/>
     </row>
     <row r="586" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A586" s="45"/>
+      <c r="A586" s="44"/>
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A587" s="45"/>
+      <c r="A587" s="44"/>
       <c r="C587" t="s">
         <v>4</v>
       </c>
@@ -11226,9 +11142,9 @@
       </c>
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A588" s="45"/>
+      <c r="A588" s="44"/>
       <c r="C588" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D588" t="s">
         <v>212</v>
@@ -11238,9 +11154,9 @@
       </c>
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A589" s="45"/>
+      <c r="A589" s="44"/>
       <c r="C589" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D589" t="s">
         <v>212</v>
@@ -11250,12 +11166,12 @@
       </c>
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A590" s="45"/>
+      <c r="A590" s="44"/>
       <c r="C590" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D590" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="E590">
         <f>POWER(E588/2, 2)*PI()*E589</f>
@@ -11263,9 +11179,9 @@
       </c>
     </row>
     <row r="591" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A591" s="45"/>
+      <c r="A591" s="44"/>
       <c r="C591" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E591" s="1">
         <f>E584</f>
@@ -11273,48 +11189,48 @@
       </c>
     </row>
     <row r="592" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A592" s="45"/>
+      <c r="A592" s="44"/>
       <c r="C592" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D592" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E592">
         <v>2300</v>
       </c>
     </row>
     <row r="593" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A593" s="45"/>
+      <c r="A593" s="44"/>
       <c r="C593" t="s">
+        <v>654</v>
+      </c>
+      <c r="D593" t="s">
         <v>655</v>
-      </c>
-      <c r="D593" t="s">
-        <v>656</v>
       </c>
       <c r="E593">
         <v>20</v>
       </c>
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A594" s="45"/>
+      <c r="A594" s="44"/>
       <c r="C594" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D594" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E594">
         <v>800</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A595" s="45"/>
+      <c r="A595" s="44"/>
       <c r="C595" t="s">
+        <v>660</v>
+      </c>
+      <c r="D595" t="s">
         <v>661</v>
-      </c>
-      <c r="D595" t="s">
-        <v>662</v>
       </c>
       <c r="E595">
         <f>E594*E590</f>
@@ -11322,12 +11238,12 @@
       </c>
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A596" s="45"/>
+      <c r="A596" s="44"/>
       <c r="C596" t="s">
+        <v>662</v>
+      </c>
+      <c r="D596" t="s">
         <v>663</v>
-      </c>
-      <c r="D596" t="s">
-        <v>664</v>
       </c>
       <c r="E596">
         <f>E592*E595*E593</f>
@@ -11335,9 +11251,9 @@
       </c>
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A597" s="45"/>
+      <c r="A597" s="44"/>
       <c r="C597" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D597" t="s">
         <v>343</v>
@@ -11348,9 +11264,9 @@
       </c>
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A598" s="45"/>
+      <c r="A598" s="44"/>
       <c r="C598" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D598" t="s">
         <v>343</v>
@@ -11361,12 +11277,12 @@
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A599" s="45"/>
+      <c r="A599" s="44"/>
       <c r="C599" t="s">
+        <v>666</v>
+      </c>
+      <c r="D599" t="s">
         <v>667</v>
-      </c>
-      <c r="D599" t="s">
-        <v>668</v>
       </c>
       <c r="E599">
         <f>E590/E598</f>
@@ -11374,12 +11290,12 @@
       </c>
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A600" s="45"/>
+      <c r="A600" s="44"/>
       <c r="C600" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D600" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E600">
         <f>(1000000)*E599</f>
@@ -11387,21 +11303,21 @@
       </c>
     </row>
     <row r="601" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A601" s="45"/>
+      <c r="A601" s="44"/>
       <c r="C601" t="s">
+        <v>669</v>
+      </c>
+      <c r="D601" t="s">
         <v>670</v>
-      </c>
-      <c r="D601" t="s">
-        <v>671</v>
       </c>
       <c r="E601">
         <v>0.1</v>
       </c>
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A602" s="45"/>
+      <c r="A602" s="44"/>
       <c r="C602" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D602" t="s">
         <v>213</v>
@@ -11412,9 +11328,9 @@
       </c>
     </row>
     <row r="603" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A603" s="45"/>
+      <c r="A603" s="44"/>
       <c r="C603" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D603" t="s">
         <v>212</v>
@@ -11425,9 +11341,9 @@
       </c>
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A604" s="45"/>
+      <c r="A604" s="44"/>
       <c r="C604" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D604" t="s">
         <v>212</v>
@@ -11438,9 +11354,9 @@
       </c>
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A605" s="45"/>
+      <c r="A605" s="44"/>
       <c r="C605" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D605" t="s">
         <v>139</v>
@@ -11451,9 +11367,9 @@
       </c>
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A606" s="45"/>
+      <c r="A606" s="44"/>
       <c r="C606" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D606" t="s">
         <v>139</v>
@@ -11464,7 +11380,7 @@
     </row>
     <row r="607" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C607" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E607">
         <f>E606/1000</f>
@@ -11473,7 +11389,7 @@
     </row>
     <row r="608" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C608" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E608">
         <f>0.00604</f>
@@ -11482,7 +11398,7 @@
     </row>
     <row r="609" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C609" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E609">
         <f>E608/E594</f>
@@ -11491,7 +11407,7 @@
     </row>
     <row r="610" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C610" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E610">
         <v>2300</v>
@@ -11499,7 +11415,7 @@
     </row>
     <row r="611" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C611" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E611">
         <f>E594*E601*E607/E608</f>
@@ -11508,7 +11424,7 @@
     </row>
     <row r="612" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C612" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E612" t="b">
         <f>E611&lt;E610</f>
@@ -11517,6 +11433,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A352:A364"/>
+    <mergeCell ref="A365:A368"/>
+    <mergeCell ref="A541:A552"/>
+    <mergeCell ref="A555:A564"/>
+    <mergeCell ref="A437:A507"/>
+    <mergeCell ref="A522:A534"/>
     <mergeCell ref="A581:A606"/>
     <mergeCell ref="A216:A267"/>
     <mergeCell ref="G19:J22"/>
@@ -11533,12 +11455,6 @@
     <mergeCell ref="A31:A47"/>
     <mergeCell ref="A291:A303"/>
     <mergeCell ref="A567:A579"/>
-    <mergeCell ref="A352:A364"/>
-    <mergeCell ref="A365:A368"/>
-    <mergeCell ref="A541:A552"/>
-    <mergeCell ref="A555:A564"/>
-    <mergeCell ref="A437:A507"/>
-    <mergeCell ref="A522:A534"/>
   </mergeCells>
   <conditionalFormatting sqref="D98">
     <cfRule type="cellIs" dxfId="9" priority="9" operator="notEqual">
@@ -12559,7 +12475,7 @@
   <sheetData>
     <row r="2" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="T2">
         <v>399</v>
@@ -12567,7 +12483,7 @@
     </row>
     <row r="3" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="T3">
         <v>14000</v>
@@ -12575,7 +12491,7 @@
     </row>
     <row r="4" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="T4" s="1">
         <v>5.4399999999999996E-6</v>
@@ -12583,7 +12499,7 @@
     </row>
     <row r="5" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="T5">
         <v>40</v>
@@ -12591,7 +12507,7 @@
     </row>
     <row r="6" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="T6">
         <v>20</v>
@@ -12599,7 +12515,7 @@
     </row>
     <row r="7" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S7" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="T7">
         <v>1E-4</v>
@@ -12607,7 +12523,7 @@
     </row>
     <row r="8" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S8" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="T8">
         <f>POWER(T4/T7, 0.5)</f>
@@ -12616,7 +12532,7 @@
     </row>
     <row r="9" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S9" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="T9">
         <v>0.1</v>
@@ -12624,7 +12540,7 @@
     </row>
     <row r="10" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S10" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="T10">
         <f>T9/T12</f>
@@ -12633,7 +12549,7 @@
     </row>
     <row r="11" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S11" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="T11">
         <f>T9/T12</f>
@@ -12642,7 +12558,7 @@
     </row>
     <row r="12" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S12" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="T12">
         <v>44.5</v>
@@ -12650,7 +12566,7 @@
     </row>
     <row r="13" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S13" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="T13">
         <f>T6-POWER(POWER((T9-(T11*T12))/T8, 2)+POWER(T6, 2), 0.5)</f>
@@ -12659,7 +12575,7 @@
     </row>
     <row r="14" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S14" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="T14">
         <f>(1/T11)*(T13-T6)</f>
@@ -12668,7 +12584,7 @@
     </row>
     <row r="15" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S15" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="T15">
         <f>T13-T14</f>
@@ -12677,7 +12593,7 @@
     </row>
     <row r="16" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S16" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="T16">
         <f>T5</f>
@@ -12686,7 +12602,7 @@
     </row>
     <row r="17" spans="19:21" x14ac:dyDescent="0.25">
       <c r="S17" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="T17">
         <f>T4*POWER(T5, 2)/POWER(T9-(T3/T2), 2)</f>
@@ -12695,7 +12611,7 @@
     </row>
     <row r="18" spans="19:21" x14ac:dyDescent="0.25">
       <c r="S18" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="T18" t="str">
         <f>IF(T11&lt;T9/T12, "Decrease V_max by", "Increase V_max by")</f>
@@ -12734,116 +12650,116 @@
   <sheetData>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B3" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C3" t="s">
         <v>129</v>
       </c>
       <c r="D3" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B4" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D4">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B5" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D5">
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B6" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D6">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B8" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D8">
         <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B9" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D9">
         <v>4</v>
       </c>
       <c r="E9" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E10" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B11" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D11">
         <v>16</v>

--- a/Spreadsheets/BasicCalculations.xlsx
+++ b/Spreadsheets/BasicCalculations.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="817">
   <si>
     <t>N stages required</t>
   </si>
@@ -708,9 +708,6 @@
   </si>
   <si>
     <t>Vsn</t>
-  </si>
-  <si>
-    <t>Leakage inductance</t>
   </si>
   <si>
     <t>t_s</t>
@@ -2404,6 +2401,102 @@
   </si>
   <si>
     <t>Maximum energy capacity</t>
+  </si>
+  <si>
+    <t>Dummy Loads For Testing Primary</t>
+  </si>
+  <si>
+    <t>Minimum current required to test above lower bound of ADC</t>
+  </si>
+  <si>
+    <t>Max resistance required</t>
+  </si>
+  <si>
+    <t>Min resistance required</t>
+  </si>
+  <si>
+    <t>Nominal resistance required</t>
+  </si>
+  <si>
+    <t>Actual resistance for minimum current test</t>
+  </si>
+  <si>
+    <t>Maximum output power</t>
+  </si>
+  <si>
+    <t>Actual individual resistor value</t>
+  </si>
+  <si>
+    <t>N in series</t>
+  </si>
+  <si>
+    <t>Series resistance</t>
+  </si>
+  <si>
+    <t>Minimum resistance for 200w test required</t>
+  </si>
+  <si>
+    <t>Maximum current reached</t>
+  </si>
+  <si>
+    <t>Maximum peak current</t>
+  </si>
+  <si>
+    <t>Minimum peak current</t>
+  </si>
+  <si>
+    <t>Maximum average power</t>
+  </si>
+  <si>
+    <t>Maximum Peak power</t>
+  </si>
+  <si>
+    <t>Minimum Peak Power</t>
+  </si>
+  <si>
+    <t>Minimum average power</t>
+  </si>
+  <si>
+    <t>1, 1, 1, 1, 1</t>
+  </si>
+  <si>
+    <t>Resistor combination for maximum supply voltage</t>
+  </si>
+  <si>
+    <t>1, 1, 1, 1, 1, 1</t>
+  </si>
+  <si>
+    <t>1, 1, 1, 2, 2</t>
+  </si>
+  <si>
+    <t>1, 1, 1, 1, 2, 2</t>
+  </si>
+  <si>
+    <t>1, 1, 1, 1, 1, 2, 2</t>
+  </si>
+  <si>
+    <t>1, 1, 1, 1, 1, 1, 2, 2</t>
+  </si>
+  <si>
+    <t>1, 1, 1, 2, 2, 4</t>
+  </si>
+  <si>
+    <t>1, 2, 2, 4, 4</t>
+  </si>
+  <si>
+    <t>1, 1, 1, 1, 2, 2, 4 OR 2, 4, 4</t>
+  </si>
+  <si>
+    <t>1, 1, 2, 2, 4, 4</t>
+  </si>
+  <si>
+    <t>Secondary Leakage inductance</t>
+  </si>
+  <si>
+    <t>L_s_actual</t>
+  </si>
+  <si>
+    <t>Use this number to begin with</t>
   </si>
 </sst>
 </file>
@@ -2602,7 +2695,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2671,11 +2764,20 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="45"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2695,9 +2797,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="11" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4075,7 +4174,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R624"/>
+  <dimension ref="A1:R649"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" customWidth="1"/>
@@ -4159,10 +4258,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
+        <v>494</v>
+      </c>
+      <c r="C6" t="s">
         <v>495</v>
-      </c>
-      <c r="C6" t="s">
-        <v>496</v>
       </c>
       <c r="D6">
         <f>12.7*3</f>
@@ -4322,15 +4421,15 @@
       <c r="C19" s="8"/>
       <c r="D19" s="13"/>
       <c r="E19" s="8"/>
-      <c r="G19" s="46" t="s">
-        <v>590</v>
-      </c>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
+      <c r="G19" s="51" t="s">
+        <v>589</v>
+      </c>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="44" t="s">
+      <c r="A20" s="50" t="s">
         <v>103</v>
       </c>
       <c r="B20" t="s">
@@ -4345,13 +4444,13 @@
       <c r="E20" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="46"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="44"/>
+      <c r="A21" s="50"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6" t="s">
         <v>3</v>
@@ -4363,13 +4462,13 @@
       <c r="E21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G21" s="46"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="44"/>
+      <c r="A22" s="50"/>
       <c r="B22" t="s">
         <v>67</v>
       </c>
@@ -4379,13 +4478,13 @@
       <c r="D22">
         <v>0.1</v>
       </c>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="44"/>
+      <c r="A23" s="50"/>
       <c r="B23" s="6"/>
       <c r="C23" s="12" t="s">
         <v>72</v>
@@ -4397,7 +4496,7 @@
       <c r="E23" s="6"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="44"/>
+      <c r="A24" s="50"/>
       <c r="C24" t="s">
         <v>7</v>
       </c>
@@ -4406,7 +4505,7 @@
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="44"/>
+      <c r="A25" s="50"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6" t="s">
         <v>28</v>
@@ -4415,7 +4514,7 @@
       <c r="E25" s="6"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="44"/>
+      <c r="A26" s="50"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
         <v>12</v>
@@ -4429,7 +4528,7 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="44"/>
+      <c r="A27" s="50"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6" t="s">
         <v>11</v>
@@ -4443,7 +4542,7 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="44"/>
+      <c r="A28" s="50"/>
       <c r="C28" t="s">
         <v>8</v>
       </c>
@@ -4455,7 +4554,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="44"/>
+      <c r="A29" s="50"/>
       <c r="C29" t="s">
         <v>10</v>
       </c>
@@ -4466,41 +4565,41 @@
       <c r="E29" t="s">
         <v>25</v>
       </c>
-      <c r="G29" s="46" t="s">
-        <v>591</v>
-      </c>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
+      <c r="G29" s="51" t="s">
+        <v>590</v>
+      </c>
+      <c r="H29" s="52"/>
+      <c r="I29" s="52"/>
+      <c r="J29" s="52"/>
+      <c r="K29" s="52"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B30" s="8"/>
       <c r="C30" s="10"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="G30" s="47"/>
-      <c r="H30" s="47"/>
-      <c r="I30" s="47"/>
-      <c r="J30" s="47"/>
-      <c r="K30" s="47"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="44" t="s">
+      <c r="A31" s="50" t="s">
         <v>132</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="7"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="47"/>
-      <c r="J31" s="47"/>
-      <c r="K31" s="47"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="52"/>
+      <c r="K31" s="52"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="44"/>
+      <c r="A32" s="50"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6" t="s">
         <v>126</v>
@@ -4512,14 +4611,14 @@
       <c r="E32" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G32" s="47"/>
-      <c r="H32" s="47"/>
-      <c r="I32" s="47"/>
-      <c r="J32" s="47"/>
-      <c r="K32" s="47"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="44"/>
+      <c r="A33" s="50"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8" t="s">
         <v>127</v>
@@ -4530,14 +4629,14 @@
       <c r="E33" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G33" s="47"/>
-      <c r="H33" s="47"/>
-      <c r="I33" s="47"/>
-      <c r="J33" s="47"/>
-      <c r="K33" s="47"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="52"/>
+      <c r="J33" s="52"/>
+      <c r="K33" s="52"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="44"/>
+      <c r="A34" s="50"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8" t="s">
         <v>128</v>
@@ -4546,14 +4645,14 @@
         <v>5</v>
       </c>
       <c r="E34" s="9"/>
-      <c r="G34" s="47"/>
-      <c r="H34" s="47"/>
-      <c r="I34" s="47"/>
-      <c r="J34" s="47"/>
-      <c r="K34" s="47"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="52"/>
+      <c r="K34" s="52"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="44"/>
+      <c r="A35" s="50"/>
       <c r="C35" t="s">
         <v>133</v>
       </c>
@@ -4563,7 +4662,7 @@
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="44"/>
+      <c r="A36" s="50"/>
       <c r="C36" t="s">
         <v>136</v>
       </c>
@@ -4575,7 +4674,7 @@
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="44"/>
+      <c r="A37" s="50"/>
       <c r="C37" t="s">
         <v>169</v>
       </c>
@@ -4585,7 +4684,7 @@
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="44"/>
+      <c r="A38" s="50"/>
       <c r="C38" t="s">
         <v>170</v>
       </c>
@@ -4595,7 +4694,7 @@
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="44"/>
+      <c r="A39" s="50"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6" t="s">
         <v>9</v>
@@ -4609,10 +4708,10 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="44"/>
+      <c r="A40" s="50"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D40" s="6">
         <f>POWER(D10, 2)*D37</f>
@@ -4623,7 +4722,7 @@
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="44"/>
+      <c r="A41" s="50"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6" t="s">
         <v>171</v>
@@ -4635,7 +4734,7 @@
       <c r="E41" s="6"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="44"/>
+      <c r="A42" s="50"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
         <v>172</v>
@@ -4647,10 +4746,10 @@
       <c r="E42" s="6"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="44"/>
+      <c r="A43" s="50"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D43" s="6">
         <f>POWER(D11, 2)*D37</f>
@@ -4661,7 +4760,7 @@
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="44"/>
+      <c r="A44" s="50"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6" t="s">
         <v>27</v>
@@ -4675,10 +4774,10 @@
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="44"/>
+      <c r="A45" s="50"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D45" s="11">
         <v>3</v>
@@ -4688,10 +4787,10 @@
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="44"/>
+      <c r="A46" s="50"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D46" t="b">
         <f>D45/D4&gt;=D41</f>
@@ -4700,10 +4799,10 @@
       <c r="E46" s="6"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="44"/>
+      <c r="A47" s="50"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D47" s="11">
         <f>D45*D34/D4</f>
@@ -4712,17 +4811,17 @@
       <c r="E47" s="6"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="44"/>
+      <c r="A48" s="50"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
       <c r="D48" s="11"/>
       <c r="E48" s="6"/>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A49" s="44"/>
+      <c r="A49" s="50"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="D49" s="13">
         <f>22000</f>
@@ -4731,10 +4830,10 @@
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A50" s="44"/>
+      <c r="A50" s="50"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D50" s="13">
         <v>0.1</v>
@@ -4742,10 +4841,10 @@
       <c r="E50" s="8"/>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A51" s="44"/>
+      <c r="A51" s="50"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D51" s="13">
         <v>0.06</v>
@@ -4753,10 +4852,10 @@
       <c r="E51" s="8"/>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A52" s="44"/>
+      <c r="A52" s="50"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D52" s="13">
         <f>PI()*D51*D51/4</f>
@@ -4765,22 +4864,22 @@
       <c r="E52" s="8"/>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A53" s="44"/>
-      <c r="B53" s="52"/>
-      <c r="C53" s="52" t="s">
+      <c r="A53" s="50"/>
+      <c r="B53" s="44"/>
+      <c r="C53" s="44" t="s">
         <v>200</v>
       </c>
-      <c r="D53" s="53">
+      <c r="D53" s="45">
         <f>D49*D50/D52</f>
         <v>778090.83289371058</v>
       </c>
-      <c r="E53" s="52"/>
+      <c r="E53" s="44"/>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A54" s="44"/>
+      <c r="A54" s="50"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D54" s="11">
         <f>D51*D52</f>
@@ -4789,23 +4888,23 @@
       <c r="E54" s="6"/>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A55" s="44"/>
+      <c r="A55" s="50"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="D55" s="11">
         <v>3990</v>
       </c>
-      <c r="E55" s="54" t="s">
-        <v>782</v>
+      <c r="E55" s="46" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A56" s="44"/>
+      <c r="A56" s="50"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D56" s="11">
         <v>1020</v>
@@ -4813,10 +4912,10 @@
       <c r="E56" s="6"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A57" s="44"/>
+      <c r="A57" s="50"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="D57" s="11">
         <f>D56*D54*D55</f>
@@ -4825,10 +4924,10 @@
       <c r="E57" s="6"/>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A58" s="44"/>
+      <c r="A58" s="50"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="D58" s="11">
         <f>20</f>
@@ -4837,10 +4936,10 @@
       <c r="E58" s="6"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A59" s="44"/>
+      <c r="A59" s="50"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="D59" s="11">
         <f>D58*D57</f>
@@ -4861,7 +4960,7 @@
       </c>
     </row>
     <row r="61" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="44" t="s">
+      <c r="A61" s="50" t="s">
         <v>30</v>
       </c>
       <c r="C61" s="8" t="s">
@@ -4871,7 +4970,7 @@
         <v>180</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P61" t="s">
         <v>80</v>
@@ -4885,7 +4984,7 @@
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A62" s="44"/>
+      <c r="A62" s="50"/>
       <c r="C62" s="8" t="s">
         <v>26</v>
       </c>
@@ -4907,7 +5006,7 @@
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A63" s="44"/>
+      <c r="A63" s="50"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6" t="s">
         <v>13</v>
@@ -4917,7 +5016,7 @@
         <v>5</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P63" t="s">
         <v>84</v>
@@ -4931,7 +5030,7 @@
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A64" s="44"/>
+      <c r="A64" s="50"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6" t="s">
         <v>14</v>
@@ -4952,7 +5051,7 @@
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A65" s="44"/>
+      <c r="A65" s="50"/>
       <c r="C65" s="8" t="s">
         <v>16</v>
       </c>
@@ -4975,7 +5074,7 @@
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A66" s="44"/>
+      <c r="A66" s="50"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6" t="s">
         <v>107</v>
@@ -4996,7 +5095,7 @@
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A67" s="44"/>
+      <c r="A67" s="50"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6" t="s">
         <v>15</v>
@@ -5017,7 +5116,7 @@
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A68" s="44"/>
+      <c r="A68" s="50"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6" t="s">
         <v>32</v>
@@ -5029,7 +5128,7 @@
       <c r="E68" s="6"/>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A69" s="44"/>
+      <c r="A69" s="50"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6" t="s">
         <v>108</v>
@@ -5048,7 +5147,7 @@
       <c r="E70" s="8"/>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A71" s="45" t="s">
+      <c r="A71" s="49" t="s">
         <v>109</v>
       </c>
       <c r="C71" s="6"/>
@@ -5056,7 +5155,7 @@
       <c r="E71" s="6"/>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A72" s="45"/>
+      <c r="A72" s="49"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6" t="s">
         <v>90</v>
@@ -5068,7 +5167,7 @@
       <c r="E72" s="6"/>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A73" s="45"/>
+      <c r="A73" s="49"/>
       <c r="B73" s="6" t="s">
         <v>124</v>
       </c>
@@ -5084,7 +5183,7 @@
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A74" s="45"/>
+      <c r="A74" s="49"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6" t="s">
         <v>135</v>
@@ -5096,7 +5195,7 @@
       <c r="E74" s="6"/>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A75" s="45"/>
+      <c r="A75" s="49"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6" t="s">
         <v>91</v>
@@ -5109,7 +5208,7 @@
       <c r="R75" s="1"/>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A76" s="45"/>
+      <c r="A76" s="49"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6" t="s">
         <v>92</v>
@@ -5121,7 +5220,7 @@
       <c r="E76" s="6"/>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A77" s="45"/>
+      <c r="A77" s="49"/>
       <c r="B77" s="6" t="s">
         <v>123</v>
       </c>
@@ -5135,7 +5234,7 @@
       <c r="E77" s="6"/>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A78" s="45"/>
+      <c r="A78" s="49"/>
       <c r="B78" s="6" t="s">
         <v>119</v>
       </c>
@@ -5149,7 +5248,7 @@
       <c r="E78" s="6"/>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A79" s="45"/>
+      <c r="A79" s="49"/>
       <c r="B79" s="6" t="s">
         <v>122</v>
       </c>
@@ -5163,7 +5262,7 @@
       <c r="E79" s="6"/>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A80" s="45"/>
+      <c r="A80" s="49"/>
       <c r="C80" t="s">
         <v>94</v>
       </c>
@@ -5172,7 +5271,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="45"/>
+      <c r="A81" s="49"/>
       <c r="C81" t="s">
         <v>95</v>
       </c>
@@ -5181,7 +5280,7 @@
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="45"/>
+      <c r="A82" s="49"/>
       <c r="C82" t="s">
         <v>96</v>
       </c>
@@ -5196,7 +5295,7 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="45"/>
+      <c r="A83" s="49"/>
       <c r="C83" t="s">
         <v>97</v>
       </c>
@@ -5206,7 +5305,7 @@
       <c r="G83" s="5"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="45"/>
+      <c r="A84" s="49"/>
       <c r="C84" t="s">
         <v>98</v>
       </c>
@@ -5215,7 +5314,7 @@
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="45"/>
+      <c r="A85" s="49"/>
       <c r="C85" t="s">
         <v>99</v>
       </c>
@@ -5224,7 +5323,7 @@
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="45"/>
+      <c r="A86" s="49"/>
       <c r="C86" t="s">
         <v>100</v>
       </c>
@@ -5233,7 +5332,7 @@
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="45"/>
+      <c r="A87" s="49"/>
       <c r="C87" t="s">
         <v>113</v>
       </c>
@@ -5242,7 +5341,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="45"/>
+      <c r="A88" s="49"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6" t="s">
         <v>110</v>
@@ -5254,7 +5353,7 @@
       <c r="E88" s="6"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="45"/>
+      <c r="A89" s="49"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6" t="s">
         <v>111</v>
@@ -5266,7 +5365,7 @@
       <c r="E89" s="6"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="45"/>
+      <c r="A90" s="49"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6" t="s">
         <v>112</v>
@@ -5278,7 +5377,7 @@
       <c r="E90" s="6"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="45"/>
+      <c r="A91" s="49"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6" t="s">
         <v>114</v>
@@ -5290,7 +5389,7 @@
       <c r="E91" s="6"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="45"/>
+      <c r="A92" s="49"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6" t="s">
         <v>115</v>
@@ -5302,7 +5401,7 @@
       <c r="E92" s="6"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="45"/>
+      <c r="A93" s="49"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6" t="s">
         <v>116</v>
@@ -5314,7 +5413,7 @@
       <c r="E93" s="6"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="45"/>
+      <c r="A94" s="49"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6" t="s">
         <v>117</v>
@@ -5326,7 +5425,7 @@
       <c r="E94" s="6"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="45"/>
+      <c r="A95" s="49"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6" t="s">
         <v>118</v>
@@ -5347,7 +5446,7 @@
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="44" t="s">
+      <c r="A98" s="50" t="s">
         <v>125</v>
       </c>
       <c r="B98" s="6" t="s">
@@ -5360,12 +5459,10 @@
         <f>D12/2</f>
         <v>7000</v>
       </c>
-      <c r="E98" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="E98" s="2"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="44"/>
+      <c r="A99" s="50"/>
       <c r="B99" t="s">
         <v>58</v>
       </c>
@@ -5377,16 +5474,16 @@
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="44"/>
+      <c r="A100" s="50"/>
       <c r="B100" t="s">
         <v>57</v>
       </c>
       <c r="D100">
-        <v>6.2679999999999995E-4</v>
+        <v>6.9999999999999999E-4</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="44"/>
+      <c r="A101" s="50"/>
       <c r="B101" t="s">
         <v>51</v>
       </c>
@@ -5398,7 +5495,7 @@
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="44"/>
+      <c r="A102" s="50"/>
       <c r="C102" t="s">
         <v>36</v>
       </c>
@@ -5407,7 +5504,7 @@
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="44"/>
+      <c r="A103" s="50"/>
       <c r="B103" t="s">
         <v>39</v>
       </c>
@@ -5419,12 +5516,12 @@
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="44"/>
+      <c r="A104" s="50"/>
       <c r="B104" t="s">
+        <v>578</v>
+      </c>
+      <c r="C104" s="35" t="s">
         <v>579</v>
-      </c>
-      <c r="C104" s="35" t="s">
-        <v>580</v>
       </c>
       <c r="D104" s="1">
         <f>D2/D3</f>
@@ -5432,7 +5529,7 @@
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="44"/>
+      <c r="A105" s="50"/>
       <c r="B105" t="s">
         <v>41</v>
       </c>
@@ -5445,7 +5542,7 @@
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="44"/>
+      <c r="A106" s="50"/>
       <c r="C106" t="s">
         <v>40</v>
       </c>
@@ -5455,7 +5552,7 @@
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="44"/>
+      <c r="A107" s="50"/>
       <c r="B107" t="s">
         <v>45</v>
       </c>
@@ -5468,7 +5565,7 @@
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="44"/>
+      <c r="A108" s="50"/>
       <c r="B108" t="s">
         <v>53</v>
       </c>
@@ -5481,7 +5578,7 @@
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="44"/>
+      <c r="A109" s="50"/>
       <c r="B109" t="s">
         <v>55</v>
       </c>
@@ -5490,11 +5587,11 @@
       </c>
       <c r="D109">
         <f>(D7 * D103) / (D108 * D100 * D3)</f>
-        <v>0.10885965835784052</v>
+        <v>9.7476048369563459E-2</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="44"/>
+      <c r="A110" s="50"/>
       <c r="C110" t="s">
         <v>60</v>
       </c>
@@ -5504,12 +5601,12 @@
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="44"/>
+      <c r="A111" s="50"/>
       <c r="B111" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C111" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D111">
         <f>D105/D113</f>
@@ -5517,12 +5614,12 @@
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="44"/>
+      <c r="A112" s="50"/>
       <c r="B112" t="s">
+        <v>581</v>
+      </c>
+      <c r="C112" t="s">
         <v>582</v>
-      </c>
-      <c r="C112" t="s">
-        <v>583</v>
       </c>
       <c r="D112">
         <f>1/D111</f>
@@ -5533,7 +5630,7 @@
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="44"/>
+      <c r="A113" s="50"/>
       <c r="B113" t="s">
         <v>64</v>
       </c>
@@ -5546,7 +5643,7 @@
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="44"/>
+      <c r="A114" s="50"/>
       <c r="C114" t="s">
         <v>66</v>
       </c>
@@ -5556,7 +5653,7 @@
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="44"/>
+      <c r="A115" s="50"/>
       <c r="B115" t="s">
         <v>68</v>
       </c>
@@ -5572,9 +5669,9 @@
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="44"/>
+      <c r="A116" s="50"/>
       <c r="B116" t="s">
-        <v>68</v>
+        <v>815</v>
       </c>
       <c r="C116" t="s">
         <v>69</v>
@@ -5583,9 +5680,12 @@
         <f>D107*POWER(D111,2)</f>
         <v>3.6</v>
       </c>
+      <c r="E116" t="s">
+        <v>816</v>
+      </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="44"/>
+      <c r="A117" s="50"/>
       <c r="B117" t="s">
         <v>174</v>
       </c>
@@ -5598,7 +5698,7 @@
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="44"/>
+      <c r="A118" s="50"/>
       <c r="C118" t="s">
         <v>176</v>
       </c>
@@ -5607,7 +5707,7 @@
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="44"/>
+      <c r="A119" s="50"/>
       <c r="C119" t="s">
         <v>227</v>
       </c>
@@ -5617,7 +5717,7 @@
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="44"/>
+      <c r="A120" s="50"/>
       <c r="C120" t="s">
         <v>187</v>
       </c>
@@ -5629,7 +5729,7 @@
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="44"/>
+      <c r="A121" s="50"/>
       <c r="C121" t="s">
         <v>185</v>
       </c>
@@ -5641,7 +5741,7 @@
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="44"/>
+      <c r="A122" s="50"/>
       <c r="C122" t="s">
         <v>184</v>
       </c>
@@ -5650,7 +5750,7 @@
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="44"/>
+      <c r="A123" s="50"/>
       <c r="C123" t="s">
         <v>178</v>
       </c>
@@ -5663,7 +5763,7 @@
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="44"/>
+      <c r="A124" s="50"/>
       <c r="C124" t="s">
         <v>179</v>
       </c>
@@ -5676,7 +5776,7 @@
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="44"/>
+      <c r="A125" s="50"/>
       <c r="C125" t="s">
         <v>180</v>
       </c>
@@ -5688,7 +5788,7 @@
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="44"/>
+      <c r="A126" s="50"/>
       <c r="C126" t="s">
         <v>189</v>
       </c>
@@ -5701,7 +5801,7 @@
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="44"/>
+      <c r="A127" s="50"/>
       <c r="C127" t="s">
         <v>181</v>
       </c>
@@ -5711,7 +5811,7 @@
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="44"/>
+      <c r="A128" s="50"/>
       <c r="C128" t="s">
         <v>182</v>
       </c>
@@ -5721,7 +5821,7 @@
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="44"/>
+      <c r="A129" s="50"/>
       <c r="C129" t="s">
         <v>177</v>
       </c>
@@ -5731,7 +5831,7 @@
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="44"/>
+      <c r="A130" s="50"/>
       <c r="C130" t="s">
         <v>183</v>
       </c>
@@ -5741,7 +5841,7 @@
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="44"/>
+      <c r="A131" s="50"/>
       <c r="C131" t="s">
         <v>195</v>
       </c>
@@ -5751,7 +5851,7 @@
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="44"/>
+      <c r="A132" s="50"/>
       <c r="C132" t="s">
         <v>194</v>
       </c>
@@ -5764,7 +5864,7 @@
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="44"/>
+      <c r="A133" s="50"/>
       <c r="C133" t="s">
         <v>186</v>
       </c>
@@ -5774,7 +5874,7 @@
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" s="44"/>
+      <c r="A134" s="50"/>
       <c r="C134" t="s">
         <v>188</v>
       </c>
@@ -5784,7 +5884,7 @@
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" s="44"/>
+      <c r="A135" s="50"/>
       <c r="C135" t="s">
         <v>189</v>
       </c>
@@ -5794,7 +5894,7 @@
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="44"/>
+      <c r="A136" s="50"/>
       <c r="C136" t="s">
         <v>190</v>
       </c>
@@ -5807,7 +5907,7 @@
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" s="44"/>
+      <c r="A137" s="50"/>
       <c r="C137" t="s">
         <v>191</v>
       </c>
@@ -5816,7 +5916,7 @@
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" s="44"/>
+      <c r="A138" s="50"/>
       <c r="C138" t="s">
         <v>193</v>
       </c>
@@ -5826,7 +5926,7 @@
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" s="44"/>
+      <c r="A139" s="50"/>
       <c r="C139" t="s">
         <v>225</v>
       </c>
@@ -5836,7 +5936,7 @@
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" s="44"/>
+      <c r="A140" s="50"/>
       <c r="C140" t="s">
         <v>201</v>
       </c>
@@ -5845,7 +5945,7 @@
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A141" s="44"/>
+      <c r="A141" s="50"/>
       <c r="C141" t="s">
         <v>200</v>
       </c>
@@ -5855,7 +5955,7 @@
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" s="44"/>
+      <c r="A142" s="50"/>
       <c r="C142" t="s">
         <v>202</v>
       </c>
@@ -5868,19 +5968,19 @@
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143" s="44"/>
+      <c r="A143" s="50"/>
       <c r="C143" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A144" s="44"/>
+      <c r="A144" s="50"/>
       <c r="C144" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" s="44"/>
+      <c r="A145" s="50"/>
       <c r="C145" t="s">
         <v>199</v>
       </c>
@@ -5892,7 +5992,7 @@
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A146" s="44"/>
+      <c r="A146" s="50"/>
       <c r="C146" t="s">
         <v>209</v>
       </c>
@@ -5902,7 +6002,7 @@
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" s="44"/>
+      <c r="A147" s="50"/>
       <c r="C147" t="s">
         <v>198</v>
       </c>
@@ -5911,7 +6011,7 @@
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" s="44"/>
+      <c r="A148" s="50"/>
       <c r="C148" t="s">
         <v>203</v>
       </c>
@@ -5920,7 +6020,7 @@
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149" s="44"/>
+      <c r="A149" s="50"/>
       <c r="C149" t="s">
         <v>204</v>
       </c>
@@ -5930,7 +6030,7 @@
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A150" s="44"/>
+      <c r="A150" s="50"/>
       <c r="C150" t="s">
         <v>189</v>
       </c>
@@ -5940,7 +6040,7 @@
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151" s="44"/>
+      <c r="A151" s="50"/>
       <c r="C151" t="s">
         <v>190</v>
       </c>
@@ -5950,7 +6050,7 @@
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A152" s="44"/>
+      <c r="A152" s="50"/>
       <c r="C152" t="s">
         <v>206</v>
       </c>
@@ -5963,7 +6063,7 @@
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153" s="44"/>
+      <c r="A153" s="50"/>
       <c r="C153" t="s">
         <v>207</v>
       </c>
@@ -5976,7 +6076,7 @@
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A154" s="44"/>
+      <c r="A154" s="50"/>
       <c r="C154" t="s">
         <v>208</v>
       </c>
@@ -5989,7 +6089,7 @@
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" s="44"/>
+      <c r="A155" s="50"/>
       <c r="C155" t="s">
         <v>210</v>
       </c>
@@ -6002,7 +6102,7 @@
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" s="44"/>
+      <c r="A156" s="50"/>
       <c r="C156" t="s">
         <v>211</v>
       </c>
@@ -6015,7 +6115,7 @@
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A157" s="44"/>
+      <c r="A157" s="50"/>
       <c r="C157" t="s">
         <v>201</v>
       </c>
@@ -6024,7 +6124,7 @@
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A158" s="44"/>
+      <c r="A158" s="50"/>
       <c r="C158" t="s">
         <v>215</v>
       </c>
@@ -6034,7 +6134,7 @@
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159" s="44"/>
+      <c r="A159" s="50"/>
       <c r="C159" t="s">
         <v>216</v>
       </c>
@@ -6044,7 +6144,7 @@
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A160" s="44"/>
+      <c r="A160" s="50"/>
       <c r="C160" t="s">
         <v>217</v>
       </c>
@@ -6057,7 +6157,7 @@
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A161" s="44"/>
+      <c r="A161" s="50"/>
       <c r="C161" t="s">
         <v>218</v>
       </c>
@@ -6067,7 +6167,7 @@
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A162" s="44"/>
+      <c r="A162" s="50"/>
       <c r="C162" t="s">
         <v>219</v>
       </c>
@@ -6077,7 +6177,7 @@
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A163" s="44"/>
+      <c r="A163" s="50"/>
       <c r="C163" t="s">
         <v>220</v>
       </c>
@@ -6087,7 +6187,7 @@
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A164" s="44"/>
+      <c r="A164" s="50"/>
       <c r="C164" t="s">
         <v>221</v>
       </c>
@@ -6097,7 +6197,7 @@
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A165" s="44"/>
+      <c r="A165" s="50"/>
       <c r="C165" t="s">
         <v>222</v>
       </c>
@@ -6107,7 +6207,7 @@
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A166" s="44"/>
+      <c r="A166" s="50"/>
       <c r="C166" t="s">
         <v>223</v>
       </c>
@@ -6120,18 +6220,18 @@
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A167" s="44"/>
+      <c r="A167" s="50"/>
       <c r="C167" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D167" s="23">
         <v>0.2</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A168" s="44"/>
+      <c r="A168" s="50"/>
       <c r="C168" t="s">
-        <v>229</v>
+        <v>814</v>
       </c>
       <c r="D168">
         <f>D167*D116</f>
@@ -6139,9 +6239,9 @@
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A169" s="44"/>
+      <c r="A169" s="50"/>
       <c r="C169" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D169">
         <f>D168/POWER(D111, 2)</f>
@@ -6152,11 +6252,11 @@
       <c r="A170" s="24"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A171" s="45" t="s">
-        <v>538</v>
+      <c r="A171" s="49" t="s">
+        <v>537</v>
       </c>
       <c r="B171" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D171">
         <f>D4</f>
@@ -6164,12 +6264,12 @@
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A172" s="45"/>
+      <c r="A172" s="49"/>
       <c r="B172" t="s">
         <v>50</v>
       </c>
       <c r="C172" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D172">
         <f>1/D111</f>
@@ -6177,7 +6277,7 @@
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A173" s="45"/>
+      <c r="A173" s="49"/>
       <c r="B173" t="s">
         <v>48</v>
       </c>
@@ -6187,7 +6287,7 @@
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A174" s="45"/>
+      <c r="A174" s="49"/>
       <c r="B174" t="s">
         <v>76</v>
       </c>
@@ -6197,21 +6297,21 @@
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A175" s="45"/>
+      <c r="A175" s="49"/>
       <c r="B175" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C175" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D175">
         <v>2.5</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A176" s="45"/>
+      <c r="A176" s="49"/>
       <c r="B176" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D176">
         <f>D105</f>
@@ -6219,9 +6319,9 @@
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A177" s="45"/>
+      <c r="A177" s="49"/>
       <c r="B177" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D177">
         <f>D169</f>
@@ -6229,9 +6329,9 @@
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A178" s="45"/>
+      <c r="A178" s="49"/>
       <c r="B178" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D178">
         <f>D174*D172</f>
@@ -6239,21 +6339,21 @@
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A179" s="45"/>
+      <c r="A179" s="49"/>
       <c r="B179" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D179">
         <v>10</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A180" s="45"/>
+      <c r="A180" s="49"/>
       <c r="B180" t="s">
         <v>228</v>
       </c>
       <c r="C180" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D180">
         <f>D175*D178</f>
@@ -6261,7 +6361,7 @@
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A181" s="45"/>
+      <c r="A181" s="49"/>
       <c r="B181" t="s">
         <v>39</v>
       </c>
@@ -6271,9 +6371,9 @@
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A182" s="45"/>
+      <c r="A182" s="49"/>
       <c r="B182" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D182">
         <f>0.5*D177*POWER(D176, 2)</f>
@@ -6281,9 +6381,9 @@
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A183" s="45"/>
+      <c r="A183" s="49"/>
       <c r="B183" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D183">
         <f>D176*D177/D180</f>
@@ -6291,9 +6391,9 @@
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A184" s="45"/>
+      <c r="A184" s="49"/>
       <c r="B184" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D184" t="b">
         <f>AND(D183&gt;0, D183&lt;((1-D181)/D173))</f>
@@ -6301,9 +6401,9 @@
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A185" s="45"/>
+      <c r="A185" s="49"/>
       <c r="B185" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D185">
         <f>D182*D173</f>
@@ -6311,9 +6411,9 @@
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A186" s="45"/>
+      <c r="A186" s="49"/>
       <c r="B186" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D186">
         <f>POWER(D180, 2)/D185</f>
@@ -6321,18 +6421,18 @@
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A187" s="45"/>
+      <c r="A187" s="49"/>
       <c r="B187" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D187">
         <v>330</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A188" s="45"/>
+      <c r="A188" s="49"/>
       <c r="B188" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D188">
         <f>POWER(D187*D185, 0.5)</f>
@@ -6340,9 +6440,9 @@
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A189" s="45"/>
+      <c r="A189" s="49"/>
       <c r="B189" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D189">
         <f>D188/D178</f>
@@ -6350,12 +6450,12 @@
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A190" s="45"/>
+      <c r="A190" s="49"/>
       <c r="B190" t="s">
+        <v>243</v>
+      </c>
+      <c r="C190" t="s">
         <v>244</v>
-      </c>
-      <c r="C190" t="s">
-        <v>245</v>
       </c>
       <c r="D190">
         <f>D185*D171</f>
@@ -6363,21 +6463,21 @@
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A191" s="45"/>
+      <c r="A191" s="49"/>
       <c r="B191" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C191" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D191">
         <v>0.5</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A192" s="45"/>
+      <c r="A192" s="49"/>
       <c r="B192" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D192">
         <f>D188/(D191*D187*D173)</f>
@@ -6385,39 +6485,39 @@
       </c>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A193" s="45"/>
+      <c r="A193" s="49"/>
       <c r="B193" t="s">
+        <v>293</v>
+      </c>
+      <c r="C193" t="s">
         <v>294</v>
-      </c>
-      <c r="C193" t="s">
-        <v>295</v>
       </c>
       <c r="D193" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A194" s="45"/>
+      <c r="A194" s="49"/>
       <c r="B194" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D194" s="1">
         <v>6.0000000000000002E-6</v>
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A195" s="45"/>
+      <c r="A195" s="49"/>
       <c r="B195" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D195" s="1">
         <v>4.1000000000000003E-3</v>
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A196" s="45"/>
+      <c r="A196" s="49"/>
       <c r="B196" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D196" s="1">
         <f>D194*D193</f>
@@ -6425,9 +6525,9 @@
       </c>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A197" s="45"/>
+      <c r="A197" s="49"/>
       <c r="B197" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D197" s="1">
         <f>D195/D193</f>
@@ -6435,53 +6535,53 @@
       </c>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A198" s="45"/>
+      <c r="A198" s="49"/>
       <c r="B198" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C198" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D198">
         <f>D188/(D196*(D187*D173))</f>
         <v>0.36266178324103715</v>
       </c>
       <c r="H198" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I198" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="J198" t="s">
+        <v>526</v>
+      </c>
+      <c r="K198" t="s">
+        <v>524</v>
+      </c>
+      <c r="L198" t="s">
+        <v>525</v>
+      </c>
+      <c r="M198" t="s">
         <v>527</v>
       </c>
-      <c r="K198" t="s">
-        <v>525</v>
-      </c>
-      <c r="L198" t="s">
-        <v>526</v>
-      </c>
-      <c r="M198" t="s">
+      <c r="N198" t="s">
         <v>528</v>
       </c>
-      <c r="N198" t="s">
-        <v>529</v>
-      </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A199" s="45"/>
+      <c r="A199" s="49"/>
       <c r="B199" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D199" s="1">
         <f>D176*D197</f>
         <v>9.2655367231638426E-3</v>
       </c>
       <c r="E199" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G199" s="5" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H199">
         <v>27</v>
@@ -6509,16 +6609,16 @@
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A200" s="45"/>
+      <c r="A200" s="49"/>
       <c r="B200" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D200" s="1">
         <f>D199+D198</f>
         <v>0.37192731996420098</v>
       </c>
       <c r="G200" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H200">
         <v>47</v>
@@ -6546,16 +6646,16 @@
       </c>
     </row>
     <row r="201" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="45"/>
+      <c r="A201" s="49"/>
       <c r="B201" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D201" s="1">
         <f>POWER(D199, 2)/D197</f>
         <v>0.20939066041048232</v>
       </c>
       <c r="G201" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H201">
         <v>8</v>
@@ -6583,16 +6683,16 @@
       </c>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A202" s="45"/>
+      <c r="A202" s="49"/>
       <c r="B202" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D202" s="1">
         <f>D201/D193</f>
         <v>2.0939066041048233E-2</v>
       </c>
       <c r="G202" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H202">
         <v>12</v>
@@ -6620,19 +6720,19 @@
       </c>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A203" s="45"/>
+      <c r="A203" s="49"/>
       <c r="B203" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D203" s="1">
         <f>2*PI()*D173*D196*D198</f>
         <v>2.1875243404182072</v>
       </c>
       <c r="E203" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G203" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H203">
         <v>6</v>
@@ -6657,19 +6757,19 @@
       </c>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A204" s="45"/>
+      <c r="A204" s="49"/>
       <c r="B204" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D204">
         <f>2*D203</f>
         <v>4.3750486808364144</v>
       </c>
       <c r="E204" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G204" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H204">
         <v>5.6</v>
@@ -6694,16 +6794,16 @@
       </c>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A205" s="45"/>
+      <c r="A205" s="49"/>
       <c r="B205" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D205" s="1">
         <f>D204/D193</f>
         <v>0.43750486808364142</v>
       </c>
       <c r="G205" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H205">
         <v>5</v>
@@ -6727,9 +6827,9 @@
       </c>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A206" s="45"/>
+      <c r="A206" s="49"/>
       <c r="B206" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D206" s="1">
         <f>D176*D4</f>
@@ -6737,9 +6837,9 @@
       </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A207" s="45"/>
+      <c r="A207" s="49"/>
       <c r="B207" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D207" s="1">
         <f>D182</f>
@@ -6747,16 +6847,16 @@
       </c>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A208" s="45"/>
+      <c r="A208" s="49"/>
       <c r="B208" t="s">
+        <v>301</v>
+      </c>
+      <c r="D208" s="1"/>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209" s="49"/>
+      <c r="B209" t="s">
         <v>302</v>
-      </c>
-      <c r="D208" s="1"/>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A209" s="45"/>
-      <c r="B209" t="s">
-        <v>303</v>
       </c>
       <c r="D209" s="1">
         <f>D182*D173</f>
@@ -6764,27 +6864,27 @@
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A210" s="45"/>
+      <c r="A210" s="49"/>
       <c r="B210" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D210">
         <v>2.85</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A211" s="45"/>
+      <c r="A211" s="49"/>
       <c r="C211" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D211">
         <v>200</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A212" s="45"/>
+      <c r="A212" s="49"/>
       <c r="C212" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D212">
         <f>(D211+D7)/D210</f>
@@ -6792,30 +6892,30 @@
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A213" s="45"/>
+      <c r="A213" s="49"/>
       <c r="C213" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D213" s="1">
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A214" s="45"/>
+      <c r="A214" s="49"/>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A215" s="45"/>
+      <c r="A215" s="49"/>
       <c r="B215" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D215">
         <v>500000</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A216" s="45"/>
+      <c r="A216" s="49"/>
       <c r="B216" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D216">
         <f>D215/D212</f>
@@ -6823,18 +6923,18 @@
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A217" s="45"/>
+      <c r="A217" s="49"/>
       <c r="B217" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D217">
         <v>6800</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A218" s="45"/>
+      <c r="A218" s="49"/>
       <c r="B218" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D218">
         <f>D215+D217</f>
@@ -6842,9 +6942,9 @@
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A219" s="45"/>
+      <c r="A219" s="49"/>
       <c r="B219" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D219">
         <f>D211/D218</f>
@@ -6855,9 +6955,9 @@
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A220" s="45"/>
+      <c r="A220" s="49"/>
       <c r="B220" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D220">
         <f>POWER(D219, 2)*D215</f>
@@ -6868,9 +6968,9 @@
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A221" s="45"/>
+      <c r="A221" s="49"/>
       <c r="B221" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D221">
         <f>POWER(D219, 2)*D217</f>
@@ -6881,12 +6981,12 @@
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A222" s="45"/>
+      <c r="A222" s="49"/>
       <c r="B222" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D222">
         <f>D220+D221</f>
@@ -6897,9 +6997,9 @@
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A223" s="45"/>
+      <c r="A223" s="49"/>
       <c r="B223" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D223">
         <f>D211/100</f>
@@ -6907,9 +7007,9 @@
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A224" s="45"/>
+      <c r="A224" s="49"/>
       <c r="C224" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D224">
         <f>POWER(2, 12)</f>
@@ -6917,9 +7017,9 @@
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A225" s="45"/>
+      <c r="A225" s="49"/>
       <c r="C225" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D225">
         <f>3.3/D224</f>
@@ -6927,9 +7027,9 @@
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A226" s="45"/>
+      <c r="A226" s="49"/>
       <c r="C226" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D226">
         <f>D225*D212</f>
@@ -6943,35 +7043,35 @@
       <c r="A227" s="29"/>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A228" s="45" t="s">
-        <v>776</v>
+      <c r="A228" s="49" t="s">
+        <v>775</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A229" s="45"/>
+      <c r="A229" s="49"/>
       <c r="B229" t="s">
+        <v>576</v>
+      </c>
+      <c r="C229" t="s">
         <v>577</v>
       </c>
-      <c r="C229" t="s">
-        <v>578</v>
-      </c>
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A230" s="45"/>
+      <c r="A230" s="49"/>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A231" s="45"/>
+      <c r="A231" s="49"/>
       <c r="B231" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D231">
         <v>2.5</v>
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A232" s="45"/>
+      <c r="A232" s="49"/>
       <c r="B232" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C232" s="34"/>
       <c r="D232">
@@ -7008,9 +7108,9 @@
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A233" s="45"/>
+      <c r="A233" s="49"/>
       <c r="B233" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C233" s="34"/>
       <c r="D233">
@@ -7047,9 +7147,9 @@
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A234" s="45"/>
+      <c r="A234" s="49"/>
       <c r="B234" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C234" s="34"/>
       <c r="D234">
@@ -7086,12 +7186,12 @@
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A235" s="45"/>
+      <c r="A235" s="49"/>
       <c r="B235" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C235" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D235">
         <f>100</f>
@@ -7127,12 +7227,12 @@
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A236" s="45"/>
+      <c r="A236" s="49"/>
       <c r="B236" t="s">
+        <v>549</v>
+      </c>
+      <c r="C236" t="s">
         <v>550</v>
-      </c>
-      <c r="C236" t="s">
-        <v>551</v>
       </c>
       <c r="D236">
         <f>D7</f>
@@ -7168,12 +7268,12 @@
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A237" s="45"/>
+      <c r="A237" s="49"/>
       <c r="B237" t="s">
+        <v>551</v>
+      </c>
+      <c r="C237" t="s">
         <v>552</v>
-      </c>
-      <c r="C237" t="s">
-        <v>553</v>
       </c>
       <c r="D237">
         <f>D174</f>
@@ -7206,9 +7306,9 @@
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A238" s="45"/>
+      <c r="A238" s="49"/>
       <c r="B238" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C238" s="34"/>
       <c r="D238">
@@ -7245,7 +7345,7 @@
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A239" s="45"/>
+      <c r="A239" s="49"/>
       <c r="B239" t="s">
         <v>48</v>
       </c>
@@ -7283,7 +7383,7 @@
       </c>
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A240" s="45"/>
+      <c r="A240" s="49"/>
       <c r="B240" t="s">
         <v>39</v>
       </c>
@@ -7321,16 +7421,16 @@
       </c>
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A241" s="45"/>
+      <c r="A241" s="49"/>
       <c r="C241" s="34"/>
     </row>
     <row r="242" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A242" s="45"/>
+      <c r="A242" s="49"/>
       <c r="B242" t="s">
+        <v>558</v>
+      </c>
+      <c r="C242" s="34" t="s">
         <v>559</v>
-      </c>
-      <c r="C242" s="34" t="s">
-        <v>560</v>
       </c>
       <c r="D242">
         <v>40</v>
@@ -7362,12 +7462,12 @@
       </c>
     </row>
     <row r="243" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A243" s="45"/>
+      <c r="A243" s="49"/>
       <c r="B243" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C243" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D243">
         <f>D232*POWER(D234, 2)/(2*POWER(D235-D236-(D237*D238), 2))</f>
@@ -7375,12 +7475,12 @@
       </c>
     </row>
     <row r="244" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A244" s="45"/>
+      <c r="A244" s="49"/>
       <c r="B244" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C244" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D244" s="1">
         <f>(0.22*0.000001)*6</f>
@@ -7417,12 +7517,12 @@
       <c r="L244" s="1"/>
     </row>
     <row r="245" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A245" s="45"/>
+      <c r="A245" s="49"/>
       <c r="B245" t="s">
+        <v>554</v>
+      </c>
+      <c r="C245" s="34" t="s">
         <v>555</v>
-      </c>
-      <c r="C245" s="34" t="s">
-        <v>556</v>
       </c>
       <c r="D245">
         <f>POWER(D240/(PI()*D239), 2)/D244</f>
@@ -7458,12 +7558,12 @@
       </c>
     </row>
     <row r="246" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A246" s="45"/>
+      <c r="A246" s="49"/>
       <c r="B246" t="s">
+        <v>556</v>
+      </c>
+      <c r="C246" s="34" t="s">
         <v>557</v>
-      </c>
-      <c r="C246" s="34" t="s">
-        <v>558</v>
       </c>
       <c r="D246">
         <f>(POWER(D242, 2)-POWER(POWER(D242, 4) - POWER(PI()*POWER(D236, 2)*D244/(D233+D232), 2), 0.5))/((D244/2)*POWER(PI()*D236/(D233+D232), 2))</f>
@@ -7499,12 +7599,12 @@
       </c>
     </row>
     <row r="247" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A247" s="45"/>
+      <c r="A247" s="49"/>
       <c r="B247" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C247" s="34" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D247" s="1">
         <v>1.5E-5</v>
@@ -7539,12 +7639,12 @@
       </c>
     </row>
     <row r="248" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A248" s="45"/>
+      <c r="A248" s="49"/>
       <c r="B248" t="s">
+        <v>563</v>
+      </c>
+      <c r="C248" s="34" t="s">
         <v>564</v>
-      </c>
-      <c r="C248" s="34" t="s">
-        <v>565</v>
       </c>
       <c r="D248" t="b">
         <f>AND(D247&gt;D246, D247&lt;D245)</f>
@@ -7580,18 +7680,18 @@
       </c>
     </row>
     <row r="249" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A249" s="45"/>
+      <c r="A249" s="49"/>
       <c r="B249" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D249">
         <v>8.4999999999999995E-4</v>
       </c>
     </row>
     <row r="250" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A250" s="45"/>
+      <c r="A250" s="49"/>
       <c r="B250" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D250">
         <f>POWER(D234, 2)*D232/2</f>
@@ -7599,12 +7699,12 @@
       </c>
     </row>
     <row r="251" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A251" s="45"/>
+      <c r="A251" s="49"/>
       <c r="B251" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C251" s="34" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D251">
         <f>POWER(D234/SQRT(3), 2)*D249</f>
@@ -7612,47 +7712,47 @@
       </c>
     </row>
     <row r="252" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A252" s="45"/>
+      <c r="A252" s="49"/>
       <c r="B252" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D252">
         <f>D232*D247/(D232+D247)</f>
         <v>5.9238739931172719E-6</v>
       </c>
       <c r="G252" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H252" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="I252" t="s">
+        <v>526</v>
+      </c>
+      <c r="J252" t="s">
+        <v>524</v>
+      </c>
+      <c r="K252" t="s">
+        <v>525</v>
+      </c>
+      <c r="L252" t="s">
         <v>527</v>
       </c>
-      <c r="J252" t="s">
-        <v>525</v>
-      </c>
-      <c r="K252" t="s">
-        <v>526</v>
-      </c>
-      <c r="L252" t="s">
+      <c r="M252" t="s">
         <v>528</v>
       </c>
-      <c r="M252" t="s">
-        <v>529</v>
-      </c>
     </row>
     <row r="253" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A253" s="45"/>
+      <c r="A253" s="49"/>
       <c r="B253" s="36" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D253" s="1">
         <f>1/POWER(D252*D244, 0.5)</f>
         <v>357610.39006916573</v>
       </c>
       <c r="F253" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G253">
         <v>2.2000000000000001E-3</v>
@@ -7680,9 +7780,9 @@
       </c>
     </row>
     <row r="254" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A254" s="45"/>
+      <c r="A254" s="49"/>
       <c r="B254" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D254">
         <f>POWER(2*D250/D252, 0.5)</f>
@@ -7690,9 +7790,9 @@
       </c>
     </row>
     <row r="255" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A255" s="45"/>
+      <c r="A255" s="49"/>
       <c r="B255" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D255">
         <f>D254</f>
@@ -7700,9 +7800,9 @@
       </c>
     </row>
     <row r="256" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A256" s="45"/>
+      <c r="A256" s="49"/>
       <c r="B256" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D256" s="1">
         <f>SQRT(D250*2/D244)</f>
@@ -7710,9 +7810,9 @@
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A257" s="45"/>
+      <c r="A257" s="49"/>
       <c r="B257" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D257" s="1">
         <f>D256+D7</f>
@@ -7720,9 +7820,9 @@
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A258" s="45"/>
+      <c r="A258" s="49"/>
       <c r="B258" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D258" s="1">
         <f>D256</f>
@@ -7730,9 +7830,9 @@
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A259" s="45"/>
+      <c r="A259" s="49"/>
       <c r="B259" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D259">
         <f>D231*D255</f>
@@ -7740,9 +7840,9 @@
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A260" s="45"/>
+      <c r="A260" s="49"/>
       <c r="B260" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D260">
         <f>D231*D255</f>
@@ -7750,9 +7850,9 @@
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A261" s="45"/>
+      <c r="A261" s="49"/>
       <c r="B261" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D261">
         <f>D231*D255</f>
@@ -7760,9 +7860,9 @@
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A262" s="45"/>
+      <c r="A262" s="49"/>
       <c r="B262" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D262" s="1">
         <f>D231*D257</f>
@@ -7770,9 +7870,9 @@
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A263" s="45"/>
+      <c r="A263" s="49"/>
       <c r="B263" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D263" s="1">
         <f>D231*D258</f>
@@ -7780,9 +7880,9 @@
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A264" s="45"/>
+      <c r="A264" s="49"/>
       <c r="B264" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D264" s="1">
         <f>D231*D256</f>
@@ -7790,18 +7890,18 @@
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A265" s="45"/>
+      <c r="A265" s="49"/>
       <c r="B265" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D265" s="1">
         <v>0.86</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A266" s="45"/>
+      <c r="A266" s="49"/>
       <c r="B266" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D266" s="1">
         <f>0.86</f>
@@ -7809,12 +7909,12 @@
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A267" s="45"/>
+      <c r="A267" s="49"/>
       <c r="B267" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C267" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D267" s="1">
         <f>D250*16000/4</f>
@@ -7822,12 +7922,12 @@
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A268" s="45"/>
+      <c r="A268" s="49"/>
       <c r="B268" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C268" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D268" s="1">
         <f>D267</f>
@@ -7835,27 +7935,27 @@
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A269" s="45"/>
+      <c r="A269" s="49"/>
       <c r="B269" t="s">
+        <v>603</v>
+      </c>
+      <c r="C269" t="s">
         <v>604</v>
-      </c>
-      <c r="C269" t="s">
-        <v>605</v>
       </c>
       <c r="D269">
         <v>0.5</v>
       </c>
       <c r="E269" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A270" s="45"/>
+      <c r="A270" s="49"/>
       <c r="B270" s="43" t="s">
+        <v>605</v>
+      </c>
+      <c r="C270" s="43" t="s">
         <v>606</v>
-      </c>
-      <c r="C270" s="43" t="s">
-        <v>607</v>
       </c>
       <c r="D270" s="43">
         <f>D250*2/POWER(D269, 2)</f>
@@ -7863,49 +7963,49 @@
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A271" s="45"/>
+      <c r="A271" s="49"/>
       <c r="C271" s="34"/>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A272" s="45"/>
+      <c r="A272" s="49"/>
       <c r="C272" s="34"/>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A273" s="45"/>
+      <c r="A273" s="49"/>
       <c r="C273" s="34"/>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A274" s="45"/>
+      <c r="A274" s="49"/>
       <c r="C274" s="34"/>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A275" s="45"/>
+      <c r="A275" s="49"/>
       <c r="C275" s="34"/>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A276" s="45"/>
+      <c r="A276" s="49"/>
       <c r="C276" s="34"/>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A277" s="45"/>
+      <c r="A277" s="49"/>
       <c r="C277" s="34"/>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A278" s="45"/>
+      <c r="A278" s="49"/>
       <c r="C278" s="34"/>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A279" s="45"/>
+      <c r="A279" s="49"/>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" s="37"/>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A281" s="45" t="s">
-        <v>609</v>
+      <c r="A281" s="49" t="s">
+        <v>608</v>
       </c>
       <c r="C281" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D281">
         <f>D223/D218</f>
@@ -7913,9 +8013,9 @@
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A282" s="45"/>
+      <c r="A282" s="49"/>
       <c r="C282" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D282">
         <f>(D223-(D215*D213))*(D217/(D217+D215))</f>
@@ -7923,9 +8023,9 @@
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A283" s="45"/>
+      <c r="A283" s="49"/>
       <c r="C283" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D283">
         <f>D223/D212</f>
@@ -7933,9 +8033,9 @@
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A284" s="45"/>
+      <c r="A284" s="49"/>
       <c r="C284" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D284">
         <f>ABS(D283-D282)/D283</f>
@@ -7943,9 +8043,9 @@
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A285" s="45"/>
+      <c r="A285" s="49"/>
       <c r="C285" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D285">
         <f>(D5-(D215*D213))*(D217/(D217+D215))</f>
@@ -7953,9 +8053,9 @@
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A286" s="45"/>
+      <c r="A286" s="49"/>
       <c r="C286" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D286">
         <f>D5/D212</f>
@@ -7963,9 +8063,9 @@
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A287" s="45"/>
+      <c r="A287" s="49"/>
       <c r="C287" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D287">
         <f>ABS(D286-D285)/D286</f>
@@ -7973,9 +8073,9 @@
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A288" s="45"/>
+      <c r="A288" s="49"/>
       <c r="C288" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D288">
         <f>(D286-D285)/D226</f>
@@ -7983,18 +8083,18 @@
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A289" s="45"/>
+      <c r="A289" s="49"/>
       <c r="B289" t="s">
+        <v>272</v>
+      </c>
+      <c r="C289" t="s">
         <v>273</v>
       </c>
-      <c r="C289" t="s">
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A290" s="49"/>
+      <c r="B290" t="s">
         <v>274</v>
-      </c>
-    </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A290" s="45"/>
-      <c r="B290" t="s">
-        <v>275</v>
       </c>
       <c r="D290">
         <f>(D215*D217)/(D215+D217)</f>
@@ -8002,9 +8102,9 @@
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A291" s="45"/>
+      <c r="A291" s="49"/>
       <c r="C291" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D291">
         <f>0.00000000001</f>
@@ -8012,12 +8112,12 @@
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A292" s="45"/>
+      <c r="A292" s="49"/>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A293" s="45"/>
+      <c r="A293" s="49"/>
       <c r="B293" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D293">
         <f>3.15/(0.000001)</f>
@@ -8025,9 +8125,9 @@
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A294" s="45"/>
+      <c r="A294" s="49"/>
       <c r="B294" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D294">
         <f>D291/((1/D290)+(1/D293))</f>
@@ -8035,9 +8135,9 @@
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A295" s="45"/>
+      <c r="A295" s="49"/>
       <c r="B295" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D295">
         <f>D210/0.012</f>
@@ -8045,21 +8145,21 @@
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A296" s="45"/>
+      <c r="A296" s="49"/>
       <c r="B296" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D296" s="25">
         <v>1000</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A297" s="45"/>
+      <c r="A297" s="49"/>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A298" s="45"/>
+      <c r="A298" s="49"/>
       <c r="B298" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D298">
         <f>D2/D5</f>
@@ -8067,21 +8167,21 @@
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A299" s="45"/>
+      <c r="A299" s="49"/>
       <c r="B299" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C299" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D299">
         <v>0.05</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A300" s="45"/>
+      <c r="A300" s="49"/>
       <c r="C300" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D300">
         <f>D298/(D3*D299)</f>
@@ -8089,9 +8189,9 @@
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A301" s="45"/>
+      <c r="A301" s="49"/>
       <c r="C301" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D301">
         <f>POWER(D7, 2)*D300/2</f>
@@ -8099,14 +8199,14 @@
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A302" s="45"/>
+      <c r="A302" s="49"/>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A303" s="44" t="s">
-        <v>608</v>
+      <c r="A303" s="50" t="s">
+        <v>607</v>
       </c>
       <c r="B303" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D303" s="1">
         <f>MAX(D333, 200)</f>
@@ -8114,27 +8214,27 @@
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A304" s="44"/>
+      <c r="A304" s="50"/>
       <c r="B304" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D304">
         <v>500000</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A305" s="44"/>
+      <c r="A305" s="50"/>
       <c r="B305" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D305">
         <v>6800</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A306" s="44"/>
+      <c r="A306" s="50"/>
       <c r="B306" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D306">
         <f>D304+D305</f>
@@ -8142,9 +8242,9 @@
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A307" s="44"/>
+      <c r="A307" s="50"/>
       <c r="B307" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D307" s="1">
         <f>D303/D306</f>
@@ -8152,9 +8252,9 @@
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A308" s="44"/>
+      <c r="A308" s="50"/>
       <c r="B308" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D308" s="1">
         <f>POWER(D307, 2)*D304</f>
@@ -8162,9 +8262,9 @@
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A309" s="44"/>
+      <c r="A309" s="50"/>
       <c r="B309" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D309" s="1">
         <f>POWER(D307, 2)*D305</f>
@@ -8172,9 +8272,9 @@
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A310" s="44"/>
+      <c r="A310" s="50"/>
       <c r="B310" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D310" s="1">
         <f>D308+D309</f>
@@ -8182,18 +8282,18 @@
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A311" s="44"/>
+      <c r="A311" s="50"/>
       <c r="C311" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D311">
         <v>2.7</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A312" s="44"/>
+      <c r="A312" s="50"/>
       <c r="C312" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D312" s="1">
         <f>D303/D311</f>
@@ -8201,9 +8301,9 @@
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A313" s="44"/>
+      <c r="A313" s="50"/>
       <c r="C313" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D313" s="1">
         <f>D306/D305</f>
@@ -8211,9 +8311,9 @@
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A314" s="44"/>
+      <c r="A314" s="50"/>
       <c r="C314" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D314" s="1" t="b">
         <f>MAX(D312, D313)/MIN(D312,D313)&lt;1.04</f>
@@ -8221,21 +8321,21 @@
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A315" s="44"/>
+      <c r="A315" s="50"/>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A316" s="44" t="s">
-        <v>585</v>
+      <c r="A316" s="50" t="s">
+        <v>584</v>
       </c>
       <c r="C316" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D316">
         <v>2</v>
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A317" s="44"/>
+      <c r="A317" s="50"/>
       <c r="B317" t="s">
         <v>38</v>
       </c>
@@ -8245,9 +8345,9 @@
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A318" s="44"/>
+      <c r="A318" s="50"/>
       <c r="B318" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D318">
         <v>10000</v>
@@ -8257,9 +8357,9 @@
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A319" s="44"/>
+      <c r="A319" s="50"/>
       <c r="C319" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D319">
         <f>D317*D316/D321</f>
@@ -8267,9 +8367,9 @@
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A320" s="44"/>
+      <c r="A320" s="50"/>
       <c r="B320" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D320">
         <f>D319*D318</f>
@@ -8280,27 +8380,27 @@
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A321" s="44"/>
+      <c r="A321" s="50"/>
       <c r="C321" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D321">
         <v>2.7</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A322" s="44"/>
+      <c r="A322" s="50"/>
       <c r="B322" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D322">
         <v>330000</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A323" s="44"/>
+      <c r="A323" s="50"/>
       <c r="B323" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D323" s="1">
         <v>1.0000000000000001E-9</v>
@@ -8310,9 +8410,9 @@
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A324" s="44"/>
+      <c r="A324" s="50"/>
       <c r="B324" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D324">
         <f>(D318*D322)/(D318+D322)</f>
@@ -8323,9 +8423,9 @@
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A325" s="44"/>
+      <c r="A325" s="50"/>
       <c r="B325" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D325">
         <f>POWER(D317*D316, 2)/(D318+D322)</f>
@@ -8340,8 +8440,8 @@
       <c r="E326" s="9"/>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A327" s="45" t="s">
-        <v>304</v>
+      <c r="A327" s="49" t="s">
+        <v>303</v>
       </c>
       <c r="B327" t="s">
         <v>48</v>
@@ -8355,7 +8455,7 @@
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A328" s="45"/>
+      <c r="A328" s="49"/>
       <c r="B328" t="s">
         <v>41</v>
       </c>
@@ -8368,7 +8468,7 @@
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A329" s="45"/>
+      <c r="A329" s="49"/>
       <c r="B329" t="s">
         <v>39</v>
       </c>
@@ -8377,9 +8477,9 @@
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A330" s="45"/>
+      <c r="A330" s="49"/>
       <c r="B330" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D330">
         <v>2.3E-2</v>
@@ -8389,9 +8489,9 @@
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A331" s="45"/>
+      <c r="A331" s="49"/>
       <c r="B331" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D331">
         <f>POWER(D328,2)*D329*D330/3</f>
@@ -8399,12 +8499,12 @@
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A332" s="45"/>
+      <c r="A332" s="49"/>
       <c r="B332" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C332" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D332" s="1">
         <f>D329*D328*D4</f>
@@ -8412,9 +8512,9 @@
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A333" s="45"/>
+      <c r="A333" s="49"/>
       <c r="B333" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D333" s="1">
         <f>D256+D7</f>
@@ -8425,9 +8525,9 @@
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A334" s="45"/>
+      <c r="A334" s="49"/>
       <c r="B334" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D334">
         <v>250</v>
@@ -8437,9 +8537,9 @@
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A335" s="45"/>
+      <c r="A335" s="49"/>
       <c r="C335" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D335" t="b">
         <f>D334&gt;=D333</f>
@@ -8447,42 +8547,42 @@
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A336" s="45"/>
+      <c r="A336" s="49"/>
       <c r="B336" t="s">
+        <v>309</v>
+      </c>
+      <c r="E336" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A337" s="49"/>
+      <c r="B337" t="s">
         <v>310</v>
       </c>
-      <c r="E336" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A337" s="45"/>
-      <c r="B337" t="s">
+      <c r="E337" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A338" s="49"/>
+      <c r="B338" t="s">
         <v>311</v>
       </c>
-      <c r="E337" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A338" s="45"/>
-      <c r="B338" t="s">
+      <c r="C338" t="s">
         <v>312</v>
-      </c>
-      <c r="C338" t="s">
-        <v>313</v>
       </c>
       <c r="D338" s="1">
         <v>4.9999999999999998E-8</v>
       </c>
       <c r="E338" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A339" s="45"/>
+      <c r="A339" s="49"/>
       <c r="B339" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D339">
         <f>D3*D338*2</f>
@@ -8493,12 +8593,12 @@
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A340" s="45"/>
+      <c r="A340" s="49"/>
       <c r="B340" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C340" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D340">
         <v>10</v>
@@ -8508,9 +8608,9 @@
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A341" s="45"/>
+      <c r="A341" s="49"/>
       <c r="B341" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D341">
         <v>5</v>
@@ -8520,57 +8620,57 @@
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A342" s="45"/>
+      <c r="A342" s="49"/>
       <c r="B342" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C342" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D342" s="1">
         <f>D338*D341/D340</f>
         <v>2.4999999999999999E-8</v>
       </c>
       <c r="E342" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A343" s="45"/>
+      <c r="A343" s="49"/>
       <c r="B343" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C343" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D343" s="1">
         <f>D342</f>
         <v>2.4999999999999999E-8</v>
       </c>
       <c r="E343" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A344" s="45"/>
+      <c r="A344" s="49"/>
       <c r="B344" t="s">
+        <v>323</v>
+      </c>
+      <c r="C344" t="s">
         <v>324</v>
-      </c>
-      <c r="C344" t="s">
-        <v>325</v>
       </c>
       <c r="D344" s="1">
         <f>D343</f>
         <v>2.4999999999999999E-8</v>
       </c>
       <c r="E344" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A345" s="45"/>
+      <c r="A345" s="49"/>
       <c r="C345" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D345">
         <f>D340/D341</f>
@@ -8581,9 +8681,9 @@
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A346" s="45"/>
+      <c r="A346" s="49"/>
       <c r="C346" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D346">
         <v>3</v>
@@ -8593,9 +8693,9 @@
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A347" s="45"/>
+      <c r="A347" s="49"/>
       <c r="C347" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D347">
         <f>D346/D4</f>
@@ -8606,9 +8706,9 @@
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A348" s="45"/>
+      <c r="A348" s="49"/>
       <c r="C348" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D348" t="b">
         <f>D345&lt;D347</f>
@@ -8616,12 +8716,12 @@
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A349" s="45"/>
+      <c r="A349" s="49"/>
       <c r="B349" t="s">
+        <v>346</v>
+      </c>
+      <c r="C349" t="s">
         <v>347</v>
-      </c>
-      <c r="C349" t="s">
-        <v>348</v>
       </c>
       <c r="D349" s="1">
         <f>D338*D340*D327</f>
@@ -8632,9 +8732,9 @@
       </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A350" s="45"/>
+      <c r="A350" s="49"/>
       <c r="B350" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D350">
         <f>D235+D7</f>
@@ -8645,9 +8745,9 @@
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A351" s="45"/>
+      <c r="A351" s="49"/>
       <c r="B351" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D351">
         <f>D328</f>
@@ -8658,9 +8758,9 @@
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A352" s="45"/>
+      <c r="A352" s="49"/>
       <c r="B352" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D352" s="1">
         <f>0.5*D350*D351*(D343+D344)*D3</f>
@@ -8671,9 +8771,9 @@
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A353" s="45"/>
+      <c r="A353" s="49"/>
       <c r="B353" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D353" s="1">
         <f>D331+D352</f>
@@ -8684,9 +8784,9 @@
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A354" s="45"/>
+      <c r="A354" s="49"/>
       <c r="B354" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D354">
         <v>1000</v>
@@ -8696,9 +8796,9 @@
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A355" s="45"/>
+      <c r="A355" s="49"/>
       <c r="B355" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D355">
         <v>2.5</v>
@@ -8708,12 +8808,12 @@
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A356" s="45"/>
+      <c r="A356" s="49"/>
       <c r="B356" t="s">
+        <v>334</v>
+      </c>
+      <c r="C356" t="s">
         <v>335</v>
-      </c>
-      <c r="C356" t="s">
-        <v>336</v>
       </c>
       <c r="D356">
         <v>210</v>
@@ -8723,25 +8823,25 @@
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A357" s="45"/>
+      <c r="A357" s="49"/>
       <c r="B357" t="s">
+        <v>331</v>
+      </c>
+      <c r="C357" t="s">
         <v>332</v>
-      </c>
-      <c r="C357" t="s">
-        <v>333</v>
       </c>
       <c r="D357" s="1">
         <f>-D354*(D338/D340)*LN(D355/D340)</f>
         <v>6.9314718055994534E-6</v>
       </c>
       <c r="E357" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A358" s="45"/>
+      <c r="A358" s="49"/>
       <c r="C358" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D358" s="1">
         <f>D328+(D7*D357/D107)</f>
@@ -8752,9 +8852,9 @@
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A359" s="45"/>
+      <c r="A359" s="49"/>
       <c r="B359" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D359">
         <v>60</v>
@@ -8764,9 +8864,9 @@
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A360" s="45"/>
+      <c r="A360" s="49"/>
       <c r="C360" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D360" t="b">
         <f>D358&lt;D356</f>
@@ -8774,9 +8874,9 @@
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A361" s="45"/>
+      <c r="A361" s="49"/>
       <c r="C361" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D361" t="b">
         <f>D358&lt;D359</f>
@@ -8784,12 +8884,12 @@
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A362" s="45"/>
+      <c r="A362" s="49"/>
       <c r="B362" t="s">
+        <v>339</v>
+      </c>
+      <c r="C362" t="s">
         <v>340</v>
-      </c>
-      <c r="C362" t="s">
-        <v>341</v>
       </c>
       <c r="D362">
         <f>0.5*POWER(D340, 2)/D354</f>
@@ -8803,11 +8903,11 @@
       <c r="A363" s="38"/>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A364" s="44" t="s">
-        <v>701</v>
+      <c r="A364" s="50" t="s">
+        <v>700</v>
       </c>
       <c r="B364" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D364" s="1">
         <f>D353</f>
@@ -8818,21 +8918,21 @@
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A365" s="44"/>
+      <c r="A365" s="50"/>
       <c r="C365" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D365">
         <v>0.9</v>
       </c>
       <c r="E365" s="39" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A366" s="50"/>
+      <c r="C366" t="s">
         <v>703</v>
-      </c>
-    </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A366" s="44"/>
-      <c r="C366" t="s">
-        <v>704</v>
       </c>
       <c r="D366">
         <v>0.15</v>
@@ -8842,9 +8942,9 @@
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A367" s="44"/>
+      <c r="A367" s="50"/>
       <c r="C367" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D367" s="1">
         <v>1.4999999999999999E-4</v>
@@ -8854,12 +8954,12 @@
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A368" s="44"/>
+      <c r="A368" s="50"/>
       <c r="B368" t="s">
+        <v>706</v>
+      </c>
+      <c r="C368" t="s">
         <v>707</v>
-      </c>
-      <c r="C368" t="s">
-        <v>708</v>
       </c>
       <c r="D368">
         <f>D366/(1000*D365*D367)</f>
@@ -8868,12 +8968,12 @@
       <c r="E368" s="40"/>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A369" s="44"/>
+      <c r="A369" s="50"/>
       <c r="B369" t="s">
+        <v>708</v>
+      </c>
+      <c r="C369" t="s">
         <v>709</v>
-      </c>
-      <c r="C369" t="s">
-        <v>710</v>
       </c>
       <c r="D369">
         <f>3.5+0.5</f>
@@ -8882,12 +8982,12 @@
       <c r="E369" s="40"/>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A370" s="44"/>
+      <c r="A370" s="50"/>
       <c r="B370" t="s">
+        <v>710</v>
+      </c>
+      <c r="C370" t="s">
         <v>711</v>
-      </c>
-      <c r="C370" t="s">
-        <v>712</v>
       </c>
       <c r="D370">
         <v>6.6665999999999999</v>
@@ -8895,9 +8995,9 @@
       <c r="E370" s="39"/>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A371" s="44"/>
+      <c r="A371" s="50"/>
       <c r="C371" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D371">
         <f>D368+D369+D370</f>
@@ -8906,12 +9006,12 @@
       <c r="E371" s="39"/>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A372" s="44"/>
+      <c r="A372" s="50"/>
       <c r="B372" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C372" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D372" s="1">
         <f>D371*D364</f>
@@ -8920,9 +9020,9 @@
       <c r="E372" s="39"/>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A373" s="44"/>
+      <c r="A373" s="50"/>
       <c r="C373" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D373">
         <v>35</v>
@@ -8930,9 +9030,9 @@
       <c r="E373" s="39"/>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A374" s="44"/>
+      <c r="A374" s="50"/>
       <c r="C374" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D374" s="1">
         <f>D373+D372</f>
@@ -8941,9 +9041,9 @@
       <c r="E374" s="39"/>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A375" s="44"/>
+      <c r="A375" s="50"/>
       <c r="C375" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D375">
         <v>150</v>
@@ -8951,9 +9051,9 @@
       <c r="E375" s="39"/>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A376" s="44"/>
+      <c r="A376" s="50"/>
       <c r="C376" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D376" t="b">
         <f>D374&lt;D375/D4</f>
@@ -8961,22 +9061,22 @@
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A377" s="44" t="s">
-        <v>719</v>
+      <c r="A377" s="50" t="s">
+        <v>718</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A378" s="44"/>
+      <c r="A378" s="50"/>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A379" s="44"/>
+      <c r="A379" s="50"/>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A380" s="44"/>
+      <c r="A380" s="50"/>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A381" s="45" t="s">
-        <v>351</v>
+      <c r="A381" s="49" t="s">
+        <v>350</v>
       </c>
       <c r="B381" t="s">
         <v>39</v>
@@ -8990,7 +9090,7 @@
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A382" s="45"/>
+      <c r="A382" s="49"/>
       <c r="B382" t="s">
         <v>48</v>
       </c>
@@ -9000,9 +9100,9 @@
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A383" s="45"/>
+      <c r="A383" s="49"/>
       <c r="B383" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D383">
         <f>D176</f>
@@ -9010,18 +9110,18 @@
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A384" s="45"/>
+      <c r="A384" s="49"/>
       <c r="C384" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D384">
         <v>2</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A385" s="45"/>
+      <c r="A385" s="49"/>
       <c r="C385" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D385">
         <f>D384*D383</f>
@@ -9029,24 +9129,24 @@
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A386" s="45"/>
+      <c r="A386" s="49"/>
       <c r="B386" t="s">
+        <v>351</v>
+      </c>
+      <c r="C386" t="s">
         <v>352</v>
-      </c>
-      <c r="C386" t="s">
-        <v>353</v>
       </c>
       <c r="D386">
         <v>1E-3</v>
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A387" s="45"/>
+      <c r="A387" s="49"/>
       <c r="B387" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C387" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D387">
         <f>D386*D383</f>
@@ -9054,12 +9154,12 @@
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A388" s="45"/>
+      <c r="A388" s="49"/>
       <c r="B388" t="s">
+        <v>403</v>
+      </c>
+      <c r="C388" t="s">
         <v>404</v>
-      </c>
-      <c r="C388" t="s">
-        <v>405</v>
       </c>
       <c r="D388">
         <f>POWER(D383, 2)*D386/3</f>
@@ -9067,12 +9167,12 @@
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A389" s="45"/>
+      <c r="A389" s="49"/>
       <c r="B389" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C389" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D389">
         <f>POWER(D385, 2)*D386/3</f>
@@ -9080,12 +9180,12 @@
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A390" s="45"/>
+      <c r="A390" s="49"/>
       <c r="B390" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C390" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D390">
         <f>D383*D386</f>
@@ -9093,12 +9193,12 @@
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A391" s="45"/>
+      <c r="A391" s="49"/>
       <c r="B391" t="s">
+        <v>360</v>
+      </c>
+      <c r="C391" t="s">
         <v>361</v>
-      </c>
-      <c r="C391" t="s">
-        <v>362</v>
       </c>
       <c r="D391">
         <f>D385*D386</f>
@@ -9106,9 +9206,9 @@
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A392" s="45"/>
+      <c r="A392" s="49"/>
       <c r="C392" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D392">
         <f>2.5</f>
@@ -9116,48 +9216,48 @@
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A393" s="45"/>
+      <c r="A393" s="49"/>
       <c r="B393" t="s">
+        <v>393</v>
+      </c>
+      <c r="C393" t="s">
         <v>394</v>
       </c>
-      <c r="C393" t="s">
+      <c r="D393" s="5" t="s">
         <v>395</v>
       </c>
-      <c r="D393" s="5" t="s">
-        <v>396</v>
-      </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A394" s="45"/>
+      <c r="A394" s="49"/>
       <c r="B394" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C394" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D394" s="1">
         <v>2.5000000000000001E-4</v>
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A395" s="45"/>
+      <c r="A395" s="49"/>
       <c r="B395" t="s">
+        <v>368</v>
+      </c>
+      <c r="C395" t="s">
         <v>369</v>
-      </c>
-      <c r="C395" t="s">
-        <v>370</v>
       </c>
       <c r="D395" s="1">
         <v>5.0000000000000001E-9</v>
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A396" s="45"/>
+      <c r="A396" s="49"/>
       <c r="B396" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C396" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D396" s="1">
         <v>10000000</v>
@@ -9167,55 +9267,55 @@
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A397" s="45"/>
+      <c r="A397" s="49"/>
       <c r="B397" t="s">
+        <v>372</v>
+      </c>
+      <c r="C397" t="s">
         <v>373</v>
-      </c>
-      <c r="C397" t="s">
-        <v>374</v>
       </c>
       <c r="D397" s="26">
         <v>7000</v>
       </c>
       <c r="E397" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A398" s="45"/>
+      <c r="A398" s="49"/>
       <c r="B398" t="s">
+        <v>374</v>
+      </c>
+      <c r="C398" t="s">
         <v>375</v>
-      </c>
-      <c r="C398" t="s">
-        <v>376</v>
       </c>
       <c r="D398" s="1">
         <f>D397*1000</f>
         <v>7000000</v>
       </c>
       <c r="E398" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A399" s="45"/>
+      <c r="A399" s="49"/>
       <c r="B399" s="27" t="s">
+        <v>378</v>
+      </c>
+      <c r="C399" t="s">
         <v>379</v>
-      </c>
-      <c r="C399" t="s">
-        <v>380</v>
       </c>
       <c r="D399" s="27">
         <v>70</v>
       </c>
       <c r="E399" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A400" s="49"/>
+      <c r="C400" t="s">
         <v>381</v>
-      </c>
-    </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A400" s="45"/>
-      <c r="C400" t="s">
-        <v>382</v>
       </c>
       <c r="D400">
         <f>D392/D391</f>
@@ -9223,12 +9323,12 @@
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A401" s="45"/>
+      <c r="A401" s="49"/>
       <c r="B401" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C401" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D401">
         <f>D400-1</f>
@@ -9236,9 +9336,9 @@
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A402" s="45"/>
+      <c r="A402" s="49"/>
       <c r="B402" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D402">
         <f>20*LOG10(D401)</f>
@@ -9246,18 +9346,18 @@
       </c>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A403" s="45"/>
+      <c r="A403" s="49"/>
       <c r="B403" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D403">
         <v>56000</v>
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A404" s="45"/>
+      <c r="A404" s="49"/>
       <c r="B404" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D404">
         <f>D403/D401</f>
@@ -9265,24 +9365,24 @@
       </c>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A405" s="45"/>
+      <c r="A405" s="49"/>
       <c r="B405" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C405" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D405">
         <v>1000</v>
       </c>
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A406" s="45"/>
+      <c r="A406" s="49"/>
       <c r="B406" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C406" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D406">
         <f>1+(D403/D405)</f>
@@ -9290,18 +9390,18 @@
       </c>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A407" s="45"/>
+      <c r="A407" s="49"/>
       <c r="C407" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D407">
         <v>1E-3</v>
       </c>
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A408" s="45"/>
+      <c r="A408" s="49"/>
       <c r="B408" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D408">
         <f>D403*(1+D407)</f>
@@ -9309,9 +9409,9 @@
       </c>
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A409" s="45"/>
+      <c r="A409" s="49"/>
       <c r="B409" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D409">
         <f>D403*(1-D407)</f>
@@ -9319,9 +9419,9 @@
       </c>
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A410" s="45"/>
+      <c r="A410" s="49"/>
       <c r="B410" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D410">
         <f>D405*(1+D407)</f>
@@ -9329,9 +9429,9 @@
       </c>
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A411" s="45"/>
+      <c r="A411" s="49"/>
       <c r="B411" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D411">
         <f>D405*(1-D407)</f>
@@ -9339,12 +9439,12 @@
       </c>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A412" s="45"/>
+      <c r="A412" s="49"/>
       <c r="B412" t="s">
+        <v>412</v>
+      </c>
+      <c r="C412" t="s">
         <v>413</v>
-      </c>
-      <c r="C412" t="s">
-        <v>414</v>
       </c>
       <c r="D412">
         <f>1+(D408/D411)</f>
@@ -9352,12 +9452,12 @@
       </c>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A413" s="45"/>
+      <c r="A413" s="49"/>
       <c r="B413" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C413" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D413">
         <f>1+(D409/D410)</f>
@@ -9365,9 +9465,9 @@
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A414" s="45"/>
+      <c r="A414" s="49"/>
       <c r="C414" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D414">
         <f>MAX(ABS((D412-D406)/D406), ABS((D413-D406)/D406))</f>
@@ -9375,9 +9475,9 @@
       </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A415" s="45"/>
+      <c r="A415" s="49"/>
       <c r="C415" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D415">
         <f>100*D414</f>
@@ -9388,9 +9488,9 @@
       </c>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A416" s="45"/>
+      <c r="A416" s="49"/>
       <c r="B416" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D416">
         <f>20*LOG10(D406)</f>
@@ -9398,9 +9498,9 @@
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A417" s="45"/>
+      <c r="A417" s="49"/>
       <c r="C417" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D417" t="b">
         <f>ABS((D406-D400)/D400)&lt;0.02</f>
@@ -9408,9 +9508,9 @@
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A418" s="45"/>
+      <c r="A418" s="49"/>
       <c r="C418" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D418" t="b">
         <f>D399&gt;D416</f>
@@ -9418,12 +9518,12 @@
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A419" s="45"/>
+      <c r="A419" s="49"/>
       <c r="B419" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C419" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D419" s="1">
         <f>D394/D386</f>
@@ -9431,9 +9531,9 @@
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A420" s="45"/>
+      <c r="A420" s="49"/>
       <c r="C420" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D420" s="1">
         <f>D383/20</f>
@@ -9441,9 +9541,9 @@
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A421" s="45"/>
+      <c r="A421" s="49"/>
       <c r="C421" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D421" s="1" t="b">
         <f>D419&lt;D420</f>
@@ -9451,9 +9551,9 @@
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A422" s="45"/>
+      <c r="A422" s="49"/>
       <c r="B422" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D422">
         <f>D396/D406</f>
@@ -9461,9 +9561,9 @@
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A423" s="45"/>
+      <c r="A423" s="49"/>
       <c r="C423" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D423">
         <f>D382*D406</f>
@@ -9471,9 +9571,9 @@
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A424" s="45"/>
+      <c r="A424" s="49"/>
       <c r="C424" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D424" t="b">
         <f>D422&gt;=D3</f>
@@ -9481,38 +9581,38 @@
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A425" s="45"/>
+      <c r="A425" s="49"/>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A426" s="45"/>
+      <c r="A426" s="49"/>
       <c r="C426" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D426">
         <f>D392*D382/D381</f>
         <v>80000</v>
       </c>
       <c r="E426" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A427" s="45"/>
+      <c r="A427" s="49"/>
       <c r="C427" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D427">
         <f>D426/1000</f>
         <v>80</v>
       </c>
       <c r="E427" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A428" s="45"/>
+      <c r="A428" s="49"/>
       <c r="C428" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D428" t="b">
         <f>D426&lt;=D398</f>
@@ -9520,9 +9620,9 @@
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A429" s="45"/>
+      <c r="A429" s="49"/>
       <c r="B429" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D429">
         <f>(D403*D405)/(D403+D405)</f>
@@ -9530,9 +9630,9 @@
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A430" s="45"/>
+      <c r="A430" s="49"/>
       <c r="B430" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D430">
         <f>D386</f>
@@ -9540,18 +9640,18 @@
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A431" s="45"/>
+      <c r="A431" s="49"/>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A432" s="45"/>
+      <c r="A432" s="49"/>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A433" s="45"/>
+      <c r="A433" s="49"/>
       <c r="B433" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C433" s="28" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D433">
         <f>D395*(D429-D430)</f>
@@ -9562,12 +9662,12 @@
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A434" s="45"/>
+      <c r="A434" s="49"/>
       <c r="B434" t="s">
+        <v>409</v>
+      </c>
+      <c r="C434" t="s">
         <v>410</v>
-      </c>
-      <c r="C434" t="s">
-        <v>411</v>
       </c>
       <c r="D434" s="1">
         <f>D406*D394</f>
@@ -9575,9 +9675,9 @@
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A435" s="45"/>
+      <c r="A435" s="49"/>
       <c r="B435" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D435" s="1">
         <f>D434+D433</f>
@@ -9585,12 +9685,12 @@
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A436" s="45"/>
+      <c r="A436" s="49"/>
       <c r="B436" t="s">
+        <v>422</v>
+      </c>
+      <c r="C436" t="s">
         <v>423</v>
-      </c>
-      <c r="C436" t="s">
-        <v>424</v>
       </c>
       <c r="D436">
         <f>D386*D406</f>
@@ -9598,9 +9698,9 @@
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A437" s="45"/>
+      <c r="A437" s="49"/>
       <c r="B437" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D437">
         <f>D436*D414</f>
@@ -9608,9 +9708,9 @@
       </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A438" s="45"/>
+      <c r="A438" s="49"/>
       <c r="B438" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D438" s="1">
         <f>D437+D435</f>
@@ -9618,9 +9718,9 @@
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A439" s="45"/>
+      <c r="A439" s="49"/>
       <c r="B439" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D439" s="1">
         <f>(D437*D383)+D435</f>
@@ -9628,9 +9728,9 @@
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A440" s="45"/>
+      <c r="A440" s="49"/>
       <c r="B440" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D440" s="1">
         <f>(D437*D385)+D435</f>
@@ -9638,9 +9738,9 @@
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A441" s="45"/>
+      <c r="A441" s="49"/>
       <c r="C441" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D441">
         <f>1/D436</f>
@@ -9648,9 +9748,9 @@
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A442" s="45"/>
+      <c r="A442" s="49"/>
       <c r="B442" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D442" s="1">
         <f>D438*D439</f>
@@ -9658,9 +9758,9 @@
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A443" s="45"/>
+      <c r="A443" s="49"/>
       <c r="B443" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D443" s="1">
         <f>D439*D441</f>
@@ -9668,9 +9768,9 @@
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A444" s="45"/>
+      <c r="A444" s="49"/>
       <c r="B444" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D444" s="1">
         <f>D440*D441</f>
@@ -9678,9 +9778,9 @@
       </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A445" s="45"/>
+      <c r="A445" s="49"/>
       <c r="B445" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D445" s="1">
         <f>D442*100</f>
@@ -9691,9 +9791,9 @@
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A446" s="45"/>
+      <c r="A446" s="49"/>
       <c r="B446" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D446" s="1">
         <f>(D443/D383)*100</f>
@@ -9704,9 +9804,9 @@
       </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A447" s="45"/>
+      <c r="A447" s="49"/>
       <c r="B447" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D447">
         <f>(D444/D385)*100</f>
@@ -9717,8 +9817,8 @@
       </c>
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A449" s="45" t="s">
-        <v>452</v>
+      <c r="A449" s="49" t="s">
+        <v>451</v>
       </c>
       <c r="B449" t="s">
         <v>48</v>
@@ -9732,12 +9832,12 @@
       </c>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A450" s="45"/>
+      <c r="A450" s="49"/>
       <c r="B450" t="s">
         <v>41</v>
       </c>
       <c r="C450" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D450">
         <f>D105</f>
@@ -9745,12 +9845,12 @@
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A451" s="45"/>
+      <c r="A451" s="49"/>
       <c r="B451" t="s">
         <v>39</v>
       </c>
       <c r="C451" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D451">
         <f>D103</f>
@@ -9758,12 +9858,12 @@
       </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A452" s="45"/>
+      <c r="A452" s="49"/>
       <c r="B452" t="s">
+        <v>432</v>
+      </c>
+      <c r="C452" t="s">
         <v>433</v>
-      </c>
-      <c r="C452" t="s">
-        <v>434</v>
       </c>
       <c r="D452">
         <f>0.5*D450/D449</f>
@@ -9771,18 +9871,18 @@
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A453" s="45"/>
+      <c r="A453" s="49"/>
       <c r="B453" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D453">
         <v>0.5</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A454" s="45"/>
+      <c r="A454" s="49"/>
       <c r="B454" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D454">
         <f>D452/D453</f>
@@ -9790,18 +9890,18 @@
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A455" s="45"/>
+      <c r="A455" s="49"/>
       <c r="C455" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D455">
         <v>10</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A456" s="45"/>
+      <c r="A456" s="49"/>
       <c r="B456" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D456">
         <f>D455*D454</f>
@@ -9809,12 +9909,12 @@
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A457" s="45"/>
+      <c r="A457" s="49"/>
       <c r="B457" t="s">
+        <v>466</v>
+      </c>
+      <c r="C457" t="s">
         <v>467</v>
-      </c>
-      <c r="C457" t="s">
-        <v>468</v>
       </c>
       <c r="D457">
         <f>3*D479</f>
@@ -9822,39 +9922,39 @@
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A458" s="45"/>
+      <c r="A458" s="49"/>
       <c r="B458" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D458" s="1">
         <v>1E-3</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A459" s="45"/>
+      <c r="A459" s="49"/>
       <c r="B459" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D459">
         <v>20</v>
       </c>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A460" s="45"/>
+      <c r="A460" s="49"/>
       <c r="B460" t="s">
+        <v>472</v>
+      </c>
+      <c r="C460" t="s">
         <v>473</v>
-      </c>
-      <c r="C460" t="s">
-        <v>474</v>
       </c>
       <c r="D460" s="30">
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A461" s="45"/>
+      <c r="A461" s="49"/>
       <c r="B461" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D461">
         <f>D460/D459</f>
@@ -9862,12 +9962,12 @@
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A462" s="45"/>
+      <c r="A462" s="49"/>
       <c r="B462" t="s">
+        <v>447</v>
+      </c>
+      <c r="C462" t="s">
         <v>448</v>
-      </c>
-      <c r="C462" t="s">
-        <v>449</v>
       </c>
       <c r="D462" s="1">
         <f>D458*D459</f>
@@ -9875,9 +9975,9 @@
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A463" s="45"/>
+      <c r="A463" s="49"/>
       <c r="C463" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D463" s="1">
         <f>0.2</f>
@@ -9885,9 +9985,9 @@
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A464" s="45"/>
+      <c r="A464" s="49"/>
       <c r="B464" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D464" s="1">
         <f>D462*(1-D463)</f>
@@ -9895,9 +9995,9 @@
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A465" s="45"/>
+      <c r="A465" s="49"/>
       <c r="B465" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D465" s="1">
         <f>D461*D450</f>
@@ -9905,9 +10005,9 @@
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A466" s="45"/>
+      <c r="A466" s="49"/>
       <c r="B466" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D466" s="1">
         <f>D452/D462</f>
@@ -9915,9 +10015,9 @@
       </c>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A467" s="45"/>
+      <c r="A467" s="49"/>
       <c r="B467" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D467" s="1">
         <f>D465+D466</f>
@@ -9925,9 +10025,9 @@
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A468" s="45"/>
+      <c r="A468" s="49"/>
       <c r="B468" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D468" s="1">
         <f>POWER(D465, 2)/D461</f>
@@ -9935,9 +10035,9 @@
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A469" s="45"/>
+      <c r="A469" s="49"/>
       <c r="B469" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D469" s="1">
         <f>D468/D459</f>
@@ -9945,24 +10045,24 @@
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A470" s="45"/>
+      <c r="A470" s="49"/>
       <c r="B470" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C470" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D470">
         <v>500</v>
       </c>
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A471" s="45"/>
+      <c r="A471" s="49"/>
       <c r="B471" t="s">
+        <v>443</v>
+      </c>
+      <c r="C471" t="s">
         <v>444</v>
-      </c>
-      <c r="C471" t="s">
-        <v>445</v>
       </c>
       <c r="D471">
         <f>1/(POWER(2*PI()*D470, 2)*D456)</f>
@@ -9970,21 +10070,21 @@
       </c>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A472" s="45"/>
+      <c r="A472" s="49"/>
       <c r="B472" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C472" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D472" s="1">
         <v>2.1999999999999999E-5</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A473" s="45"/>
+      <c r="A473" s="49"/>
       <c r="B473" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D473" s="1">
         <f>D2*2/D5</f>
@@ -9992,9 +10092,9 @@
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A474" s="45"/>
+      <c r="A474" s="49"/>
       <c r="B474" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D474" s="1">
         <f>2*D473</f>
@@ -10002,12 +10102,12 @@
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A475" s="45"/>
+      <c r="A475" s="49"/>
       <c r="B475" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C475" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D475" s="1">
         <f>1/(2*PI()*POWER(D462*D472, 0.5))</f>
@@ -10015,9 +10115,9 @@
       </c>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A476" s="45"/>
+      <c r="A476" s="49"/>
       <c r="B476" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D476" s="1">
         <f>40*LOG10(D449/D475)</f>
@@ -10025,9 +10125,9 @@
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A477" s="45"/>
+      <c r="A477" s="49"/>
       <c r="C477" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D477">
         <f>POWER(D7, 2)*0.5*D462</f>
@@ -10035,19 +10135,19 @@
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A478" s="45"/>
+      <c r="A478" s="49"/>
       <c r="B478" t="s">
+        <v>452</v>
+      </c>
+      <c r="C478" t="s">
         <v>453</v>
-      </c>
-      <c r="C478" t="s">
-        <v>454</v>
       </c>
       <c r="D478">
         <v>33</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A479" s="45"/>
+      <c r="A479" s="49"/>
       <c r="B479" t="s">
         <v>38</v>
       </c>
@@ -10057,12 +10157,12 @@
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A480" s="45"/>
+      <c r="A480" s="49"/>
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A481" s="45"/>
+      <c r="A481" s="49"/>
       <c r="B481" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D481" s="1">
         <f>((-D478)+POWER(POWER(D478, 2)-(4*D472/D462), 0.5))/(2*D472)</f>
@@ -10070,9 +10170,9 @@
       </c>
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A482" s="45"/>
+      <c r="A482" s="49"/>
       <c r="B482" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D482" s="1">
         <f>((-D478)-POWER(POWER(D478, 2)-(4*D472/D462), 0.5))/(2*D472)</f>
@@ -10080,9 +10180,9 @@
       </c>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A483" s="45"/>
+      <c r="A483" s="49"/>
       <c r="B483" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D483" s="1">
         <f>LN(D482/D481)/(D481-D482)</f>
@@ -10090,9 +10190,9 @@
       </c>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A484" s="45"/>
+      <c r="A484" s="49"/>
       <c r="B484" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D484" s="1">
         <f>(D479/(D472*(D481-D482)))*(EXP(D481*D483)-EXP(D482*D483))</f>
@@ -10100,9 +10200,9 @@
       </c>
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A485" s="45"/>
+      <c r="A485" s="49"/>
       <c r="B485" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D485" s="1">
         <f>D478*POWER(D484, 2)</f>
@@ -10110,9 +10210,9 @@
       </c>
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A486" s="45"/>
+      <c r="A486" s="49"/>
       <c r="C486" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D486" s="1">
         <f>D485*D4</f>
@@ -10120,12 +10220,12 @@
       </c>
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A487" s="45"/>
+      <c r="A487" s="49"/>
       <c r="B487" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C487" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D487" t="b">
         <f>(POWER(D478, 2)/(4*POWER(D472, 2)))&lt;(1/(D472*D462))</f>
@@ -10133,9 +10233,9 @@
       </c>
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A488" s="45"/>
+      <c r="A488" s="49"/>
       <c r="B488" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D488" s="1">
         <f>D478/(2*D472)</f>
@@ -10143,9 +10243,9 @@
       </c>
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A489" s="45"/>
+      <c r="A489" s="49"/>
       <c r="B489" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D489" s="1">
         <f>1/POWER(D472*D462, 0.5)</f>
@@ -10153,9 +10253,9 @@
       </c>
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A490" s="45"/>
+      <c r="A490" s="49"/>
       <c r="B490" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D490" t="str">
         <f>IF(D487, POWER(POWER(D489, 2)-POWER(D488, 2), 0.5),"NA")</f>
@@ -10163,9 +10263,9 @@
       </c>
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A491" s="45"/>
+      <c r="A491" s="49"/>
       <c r="C491" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D491" s="1" t="str">
         <f>IF(D487, 100*EXP(-PI()*D488/D490), "Not Under-damped")</f>
@@ -10173,9 +10273,9 @@
       </c>
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A492" s="45"/>
+      <c r="A492" s="49"/>
       <c r="B492" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D492" s="1">
         <f>5/MIN(ABS(D481), ABS(D482))</f>
@@ -10183,30 +10283,30 @@
       </c>
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A493" s="45"/>
+      <c r="A493" s="49"/>
       <c r="B493" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C493" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D493">
         <v>1600</v>
       </c>
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A494" s="45"/>
+      <c r="A494" s="49"/>
       <c r="C494" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D494">
         <v>0.1</v>
       </c>
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A495" s="45"/>
+      <c r="A495" s="49"/>
       <c r="B495" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D495">
         <f>D493*(1-D494)</f>
@@ -10214,9 +10314,9 @@
       </c>
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A496" s="45"/>
+      <c r="A496" s="49"/>
       <c r="B496" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D496">
         <f>D493*(1+D494)</f>
@@ -10224,27 +10324,27 @@
       </c>
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A497" s="45"/>
+      <c r="A497" s="49"/>
       <c r="B497" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D497">
         <v>24</v>
       </c>
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A498" s="45"/>
+      <c r="A498" s="49"/>
       <c r="B498" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D498">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A499" s="45"/>
+      <c r="A499" s="49"/>
       <c r="C499" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D499" t="b">
         <f>(D497/D493)=D498</f>
@@ -10252,12 +10352,12 @@
       </c>
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A500" s="45"/>
+      <c r="A500" s="49"/>
       <c r="B500" t="s">
+        <v>488</v>
+      </c>
+      <c r="C500" t="s">
         <v>489</v>
-      </c>
-      <c r="C500" t="s">
-        <v>490</v>
       </c>
       <c r="D500">
         <f>1.3*D497</f>
@@ -10265,12 +10365,12 @@
       </c>
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A501" s="45"/>
+      <c r="A501" s="49"/>
       <c r="B501" t="s">
+        <v>490</v>
+      </c>
+      <c r="C501" t="s">
         <v>491</v>
-      </c>
-      <c r="C501" t="s">
-        <v>492</v>
       </c>
       <c r="D501">
         <f>0.75*D497</f>
@@ -10278,9 +10378,9 @@
       </c>
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A502" s="45"/>
+      <c r="A502" s="49"/>
       <c r="B502" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D502">
         <f>D501/D496</f>
@@ -10288,9 +10388,9 @@
       </c>
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A503" s="45"/>
+      <c r="A503" s="49"/>
       <c r="B503" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D503">
         <f>D500/D496</f>
@@ -10298,27 +10398,27 @@
       </c>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A504" s="45"/>
+      <c r="A504" s="49"/>
       <c r="B504" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D504">
         <v>1330</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A505" s="45"/>
+      <c r="A505" s="49"/>
       <c r="C505" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D505">
         <v>0.05</v>
       </c>
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A506" s="45"/>
+      <c r="A506" s="49"/>
       <c r="B506" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D506">
         <f>D504*(1-D505)</f>
@@ -10326,9 +10426,9 @@
       </c>
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A507" s="45"/>
+      <c r="A507" s="49"/>
       <c r="B507" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D507">
         <f>D504*(1+D505)</f>
@@ -10336,9 +10436,9 @@
       </c>
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A508" s="45"/>
+      <c r="A508" s="49"/>
       <c r="C508" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D508">
         <f>D6/(D493+D504)</f>
@@ -10346,9 +10446,9 @@
       </c>
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A509" s="45"/>
+      <c r="A509" s="49"/>
       <c r="C509" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D509">
         <f>D5/(D495+D507)</f>
@@ -10356,9 +10456,9 @@
       </c>
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A510" s="45"/>
+      <c r="A510" s="49"/>
       <c r="C510" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D510">
         <f>D7/(D495+D506)</f>
@@ -10366,9 +10466,9 @@
       </c>
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A511" s="45"/>
+      <c r="A511" s="49"/>
       <c r="C511" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D511" t="b">
         <f>AND((D508&gt;D502), (D510&lt;D503))</f>
@@ -10376,12 +10476,12 @@
       </c>
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A512" s="45"/>
+      <c r="A512" s="49"/>
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A513" s="45"/>
+      <c r="A513" s="49"/>
       <c r="B513" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D513">
         <f xml:space="preserve"> POWER(D510, 2)*D504</f>
@@ -10389,9 +10489,9 @@
       </c>
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A514" s="45"/>
+      <c r="A514" s="49"/>
       <c r="B514" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D514">
         <f>POWER(D508, 2)*D493</f>
@@ -10399,9 +10499,9 @@
       </c>
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A515" s="45"/>
+      <c r="A515" s="49"/>
       <c r="B515" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D515">
         <f>POWER(D509, 2)*D496</f>
@@ -10409,9 +10509,9 @@
       </c>
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A516" s="45"/>
+      <c r="A516" s="49"/>
       <c r="C516" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D516" s="1">
         <f>0.5*D472*POWER(D517, 2)</f>
@@ -10419,9 +10519,9 @@
       </c>
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A517" s="45"/>
+      <c r="A517" s="49"/>
       <c r="C517" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D517">
         <f>D2/D6</f>
@@ -10429,9 +10529,9 @@
       </c>
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A518" s="45"/>
+      <c r="A518" s="49"/>
       <c r="C518" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D518">
         <f>D6</f>
@@ -10439,9 +10539,9 @@
       </c>
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A519" s="45"/>
+      <c r="A519" s="49"/>
       <c r="C519" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D519">
         <f>POWER(((0.5*D462*POWER(D518, 2))+D516)*2/D462, 0.5)</f>
@@ -10450,13 +10550,13 @@
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
+        <v>737</v>
+      </c>
+      <c r="B520" t="s">
+        <v>739</v>
+      </c>
+      <c r="C520" t="s">
         <v>738</v>
-      </c>
-      <c r="B520" t="s">
-        <v>740</v>
-      </c>
-      <c r="C520" t="s">
-        <v>739</v>
       </c>
       <c r="D520" s="1">
         <f>0.5*D462*POWER(D7, 2)</f>
@@ -10465,10 +10565,10 @@
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B521" t="s">
+        <v>740</v>
+      </c>
+      <c r="C521" t="s">
         <v>741</v>
-      </c>
-      <c r="C521" t="s">
-        <v>742</v>
       </c>
       <c r="D521">
         <f>(0.06*0.022*0.0018)+(2*(0.06*0.0129*0.001))+(0.06*0.0091*0.0018)</f>
@@ -10477,10 +10577,10 @@
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B522" t="s">
+        <v>742</v>
+      </c>
+      <c r="C522" t="s">
         <v>743</v>
-      </c>
-      <c r="C522" t="s">
-        <v>744</v>
       </c>
       <c r="D522">
         <v>850</v>
@@ -10488,10 +10588,10 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B523" t="s">
+        <v>744</v>
+      </c>
+      <c r="C523" t="s">
         <v>745</v>
-      </c>
-      <c r="C523" t="s">
-        <v>746</v>
       </c>
       <c r="D523">
         <v>2700</v>
@@ -10499,7 +10599,7 @@
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B524" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D524">
         <f>D520/(D523*D521*D522)</f>
@@ -10508,10 +10608,10 @@
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B525" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C525" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D525">
         <v>0.2</v>
@@ -10519,10 +10619,10 @@
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B526" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C526" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D526">
         <f>D522*D521*D523</f>
@@ -10531,10 +10631,10 @@
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B527" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C527" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D527">
         <f>0.022*0.06</f>
@@ -10543,10 +10643,10 @@
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B528" t="s">
+        <v>758</v>
+      </c>
+      <c r="C528" t="s">
         <v>759</v>
-      </c>
-      <c r="C528" t="s">
-        <v>760</v>
       </c>
       <c r="D528">
         <f>0.002</f>
@@ -10555,10 +10655,10 @@
     </row>
     <row r="529" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B529" t="s">
+        <v>747</v>
+      </c>
+      <c r="C529" t="s">
         <v>748</v>
-      </c>
-      <c r="C529" t="s">
-        <v>749</v>
       </c>
       <c r="D529">
         <v>0.5</v>
@@ -10566,10 +10666,10 @@
     </row>
     <row r="530" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B530" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C530" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D530">
         <f>4.605*D526/D529</f>
@@ -10578,10 +10678,10 @@
     </row>
     <row r="531" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B531" t="s">
+        <v>754</v>
+      </c>
+      <c r="C531" t="s">
         <v>755</v>
-      </c>
-      <c r="C531" t="s">
-        <v>756</v>
       </c>
       <c r="D531">
         <f>D528/(D525*D527)</f>
@@ -10590,7 +10690,7 @@
     </row>
     <row r="532" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B532" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D532">
         <f>D526*D524/D530</f>
@@ -10600,7 +10700,7 @@
     <row r="533" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A533" s="42"/>
       <c r="B533" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D533">
         <f>D532*D531</f>
@@ -10608,29 +10708,29 @@
       </c>
     </row>
     <row r="534" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A534" s="45" t="s">
+      <c r="A534" s="49" t="s">
+        <v>630</v>
+      </c>
+      <c r="C534" t="s">
+        <v>634</v>
+      </c>
+      <c r="D534" t="s">
+        <v>635</v>
+      </c>
+      <c r="E534" t="s">
+        <v>637</v>
+      </c>
+      <c r="F534" t="s">
+        <v>636</v>
+      </c>
+      <c r="G534" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="535" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A535" s="49"/>
+      <c r="C535" t="s">
         <v>631</v>
-      </c>
-      <c r="C534" t="s">
-        <v>635</v>
-      </c>
-      <c r="D534" t="s">
-        <v>636</v>
-      </c>
-      <c r="E534" t="s">
-        <v>638</v>
-      </c>
-      <c r="F534" t="s">
-        <v>637</v>
-      </c>
-      <c r="G534" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="535" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A535" s="45"/>
-      <c r="C535" t="s">
-        <v>632</v>
       </c>
       <c r="D535">
         <f>D2/D5</f>
@@ -10657,9 +10757,9 @@
       </c>
     </row>
     <row r="536" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A536" s="45"/>
+      <c r="A536" s="49"/>
       <c r="C536" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D536">
         <v>2</v>
@@ -10684,9 +10784,9 @@
       </c>
     </row>
     <row r="537" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A537" s="45"/>
+      <c r="A537" s="49"/>
       <c r="C537" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D537">
         <v>5</v>
@@ -10711,9 +10811,9 @@
       </c>
     </row>
     <row r="538" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A538" s="45"/>
+      <c r="A538" s="49"/>
       <c r="C538" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D538">
         <f>0.0254*POWER(D535/(0.048*POWER(D537, 0.44)), 1/0.725)/(D536*1.378)</f>
@@ -10745,9 +10845,9 @@
       </c>
     </row>
     <row r="539" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A539" s="45"/>
+      <c r="A539" s="49"/>
       <c r="C539" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D539">
         <f>0.0254*POWER(D535/(0.024*POWER(D537, 0.44)), 1/0.725)/(D536*1.378)</f>
@@ -10775,9 +10875,9 @@
       </c>
     </row>
     <row r="540" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A540" s="45"/>
+      <c r="A540" s="49"/>
       <c r="C540" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D540">
         <v>8</v>
@@ -10796,9 +10896,9 @@
       </c>
     </row>
     <row r="541" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A541" s="45"/>
+      <c r="A541" s="49"/>
       <c r="C541" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D541">
         <f>POWER(D535/POWER(D540*(D536*1.378)/0.0254, 0.725)/0.048, 1/0.44)</f>
@@ -10822,9 +10922,9 @@
       </c>
     </row>
     <row r="542" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A542" s="45"/>
+      <c r="A542" s="49"/>
       <c r="C542" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D542">
         <f>POWER(D535/POWER(D540*(D536*1.378)/0.0254, 0.725)/0.024, 1/0.44)</f>
@@ -10848,9 +10948,9 @@
       </c>
     </row>
     <row r="543" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A543" s="45"/>
+      <c r="A543" s="49"/>
       <c r="C543" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D543">
         <v>100</v>
@@ -10869,7 +10969,7 @@
       </c>
     </row>
     <row r="544" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A544" s="45"/>
+      <c r="A544" s="49"/>
       <c r="C544" t="s">
         <v>200</v>
       </c>
@@ -10895,9 +10995,9 @@
       </c>
     </row>
     <row r="545" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A545" s="45"/>
+      <c r="A545" s="49"/>
       <c r="C545" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D545">
         <f>POWER(D535, 2)*D544</f>
@@ -10921,9 +11021,9 @@
       </c>
     </row>
     <row r="546" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A546" s="45"/>
+      <c r="A546" s="49"/>
       <c r="C546" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D546">
         <f>D535*D544</f>
@@ -10953,30 +11053,30 @@
       <c r="A548" s="42"/>
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A553" s="44" t="s">
+      <c r="A553" s="50" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="554" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A554" s="50"/>
+      <c r="C554" t="s">
         <v>720</v>
-      </c>
-    </row>
-    <row r="554" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A554" s="44"/>
-      <c r="C554" t="s">
-        <v>721</v>
       </c>
       <c r="D554" s="1">
         <v>1000000000</v>
       </c>
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A555" s="44"/>
+      <c r="A555" s="50"/>
       <c r="C555" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D555">
         <v>14</v>
       </c>
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A556" s="44"/>
+      <c r="A556" s="50"/>
       <c r="C556" t="s">
         <v>219</v>
       </c>
@@ -10986,9 +11086,9 @@
       </c>
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A557" s="44"/>
+      <c r="A557" s="50"/>
       <c r="C557" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D557">
         <f>2.5</f>
@@ -10996,9 +11096,9 @@
       </c>
     </row>
     <row r="558" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A558" s="44"/>
+      <c r="A558" s="50"/>
       <c r="C558" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D558">
         <f>D8/D557</f>
@@ -11006,9 +11106,9 @@
       </c>
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A559" s="44"/>
+      <c r="A559" s="50"/>
       <c r="C559" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D559">
         <f>D556/D558</f>
@@ -11016,18 +11116,18 @@
       </c>
     </row>
     <row r="560" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A560" s="44"/>
+      <c r="A560" s="50"/>
       <c r="C560" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D560" s="1">
         <v>130000</v>
       </c>
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A561" s="44"/>
+      <c r="A561" s="50"/>
       <c r="C561" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D561" s="1">
         <f>D8/D556</f>
@@ -11035,9 +11135,9 @@
       </c>
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A562" s="44"/>
+      <c r="A562" s="50"/>
       <c r="C562" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D562" s="1">
         <f>D561*D561*D554</f>
@@ -11045,9 +11145,9 @@
       </c>
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A563" s="44"/>
+      <c r="A563" s="50"/>
       <c r="C563" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D563" s="1">
         <f>D562*D555</f>
@@ -11055,9 +11155,9 @@
       </c>
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A564" s="44"/>
+      <c r="A564" s="50"/>
       <c r="C564" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D564" s="1">
         <f>POWER(D561, 2)*D560</f>
@@ -11065,27 +11165,27 @@
       </c>
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A567" s="44" t="s">
-        <v>730</v>
+      <c r="A567" s="50" t="s">
+        <v>729</v>
       </c>
       <c r="C567" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D567" s="1">
         <v>100000000</v>
       </c>
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A568" s="44"/>
+      <c r="A568" s="50"/>
       <c r="C568" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D568">
         <v>1</v>
       </c>
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A569" s="44"/>
+      <c r="A569" s="50"/>
       <c r="C569" t="s">
         <v>219</v>
       </c>
@@ -11095,18 +11195,18 @@
       </c>
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A570" s="44"/>
+      <c r="A570" s="50"/>
       <c r="C570" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D570">
         <v>2.5</v>
       </c>
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A571" s="44"/>
+      <c r="A571" s="50"/>
       <c r="C571" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D571">
         <f>D12/D570</f>
@@ -11114,9 +11214,9 @@
       </c>
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A572" s="44"/>
+      <c r="A572" s="50"/>
       <c r="C572" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D572">
         <f>D569/D571</f>
@@ -11124,18 +11224,18 @@
       </c>
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A573" s="44"/>
+      <c r="A573" s="50"/>
       <c r="C573" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D573" s="1">
         <v>20000</v>
       </c>
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A574" s="44"/>
+      <c r="A574" s="50"/>
       <c r="C574" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D574" s="1">
         <f>D12/D569</f>
@@ -11143,9 +11243,9 @@
       </c>
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A575" s="44"/>
+      <c r="A575" s="50"/>
       <c r="C575" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D575" s="1">
         <f>D574*D574*D567</f>
@@ -11153,9 +11253,9 @@
       </c>
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A576" s="44"/>
+      <c r="A576" s="50"/>
       <c r="C576" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D576" s="1">
         <f>D575*D568</f>
@@ -11164,7 +11264,7 @@
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C577" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D577" s="1">
         <f>POWER(D574, 2)*D573</f>
@@ -11172,32 +11272,32 @@
       </c>
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A579" s="45" t="s">
+      <c r="A579" s="49" t="s">
+        <v>730</v>
+      </c>
+      <c r="C579" t="s">
         <v>731</v>
-      </c>
-      <c r="C579" t="s">
-        <v>732</v>
       </c>
       <c r="D579">
         <v>3</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A580" s="45"/>
+      <c r="A580" s="49"/>
       <c r="C580" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D580">
         <v>550</v>
       </c>
       <c r="E580" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A581" s="45"/>
+      <c r="A581" s="49"/>
       <c r="C581" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D581">
         <f>25.4*41.9*0.000001</f>
@@ -11205,22 +11305,22 @@
       </c>
     </row>
     <row r="582" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A582" s="45"/>
+      <c r="A582" s="49"/>
       <c r="C582" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D582">
         <f>D581*D580*0.3048</f>
         <v>0.17841254640000004</v>
       </c>
       <c r="E582" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A583" s="45"/>
+      <c r="A583" s="49"/>
       <c r="C583" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D583">
         <f>D582*50</f>
@@ -11228,35 +11328,35 @@
       </c>
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A584" s="45"/>
+      <c r="A584" s="49"/>
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A585" s="45"/>
+      <c r="A585" s="49"/>
     </row>
     <row r="586" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A586" s="45"/>
+      <c r="A586" s="49"/>
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A587" s="45"/>
+      <c r="A587" s="49"/>
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A588" s="45"/>
+      <c r="A588" s="49"/>
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A589" s="45"/>
+      <c r="A589" s="49"/>
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A590" s="45"/>
+      <c r="A590" s="49"/>
     </row>
     <row r="591" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A591" s="45"/>
+      <c r="A591" s="49"/>
     </row>
     <row r="593" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A593" s="45" t="s">
+      <c r="A593" s="49" t="s">
+        <v>764</v>
+      </c>
+      <c r="C593" t="s">
         <v>765</v>
-      </c>
-      <c r="C593" t="s">
-        <v>766</v>
       </c>
       <c r="E593" s="1">
         <f>D67</f>
@@ -11264,9 +11364,9 @@
       </c>
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A594" s="45"/>
+      <c r="A594" s="49"/>
       <c r="C594" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E594">
         <f>D27</f>
@@ -11274,9 +11374,9 @@
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A595" s="45"/>
+      <c r="A595" s="49"/>
       <c r="C595" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="E595" s="1">
         <f>D163+D164</f>
@@ -11284,9 +11384,9 @@
       </c>
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A596" s="45"/>
+      <c r="A596" s="49"/>
       <c r="C596" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E596" s="1">
         <f>E593+E594+E595</f>
@@ -11294,13 +11394,13 @@
       </c>
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A597" s="45"/>
+      <c r="A597" s="49"/>
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A598" s="45"/>
+      <c r="A598" s="49"/>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A599" s="45"/>
+      <c r="A599" s="49"/>
       <c r="C599" t="s">
         <v>4</v>
       </c>
@@ -11309,9 +11409,9 @@
       </c>
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A600" s="45"/>
+      <c r="A600" s="49"/>
       <c r="C600" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D600" t="s">
         <v>212</v>
@@ -11321,9 +11421,9 @@
       </c>
     </row>
     <row r="601" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A601" s="45"/>
+      <c r="A601" s="49"/>
       <c r="C601" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D601" t="s">
         <v>212</v>
@@ -11333,12 +11433,12 @@
       </c>
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A602" s="45"/>
+      <c r="A602" s="49"/>
       <c r="C602" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D602" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E602">
         <f>POWER(E600/2, 2)*PI()*E601</f>
@@ -11346,9 +11446,9 @@
       </c>
     </row>
     <row r="603" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A603" s="45"/>
+      <c r="A603" s="49"/>
       <c r="C603" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E603" s="1">
         <f>E596</f>
@@ -11356,48 +11456,48 @@
       </c>
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A604" s="45"/>
+      <c r="A604" s="49"/>
       <c r="C604" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D604" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E604">
         <v>2300</v>
       </c>
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A605" s="45"/>
+      <c r="A605" s="49"/>
       <c r="C605" t="s">
+        <v>653</v>
+      </c>
+      <c r="D605" t="s">
         <v>654</v>
-      </c>
-      <c r="D605" t="s">
-        <v>655</v>
       </c>
       <c r="E605">
         <v>20</v>
       </c>
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A606" s="45"/>
+      <c r="A606" s="49"/>
       <c r="C606" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D606" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E606">
         <v>800</v>
       </c>
     </row>
     <row r="607" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A607" s="45"/>
+      <c r="A607" s="49"/>
       <c r="C607" t="s">
+        <v>659</v>
+      </c>
+      <c r="D607" t="s">
         <v>660</v>
-      </c>
-      <c r="D607" t="s">
-        <v>661</v>
       </c>
       <c r="E607">
         <f>E606*E602</f>
@@ -11405,12 +11505,12 @@
       </c>
     </row>
     <row r="608" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A608" s="45"/>
+      <c r="A608" s="49"/>
       <c r="C608" t="s">
+        <v>661</v>
+      </c>
+      <c r="D608" t="s">
         <v>662</v>
-      </c>
-      <c r="D608" t="s">
-        <v>663</v>
       </c>
       <c r="E608">
         <f>E604*E607*E605</f>
@@ -11418,12 +11518,12 @@
       </c>
     </row>
     <row r="609" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A609" s="45"/>
+      <c r="A609" s="49"/>
       <c r="C609" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D609" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E609">
         <f>E608/E603</f>
@@ -11431,12 +11531,12 @@
       </c>
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A610" s="45"/>
+      <c r="A610" s="49"/>
       <c r="C610" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D610" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E610">
         <f>E609/E599</f>
@@ -11444,12 +11544,12 @@
       </c>
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A611" s="45"/>
+      <c r="A611" s="49"/>
       <c r="C611" t="s">
+        <v>665</v>
+      </c>
+      <c r="D611" t="s">
         <v>666</v>
-      </c>
-      <c r="D611" t="s">
-        <v>667</v>
       </c>
       <c r="E611">
         <f>E602/E610</f>
@@ -11457,12 +11557,12 @@
       </c>
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A612" s="45"/>
+      <c r="A612" s="49"/>
       <c r="C612" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D612" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E612">
         <f>(1000000)*E611</f>
@@ -11470,21 +11570,21 @@
       </c>
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A613" s="45"/>
+      <c r="A613" s="49"/>
       <c r="C613" t="s">
+        <v>668</v>
+      </c>
+      <c r="D613" t="s">
         <v>669</v>
-      </c>
-      <c r="D613" t="s">
-        <v>670</v>
       </c>
       <c r="E613">
         <v>0.1</v>
       </c>
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A614" s="45"/>
+      <c r="A614" s="49"/>
       <c r="C614" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D614" t="s">
         <v>213</v>
@@ -11495,9 +11595,9 @@
       </c>
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A615" s="45"/>
+      <c r="A615" s="49"/>
       <c r="C615" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D615" t="s">
         <v>212</v>
@@ -11508,9 +11608,9 @@
       </c>
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A616" s="45"/>
+      <c r="A616" s="49"/>
       <c r="C616" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D616" t="s">
         <v>212</v>
@@ -11521,9 +11621,9 @@
       </c>
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A617" s="45"/>
+      <c r="A617" s="49"/>
       <c r="C617" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D617" t="s">
         <v>139</v>
@@ -11534,9 +11634,9 @@
       </c>
     </row>
     <row r="618" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A618" s="45"/>
+      <c r="A618" s="49"/>
       <c r="C618" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D618" t="s">
         <v>139</v>
@@ -11547,7 +11647,7 @@
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C619" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E619">
         <f>E618/1000</f>
@@ -11556,7 +11656,7 @@
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C620" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E620">
         <f>0.00604</f>
@@ -11565,7 +11665,7 @@
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C621" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E621">
         <f>E620/E606</f>
@@ -11574,7 +11674,7 @@
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C622" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E622">
         <v>2300</v>
@@ -11582,7 +11682,7 @@
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C623" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E623">
         <f>E606*E613*E619/E620</f>
@@ -11591,15 +11691,630 @@
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C624" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E624" t="b">
         <f>E623&lt;E622</f>
         <v>1</v>
       </c>
     </row>
+    <row r="627" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A627" s="49" t="s">
+        <v>785</v>
+      </c>
+      <c r="B627" t="s">
+        <v>37</v>
+      </c>
+      <c r="C627" t="s">
+        <v>44</v>
+      </c>
+      <c r="D627" t="s">
+        <v>21</v>
+      </c>
+      <c r="E627">
+        <f>D5</f>
+        <v>35.400000000000006</v>
+      </c>
+    </row>
+    <row r="628" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A628" s="49"/>
+      <c r="B628" t="s">
+        <v>494</v>
+      </c>
+      <c r="C628" t="s">
+        <v>495</v>
+      </c>
+      <c r="D628" t="s">
+        <v>21</v>
+      </c>
+      <c r="E628">
+        <f>D6</f>
+        <v>38.099999999999994</v>
+      </c>
+    </row>
+    <row r="629" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A629" s="49"/>
+      <c r="B629" t="s">
+        <v>38</v>
+      </c>
+      <c r="C629" t="s">
+        <v>43</v>
+      </c>
+      <c r="D629" t="s">
+        <v>21</v>
+      </c>
+      <c r="E629">
+        <f>D7</f>
+        <v>44.1</v>
+      </c>
+    </row>
+    <row r="630" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A630" s="49"/>
+      <c r="C630" t="s">
+        <v>786</v>
+      </c>
+      <c r="D630" t="s">
+        <v>20</v>
+      </c>
+      <c r="E630">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="631" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A631" s="49"/>
+      <c r="C631" t="s">
+        <v>787</v>
+      </c>
+      <c r="E631">
+        <f>(E629/E630)</f>
+        <v>14.700000000000001</v>
+      </c>
+    </row>
+    <row r="632" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A632" s="49"/>
+      <c r="C632" t="s">
+        <v>788</v>
+      </c>
+      <c r="E632">
+        <f>E627/E630</f>
+        <v>11.800000000000002</v>
+      </c>
+    </row>
+    <row r="633" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A633" s="49"/>
+      <c r="C633" t="s">
+        <v>789</v>
+      </c>
+      <c r="E633">
+        <f>E628/E630</f>
+        <v>12.699999999999998</v>
+      </c>
+    </row>
+    <row r="634" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A634" s="49"/>
+      <c r="C634" t="s">
+        <v>790</v>
+      </c>
+      <c r="E634">
+        <f>12</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="635" spans="1:15" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A635" s="49"/>
+      <c r="C635" t="s">
+        <v>791</v>
+      </c>
+      <c r="E635">
+        <f>E629*E629/E634</f>
+        <v>162.06750000000002</v>
+      </c>
+      <c r="G635" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="H635" s="48" t="s">
+        <v>797</v>
+      </c>
+      <c r="I635" s="48" t="s">
+        <v>800</v>
+      </c>
+      <c r="J635" s="48" t="s">
+        <v>799</v>
+      </c>
+      <c r="K635" s="48" t="s">
+        <v>798</v>
+      </c>
+      <c r="L635" s="48" t="s">
+        <v>801</v>
+      </c>
+      <c r="M635" s="48" t="s">
+        <v>802</v>
+      </c>
+      <c r="N635" s="48" t="s">
+        <v>804</v>
+      </c>
+      <c r="O635" s="47"/>
+    </row>
+    <row r="636" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A636" s="49"/>
+      <c r="C636" t="s">
+        <v>792</v>
+      </c>
+      <c r="E636">
+        <f>6</f>
+        <v>6</v>
+      </c>
+      <c r="G636" s="18">
+        <v>1</v>
+      </c>
+      <c r="H636" s="18">
+        <f>E629/G636</f>
+        <v>44.1</v>
+      </c>
+      <c r="I636" s="18">
+        <f>H636*H636*G636</f>
+        <v>1944.8100000000002</v>
+      </c>
+      <c r="J636" s="18">
+        <f>I636/2</f>
+        <v>972.40500000000009</v>
+      </c>
+      <c r="K636" s="18">
+        <f>E627/G636</f>
+        <v>35.400000000000006</v>
+      </c>
+      <c r="L636" s="18">
+        <f>E627*E627/G636</f>
+        <v>1253.1600000000003</v>
+      </c>
+      <c r="M636" s="18">
+        <f>L636/2</f>
+        <v>626.58000000000015</v>
+      </c>
+      <c r="N636" s="47"/>
+    </row>
+    <row r="637" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A637" s="49"/>
+      <c r="C637" t="s">
+        <v>793</v>
+      </c>
+      <c r="E637">
+        <v>2</v>
+      </c>
+      <c r="G637" s="18">
+        <v>2</v>
+      </c>
+      <c r="H637" s="18">
+        <f>E629/G637</f>
+        <v>22.05</v>
+      </c>
+      <c r="I637" s="18">
+        <f t="shared" ref="I637:I649" si="27">H637*H637*G637</f>
+        <v>972.40500000000009</v>
+      </c>
+      <c r="J637" s="18">
+        <f>I637/2</f>
+        <v>486.20250000000004</v>
+      </c>
+      <c r="K637" s="18">
+        <f>E627/G637</f>
+        <v>17.700000000000003</v>
+      </c>
+      <c r="L637" s="18">
+        <f>E627*E627/G637</f>
+        <v>626.58000000000015</v>
+      </c>
+      <c r="M637" s="18">
+        <f>L637/2</f>
+        <v>313.29000000000008</v>
+      </c>
+      <c r="N637" s="47"/>
+    </row>
+    <row r="638" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A638" s="49"/>
+      <c r="C638" t="s">
+        <v>794</v>
+      </c>
+      <c r="E638">
+        <f xml:space="preserve"> E636*E637</f>
+        <v>12</v>
+      </c>
+      <c r="G638" s="18">
+        <v>3</v>
+      </c>
+      <c r="H638" s="18">
+        <f>E629/G638</f>
+        <v>14.700000000000001</v>
+      </c>
+      <c r="I638" s="18">
+        <f t="shared" si="27"/>
+        <v>648.2700000000001</v>
+      </c>
+      <c r="J638" s="18">
+        <f>I638/2</f>
+        <v>324.13500000000005</v>
+      </c>
+      <c r="K638" s="18">
+        <f>E627/G638</f>
+        <v>11.800000000000002</v>
+      </c>
+      <c r="L638" s="18">
+        <f>E627*E627/G638</f>
+        <v>417.72000000000008</v>
+      </c>
+      <c r="M638" s="18">
+        <f>L638/2</f>
+        <v>208.86000000000004</v>
+      </c>
+    </row>
+    <row r="639" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A639" s="49"/>
+      <c r="G639" s="18">
+        <v>4</v>
+      </c>
+      <c r="H639" s="18">
+        <f>E629/G639</f>
+        <v>11.025</v>
+      </c>
+      <c r="I639" s="18">
+        <f t="shared" si="27"/>
+        <v>486.20250000000004</v>
+      </c>
+      <c r="J639" s="18">
+        <f t="shared" ref="J639:J649" si="28">I639/2</f>
+        <v>243.10125000000002</v>
+      </c>
+      <c r="K639" s="18">
+        <f>E627/G639</f>
+        <v>8.8500000000000014</v>
+      </c>
+      <c r="L639" s="18">
+        <f>E627*E627/G639</f>
+        <v>313.29000000000008</v>
+      </c>
+      <c r="M639" s="18">
+        <f t="shared" ref="M639:M649" si="29">L639/2</f>
+        <v>156.64500000000004</v>
+      </c>
+    </row>
+    <row r="640" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A640" s="49"/>
+      <c r="C640" t="s">
+        <v>795</v>
+      </c>
+      <c r="E640">
+        <f>(POWER(E629,2))/(200*2)</f>
+        <v>4.862025</v>
+      </c>
+      <c r="G640" s="18">
+        <v>5</v>
+      </c>
+      <c r="H640" s="18">
+        <f>E629/G640</f>
+        <v>8.82</v>
+      </c>
+      <c r="I640" s="18">
+        <f t="shared" si="27"/>
+        <v>388.96199999999999</v>
+      </c>
+      <c r="J640" s="18">
+        <f t="shared" si="28"/>
+        <v>194.48099999999999</v>
+      </c>
+      <c r="K640" s="18">
+        <f>E627/G640</f>
+        <v>7.080000000000001</v>
+      </c>
+      <c r="L640" s="18">
+        <f>E627*E627/G640</f>
+        <v>250.63200000000006</v>
+      </c>
+      <c r="M640" s="18">
+        <f t="shared" si="29"/>
+        <v>125.31600000000003</v>
+      </c>
+      <c r="N640" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="641" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A641" s="49"/>
+      <c r="C641" t="s">
+        <v>796</v>
+      </c>
+      <c r="E641">
+        <f>E629/E640</f>
+        <v>9.0702947845804989</v>
+      </c>
+      <c r="G641" s="18">
+        <v>6</v>
+      </c>
+      <c r="H641" s="18">
+        <f>E629/G641</f>
+        <v>7.3500000000000005</v>
+      </c>
+      <c r="I641" s="18">
+        <f t="shared" si="27"/>
+        <v>324.13500000000005</v>
+      </c>
+      <c r="J641" s="18">
+        <f t="shared" si="28"/>
+        <v>162.06750000000002</v>
+      </c>
+      <c r="K641" s="18">
+        <f>E627/G641</f>
+        <v>5.9000000000000012</v>
+      </c>
+      <c r="L641" s="18">
+        <f>E627*E627/G641</f>
+        <v>208.86000000000004</v>
+      </c>
+      <c r="M641" s="18">
+        <f t="shared" si="29"/>
+        <v>104.43000000000002</v>
+      </c>
+      <c r="N641" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="642" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G642" s="18">
+        <v>7</v>
+      </c>
+      <c r="H642" s="18">
+        <f>E629/G642</f>
+        <v>6.3</v>
+      </c>
+      <c r="I642" s="18">
+        <f t="shared" si="27"/>
+        <v>277.83</v>
+      </c>
+      <c r="J642" s="18">
+        <f t="shared" si="28"/>
+        <v>138.91499999999999</v>
+      </c>
+      <c r="K642" s="18">
+        <f>E627/G642</f>
+        <v>5.0571428571428578</v>
+      </c>
+      <c r="L642" s="18">
+        <f>E627*E627/G642</f>
+        <v>179.02285714285719</v>
+      </c>
+      <c r="M642" s="18">
+        <f t="shared" si="29"/>
+        <v>89.511428571428596</v>
+      </c>
+      <c r="N642" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="643" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G643" s="18">
+        <v>8</v>
+      </c>
+      <c r="H643" s="18">
+        <f>E629/G643</f>
+        <v>5.5125000000000002</v>
+      </c>
+      <c r="I643" s="18">
+        <f t="shared" si="27"/>
+        <v>243.10125000000002</v>
+      </c>
+      <c r="J643" s="18">
+        <f t="shared" si="28"/>
+        <v>121.55062500000001</v>
+      </c>
+      <c r="K643" s="18">
+        <f>E627/G643</f>
+        <v>4.4250000000000007</v>
+      </c>
+      <c r="L643" s="18">
+        <f>E627*E627/G643</f>
+        <v>156.64500000000004</v>
+      </c>
+      <c r="M643" s="18">
+        <f t="shared" si="29"/>
+        <v>78.322500000000019</v>
+      </c>
+      <c r="N643" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="644" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G644" s="18">
+        <v>9</v>
+      </c>
+      <c r="H644" s="18">
+        <f>E629/G644</f>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="I644" s="18">
+        <f t="shared" si="27"/>
+        <v>216.09000000000003</v>
+      </c>
+      <c r="J644" s="18">
+        <f t="shared" si="28"/>
+        <v>108.04500000000002</v>
+      </c>
+      <c r="K644" s="18">
+        <f>E627/G644</f>
+        <v>3.933333333333334</v>
+      </c>
+      <c r="L644" s="18">
+        <f>E627*E627/G644</f>
+        <v>139.24000000000004</v>
+      </c>
+      <c r="M644" s="18">
+        <f t="shared" si="29"/>
+        <v>69.620000000000019</v>
+      </c>
+      <c r="N644" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="645" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G645" s="18">
+        <v>10</v>
+      </c>
+      <c r="H645" s="18">
+        <f>E629/G645</f>
+        <v>4.41</v>
+      </c>
+      <c r="I645" s="18">
+        <f t="shared" si="27"/>
+        <v>194.48099999999999</v>
+      </c>
+      <c r="J645" s="18">
+        <f t="shared" si="28"/>
+        <v>97.240499999999997</v>
+      </c>
+      <c r="K645" s="18">
+        <f>E627/G645</f>
+        <v>3.5400000000000005</v>
+      </c>
+      <c r="L645" s="18">
+        <f>E627*E627/G645</f>
+        <v>125.31600000000003</v>
+      </c>
+      <c r="M645" s="18">
+        <f t="shared" si="29"/>
+        <v>62.658000000000015</v>
+      </c>
+      <c r="N645" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="646" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G646" s="18">
+        <v>11</v>
+      </c>
+      <c r="H646" s="18">
+        <f>E629/G646</f>
+        <v>4.0090909090909088</v>
+      </c>
+      <c r="I646" s="18">
+        <f t="shared" si="27"/>
+        <v>176.80090909090904</v>
+      </c>
+      <c r="J646" s="18">
+        <f t="shared" si="28"/>
+        <v>88.400454545454522</v>
+      </c>
+      <c r="K646" s="18">
+        <f>E627/G646</f>
+        <v>3.2181818181818187</v>
+      </c>
+      <c r="L646" s="18">
+        <f>E627*E627/G646</f>
+        <v>113.92363636363639</v>
+      </c>
+      <c r="M646" s="18">
+        <f t="shared" si="29"/>
+        <v>56.961818181818195</v>
+      </c>
+      <c r="N646" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="647" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G647" s="18">
+        <v>12</v>
+      </c>
+      <c r="H647" s="18">
+        <f>E629/G647</f>
+        <v>3.6750000000000003</v>
+      </c>
+      <c r="I647" s="18">
+        <f t="shared" si="27"/>
+        <v>162.06750000000002</v>
+      </c>
+      <c r="J647" s="18">
+        <f t="shared" si="28"/>
+        <v>81.033750000000012</v>
+      </c>
+      <c r="K647" s="18">
+        <f>E627/G647</f>
+        <v>2.9500000000000006</v>
+      </c>
+      <c r="L647" s="18">
+        <f>E627*E627/G647</f>
+        <v>104.43000000000002</v>
+      </c>
+      <c r="M647" s="18">
+        <f t="shared" si="29"/>
+        <v>52.215000000000011</v>
+      </c>
+      <c r="N647" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="648" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G648" s="18">
+        <v>13</v>
+      </c>
+      <c r="H648" s="18">
+        <f>E629/G648</f>
+        <v>3.3923076923076922</v>
+      </c>
+      <c r="I648" s="18">
+        <f t="shared" si="27"/>
+        <v>149.60076923076923</v>
+      </c>
+      <c r="J648" s="18">
+        <f t="shared" si="28"/>
+        <v>74.800384615384615</v>
+      </c>
+      <c r="K648" s="18">
+        <f>E627/G648</f>
+        <v>2.7230769230769236</v>
+      </c>
+      <c r="L648" s="18">
+        <f>E627*E627/G648</f>
+        <v>96.396923076923102</v>
+      </c>
+      <c r="M648" s="18">
+        <f t="shared" si="29"/>
+        <v>48.198461538461551</v>
+      </c>
+      <c r="N648" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="649" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G649" s="18">
+        <v>14</v>
+      </c>
+      <c r="H649" s="18">
+        <f>E629/G649</f>
+        <v>3.15</v>
+      </c>
+      <c r="I649" s="18">
+        <f t="shared" si="27"/>
+        <v>138.91499999999999</v>
+      </c>
+      <c r="J649" s="18">
+        <f t="shared" si="28"/>
+        <v>69.457499999999996</v>
+      </c>
+      <c r="K649" s="18">
+        <f>E627/G649</f>
+        <v>2.5285714285714289</v>
+      </c>
+      <c r="L649" s="18">
+        <f>E627*E627/G649</f>
+        <v>89.511428571428596</v>
+      </c>
+      <c r="M649" s="18">
+        <f t="shared" si="29"/>
+        <v>44.755714285714298</v>
+      </c>
+      <c r="N649" t="s">
+        <v>813</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="23">
     <mergeCell ref="A31:A59"/>
     <mergeCell ref="A593:A618"/>
     <mergeCell ref="A228:A279"/>
@@ -11616,6 +12331,7 @@
     <mergeCell ref="A171:A226"/>
     <mergeCell ref="A303:A315"/>
     <mergeCell ref="A579:A591"/>
+    <mergeCell ref="A627:A641"/>
     <mergeCell ref="A364:A376"/>
     <mergeCell ref="A377:A380"/>
     <mergeCell ref="A553:A564"/>
@@ -11915,17 +12631,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="53" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="53"/>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C18" s="49" t="s">
+      <c r="C18" s="54" t="s">
         <v>167</v>
       </c>
-      <c r="D18" s="50"/>
-      <c r="E18" s="51"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="56"/>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C19" s="18" t="s">
@@ -12119,17 +12835,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="53" t="s">
         <v>166</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="53"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="49" t="s">
+      <c r="B17" s="54" t="s">
         <v>167</v>
       </c>
-      <c r="C17" s="50"/>
-      <c r="D17" s="51"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="56"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B18" s="18" t="s">
@@ -12382,17 +13098,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="53" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="48"/>
+      <c r="B1" s="53"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="49" t="s">
+      <c r="B17" s="54" t="s">
         <v>167</v>
       </c>
-      <c r="C17" s="50"/>
-      <c r="D17" s="51"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="56"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B18" s="18" t="s">
@@ -12643,7 +13359,7 @@
   <sheetData>
     <row r="2" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="T2">
         <v>399</v>
@@ -12651,7 +13367,7 @@
     </row>
     <row r="3" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S3" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="T3">
         <v>14000</v>
@@ -12659,7 +13375,7 @@
     </row>
     <row r="4" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="T4" s="1">
         <v>5.4399999999999996E-6</v>
@@ -12667,7 +13383,7 @@
     </row>
     <row r="5" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="T5">
         <v>40</v>
@@ -12675,7 +13391,7 @@
     </row>
     <row r="6" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S6" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="T6">
         <v>20</v>
@@ -12683,7 +13399,7 @@
     </row>
     <row r="7" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="T7">
         <v>1E-4</v>
@@ -12691,7 +13407,7 @@
     </row>
     <row r="8" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S8" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="T8">
         <f>POWER(T4/T7, 0.5)</f>
@@ -12700,7 +13416,7 @@
     </row>
     <row r="9" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S9" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="T9">
         <v>0.1</v>
@@ -12708,7 +13424,7 @@
     </row>
     <row r="10" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S10" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="T10">
         <f>T9/T12</f>
@@ -12717,7 +13433,7 @@
     </row>
     <row r="11" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S11" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="T11">
         <f>T9/T12</f>
@@ -12726,7 +13442,7 @@
     </row>
     <row r="12" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S12" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="T12">
         <v>44.5</v>
@@ -12734,7 +13450,7 @@
     </row>
     <row r="13" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S13" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="T13">
         <f>T6-POWER(POWER((T9-(T11*T12))/T8, 2)+POWER(T6, 2), 0.5)</f>
@@ -12743,7 +13459,7 @@
     </row>
     <row r="14" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S14" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="T14">
         <f>(1/T11)*(T13-T6)</f>
@@ -12752,7 +13468,7 @@
     </row>
     <row r="15" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S15" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="T15">
         <f>T13-T14</f>
@@ -12761,7 +13477,7 @@
     </row>
     <row r="16" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S16" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="T16">
         <f>T5</f>
@@ -12770,7 +13486,7 @@
     </row>
     <row r="17" spans="19:21" x14ac:dyDescent="0.25">
       <c r="S17" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="T17">
         <f>T4*POWER(T5, 2)/POWER(T9-(T3/T2), 2)</f>
@@ -12779,7 +13495,7 @@
     </row>
     <row r="18" spans="19:21" x14ac:dyDescent="0.25">
       <c r="S18" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="T18" t="str">
         <f>IF(T11&lt;T9/T12, "Decrease V_max by", "Increase V_max by")</f>
@@ -12818,116 +13534,116 @@
   <sheetData>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C3" t="s">
         <v>129</v>
       </c>
       <c r="D3" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D4">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B5" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D5">
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B6" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D6">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B7" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B8" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D8">
         <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B9" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D9">
         <v>4</v>
       </c>
       <c r="E9" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E10" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B11" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D11">
         <v>16</v>

--- a/Spreadsheets/BasicCalculations.xlsx
+++ b/Spreadsheets/BasicCalculations.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="817">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1185" uniqueCount="866">
   <si>
     <t>N stages required</t>
   </si>
@@ -2498,6 +2498,153 @@
   <si>
     <t>Use this number to begin with</t>
   </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>drive frequency (Hz) (16 kHz nominal)</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>CT turns ratio (e.g. 1000:1 ⇒ N=1000)</t>
+  </si>
+  <si>
+    <t>Vadc_fs</t>
+  </si>
+  <si>
+    <t>Vf</t>
+  </si>
+  <si>
+    <t>forward drop of one rectifier diode at your CT secondary current (V)</t>
+  </si>
+  <si>
+    <t>Burden resistor resistance = Vtarget_pk / Isec_pk</t>
+  </si>
+  <si>
+    <t>Rb_suggested</t>
+  </si>
+  <si>
+    <t>Rb_actual</t>
+  </si>
+  <si>
+    <t>Actual value chosen</t>
+  </si>
+  <si>
+    <t>Primary peak current (A) under typical operating conditions</t>
+  </si>
+  <si>
+    <t>Maximum peak current to ever be potentially seen</t>
+  </si>
+  <si>
+    <t>I_pri_pk_max</t>
+  </si>
+  <si>
+    <t>Expected RMS at the maximum operating point</t>
+  </si>
+  <si>
+    <t>I_pri_rms_max</t>
+  </si>
+  <si>
+    <t>I_sec_pk_max</t>
+  </si>
+  <si>
+    <t>I_sec_rms_max</t>
+  </si>
+  <si>
+    <t>ADC full-scale you want to use at the maximum primary peak current</t>
+  </si>
+  <si>
+    <t>Peak power in Rb at maximum primary current</t>
+  </si>
+  <si>
+    <t>Peak power seen in a bridge rectifier diode at maximum primary current</t>
+  </si>
+  <si>
+    <t>Actual peak voltage seen by ADC at maximum primary current</t>
+  </si>
+  <si>
+    <t>Vadc_actual_pk_max</t>
+  </si>
+  <si>
+    <t>P_D_peak_max</t>
+  </si>
+  <si>
+    <t>P_Rb_peak_max</t>
+  </si>
+  <si>
+    <t>Peak power in Rb at typical peak primary current</t>
+  </si>
+  <si>
+    <t>P_Rb_peak_typ</t>
+  </si>
+  <si>
+    <t>I_sec_pk_typ</t>
+  </si>
+  <si>
+    <t>P_D_peak_typ</t>
+  </si>
+  <si>
+    <t>Peak power seen in a bridge rectifier diode at typical peak primary current</t>
+  </si>
+  <si>
+    <t>V_adc_peak_typ</t>
+  </si>
+  <si>
+    <t>Typical Peak voltage seen by ADC</t>
+  </si>
+  <si>
+    <t>P_Rb_average_max</t>
+  </si>
+  <si>
+    <t>P_Rb_average_typ</t>
+  </si>
+  <si>
+    <t>Average power in Rb at typical primary current</t>
+  </si>
+  <si>
+    <t>Average power in Rb at maximum primary current</t>
+  </si>
+  <si>
+    <t>I_sec_rms_typ</t>
+  </si>
+  <si>
+    <t>I_pri_rms_typ</t>
+  </si>
+  <si>
+    <t>I_pri_pk_typ</t>
+  </si>
+  <si>
+    <t>Rb_peak_max</t>
+  </si>
+  <si>
+    <t>Maximum peak burden seen by current transformer</t>
+  </si>
+  <si>
+    <t>Id_pk</t>
+  </si>
+  <si>
+    <t>Minimum diode current rating (comfortably rated for repetitive peak current)</t>
+  </si>
+  <si>
+    <t>Id_actual</t>
+  </si>
+  <si>
+    <t>Actual diode repetitive peak current rating</t>
+  </si>
+  <si>
+    <t>V_zener_min_actual</t>
+  </si>
+  <si>
+    <t>Minimum ADC input protection zener diode voltage</t>
+  </si>
+  <si>
+    <t>R_series_min</t>
+  </si>
+  <si>
+    <t>Minimum resistor value between Rb node and ADC input node</t>
+  </si>
 </sst>
 </file>
 
@@ -2507,7 +2654,7 @@
     <numFmt numFmtId="6" formatCode="&quot;£&quot;#,##0;[Red]\-&quot;£&quot;#,##0"/>
     <numFmt numFmtId="8" formatCode="&quot;£&quot;#,##0.00;[Red]\-&quot;£&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2574,6 +2721,12 @@
       <sz val="11"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -2695,7 +2848,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2777,6 +2930,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2797,6 +2956,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3248,13 +3408,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>394607</xdr:colOff>
-      <xdr:row>556</xdr:row>
+      <xdr:row>585</xdr:row>
       <xdr:rowOff>81643</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>1282199</xdr:colOff>
-      <xdr:row>578</xdr:row>
+      <xdr:row>607</xdr:row>
       <xdr:rowOff>101281</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4174,7 +4334,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R649"/>
+  <dimension ref="A1:R678"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" customWidth="1"/>
@@ -4421,15 +4581,15 @@
       <c r="C19" s="8"/>
       <c r="D19" s="13"/>
       <c r="E19" s="8"/>
-      <c r="G19" s="51" t="s">
+      <c r="G19" s="53" t="s">
         <v>589</v>
       </c>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="51"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="50" t="s">
+      <c r="A20" s="52" t="s">
         <v>103</v>
       </c>
       <c r="B20" t="s">
@@ -4444,13 +4604,13 @@
       <c r="E20" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="51"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="50"/>
+      <c r="A21" s="52"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6" t="s">
         <v>3</v>
@@ -4462,13 +4622,13 @@
       <c r="E21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="51"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="50"/>
+      <c r="A22" s="52"/>
       <c r="B22" t="s">
         <v>67</v>
       </c>
@@ -4478,13 +4638,13 @@
       <c r="D22">
         <v>0.1</v>
       </c>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="51"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="50"/>
+      <c r="A23" s="52"/>
       <c r="B23" s="6"/>
       <c r="C23" s="12" t="s">
         <v>72</v>
@@ -4496,7 +4656,7 @@
       <c r="E23" s="6"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="50"/>
+      <c r="A24" s="52"/>
       <c r="C24" t="s">
         <v>7</v>
       </c>
@@ -4505,7 +4665,7 @@
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="50"/>
+      <c r="A25" s="52"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6" t="s">
         <v>28</v>
@@ -4514,7 +4674,7 @@
       <c r="E25" s="6"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="50"/>
+      <c r="A26" s="52"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
         <v>12</v>
@@ -4528,7 +4688,7 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="50"/>
+      <c r="A27" s="52"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6" t="s">
         <v>11</v>
@@ -4542,7 +4702,7 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="50"/>
+      <c r="A28" s="52"/>
       <c r="C28" t="s">
         <v>8</v>
       </c>
@@ -4554,7 +4714,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="50"/>
+      <c r="A29" s="52"/>
       <c r="C29" t="s">
         <v>10</v>
       </c>
@@ -4565,41 +4725,41 @@
       <c r="E29" t="s">
         <v>25</v>
       </c>
-      <c r="G29" s="51" t="s">
+      <c r="G29" s="53" t="s">
         <v>590</v>
       </c>
-      <c r="H29" s="52"/>
-      <c r="I29" s="52"/>
-      <c r="J29" s="52"/>
-      <c r="K29" s="52"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="54"/>
+      <c r="K29" s="54"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B30" s="8"/>
       <c r="C30" s="10"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="52"/>
-      <c r="K30" s="52"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="54"/>
+      <c r="K30" s="54"/>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="52" t="s">
         <v>132</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="7"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="52"/>
-      <c r="K31" s="52"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="54"/>
+      <c r="J31" s="54"/>
+      <c r="K31" s="54"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="50"/>
+      <c r="A32" s="52"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6" t="s">
         <v>126</v>
@@ -4611,14 +4771,14 @@
       <c r="E32" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
-      <c r="K32" s="52"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="54"/>
+      <c r="J32" s="54"/>
+      <c r="K32" s="54"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="50"/>
+      <c r="A33" s="52"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8" t="s">
         <v>127</v>
@@ -4629,14 +4789,14 @@
       <c r="E33" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G33" s="52"/>
-      <c r="H33" s="52"/>
-      <c r="I33" s="52"/>
-      <c r="J33" s="52"/>
-      <c r="K33" s="52"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="54"/>
+      <c r="J33" s="54"/>
+      <c r="K33" s="54"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="50"/>
+      <c r="A34" s="52"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8" t="s">
         <v>128</v>
@@ -4645,14 +4805,14 @@
         <v>5</v>
       </c>
       <c r="E34" s="9"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="52"/>
-      <c r="K34" s="52"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="54"/>
+      <c r="J34" s="54"/>
+      <c r="K34" s="54"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="50"/>
+      <c r="A35" s="52"/>
       <c r="C35" t="s">
         <v>133</v>
       </c>
@@ -4662,7 +4822,7 @@
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="50"/>
+      <c r="A36" s="52"/>
       <c r="C36" t="s">
         <v>136</v>
       </c>
@@ -4674,7 +4834,7 @@
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="50"/>
+      <c r="A37" s="52"/>
       <c r="C37" t="s">
         <v>169</v>
       </c>
@@ -4684,7 +4844,7 @@
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="50"/>
+      <c r="A38" s="52"/>
       <c r="C38" t="s">
         <v>170</v>
       </c>
@@ -4694,7 +4854,7 @@
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="50"/>
+      <c r="A39" s="52"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6" t="s">
         <v>9</v>
@@ -4708,7 +4868,7 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="50"/>
+      <c r="A40" s="52"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6" t="s">
         <v>772</v>
@@ -4722,7 +4882,7 @@
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="50"/>
+      <c r="A41" s="52"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6" t="s">
         <v>171</v>
@@ -4734,7 +4894,7 @@
       <c r="E41" s="6"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="50"/>
+      <c r="A42" s="52"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
         <v>172</v>
@@ -4746,7 +4906,7 @@
       <c r="E42" s="6"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="50"/>
+      <c r="A43" s="52"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6" t="s">
         <v>773</v>
@@ -4760,7 +4920,7 @@
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="50"/>
+      <c r="A44" s="52"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6" t="s">
         <v>27</v>
@@ -4774,7 +4934,7 @@
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="50"/>
+      <c r="A45" s="52"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6" t="s">
         <v>770</v>
@@ -4787,7 +4947,7 @@
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="50"/>
+      <c r="A46" s="52"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6" t="s">
         <v>771</v>
@@ -4799,7 +4959,7 @@
       <c r="E46" s="6"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="50"/>
+      <c r="A47" s="52"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6" t="s">
         <v>774</v>
@@ -4811,14 +4971,14 @@
       <c r="E47" s="6"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="50"/>
+      <c r="A48" s="52"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
       <c r="D48" s="11"/>
       <c r="E48" s="6"/>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A49" s="50"/>
+      <c r="A49" s="52"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8" t="s">
         <v>776</v>
@@ -4830,7 +4990,7 @@
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A50" s="50"/>
+      <c r="A50" s="52"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8" t="s">
         <v>682</v>
@@ -4841,7 +5001,7 @@
       <c r="E50" s="8"/>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A51" s="50"/>
+      <c r="A51" s="52"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8" t="s">
         <v>683</v>
@@ -4852,7 +5012,7 @@
       <c r="E51" s="8"/>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A52" s="50"/>
+      <c r="A52" s="52"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8" t="s">
         <v>777</v>
@@ -4864,7 +5024,7 @@
       <c r="E52" s="8"/>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A53" s="50"/>
+      <c r="A53" s="52"/>
       <c r="B53" s="44"/>
       <c r="C53" s="44" t="s">
         <v>200</v>
@@ -4876,7 +5036,7 @@
       <c r="E53" s="44"/>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A54" s="50"/>
+      <c r="A54" s="52"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6" t="s">
         <v>779</v>
@@ -4888,7 +5048,7 @@
       <c r="E54" s="6"/>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A55" s="50"/>
+      <c r="A55" s="52"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6" t="s">
         <v>780</v>
@@ -4901,7 +5061,7 @@
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A56" s="50"/>
+      <c r="A56" s="52"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6" t="s">
         <v>782</v>
@@ -4912,7 +5072,7 @@
       <c r="E56" s="6"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A57" s="50"/>
+      <c r="A57" s="52"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6" t="s">
         <v>778</v>
@@ -4924,7 +5084,7 @@
       <c r="E57" s="6"/>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A58" s="50"/>
+      <c r="A58" s="52"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6" t="s">
         <v>783</v>
@@ -4936,7 +5096,7 @@
       <c r="E58" s="6"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A59" s="50"/>
+      <c r="A59" s="52"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6" t="s">
         <v>784</v>
@@ -4960,7 +5120,7 @@
       </c>
     </row>
     <row r="61" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="50" t="s">
+      <c r="A61" s="52" t="s">
         <v>30</v>
       </c>
       <c r="C61" s="8" t="s">
@@ -4984,7 +5144,7 @@
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A62" s="50"/>
+      <c r="A62" s="52"/>
       <c r="C62" s="8" t="s">
         <v>26</v>
       </c>
@@ -5006,7 +5166,7 @@
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A63" s="50"/>
+      <c r="A63" s="52"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6" t="s">
         <v>13</v>
@@ -5030,7 +5190,7 @@
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A64" s="50"/>
+      <c r="A64" s="52"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6" t="s">
         <v>14</v>
@@ -5051,7 +5211,7 @@
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A65" s="50"/>
+      <c r="A65" s="52"/>
       <c r="C65" s="8" t="s">
         <v>16</v>
       </c>
@@ -5074,7 +5234,7 @@
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A66" s="50"/>
+      <c r="A66" s="52"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6" t="s">
         <v>107</v>
@@ -5095,7 +5255,7 @@
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A67" s="50"/>
+      <c r="A67" s="52"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6" t="s">
         <v>15</v>
@@ -5116,7 +5276,7 @@
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A68" s="50"/>
+      <c r="A68" s="52"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6" t="s">
         <v>32</v>
@@ -5128,7 +5288,7 @@
       <c r="E68" s="6"/>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A69" s="50"/>
+      <c r="A69" s="52"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6" t="s">
         <v>108</v>
@@ -5147,7 +5307,7 @@
       <c r="E70" s="8"/>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A71" s="49" t="s">
+      <c r="A71" s="51" t="s">
         <v>109</v>
       </c>
       <c r="C71" s="6"/>
@@ -5155,7 +5315,7 @@
       <c r="E71" s="6"/>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A72" s="49"/>
+      <c r="A72" s="51"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6" t="s">
         <v>90</v>
@@ -5167,7 +5327,7 @@
       <c r="E72" s="6"/>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A73" s="49"/>
+      <c r="A73" s="51"/>
       <c r="B73" s="6" t="s">
         <v>124</v>
       </c>
@@ -5183,7 +5343,7 @@
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A74" s="49"/>
+      <c r="A74" s="51"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6" t="s">
         <v>135</v>
@@ -5195,7 +5355,7 @@
       <c r="E74" s="6"/>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A75" s="49"/>
+      <c r="A75" s="51"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6" t="s">
         <v>91</v>
@@ -5208,7 +5368,7 @@
       <c r="R75" s="1"/>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A76" s="49"/>
+      <c r="A76" s="51"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6" t="s">
         <v>92</v>
@@ -5220,7 +5380,7 @@
       <c r="E76" s="6"/>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A77" s="49"/>
+      <c r="A77" s="51"/>
       <c r="B77" s="6" t="s">
         <v>123</v>
       </c>
@@ -5234,7 +5394,7 @@
       <c r="E77" s="6"/>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A78" s="49"/>
+      <c r="A78" s="51"/>
       <c r="B78" s="6" t="s">
         <v>119</v>
       </c>
@@ -5248,7 +5408,7 @@
       <c r="E78" s="6"/>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A79" s="49"/>
+      <c r="A79" s="51"/>
       <c r="B79" s="6" t="s">
         <v>122</v>
       </c>
@@ -5262,7 +5422,7 @@
       <c r="E79" s="6"/>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A80" s="49"/>
+      <c r="A80" s="51"/>
       <c r="C80" t="s">
         <v>94</v>
       </c>
@@ -5271,7 +5431,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="49"/>
+      <c r="A81" s="51"/>
       <c r="C81" t="s">
         <v>95</v>
       </c>
@@ -5280,7 +5440,7 @@
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="49"/>
+      <c r="A82" s="51"/>
       <c r="C82" t="s">
         <v>96</v>
       </c>
@@ -5295,7 +5455,7 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="49"/>
+      <c r="A83" s="51"/>
       <c r="C83" t="s">
         <v>97</v>
       </c>
@@ -5305,7 +5465,7 @@
       <c r="G83" s="5"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="49"/>
+      <c r="A84" s="51"/>
       <c r="C84" t="s">
         <v>98</v>
       </c>
@@ -5314,7 +5474,7 @@
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="49"/>
+      <c r="A85" s="51"/>
       <c r="C85" t="s">
         <v>99</v>
       </c>
@@ -5323,7 +5483,7 @@
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="49"/>
+      <c r="A86" s="51"/>
       <c r="C86" t="s">
         <v>100</v>
       </c>
@@ -5332,7 +5492,7 @@
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="49"/>
+      <c r="A87" s="51"/>
       <c r="C87" t="s">
         <v>113</v>
       </c>
@@ -5341,7 +5501,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="49"/>
+      <c r="A88" s="51"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6" t="s">
         <v>110</v>
@@ -5353,7 +5513,7 @@
       <c r="E88" s="6"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="49"/>
+      <c r="A89" s="51"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6" t="s">
         <v>111</v>
@@ -5365,7 +5525,7 @@
       <c r="E89" s="6"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="49"/>
+      <c r="A90" s="51"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6" t="s">
         <v>112</v>
@@ -5377,7 +5537,7 @@
       <c r="E90" s="6"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="49"/>
+      <c r="A91" s="51"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6" t="s">
         <v>114</v>
@@ -5389,7 +5549,7 @@
       <c r="E91" s="6"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="49"/>
+      <c r="A92" s="51"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6" t="s">
         <v>115</v>
@@ -5401,7 +5561,7 @@
       <c r="E92" s="6"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="49"/>
+      <c r="A93" s="51"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6" t="s">
         <v>116</v>
@@ -5413,7 +5573,7 @@
       <c r="E93" s="6"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="49"/>
+      <c r="A94" s="51"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6" t="s">
         <v>117</v>
@@ -5425,7 +5585,7 @@
       <c r="E94" s="6"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="49"/>
+      <c r="A95" s="51"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6" t="s">
         <v>118</v>
@@ -5446,7 +5606,7 @@
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="50" t="s">
+      <c r="A98" s="52" t="s">
         <v>125</v>
       </c>
       <c r="B98" s="6" t="s">
@@ -5462,7 +5622,7 @@
       <c r="E98" s="2"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="50"/>
+      <c r="A99" s="52"/>
       <c r="B99" t="s">
         <v>58</v>
       </c>
@@ -5474,7 +5634,7 @@
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="50"/>
+      <c r="A100" s="52"/>
       <c r="B100" t="s">
         <v>57</v>
       </c>
@@ -5483,7 +5643,7 @@
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="50"/>
+      <c r="A101" s="52"/>
       <c r="B101" t="s">
         <v>51</v>
       </c>
@@ -5495,7 +5655,7 @@
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="50"/>
+      <c r="A102" s="52"/>
       <c r="C102" t="s">
         <v>36</v>
       </c>
@@ -5504,7 +5664,7 @@
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="50"/>
+      <c r="A103" s="52"/>
       <c r="B103" t="s">
         <v>39</v>
       </c>
@@ -5516,7 +5676,7 @@
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="50"/>
+      <c r="A104" s="52"/>
       <c r="B104" t="s">
         <v>578</v>
       </c>
@@ -5529,7 +5689,7 @@
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="50"/>
+      <c r="A105" s="52"/>
       <c r="B105" t="s">
         <v>41</v>
       </c>
@@ -5542,7 +5702,7 @@
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="50"/>
+      <c r="A106" s="52"/>
       <c r="C106" t="s">
         <v>40</v>
       </c>
@@ -5552,7 +5712,7 @@
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="50"/>
+      <c r="A107" s="52"/>
       <c r="B107" t="s">
         <v>45</v>
       </c>
@@ -5565,7 +5725,7 @@
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="50"/>
+      <c r="A108" s="52"/>
       <c r="B108" t="s">
         <v>53</v>
       </c>
@@ -5578,7 +5738,7 @@
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="50"/>
+      <c r="A109" s="52"/>
       <c r="B109" t="s">
         <v>55</v>
       </c>
@@ -5591,7 +5751,7 @@
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="50"/>
+      <c r="A110" s="52"/>
       <c r="C110" t="s">
         <v>60</v>
       </c>
@@ -5601,7 +5761,7 @@
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="50"/>
+      <c r="A111" s="52"/>
       <c r="B111" t="s">
         <v>580</v>
       </c>
@@ -5614,7 +5774,7 @@
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="50"/>
+      <c r="A112" s="52"/>
       <c r="B112" t="s">
         <v>581</v>
       </c>
@@ -5630,7 +5790,7 @@
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="50"/>
+      <c r="A113" s="52"/>
       <c r="B113" t="s">
         <v>64</v>
       </c>
@@ -5643,7 +5803,7 @@
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="50"/>
+      <c r="A114" s="52"/>
       <c r="C114" t="s">
         <v>66</v>
       </c>
@@ -5653,7 +5813,7 @@
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="50"/>
+      <c r="A115" s="52"/>
       <c r="B115" t="s">
         <v>68</v>
       </c>
@@ -5669,7 +5829,7 @@
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="50"/>
+      <c r="A116" s="52"/>
       <c r="B116" t="s">
         <v>815</v>
       </c>
@@ -5685,7 +5845,7 @@
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="50"/>
+      <c r="A117" s="52"/>
       <c r="B117" t="s">
         <v>174</v>
       </c>
@@ -5698,7 +5858,7 @@
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="50"/>
+      <c r="A118" s="52"/>
       <c r="C118" t="s">
         <v>176</v>
       </c>
@@ -5707,7 +5867,7 @@
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="50"/>
+      <c r="A119" s="52"/>
       <c r="C119" t="s">
         <v>227</v>
       </c>
@@ -5717,7 +5877,7 @@
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="50"/>
+      <c r="A120" s="52"/>
       <c r="C120" t="s">
         <v>187</v>
       </c>
@@ -5729,7 +5889,7 @@
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="50"/>
+      <c r="A121" s="52"/>
       <c r="C121" t="s">
         <v>185</v>
       </c>
@@ -5741,7 +5901,7 @@
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="50"/>
+      <c r="A122" s="52"/>
       <c r="C122" t="s">
         <v>184</v>
       </c>
@@ -5750,7 +5910,7 @@
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="50"/>
+      <c r="A123" s="52"/>
       <c r="C123" t="s">
         <v>178</v>
       </c>
@@ -5763,7 +5923,7 @@
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="50"/>
+      <c r="A124" s="52"/>
       <c r="C124" t="s">
         <v>179</v>
       </c>
@@ -5776,7 +5936,7 @@
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="50"/>
+      <c r="A125" s="52"/>
       <c r="C125" t="s">
         <v>180</v>
       </c>
@@ -5788,7 +5948,7 @@
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="50"/>
+      <c r="A126" s="52"/>
       <c r="C126" t="s">
         <v>189</v>
       </c>
@@ -5801,7 +5961,7 @@
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="50"/>
+      <c r="A127" s="52"/>
       <c r="C127" t="s">
         <v>181</v>
       </c>
@@ -5811,7 +5971,7 @@
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="50"/>
+      <c r="A128" s="52"/>
       <c r="C128" t="s">
         <v>182</v>
       </c>
@@ -5821,7 +5981,7 @@
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="50"/>
+      <c r="A129" s="52"/>
       <c r="C129" t="s">
         <v>177</v>
       </c>
@@ -5831,7 +5991,7 @@
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="50"/>
+      <c r="A130" s="52"/>
       <c r="C130" t="s">
         <v>183</v>
       </c>
@@ -5841,7 +6001,7 @@
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="50"/>
+      <c r="A131" s="52"/>
       <c r="C131" t="s">
         <v>195</v>
       </c>
@@ -5851,7 +6011,7 @@
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="50"/>
+      <c r="A132" s="52"/>
       <c r="C132" t="s">
         <v>194</v>
       </c>
@@ -5864,7 +6024,7 @@
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="50"/>
+      <c r="A133" s="52"/>
       <c r="C133" t="s">
         <v>186</v>
       </c>
@@ -5874,7 +6034,7 @@
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" s="50"/>
+      <c r="A134" s="52"/>
       <c r="C134" t="s">
         <v>188</v>
       </c>
@@ -5884,7 +6044,7 @@
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" s="50"/>
+      <c r="A135" s="52"/>
       <c r="C135" t="s">
         <v>189</v>
       </c>
@@ -5894,7 +6054,7 @@
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="50"/>
+      <c r="A136" s="52"/>
       <c r="C136" t="s">
         <v>190</v>
       </c>
@@ -5907,7 +6067,7 @@
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" s="50"/>
+      <c r="A137" s="52"/>
       <c r="C137" t="s">
         <v>191</v>
       </c>
@@ -5916,7 +6076,7 @@
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" s="50"/>
+      <c r="A138" s="52"/>
       <c r="C138" t="s">
         <v>193</v>
       </c>
@@ -5926,7 +6086,7 @@
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" s="50"/>
+      <c r="A139" s="52"/>
       <c r="C139" t="s">
         <v>225</v>
       </c>
@@ -5936,7 +6096,7 @@
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" s="50"/>
+      <c r="A140" s="52"/>
       <c r="C140" t="s">
         <v>201</v>
       </c>
@@ -5945,7 +6105,7 @@
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A141" s="50"/>
+      <c r="A141" s="52"/>
       <c r="C141" t="s">
         <v>200</v>
       </c>
@@ -5955,7 +6115,7 @@
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" s="50"/>
+      <c r="A142" s="52"/>
       <c r="C142" t="s">
         <v>202</v>
       </c>
@@ -5968,19 +6128,19 @@
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143" s="50"/>
+      <c r="A143" s="52"/>
       <c r="C143" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A144" s="50"/>
+      <c r="A144" s="52"/>
       <c r="C144" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" s="50"/>
+      <c r="A145" s="52"/>
       <c r="C145" t="s">
         <v>199</v>
       </c>
@@ -5992,7 +6152,7 @@
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A146" s="50"/>
+      <c r="A146" s="52"/>
       <c r="C146" t="s">
         <v>209</v>
       </c>
@@ -6002,7 +6162,7 @@
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" s="50"/>
+      <c r="A147" s="52"/>
       <c r="C147" t="s">
         <v>198</v>
       </c>
@@ -6011,7 +6171,7 @@
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" s="50"/>
+      <c r="A148" s="52"/>
       <c r="C148" t="s">
         <v>203</v>
       </c>
@@ -6020,7 +6180,7 @@
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149" s="50"/>
+      <c r="A149" s="52"/>
       <c r="C149" t="s">
         <v>204</v>
       </c>
@@ -6030,7 +6190,7 @@
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A150" s="50"/>
+      <c r="A150" s="52"/>
       <c r="C150" t="s">
         <v>189</v>
       </c>
@@ -6040,7 +6200,7 @@
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151" s="50"/>
+      <c r="A151" s="52"/>
       <c r="C151" t="s">
         <v>190</v>
       </c>
@@ -6050,7 +6210,7 @@
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A152" s="50"/>
+      <c r="A152" s="52"/>
       <c r="C152" t="s">
         <v>206</v>
       </c>
@@ -6063,7 +6223,7 @@
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153" s="50"/>
+      <c r="A153" s="52"/>
       <c r="C153" t="s">
         <v>207</v>
       </c>
@@ -6076,7 +6236,7 @@
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A154" s="50"/>
+      <c r="A154" s="52"/>
       <c r="C154" t="s">
         <v>208</v>
       </c>
@@ -6089,7 +6249,7 @@
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" s="50"/>
+      <c r="A155" s="52"/>
       <c r="C155" t="s">
         <v>210</v>
       </c>
@@ -6102,7 +6262,7 @@
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" s="50"/>
+      <c r="A156" s="52"/>
       <c r="C156" t="s">
         <v>211</v>
       </c>
@@ -6115,7 +6275,7 @@
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A157" s="50"/>
+      <c r="A157" s="52"/>
       <c r="C157" t="s">
         <v>201</v>
       </c>
@@ -6124,7 +6284,7 @@
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A158" s="50"/>
+      <c r="A158" s="52"/>
       <c r="C158" t="s">
         <v>215</v>
       </c>
@@ -6134,7 +6294,7 @@
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159" s="50"/>
+      <c r="A159" s="52"/>
       <c r="C159" t="s">
         <v>216</v>
       </c>
@@ -6144,7 +6304,7 @@
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A160" s="50"/>
+      <c r="A160" s="52"/>
       <c r="C160" t="s">
         <v>217</v>
       </c>
@@ -6157,7 +6317,7 @@
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A161" s="50"/>
+      <c r="A161" s="52"/>
       <c r="C161" t="s">
         <v>218</v>
       </c>
@@ -6167,7 +6327,7 @@
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A162" s="50"/>
+      <c r="A162" s="52"/>
       <c r="C162" t="s">
         <v>219</v>
       </c>
@@ -6177,7 +6337,7 @@
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A163" s="50"/>
+      <c r="A163" s="52"/>
       <c r="C163" t="s">
         <v>220</v>
       </c>
@@ -6187,7 +6347,7 @@
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A164" s="50"/>
+      <c r="A164" s="52"/>
       <c r="C164" t="s">
         <v>221</v>
       </c>
@@ -6197,7 +6357,7 @@
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A165" s="50"/>
+      <c r="A165" s="52"/>
       <c r="C165" t="s">
         <v>222</v>
       </c>
@@ -6207,7 +6367,7 @@
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A166" s="50"/>
+      <c r="A166" s="52"/>
       <c r="C166" t="s">
         <v>223</v>
       </c>
@@ -6220,7 +6380,7 @@
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A167" s="50"/>
+      <c r="A167" s="52"/>
       <c r="C167" t="s">
         <v>295</v>
       </c>
@@ -6229,7 +6389,7 @@
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A168" s="50"/>
+      <c r="A168" s="52"/>
       <c r="C168" t="s">
         <v>814</v>
       </c>
@@ -6239,7 +6399,7 @@
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A169" s="50"/>
+      <c r="A169" s="52"/>
       <c r="C169" t="s">
         <v>231</v>
       </c>
@@ -6252,7 +6412,7 @@
       <c r="A170" s="24"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A171" s="49" t="s">
+      <c r="A171" s="51" t="s">
         <v>537</v>
       </c>
       <c r="B171" t="s">
@@ -6264,7 +6424,7 @@
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A172" s="49"/>
+      <c r="A172" s="51"/>
       <c r="B172" t="s">
         <v>50</v>
       </c>
@@ -6277,7 +6437,7 @@
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A173" s="49"/>
+      <c r="A173" s="51"/>
       <c r="B173" t="s">
         <v>48</v>
       </c>
@@ -6287,7 +6447,7 @@
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A174" s="49"/>
+      <c r="A174" s="51"/>
       <c r="B174" t="s">
         <v>76</v>
       </c>
@@ -6297,7 +6457,7 @@
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A175" s="49"/>
+      <c r="A175" s="51"/>
       <c r="B175" t="s">
         <v>531</v>
       </c>
@@ -6309,7 +6469,7 @@
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A176" s="49"/>
+      <c r="A176" s="51"/>
       <c r="B176" t="s">
         <v>240</v>
       </c>
@@ -6319,7 +6479,7 @@
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A177" s="49"/>
+      <c r="A177" s="51"/>
       <c r="B177" t="s">
         <v>241</v>
       </c>
@@ -6329,7 +6489,7 @@
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A178" s="49"/>
+      <c r="A178" s="51"/>
       <c r="B178" t="s">
         <v>536</v>
       </c>
@@ -6339,7 +6499,7 @@
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A179" s="49"/>
+      <c r="A179" s="51"/>
       <c r="B179" t="s">
         <v>238</v>
       </c>
@@ -6348,7 +6508,7 @@
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A180" s="49"/>
+      <c r="A180" s="51"/>
       <c r="B180" t="s">
         <v>228</v>
       </c>
@@ -6361,7 +6521,7 @@
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A181" s="49"/>
+      <c r="A181" s="51"/>
       <c r="B181" t="s">
         <v>39</v>
       </c>
@@ -6371,7 +6531,7 @@
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A182" s="49"/>
+      <c r="A182" s="51"/>
       <c r="B182" t="s">
         <v>300</v>
       </c>
@@ -6381,7 +6541,7 @@
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A183" s="49"/>
+      <c r="A183" s="51"/>
       <c r="B183" t="s">
         <v>229</v>
       </c>
@@ -6391,7 +6551,7 @@
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A184" s="49"/>
+      <c r="A184" s="51"/>
       <c r="B184" t="s">
         <v>230</v>
       </c>
@@ -6401,7 +6561,7 @@
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A185" s="49"/>
+      <c r="A185" s="51"/>
       <c r="B185" t="s">
         <v>242</v>
       </c>
@@ -6411,7 +6571,7 @@
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A186" s="49"/>
+      <c r="A186" s="51"/>
       <c r="B186" t="s">
         <v>235</v>
       </c>
@@ -6421,7 +6581,7 @@
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A187" s="49"/>
+      <c r="A187" s="51"/>
       <c r="B187" t="s">
         <v>233</v>
       </c>
@@ -6430,7 +6590,7 @@
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A188" s="49"/>
+      <c r="A188" s="51"/>
       <c r="B188" t="s">
         <v>533</v>
       </c>
@@ -6440,7 +6600,7 @@
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A189" s="49"/>
+      <c r="A189" s="51"/>
       <c r="B189" t="s">
         <v>535</v>
       </c>
@@ -6450,7 +6610,7 @@
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A190" s="49"/>
+      <c r="A190" s="51"/>
       <c r="B190" t="s">
         <v>243</v>
       </c>
@@ -6463,7 +6623,7 @@
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A191" s="49"/>
+      <c r="A191" s="51"/>
       <c r="B191" t="s">
         <v>232</v>
       </c>
@@ -6475,7 +6635,7 @@
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A192" s="49"/>
+      <c r="A192" s="51"/>
       <c r="B192" t="s">
         <v>234</v>
       </c>
@@ -6485,7 +6645,7 @@
       </c>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A193" s="49"/>
+      <c r="A193" s="51"/>
       <c r="B193" t="s">
         <v>293</v>
       </c>
@@ -6497,7 +6657,7 @@
       </c>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A194" s="49"/>
+      <c r="A194" s="51"/>
       <c r="B194" t="s">
         <v>534</v>
       </c>
@@ -6506,7 +6666,7 @@
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A195" s="49"/>
+      <c r="A195" s="51"/>
       <c r="B195" t="s">
         <v>510</v>
       </c>
@@ -6515,7 +6675,7 @@
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A196" s="49"/>
+      <c r="A196" s="51"/>
       <c r="B196" t="s">
         <v>236</v>
       </c>
@@ -6525,7 +6685,7 @@
       </c>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A197" s="49"/>
+      <c r="A197" s="51"/>
       <c r="B197" t="s">
         <v>511</v>
       </c>
@@ -6535,7 +6695,7 @@
       </c>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A198" s="49"/>
+      <c r="A198" s="51"/>
       <c r="B198" t="s">
         <v>515</v>
       </c>
@@ -6569,7 +6729,7 @@
       </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A199" s="49"/>
+      <c r="A199" s="51"/>
       <c r="B199" t="s">
         <v>516</v>
       </c>
@@ -6609,7 +6769,7 @@
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A200" s="49"/>
+      <c r="A200" s="51"/>
       <c r="B200" t="s">
         <v>514</v>
       </c>
@@ -6646,7 +6806,7 @@
       </c>
     </row>
     <row r="201" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="49"/>
+      <c r="A201" s="51"/>
       <c r="B201" t="s">
         <v>512</v>
       </c>
@@ -6683,7 +6843,7 @@
       </c>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A202" s="49"/>
+      <c r="A202" s="51"/>
       <c r="B202" t="s">
         <v>513</v>
       </c>
@@ -6720,7 +6880,7 @@
       </c>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A203" s="49"/>
+      <c r="A203" s="51"/>
       <c r="B203" t="s">
         <v>296</v>
       </c>
@@ -6757,7 +6917,7 @@
       </c>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A204" s="49"/>
+      <c r="A204" s="51"/>
       <c r="B204" t="s">
         <v>297</v>
       </c>
@@ -6794,7 +6954,7 @@
       </c>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A205" s="49"/>
+      <c r="A205" s="51"/>
       <c r="B205" t="s">
         <v>298</v>
       </c>
@@ -6827,7 +6987,7 @@
       </c>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A206" s="49"/>
+      <c r="A206" s="51"/>
       <c r="B206" t="s">
         <v>299</v>
       </c>
@@ -6837,7 +6997,7 @@
       </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A207" s="49"/>
+      <c r="A207" s="51"/>
       <c r="B207" t="s">
         <v>300</v>
       </c>
@@ -6847,14 +7007,14 @@
       </c>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A208" s="49"/>
+      <c r="A208" s="51"/>
       <c r="B208" t="s">
         <v>301</v>
       </c>
       <c r="D208" s="1"/>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A209" s="49"/>
+      <c r="A209" s="51"/>
       <c r="B209" t="s">
         <v>302</v>
       </c>
@@ -6864,7 +7024,7 @@
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A210" s="49"/>
+      <c r="A210" s="51"/>
       <c r="B210" t="s">
         <v>248</v>
       </c>
@@ -6873,7 +7033,7 @@
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A211" s="49"/>
+      <c r="A211" s="51"/>
       <c r="C211" t="s">
         <v>249</v>
       </c>
@@ -6882,7 +7042,7 @@
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A212" s="49"/>
+      <c r="A212" s="51"/>
       <c r="C212" t="s">
         <v>250</v>
       </c>
@@ -6892,7 +7052,7 @@
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A213" s="49"/>
+      <c r="A213" s="51"/>
       <c r="C213" t="s">
         <v>251</v>
       </c>
@@ -6901,10 +7061,10 @@
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A214" s="49"/>
+      <c r="A214" s="51"/>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A215" s="49"/>
+      <c r="A215" s="51"/>
       <c r="B215" t="s">
         <v>253</v>
       </c>
@@ -6913,7 +7073,7 @@
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A216" s="49"/>
+      <c r="A216" s="51"/>
       <c r="B216" t="s">
         <v>277</v>
       </c>
@@ -6923,7 +7083,7 @@
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A217" s="49"/>
+      <c r="A217" s="51"/>
       <c r="B217" t="s">
         <v>254</v>
       </c>
@@ -6932,7 +7092,7 @@
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A218" s="49"/>
+      <c r="A218" s="51"/>
       <c r="B218" t="s">
         <v>255</v>
       </c>
@@ -6942,7 +7102,7 @@
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A219" s="49"/>
+      <c r="A219" s="51"/>
       <c r="B219" t="s">
         <v>256</v>
       </c>
@@ -6955,7 +7115,7 @@
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A220" s="49"/>
+      <c r="A220" s="51"/>
       <c r="B220" t="s">
         <v>257</v>
       </c>
@@ -6968,7 +7128,7 @@
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A221" s="49"/>
+      <c r="A221" s="51"/>
       <c r="B221" t="s">
         <v>258</v>
       </c>
@@ -6981,7 +7141,7 @@
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A222" s="49"/>
+      <c r="A222" s="51"/>
       <c r="B222" t="s">
         <v>259</v>
       </c>
@@ -6997,7 +7157,7 @@
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A223" s="49"/>
+      <c r="A223" s="51"/>
       <c r="B223" t="s">
         <v>260</v>
       </c>
@@ -7007,7 +7167,7 @@
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A224" s="49"/>
+      <c r="A224" s="51"/>
       <c r="C224" t="s">
         <v>261</v>
       </c>
@@ -7017,7 +7177,7 @@
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A225" s="49"/>
+      <c r="A225" s="51"/>
       <c r="C225" t="s">
         <v>262</v>
       </c>
@@ -7027,7 +7187,7 @@
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A226" s="49"/>
+      <c r="A226" s="51"/>
       <c r="C226" t="s">
         <v>263</v>
       </c>
@@ -7043,12 +7203,12 @@
       <c r="A227" s="29"/>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A228" s="49" t="s">
+      <c r="A228" s="51" t="s">
         <v>775</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A229" s="49"/>
+      <c r="A229" s="51"/>
       <c r="B229" t="s">
         <v>576</v>
       </c>
@@ -7057,10 +7217,10 @@
       </c>
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A230" s="49"/>
+      <c r="A230" s="51"/>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A231" s="49"/>
+      <c r="A231" s="51"/>
       <c r="B231" t="s">
         <v>532</v>
       </c>
@@ -7069,7 +7229,7 @@
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A232" s="49"/>
+      <c r="A232" s="51"/>
       <c r="B232" t="s">
         <v>547</v>
       </c>
@@ -7108,7 +7268,7 @@
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A233" s="49"/>
+      <c r="A233" s="51"/>
       <c r="B233" t="s">
         <v>561</v>
       </c>
@@ -7147,7 +7307,7 @@
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A234" s="49"/>
+      <c r="A234" s="51"/>
       <c r="B234" t="s">
         <v>548</v>
       </c>
@@ -7186,7 +7346,7 @@
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A235" s="49"/>
+      <c r="A235" s="51"/>
       <c r="B235" t="s">
         <v>327</v>
       </c>
@@ -7227,7 +7387,7 @@
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A236" s="49"/>
+      <c r="A236" s="51"/>
       <c r="B236" t="s">
         <v>549</v>
       </c>
@@ -7268,7 +7428,7 @@
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A237" s="49"/>
+      <c r="A237" s="51"/>
       <c r="B237" t="s">
         <v>551</v>
       </c>
@@ -7306,7 +7466,7 @@
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A238" s="49"/>
+      <c r="A238" s="51"/>
       <c r="B238" t="s">
         <v>553</v>
       </c>
@@ -7345,7 +7505,7 @@
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A239" s="49"/>
+      <c r="A239" s="51"/>
       <c r="B239" t="s">
         <v>48</v>
       </c>
@@ -7383,7 +7543,7 @@
       </c>
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A240" s="49"/>
+      <c r="A240" s="51"/>
       <c r="B240" t="s">
         <v>39</v>
       </c>
@@ -7421,11 +7581,11 @@
       </c>
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A241" s="49"/>
+      <c r="A241" s="51"/>
       <c r="C241" s="34"/>
     </row>
     <row r="242" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A242" s="49"/>
+      <c r="A242" s="51"/>
       <c r="B242" t="s">
         <v>558</v>
       </c>
@@ -7462,7 +7622,7 @@
       </c>
     </row>
     <row r="243" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A243" s="49"/>
+      <c r="A243" s="51"/>
       <c r="B243" t="s">
         <v>567</v>
       </c>
@@ -7475,7 +7635,7 @@
       </c>
     </row>
     <row r="244" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A244" s="49"/>
+      <c r="A244" s="51"/>
       <c r="B244" t="s">
         <v>546</v>
       </c>
@@ -7517,7 +7677,7 @@
       <c r="L244" s="1"/>
     </row>
     <row r="245" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A245" s="49"/>
+      <c r="A245" s="51"/>
       <c r="B245" t="s">
         <v>554</v>
       </c>
@@ -7558,7 +7718,7 @@
       </c>
     </row>
     <row r="246" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A246" s="49"/>
+      <c r="A246" s="51"/>
       <c r="B246" t="s">
         <v>556</v>
       </c>
@@ -7599,7 +7759,7 @@
       </c>
     </row>
     <row r="247" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A247" s="49"/>
+      <c r="A247" s="51"/>
       <c r="B247" t="s">
         <v>560</v>
       </c>
@@ -7639,7 +7799,7 @@
       </c>
     </row>
     <row r="248" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A248" s="49"/>
+      <c r="A248" s="51"/>
       <c r="B248" t="s">
         <v>563</v>
       </c>
@@ -7680,7 +7840,7 @@
       </c>
     </row>
     <row r="249" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A249" s="49"/>
+      <c r="A249" s="51"/>
       <c r="B249" t="s">
         <v>586</v>
       </c>
@@ -7689,7 +7849,7 @@
       </c>
     </row>
     <row r="250" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A250" s="49"/>
+      <c r="A250" s="51"/>
       <c r="B250" t="s">
         <v>300</v>
       </c>
@@ -7699,7 +7859,7 @@
       </c>
     </row>
     <row r="251" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A251" s="49"/>
+      <c r="A251" s="51"/>
       <c r="B251" t="s">
         <v>585</v>
       </c>
@@ -7712,7 +7872,7 @@
       </c>
     </row>
     <row r="252" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A252" s="49"/>
+      <c r="A252" s="51"/>
       <c r="B252" t="s">
         <v>592</v>
       </c>
@@ -7743,7 +7903,7 @@
       </c>
     </row>
     <row r="253" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A253" s="49"/>
+      <c r="A253" s="51"/>
       <c r="B253" s="36" t="s">
         <v>591</v>
       </c>
@@ -7780,7 +7940,7 @@
       </c>
     </row>
     <row r="254" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A254" s="49"/>
+      <c r="A254" s="51"/>
       <c r="B254" t="s">
         <v>594</v>
       </c>
@@ -7790,7 +7950,7 @@
       </c>
     </row>
     <row r="255" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A255" s="49"/>
+      <c r="A255" s="51"/>
       <c r="B255" t="s">
         <v>595</v>
       </c>
@@ -7800,7 +7960,7 @@
       </c>
     </row>
     <row r="256" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A256" s="49"/>
+      <c r="A256" s="51"/>
       <c r="B256" t="s">
         <v>593</v>
       </c>
@@ -7810,7 +7970,7 @@
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A257" s="49"/>
+      <c r="A257" s="51"/>
       <c r="B257" t="s">
         <v>596</v>
       </c>
@@ -7820,7 +7980,7 @@
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A258" s="49"/>
+      <c r="A258" s="51"/>
       <c r="B258" t="s">
         <v>597</v>
       </c>
@@ -7830,7 +7990,7 @@
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A259" s="49"/>
+      <c r="A259" s="51"/>
       <c r="B259" t="s">
         <v>600</v>
       </c>
@@ -7840,7 +8000,7 @@
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A260" s="49"/>
+      <c r="A260" s="51"/>
       <c r="B260" t="s">
         <v>598</v>
       </c>
@@ -7850,7 +8010,7 @@
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A261" s="49"/>
+      <c r="A261" s="51"/>
       <c r="B261" t="s">
         <v>598</v>
       </c>
@@ -7860,7 +8020,7 @@
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A262" s="49"/>
+      <c r="A262" s="51"/>
       <c r="B262" t="s">
         <v>602</v>
       </c>
@@ -7870,7 +8030,7 @@
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A263" s="49"/>
+      <c r="A263" s="51"/>
       <c r="B263" t="s">
         <v>601</v>
       </c>
@@ -7880,7 +8040,7 @@
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A264" s="49"/>
+      <c r="A264" s="51"/>
       <c r="B264" t="s">
         <v>599</v>
       </c>
@@ -7890,7 +8050,7 @@
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A265" s="49"/>
+      <c r="A265" s="51"/>
       <c r="B265" t="s">
         <v>623</v>
       </c>
@@ -7899,7 +8059,7 @@
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A266" s="49"/>
+      <c r="A266" s="51"/>
       <c r="B266" t="s">
         <v>624</v>
       </c>
@@ -7909,7 +8069,7 @@
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A267" s="49"/>
+      <c r="A267" s="51"/>
       <c r="B267" t="s">
         <v>621</v>
       </c>
@@ -7922,7 +8082,7 @@
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A268" s="49"/>
+      <c r="A268" s="51"/>
       <c r="B268" t="s">
         <v>622</v>
       </c>
@@ -7935,7 +8095,7 @@
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A269" s="49"/>
+      <c r="A269" s="51"/>
       <c r="B269" t="s">
         <v>603</v>
       </c>
@@ -7950,7 +8110,7 @@
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A270" s="49"/>
+      <c r="A270" s="51"/>
       <c r="B270" s="43" t="s">
         <v>605</v>
       </c>
@@ -7963,45 +8123,45 @@
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A271" s="49"/>
+      <c r="A271" s="51"/>
       <c r="C271" s="34"/>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A272" s="49"/>
+      <c r="A272" s="51"/>
       <c r="C272" s="34"/>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A273" s="49"/>
+      <c r="A273" s="51"/>
       <c r="C273" s="34"/>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A274" s="49"/>
+      <c r="A274" s="51"/>
       <c r="C274" s="34"/>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A275" s="49"/>
+      <c r="A275" s="51"/>
       <c r="C275" s="34"/>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A276" s="49"/>
+      <c r="A276" s="51"/>
       <c r="C276" s="34"/>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A277" s="49"/>
+      <c r="A277" s="51"/>
       <c r="C277" s="34"/>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A278" s="49"/>
+      <c r="A278" s="51"/>
       <c r="C278" s="34"/>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A279" s="49"/>
+      <c r="A279" s="51"/>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" s="37"/>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A281" s="49" t="s">
+      <c r="A281" s="51" t="s">
         <v>608</v>
       </c>
       <c r="C281" t="s">
@@ -8013,7 +8173,7 @@
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A282" s="49"/>
+      <c r="A282" s="51"/>
       <c r="C282" t="s">
         <v>265</v>
       </c>
@@ -8023,7 +8183,7 @@
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A283" s="49"/>
+      <c r="A283" s="51"/>
       <c r="C283" t="s">
         <v>266</v>
       </c>
@@ -8033,7 +8193,7 @@
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A284" s="49"/>
+      <c r="A284" s="51"/>
       <c r="C284" t="s">
         <v>267</v>
       </c>
@@ -8043,7 +8203,7 @@
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A285" s="49"/>
+      <c r="A285" s="51"/>
       <c r="C285" t="s">
         <v>268</v>
       </c>
@@ -8053,7 +8213,7 @@
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A286" s="49"/>
+      <c r="A286" s="51"/>
       <c r="C286" t="s">
         <v>269</v>
       </c>
@@ -8063,7 +8223,7 @@
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A287" s="49"/>
+      <c r="A287" s="51"/>
       <c r="C287" t="s">
         <v>270</v>
       </c>
@@ -8073,7 +8233,7 @@
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A288" s="49"/>
+      <c r="A288" s="51"/>
       <c r="C288" t="s">
         <v>271</v>
       </c>
@@ -8083,7 +8243,7 @@
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A289" s="49"/>
+      <c r="A289" s="51"/>
       <c r="B289" t="s">
         <v>272</v>
       </c>
@@ -8092,7 +8252,7 @@
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A290" s="49"/>
+      <c r="A290" s="51"/>
       <c r="B290" t="s">
         <v>274</v>
       </c>
@@ -8102,7 +8262,7 @@
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A291" s="49"/>
+      <c r="A291" s="51"/>
       <c r="C291" t="s">
         <v>275</v>
       </c>
@@ -8112,10 +8272,10 @@
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A292" s="49"/>
+      <c r="A292" s="51"/>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A293" s="49"/>
+      <c r="A293" s="51"/>
       <c r="B293" t="s">
         <v>276</v>
       </c>
@@ -8125,7 +8285,7 @@
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A294" s="49"/>
+      <c r="A294" s="51"/>
       <c r="B294" t="s">
         <v>348</v>
       </c>
@@ -8135,7 +8295,7 @@
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A295" s="49"/>
+      <c r="A295" s="51"/>
       <c r="B295" t="s">
         <v>284</v>
       </c>
@@ -8145,7 +8305,7 @@
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A296" s="49"/>
+      <c r="A296" s="51"/>
       <c r="B296" t="s">
         <v>283</v>
       </c>
@@ -8154,10 +8314,10 @@
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A297" s="49"/>
+      <c r="A297" s="51"/>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A298" s="49"/>
+      <c r="A298" s="51"/>
       <c r="B298" t="s">
         <v>281</v>
       </c>
@@ -8167,7 +8327,7 @@
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A299" s="49"/>
+      <c r="A299" s="51"/>
       <c r="B299" t="s">
         <v>280</v>
       </c>
@@ -8179,7 +8339,7 @@
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A300" s="49"/>
+      <c r="A300" s="51"/>
       <c r="C300" t="s">
         <v>278</v>
       </c>
@@ -8189,7 +8349,7 @@
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A301" s="49"/>
+      <c r="A301" s="51"/>
       <c r="C301" t="s">
         <v>282</v>
       </c>
@@ -8199,10 +8359,10 @@
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A302" s="49"/>
+      <c r="A302" s="51"/>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A303" s="50" t="s">
+      <c r="A303" s="52" t="s">
         <v>607</v>
       </c>
       <c r="B303" t="s">
@@ -8214,7 +8374,7 @@
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A304" s="50"/>
+      <c r="A304" s="52"/>
       <c r="B304" t="s">
         <v>609</v>
       </c>
@@ -8223,7 +8383,7 @@
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A305" s="50"/>
+      <c r="A305" s="52"/>
       <c r="B305" t="s">
         <v>610</v>
       </c>
@@ -8232,7 +8392,7 @@
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A306" s="50"/>
+      <c r="A306" s="52"/>
       <c r="B306" t="s">
         <v>611</v>
       </c>
@@ -8242,7 +8402,7 @@
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A307" s="50"/>
+      <c r="A307" s="52"/>
       <c r="B307" t="s">
         <v>615</v>
       </c>
@@ -8252,7 +8412,7 @@
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A308" s="50"/>
+      <c r="A308" s="52"/>
       <c r="B308" t="s">
         <v>613</v>
       </c>
@@ -8262,7 +8422,7 @@
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A309" s="50"/>
+      <c r="A309" s="52"/>
       <c r="B309" t="s">
         <v>614</v>
       </c>
@@ -8272,7 +8432,7 @@
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A310" s="50"/>
+      <c r="A310" s="52"/>
       <c r="B310" t="s">
         <v>616</v>
       </c>
@@ -8282,7 +8442,7 @@
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A311" s="50"/>
+      <c r="A311" s="52"/>
       <c r="C311" t="s">
         <v>617</v>
       </c>
@@ -8291,7 +8451,7 @@
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A312" s="50"/>
+      <c r="A312" s="52"/>
       <c r="C312" t="s">
         <v>618</v>
       </c>
@@ -8301,7 +8461,7 @@
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A313" s="50"/>
+      <c r="A313" s="52"/>
       <c r="C313" t="s">
         <v>619</v>
       </c>
@@ -8311,7 +8471,7 @@
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A314" s="50"/>
+      <c r="A314" s="52"/>
       <c r="C314" t="s">
         <v>620</v>
       </c>
@@ -8321,10 +8481,10 @@
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A315" s="50"/>
+      <c r="A315" s="52"/>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A316" s="50" t="s">
+      <c r="A316" s="52" t="s">
         <v>584</v>
       </c>
       <c r="C316" t="s">
@@ -8335,7 +8495,7 @@
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A317" s="50"/>
+      <c r="A317" s="52"/>
       <c r="B317" t="s">
         <v>38</v>
       </c>
@@ -8345,7 +8505,7 @@
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A318" s="50"/>
+      <c r="A318" s="52"/>
       <c r="B318" t="s">
         <v>286</v>
       </c>
@@ -8357,7 +8517,7 @@
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A319" s="50"/>
+      <c r="A319" s="52"/>
       <c r="C319" t="s">
         <v>289</v>
       </c>
@@ -8367,7 +8527,7 @@
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A320" s="50"/>
+      <c r="A320" s="52"/>
       <c r="B320" t="s">
         <v>290</v>
       </c>
@@ -8380,7 +8540,7 @@
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A321" s="50"/>
+      <c r="A321" s="52"/>
       <c r="C321" t="s">
         <v>288</v>
       </c>
@@ -8389,7 +8549,7 @@
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A322" s="50"/>
+      <c r="A322" s="52"/>
       <c r="B322" t="s">
         <v>287</v>
       </c>
@@ -8398,7 +8558,7 @@
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A323" s="50"/>
+      <c r="A323" s="52"/>
       <c r="B323" t="s">
         <v>291</v>
       </c>
@@ -8410,7 +8570,7 @@
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A324" s="50"/>
+      <c r="A324" s="52"/>
       <c r="B324" t="s">
         <v>292</v>
       </c>
@@ -8423,7 +8583,7 @@
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A325" s="50"/>
+      <c r="A325" s="52"/>
       <c r="B325" t="s">
         <v>349</v>
       </c>
@@ -8440,7 +8600,7 @@
       <c r="E326" s="9"/>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A327" s="49" t="s">
+      <c r="A327" s="51" t="s">
         <v>303</v>
       </c>
       <c r="B327" t="s">
@@ -8455,7 +8615,7 @@
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A328" s="49"/>
+      <c r="A328" s="51"/>
       <c r="B328" t="s">
         <v>41</v>
       </c>
@@ -8468,7 +8628,7 @@
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A329" s="49"/>
+      <c r="A329" s="51"/>
       <c r="B329" t="s">
         <v>39</v>
       </c>
@@ -8477,7 +8637,7 @@
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A330" s="49"/>
+      <c r="A330" s="51"/>
       <c r="B330" t="s">
         <v>305</v>
       </c>
@@ -8489,7 +8649,7 @@
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A331" s="49"/>
+      <c r="A331" s="51"/>
       <c r="B331" t="s">
         <v>304</v>
       </c>
@@ -8499,7 +8659,7 @@
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A332" s="49"/>
+      <c r="A332" s="51"/>
       <c r="B332" t="s">
         <v>307</v>
       </c>
@@ -8512,7 +8672,7 @@
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A333" s="49"/>
+      <c r="A333" s="51"/>
       <c r="B333" t="s">
         <v>308</v>
       </c>
@@ -8525,7 +8685,7 @@
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A334" s="49"/>
+      <c r="A334" s="51"/>
       <c r="B334" t="s">
         <v>326</v>
       </c>
@@ -8537,7 +8697,7 @@
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A335" s="49"/>
+      <c r="A335" s="51"/>
       <c r="C335" t="s">
         <v>344</v>
       </c>
@@ -8547,7 +8707,7 @@
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A336" s="49"/>
+      <c r="A336" s="51"/>
       <c r="B336" t="s">
         <v>309</v>
       </c>
@@ -8556,7 +8716,7 @@
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A337" s="49"/>
+      <c r="A337" s="51"/>
       <c r="B337" t="s">
         <v>310</v>
       </c>
@@ -8565,7 +8725,7 @@
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A338" s="49"/>
+      <c r="A338" s="51"/>
       <c r="B338" t="s">
         <v>311</v>
       </c>
@@ -8580,7 +8740,7 @@
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A339" s="49"/>
+      <c r="A339" s="51"/>
       <c r="B339" t="s">
         <v>313</v>
       </c>
@@ -8593,7 +8753,7 @@
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A340" s="49"/>
+      <c r="A340" s="51"/>
       <c r="B340" t="s">
         <v>315</v>
       </c>
@@ -8608,7 +8768,7 @@
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A341" s="49"/>
+      <c r="A341" s="51"/>
       <c r="B341" t="s">
         <v>316</v>
       </c>
@@ -8620,7 +8780,7 @@
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A342" s="49"/>
+      <c r="A342" s="51"/>
       <c r="B342" t="s">
         <v>229</v>
       </c>
@@ -8636,7 +8796,7 @@
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A343" s="49"/>
+      <c r="A343" s="51"/>
       <c r="B343" t="s">
         <v>322</v>
       </c>
@@ -8652,7 +8812,7 @@
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A344" s="49"/>
+      <c r="A344" s="51"/>
       <c r="B344" t="s">
         <v>323</v>
       </c>
@@ -8668,7 +8828,7 @@
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A345" s="49"/>
+      <c r="A345" s="51"/>
       <c r="C345" t="s">
         <v>317</v>
       </c>
@@ -8681,7 +8841,7 @@
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A346" s="49"/>
+      <c r="A346" s="51"/>
       <c r="C346" t="s">
         <v>319</v>
       </c>
@@ -8693,7 +8853,7 @@
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A347" s="49"/>
+      <c r="A347" s="51"/>
       <c r="C347" t="s">
         <v>320</v>
       </c>
@@ -8706,7 +8866,7 @@
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A348" s="49"/>
+      <c r="A348" s="51"/>
       <c r="C348" t="s">
         <v>318</v>
       </c>
@@ -8716,7 +8876,7 @@
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A349" s="49"/>
+      <c r="A349" s="51"/>
       <c r="B349" t="s">
         <v>346</v>
       </c>
@@ -8732,7 +8892,7 @@
       </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A350" s="49"/>
+      <c r="A350" s="51"/>
       <c r="B350" t="s">
         <v>327</v>
       </c>
@@ -8745,7 +8905,7 @@
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A351" s="49"/>
+      <c r="A351" s="51"/>
       <c r="B351" t="s">
         <v>328</v>
       </c>
@@ -8758,7 +8918,7 @@
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A352" s="49"/>
+      <c r="A352" s="51"/>
       <c r="B352" t="s">
         <v>321</v>
       </c>
@@ -8771,7 +8931,7 @@
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A353" s="49"/>
+      <c r="A353" s="51"/>
       <c r="B353" t="s">
         <v>341</v>
       </c>
@@ -8784,7 +8944,7 @@
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A354" s="49"/>
+      <c r="A354" s="51"/>
       <c r="B354" t="s">
         <v>330</v>
       </c>
@@ -8796,7 +8956,7 @@
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A355" s="49"/>
+      <c r="A355" s="51"/>
       <c r="B355" t="s">
         <v>333</v>
       </c>
@@ -8808,7 +8968,7 @@
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A356" s="49"/>
+      <c r="A356" s="51"/>
       <c r="B356" t="s">
         <v>334</v>
       </c>
@@ -8823,7 +8983,7 @@
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A357" s="49"/>
+      <c r="A357" s="51"/>
       <c r="B357" t="s">
         <v>331</v>
       </c>
@@ -8839,7 +8999,7 @@
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A358" s="49"/>
+      <c r="A358" s="51"/>
       <c r="C358" t="s">
         <v>345</v>
       </c>
@@ -8852,7 +9012,7 @@
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A359" s="49"/>
+      <c r="A359" s="51"/>
       <c r="B359" t="s">
         <v>336</v>
       </c>
@@ -8864,7 +9024,7 @@
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A360" s="49"/>
+      <c r="A360" s="51"/>
       <c r="C360" t="s">
         <v>338</v>
       </c>
@@ -8874,7 +9034,7 @@
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A361" s="49"/>
+      <c r="A361" s="51"/>
       <c r="C361" t="s">
         <v>337</v>
       </c>
@@ -8884,7 +9044,7 @@
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A362" s="49"/>
+      <c r="A362" s="51"/>
       <c r="B362" t="s">
         <v>339</v>
       </c>
@@ -8903,7 +9063,7 @@
       <c r="A363" s="38"/>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A364" s="50" t="s">
+      <c r="A364" s="52" t="s">
         <v>700</v>
       </c>
       <c r="B364" t="s">
@@ -8918,7 +9078,7 @@
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A365" s="50"/>
+      <c r="A365" s="52"/>
       <c r="C365" t="s">
         <v>701</v>
       </c>
@@ -8930,7 +9090,7 @@
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A366" s="50"/>
+      <c r="A366" s="52"/>
       <c r="C366" t="s">
         <v>703</v>
       </c>
@@ -8942,7 +9102,7 @@
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A367" s="50"/>
+      <c r="A367" s="52"/>
       <c r="C367" t="s">
         <v>704</v>
       </c>
@@ -8954,7 +9114,7 @@
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A368" s="50"/>
+      <c r="A368" s="52"/>
       <c r="B368" t="s">
         <v>706</v>
       </c>
@@ -8968,7 +9128,7 @@
       <c r="E368" s="40"/>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A369" s="50"/>
+      <c r="A369" s="52"/>
       <c r="B369" t="s">
         <v>708</v>
       </c>
@@ -8982,7 +9142,7 @@
       <c r="E369" s="40"/>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A370" s="50"/>
+      <c r="A370" s="52"/>
       <c r="B370" t="s">
         <v>710</v>
       </c>
@@ -8995,7 +9155,7 @@
       <c r="E370" s="39"/>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A371" s="50"/>
+      <c r="A371" s="52"/>
       <c r="C371" t="s">
         <v>705</v>
       </c>
@@ -9006,7 +9166,7 @@
       <c r="E371" s="39"/>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A372" s="50"/>
+      <c r="A372" s="52"/>
       <c r="B372" t="s">
         <v>713</v>
       </c>
@@ -9020,7 +9180,7 @@
       <c r="E372" s="39"/>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A373" s="50"/>
+      <c r="A373" s="52"/>
       <c r="C373" t="s">
         <v>714</v>
       </c>
@@ -9030,7 +9190,7 @@
       <c r="E373" s="39"/>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A374" s="50"/>
+      <c r="A374" s="52"/>
       <c r="C374" t="s">
         <v>715</v>
       </c>
@@ -9041,7 +9201,7 @@
       <c r="E374" s="39"/>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A375" s="50"/>
+      <c r="A375" s="52"/>
       <c r="C375" t="s">
         <v>716</v>
       </c>
@@ -9051,7 +9211,7 @@
       <c r="E375" s="39"/>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A376" s="50"/>
+      <c r="A376" s="52"/>
       <c r="C376" t="s">
         <v>717</v>
       </c>
@@ -9061,21 +9221,21 @@
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A377" s="50" t="s">
+      <c r="A377" s="52" t="s">
         <v>718</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A378" s="50"/>
+      <c r="A378" s="52"/>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A379" s="50"/>
+      <c r="A379" s="52"/>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A380" s="50"/>
+      <c r="A380" s="52"/>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A381" s="49" t="s">
+      <c r="A381" s="51" t="s">
         <v>350</v>
       </c>
       <c r="B381" t="s">
@@ -9090,7 +9250,7 @@
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A382" s="49"/>
+      <c r="A382" s="51"/>
       <c r="B382" t="s">
         <v>48</v>
       </c>
@@ -9100,7 +9260,7 @@
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A383" s="49"/>
+      <c r="A383" s="51"/>
       <c r="B383" t="s">
         <v>240</v>
       </c>
@@ -9110,7 +9270,7 @@
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A384" s="49"/>
+      <c r="A384" s="51"/>
       <c r="C384" t="s">
         <v>354</v>
       </c>
@@ -9119,7 +9279,7 @@
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A385" s="49"/>
+      <c r="A385" s="51"/>
       <c r="C385" t="s">
         <v>356</v>
       </c>
@@ -9129,7 +9289,7 @@
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A386" s="49"/>
+      <c r="A386" s="51"/>
       <c r="B386" t="s">
         <v>351</v>
       </c>
@@ -9141,7 +9301,7 @@
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A387" s="49"/>
+      <c r="A387" s="51"/>
       <c r="B387" t="s">
         <v>353</v>
       </c>
@@ -9154,7 +9314,7 @@
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A388" s="49"/>
+      <c r="A388" s="51"/>
       <c r="B388" t="s">
         <v>403</v>
       </c>
@@ -9167,7 +9327,7 @@
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A389" s="49"/>
+      <c r="A389" s="51"/>
       <c r="B389" t="s">
         <v>358</v>
       </c>
@@ -9180,7 +9340,7 @@
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A390" s="49"/>
+      <c r="A390" s="51"/>
       <c r="B390" t="s">
         <v>359</v>
       </c>
@@ -9193,7 +9353,7 @@
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A391" s="49"/>
+      <c r="A391" s="51"/>
       <c r="B391" t="s">
         <v>360</v>
       </c>
@@ -9206,7 +9366,7 @@
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A392" s="49"/>
+      <c r="A392" s="51"/>
       <c r="C392" t="s">
         <v>362</v>
       </c>
@@ -9216,7 +9376,7 @@
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A393" s="49"/>
+      <c r="A393" s="51"/>
       <c r="B393" t="s">
         <v>393</v>
       </c>
@@ -9228,7 +9388,7 @@
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A394" s="49"/>
+      <c r="A394" s="51"/>
       <c r="B394" t="s">
         <v>367</v>
       </c>
@@ -9240,7 +9400,7 @@
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A395" s="49"/>
+      <c r="A395" s="51"/>
       <c r="B395" t="s">
         <v>368</v>
       </c>
@@ -9252,7 +9412,7 @@
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A396" s="49"/>
+      <c r="A396" s="51"/>
       <c r="B396" t="s">
         <v>371</v>
       </c>
@@ -9267,7 +9427,7 @@
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A397" s="49"/>
+      <c r="A397" s="51"/>
       <c r="B397" t="s">
         <v>372</v>
       </c>
@@ -9282,7 +9442,7 @@
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A398" s="49"/>
+      <c r="A398" s="51"/>
       <c r="B398" t="s">
         <v>374</v>
       </c>
@@ -9298,7 +9458,7 @@
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A399" s="49"/>
+      <c r="A399" s="51"/>
       <c r="B399" s="27" t="s">
         <v>378</v>
       </c>
@@ -9313,7 +9473,7 @@
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A400" s="49"/>
+      <c r="A400" s="51"/>
       <c r="C400" t="s">
         <v>381</v>
       </c>
@@ -9323,7 +9483,7 @@
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A401" s="49"/>
+      <c r="A401" s="51"/>
       <c r="B401" t="s">
         <v>396</v>
       </c>
@@ -9336,7 +9496,7 @@
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A402" s="49"/>
+      <c r="A402" s="51"/>
       <c r="B402" t="s">
         <v>397</v>
       </c>
@@ -9346,7 +9506,7 @@
       </c>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A403" s="49"/>
+      <c r="A403" s="51"/>
       <c r="B403" t="s">
         <v>363</v>
       </c>
@@ -9355,7 +9515,7 @@
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A404" s="49"/>
+      <c r="A404" s="51"/>
       <c r="B404" t="s">
         <v>365</v>
       </c>
@@ -9365,7 +9525,7 @@
       </c>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A405" s="49"/>
+      <c r="A405" s="51"/>
       <c r="B405" t="s">
         <v>364</v>
       </c>
@@ -9377,7 +9537,7 @@
       </c>
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A406" s="49"/>
+      <c r="A406" s="51"/>
       <c r="B406" t="s">
         <v>398</v>
       </c>
@@ -9390,7 +9550,7 @@
       </c>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A407" s="49"/>
+      <c r="A407" s="51"/>
       <c r="C407" t="s">
         <v>414</v>
       </c>
@@ -9399,7 +9559,7 @@
       </c>
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A408" s="49"/>
+      <c r="A408" s="51"/>
       <c r="B408" t="s">
         <v>415</v>
       </c>
@@ -9409,7 +9569,7 @@
       </c>
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A409" s="49"/>
+      <c r="A409" s="51"/>
       <c r="B409" t="s">
         <v>416</v>
       </c>
@@ -9419,7 +9579,7 @@
       </c>
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A410" s="49"/>
+      <c r="A410" s="51"/>
       <c r="B410" t="s">
         <v>417</v>
       </c>
@@ -9429,7 +9589,7 @@
       </c>
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A411" s="49"/>
+      <c r="A411" s="51"/>
       <c r="B411" t="s">
         <v>418</v>
       </c>
@@ -9439,7 +9599,7 @@
       </c>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A412" s="49"/>
+      <c r="A412" s="51"/>
       <c r="B412" t="s">
         <v>412</v>
       </c>
@@ -9452,7 +9612,7 @@
       </c>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A413" s="49"/>
+      <c r="A413" s="51"/>
       <c r="B413" t="s">
         <v>419</v>
       </c>
@@ -9465,7 +9625,7 @@
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A414" s="49"/>
+      <c r="A414" s="51"/>
       <c r="C414" t="s">
         <v>420</v>
       </c>
@@ -9475,7 +9635,7 @@
       </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A415" s="49"/>
+      <c r="A415" s="51"/>
       <c r="C415" t="s">
         <v>421</v>
       </c>
@@ -9488,7 +9648,7 @@
       </c>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A416" s="49"/>
+      <c r="A416" s="51"/>
       <c r="B416" t="s">
         <v>399</v>
       </c>
@@ -9498,7 +9658,7 @@
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A417" s="49"/>
+      <c r="A417" s="51"/>
       <c r="C417" t="s">
         <v>388</v>
       </c>
@@ -9508,7 +9668,7 @@
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A418" s="49"/>
+      <c r="A418" s="51"/>
       <c r="C418" t="s">
         <v>400</v>
       </c>
@@ -9518,7 +9678,7 @@
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A419" s="49"/>
+      <c r="A419" s="51"/>
       <c r="B419" t="s">
         <v>386</v>
       </c>
@@ -9531,7 +9691,7 @@
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A420" s="49"/>
+      <c r="A420" s="51"/>
       <c r="C420" t="s">
         <v>401</v>
       </c>
@@ -9541,7 +9701,7 @@
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A421" s="49"/>
+      <c r="A421" s="51"/>
       <c r="C421" t="s">
         <v>402</v>
       </c>
@@ -9551,7 +9711,7 @@
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A422" s="49"/>
+      <c r="A422" s="51"/>
       <c r="B422" t="s">
         <v>387</v>
       </c>
@@ -9561,7 +9721,7 @@
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A423" s="49"/>
+      <c r="A423" s="51"/>
       <c r="C423" t="s">
         <v>392</v>
       </c>
@@ -9571,7 +9731,7 @@
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A424" s="49"/>
+      <c r="A424" s="51"/>
       <c r="C424" t="s">
         <v>389</v>
       </c>
@@ -9581,10 +9741,10 @@
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A425" s="49"/>
+      <c r="A425" s="51"/>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A426" s="49"/>
+      <c r="A426" s="51"/>
       <c r="C426" t="s">
         <v>390</v>
       </c>
@@ -9597,7 +9757,7 @@
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A427" s="49"/>
+      <c r="A427" s="51"/>
       <c r="C427" t="s">
         <v>390</v>
       </c>
@@ -9610,7 +9770,7 @@
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A428" s="49"/>
+      <c r="A428" s="51"/>
       <c r="C428" t="s">
         <v>391</v>
       </c>
@@ -9620,7 +9780,7 @@
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A429" s="49"/>
+      <c r="A429" s="51"/>
       <c r="B429" t="s">
         <v>405</v>
       </c>
@@ -9630,7 +9790,7 @@
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A430" s="49"/>
+      <c r="A430" s="51"/>
       <c r="B430" t="s">
         <v>406</v>
       </c>
@@ -9640,13 +9800,13 @@
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A431" s="49"/>
+      <c r="A431" s="51"/>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A432" s="49"/>
+      <c r="A432" s="51"/>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A433" s="49"/>
+      <c r="A433" s="51"/>
       <c r="B433" t="s">
         <v>408</v>
       </c>
@@ -9662,7 +9822,7 @@
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A434" s="49"/>
+      <c r="A434" s="51"/>
       <c r="B434" t="s">
         <v>409</v>
       </c>
@@ -9675,7 +9835,7 @@
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A435" s="49"/>
+      <c r="A435" s="51"/>
       <c r="B435" t="s">
         <v>411</v>
       </c>
@@ -9685,7 +9845,7 @@
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A436" s="49"/>
+      <c r="A436" s="51"/>
       <c r="B436" t="s">
         <v>422</v>
       </c>
@@ -9698,7 +9858,7 @@
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A437" s="49"/>
+      <c r="A437" s="51"/>
       <c r="B437" t="s">
         <v>424</v>
       </c>
@@ -9708,7 +9868,7 @@
       </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A438" s="49"/>
+      <c r="A438" s="51"/>
       <c r="B438" t="s">
         <v>425</v>
       </c>
@@ -9718,7 +9878,7 @@
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A439" s="49"/>
+      <c r="A439" s="51"/>
       <c r="B439" t="s">
         <v>426</v>
       </c>
@@ -9728,7 +9888,7 @@
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A440" s="49"/>
+      <c r="A440" s="51"/>
       <c r="B440" t="s">
         <v>427</v>
       </c>
@@ -9738,7 +9898,7 @@
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A441" s="49"/>
+      <c r="A441" s="51"/>
       <c r="C441" t="s">
         <v>428</v>
       </c>
@@ -9748,7 +9908,7 @@
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A442" s="49"/>
+      <c r="A442" s="51"/>
       <c r="B442" t="s">
         <v>429</v>
       </c>
@@ -9758,7 +9918,7 @@
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A443" s="49"/>
+      <c r="A443" s="51"/>
       <c r="B443" t="s">
         <v>430</v>
       </c>
@@ -9768,7 +9928,7 @@
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A444" s="49"/>
+      <c r="A444" s="51"/>
       <c r="B444" t="s">
         <v>431</v>
       </c>
@@ -9778,7 +9938,7 @@
       </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A445" s="49"/>
+      <c r="A445" s="51"/>
       <c r="B445" t="s">
         <v>429</v>
       </c>
@@ -9791,7 +9951,7 @@
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A446" s="49"/>
+      <c r="A446" s="51"/>
       <c r="B446" t="s">
         <v>430</v>
       </c>
@@ -9804,7 +9964,7 @@
       </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A447" s="49"/>
+      <c r="A447" s="51"/>
       <c r="B447" t="s">
         <v>431</v>
       </c>
@@ -9816,2507 +9976,2912 @@
         <v>168</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A449" s="49" t="s">
-        <v>451</v>
-      </c>
+    <row r="448" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A448" s="49"/>
+    </row>
+    <row r="449" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A449" s="49"/>
       <c r="B449" t="s">
-        <v>48</v>
+        <v>855</v>
       </c>
       <c r="C449" t="s">
-        <v>47</v>
+        <v>828</v>
       </c>
       <c r="D449">
+        <f>D105</f>
+        <v>22.598870056497173</v>
+      </c>
+      <c r="E449" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A450" s="50"/>
+      <c r="B450" t="s">
+        <v>854</v>
+      </c>
+      <c r="D450">
+        <f>D449/SQRT(3)</f>
+        <v>13.047463710500017</v>
+      </c>
+      <c r="E450" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A451" s="49"/>
+      <c r="B451" s="59" t="s">
+        <v>830</v>
+      </c>
+      <c r="C451" t="s">
+        <v>829</v>
+      </c>
+      <c r="D451">
+        <f xml:space="preserve"> 40</f>
+        <v>40</v>
+      </c>
+      <c r="E451" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A452" s="50"/>
+      <c r="B452" s="59" t="s">
+        <v>832</v>
+      </c>
+      <c r="C452" t="s">
+        <v>831</v>
+      </c>
+      <c r="D452" s="8">
+        <f>D451/SQRT(3)</f>
+        <v>23.094010767585033</v>
+      </c>
+      <c r="E452" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A453" s="49"/>
+      <c r="B453" s="59" t="s">
+        <v>817</v>
+      </c>
+      <c r="C453" t="s">
+        <v>818</v>
+      </c>
+      <c r="D453" s="8">
         <f>D3</f>
         <v>16000</v>
       </c>
-    </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A450" s="49"/>
-      <c r="B450" t="s">
+      <c r="E453" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A454" s="49"/>
+      <c r="B454" s="59" t="s">
+        <v>819</v>
+      </c>
+      <c r="C454" t="s">
+        <v>820</v>
+      </c>
+      <c r="D454" s="8">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A455" s="50"/>
+      <c r="B455" s="59" t="s">
+        <v>844</v>
+      </c>
+      <c r="D455" s="8">
+        <f>D449/D454</f>
+        <v>0.15065913370998116</v>
+      </c>
+      <c r="E455" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A456" s="49"/>
+      <c r="B456" t="s">
+        <v>833</v>
+      </c>
+      <c r="D456" s="8">
+        <f>D451/D454</f>
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="E456" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A457" s="50"/>
+      <c r="B457" t="s">
+        <v>853</v>
+      </c>
+      <c r="D457" s="8">
+        <f>D450/D454</f>
+        <v>8.6983091403333448E-2</v>
+      </c>
+      <c r="E457" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A458" s="49"/>
+      <c r="B458" t="s">
+        <v>834</v>
+      </c>
+      <c r="D458" s="8">
+        <f>D452/D454</f>
+        <v>0.15396007178390023</v>
+      </c>
+      <c r="E458" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A459" s="49"/>
+      <c r="B459" t="s">
+        <v>821</v>
+      </c>
+      <c r="C459" t="s">
+        <v>835</v>
+      </c>
+      <c r="D459" s="8">
+        <v>2.7</v>
+      </c>
+      <c r="E459" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A460" s="49"/>
+      <c r="B460" t="s">
+        <v>822</v>
+      </c>
+      <c r="C460" t="s">
+        <v>823</v>
+      </c>
+      <c r="D460">
+        <v>0.6</v>
+      </c>
+      <c r="E460" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A461" s="49"/>
+      <c r="B461" t="s">
+        <v>825</v>
+      </c>
+      <c r="C461" t="s">
+        <v>824</v>
+      </c>
+      <c r="D461">
+        <f>(D459)/D456</f>
+        <v>10.125</v>
+      </c>
+      <c r="E461" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A462" s="49"/>
+      <c r="B462" t="s">
+        <v>826</v>
+      </c>
+      <c r="C462" t="s">
+        <v>827</v>
+      </c>
+      <c r="D462">
+        <v>10</v>
+      </c>
+      <c r="E462" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A463" s="50"/>
+      <c r="B463" t="s">
+        <v>839</v>
+      </c>
+      <c r="C463" t="s">
+        <v>838</v>
+      </c>
+      <c r="D463">
+        <f xml:space="preserve"> D456*D462</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="E463" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A464" s="50"/>
+    </row>
+    <row r="465" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A465" s="50"/>
+      <c r="B465" t="s">
+        <v>841</v>
+      </c>
+      <c r="C465" t="s">
+        <v>836</v>
+      </c>
+      <c r="D465">
+        <f xml:space="preserve"> POWER(D456, 2)*D462</f>
+        <v>0.71111111111111114</v>
+      </c>
+      <c r="E465" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A466" s="50"/>
+      <c r="B466" t="s">
+        <v>849</v>
+      </c>
+      <c r="C466" t="s">
+        <v>852</v>
+      </c>
+      <c r="D466">
+        <f>POWER(D458, 2)*D462</f>
+        <v>0.2370370370370371</v>
+      </c>
+      <c r="E466" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A467" s="50"/>
+      <c r="B467" t="s">
+        <v>843</v>
+      </c>
+      <c r="C467" t="s">
+        <v>842</v>
+      </c>
+      <c r="D467">
+        <f>POWER(D455, 2)*D462</f>
+        <v>0.2269817457024198</v>
+      </c>
+      <c r="E467" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A468" s="50"/>
+      <c r="B468" t="s">
+        <v>850</v>
+      </c>
+      <c r="C468" t="s">
+        <v>851</v>
+      </c>
+      <c r="D468">
+        <f>POWER(D457, 2)*D462</f>
+        <v>7.5660581900806614E-2</v>
+      </c>
+      <c r="E468" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A469" s="50"/>
+      <c r="B469" t="s">
+        <v>840</v>
+      </c>
+      <c r="C469" t="s">
+        <v>837</v>
+      </c>
+      <c r="D469">
+        <f>D460*D456</f>
+        <v>0.16</v>
+      </c>
+      <c r="E469" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A470" s="50"/>
+      <c r="B470" t="s">
+        <v>845</v>
+      </c>
+      <c r="C470" t="s">
+        <v>846</v>
+      </c>
+      <c r="D470">
+        <f>D460*D455</f>
+        <v>9.0395480225988686E-2</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A471" s="50"/>
+    </row>
+    <row r="472" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A472" s="50"/>
+      <c r="B472" t="s">
+        <v>856</v>
+      </c>
+      <c r="C472" t="s">
+        <v>857</v>
+      </c>
+      <c r="D472">
+        <f>D462+(2*(D460/D456))</f>
+        <v>14.5</v>
+      </c>
+      <c r="E472" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="473" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A473" s="50"/>
+      <c r="B473" t="s">
+        <v>847</v>
+      </c>
+      <c r="C473" t="s">
+        <v>848</v>
+      </c>
+      <c r="D473">
+        <f>D455*D462</f>
+        <v>1.5065913370998116</v>
+      </c>
+      <c r="E473" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A474" s="50"/>
+      <c r="B474" t="s">
+        <v>858</v>
+      </c>
+      <c r="C474" t="s">
+        <v>859</v>
+      </c>
+      <c r="D474">
+        <f>D456</f>
+        <v>0.26666666666666666</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A475" s="50"/>
+      <c r="B475" t="s">
+        <v>860</v>
+      </c>
+      <c r="C475" t="s">
+        <v>861</v>
+      </c>
+      <c r="D475" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A476" s="50"/>
+      <c r="B476" t="s">
+        <v>862</v>
+      </c>
+      <c r="C476" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="477" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A477" s="50"/>
+      <c r="B477" t="s">
+        <v>864</v>
+      </c>
+      <c r="C477" t="s">
+        <v>865</v>
+      </c>
+      <c r="D477">
+        <v>100</v>
+      </c>
+      <c r="E477" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="478" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B478" t="s">
+        <v>48</v>
+      </c>
+      <c r="C478" t="s">
+        <v>47</v>
+      </c>
+      <c r="D478">
+        <f>D3</f>
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A479" s="51" t="s">
+        <v>451</v>
+      </c>
+      <c r="B479" t="s">
         <v>41</v>
       </c>
-      <c r="C450" t="s">
+      <c r="C479" t="s">
         <v>434</v>
       </c>
-      <c r="D450">
+      <c r="D479">
         <f>D105</f>
         <v>22.598870056497173</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A451" s="49"/>
-      <c r="B451" t="s">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A480" s="51"/>
+      <c r="B480" t="s">
         <v>39</v>
       </c>
-      <c r="C451" t="s">
+      <c r="C480" t="s">
         <v>435</v>
       </c>
-      <c r="D451">
+      <c r="D480">
         <f>D103</f>
         <v>0.5</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A452" s="49"/>
-      <c r="B452" t="s">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A481" s="51"/>
+      <c r="B481" t="s">
         <v>432</v>
       </c>
-      <c r="C452" t="s">
+      <c r="C481" t="s">
         <v>433</v>
       </c>
-      <c r="D452">
-        <f>0.5*D450/D449</f>
+      <c r="D481">
+        <f>0.5*D479/D478</f>
         <v>7.0621468926553661E-4</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A453" s="49"/>
-      <c r="B453" t="s">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A482" s="51"/>
+      <c r="B482" t="s">
         <v>436</v>
       </c>
-      <c r="D453">
+      <c r="D482">
         <v>0.5</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A454" s="49"/>
-      <c r="B454" t="s">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A483" s="51"/>
+      <c r="B483" t="s">
         <v>442</v>
       </c>
-      <c r="D454">
-        <f>D452/D453</f>
+      <c r="D483">
+        <f>D481/D482</f>
         <v>1.4124293785310732E-3</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A455" s="49"/>
-      <c r="C455" t="s">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A484" s="51"/>
+      <c r="C484" t="s">
         <v>437</v>
       </c>
-      <c r="D455">
+      <c r="D484">
         <v>10</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A456" s="49"/>
-      <c r="B456" t="s">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A485" s="51"/>
+      <c r="B485" t="s">
         <v>441</v>
       </c>
-      <c r="D456">
-        <f>D455*D454</f>
+      <c r="D485">
+        <f>D484*D483</f>
         <v>1.4124293785310733E-2</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A457" s="49"/>
-      <c r="B457" t="s">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A486" s="51"/>
+      <c r="B486" t="s">
         <v>466</v>
       </c>
-      <c r="C457" t="s">
+      <c r="C486" t="s">
         <v>467</v>
       </c>
-      <c r="D457">
-        <f>3*D479</f>
+      <c r="D486">
+        <f>3*D508</f>
         <v>132.30000000000001</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A458" s="49"/>
-      <c r="B458" t="s">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A487" s="51"/>
+      <c r="B487" t="s">
         <v>468</v>
       </c>
-      <c r="D458" s="1">
+      <c r="D487" s="1">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A459" s="49"/>
-      <c r="B459" t="s">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A488" s="51"/>
+      <c r="B488" t="s">
         <v>469</v>
       </c>
-      <c r="D459">
+      <c r="D488">
         <v>20</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A460" s="49"/>
-      <c r="B460" t="s">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A489" s="51"/>
+      <c r="B489" t="s">
         <v>472</v>
       </c>
-      <c r="C460" t="s">
+      <c r="C489" t="s">
         <v>473</v>
       </c>
-      <c r="D460" s="30">
+      <c r="D489" s="30">
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A461" s="49"/>
-      <c r="B461" t="s">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A490" s="51"/>
+      <c r="B490" t="s">
         <v>474</v>
       </c>
-      <c r="D461">
-        <f>D460/D459</f>
+      <c r="D490">
+        <f>D489/D488</f>
         <v>8.5000000000000006E-4</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A462" s="49"/>
-      <c r="B462" t="s">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A491" s="51"/>
+      <c r="B491" t="s">
         <v>447</v>
       </c>
-      <c r="C462" t="s">
+      <c r="C491" t="s">
         <v>448</v>
       </c>
-      <c r="D462" s="1">
-        <f>D458*D459</f>
+      <c r="D491" s="1">
+        <f>D487*D488</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A463" s="49"/>
-      <c r="C463" t="s">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A492" s="51"/>
+      <c r="C492" t="s">
         <v>470</v>
       </c>
-      <c r="D463" s="1">
+      <c r="D492" s="1">
         <f>0.2</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A464" s="49"/>
-      <c r="B464" t="s">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A493" s="51"/>
+      <c r="B493" t="s">
         <v>471</v>
       </c>
-      <c r="D464" s="1">
-        <f>D462*(1-D463)</f>
+      <c r="D493" s="1">
+        <f>D491*(1-D492)</f>
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A465" s="49"/>
-      <c r="B465" t="s">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A494" s="51"/>
+      <c r="B494" t="s">
         <v>507</v>
       </c>
-      <c r="D465" s="1">
-        <f>D461*D450</f>
+      <c r="D494" s="1">
+        <f>D490*D479</f>
         <v>1.9209039548022597E-2</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A466" s="49"/>
-      <c r="B466" t="s">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A495" s="51"/>
+      <c r="B495" t="s">
         <v>508</v>
       </c>
-      <c r="D466" s="1">
-        <f>D452/D462</f>
+      <c r="D495" s="1">
+        <f>D481/D491</f>
         <v>3.531073446327683E-2</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A467" s="49"/>
-      <c r="B467" t="s">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A496" s="51"/>
+      <c r="B496" t="s">
         <v>509</v>
       </c>
-      <c r="D467" s="1">
-        <f>D465+D466</f>
+      <c r="D496" s="1">
+        <f>D494+D495</f>
         <v>5.4519774011299427E-2</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A468" s="49"/>
-      <c r="B468" t="s">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A497" s="51"/>
+      <c r="B497" t="s">
         <v>475</v>
       </c>
-      <c r="D468" s="1">
-        <f>POWER(D465, 2)/D461</f>
+      <c r="D497" s="1">
+        <f>POWER(D494, 2)/D490</f>
         <v>0.43410258865587781</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A469" s="49"/>
-      <c r="B469" t="s">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A498" s="51"/>
+      <c r="B498" t="s">
         <v>476</v>
       </c>
-      <c r="D469" s="1">
-        <f>D468/D459</f>
+      <c r="D498" s="1">
+        <f>D497/D488</f>
         <v>2.1705129432793891E-2</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A470" s="49"/>
-      <c r="B470" t="s">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A499" s="51"/>
+      <c r="B499" t="s">
         <v>445</v>
       </c>
-      <c r="C470" t="s">
+      <c r="C499" t="s">
         <v>439</v>
       </c>
-      <c r="D470">
+      <c r="D499">
         <v>500</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A471" s="49"/>
-      <c r="B471" t="s">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A500" s="51"/>
+      <c r="B500" t="s">
         <v>443</v>
       </c>
-      <c r="C471" t="s">
+      <c r="C500" t="s">
         <v>444</v>
       </c>
-      <c r="D471">
-        <f>1/(POWER(2*PI()*D470, 2)*D456)</f>
+      <c r="D500">
+        <f>1/(POWER(2*PI()*D499, 2)*D485)</f>
         <v>7.1735398018775158E-6</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A472" s="49"/>
-      <c r="B472" t="s">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A501" s="51"/>
+      <c r="B501" t="s">
         <v>440</v>
       </c>
-      <c r="C472" t="s">
+      <c r="C501" t="s">
         <v>477</v>
       </c>
-      <c r="D472" s="1">
+      <c r="D501" s="1">
         <v>2.1999999999999999E-5</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A473" s="49"/>
-      <c r="B473" t="s">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A502" s="51"/>
+      <c r="B502" t="s">
         <v>478</v>
       </c>
-      <c r="D473" s="1">
+      <c r="D502" s="1">
         <f>D2*2/D5</f>
         <v>11.299435028248586</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A474" s="49"/>
-      <c r="B474" t="s">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A503" s="51"/>
+      <c r="B503" t="s">
         <v>479</v>
       </c>
-      <c r="D474" s="1">
-        <f>2*D473</f>
+      <c r="D503" s="1">
+        <f>2*D502</f>
         <v>22.598870056497173</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A475" s="49"/>
-      <c r="B475" t="s">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A504" s="51"/>
+      <c r="B504" t="s">
         <v>438</v>
       </c>
-      <c r="C475" t="s">
+      <c r="C504" t="s">
         <v>446</v>
       </c>
-      <c r="D475" s="1">
-        <f>1/(2*PI()*POWER(D462*D472, 0.5))</f>
+      <c r="D504" s="1">
+        <f>1/(2*PI()*POWER(D491*D501, 0.5))</f>
         <v>239.93510443917407</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A476" s="49"/>
-      <c r="B476" t="s">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A505" s="51"/>
+      <c r="B505" t="s">
         <v>449</v>
       </c>
-      <c r="D476" s="1">
-        <f>40*LOG10(D449/D475)</f>
+      <c r="D505" s="1">
+        <f>40*LOG10(D478/D504)</f>
         <v>72.961047570285331</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A477" s="49"/>
-      <c r="C477" t="s">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A506" s="51"/>
+      <c r="C506" t="s">
         <v>450</v>
       </c>
-      <c r="D477">
-        <f>POWER(D7, 2)*0.5*D462</f>
+      <c r="D506">
+        <f>POWER(D7, 2)*0.5*D491</f>
         <v>19.448100000000004</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A478" s="49"/>
-      <c r="B478" t="s">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A507" s="51"/>
+      <c r="B507" t="s">
         <v>452</v>
       </c>
-      <c r="C478" t="s">
+      <c r="C507" t="s">
         <v>453</v>
       </c>
-      <c r="D478">
+      <c r="D507">
         <v>33</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A479" s="49"/>
-      <c r="B479" t="s">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A508" s="51"/>
+      <c r="B508" t="s">
         <v>38</v>
       </c>
-      <c r="D479">
+      <c r="D508">
         <f>D7</f>
         <v>44.1</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A480" s="49"/>
-    </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A481" s="49"/>
-      <c r="B481" t="s">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A509" s="51"/>
+    </row>
+    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A510" s="51"/>
+      <c r="B510" t="s">
         <v>455</v>
       </c>
-      <c r="D481" s="1">
-        <f>((-D478)+POWER(POWER(D478, 2)-(4*D472/D462), 0.5))/(2*D472)</f>
+      <c r="D510" s="1">
+        <f>((-D507)+POWER(POWER(D507, 2)-(4*D501/D491), 0.5))/(2*D501)</f>
         <v>-1.5151530456139737</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A482" s="49"/>
-      <c r="B482" t="s">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A511" s="51"/>
+      <c r="B511" t="s">
         <v>456</v>
       </c>
-      <c r="D482" s="1">
-        <f>((-D478)-POWER(POWER(D478, 2)-(4*D472/D462), 0.5))/(2*D472)</f>
+      <c r="D511" s="1">
+        <f>((-D507)-POWER(POWER(D507, 2)-(4*D501/D491), 0.5))/(2*D501)</f>
         <v>-1499998.4848469547</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A483" s="49"/>
-      <c r="B483" t="s">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A512" s="51"/>
+      <c r="B512" t="s">
         <v>457</v>
       </c>
-      <c r="D483" s="1">
-        <f>LN(D482/D481)/(D481-D482)</f>
+      <c r="D512" s="1">
+        <f>LN(D511/D510)/(D510-D511)</f>
         <v>9.2036573945350537E-6</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A484" s="49"/>
-      <c r="B484" t="s">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A513" s="51"/>
+      <c r="B513" t="s">
         <v>240</v>
       </c>
-      <c r="D484" s="1">
-        <f>(D479/(D472*(D481-D482)))*(EXP(D481*D483)-EXP(D482*D483))</f>
+      <c r="D513" s="1">
+        <f>(D508/(D501*(D510-D511)))*(EXP(D510*D512)-EXP(D511*D512))</f>
         <v>1.3363463508162678</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A485" s="49"/>
-      <c r="B485" t="s">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A514" s="51"/>
+      <c r="B514" t="s">
         <v>458</v>
       </c>
-      <c r="D485" s="1">
-        <f>D478*POWER(D484, 2)</f>
+      <c r="D514" s="1">
+        <f>D507*POWER(D513, 2)</f>
         <v>58.932111788218542</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A486" s="49"/>
-      <c r="C486" t="s">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A515" s="51"/>
+      <c r="C515" t="s">
         <v>454</v>
       </c>
-      <c r="D486" s="1">
-        <f>D485*D4</f>
+      <c r="D515" s="1">
+        <f>D514*D4</f>
         <v>70.71853414586225</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A487" s="49"/>
-      <c r="B487" t="s">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A516" s="51"/>
+      <c r="B516" t="s">
         <v>460</v>
       </c>
-      <c r="C487" t="s">
+      <c r="C516" t="s">
         <v>459</v>
       </c>
-      <c r="D487" t="b">
-        <f>(POWER(D478, 2)/(4*POWER(D472, 2)))&lt;(1/(D472*D462))</f>
+      <c r="D516" t="b">
+        <f>(POWER(D507, 2)/(4*POWER(D501, 2)))&lt;(1/(D501*D491))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A488" s="49"/>
-      <c r="B488" t="s">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A517" s="51"/>
+      <c r="B517" t="s">
         <v>461</v>
       </c>
-      <c r="D488" s="1">
-        <f>D478/(2*D472)</f>
+      <c r="D517" s="1">
+        <f>D507/(2*D501)</f>
         <v>750000</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A489" s="49"/>
-      <c r="B489" t="s">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A518" s="51"/>
+      <c r="B518" t="s">
         <v>462</v>
       </c>
-      <c r="D489" s="1">
-        <f>1/POWER(D472*D462, 0.5)</f>
+      <c r="D518" s="1">
+        <f>1/POWER(D501*D491, 0.5)</f>
         <v>1507.5567228888181</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A490" s="49"/>
-      <c r="B490" t="s">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A519" s="51"/>
+      <c r="B519" t="s">
         <v>463</v>
       </c>
-      <c r="D490" t="str">
-        <f>IF(D487, POWER(POWER(D489, 2)-POWER(D488, 2), 0.5),"NA")</f>
+      <c r="D519" t="str">
+        <f>IF(D516, POWER(POWER(D518, 2)-POWER(D517, 2), 0.5),"NA")</f>
         <v>NA</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A491" s="49"/>
-      <c r="C491" t="s">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A520" s="51"/>
+      <c r="C520" t="s">
         <v>464</v>
       </c>
-      <c r="D491" s="1" t="str">
-        <f>IF(D487, 100*EXP(-PI()*D488/D490), "Not Under-damped")</f>
+      <c r="D520" s="1" t="str">
+        <f>IF(D516, 100*EXP(-PI()*D517/D519), "Not Under-damped")</f>
         <v>Not Under-damped</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A492" s="49"/>
-      <c r="B492" t="s">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A521" s="51"/>
+      <c r="B521" t="s">
         <v>465</v>
       </c>
-      <c r="D492" s="1">
-        <f>5/MIN(ABS(D481), ABS(D482))</f>
+      <c r="D521" s="1">
+        <f>5/MIN(ABS(D510), ABS(D511))</f>
         <v>3.2999966666561322</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A493" s="49"/>
-      <c r="B493" t="s">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A522" s="51"/>
+      <c r="B522" t="s">
         <v>483</v>
       </c>
-      <c r="C493" t="s">
+      <c r="C522" t="s">
         <v>480</v>
       </c>
-      <c r="D493">
+      <c r="D522">
         <v>1600</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A494" s="49"/>
-      <c r="C494" t="s">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A523" s="51"/>
+      <c r="C523" t="s">
         <v>481</v>
       </c>
-      <c r="D494">
+      <c r="D523">
         <v>0.1</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A495" s="49"/>
-      <c r="B495" t="s">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A524" s="51"/>
+      <c r="B524" t="s">
         <v>482</v>
       </c>
-      <c r="D495">
-        <f>D493*(1-D494)</f>
+      <c r="D524">
+        <f>D522*(1-D523)</f>
         <v>1440</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A496" s="49"/>
-      <c r="B496" t="s">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A525" s="51"/>
+      <c r="B525" t="s">
         <v>484</v>
       </c>
-      <c r="D496">
-        <f>D493*(1+D494)</f>
+      <c r="D525">
+        <f>D522*(1+D523)</f>
         <v>1760.0000000000002</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A497" s="49"/>
-      <c r="B497" t="s">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A526" s="51"/>
+      <c r="B526" t="s">
         <v>485</v>
       </c>
-      <c r="D497">
+      <c r="D526">
         <v>24</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A498" s="49"/>
-      <c r="B498" t="s">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A527" s="51"/>
+      <c r="B527" t="s">
         <v>486</v>
       </c>
-      <c r="D498">
+      <c r="D527">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A499" s="49"/>
-      <c r="C499" t="s">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A528" s="51"/>
+      <c r="C528" t="s">
         <v>487</v>
       </c>
-      <c r="D499" t="b">
-        <f>(D497/D493)=D498</f>
+      <c r="D528" t="b">
+        <f>(D526/D522)=D527</f>
         <v>1</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A500" s="49"/>
-      <c r="B500" t="s">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A529" s="51"/>
+      <c r="B529" t="s">
         <v>488</v>
       </c>
-      <c r="C500" t="s">
+      <c r="C529" t="s">
         <v>489</v>
       </c>
-      <c r="D500">
-        <f>1.3*D497</f>
+      <c r="D529">
+        <f>1.3*D526</f>
         <v>31.200000000000003</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A501" s="49"/>
-      <c r="B501" t="s">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A530" s="51"/>
+      <c r="B530" t="s">
         <v>490</v>
       </c>
-      <c r="C501" t="s">
+      <c r="C530" t="s">
         <v>491</v>
       </c>
-      <c r="D501">
-        <f>0.75*D497</f>
+      <c r="D530">
+        <f>0.75*D526</f>
         <v>18</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A502" s="49"/>
-      <c r="B502" t="s">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A531" s="51"/>
+      <c r="B531" t="s">
         <v>492</v>
       </c>
-      <c r="D502">
-        <f>D501/D496</f>
+      <c r="D531">
+        <f>D530/D525</f>
         <v>1.0227272727272725E-2</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A503" s="49"/>
-      <c r="B503" t="s">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A532" s="51"/>
+      <c r="B532" t="s">
         <v>493</v>
       </c>
-      <c r="D503">
-        <f>D500/D496</f>
+      <c r="D532">
+        <f>D529/D525</f>
         <v>1.7727272727272727E-2</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A504" s="49"/>
-      <c r="B504" t="s">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A533" s="51"/>
+      <c r="B533" t="s">
         <v>499</v>
       </c>
-      <c r="D504">
+      <c r="D533">
         <v>1330</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A505" s="49"/>
-      <c r="C505" t="s">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A534" s="51"/>
+      <c r="C534" t="s">
         <v>503</v>
       </c>
-      <c r="D505">
+      <c r="D534">
         <v>0.05</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A506" s="49"/>
-      <c r="B506" t="s">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A535" s="51"/>
+      <c r="B535" t="s">
         <v>504</v>
       </c>
-      <c r="D506">
-        <f>D504*(1-D505)</f>
+      <c r="D535">
+        <f>D533*(1-D534)</f>
         <v>1263.5</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A507" s="49"/>
-      <c r="B507" t="s">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A536" s="51"/>
+      <c r="B536" t="s">
         <v>505</v>
       </c>
-      <c r="D507">
-        <f>D504*(1+D505)</f>
+      <c r="D536">
+        <f>D533*(1+D534)</f>
         <v>1396.5</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A508" s="49"/>
-      <c r="C508" t="s">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A537" s="51"/>
+      <c r="C537" t="s">
         <v>496</v>
       </c>
-      <c r="D508">
-        <f>D6/(D493+D504)</f>
+      <c r="D537">
+        <f>D6/(D522+D533)</f>
         <v>1.3003412969283274E-2</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A509" s="49"/>
-      <c r="C509" t="s">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A538" s="51"/>
+      <c r="C538" t="s">
         <v>497</v>
       </c>
-      <c r="D509">
-        <f>D5/(D495+D507)</f>
+      <c r="D538">
+        <f>D5/(D524+D536)</f>
         <v>1.2480169222633529E-2</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A510" s="49"/>
-      <c r="C510" t="s">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A539" s="51"/>
+      <c r="C539" t="s">
         <v>498</v>
       </c>
-      <c r="D510">
-        <f>D7/(D495+D506)</f>
+      <c r="D539">
+        <f>D7/(D524+D535)</f>
         <v>1.6312187904568152E-2</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A511" s="49"/>
-      <c r="C511" t="s">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A540" s="51"/>
+      <c r="C540" t="s">
         <v>500</v>
       </c>
-      <c r="D511" t="b">
-        <f>AND((D508&gt;D502), (D510&lt;D503))</f>
+      <c r="D540" t="b">
+        <f>AND((D537&gt;D531), (D539&lt;D532))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A512" s="49"/>
-    </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A513" s="49"/>
-      <c r="B513" t="s">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A541" s="51"/>
+    </row>
+    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A542" s="51"/>
+      <c r="B542" t="s">
         <v>501</v>
       </c>
-      <c r="D513">
-        <f xml:space="preserve"> POWER(D510, 2)*D504</f>
+      <c r="D542">
+        <f xml:space="preserve"> POWER(D539, 2)*D533</f>
         <v>0.35389634073113957</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A514" s="49"/>
-      <c r="B514" t="s">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A543" s="51"/>
+      <c r="B543" t="s">
         <v>506</v>
       </c>
-      <c r="D514">
-        <f>POWER(D508, 2)*D493</f>
+      <c r="D543">
+        <f>POWER(D537, 2)*D522</f>
         <v>0.27054199815955915</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A515" s="49"/>
-      <c r="B515" t="s">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A544" s="51"/>
+      <c r="B544" t="s">
         <v>502</v>
       </c>
-      <c r="D515">
-        <f>POWER(D509, 2)*D496</f>
+      <c r="D544">
+        <f>POWER(D538, 2)*D525</f>
         <v>0.27412813793300184</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A516" s="49"/>
-      <c r="C516" t="s">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A545" s="51"/>
+      <c r="C545" t="s">
         <v>626</v>
       </c>
-      <c r="D516" s="1">
-        <f>0.5*D472*POWER(D517, 2)</f>
+      <c r="D545" s="1">
+        <f>0.5*D501*POWER(D546, 2)</f>
         <v>3.0311171733454588E-4</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A517" s="49"/>
-      <c r="C517" t="s">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A546" s="51"/>
+      <c r="C546" t="s">
         <v>627</v>
       </c>
-      <c r="D517">
+      <c r="D546">
         <f>D2/D6</f>
         <v>5.2493438320209984</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A518" s="49"/>
-      <c r="C518" t="s">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A547" s="51"/>
+      <c r="C547" t="s">
         <v>628</v>
       </c>
-      <c r="D518">
+      <c r="D547">
         <f>D6</f>
         <v>38.099999999999994</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A519" s="49"/>
-      <c r="C519" t="s">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A548" s="51"/>
+      <c r="C548" t="s">
         <v>629</v>
       </c>
-      <c r="D519">
-        <f>POWER(((0.5*D462*POWER(D518, 2))+D516)*2/D462, 0.5)</f>
+      <c r="D548">
+        <f>POWER(((0.5*D491*POWER(D547, 2))+D545)*2/D491, 0.5)</f>
         <v>38.100397782329424</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A520" t="s">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A549" s="51"/>
+      <c r="B549" t="s">
+        <v>739</v>
+      </c>
+      <c r="C549" t="s">
+        <v>738</v>
+      </c>
+      <c r="D549" s="1">
+        <f>0.5*D491*POWER(D7, 2)</f>
+        <v>19.448100000000004</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A550" t="s">
         <v>737</v>
       </c>
-      <c r="B520" t="s">
-        <v>739</v>
-      </c>
-      <c r="C520" t="s">
-        <v>738</v>
-      </c>
-      <c r="D520" s="1">
-        <f>0.5*D462*POWER(D7, 2)</f>
-        <v>19.448100000000004</v>
-      </c>
-    </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B521" t="s">
+      <c r="B550" t="s">
         <v>740</v>
       </c>
-      <c r="C521" t="s">
+      <c r="C550" t="s">
         <v>741</v>
       </c>
-      <c r="D521">
+      <c r="D550">
         <f>(0.06*0.022*0.0018)+(2*(0.06*0.0129*0.001))+(0.06*0.0091*0.0018)</f>
         <v>4.9067999999999993E-6</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B522" t="s">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B551" t="s">
         <v>742</v>
       </c>
-      <c r="C522" t="s">
+      <c r="C551" t="s">
         <v>743</v>
       </c>
-      <c r="D522">
+      <c r="D551">
         <v>850</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B523" t="s">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B552" t="s">
         <v>744</v>
       </c>
-      <c r="C523" t="s">
+      <c r="C552" t="s">
         <v>745</v>
       </c>
-      <c r="D523">
+      <c r="D552">
         <v>2700</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B524" t="s">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B553" t="s">
         <v>713</v>
       </c>
-      <c r="D524">
-        <f>D520/(D523*D521*D522)</f>
+      <c r="D553">
+        <f>D549/(D552*D550*D551)</f>
         <v>1.7270150907024588</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B525" t="s">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B554" t="s">
         <v>746</v>
       </c>
-      <c r="C525" t="s">
+      <c r="C554" t="s">
         <v>753</v>
       </c>
-      <c r="D525">
+      <c r="D554">
         <v>0.2</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B526" t="s">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B555" t="s">
         <v>751</v>
       </c>
-      <c r="C526" t="s">
+      <c r="C555" t="s">
         <v>750</v>
       </c>
-      <c r="D526">
-        <f>D522*D521*D523</f>
+      <c r="D555">
+        <f>D551*D550*D552</f>
         <v>11.261106</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B527" t="s">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B556" t="s">
         <v>757</v>
       </c>
-      <c r="C527" t="s">
+      <c r="C556" t="s">
         <v>756</v>
       </c>
-      <c r="D527">
+      <c r="D556">
         <f>0.022*0.06</f>
         <v>1.3199999999999998E-3</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B528" t="s">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B557" t="s">
         <v>758</v>
       </c>
-      <c r="C528" t="s">
+      <c r="C557" t="s">
         <v>759</v>
       </c>
-      <c r="D528">
+      <c r="D557">
         <f>0.002</f>
         <v>2E-3</v>
       </c>
     </row>
-    <row r="529" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B529" t="s">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B558" t="s">
         <v>747</v>
       </c>
-      <c r="C529" t="s">
+      <c r="C558" t="s">
         <v>748</v>
       </c>
-      <c r="D529">
+      <c r="D558">
         <v>0.5</v>
       </c>
     </row>
-    <row r="530" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B530" t="s">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B559" t="s">
         <v>752</v>
       </c>
-      <c r="C530" t="s">
+      <c r="C559" t="s">
         <v>749</v>
       </c>
-      <c r="D530">
-        <f>4.605*D526/D529</f>
+      <c r="D559">
+        <f>4.605*D555/D558</f>
         <v>103.71478626000001</v>
       </c>
     </row>
-    <row r="531" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B531" t="s">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B560" t="s">
         <v>754</v>
       </c>
-      <c r="C531" t="s">
+      <c r="C560" t="s">
         <v>755</v>
       </c>
-      <c r="D531">
-        <f>D528/(D525*D527)</f>
+      <c r="D560">
+        <f>D557/(D554*D556)</f>
         <v>7.575757575757577</v>
       </c>
     </row>
-    <row r="532" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B532" t="s">
+    <row r="561" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B561" t="s">
         <v>760</v>
       </c>
-      <c r="D532">
-        <f>D526*D524/D530</f>
+      <c r="D561">
+        <f>D555*D553/D559</f>
         <v>0.18751521071687935</v>
       </c>
     </row>
-    <row r="533" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A533" s="42"/>
-      <c r="B533" t="s">
+    <row r="562" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B562" t="s">
         <v>761</v>
       </c>
-      <c r="D533">
-        <f>D532*D531</f>
+      <c r="D562">
+        <f>D561*D560</f>
         <v>1.4205697781581772</v>
       </c>
     </row>
-    <row r="534" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A534" s="49" t="s">
+    <row r="563" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A563" s="42"/>
+      <c r="C563" t="s">
+        <v>634</v>
+      </c>
+      <c r="D563" t="s">
+        <v>635</v>
+      </c>
+      <c r="E563" t="s">
+        <v>637</v>
+      </c>
+      <c r="F563" t="s">
+        <v>636</v>
+      </c>
+      <c r="G563" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="564" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A564" s="51" t="s">
         <v>630</v>
       </c>
-      <c r="C534" t="s">
-        <v>634</v>
-      </c>
-      <c r="D534" t="s">
-        <v>635</v>
-      </c>
-      <c r="E534" t="s">
-        <v>637</v>
-      </c>
-      <c r="F534" t="s">
-        <v>636</v>
-      </c>
-      <c r="G534" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="535" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A535" s="49"/>
-      <c r="C535" t="s">
+      <c r="C564" t="s">
         <v>631</v>
       </c>
-      <c r="D535">
+      <c r="D564">
         <f>D2/D5</f>
         <v>5.6497175141242932</v>
       </c>
-      <c r="E535">
+      <c r="E564">
         <f>11*0.01</f>
         <v>0.11</v>
       </c>
-      <c r="F535">
+      <c r="F564">
         <v>1</v>
       </c>
-      <c r="G535">
+      <c r="G564">
         <v>22</v>
       </c>
-      <c r="H535">
+      <c r="H564">
         <v>10</v>
       </c>
-      <c r="I535">
+      <c r="I564">
         <v>10</v>
       </c>
-      <c r="J535">
+      <c r="J564">
         <v>10</v>
       </c>
     </row>
-    <row r="536" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A536" s="49"/>
-      <c r="C536" t="s">
+    <row r="565" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A565" s="51"/>
+      <c r="C565" t="s">
         <v>632</v>
       </c>
-      <c r="D536">
+      <c r="D565">
         <v>2</v>
       </c>
-      <c r="E536">
+      <c r="E565">
         <v>2</v>
       </c>
-      <c r="F536">
+      <c r="F565">
         <v>2</v>
       </c>
-      <c r="G536">
+      <c r="G565">
         <v>2</v>
       </c>
-      <c r="H536">
+      <c r="H565">
         <v>2</v>
       </c>
-      <c r="I536">
+      <c r="I565">
         <v>2</v>
       </c>
-      <c r="J536">
+      <c r="J565">
         <v>2</v>
       </c>
     </row>
-    <row r="537" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A537" s="49"/>
-      <c r="C537" t="s">
+    <row r="566" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A566" s="51"/>
+      <c r="C566" t="s">
         <v>633</v>
       </c>
-      <c r="D537">
+      <c r="D566">
         <v>5</v>
       </c>
-      <c r="E537">
+      <c r="E566">
         <v>5</v>
       </c>
-      <c r="F537">
+      <c r="F566">
         <v>5</v>
       </c>
-      <c r="G537">
+      <c r="G566">
         <v>5</v>
       </c>
-      <c r="H537">
+      <c r="H566">
         <v>5</v>
       </c>
-      <c r="I537">
+      <c r="I566">
         <v>5</v>
       </c>
-      <c r="J537">
+      <c r="J566">
         <v>5</v>
       </c>
     </row>
-    <row r="538" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A538" s="49"/>
-      <c r="C538" t="s">
+    <row r="567" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A567" s="51"/>
+      <c r="C567" t="s">
         <v>641</v>
       </c>
-      <c r="D538">
-        <f>0.0254*POWER(D535/(0.048*POWER(D537, 0.44)), 1/0.725)/(D536*1.378)</f>
+      <c r="D567">
+        <f>0.0254*POWER(D564/(0.048*POWER(D566, 0.44)), 1/0.725)/(D565*1.378)</f>
         <v>2.4923433704232472</v>
       </c>
-      <c r="E538">
-        <f t="shared" ref="E538:G538" si="20">0.0254*POWER(E535/(0.048*POWER(E537, 0.44)), 1/0.725)/(E536*1.378)</f>
+      <c r="E567">
+        <f t="shared" ref="E567:G567" si="20">0.0254*POWER(E564/(0.048*POWER(E566, 0.44)), 1/0.725)/(E565*1.378)</f>
         <v>1.0892125473680554E-2</v>
       </c>
-      <c r="F538">
+      <c r="F567">
         <f t="shared" si="20"/>
         <v>0.22873341897835012</v>
       </c>
-      <c r="G538">
+      <c r="G567">
         <f t="shared" si="20"/>
         <v>16.253508114154439</v>
       </c>
-      <c r="H538">
-        <f t="shared" ref="H538" si="21">0.0254*POWER(H535/(0.048*POWER(H537, 0.44)), 1/0.725)/(H536*1.378)</f>
+      <c r="H567">
+        <f t="shared" ref="H567" si="21">0.0254*POWER(H564/(0.048*POWER(H566, 0.44)), 1/0.725)/(H565*1.378)</f>
         <v>5.4782262733389961</v>
       </c>
-      <c r="I538">
-        <f t="shared" ref="I538:J538" si="22">0.0254*POWER(I535/(0.048*POWER(I537, 0.44)), 1/0.725)/(I536*1.378)</f>
+      <c r="I567">
+        <f t="shared" ref="I567:J567" si="22">0.0254*POWER(I564/(0.048*POWER(I566, 0.44)), 1/0.725)/(I565*1.378)</f>
         <v>5.4782262733389961</v>
       </c>
-      <c r="J538">
+      <c r="J567">
         <f t="shared" si="22"/>
         <v>5.4782262733389961</v>
       </c>
     </row>
-    <row r="539" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A539" s="49"/>
-      <c r="C539" t="s">
+    <row r="568" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A568" s="51"/>
+      <c r="C568" t="s">
         <v>642</v>
       </c>
-      <c r="D539">
-        <f>0.0254*POWER(D535/(0.024*POWER(D537, 0.44)), 1/0.725)/(D536*1.378)</f>
+      <c r="D568">
+        <f>0.0254*POWER(D564/(0.024*POWER(D566, 0.44)), 1/0.725)/(D565*1.378)</f>
         <v>6.4836813405534928</v>
       </c>
-      <c r="E539">
-        <f t="shared" ref="E539:I539" si="23">0.0254*POWER(E535/(0.024*POWER(E537, 0.44)), 1/0.725)/(E536*1.378)</f>
+      <c r="E568">
+        <f t="shared" ref="E568:I568" si="23">0.0254*POWER(E564/(0.024*POWER(E566, 0.44)), 1/0.725)/(E565*1.378)</f>
         <v>2.8335209157266786E-2</v>
       </c>
-      <c r="F539">
+      <c r="F568">
         <f t="shared" si="23"/>
         <v>0.59503622903255293</v>
       </c>
-      <c r="G539">
+      <c r="G568">
         <f t="shared" si="23"/>
         <v>42.282523559497292</v>
       </c>
-      <c r="H539">
+      <c r="H568">
         <f t="shared" si="23"/>
         <v>14.251276083899347</v>
       </c>
-      <c r="I539">
+      <c r="I568">
         <f t="shared" si="23"/>
         <v>14.251276083899347</v>
       </c>
     </row>
-    <row r="540" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A540" s="49"/>
-      <c r="C540" t="s">
+    <row r="569" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A569" s="51"/>
+      <c r="C569" t="s">
         <v>640</v>
       </c>
-      <c r="D540">
+      <c r="D569">
         <v>8</v>
       </c>
-      <c r="E540">
+      <c r="E569">
         <v>1</v>
       </c>
-      <c r="F540">
+      <c r="F569">
         <v>1</v>
       </c>
-      <c r="G540">
+      <c r="G569">
         <v>8</v>
       </c>
-      <c r="H540">
+      <c r="H569">
         <v>8</v>
       </c>
     </row>
-    <row r="541" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A541" s="49"/>
-      <c r="C541" t="s">
+    <row r="570" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A570" s="51"/>
+      <c r="C570" t="s">
         <v>645</v>
       </c>
-      <c r="D541">
-        <f>POWER(D535/POWER(D540*(D536*1.378)/0.0254, 0.725)/0.048, 1/0.44)</f>
+      <c r="D570">
+        <f>POWER(D564/POWER(D569*(D565*1.378)/0.0254, 0.725)/0.048, 1/0.44)</f>
         <v>0.7318559619713908</v>
       </c>
-      <c r="E541">
-        <f t="shared" ref="E541:H541" si="24">POWER(E535/POWER(E540*(E536*1.378)/0.0254, 0.725)/0.048, 1/0.44)</f>
+      <c r="E570">
+        <f t="shared" ref="E570:H570" si="24">POWER(E564/POWER(E569*(E565*1.378)/0.0254, 0.725)/0.048, 1/0.44)</f>
         <v>2.9151906392472556E-3</v>
       </c>
-      <c r="F541">
+      <c r="F570">
         <f t="shared" si="24"/>
         <v>0.43986554940209394</v>
       </c>
-      <c r="G541">
+      <c r="G570">
         <f t="shared" si="24"/>
         <v>16.078094835159579</v>
       </c>
-      <c r="H541">
+      <c r="H570">
         <f t="shared" si="24"/>
         <v>2.6791758539545092</v>
       </c>
     </row>
-    <row r="542" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A542" s="49"/>
-      <c r="C542" t="s">
+    <row r="571" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A571" s="51"/>
+      <c r="C571" t="s">
         <v>644</v>
       </c>
-      <c r="D542">
-        <f>POWER(D535/POWER(D540*(D536*1.378)/0.0254, 0.725)/0.024, 1/0.44)</f>
+      <c r="D571">
+        <f>POWER(D564/POWER(D569*(D565*1.378)/0.0254, 0.725)/0.024, 1/0.44)</f>
         <v>3.5365898499283999</v>
       </c>
-      <c r="E542">
-        <f t="shared" ref="E542:H542" si="25">POWER(E535/POWER(E540*(E536*1.378)/0.0254, 0.725)/0.024, 1/0.44)</f>
+      <c r="E571">
+        <f t="shared" ref="E571:H571" si="25">POWER(E564/POWER(E569*(E565*1.378)/0.0254, 0.725)/0.024, 1/0.44)</f>
         <v>1.4087244158805046E-2</v>
       </c>
-      <c r="F542">
+      <c r="F571">
         <f t="shared" si="25"/>
         <v>2.1255877087593311</v>
       </c>
-      <c r="G542">
+      <c r="G571">
         <f t="shared" si="25"/>
         <v>77.695106625959824</v>
       </c>
-      <c r="H542">
+      <c r="H571">
         <f t="shared" si="25"/>
         <v>12.946736275462857</v>
       </c>
     </row>
-    <row r="543" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A543" s="49"/>
-      <c r="C543" t="s">
+    <row r="572" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A572" s="51"/>
+      <c r="C572" t="s">
         <v>639</v>
       </c>
-      <c r="D543">
+      <c r="D572">
         <v>100</v>
       </c>
-      <c r="E543">
+      <c r="E572">
         <v>200</v>
       </c>
-      <c r="F543">
+      <c r="F572">
         <v>120</v>
       </c>
-      <c r="G543">
+      <c r="G572">
         <v>100</v>
       </c>
-      <c r="H543">
+      <c r="H572">
         <v>100</v>
       </c>
     </row>
-    <row r="544" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A544" s="49"/>
-      <c r="C544" t="s">
+    <row r="573" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A573" s="51"/>
+      <c r="C573" t="s">
         <v>200</v>
       </c>
-      <c r="D544">
-        <f>(0.0000000168)*(D543/1000)/((D540/1000)*0.0000348*D536)</f>
+      <c r="D573">
+        <f>(0.0000000168)*(D572/1000)/((D569/1000)*0.0000348*D565)</f>
         <v>3.0172413793103452E-3</v>
       </c>
-      <c r="E544">
-        <f>(0.0000000168)*(E543/1000)/((E540/1000)*0.0000348*E536)</f>
+      <c r="E573">
+        <f>(0.0000000168)*(E572/1000)/((E569/1000)*0.0000348*E565)</f>
         <v>4.8275862068965524E-2</v>
       </c>
-      <c r="F544">
-        <f>(0.0000000168)*(F543/1000)/((F540/1000)*0.0000348*F536)</f>
+      <c r="F573">
+        <f>(0.0000000168)*(F572/1000)/((F569/1000)*0.0000348*F565)</f>
         <v>2.8965517241379312E-2</v>
       </c>
-      <c r="G544">
-        <f>(0.0000000168)*(G543/1000)/((G540/1000)*0.0000348*G536)</f>
+      <c r="G573">
+        <f>(0.0000000168)*(G572/1000)/((G569/1000)*0.0000348*G565)</f>
         <v>3.0172413793103452E-3</v>
       </c>
-      <c r="H544">
-        <f>(0.0000000168)*(H543/1000)/((H540/1000)*0.0000348*H536)</f>
+      <c r="H573">
+        <f>(0.0000000168)*(H572/1000)/((H569/1000)*0.0000348*H565)</f>
         <v>3.0172413793103452E-3</v>
       </c>
     </row>
-    <row r="545" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A545" s="49"/>
-      <c r="C545" t="s">
+    <row r="574" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A574" s="51"/>
+      <c r="C574" t="s">
         <v>643</v>
       </c>
-      <c r="D545">
-        <f>POWER(D535, 2)*D544</f>
+      <c r="D574">
+        <f>POWER(D564, 2)*D573</f>
         <v>9.6308256864577377E-2</v>
       </c>
-      <c r="E545">
-        <f>POWER(E535, 2)*E544</f>
+      <c r="E574">
+        <f>POWER(E564, 2)*E573</f>
         <v>5.8413793103448278E-4</v>
       </c>
-      <c r="F545">
-        <f>POWER(F535, 2)*F544</f>
+      <c r="F574">
+        <f>POWER(F564, 2)*F573</f>
         <v>2.8965517241379312E-2</v>
       </c>
-      <c r="G545">
-        <f>POWER(G535, 2)*G544</f>
+      <c r="G574">
+        <f>POWER(G564, 2)*G573</f>
         <v>1.460344827586207</v>
       </c>
-      <c r="H545">
-        <f>POWER(H535, 2)*H544</f>
+      <c r="H574">
+        <f>POWER(H564, 2)*H573</f>
         <v>0.30172413793103453</v>
       </c>
     </row>
-    <row r="546" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A546" s="49"/>
-      <c r="C546" t="s">
+    <row r="575" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A575" s="51"/>
+      <c r="C575" t="s">
         <v>646</v>
       </c>
-      <c r="D546">
-        <f>D535*D544</f>
+      <c r="D575">
+        <f>D564*D573</f>
         <v>1.7046561465030197E-2</v>
       </c>
-      <c r="E546">
-        <f t="shared" ref="E546:H546" si="26">E535*E544</f>
+      <c r="E575">
+        <f t="shared" ref="E575:H575" si="26">E564*E573</f>
         <v>5.3103448275862077E-3</v>
       </c>
-      <c r="F546">
+      <c r="F575">
         <f t="shared" si="26"/>
         <v>2.8965517241379312E-2</v>
       </c>
-      <c r="G546">
+      <c r="G575">
         <f t="shared" si="26"/>
         <v>6.6379310344827594E-2</v>
       </c>
-      <c r="H546">
+      <c r="H575">
         <f t="shared" si="26"/>
         <v>3.0172413793103453E-2</v>
       </c>
     </row>
-    <row r="547" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A547" s="42"/>
-    </row>
-    <row r="548" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A548" s="42"/>
-    </row>
-    <row r="553" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A553" s="50" t="s">
+    <row r="576" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A576" s="51"/>
+    </row>
+    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A577" s="42"/>
+    </row>
+    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A578" s="42"/>
+    </row>
+    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A583" s="52" t="s">
         <v>719</v>
       </c>
-    </row>
-    <row r="554" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A554" s="50"/>
-      <c r="C554" t="s">
+      <c r="C583" t="s">
         <v>720</v>
       </c>
-      <c r="D554" s="1">
+      <c r="D583" s="1">
         <v>1000000000</v>
       </c>
     </row>
-    <row r="555" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A555" s="50"/>
-      <c r="C555" t="s">
+    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A584" s="52"/>
+      <c r="C584" t="s">
         <v>721</v>
       </c>
-      <c r="D555">
+      <c r="D584">
         <v>14</v>
       </c>
     </row>
-    <row r="556" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A556" s="50"/>
-      <c r="C556" t="s">
+    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A585" s="52"/>
+      <c r="C585" t="s">
         <v>219</v>
       </c>
-      <c r="D556" s="1">
-        <f>D554*D555</f>
+      <c r="D585" s="1">
+        <f>D583*D584</f>
         <v>14000000000</v>
       </c>
     </row>
-    <row r="557" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A557" s="50"/>
-      <c r="C557" t="s">
+    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A586" s="52"/>
+      <c r="C586" t="s">
         <v>722</v>
       </c>
-      <c r="D557">
+      <c r="D586">
         <f>2.5</f>
         <v>2.5</v>
       </c>
     </row>
-    <row r="558" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A558" s="50"/>
-      <c r="C558" t="s">
+    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A587" s="52"/>
+      <c r="C587" t="s">
         <v>723</v>
       </c>
-      <c r="D558">
-        <f>D8/D557</f>
+      <c r="D587">
+        <f>D8/D586</f>
         <v>32000</v>
       </c>
     </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A559" s="50"/>
-      <c r="C559" t="s">
+    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A588" s="52"/>
+      <c r="C588" t="s">
         <v>724</v>
       </c>
-      <c r="D559">
-        <f>D556/D558</f>
+      <c r="D588">
+        <f>D585/D587</f>
         <v>437500</v>
       </c>
     </row>
-    <row r="560" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A560" s="50"/>
-      <c r="C560" t="s">
+    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A589" s="52"/>
+      <c r="C589" t="s">
         <v>762</v>
       </c>
-      <c r="D560" s="1">
+      <c r="D589" s="1">
         <v>130000</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A561" s="50"/>
-      <c r="C561" t="s">
+    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A590" s="52"/>
+      <c r="C590" t="s">
         <v>725</v>
       </c>
-      <c r="D561" s="1">
-        <f>D8/D556</f>
+      <c r="D590" s="1">
+        <f>D8/D585</f>
         <v>5.7142857142857145E-6</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A562" s="50"/>
-      <c r="C562" t="s">
+    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A591" s="52"/>
+      <c r="C591" t="s">
         <v>726</v>
       </c>
-      <c r="D562" s="1">
-        <f>D561*D561*D554</f>
+      <c r="D591" s="1">
+        <f>D590*D590*D583</f>
         <v>3.2653061224489799E-2</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A563" s="50"/>
-      <c r="C563" t="s">
+    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A592" s="52"/>
+      <c r="C592" t="s">
         <v>727</v>
       </c>
-      <c r="D563" s="1">
-        <f>D562*D555</f>
+      <c r="D592" s="1">
+        <f>D591*D584</f>
         <v>0.45714285714285718</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A564" s="50"/>
-      <c r="C564" t="s">
+    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A593" s="52"/>
+      <c r="C593" t="s">
         <v>728</v>
       </c>
-      <c r="D564" s="1">
-        <f>POWER(D561, 2)*D560</f>
+      <c r="D593" s="1">
+        <f>POWER(D590, 2)*D589</f>
         <v>4.2448979591836746E-6</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A567" s="50" t="s">
+    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A594" s="52"/>
+    </row>
+    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C596" t="s">
+        <v>720</v>
+      </c>
+      <c r="D596" s="1">
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A597" s="52" t="s">
         <v>729</v>
       </c>
-      <c r="C567" t="s">
-        <v>720</v>
-      </c>
-      <c r="D567" s="1">
+      <c r="C597" t="s">
+        <v>721</v>
+      </c>
+      <c r="D597">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A598" s="52"/>
+      <c r="C598" t="s">
+        <v>219</v>
+      </c>
+      <c r="D598" s="1">
+        <f>D596*D597</f>
         <v>100000000</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A568" s="50"/>
-      <c r="C568" t="s">
-        <v>721</v>
-      </c>
-      <c r="D568">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A569" s="50"/>
-      <c r="C569" t="s">
-        <v>219</v>
-      </c>
-      <c r="D569" s="1">
-        <f>D567*D568</f>
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A570" s="50"/>
-      <c r="C570" t="s">
+    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A599" s="52"/>
+      <c r="C599" t="s">
         <v>722</v>
       </c>
-      <c r="D570">
+      <c r="D599">
         <v>2.5</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A571" s="50"/>
-      <c r="C571" t="s">
+    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A600" s="52"/>
+      <c r="C600" t="s">
         <v>723</v>
       </c>
-      <c r="D571">
-        <f>D12/D570</f>
+      <c r="D600">
+        <f>D12/D599</f>
         <v>5600</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A572" s="50"/>
-      <c r="C572" t="s">
+    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A601" s="52"/>
+      <c r="C601" t="s">
         <v>724</v>
       </c>
-      <c r="D572">
-        <f>D569/D571</f>
+      <c r="D601">
+        <f>D598/D600</f>
         <v>17857.142857142859</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A573" s="50"/>
-      <c r="C573" t="s">
+    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A602" s="52"/>
+      <c r="C602" t="s">
         <v>763</v>
       </c>
-      <c r="D573" s="1">
+      <c r="D602" s="1">
         <v>20000</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A574" s="50"/>
-      <c r="C574" t="s">
+    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A603" s="52"/>
+      <c r="C603" t="s">
         <v>725</v>
       </c>
-      <c r="D574" s="1">
-        <f>D12/D569</f>
+      <c r="D603" s="1">
+        <f>D12/D598</f>
         <v>1.3999999999999999E-4</v>
       </c>
     </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A575" s="50"/>
-      <c r="C575" t="s">
+    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A604" s="52"/>
+      <c r="C604" t="s">
         <v>726</v>
       </c>
-      <c r="D575" s="1">
-        <f>D574*D574*D567</f>
+      <c r="D604" s="1">
+        <f>D603*D603*D596</f>
         <v>1.9599999999999997</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A576" s="50"/>
-      <c r="C576" t="s">
+    <row r="605" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A605" s="52"/>
+      <c r="C605" t="s">
         <v>727</v>
       </c>
-      <c r="D576" s="1">
-        <f>D575*D568</f>
+      <c r="D605" s="1">
+        <f>D604*D597</f>
         <v>1.9599999999999997</v>
       </c>
     </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C577" t="s">
+    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A606" s="52"/>
+      <c r="C606" t="s">
         <v>728</v>
       </c>
-      <c r="D577" s="1">
-        <f>POWER(D574, 2)*D573</f>
+      <c r="D606" s="1">
+        <f>POWER(D603, 2)*D602</f>
         <v>3.9199999999999993E-4</v>
       </c>
     </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A579" s="49" t="s">
+    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C608" t="s">
+        <v>731</v>
+      </c>
+      <c r="D608">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="609" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A609" s="51" t="s">
         <v>730</v>
       </c>
-      <c r="C579" t="s">
-        <v>731</v>
-      </c>
-      <c r="D579">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A580" s="49"/>
-      <c r="C580" t="s">
+      <c r="C609" t="s">
         <v>732</v>
       </c>
-      <c r="D580">
+      <c r="D609">
         <v>550</v>
       </c>
-      <c r="E580" t="s">
+      <c r="E609" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A581" s="49"/>
-      <c r="C581" t="s">
+    <row r="610" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A610" s="51"/>
+      <c r="C610" t="s">
         <v>733</v>
       </c>
-      <c r="D581">
+      <c r="D610">
         <f>25.4*41.9*0.000001</f>
         <v>1.06426E-3</v>
       </c>
     </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A582" s="49"/>
-      <c r="C582" t="s">
+    <row r="611" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A611" s="51"/>
+      <c r="C611" t="s">
         <v>735</v>
       </c>
-      <c r="D582">
-        <f>D581*D580*0.3048</f>
+      <c r="D611">
+        <f>D610*D609*0.3048</f>
         <v>0.17841254640000004</v>
       </c>
-      <c r="E582" t="s">
+      <c r="E611" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A583" s="49"/>
-      <c r="C583" t="s">
+    <row r="612" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A612" s="51"/>
+      <c r="C612" t="s">
         <v>736</v>
       </c>
-      <c r="D583">
-        <f>D582*50</f>
+      <c r="D612">
+        <f>D611*50</f>
         <v>8.9206273200000012</v>
       </c>
     </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A584" s="49"/>
-    </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A585" s="49"/>
-    </row>
-    <row r="586" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A586" s="49"/>
-    </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A587" s="49"/>
-    </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A588" s="49"/>
-    </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A589" s="49"/>
-    </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A590" s="49"/>
-    </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A591" s="49"/>
-    </row>
-    <row r="593" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A593" s="49" t="s">
-        <v>764</v>
-      </c>
-      <c r="C593" t="s">
+    <row r="613" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A613" s="51"/>
+    </row>
+    <row r="614" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A614" s="51"/>
+    </row>
+    <row r="615" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A615" s="51"/>
+    </row>
+    <row r="616" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A616" s="51"/>
+    </row>
+    <row r="617" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A617" s="51"/>
+    </row>
+    <row r="618" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A618" s="51"/>
+    </row>
+    <row r="619" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A619" s="51"/>
+    </row>
+    <row r="620" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A620" s="51"/>
+    </row>
+    <row r="621" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A621" s="51"/>
+    </row>
+    <row r="622" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C622" t="s">
         <v>765</v>
       </c>
-      <c r="E593" s="1">
+      <c r="E622" s="1">
         <f>D67</f>
         <v>0.15679999999999999</v>
       </c>
     </row>
-    <row r="594" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A594" s="49"/>
-      <c r="C594" t="s">
+    <row r="623" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A623" s="51" t="s">
+        <v>764</v>
+      </c>
+      <c r="C623" t="s">
         <v>766</v>
       </c>
-      <c r="E594">
+      <c r="E623">
         <f>D27</f>
         <v>0.7</v>
       </c>
     </row>
-    <row r="595" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A595" s="49"/>
-      <c r="C595" t="s">
+    <row r="624" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A624" s="51"/>
+      <c r="C624" t="s">
         <v>767</v>
       </c>
-      <c r="E595" s="1">
+      <c r="E624" s="1">
         <f>D163+D164</f>
         <v>3.2288346657248184</v>
       </c>
     </row>
-    <row r="596" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A596" s="49"/>
-      <c r="C596" t="s">
+    <row r="625" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A625" s="51"/>
+      <c r="C625" t="s">
         <v>768</v>
       </c>
-      <c r="E596" s="1">
-        <f>E593+E594+E595</f>
+      <c r="E625" s="1">
+        <f>E622+E623+E624</f>
         <v>4.0856346657248181</v>
       </c>
     </row>
-    <row r="597" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A597" s="49"/>
-    </row>
-    <row r="598" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A598" s="49"/>
-    </row>
-    <row r="599" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A599" s="49"/>
-      <c r="C599" t="s">
+    <row r="626" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A626" s="51"/>
+    </row>
+    <row r="627" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A627" s="51"/>
+    </row>
+    <row r="628" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A628" s="51"/>
+      <c r="C628" t="s">
         <v>4</v>
       </c>
-      <c r="E599">
+      <c r="E628">
         <v>2</v>
       </c>
     </row>
-    <row r="600" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A600" s="49"/>
-      <c r="C600" t="s">
+    <row r="629" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A629" s="51"/>
+      <c r="C629" t="s">
         <v>649</v>
       </c>
-      <c r="D600" t="s">
+      <c r="D629" t="s">
         <v>212</v>
       </c>
-      <c r="E600">
+      <c r="E629">
         <v>0.17399999999999999</v>
       </c>
     </row>
-    <row r="601" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A601" s="49"/>
-      <c r="C601" t="s">
+    <row r="630" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A630" s="51"/>
+      <c r="C630" t="s">
         <v>650</v>
       </c>
-      <c r="D601" t="s">
+      <c r="D630" t="s">
         <v>212</v>
       </c>
-      <c r="E601">
+      <c r="E630">
         <v>0.5</v>
       </c>
     </row>
-    <row r="602" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A602" s="49"/>
-      <c r="C602" t="s">
+    <row r="631" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A631" s="51"/>
+      <c r="C631" t="s">
         <v>647</v>
       </c>
-      <c r="D602" t="s">
+      <c r="D631" t="s">
         <v>658</v>
       </c>
-      <c r="E602">
-        <f>POWER(E600/2, 2)*PI()*E601</f>
+      <c r="E631">
+        <f>POWER(E629/2, 2)*PI()*E630</f>
         <v>1.1889357397510571E-2</v>
       </c>
     </row>
-    <row r="603" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A603" s="49"/>
-      <c r="C603" t="s">
+    <row r="632" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A632" s="51"/>
+      <c r="C632" t="s">
         <v>651</v>
       </c>
-      <c r="E603" s="1">
-        <f>E596</f>
+      <c r="E632" s="1">
+        <f>E625</f>
         <v>4.0856346657248181</v>
       </c>
     </row>
-    <row r="604" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A604" s="49"/>
-      <c r="C604" t="s">
+    <row r="633" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A633" s="51"/>
+      <c r="C633" t="s">
         <v>656</v>
       </c>
-      <c r="D604" t="s">
+      <c r="D633" t="s">
         <v>652</v>
       </c>
-      <c r="E604">
+      <c r="E633">
         <v>2300</v>
       </c>
     </row>
-    <row r="605" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A605" s="49"/>
-      <c r="C605" t="s">
+    <row r="634" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A634" s="51"/>
+      <c r="C634" t="s">
         <v>653</v>
       </c>
-      <c r="D605" t="s">
+      <c r="D634" t="s">
         <v>654</v>
       </c>
-      <c r="E605">
+      <c r="E634">
         <v>20</v>
       </c>
     </row>
-    <row r="606" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A606" s="49"/>
-      <c r="C606" t="s">
+    <row r="635" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A635" s="51"/>
+      <c r="C635" t="s">
         <v>655</v>
       </c>
-      <c r="D606" t="s">
+      <c r="D635" t="s">
         <v>657</v>
       </c>
-      <c r="E606">
+      <c r="E635">
         <v>800</v>
       </c>
     </row>
-    <row r="607" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A607" s="49"/>
-      <c r="C607" t="s">
+    <row r="636" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A636" s="51"/>
+      <c r="C636" t="s">
         <v>659</v>
       </c>
-      <c r="D607" t="s">
+      <c r="D636" t="s">
         <v>660</v>
       </c>
-      <c r="E607">
-        <f>E606*E602</f>
+      <c r="E636">
+        <f>E635*E631</f>
         <v>9.5114859180084572</v>
       </c>
     </row>
-    <row r="608" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A608" s="49"/>
-      <c r="C608" t="s">
+    <row r="637" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A637" s="51"/>
+      <c r="C637" t="s">
         <v>661</v>
       </c>
-      <c r="D608" t="s">
+      <c r="D637" t="s">
         <v>662</v>
       </c>
-      <c r="E608">
-        <f>E604*E607*E605</f>
+      <c r="E637">
+        <f>E633*E636*E634</f>
         <v>437528.35222838906</v>
       </c>
     </row>
-    <row r="609" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A609" s="49"/>
-      <c r="C609" t="s">
+    <row r="638" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A638" s="51"/>
+      <c r="C638" t="s">
         <v>663</v>
       </c>
-      <c r="D609" t="s">
+      <c r="D638" t="s">
         <v>342</v>
       </c>
-      <c r="E609">
-        <f>E608/E603</f>
+      <c r="E638">
+        <f>E637/E632</f>
         <v>107089.44583295695</v>
       </c>
     </row>
-    <row r="610" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A610" s="49"/>
-      <c r="C610" t="s">
+    <row r="639" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A639" s="51"/>
+      <c r="C639" t="s">
         <v>664</v>
       </c>
-      <c r="D610" t="s">
+      <c r="D639" t="s">
         <v>342</v>
       </c>
-      <c r="E610">
-        <f>E609/E599</f>
+      <c r="E639">
+        <f>E638/E628</f>
         <v>53544.722916478473</v>
       </c>
     </row>
-    <row r="611" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A611" s="49"/>
-      <c r="C611" t="s">
+    <row r="640" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A640" s="51"/>
+      <c r="C640" t="s">
         <v>665</v>
       </c>
-      <c r="D611" t="s">
+      <c r="D640" t="s">
         <v>666</v>
       </c>
-      <c r="E611">
-        <f>E602/E610</f>
+      <c r="E640">
+        <f>E631/E639</f>
         <v>2.2204536226765314E-7</v>
       </c>
     </row>
-    <row r="612" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A612" s="49"/>
-      <c r="C612" t="s">
+    <row r="641" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A641" s="51"/>
+      <c r="C641" t="s">
         <v>665</v>
       </c>
-      <c r="D612" t="s">
+      <c r="D641" t="s">
         <v>667</v>
       </c>
-      <c r="E612">
-        <f>(1000000)*E611</f>
+      <c r="E641">
+        <f>(1000000)*E640</f>
         <v>0.22204536226765315</v>
       </c>
     </row>
-    <row r="613" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A613" s="49"/>
-      <c r="C613" t="s">
+    <row r="642" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A642" s="51"/>
+      <c r="C642" t="s">
         <v>668</v>
       </c>
-      <c r="D613" t="s">
+      <c r="D642" t="s">
         <v>669</v>
       </c>
-      <c r="E613">
+      <c r="E642">
         <v>0.1</v>
       </c>
     </row>
-    <row r="614" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A614" s="49"/>
-      <c r="C614" t="s">
+    <row r="643" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A643" s="51"/>
+      <c r="C643" t="s">
         <v>670</v>
       </c>
-      <c r="D614" t="s">
+      <c r="D643" t="s">
         <v>213</v>
       </c>
-      <c r="E614">
-        <f>E611/E613</f>
+      <c r="E643">
+        <f>E640/E642</f>
         <v>2.2204536226765314E-6</v>
       </c>
     </row>
-    <row r="615" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A615" s="49"/>
-      <c r="C615" t="s">
+    <row r="644" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A644" s="51"/>
+      <c r="C644" t="s">
         <v>671</v>
       </c>
-      <c r="D615" t="s">
+      <c r="D644" t="s">
         <v>212</v>
       </c>
-      <c r="E615">
-        <f>2*POWER(E614/PI(), 0.5)</f>
+      <c r="E644">
+        <f>2*POWER(E643/PI(), 0.5)</f>
         <v>1.681418853124411E-3</v>
       </c>
     </row>
-    <row r="616" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A616" s="49"/>
-      <c r="C616" t="s">
+    <row r="645" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A645" s="51"/>
+      <c r="C645" t="s">
         <v>673</v>
       </c>
-      <c r="D616" t="s">
+      <c r="D645" t="s">
         <v>212</v>
       </c>
-      <c r="E616">
-        <f>CEILING(E615, 0.001)</f>
+      <c r="E645">
+        <f>CEILING(E644, 0.001)</f>
         <v>2E-3</v>
       </c>
     </row>
-    <row r="617" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A617" s="49"/>
-      <c r="C617" t="s">
+    <row r="646" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A646" s="51"/>
+      <c r="C646" t="s">
         <v>672</v>
       </c>
-      <c r="D617" t="s">
+      <c r="D646" t="s">
         <v>139</v>
       </c>
-      <c r="E617">
-        <f>E616*1000</f>
+      <c r="E646">
+        <f>E645*1000</f>
         <v>2</v>
       </c>
     </row>
-    <row r="618" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A618" s="49"/>
-      <c r="C618" t="s">
+    <row r="647" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A647" s="51"/>
+      <c r="C647" t="s">
         <v>678</v>
       </c>
-      <c r="D618" t="s">
+      <c r="D647" t="s">
         <v>139</v>
       </c>
-      <c r="E618">
+      <c r="E647">
         <v>9</v>
       </c>
     </row>
-    <row r="619" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C619" t="s">
+    <row r="648" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A648" s="51"/>
+      <c r="C648" t="s">
         <v>679</v>
       </c>
-      <c r="E619">
-        <f>E618/1000</f>
+      <c r="E648">
+        <f>E647/1000</f>
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="620" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C620" t="s">
+    <row r="649" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C649" t="s">
         <v>676</v>
       </c>
-      <c r="E620">
+      <c r="E649">
         <f>0.00604</f>
         <v>6.0400000000000002E-3</v>
       </c>
     </row>
-    <row r="621" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C621" t="s">
+    <row r="650" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C650" t="s">
         <v>675</v>
       </c>
-      <c r="E621">
-        <f>E620/E606</f>
+      <c r="E650">
+        <f>E649/E635</f>
         <v>7.5500000000000006E-6</v>
       </c>
     </row>
-    <row r="622" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C622" t="s">
+    <row r="651" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C651" t="s">
         <v>674</v>
       </c>
-      <c r="E622">
+      <c r="E651">
         <v>2300</v>
       </c>
     </row>
-    <row r="623" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C623" t="s">
+    <row r="652" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C652" t="s">
         <v>677</v>
       </c>
-      <c r="E623">
-        <f>E606*E613*E619/E620</f>
+      <c r="E652">
+        <f>E635*E642*E648/E649</f>
         <v>119.20529801324503</v>
       </c>
     </row>
-    <row r="624" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C624" t="s">
+    <row r="653" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C653" t="s">
         <v>680</v>
       </c>
-      <c r="E624" t="b">
-        <f>E623&lt;E622</f>
+      <c r="E653" t="b">
+        <f>E652&lt;E651</f>
         <v>1</v>
       </c>
     </row>
-    <row r="627" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A627" s="49" t="s">
-        <v>785</v>
-      </c>
-      <c r="B627" t="s">
+    <row r="656" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B656" t="s">
         <v>37</v>
       </c>
-      <c r="C627" t="s">
+      <c r="C656" t="s">
         <v>44</v>
       </c>
-      <c r="D627" t="s">
+      <c r="D656" t="s">
         <v>21</v>
       </c>
-      <c r="E627">
+      <c r="E656">
         <f>D5</f>
         <v>35.400000000000006</v>
       </c>
     </row>
-    <row r="628" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A628" s="49"/>
-      <c r="B628" t="s">
+    <row r="657" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A657" s="51" t="s">
+        <v>785</v>
+      </c>
+      <c r="B657" t="s">
         <v>494</v>
       </c>
-      <c r="C628" t="s">
+      <c r="C657" t="s">
         <v>495</v>
       </c>
-      <c r="D628" t="s">
+      <c r="D657" t="s">
         <v>21</v>
       </c>
-      <c r="E628">
+      <c r="E657">
         <f>D6</f>
         <v>38.099999999999994</v>
       </c>
     </row>
-    <row r="629" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A629" s="49"/>
-      <c r="B629" t="s">
+    <row r="658" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A658" s="51"/>
+      <c r="B658" t="s">
         <v>38</v>
       </c>
-      <c r="C629" t="s">
+      <c r="C658" t="s">
         <v>43</v>
       </c>
-      <c r="D629" t="s">
+      <c r="D658" t="s">
         <v>21</v>
       </c>
-      <c r="E629">
+      <c r="E658">
         <f>D7</f>
         <v>44.1</v>
       </c>
     </row>
-    <row r="630" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A630" s="49"/>
-      <c r="C630" t="s">
+    <row r="659" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A659" s="51"/>
+      <c r="C659" t="s">
         <v>786</v>
       </c>
-      <c r="D630" t="s">
+      <c r="D659" t="s">
         <v>20</v>
       </c>
-      <c r="E630">
+      <c r="E659">
         <v>3</v>
       </c>
     </row>
-    <row r="631" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A631" s="49"/>
-      <c r="C631" t="s">
+    <row r="660" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A660" s="51"/>
+      <c r="C660" t="s">
         <v>787</v>
       </c>
-      <c r="E631">
-        <f>(E629/E630)</f>
+      <c r="E660">
+        <f>(E658/E659)</f>
         <v>14.700000000000001</v>
       </c>
     </row>
-    <row r="632" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A632" s="49"/>
-      <c r="C632" t="s">
+    <row r="661" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A661" s="51"/>
+      <c r="C661" t="s">
         <v>788</v>
       </c>
-      <c r="E632">
-        <f>E627/E630</f>
+      <c r="E661">
+        <f>E656/E659</f>
         <v>11.800000000000002</v>
       </c>
     </row>
-    <row r="633" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A633" s="49"/>
-      <c r="C633" t="s">
+    <row r="662" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A662" s="51"/>
+      <c r="C662" t="s">
         <v>789</v>
       </c>
-      <c r="E633">
-        <f>E628/E630</f>
+      <c r="E662">
+        <f>E657/E659</f>
         <v>12.699999999999998</v>
       </c>
     </row>
-    <row r="634" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A634" s="49"/>
-      <c r="C634" t="s">
+    <row r="663" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A663" s="51"/>
+      <c r="C663" t="s">
         <v>790</v>
       </c>
-      <c r="E634">
+      <c r="E663">
         <f>12</f>
         <v>12</v>
       </c>
     </row>
-    <row r="635" spans="1:15" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A635" s="49"/>
-      <c r="C635" t="s">
+    <row r="664" spans="1:15" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A664" s="51"/>
+      <c r="C664" t="s">
         <v>791</v>
       </c>
-      <c r="E635">
-        <f>E629*E629/E634</f>
+      <c r="E664">
+        <f>E658*E658/E663</f>
         <v>162.06750000000002</v>
       </c>
-      <c r="G635" s="18" t="s">
+      <c r="G664" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="H635" s="48" t="s">
+      <c r="H664" s="48" t="s">
         <v>797</v>
       </c>
-      <c r="I635" s="48" t="s">
+      <c r="I664" s="48" t="s">
         <v>800</v>
       </c>
-      <c r="J635" s="48" t="s">
+      <c r="J664" s="48" t="s">
         <v>799</v>
       </c>
-      <c r="K635" s="48" t="s">
+      <c r="K664" s="48" t="s">
         <v>798</v>
       </c>
-      <c r="L635" s="48" t="s">
+      <c r="L664" s="48" t="s">
         <v>801</v>
       </c>
-      <c r="M635" s="48" t="s">
+      <c r="M664" s="48" t="s">
         <v>802</v>
       </c>
-      <c r="N635" s="48" t="s">
+      <c r="N664" s="48" t="s">
         <v>804</v>
       </c>
-      <c r="O635" s="47"/>
-    </row>
-    <row r="636" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A636" s="49"/>
-      <c r="C636" t="s">
+      <c r="O664" s="47"/>
+    </row>
+    <row r="665" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A665" s="51"/>
+      <c r="C665" t="s">
         <v>792</v>
       </c>
-      <c r="E636">
+      <c r="E665">
         <f>6</f>
         <v>6</v>
       </c>
-      <c r="G636" s="18">
+      <c r="G665" s="18">
         <v>1</v>
       </c>
-      <c r="H636" s="18">
-        <f>E629/G636</f>
+      <c r="H665" s="18">
+        <f>E658/G665</f>
         <v>44.1</v>
       </c>
-      <c r="I636" s="18">
-        <f>H636*H636*G636</f>
+      <c r="I665" s="18">
+        <f>H665*H665*G665</f>
         <v>1944.8100000000002</v>
       </c>
-      <c r="J636" s="18">
-        <f>I636/2</f>
+      <c r="J665" s="18">
+        <f>I665/2</f>
         <v>972.40500000000009</v>
       </c>
-      <c r="K636" s="18">
-        <f>E627/G636</f>
+      <c r="K665" s="18">
+        <f>E656/G665</f>
         <v>35.400000000000006</v>
       </c>
-      <c r="L636" s="18">
-        <f>E627*E627/G636</f>
+      <c r="L665" s="18">
+        <f>E656*E656/G665</f>
         <v>1253.1600000000003</v>
       </c>
-      <c r="M636" s="18">
-        <f>L636/2</f>
+      <c r="M665" s="18">
+        <f>L665/2</f>
         <v>626.58000000000015</v>
       </c>
-      <c r="N636" s="47"/>
-    </row>
-    <row r="637" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A637" s="49"/>
-      <c r="C637" t="s">
+      <c r="N665" s="47"/>
+    </row>
+    <row r="666" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A666" s="51"/>
+      <c r="C666" t="s">
         <v>793</v>
       </c>
-      <c r="E637">
+      <c r="E666">
         <v>2</v>
       </c>
-      <c r="G637" s="18">
+      <c r="G666" s="18">
         <v>2</v>
       </c>
-      <c r="H637" s="18">
-        <f>E629/G637</f>
+      <c r="H666" s="18">
+        <f>E658/G666</f>
         <v>22.05</v>
       </c>
-      <c r="I637" s="18">
-        <f t="shared" ref="I637:I649" si="27">H637*H637*G637</f>
+      <c r="I666" s="18">
+        <f t="shared" ref="I666:I678" si="27">H666*H666*G666</f>
         <v>972.40500000000009</v>
       </c>
-      <c r="J637" s="18">
-        <f>I637/2</f>
+      <c r="J666" s="18">
+        <f>I666/2</f>
         <v>486.20250000000004</v>
       </c>
-      <c r="K637" s="18">
-        <f>E627/G637</f>
+      <c r="K666" s="18">
+        <f>E656/G666</f>
         <v>17.700000000000003</v>
       </c>
-      <c r="L637" s="18">
-        <f>E627*E627/G637</f>
+      <c r="L666" s="18">
+        <f>E656*E656/G666</f>
         <v>626.58000000000015</v>
       </c>
-      <c r="M637" s="18">
-        <f>L637/2</f>
+      <c r="M666" s="18">
+        <f>L666/2</f>
         <v>313.29000000000008</v>
       </c>
-      <c r="N637" s="47"/>
-    </row>
-    <row r="638" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A638" s="49"/>
-      <c r="C638" t="s">
+      <c r="N666" s="47"/>
+    </row>
+    <row r="667" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A667" s="51"/>
+      <c r="C667" t="s">
         <v>794</v>
       </c>
-      <c r="E638">
-        <f xml:space="preserve"> E636*E637</f>
+      <c r="E667">
+        <f xml:space="preserve"> E665*E666</f>
         <v>12</v>
       </c>
-      <c r="G638" s="18">
+      <c r="G667" s="18">
         <v>3</v>
       </c>
-      <c r="H638" s="18">
-        <f>E629/G638</f>
+      <c r="H667" s="18">
+        <f>E658/G667</f>
         <v>14.700000000000001</v>
       </c>
-      <c r="I638" s="18">
+      <c r="I667" s="18">
         <f t="shared" si="27"/>
         <v>648.2700000000001</v>
       </c>
-      <c r="J638" s="18">
-        <f>I638/2</f>
+      <c r="J667" s="18">
+        <f>I667/2</f>
         <v>324.13500000000005</v>
       </c>
-      <c r="K638" s="18">
-        <f>E627/G638</f>
+      <c r="K667" s="18">
+        <f>E656/G667</f>
         <v>11.800000000000002</v>
       </c>
-      <c r="L638" s="18">
-        <f>E627*E627/G638</f>
+      <c r="L667" s="18">
+        <f>E656*E656/G667</f>
         <v>417.72000000000008</v>
       </c>
-      <c r="M638" s="18">
-        <f>L638/2</f>
+      <c r="M667" s="18">
+        <f>L667/2</f>
         <v>208.86000000000004</v>
       </c>
     </row>
-    <row r="639" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A639" s="49"/>
-      <c r="G639" s="18">
+    <row r="668" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A668" s="51"/>
+      <c r="G668" s="18">
         <v>4</v>
       </c>
-      <c r="H639" s="18">
-        <f>E629/G639</f>
+      <c r="H668" s="18">
+        <f>E658/G668</f>
         <v>11.025</v>
       </c>
-      <c r="I639" s="18">
+      <c r="I668" s="18">
         <f t="shared" si="27"/>
         <v>486.20250000000004</v>
       </c>
-      <c r="J639" s="18">
-        <f t="shared" ref="J639:J649" si="28">I639/2</f>
+      <c r="J668" s="18">
+        <f t="shared" ref="J668:J678" si="28">I668/2</f>
         <v>243.10125000000002</v>
       </c>
-      <c r="K639" s="18">
-        <f>E627/G639</f>
+      <c r="K668" s="18">
+        <f>E656/G668</f>
         <v>8.8500000000000014</v>
       </c>
-      <c r="L639" s="18">
-        <f>E627*E627/G639</f>
+      <c r="L668" s="18">
+        <f>E656*E656/G668</f>
         <v>313.29000000000008</v>
       </c>
-      <c r="M639" s="18">
-        <f t="shared" ref="M639:M649" si="29">L639/2</f>
+      <c r="M668" s="18">
+        <f t="shared" ref="M668:M678" si="29">L668/2</f>
         <v>156.64500000000004</v>
       </c>
     </row>
-    <row r="640" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A640" s="49"/>
-      <c r="C640" t="s">
+    <row r="669" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A669" s="51"/>
+      <c r="C669" t="s">
         <v>795</v>
       </c>
-      <c r="E640">
-        <f>(POWER(E629,2))/(200*2)</f>
+      <c r="E669">
+        <f>(POWER(E658,2))/(200*2)</f>
         <v>4.862025</v>
       </c>
-      <c r="G640" s="18">
+      <c r="G669" s="18">
         <v>5</v>
       </c>
-      <c r="H640" s="18">
-        <f>E629/G640</f>
+      <c r="H669" s="18">
+        <f>E658/G669</f>
         <v>8.82</v>
       </c>
-      <c r="I640" s="18">
+      <c r="I669" s="18">
         <f t="shared" si="27"/>
         <v>388.96199999999999</v>
       </c>
-      <c r="J640" s="18">
+      <c r="J669" s="18">
         <f t="shared" si="28"/>
         <v>194.48099999999999</v>
       </c>
-      <c r="K640" s="18">
-        <f>E627/G640</f>
+      <c r="K669" s="18">
+        <f>E656/G669</f>
         <v>7.080000000000001</v>
       </c>
-      <c r="L640" s="18">
-        <f>E627*E627/G640</f>
+      <c r="L669" s="18">
+        <f>E656*E656/G669</f>
         <v>250.63200000000006</v>
       </c>
-      <c r="M640" s="18">
+      <c r="M669" s="18">
         <f t="shared" si="29"/>
         <v>125.31600000000003</v>
       </c>
-      <c r="N640" t="s">
+      <c r="N669" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="641" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A641" s="49"/>
-      <c r="C641" t="s">
+    <row r="670" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A670" s="51"/>
+      <c r="C670" t="s">
         <v>796</v>
       </c>
-      <c r="E641">
-        <f>E629/E640</f>
+      <c r="E670">
+        <f>E658/E669</f>
         <v>9.0702947845804989</v>
       </c>
-      <c r="G641" s="18">
+      <c r="G670" s="18">
         <v>6</v>
       </c>
-      <c r="H641" s="18">
-        <f>E629/G641</f>
+      <c r="H670" s="18">
+        <f>E658/G670</f>
         <v>7.3500000000000005</v>
       </c>
-      <c r="I641" s="18">
+      <c r="I670" s="18">
         <f t="shared" si="27"/>
         <v>324.13500000000005</v>
       </c>
-      <c r="J641" s="18">
+      <c r="J670" s="18">
         <f t="shared" si="28"/>
         <v>162.06750000000002</v>
       </c>
-      <c r="K641" s="18">
-        <f>E627/G641</f>
+      <c r="K670" s="18">
+        <f>E656/G670</f>
         <v>5.9000000000000012</v>
       </c>
-      <c r="L641" s="18">
-        <f>E627*E627/G641</f>
+      <c r="L670" s="18">
+        <f>E656*E656/G670</f>
         <v>208.86000000000004</v>
       </c>
-      <c r="M641" s="18">
+      <c r="M670" s="18">
         <f t="shared" si="29"/>
         <v>104.43000000000002</v>
       </c>
-      <c r="N641" t="s">
+      <c r="N670" t="s">
         <v>805</v>
       </c>
     </row>
-    <row r="642" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G642" s="18">
+    <row r="671" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A671" s="51"/>
+      <c r="G671" s="18">
         <v>7</v>
       </c>
-      <c r="H642" s="18">
-        <f>E629/G642</f>
+      <c r="H671" s="18">
+        <f>E658/G671</f>
         <v>6.3</v>
       </c>
-      <c r="I642" s="18">
+      <c r="I671" s="18">
         <f t="shared" si="27"/>
         <v>277.83</v>
       </c>
-      <c r="J642" s="18">
+      <c r="J671" s="18">
         <f t="shared" si="28"/>
         <v>138.91499999999999</v>
       </c>
-      <c r="K642" s="18">
-        <f>E627/G642</f>
+      <c r="K671" s="18">
+        <f>E656/G671</f>
         <v>5.0571428571428578</v>
       </c>
-      <c r="L642" s="18">
-        <f>E627*E627/G642</f>
+      <c r="L671" s="18">
+        <f>E656*E656/G671</f>
         <v>179.02285714285719</v>
       </c>
-      <c r="M642" s="18">
+      <c r="M671" s="18">
         <f t="shared" si="29"/>
         <v>89.511428571428596</v>
       </c>
-      <c r="N642" t="s">
+      <c r="N671" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="643" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G643" s="18">
+    <row r="672" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G672" s="18">
         <v>8</v>
       </c>
-      <c r="H643" s="18">
-        <f>E629/G643</f>
+      <c r="H672" s="18">
+        <f>E658/G672</f>
         <v>5.5125000000000002</v>
       </c>
-      <c r="I643" s="18">
+      <c r="I672" s="18">
         <f t="shared" si="27"/>
         <v>243.10125000000002</v>
       </c>
-      <c r="J643" s="18">
+      <c r="J672" s="18">
         <f t="shared" si="28"/>
         <v>121.55062500000001</v>
       </c>
-      <c r="K643" s="18">
-        <f>E627/G643</f>
+      <c r="K672" s="18">
+        <f>E656/G672</f>
         <v>4.4250000000000007</v>
       </c>
-      <c r="L643" s="18">
-        <f>E627*E627/G643</f>
+      <c r="L672" s="18">
+        <f>E656*E656/G672</f>
         <v>156.64500000000004</v>
       </c>
-      <c r="M643" s="18">
+      <c r="M672" s="18">
         <f t="shared" si="29"/>
         <v>78.322500000000019</v>
       </c>
-      <c r="N643" t="s">
+      <c r="N672" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="644" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G644" s="18">
+    <row r="673" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G673" s="18">
         <v>9</v>
       </c>
-      <c r="H644" s="18">
-        <f>E629/G644</f>
+      <c r="H673" s="18">
+        <f>E658/G673</f>
         <v>4.9000000000000004</v>
       </c>
-      <c r="I644" s="18">
+      <c r="I673" s="18">
         <f t="shared" si="27"/>
         <v>216.09000000000003</v>
       </c>
-      <c r="J644" s="18">
+      <c r="J673" s="18">
         <f t="shared" si="28"/>
         <v>108.04500000000002</v>
       </c>
-      <c r="K644" s="18">
-        <f>E627/G644</f>
+      <c r="K673" s="18">
+        <f>E656/G673</f>
         <v>3.933333333333334</v>
       </c>
-      <c r="L644" s="18">
-        <f>E627*E627/G644</f>
+      <c r="L673" s="18">
+        <f>E656*E656/G673</f>
         <v>139.24000000000004</v>
       </c>
-      <c r="M644" s="18">
+      <c r="M673" s="18">
         <f t="shared" si="29"/>
         <v>69.620000000000019</v>
       </c>
-      <c r="N644" t="s">
+      <c r="N673" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="645" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G645" s="18">
+    <row r="674" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G674" s="18">
         <v>10</v>
       </c>
-      <c r="H645" s="18">
-        <f>E629/G645</f>
+      <c r="H674" s="18">
+        <f>E658/G674</f>
         <v>4.41</v>
       </c>
-      <c r="I645" s="18">
+      <c r="I674" s="18">
         <f t="shared" si="27"/>
         <v>194.48099999999999</v>
       </c>
-      <c r="J645" s="18">
+      <c r="J674" s="18">
         <f t="shared" si="28"/>
         <v>97.240499999999997</v>
       </c>
-      <c r="K645" s="18">
-        <f>E627/G645</f>
+      <c r="K674" s="18">
+        <f>E656/G674</f>
         <v>3.5400000000000005</v>
       </c>
-      <c r="L645" s="18">
-        <f>E627*E627/G645</f>
+      <c r="L674" s="18">
+        <f>E656*E656/G674</f>
         <v>125.31600000000003</v>
       </c>
-      <c r="M645" s="18">
+      <c r="M674" s="18">
         <f t="shared" si="29"/>
         <v>62.658000000000015</v>
       </c>
-      <c r="N645" t="s">
+      <c r="N674" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="646" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G646" s="18">
+    <row r="675" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G675" s="18">
         <v>11</v>
       </c>
-      <c r="H646" s="18">
-        <f>E629/G646</f>
+      <c r="H675" s="18">
+        <f>E658/G675</f>
         <v>4.0090909090909088</v>
       </c>
-      <c r="I646" s="18">
+      <c r="I675" s="18">
         <f t="shared" si="27"/>
         <v>176.80090909090904</v>
       </c>
-      <c r="J646" s="18">
+      <c r="J675" s="18">
         <f t="shared" si="28"/>
         <v>88.400454545454522</v>
       </c>
-      <c r="K646" s="18">
-        <f>E627/G646</f>
+      <c r="K675" s="18">
+        <f>E656/G675</f>
         <v>3.2181818181818187</v>
       </c>
-      <c r="L646" s="18">
-        <f>E627*E627/G646</f>
+      <c r="L675" s="18">
+        <f>E656*E656/G675</f>
         <v>113.92363636363639</v>
       </c>
-      <c r="M646" s="18">
+      <c r="M675" s="18">
         <f t="shared" si="29"/>
         <v>56.961818181818195</v>
       </c>
-      <c r="N646" t="s">
+      <c r="N675" t="s">
         <v>810</v>
       </c>
     </row>
-    <row r="647" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G647" s="18">
+    <row r="676" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G676" s="18">
         <v>12</v>
       </c>
-      <c r="H647" s="18">
-        <f>E629/G647</f>
+      <c r="H676" s="18">
+        <f>E658/G676</f>
         <v>3.6750000000000003</v>
       </c>
-      <c r="I647" s="18">
+      <c r="I676" s="18">
         <f t="shared" si="27"/>
         <v>162.06750000000002</v>
       </c>
-      <c r="J647" s="18">
+      <c r="J676" s="18">
         <f t="shared" si="28"/>
         <v>81.033750000000012</v>
       </c>
-      <c r="K647" s="18">
-        <f>E627/G647</f>
+      <c r="K676" s="18">
+        <f>E656/G676</f>
         <v>2.9500000000000006</v>
       </c>
-      <c r="L647" s="18">
-        <f>E627*E627/G647</f>
+      <c r="L676" s="18">
+        <f>E656*E656/G676</f>
         <v>104.43000000000002</v>
       </c>
-      <c r="M647" s="18">
+      <c r="M676" s="18">
         <f t="shared" si="29"/>
         <v>52.215000000000011</v>
       </c>
-      <c r="N647" t="s">
+      <c r="N676" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="648" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G648" s="18">
+    <row r="677" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G677" s="18">
         <v>13</v>
       </c>
-      <c r="H648" s="18">
-        <f>E629/G648</f>
+      <c r="H677" s="18">
+        <f>E658/G677</f>
         <v>3.3923076923076922</v>
       </c>
-      <c r="I648" s="18">
+      <c r="I677" s="18">
         <f t="shared" si="27"/>
         <v>149.60076923076923</v>
       </c>
-      <c r="J648" s="18">
+      <c r="J677" s="18">
         <f t="shared" si="28"/>
         <v>74.800384615384615</v>
       </c>
-      <c r="K648" s="18">
-        <f>E627/G648</f>
+      <c r="K677" s="18">
+        <f>E656/G677</f>
         <v>2.7230769230769236</v>
       </c>
-      <c r="L648" s="18">
-        <f>E627*E627/G648</f>
+      <c r="L677" s="18">
+        <f>E656*E656/G677</f>
         <v>96.396923076923102</v>
       </c>
-      <c r="M648" s="18">
+      <c r="M677" s="18">
         <f t="shared" si="29"/>
         <v>48.198461538461551</v>
       </c>
-      <c r="N648" t="s">
+      <c r="N677" t="s">
         <v>811</v>
       </c>
     </row>
-    <row r="649" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G649" s="18">
+    <row r="678" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G678" s="18">
         <v>14</v>
       </c>
-      <c r="H649" s="18">
-        <f>E629/G649</f>
+      <c r="H678" s="18">
+        <f>E658/G678</f>
         <v>3.15</v>
       </c>
-      <c r="I649" s="18">
+      <c r="I678" s="18">
         <f t="shared" si="27"/>
         <v>138.91499999999999</v>
       </c>
-      <c r="J649" s="18">
+      <c r="J678" s="18">
         <f t="shared" si="28"/>
         <v>69.457499999999996</v>
       </c>
-      <c r="K649" s="18">
-        <f>E627/G649</f>
+      <c r="K678" s="18">
+        <f>E656/G678</f>
         <v>2.5285714285714289</v>
       </c>
-      <c r="L649" s="18">
-        <f>E627*E627/G649</f>
+      <c r="L678" s="18">
+        <f>E656*E656/G678</f>
         <v>89.511428571428596</v>
       </c>
-      <c r="M649" s="18">
+      <c r="M678" s="18">
         <f t="shared" si="29"/>
         <v>44.755714285714298</v>
       </c>
-      <c r="N649" t="s">
+      <c r="N678" t="s">
         <v>813</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
     <mergeCell ref="A31:A59"/>
-    <mergeCell ref="A593:A618"/>
+    <mergeCell ref="A623:A648"/>
     <mergeCell ref="A228:A279"/>
     <mergeCell ref="G19:J22"/>
     <mergeCell ref="G29:K34"/>
@@ -12330,14 +12895,14 @@
     <mergeCell ref="A98:A169"/>
     <mergeCell ref="A171:A226"/>
     <mergeCell ref="A303:A315"/>
-    <mergeCell ref="A579:A591"/>
-    <mergeCell ref="A627:A641"/>
+    <mergeCell ref="A609:A621"/>
+    <mergeCell ref="A657:A671"/>
     <mergeCell ref="A364:A376"/>
     <mergeCell ref="A377:A380"/>
-    <mergeCell ref="A553:A564"/>
-    <mergeCell ref="A567:A576"/>
-    <mergeCell ref="A449:A519"/>
-    <mergeCell ref="A534:A546"/>
+    <mergeCell ref="A583:A594"/>
+    <mergeCell ref="A597:A606"/>
+    <mergeCell ref="A479:A549"/>
+    <mergeCell ref="A564:A576"/>
   </mergeCells>
   <conditionalFormatting sqref="D110">
     <cfRule type="cellIs" dxfId="9" priority="9" operator="notEqual">
@@ -12347,7 +12912,7 @@
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E624">
+  <conditionalFormatting sqref="E653">
     <cfRule type="cellIs" dxfId="7" priority="7" operator="notEqual">
       <formula>TRUE</formula>
     </cfRule>
@@ -12631,17 +13196,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="53"/>
+      <c r="B1" s="55"/>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C18" s="54" t="s">
+      <c r="C18" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="D18" s="55"/>
-      <c r="E18" s="56"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="58"/>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C19" s="18" t="s">
@@ -12835,17 +13400,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="55" t="s">
         <v>166</v>
       </c>
-      <c r="B1" s="53"/>
+      <c r="B1" s="55"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="54" t="s">
+      <c r="B17" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="C17" s="55"/>
-      <c r="D17" s="56"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="58"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B18" s="18" t="s">
@@ -13098,17 +13663,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="55" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="53"/>
+      <c r="B1" s="55"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="54" t="s">
+      <c r="B17" s="56" t="s">
         <v>167</v>
       </c>
-      <c r="C17" s="55"/>
-      <c r="D17" s="56"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="58"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B18" s="18" t="s">

--- a/Spreadsheets/BasicCalculations.xlsx
+++ b/Spreadsheets/BasicCalculations.xlsx
@@ -16,12 +16,12 @@
     <sheet name="Active Cooling" sheetId="8" r:id="rId7"/>
     <sheet name="Sheet3" sheetId="9" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="144525" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1185" uniqueCount="866">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="878">
   <si>
     <t>N stages required</t>
   </si>
@@ -2644,6 +2644,42 @@
   </si>
   <si>
     <t>Minimum resistor value between Rb node and ADC input node</t>
+  </si>
+  <si>
+    <t>t_half_cycle</t>
+  </si>
+  <si>
+    <t>N_ts</t>
+  </si>
+  <si>
+    <t>N time steps for integrating volt-time-product</t>
+  </si>
+  <si>
+    <t>Time step</t>
+  </si>
+  <si>
+    <t>Interval</t>
+  </si>
+  <si>
+    <t>I_primary</t>
+  </si>
+  <si>
+    <t>I_primary_pk</t>
+  </si>
+  <si>
+    <t>I_secondary</t>
+  </si>
+  <si>
+    <t>Vs_step</t>
+  </si>
+  <si>
+    <t>Vs</t>
+  </si>
+  <si>
+    <t>Vs_max_actual</t>
+  </si>
+  <si>
+    <t>Vs acceptible</t>
   </si>
 </sst>
 </file>
@@ -2848,7 +2884,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2935,8 +2971,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2956,7 +2996,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3408,13 +3447,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>394607</xdr:colOff>
-      <xdr:row>585</xdr:row>
+      <xdr:row>598</xdr:row>
       <xdr:rowOff>81643</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>1282199</xdr:colOff>
-      <xdr:row>607</xdr:row>
+      <xdr:row>620</xdr:row>
       <xdr:rowOff>101281</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4334,7 +4373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R678"/>
+  <dimension ref="A1:CX691"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" customWidth="1"/>
@@ -4581,15 +4620,15 @@
       <c r="C19" s="8"/>
       <c r="D19" s="13"/>
       <c r="E19" s="8"/>
-      <c r="G19" s="53" t="s">
+      <c r="G19" s="55" t="s">
         <v>589</v>
       </c>
-      <c r="H19" s="53"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="53"/>
+      <c r="H19" s="55"/>
+      <c r="I19" s="55"/>
+      <c r="J19" s="55"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="52" t="s">
+      <c r="A20" s="53" t="s">
         <v>103</v>
       </c>
       <c r="B20" t="s">
@@ -4604,13 +4643,13 @@
       <c r="E20" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="53"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
+      <c r="G20" s="55"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="55"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="52"/>
+      <c r="A21" s="53"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6" t="s">
         <v>3</v>
@@ -4622,13 +4661,13 @@
       <c r="E21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G21" s="53"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="55"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="52"/>
+      <c r="A22" s="53"/>
       <c r="B22" t="s">
         <v>67</v>
       </c>
@@ -4638,13 +4677,13 @@
       <c r="D22">
         <v>0.1</v>
       </c>
-      <c r="G22" s="53"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="55"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="52"/>
+      <c r="A23" s="53"/>
       <c r="B23" s="6"/>
       <c r="C23" s="12" t="s">
         <v>72</v>
@@ -4656,7 +4695,7 @@
       <c r="E23" s="6"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="52"/>
+      <c r="A24" s="53"/>
       <c r="C24" t="s">
         <v>7</v>
       </c>
@@ -4665,7 +4704,7 @@
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="52"/>
+      <c r="A25" s="53"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6" t="s">
         <v>28</v>
@@ -4674,7 +4713,7 @@
       <c r="E25" s="6"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="52"/>
+      <c r="A26" s="53"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
         <v>12</v>
@@ -4688,7 +4727,7 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="52"/>
+      <c r="A27" s="53"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6" t="s">
         <v>11</v>
@@ -4702,7 +4741,7 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="52"/>
+      <c r="A28" s="53"/>
       <c r="C28" t="s">
         <v>8</v>
       </c>
@@ -4714,7 +4753,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="52"/>
+      <c r="A29" s="53"/>
       <c r="C29" t="s">
         <v>10</v>
       </c>
@@ -4725,41 +4764,41 @@
       <c r="E29" t="s">
         <v>25</v>
       </c>
-      <c r="G29" s="53" t="s">
+      <c r="G29" s="55" t="s">
         <v>590</v>
       </c>
-      <c r="H29" s="54"/>
-      <c r="I29" s="54"/>
-      <c r="J29" s="54"/>
-      <c r="K29" s="54"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="56"/>
+      <c r="K29" s="56"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B30" s="8"/>
       <c r="C30" s="10"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="G30" s="54"/>
-      <c r="H30" s="54"/>
-      <c r="I30" s="54"/>
-      <c r="J30" s="54"/>
-      <c r="K30" s="54"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="56"/>
+      <c r="K30" s="56"/>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="52" t="s">
+      <c r="A31" s="53" t="s">
         <v>132</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="7"/>
-      <c r="G31" s="54"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="54"/>
-      <c r="J31" s="54"/>
-      <c r="K31" s="54"/>
+      <c r="G31" s="56"/>
+      <c r="H31" s="56"/>
+      <c r="I31" s="56"/>
+      <c r="J31" s="56"/>
+      <c r="K31" s="56"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="52"/>
+      <c r="A32" s="53"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6" t="s">
         <v>126</v>
@@ -4771,14 +4810,14 @@
       <c r="E32" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G32" s="54"/>
-      <c r="H32" s="54"/>
-      <c r="I32" s="54"/>
-      <c r="J32" s="54"/>
-      <c r="K32" s="54"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="56"/>
+      <c r="J32" s="56"/>
+      <c r="K32" s="56"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="52"/>
+      <c r="A33" s="53"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8" t="s">
         <v>127</v>
@@ -4789,14 +4828,14 @@
       <c r="E33" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="54"/>
-      <c r="J33" s="54"/>
-      <c r="K33" s="54"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="56"/>
+      <c r="J33" s="56"/>
+      <c r="K33" s="56"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="52"/>
+      <c r="A34" s="53"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8" t="s">
         <v>128</v>
@@ -4805,14 +4844,14 @@
         <v>5</v>
       </c>
       <c r="E34" s="9"/>
-      <c r="G34" s="54"/>
-      <c r="H34" s="54"/>
-      <c r="I34" s="54"/>
-      <c r="J34" s="54"/>
-      <c r="K34" s="54"/>
+      <c r="G34" s="56"/>
+      <c r="H34" s="56"/>
+      <c r="I34" s="56"/>
+      <c r="J34" s="56"/>
+      <c r="K34" s="56"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="52"/>
+      <c r="A35" s="53"/>
       <c r="C35" t="s">
         <v>133</v>
       </c>
@@ -4822,7 +4861,7 @@
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="52"/>
+      <c r="A36" s="53"/>
       <c r="C36" t="s">
         <v>136</v>
       </c>
@@ -4834,7 +4873,7 @@
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="52"/>
+      <c r="A37" s="53"/>
       <c r="C37" t="s">
         <v>169</v>
       </c>
@@ -4844,7 +4883,7 @@
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="52"/>
+      <c r="A38" s="53"/>
       <c r="C38" t="s">
         <v>170</v>
       </c>
@@ -4854,7 +4893,7 @@
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="52"/>
+      <c r="A39" s="53"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6" t="s">
         <v>9</v>
@@ -4868,7 +4907,7 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="52"/>
+      <c r="A40" s="53"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6" t="s">
         <v>772</v>
@@ -4882,7 +4921,7 @@
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="52"/>
+      <c r="A41" s="53"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6" t="s">
         <v>171</v>
@@ -4894,7 +4933,7 @@
       <c r="E41" s="6"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="52"/>
+      <c r="A42" s="53"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
         <v>172</v>
@@ -4906,7 +4945,7 @@
       <c r="E42" s="6"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="52"/>
+      <c r="A43" s="53"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6" t="s">
         <v>773</v>
@@ -4920,7 +4959,7 @@
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="52"/>
+      <c r="A44" s="53"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6" t="s">
         <v>27</v>
@@ -4934,7 +4973,7 @@
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="52"/>
+      <c r="A45" s="53"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6" t="s">
         <v>770</v>
@@ -4947,7 +4986,7 @@
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="52"/>
+      <c r="A46" s="53"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6" t="s">
         <v>771</v>
@@ -4959,7 +4998,7 @@
       <c r="E46" s="6"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="52"/>
+      <c r="A47" s="53"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6" t="s">
         <v>774</v>
@@ -4971,14 +5010,14 @@
       <c r="E47" s="6"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="52"/>
+      <c r="A48" s="53"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
       <c r="D48" s="11"/>
       <c r="E48" s="6"/>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A49" s="52"/>
+      <c r="A49" s="53"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8" t="s">
         <v>776</v>
@@ -4990,7 +5029,7 @@
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A50" s="52"/>
+      <c r="A50" s="53"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8" t="s">
         <v>682</v>
@@ -5001,7 +5040,7 @@
       <c r="E50" s="8"/>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A51" s="52"/>
+      <c r="A51" s="53"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8" t="s">
         <v>683</v>
@@ -5012,7 +5051,7 @@
       <c r="E51" s="8"/>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A52" s="52"/>
+      <c r="A52" s="53"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8" t="s">
         <v>777</v>
@@ -5024,7 +5063,7 @@
       <c r="E52" s="8"/>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A53" s="52"/>
+      <c r="A53" s="53"/>
       <c r="B53" s="44"/>
       <c r="C53" s="44" t="s">
         <v>200</v>
@@ -5036,7 +5075,7 @@
       <c r="E53" s="44"/>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A54" s="52"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6" t="s">
         <v>779</v>
@@ -5048,7 +5087,7 @@
       <c r="E54" s="6"/>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A55" s="52"/>
+      <c r="A55" s="53"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6" t="s">
         <v>780</v>
@@ -5061,7 +5100,7 @@
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A56" s="52"/>
+      <c r="A56" s="53"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6" t="s">
         <v>782</v>
@@ -5072,7 +5111,7 @@
       <c r="E56" s="6"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A57" s="52"/>
+      <c r="A57" s="53"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6" t="s">
         <v>778</v>
@@ -5084,7 +5123,7 @@
       <c r="E57" s="6"/>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A58" s="52"/>
+      <c r="A58" s="53"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6" t="s">
         <v>783</v>
@@ -5096,7 +5135,7 @@
       <c r="E58" s="6"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A59" s="52"/>
+      <c r="A59" s="53"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6" t="s">
         <v>784</v>
@@ -5120,7 +5159,7 @@
       </c>
     </row>
     <row r="61" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="52" t="s">
+      <c r="A61" s="53" t="s">
         <v>30</v>
       </c>
       <c r="C61" s="8" t="s">
@@ -5144,7 +5183,7 @@
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A62" s="52"/>
+      <c r="A62" s="53"/>
       <c r="C62" s="8" t="s">
         <v>26</v>
       </c>
@@ -5166,7 +5205,7 @@
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A63" s="52"/>
+      <c r="A63" s="53"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6" t="s">
         <v>13</v>
@@ -5190,7 +5229,7 @@
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A64" s="52"/>
+      <c r="A64" s="53"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6" t="s">
         <v>14</v>
@@ -5211,7 +5250,7 @@
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A65" s="52"/>
+      <c r="A65" s="53"/>
       <c r="C65" s="8" t="s">
         <v>16</v>
       </c>
@@ -5234,7 +5273,7 @@
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A66" s="52"/>
+      <c r="A66" s="53"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6" t="s">
         <v>107</v>
@@ -5255,7 +5294,7 @@
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A67" s="52"/>
+      <c r="A67" s="53"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6" t="s">
         <v>15</v>
@@ -5276,7 +5315,7 @@
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A68" s="52"/>
+      <c r="A68" s="53"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6" t="s">
         <v>32</v>
@@ -5288,7 +5327,7 @@
       <c r="E68" s="6"/>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A69" s="52"/>
+      <c r="A69" s="53"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6" t="s">
         <v>108</v>
@@ -5307,7 +5346,7 @@
       <c r="E70" s="8"/>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A71" s="51" t="s">
+      <c r="A71" s="54" t="s">
         <v>109</v>
       </c>
       <c r="C71" s="6"/>
@@ -5315,7 +5354,7 @@
       <c r="E71" s="6"/>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A72" s="51"/>
+      <c r="A72" s="54"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6" t="s">
         <v>90</v>
@@ -5327,7 +5366,7 @@
       <c r="E72" s="6"/>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A73" s="51"/>
+      <c r="A73" s="54"/>
       <c r="B73" s="6" t="s">
         <v>124</v>
       </c>
@@ -5343,7 +5382,7 @@
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A74" s="51"/>
+      <c r="A74" s="54"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6" t="s">
         <v>135</v>
@@ -5355,7 +5394,7 @@
       <c r="E74" s="6"/>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A75" s="51"/>
+      <c r="A75" s="54"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6" t="s">
         <v>91</v>
@@ -5368,7 +5407,7 @@
       <c r="R75" s="1"/>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A76" s="51"/>
+      <c r="A76" s="54"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6" t="s">
         <v>92</v>
@@ -5380,7 +5419,7 @@
       <c r="E76" s="6"/>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A77" s="51"/>
+      <c r="A77" s="54"/>
       <c r="B77" s="6" t="s">
         <v>123</v>
       </c>
@@ -5394,7 +5433,7 @@
       <c r="E77" s="6"/>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A78" s="51"/>
+      <c r="A78" s="54"/>
       <c r="B78" s="6" t="s">
         <v>119</v>
       </c>
@@ -5408,7 +5447,7 @@
       <c r="E78" s="6"/>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A79" s="51"/>
+      <c r="A79" s="54"/>
       <c r="B79" s="6" t="s">
         <v>122</v>
       </c>
@@ -5422,7 +5461,7 @@
       <c r="E79" s="6"/>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A80" s="51"/>
+      <c r="A80" s="54"/>
       <c r="C80" t="s">
         <v>94</v>
       </c>
@@ -5431,7 +5470,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="51"/>
+      <c r="A81" s="54"/>
       <c r="C81" t="s">
         <v>95</v>
       </c>
@@ -5440,7 +5479,7 @@
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="51"/>
+      <c r="A82" s="54"/>
       <c r="C82" t="s">
         <v>96</v>
       </c>
@@ -5455,7 +5494,7 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="51"/>
+      <c r="A83" s="54"/>
       <c r="C83" t="s">
         <v>97</v>
       </c>
@@ -5465,7 +5504,7 @@
       <c r="G83" s="5"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="51"/>
+      <c r="A84" s="54"/>
       <c r="C84" t="s">
         <v>98</v>
       </c>
@@ -5474,7 +5513,7 @@
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="51"/>
+      <c r="A85" s="54"/>
       <c r="C85" t="s">
         <v>99</v>
       </c>
@@ -5483,7 +5522,7 @@
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="51"/>
+      <c r="A86" s="54"/>
       <c r="C86" t="s">
         <v>100</v>
       </c>
@@ -5492,7 +5531,7 @@
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="51"/>
+      <c r="A87" s="54"/>
       <c r="C87" t="s">
         <v>113</v>
       </c>
@@ -5501,7 +5540,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="51"/>
+      <c r="A88" s="54"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6" t="s">
         <v>110</v>
@@ -5513,7 +5552,7 @@
       <c r="E88" s="6"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="51"/>
+      <c r="A89" s="54"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6" t="s">
         <v>111</v>
@@ -5525,7 +5564,7 @@
       <c r="E89" s="6"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="51"/>
+      <c r="A90" s="54"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6" t="s">
         <v>112</v>
@@ -5537,7 +5576,7 @@
       <c r="E90" s="6"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="51"/>
+      <c r="A91" s="54"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6" t="s">
         <v>114</v>
@@ -5549,7 +5588,7 @@
       <c r="E91" s="6"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="51"/>
+      <c r="A92" s="54"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6" t="s">
         <v>115</v>
@@ -5561,7 +5600,7 @@
       <c r="E92" s="6"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="51"/>
+      <c r="A93" s="54"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6" t="s">
         <v>116</v>
@@ -5573,7 +5612,7 @@
       <c r="E93" s="6"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="51"/>
+      <c r="A94" s="54"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6" t="s">
         <v>117</v>
@@ -5585,7 +5624,7 @@
       <c r="E94" s="6"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="51"/>
+      <c r="A95" s="54"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6" t="s">
         <v>118</v>
@@ -5606,7 +5645,7 @@
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="52" t="s">
+      <c r="A98" s="53" t="s">
         <v>125</v>
       </c>
       <c r="B98" s="6" t="s">
@@ -5622,7 +5661,7 @@
       <c r="E98" s="2"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="52"/>
+      <c r="A99" s="53"/>
       <c r="B99" t="s">
         <v>58</v>
       </c>
@@ -5634,7 +5673,7 @@
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="52"/>
+      <c r="A100" s="53"/>
       <c r="B100" t="s">
         <v>57</v>
       </c>
@@ -5643,7 +5682,7 @@
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="52"/>
+      <c r="A101" s="53"/>
       <c r="B101" t="s">
         <v>51</v>
       </c>
@@ -5655,7 +5694,7 @@
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="52"/>
+      <c r="A102" s="53"/>
       <c r="C102" t="s">
         <v>36</v>
       </c>
@@ -5664,7 +5703,7 @@
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="52"/>
+      <c r="A103" s="53"/>
       <c r="B103" t="s">
         <v>39</v>
       </c>
@@ -5676,7 +5715,7 @@
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="52"/>
+      <c r="A104" s="53"/>
       <c r="B104" t="s">
         <v>578</v>
       </c>
@@ -5689,7 +5728,7 @@
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="52"/>
+      <c r="A105" s="53"/>
       <c r="B105" t="s">
         <v>41</v>
       </c>
@@ -5702,7 +5741,7 @@
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="52"/>
+      <c r="A106" s="53"/>
       <c r="C106" t="s">
         <v>40</v>
       </c>
@@ -5712,7 +5751,7 @@
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="52"/>
+      <c r="A107" s="53"/>
       <c r="B107" t="s">
         <v>45</v>
       </c>
@@ -5725,7 +5764,7 @@
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="52"/>
+      <c r="A108" s="53"/>
       <c r="B108" t="s">
         <v>53</v>
       </c>
@@ -5738,7 +5777,7 @@
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="52"/>
+      <c r="A109" s="53"/>
       <c r="B109" t="s">
         <v>55</v>
       </c>
@@ -5751,7 +5790,7 @@
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="52"/>
+      <c r="A110" s="53"/>
       <c r="C110" t="s">
         <v>60</v>
       </c>
@@ -5761,7 +5800,7 @@
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="52"/>
+      <c r="A111" s="53"/>
       <c r="B111" t="s">
         <v>580</v>
       </c>
@@ -5774,7 +5813,7 @@
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="52"/>
+      <c r="A112" s="53"/>
       <c r="B112" t="s">
         <v>581</v>
       </c>
@@ -5790,7 +5829,7 @@
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="52"/>
+      <c r="A113" s="53"/>
       <c r="B113" t="s">
         <v>64</v>
       </c>
@@ -5803,7 +5842,7 @@
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="52"/>
+      <c r="A114" s="53"/>
       <c r="C114" t="s">
         <v>66</v>
       </c>
@@ -5813,7 +5852,7 @@
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="52"/>
+      <c r="A115" s="53"/>
       <c r="B115" t="s">
         <v>68</v>
       </c>
@@ -5829,7 +5868,7 @@
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="52"/>
+      <c r="A116" s="53"/>
       <c r="B116" t="s">
         <v>815</v>
       </c>
@@ -5845,7 +5884,7 @@
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="52"/>
+      <c r="A117" s="53"/>
       <c r="B117" t="s">
         <v>174</v>
       </c>
@@ -5858,7 +5897,7 @@
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="52"/>
+      <c r="A118" s="53"/>
       <c r="C118" t="s">
         <v>176</v>
       </c>
@@ -5867,7 +5906,7 @@
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="52"/>
+      <c r="A119" s="53"/>
       <c r="C119" t="s">
         <v>227</v>
       </c>
@@ -5877,7 +5916,7 @@
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="52"/>
+      <c r="A120" s="53"/>
       <c r="C120" t="s">
         <v>187</v>
       </c>
@@ -5889,7 +5928,7 @@
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="52"/>
+      <c r="A121" s="53"/>
       <c r="C121" t="s">
         <v>185</v>
       </c>
@@ -5901,7 +5940,7 @@
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="52"/>
+      <c r="A122" s="53"/>
       <c r="C122" t="s">
         <v>184</v>
       </c>
@@ -5910,7 +5949,7 @@
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="52"/>
+      <c r="A123" s="53"/>
       <c r="C123" t="s">
         <v>178</v>
       </c>
@@ -5923,7 +5962,7 @@
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="52"/>
+      <c r="A124" s="53"/>
       <c r="C124" t="s">
         <v>179</v>
       </c>
@@ -5936,7 +5975,7 @@
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="52"/>
+      <c r="A125" s="53"/>
       <c r="C125" t="s">
         <v>180</v>
       </c>
@@ -5948,7 +5987,7 @@
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="52"/>
+      <c r="A126" s="53"/>
       <c r="C126" t="s">
         <v>189</v>
       </c>
@@ -5961,7 +6000,7 @@
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="52"/>
+      <c r="A127" s="53"/>
       <c r="C127" t="s">
         <v>181</v>
       </c>
@@ -5971,7 +6010,7 @@
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="52"/>
+      <c r="A128" s="53"/>
       <c r="C128" t="s">
         <v>182</v>
       </c>
@@ -5981,7 +6020,7 @@
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="52"/>
+      <c r="A129" s="53"/>
       <c r="C129" t="s">
         <v>177</v>
       </c>
@@ -5991,7 +6030,7 @@
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="52"/>
+      <c r="A130" s="53"/>
       <c r="C130" t="s">
         <v>183</v>
       </c>
@@ -6001,7 +6040,7 @@
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="52"/>
+      <c r="A131" s="53"/>
       <c r="C131" t="s">
         <v>195</v>
       </c>
@@ -6011,7 +6050,7 @@
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="52"/>
+      <c r="A132" s="53"/>
       <c r="C132" t="s">
         <v>194</v>
       </c>
@@ -6024,7 +6063,7 @@
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="52"/>
+      <c r="A133" s="53"/>
       <c r="C133" t="s">
         <v>186</v>
       </c>
@@ -6034,7 +6073,7 @@
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" s="52"/>
+      <c r="A134" s="53"/>
       <c r="C134" t="s">
         <v>188</v>
       </c>
@@ -6044,7 +6083,7 @@
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" s="52"/>
+      <c r="A135" s="53"/>
       <c r="C135" t="s">
         <v>189</v>
       </c>
@@ -6054,7 +6093,7 @@
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="52"/>
+      <c r="A136" s="53"/>
       <c r="C136" t="s">
         <v>190</v>
       </c>
@@ -6067,7 +6106,7 @@
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" s="52"/>
+      <c r="A137" s="53"/>
       <c r="C137" t="s">
         <v>191</v>
       </c>
@@ -6076,7 +6115,7 @@
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" s="52"/>
+      <c r="A138" s="53"/>
       <c r="C138" t="s">
         <v>193</v>
       </c>
@@ -6086,7 +6125,7 @@
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" s="52"/>
+      <c r="A139" s="53"/>
       <c r="C139" t="s">
         <v>225</v>
       </c>
@@ -6096,7 +6135,7 @@
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" s="52"/>
+      <c r="A140" s="53"/>
       <c r="C140" t="s">
         <v>201</v>
       </c>
@@ -6105,7 +6144,7 @@
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A141" s="52"/>
+      <c r="A141" s="53"/>
       <c r="C141" t="s">
         <v>200</v>
       </c>
@@ -6115,7 +6154,7 @@
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" s="52"/>
+      <c r="A142" s="53"/>
       <c r="C142" t="s">
         <v>202</v>
       </c>
@@ -6128,19 +6167,19 @@
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143" s="52"/>
+      <c r="A143" s="53"/>
       <c r="C143" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A144" s="52"/>
+      <c r="A144" s="53"/>
       <c r="C144" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" s="52"/>
+      <c r="A145" s="53"/>
       <c r="C145" t="s">
         <v>199</v>
       </c>
@@ -6152,7 +6191,7 @@
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A146" s="52"/>
+      <c r="A146" s="53"/>
       <c r="C146" t="s">
         <v>209</v>
       </c>
@@ -6162,7 +6201,7 @@
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" s="52"/>
+      <c r="A147" s="53"/>
       <c r="C147" t="s">
         <v>198</v>
       </c>
@@ -6171,7 +6210,7 @@
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" s="52"/>
+      <c r="A148" s="53"/>
       <c r="C148" t="s">
         <v>203</v>
       </c>
@@ -6180,7 +6219,7 @@
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149" s="52"/>
+      <c r="A149" s="53"/>
       <c r="C149" t="s">
         <v>204</v>
       </c>
@@ -6190,7 +6229,7 @@
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A150" s="52"/>
+      <c r="A150" s="53"/>
       <c r="C150" t="s">
         <v>189</v>
       </c>
@@ -6200,7 +6239,7 @@
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151" s="52"/>
+      <c r="A151" s="53"/>
       <c r="C151" t="s">
         <v>190</v>
       </c>
@@ -6210,7 +6249,7 @@
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A152" s="52"/>
+      <c r="A152" s="53"/>
       <c r="C152" t="s">
         <v>206</v>
       </c>
@@ -6223,7 +6262,7 @@
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153" s="52"/>
+      <c r="A153" s="53"/>
       <c r="C153" t="s">
         <v>207</v>
       </c>
@@ -6236,7 +6275,7 @@
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A154" s="52"/>
+      <c r="A154" s="53"/>
       <c r="C154" t="s">
         <v>208</v>
       </c>
@@ -6249,7 +6288,7 @@
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" s="52"/>
+      <c r="A155" s="53"/>
       <c r="C155" t="s">
         <v>210</v>
       </c>
@@ -6262,7 +6301,7 @@
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" s="52"/>
+      <c r="A156" s="53"/>
       <c r="C156" t="s">
         <v>211</v>
       </c>
@@ -6275,7 +6314,7 @@
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A157" s="52"/>
+      <c r="A157" s="53"/>
       <c r="C157" t="s">
         <v>201</v>
       </c>
@@ -6284,7 +6323,7 @@
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A158" s="52"/>
+      <c r="A158" s="53"/>
       <c r="C158" t="s">
         <v>215</v>
       </c>
@@ -6294,7 +6333,7 @@
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159" s="52"/>
+      <c r="A159" s="53"/>
       <c r="C159" t="s">
         <v>216</v>
       </c>
@@ -6304,7 +6343,7 @@
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A160" s="52"/>
+      <c r="A160" s="53"/>
       <c r="C160" t="s">
         <v>217</v>
       </c>
@@ -6317,7 +6356,7 @@
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A161" s="52"/>
+      <c r="A161" s="53"/>
       <c r="C161" t="s">
         <v>218</v>
       </c>
@@ -6327,7 +6366,7 @@
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A162" s="52"/>
+      <c r="A162" s="53"/>
       <c r="C162" t="s">
         <v>219</v>
       </c>
@@ -6337,7 +6376,7 @@
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A163" s="52"/>
+      <c r="A163" s="53"/>
       <c r="C163" t="s">
         <v>220</v>
       </c>
@@ -6347,7 +6386,7 @@
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A164" s="52"/>
+      <c r="A164" s="53"/>
       <c r="C164" t="s">
         <v>221</v>
       </c>
@@ -6357,7 +6396,7 @@
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A165" s="52"/>
+      <c r="A165" s="53"/>
       <c r="C165" t="s">
         <v>222</v>
       </c>
@@ -6367,7 +6406,7 @@
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A166" s="52"/>
+      <c r="A166" s="53"/>
       <c r="C166" t="s">
         <v>223</v>
       </c>
@@ -6380,7 +6419,7 @@
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A167" s="52"/>
+      <c r="A167" s="53"/>
       <c r="C167" t="s">
         <v>295</v>
       </c>
@@ -6389,7 +6428,7 @@
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A168" s="52"/>
+      <c r="A168" s="53"/>
       <c r="C168" t="s">
         <v>814</v>
       </c>
@@ -6399,7 +6438,7 @@
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A169" s="52"/>
+      <c r="A169" s="53"/>
       <c r="C169" t="s">
         <v>231</v>
       </c>
@@ -6412,7 +6451,7 @@
       <c r="A170" s="24"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A171" s="51" t="s">
+      <c r="A171" s="54" t="s">
         <v>537</v>
       </c>
       <c r="B171" t="s">
@@ -6424,7 +6463,7 @@
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A172" s="51"/>
+      <c r="A172" s="54"/>
       <c r="B172" t="s">
         <v>50</v>
       </c>
@@ -6437,7 +6476,7 @@
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A173" s="51"/>
+      <c r="A173" s="54"/>
       <c r="B173" t="s">
         <v>48</v>
       </c>
@@ -6447,7 +6486,7 @@
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A174" s="51"/>
+      <c r="A174" s="54"/>
       <c r="B174" t="s">
         <v>76</v>
       </c>
@@ -6457,7 +6496,7 @@
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A175" s="51"/>
+      <c r="A175" s="54"/>
       <c r="B175" t="s">
         <v>531</v>
       </c>
@@ -6469,7 +6508,7 @@
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A176" s="51"/>
+      <c r="A176" s="54"/>
       <c r="B176" t="s">
         <v>240</v>
       </c>
@@ -6479,7 +6518,7 @@
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A177" s="51"/>
+      <c r="A177" s="54"/>
       <c r="B177" t="s">
         <v>241</v>
       </c>
@@ -6489,7 +6528,7 @@
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A178" s="51"/>
+      <c r="A178" s="54"/>
       <c r="B178" t="s">
         <v>536</v>
       </c>
@@ -6499,7 +6538,7 @@
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A179" s="51"/>
+      <c r="A179" s="54"/>
       <c r="B179" t="s">
         <v>238</v>
       </c>
@@ -6508,7 +6547,7 @@
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A180" s="51"/>
+      <c r="A180" s="54"/>
       <c r="B180" t="s">
         <v>228</v>
       </c>
@@ -6521,7 +6560,7 @@
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A181" s="51"/>
+      <c r="A181" s="54"/>
       <c r="B181" t="s">
         <v>39</v>
       </c>
@@ -6531,7 +6570,7 @@
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A182" s="51"/>
+      <c r="A182" s="54"/>
       <c r="B182" t="s">
         <v>300</v>
       </c>
@@ -6541,7 +6580,7 @@
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A183" s="51"/>
+      <c r="A183" s="54"/>
       <c r="B183" t="s">
         <v>229</v>
       </c>
@@ -6551,7 +6590,7 @@
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A184" s="51"/>
+      <c r="A184" s="54"/>
       <c r="B184" t="s">
         <v>230</v>
       </c>
@@ -6561,7 +6600,7 @@
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A185" s="51"/>
+      <c r="A185" s="54"/>
       <c r="B185" t="s">
         <v>242</v>
       </c>
@@ -6571,7 +6610,7 @@
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A186" s="51"/>
+      <c r="A186" s="54"/>
       <c r="B186" t="s">
         <v>235</v>
       </c>
@@ -6581,7 +6620,7 @@
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A187" s="51"/>
+      <c r="A187" s="54"/>
       <c r="B187" t="s">
         <v>233</v>
       </c>
@@ -6590,7 +6629,7 @@
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A188" s="51"/>
+      <c r="A188" s="54"/>
       <c r="B188" t="s">
         <v>533</v>
       </c>
@@ -6600,7 +6639,7 @@
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A189" s="51"/>
+      <c r="A189" s="54"/>
       <c r="B189" t="s">
         <v>535</v>
       </c>
@@ -6610,7 +6649,7 @@
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A190" s="51"/>
+      <c r="A190" s="54"/>
       <c r="B190" t="s">
         <v>243</v>
       </c>
@@ -6623,7 +6662,7 @@
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A191" s="51"/>
+      <c r="A191" s="54"/>
       <c r="B191" t="s">
         <v>232</v>
       </c>
@@ -6635,7 +6674,7 @@
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A192" s="51"/>
+      <c r="A192" s="54"/>
       <c r="B192" t="s">
         <v>234</v>
       </c>
@@ -6645,7 +6684,7 @@
       </c>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A193" s="51"/>
+      <c r="A193" s="54"/>
       <c r="B193" t="s">
         <v>293</v>
       </c>
@@ -6657,7 +6696,7 @@
       </c>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A194" s="51"/>
+      <c r="A194" s="54"/>
       <c r="B194" t="s">
         <v>534</v>
       </c>
@@ -6666,7 +6705,7 @@
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A195" s="51"/>
+      <c r="A195" s="54"/>
       <c r="B195" t="s">
         <v>510</v>
       </c>
@@ -6675,7 +6714,7 @@
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A196" s="51"/>
+      <c r="A196" s="54"/>
       <c r="B196" t="s">
         <v>236</v>
       </c>
@@ -6685,7 +6724,7 @@
       </c>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A197" s="51"/>
+      <c r="A197" s="54"/>
       <c r="B197" t="s">
         <v>511</v>
       </c>
@@ -6695,7 +6734,7 @@
       </c>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A198" s="51"/>
+      <c r="A198" s="54"/>
       <c r="B198" t="s">
         <v>515</v>
       </c>
@@ -6729,7 +6768,7 @@
       </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A199" s="51"/>
+      <c r="A199" s="54"/>
       <c r="B199" t="s">
         <v>516</v>
       </c>
@@ -6769,7 +6808,7 @@
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A200" s="51"/>
+      <c r="A200" s="54"/>
       <c r="B200" t="s">
         <v>514</v>
       </c>
@@ -6806,7 +6845,7 @@
       </c>
     </row>
     <row r="201" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="51"/>
+      <c r="A201" s="54"/>
       <c r="B201" t="s">
         <v>512</v>
       </c>
@@ -6843,7 +6882,7 @@
       </c>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A202" s="51"/>
+      <c r="A202" s="54"/>
       <c r="B202" t="s">
         <v>513</v>
       </c>
@@ -6880,7 +6919,7 @@
       </c>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A203" s="51"/>
+      <c r="A203" s="54"/>
       <c r="B203" t="s">
         <v>296</v>
       </c>
@@ -6917,7 +6956,7 @@
       </c>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A204" s="51"/>
+      <c r="A204" s="54"/>
       <c r="B204" t="s">
         <v>297</v>
       </c>
@@ -6954,7 +6993,7 @@
       </c>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A205" s="51"/>
+      <c r="A205" s="54"/>
       <c r="B205" t="s">
         <v>298</v>
       </c>
@@ -6987,7 +7026,7 @@
       </c>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A206" s="51"/>
+      <c r="A206" s="54"/>
       <c r="B206" t="s">
         <v>299</v>
       </c>
@@ -6997,7 +7036,7 @@
       </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A207" s="51"/>
+      <c r="A207" s="54"/>
       <c r="B207" t="s">
         <v>300</v>
       </c>
@@ -7007,14 +7046,14 @@
       </c>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A208" s="51"/>
+      <c r="A208" s="54"/>
       <c r="B208" t="s">
         <v>301</v>
       </c>
       <c r="D208" s="1"/>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A209" s="51"/>
+      <c r="A209" s="54"/>
       <c r="B209" t="s">
         <v>302</v>
       </c>
@@ -7024,7 +7063,7 @@
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A210" s="51"/>
+      <c r="A210" s="54"/>
       <c r="B210" t="s">
         <v>248</v>
       </c>
@@ -7033,7 +7072,7 @@
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A211" s="51"/>
+      <c r="A211" s="54"/>
       <c r="C211" t="s">
         <v>249</v>
       </c>
@@ -7042,7 +7081,7 @@
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A212" s="51"/>
+      <c r="A212" s="54"/>
       <c r="C212" t="s">
         <v>250</v>
       </c>
@@ -7052,7 +7091,7 @@
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A213" s="51"/>
+      <c r="A213" s="54"/>
       <c r="C213" t="s">
         <v>251</v>
       </c>
@@ -7061,10 +7100,10 @@
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A214" s="51"/>
+      <c r="A214" s="54"/>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A215" s="51"/>
+      <c r="A215" s="54"/>
       <c r="B215" t="s">
         <v>253</v>
       </c>
@@ -7073,7 +7112,7 @@
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A216" s="51"/>
+      <c r="A216" s="54"/>
       <c r="B216" t="s">
         <v>277</v>
       </c>
@@ -7083,7 +7122,7 @@
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A217" s="51"/>
+      <c r="A217" s="54"/>
       <c r="B217" t="s">
         <v>254</v>
       </c>
@@ -7092,7 +7131,7 @@
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A218" s="51"/>
+      <c r="A218" s="54"/>
       <c r="B218" t="s">
         <v>255</v>
       </c>
@@ -7102,7 +7141,7 @@
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A219" s="51"/>
+      <c r="A219" s="54"/>
       <c r="B219" t="s">
         <v>256</v>
       </c>
@@ -7115,7 +7154,7 @@
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A220" s="51"/>
+      <c r="A220" s="54"/>
       <c r="B220" t="s">
         <v>257</v>
       </c>
@@ -7128,7 +7167,7 @@
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A221" s="51"/>
+      <c r="A221" s="54"/>
       <c r="B221" t="s">
         <v>258</v>
       </c>
@@ -7141,7 +7180,7 @@
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A222" s="51"/>
+      <c r="A222" s="54"/>
       <c r="B222" t="s">
         <v>259</v>
       </c>
@@ -7157,7 +7196,7 @@
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A223" s="51"/>
+      <c r="A223" s="54"/>
       <c r="B223" t="s">
         <v>260</v>
       </c>
@@ -7167,7 +7206,7 @@
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A224" s="51"/>
+      <c r="A224" s="54"/>
       <c r="C224" t="s">
         <v>261</v>
       </c>
@@ -7177,7 +7216,7 @@
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A225" s="51"/>
+      <c r="A225" s="54"/>
       <c r="C225" t="s">
         <v>262</v>
       </c>
@@ -7187,7 +7226,7 @@
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A226" s="51"/>
+      <c r="A226" s="54"/>
       <c r="C226" t="s">
         <v>263</v>
       </c>
@@ -7203,12 +7242,12 @@
       <c r="A227" s="29"/>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A228" s="51" t="s">
+      <c r="A228" s="54" t="s">
         <v>775</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A229" s="51"/>
+      <c r="A229" s="54"/>
       <c r="B229" t="s">
         <v>576</v>
       </c>
@@ -7217,10 +7256,10 @@
       </c>
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A230" s="51"/>
+      <c r="A230" s="54"/>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A231" s="51"/>
+      <c r="A231" s="54"/>
       <c r="B231" t="s">
         <v>532</v>
       </c>
@@ -7229,7 +7268,7 @@
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A232" s="51"/>
+      <c r="A232" s="54"/>
       <c r="B232" t="s">
         <v>547</v>
       </c>
@@ -7268,7 +7307,7 @@
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A233" s="51"/>
+      <c r="A233" s="54"/>
       <c r="B233" t="s">
         <v>561</v>
       </c>
@@ -7307,7 +7346,7 @@
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A234" s="51"/>
+      <c r="A234" s="54"/>
       <c r="B234" t="s">
         <v>548</v>
       </c>
@@ -7346,7 +7385,7 @@
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A235" s="51"/>
+      <c r="A235" s="54"/>
       <c r="B235" t="s">
         <v>327</v>
       </c>
@@ -7387,7 +7426,7 @@
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A236" s="51"/>
+      <c r="A236" s="54"/>
       <c r="B236" t="s">
         <v>549</v>
       </c>
@@ -7428,7 +7467,7 @@
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A237" s="51"/>
+      <c r="A237" s="54"/>
       <c r="B237" t="s">
         <v>551</v>
       </c>
@@ -7466,7 +7505,7 @@
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A238" s="51"/>
+      <c r="A238" s="54"/>
       <c r="B238" t="s">
         <v>553</v>
       </c>
@@ -7505,7 +7544,7 @@
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A239" s="51"/>
+      <c r="A239" s="54"/>
       <c r="B239" t="s">
         <v>48</v>
       </c>
@@ -7543,7 +7582,7 @@
       </c>
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A240" s="51"/>
+      <c r="A240" s="54"/>
       <c r="B240" t="s">
         <v>39</v>
       </c>
@@ -7581,11 +7620,11 @@
       </c>
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A241" s="51"/>
+      <c r="A241" s="54"/>
       <c r="C241" s="34"/>
     </row>
     <row r="242" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A242" s="51"/>
+      <c r="A242" s="54"/>
       <c r="B242" t="s">
         <v>558</v>
       </c>
@@ -7622,7 +7661,7 @@
       </c>
     </row>
     <row r="243" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A243" s="51"/>
+      <c r="A243" s="54"/>
       <c r="B243" t="s">
         <v>567</v>
       </c>
@@ -7635,7 +7674,7 @@
       </c>
     </row>
     <row r="244" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A244" s="51"/>
+      <c r="A244" s="54"/>
       <c r="B244" t="s">
         <v>546</v>
       </c>
@@ -7677,7 +7716,7 @@
       <c r="L244" s="1"/>
     </row>
     <row r="245" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A245" s="51"/>
+      <c r="A245" s="54"/>
       <c r="B245" t="s">
         <v>554</v>
       </c>
@@ -7718,7 +7757,7 @@
       </c>
     </row>
     <row r="246" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A246" s="51"/>
+      <c r="A246" s="54"/>
       <c r="B246" t="s">
         <v>556</v>
       </c>
@@ -7759,7 +7798,7 @@
       </c>
     </row>
     <row r="247" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A247" s="51"/>
+      <c r="A247" s="54"/>
       <c r="B247" t="s">
         <v>560</v>
       </c>
@@ -7799,7 +7838,7 @@
       </c>
     </row>
     <row r="248" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A248" s="51"/>
+      <c r="A248" s="54"/>
       <c r="B248" t="s">
         <v>563</v>
       </c>
@@ -7840,7 +7879,7 @@
       </c>
     </row>
     <row r="249" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A249" s="51"/>
+      <c r="A249" s="54"/>
       <c r="B249" t="s">
         <v>586</v>
       </c>
@@ -7849,7 +7888,7 @@
       </c>
     </row>
     <row r="250" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A250" s="51"/>
+      <c r="A250" s="54"/>
       <c r="B250" t="s">
         <v>300</v>
       </c>
@@ -7859,7 +7898,7 @@
       </c>
     </row>
     <row r="251" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A251" s="51"/>
+      <c r="A251" s="54"/>
       <c r="B251" t="s">
         <v>585</v>
       </c>
@@ -7872,7 +7911,7 @@
       </c>
     </row>
     <row r="252" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A252" s="51"/>
+      <c r="A252" s="54"/>
       <c r="B252" t="s">
         <v>592</v>
       </c>
@@ -7903,7 +7942,7 @@
       </c>
     </row>
     <row r="253" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A253" s="51"/>
+      <c r="A253" s="54"/>
       <c r="B253" s="36" t="s">
         <v>591</v>
       </c>
@@ -7940,7 +7979,7 @@
       </c>
     </row>
     <row r="254" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A254" s="51"/>
+      <c r="A254" s="54"/>
       <c r="B254" t="s">
         <v>594</v>
       </c>
@@ -7950,7 +7989,7 @@
       </c>
     </row>
     <row r="255" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A255" s="51"/>
+      <c r="A255" s="54"/>
       <c r="B255" t="s">
         <v>595</v>
       </c>
@@ -7960,7 +7999,7 @@
       </c>
     </row>
     <row r="256" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A256" s="51"/>
+      <c r="A256" s="54"/>
       <c r="B256" t="s">
         <v>593</v>
       </c>
@@ -7970,7 +8009,7 @@
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A257" s="51"/>
+      <c r="A257" s="54"/>
       <c r="B257" t="s">
         <v>596</v>
       </c>
@@ -7980,7 +8019,7 @@
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A258" s="51"/>
+      <c r="A258" s="54"/>
       <c r="B258" t="s">
         <v>597</v>
       </c>
@@ -7990,7 +8029,7 @@
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A259" s="51"/>
+      <c r="A259" s="54"/>
       <c r="B259" t="s">
         <v>600</v>
       </c>
@@ -8000,7 +8039,7 @@
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A260" s="51"/>
+      <c r="A260" s="54"/>
       <c r="B260" t="s">
         <v>598</v>
       </c>
@@ -8010,7 +8049,7 @@
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A261" s="51"/>
+      <c r="A261" s="54"/>
       <c r="B261" t="s">
         <v>598</v>
       </c>
@@ -8020,7 +8059,7 @@
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A262" s="51"/>
+      <c r="A262" s="54"/>
       <c r="B262" t="s">
         <v>602</v>
       </c>
@@ -8030,7 +8069,7 @@
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A263" s="51"/>
+      <c r="A263" s="54"/>
       <c r="B263" t="s">
         <v>601</v>
       </c>
@@ -8040,7 +8079,7 @@
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A264" s="51"/>
+      <c r="A264" s="54"/>
       <c r="B264" t="s">
         <v>599</v>
       </c>
@@ -8050,7 +8089,7 @@
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A265" s="51"/>
+      <c r="A265" s="54"/>
       <c r="B265" t="s">
         <v>623</v>
       </c>
@@ -8059,7 +8098,7 @@
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A266" s="51"/>
+      <c r="A266" s="54"/>
       <c r="B266" t="s">
         <v>624</v>
       </c>
@@ -8069,7 +8108,7 @@
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A267" s="51"/>
+      <c r="A267" s="54"/>
       <c r="B267" t="s">
         <v>621</v>
       </c>
@@ -8082,7 +8121,7 @@
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A268" s="51"/>
+      <c r="A268" s="54"/>
       <c r="B268" t="s">
         <v>622</v>
       </c>
@@ -8095,7 +8134,7 @@
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A269" s="51"/>
+      <c r="A269" s="54"/>
       <c r="B269" t="s">
         <v>603</v>
       </c>
@@ -8110,7 +8149,7 @@
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A270" s="51"/>
+      <c r="A270" s="54"/>
       <c r="B270" s="43" t="s">
         <v>605</v>
       </c>
@@ -8123,45 +8162,45 @@
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A271" s="51"/>
+      <c r="A271" s="54"/>
       <c r="C271" s="34"/>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A272" s="51"/>
+      <c r="A272" s="54"/>
       <c r="C272" s="34"/>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A273" s="51"/>
+      <c r="A273" s="54"/>
       <c r="C273" s="34"/>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A274" s="51"/>
+      <c r="A274" s="54"/>
       <c r="C274" s="34"/>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A275" s="51"/>
+      <c r="A275" s="54"/>
       <c r="C275" s="34"/>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A276" s="51"/>
+      <c r="A276" s="54"/>
       <c r="C276" s="34"/>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A277" s="51"/>
+      <c r="A277" s="54"/>
       <c r="C277" s="34"/>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A278" s="51"/>
+      <c r="A278" s="54"/>
       <c r="C278" s="34"/>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A279" s="51"/>
+      <c r="A279" s="54"/>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" s="37"/>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A281" s="51" t="s">
+      <c r="A281" s="54" t="s">
         <v>608</v>
       </c>
       <c r="C281" t="s">
@@ -8173,7 +8212,7 @@
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A282" s="51"/>
+      <c r="A282" s="54"/>
       <c r="C282" t="s">
         <v>265</v>
       </c>
@@ -8183,7 +8222,7 @@
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A283" s="51"/>
+      <c r="A283" s="54"/>
       <c r="C283" t="s">
         <v>266</v>
       </c>
@@ -8193,7 +8232,7 @@
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A284" s="51"/>
+      <c r="A284" s="54"/>
       <c r="C284" t="s">
         <v>267</v>
       </c>
@@ -8203,7 +8242,7 @@
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A285" s="51"/>
+      <c r="A285" s="54"/>
       <c r="C285" t="s">
         <v>268</v>
       </c>
@@ -8213,7 +8252,7 @@
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A286" s="51"/>
+      <c r="A286" s="54"/>
       <c r="C286" t="s">
         <v>269</v>
       </c>
@@ -8223,7 +8262,7 @@
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A287" s="51"/>
+      <c r="A287" s="54"/>
       <c r="C287" t="s">
         <v>270</v>
       </c>
@@ -8233,7 +8272,7 @@
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A288" s="51"/>
+      <c r="A288" s="54"/>
       <c r="C288" t="s">
         <v>271</v>
       </c>
@@ -8243,7 +8282,7 @@
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A289" s="51"/>
+      <c r="A289" s="54"/>
       <c r="B289" t="s">
         <v>272</v>
       </c>
@@ -8252,7 +8291,7 @@
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A290" s="51"/>
+      <c r="A290" s="54"/>
       <c r="B290" t="s">
         <v>274</v>
       </c>
@@ -8262,7 +8301,7 @@
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A291" s="51"/>
+      <c r="A291" s="54"/>
       <c r="C291" t="s">
         <v>275</v>
       </c>
@@ -8272,10 +8311,10 @@
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A292" s="51"/>
+      <c r="A292" s="54"/>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A293" s="51"/>
+      <c r="A293" s="54"/>
       <c r="B293" t="s">
         <v>276</v>
       </c>
@@ -8285,7 +8324,7 @@
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A294" s="51"/>
+      <c r="A294" s="54"/>
       <c r="B294" t="s">
         <v>348</v>
       </c>
@@ -8295,7 +8334,7 @@
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A295" s="51"/>
+      <c r="A295" s="54"/>
       <c r="B295" t="s">
         <v>284</v>
       </c>
@@ -8305,7 +8344,7 @@
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A296" s="51"/>
+      <c r="A296" s="54"/>
       <c r="B296" t="s">
         <v>283</v>
       </c>
@@ -8314,10 +8353,10 @@
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A297" s="51"/>
+      <c r="A297" s="54"/>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A298" s="51"/>
+      <c r="A298" s="54"/>
       <c r="B298" t="s">
         <v>281</v>
       </c>
@@ -8327,7 +8366,7 @@
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A299" s="51"/>
+      <c r="A299" s="54"/>
       <c r="B299" t="s">
         <v>280</v>
       </c>
@@ -8339,7 +8378,7 @@
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A300" s="51"/>
+      <c r="A300" s="54"/>
       <c r="C300" t="s">
         <v>278</v>
       </c>
@@ -8349,7 +8388,7 @@
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A301" s="51"/>
+      <c r="A301" s="54"/>
       <c r="C301" t="s">
         <v>282</v>
       </c>
@@ -8359,10 +8398,10 @@
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A302" s="51"/>
+      <c r="A302" s="54"/>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A303" s="52" t="s">
+      <c r="A303" s="53" t="s">
         <v>607</v>
       </c>
       <c r="B303" t="s">
@@ -8374,7 +8413,7 @@
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A304" s="52"/>
+      <c r="A304" s="53"/>
       <c r="B304" t="s">
         <v>609</v>
       </c>
@@ -8383,7 +8422,7 @@
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A305" s="52"/>
+      <c r="A305" s="53"/>
       <c r="B305" t="s">
         <v>610</v>
       </c>
@@ -8392,7 +8431,7 @@
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A306" s="52"/>
+      <c r="A306" s="53"/>
       <c r="B306" t="s">
         <v>611</v>
       </c>
@@ -8402,7 +8441,7 @@
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A307" s="52"/>
+      <c r="A307" s="53"/>
       <c r="B307" t="s">
         <v>615</v>
       </c>
@@ -8412,7 +8451,7 @@
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A308" s="52"/>
+      <c r="A308" s="53"/>
       <c r="B308" t="s">
         <v>613</v>
       </c>
@@ -8422,7 +8461,7 @@
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A309" s="52"/>
+      <c r="A309" s="53"/>
       <c r="B309" t="s">
         <v>614</v>
       </c>
@@ -8432,7 +8471,7 @@
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A310" s="52"/>
+      <c r="A310" s="53"/>
       <c r="B310" t="s">
         <v>616</v>
       </c>
@@ -8442,7 +8481,7 @@
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A311" s="52"/>
+      <c r="A311" s="53"/>
       <c r="C311" t="s">
         <v>617</v>
       </c>
@@ -8451,7 +8490,7 @@
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A312" s="52"/>
+      <c r="A312" s="53"/>
       <c r="C312" t="s">
         <v>618</v>
       </c>
@@ -8461,7 +8500,7 @@
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A313" s="52"/>
+      <c r="A313" s="53"/>
       <c r="C313" t="s">
         <v>619</v>
       </c>
@@ -8471,7 +8510,7 @@
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A314" s="52"/>
+      <c r="A314" s="53"/>
       <c r="C314" t="s">
         <v>620</v>
       </c>
@@ -8481,10 +8520,10 @@
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A315" s="52"/>
+      <c r="A315" s="53"/>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A316" s="52" t="s">
+      <c r="A316" s="53" t="s">
         <v>584</v>
       </c>
       <c r="C316" t="s">
@@ -8495,7 +8534,7 @@
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A317" s="52"/>
+      <c r="A317" s="53"/>
       <c r="B317" t="s">
         <v>38</v>
       </c>
@@ -8505,7 +8544,7 @@
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A318" s="52"/>
+      <c r="A318" s="53"/>
       <c r="B318" t="s">
         <v>286</v>
       </c>
@@ -8517,7 +8556,7 @@
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A319" s="52"/>
+      <c r="A319" s="53"/>
       <c r="C319" t="s">
         <v>289</v>
       </c>
@@ -8527,7 +8566,7 @@
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A320" s="52"/>
+      <c r="A320" s="53"/>
       <c r="B320" t="s">
         <v>290</v>
       </c>
@@ -8540,7 +8579,7 @@
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A321" s="52"/>
+      <c r="A321" s="53"/>
       <c r="C321" t="s">
         <v>288</v>
       </c>
@@ -8549,7 +8588,7 @@
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A322" s="52"/>
+      <c r="A322" s="53"/>
       <c r="B322" t="s">
         <v>287</v>
       </c>
@@ -8558,7 +8597,7 @@
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A323" s="52"/>
+      <c r="A323" s="53"/>
       <c r="B323" t="s">
         <v>291</v>
       </c>
@@ -8570,7 +8609,7 @@
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A324" s="52"/>
+      <c r="A324" s="53"/>
       <c r="B324" t="s">
         <v>292</v>
       </c>
@@ -8583,7 +8622,7 @@
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A325" s="52"/>
+      <c r="A325" s="53"/>
       <c r="B325" t="s">
         <v>349</v>
       </c>
@@ -8600,7 +8639,7 @@
       <c r="E326" s="9"/>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A327" s="51" t="s">
+      <c r="A327" s="54" t="s">
         <v>303</v>
       </c>
       <c r="B327" t="s">
@@ -8615,7 +8654,7 @@
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A328" s="51"/>
+      <c r="A328" s="54"/>
       <c r="B328" t="s">
         <v>41</v>
       </c>
@@ -8628,7 +8667,7 @@
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A329" s="51"/>
+      <c r="A329" s="54"/>
       <c r="B329" t="s">
         <v>39</v>
       </c>
@@ -8637,7 +8676,7 @@
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A330" s="51"/>
+      <c r="A330" s="54"/>
       <c r="B330" t="s">
         <v>305</v>
       </c>
@@ -8649,7 +8688,7 @@
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A331" s="51"/>
+      <c r="A331" s="54"/>
       <c r="B331" t="s">
         <v>304</v>
       </c>
@@ -8659,7 +8698,7 @@
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A332" s="51"/>
+      <c r="A332" s="54"/>
       <c r="B332" t="s">
         <v>307</v>
       </c>
@@ -8672,7 +8711,7 @@
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A333" s="51"/>
+      <c r="A333" s="54"/>
       <c r="B333" t="s">
         <v>308</v>
       </c>
@@ -8685,7 +8724,7 @@
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A334" s="51"/>
+      <c r="A334" s="54"/>
       <c r="B334" t="s">
         <v>326</v>
       </c>
@@ -8697,7 +8736,7 @@
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A335" s="51"/>
+      <c r="A335" s="54"/>
       <c r="C335" t="s">
         <v>344</v>
       </c>
@@ -8707,7 +8746,7 @@
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A336" s="51"/>
+      <c r="A336" s="54"/>
       <c r="B336" t="s">
         <v>309</v>
       </c>
@@ -8716,7 +8755,7 @@
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A337" s="51"/>
+      <c r="A337" s="54"/>
       <c r="B337" t="s">
         <v>310</v>
       </c>
@@ -8725,7 +8764,7 @@
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A338" s="51"/>
+      <c r="A338" s="54"/>
       <c r="B338" t="s">
         <v>311</v>
       </c>
@@ -8740,7 +8779,7 @@
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A339" s="51"/>
+      <c r="A339" s="54"/>
       <c r="B339" t="s">
         <v>313</v>
       </c>
@@ -8753,7 +8792,7 @@
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A340" s="51"/>
+      <c r="A340" s="54"/>
       <c r="B340" t="s">
         <v>315</v>
       </c>
@@ -8768,7 +8807,7 @@
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A341" s="51"/>
+      <c r="A341" s="54"/>
       <c r="B341" t="s">
         <v>316</v>
       </c>
@@ -8780,7 +8819,7 @@
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A342" s="51"/>
+      <c r="A342" s="54"/>
       <c r="B342" t="s">
         <v>229</v>
       </c>
@@ -8796,7 +8835,7 @@
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A343" s="51"/>
+      <c r="A343" s="54"/>
       <c r="B343" t="s">
         <v>322</v>
       </c>
@@ -8812,7 +8851,7 @@
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A344" s="51"/>
+      <c r="A344" s="54"/>
       <c r="B344" t="s">
         <v>323</v>
       </c>
@@ -8828,7 +8867,7 @@
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A345" s="51"/>
+      <c r="A345" s="54"/>
       <c r="C345" t="s">
         <v>317</v>
       </c>
@@ -8841,7 +8880,7 @@
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A346" s="51"/>
+      <c r="A346" s="54"/>
       <c r="C346" t="s">
         <v>319</v>
       </c>
@@ -8853,7 +8892,7 @@
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A347" s="51"/>
+      <c r="A347" s="54"/>
       <c r="C347" t="s">
         <v>320</v>
       </c>
@@ -8866,7 +8905,7 @@
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A348" s="51"/>
+      <c r="A348" s="54"/>
       <c r="C348" t="s">
         <v>318</v>
       </c>
@@ -8876,7 +8915,7 @@
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A349" s="51"/>
+      <c r="A349" s="54"/>
       <c r="B349" t="s">
         <v>346</v>
       </c>
@@ -8892,7 +8931,7 @@
       </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A350" s="51"/>
+      <c r="A350" s="54"/>
       <c r="B350" t="s">
         <v>327</v>
       </c>
@@ -8905,7 +8944,7 @@
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A351" s="51"/>
+      <c r="A351" s="54"/>
       <c r="B351" t="s">
         <v>328</v>
       </c>
@@ -8918,7 +8957,7 @@
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A352" s="51"/>
+      <c r="A352" s="54"/>
       <c r="B352" t="s">
         <v>321</v>
       </c>
@@ -8931,7 +8970,7 @@
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A353" s="51"/>
+      <c r="A353" s="54"/>
       <c r="B353" t="s">
         <v>341</v>
       </c>
@@ -8944,7 +8983,7 @@
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A354" s="51"/>
+      <c r="A354" s="54"/>
       <c r="B354" t="s">
         <v>330</v>
       </c>
@@ -8956,7 +8995,7 @@
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A355" s="51"/>
+      <c r="A355" s="54"/>
       <c r="B355" t="s">
         <v>333</v>
       </c>
@@ -8968,7 +9007,7 @@
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A356" s="51"/>
+      <c r="A356" s="54"/>
       <c r="B356" t="s">
         <v>334</v>
       </c>
@@ -8983,7 +9022,7 @@
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A357" s="51"/>
+      <c r="A357" s="54"/>
       <c r="B357" t="s">
         <v>331</v>
       </c>
@@ -8999,7 +9038,7 @@
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A358" s="51"/>
+      <c r="A358" s="54"/>
       <c r="C358" t="s">
         <v>345</v>
       </c>
@@ -9012,7 +9051,7 @@
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A359" s="51"/>
+      <c r="A359" s="54"/>
       <c r="B359" t="s">
         <v>336</v>
       </c>
@@ -9024,7 +9063,7 @@
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A360" s="51"/>
+      <c r="A360" s="54"/>
       <c r="C360" t="s">
         <v>338</v>
       </c>
@@ -9034,7 +9073,7 @@
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A361" s="51"/>
+      <c r="A361" s="54"/>
       <c r="C361" t="s">
         <v>337</v>
       </c>
@@ -9044,7 +9083,7 @@
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A362" s="51"/>
+      <c r="A362" s="54"/>
       <c r="B362" t="s">
         <v>339</v>
       </c>
@@ -9063,7 +9102,7 @@
       <c r="A363" s="38"/>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A364" s="52" t="s">
+      <c r="A364" s="53" t="s">
         <v>700</v>
       </c>
       <c r="B364" t="s">
@@ -9078,7 +9117,7 @@
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A365" s="52"/>
+      <c r="A365" s="53"/>
       <c r="C365" t="s">
         <v>701</v>
       </c>
@@ -9090,7 +9129,7 @@
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A366" s="52"/>
+      <c r="A366" s="53"/>
       <c r="C366" t="s">
         <v>703</v>
       </c>
@@ -9102,7 +9141,7 @@
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A367" s="52"/>
+      <c r="A367" s="53"/>
       <c r="C367" t="s">
         <v>704</v>
       </c>
@@ -9114,7 +9153,7 @@
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A368" s="52"/>
+      <c r="A368" s="53"/>
       <c r="B368" t="s">
         <v>706</v>
       </c>
@@ -9128,7 +9167,7 @@
       <c r="E368" s="40"/>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A369" s="52"/>
+      <c r="A369" s="53"/>
       <c r="B369" t="s">
         <v>708</v>
       </c>
@@ -9142,7 +9181,7 @@
       <c r="E369" s="40"/>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A370" s="52"/>
+      <c r="A370" s="53"/>
       <c r="B370" t="s">
         <v>710</v>
       </c>
@@ -9155,7 +9194,7 @@
       <c r="E370" s="39"/>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A371" s="52"/>
+      <c r="A371" s="53"/>
       <c r="C371" t="s">
         <v>705</v>
       </c>
@@ -9166,7 +9205,7 @@
       <c r="E371" s="39"/>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A372" s="52"/>
+      <c r="A372" s="53"/>
       <c r="B372" t="s">
         <v>713</v>
       </c>
@@ -9180,7 +9219,7 @@
       <c r="E372" s="39"/>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A373" s="52"/>
+      <c r="A373" s="53"/>
       <c r="C373" t="s">
         <v>714</v>
       </c>
@@ -9190,7 +9229,7 @@
       <c r="E373" s="39"/>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A374" s="52"/>
+      <c r="A374" s="53"/>
       <c r="C374" t="s">
         <v>715</v>
       </c>
@@ -9201,7 +9240,7 @@
       <c r="E374" s="39"/>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A375" s="52"/>
+      <c r="A375" s="53"/>
       <c r="C375" t="s">
         <v>716</v>
       </c>
@@ -9211,7 +9250,7 @@
       <c r="E375" s="39"/>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A376" s="52"/>
+      <c r="A376" s="53"/>
       <c r="C376" t="s">
         <v>717</v>
       </c>
@@ -9221,21 +9260,21 @@
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A377" s="52" t="s">
+      <c r="A377" s="53" t="s">
         <v>718</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A378" s="52"/>
+      <c r="A378" s="53"/>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A379" s="52"/>
+      <c r="A379" s="53"/>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A380" s="52"/>
+      <c r="A380" s="53"/>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A381" s="51" t="s">
+      <c r="A381" s="54" t="s">
         <v>350</v>
       </c>
       <c r="B381" t="s">
@@ -9250,7 +9289,7 @@
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A382" s="51"/>
+      <c r="A382" s="54"/>
       <c r="B382" t="s">
         <v>48</v>
       </c>
@@ -9260,7 +9299,7 @@
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A383" s="51"/>
+      <c r="A383" s="54"/>
       <c r="B383" t="s">
         <v>240</v>
       </c>
@@ -9270,7 +9309,7 @@
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A384" s="51"/>
+      <c r="A384" s="54"/>
       <c r="C384" t="s">
         <v>354</v>
       </c>
@@ -9279,7 +9318,7 @@
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A385" s="51"/>
+      <c r="A385" s="54"/>
       <c r="C385" t="s">
         <v>356</v>
       </c>
@@ -9289,7 +9328,7 @@
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A386" s="51"/>
+      <c r="A386" s="54"/>
       <c r="B386" t="s">
         <v>351</v>
       </c>
@@ -9301,7 +9340,7 @@
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A387" s="51"/>
+      <c r="A387" s="54"/>
       <c r="B387" t="s">
         <v>353</v>
       </c>
@@ -9314,7 +9353,7 @@
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A388" s="51"/>
+      <c r="A388" s="54"/>
       <c r="B388" t="s">
         <v>403</v>
       </c>
@@ -9327,7 +9366,7 @@
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A389" s="51"/>
+      <c r="A389" s="54"/>
       <c r="B389" t="s">
         <v>358</v>
       </c>
@@ -9340,7 +9379,7 @@
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A390" s="51"/>
+      <c r="A390" s="54"/>
       <c r="B390" t="s">
         <v>359</v>
       </c>
@@ -9353,7 +9392,7 @@
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A391" s="51"/>
+      <c r="A391" s="54"/>
       <c r="B391" t="s">
         <v>360</v>
       </c>
@@ -9366,7 +9405,7 @@
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A392" s="51"/>
+      <c r="A392" s="54"/>
       <c r="C392" t="s">
         <v>362</v>
       </c>
@@ -9376,7 +9415,7 @@
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A393" s="51"/>
+      <c r="A393" s="54"/>
       <c r="B393" t="s">
         <v>393</v>
       </c>
@@ -9388,7 +9427,7 @@
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A394" s="51"/>
+      <c r="A394" s="54"/>
       <c r="B394" t="s">
         <v>367</v>
       </c>
@@ -9400,7 +9439,7 @@
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A395" s="51"/>
+      <c r="A395" s="54"/>
       <c r="B395" t="s">
         <v>368</v>
       </c>
@@ -9412,7 +9451,7 @@
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A396" s="51"/>
+      <c r="A396" s="54"/>
       <c r="B396" t="s">
         <v>371</v>
       </c>
@@ -9427,7 +9466,7 @@
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A397" s="51"/>
+      <c r="A397" s="54"/>
       <c r="B397" t="s">
         <v>372</v>
       </c>
@@ -9442,7 +9481,7 @@
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A398" s="51"/>
+      <c r="A398" s="54"/>
       <c r="B398" t="s">
         <v>374</v>
       </c>
@@ -9458,7 +9497,7 @@
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A399" s="51"/>
+      <c r="A399" s="54"/>
       <c r="B399" s="27" t="s">
         <v>378</v>
       </c>
@@ -9473,7 +9512,7 @@
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A400" s="51"/>
+      <c r="A400" s="54"/>
       <c r="C400" t="s">
         <v>381</v>
       </c>
@@ -9483,7 +9522,7 @@
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A401" s="51"/>
+      <c r="A401" s="54"/>
       <c r="B401" t="s">
         <v>396</v>
       </c>
@@ -9496,7 +9535,7 @@
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A402" s="51"/>
+      <c r="A402" s="54"/>
       <c r="B402" t="s">
         <v>397</v>
       </c>
@@ -9506,7 +9545,7 @@
       </c>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A403" s="51"/>
+      <c r="A403" s="54"/>
       <c r="B403" t="s">
         <v>363</v>
       </c>
@@ -9515,7 +9554,7 @@
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A404" s="51"/>
+      <c r="A404" s="54"/>
       <c r="B404" t="s">
         <v>365</v>
       </c>
@@ -9525,7 +9564,7 @@
       </c>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A405" s="51"/>
+      <c r="A405" s="54"/>
       <c r="B405" t="s">
         <v>364</v>
       </c>
@@ -9537,7 +9576,7 @@
       </c>
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A406" s="51"/>
+      <c r="A406" s="54"/>
       <c r="B406" t="s">
         <v>398</v>
       </c>
@@ -9550,7 +9589,7 @@
       </c>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A407" s="51"/>
+      <c r="A407" s="54"/>
       <c r="C407" t="s">
         <v>414</v>
       </c>
@@ -9559,7 +9598,7 @@
       </c>
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A408" s="51"/>
+      <c r="A408" s="54"/>
       <c r="B408" t="s">
         <v>415</v>
       </c>
@@ -9569,7 +9608,7 @@
       </c>
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A409" s="51"/>
+      <c r="A409" s="54"/>
       <c r="B409" t="s">
         <v>416</v>
       </c>
@@ -9579,7 +9618,7 @@
       </c>
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A410" s="51"/>
+      <c r="A410" s="54"/>
       <c r="B410" t="s">
         <v>417</v>
       </c>
@@ -9589,7 +9628,7 @@
       </c>
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A411" s="51"/>
+      <c r="A411" s="54"/>
       <c r="B411" t="s">
         <v>418</v>
       </c>
@@ -9599,7 +9638,7 @@
       </c>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A412" s="51"/>
+      <c r="A412" s="54"/>
       <c r="B412" t="s">
         <v>412</v>
       </c>
@@ -9612,7 +9651,7 @@
       </c>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A413" s="51"/>
+      <c r="A413" s="54"/>
       <c r="B413" t="s">
         <v>419</v>
       </c>
@@ -9625,7 +9664,7 @@
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A414" s="51"/>
+      <c r="A414" s="54"/>
       <c r="C414" t="s">
         <v>420</v>
       </c>
@@ -9635,7 +9674,7 @@
       </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A415" s="51"/>
+      <c r="A415" s="54"/>
       <c r="C415" t="s">
         <v>421</v>
       </c>
@@ -9648,7 +9687,7 @@
       </c>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A416" s="51"/>
+      <c r="A416" s="54"/>
       <c r="B416" t="s">
         <v>399</v>
       </c>
@@ -9658,7 +9697,7 @@
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A417" s="51"/>
+      <c r="A417" s="54"/>
       <c r="C417" t="s">
         <v>388</v>
       </c>
@@ -9668,7 +9707,7 @@
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A418" s="51"/>
+      <c r="A418" s="54"/>
       <c r="C418" t="s">
         <v>400</v>
       </c>
@@ -9678,7 +9717,7 @@
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A419" s="51"/>
+      <c r="A419" s="54"/>
       <c r="B419" t="s">
         <v>386</v>
       </c>
@@ -9691,7 +9730,7 @@
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A420" s="51"/>
+      <c r="A420" s="54"/>
       <c r="C420" t="s">
         <v>401</v>
       </c>
@@ -9701,7 +9740,7 @@
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A421" s="51"/>
+      <c r="A421" s="54"/>
       <c r="C421" t="s">
         <v>402</v>
       </c>
@@ -9711,7 +9750,7 @@
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A422" s="51"/>
+      <c r="A422" s="54"/>
       <c r="B422" t="s">
         <v>387</v>
       </c>
@@ -9721,7 +9760,7 @@
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A423" s="51"/>
+      <c r="A423" s="54"/>
       <c r="C423" t="s">
         <v>392</v>
       </c>
@@ -9731,7 +9770,7 @@
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A424" s="51"/>
+      <c r="A424" s="54"/>
       <c r="C424" t="s">
         <v>389</v>
       </c>
@@ -9741,10 +9780,10 @@
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A425" s="51"/>
+      <c r="A425" s="54"/>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A426" s="51"/>
+      <c r="A426" s="54"/>
       <c r="C426" t="s">
         <v>390</v>
       </c>
@@ -9757,7 +9796,7 @@
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A427" s="51"/>
+      <c r="A427" s="54"/>
       <c r="C427" t="s">
         <v>390</v>
       </c>
@@ -9770,7 +9809,7 @@
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A428" s="51"/>
+      <c r="A428" s="54"/>
       <c r="C428" t="s">
         <v>391</v>
       </c>
@@ -9780,7 +9819,7 @@
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A429" s="51"/>
+      <c r="A429" s="54"/>
       <c r="B429" t="s">
         <v>405</v>
       </c>
@@ -9790,7 +9829,7 @@
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A430" s="51"/>
+      <c r="A430" s="54"/>
       <c r="B430" t="s">
         <v>406</v>
       </c>
@@ -9800,13 +9839,13 @@
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A431" s="51"/>
+      <c r="A431" s="54"/>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A432" s="51"/>
+      <c r="A432" s="54"/>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A433" s="51"/>
+      <c r="A433" s="54"/>
       <c r="B433" t="s">
         <v>408</v>
       </c>
@@ -9822,7 +9861,7 @@
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A434" s="51"/>
+      <c r="A434" s="54"/>
       <c r="B434" t="s">
         <v>409</v>
       </c>
@@ -9835,7 +9874,7 @@
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A435" s="51"/>
+      <c r="A435" s="54"/>
       <c r="B435" t="s">
         <v>411</v>
       </c>
@@ -9845,7 +9884,7 @@
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A436" s="51"/>
+      <c r="A436" s="54"/>
       <c r="B436" t="s">
         <v>422</v>
       </c>
@@ -9858,7 +9897,7 @@
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A437" s="51"/>
+      <c r="A437" s="54"/>
       <c r="B437" t="s">
         <v>424</v>
       </c>
@@ -9868,7 +9907,7 @@
       </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A438" s="51"/>
+      <c r="A438" s="54"/>
       <c r="B438" t="s">
         <v>425</v>
       </c>
@@ -9878,7 +9917,7 @@
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A439" s="51"/>
+      <c r="A439" s="54"/>
       <c r="B439" t="s">
         <v>426</v>
       </c>
@@ -9888,7 +9927,7 @@
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A440" s="51"/>
+      <c r="A440" s="54"/>
       <c r="B440" t="s">
         <v>427</v>
       </c>
@@ -9898,7 +9937,7 @@
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A441" s="51"/>
+      <c r="A441" s="54"/>
       <c r="C441" t="s">
         <v>428</v>
       </c>
@@ -9908,7 +9947,7 @@
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A442" s="51"/>
+      <c r="A442" s="54"/>
       <c r="B442" t="s">
         <v>429</v>
       </c>
@@ -9918,7 +9957,7 @@
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A443" s="51"/>
+      <c r="A443" s="54"/>
       <c r="B443" t="s">
         <v>430</v>
       </c>
@@ -9928,7 +9967,7 @@
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A444" s="51"/>
+      <c r="A444" s="54"/>
       <c r="B444" t="s">
         <v>431</v>
       </c>
@@ -9938,7 +9977,7 @@
       </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A445" s="51"/>
+      <c r="A445" s="54"/>
       <c r="B445" t="s">
         <v>429</v>
       </c>
@@ -9951,7 +9990,7 @@
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A446" s="51"/>
+      <c r="A446" s="54"/>
       <c r="B446" t="s">
         <v>430</v>
       </c>
@@ -9964,7 +10003,7 @@
       </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A447" s="51"/>
+      <c r="A447" s="54"/>
       <c r="B447" t="s">
         <v>431</v>
       </c>
@@ -10010,7 +10049,7 @@
     </row>
     <row r="451" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A451" s="49"/>
-      <c r="B451" s="59" t="s">
+      <c r="B451" s="52" t="s">
         <v>830</v>
       </c>
       <c r="C451" t="s">
@@ -10026,7 +10065,7 @@
     </row>
     <row r="452" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A452" s="50"/>
-      <c r="B452" s="59" t="s">
+      <c r="B452" s="52" t="s">
         <v>832</v>
       </c>
       <c r="C452" t="s">
@@ -10042,7 +10081,7 @@
     </row>
     <row r="453" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A453" s="49"/>
-      <c r="B453" s="59" t="s">
+      <c r="B453" s="52" t="s">
         <v>817</v>
       </c>
       <c r="C453" t="s">
@@ -10058,7 +10097,7 @@
     </row>
     <row r="454" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A454" s="49"/>
-      <c r="B454" s="59" t="s">
+      <c r="B454" s="52" t="s">
         <v>819</v>
       </c>
       <c r="C454" t="s">
@@ -10070,7 +10109,7 @@
     </row>
     <row r="455" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A455" s="50"/>
-      <c r="B455" s="59" t="s">
+      <c r="B455" s="52" t="s">
         <v>844</v>
       </c>
       <c r="D455" s="8">
@@ -10378,2510 +10417,4523 @@
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A478" s="51"/>
       <c r="B478" t="s">
-        <v>48</v>
-      </c>
-      <c r="C478" t="s">
-        <v>47</v>
-      </c>
-      <c r="D478">
-        <f>D3</f>
-        <v>16000</v>
-      </c>
+        <v>866</v>
+      </c>
+      <c r="C478">
+        <f xml:space="preserve"> (1/D453)/2</f>
+        <v>3.1250000000000001E-5</v>
+      </c>
+      <c r="E478" s="9"/>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A479" s="51" t="s">
-        <v>451</v>
-      </c>
+      <c r="A479" s="51"/>
       <c r="B479" t="s">
-        <v>41</v>
+        <v>867</v>
       </c>
       <c r="C479" t="s">
-        <v>434</v>
+        <v>868</v>
       </c>
       <c r="D479">
-        <f>D105</f>
-        <v>22.598870056497173</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E479" s="9"/>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" s="51"/>
       <c r="B480" t="s">
+        <v>713</v>
+      </c>
+      <c r="C480" t="s">
+        <v>869</v>
+      </c>
+      <c r="D480">
+        <f>C478/D479</f>
+        <v>3.1250000000000003E-7</v>
+      </c>
+      <c r="E480" s="9"/>
+    </row>
+    <row r="481" spans="1:102" x14ac:dyDescent="0.25">
+      <c r="A481" s="51"/>
+      <c r="B481" t="s">
+        <v>872</v>
+      </c>
+      <c r="C481">
+        <f>D451</f>
+        <v>40</v>
+      </c>
+      <c r="D481">
+        <f>D451</f>
+        <v>40</v>
+      </c>
+      <c r="E481" s="9">
+        <f>D481</f>
+        <v>40</v>
+      </c>
+      <c r="F481">
+        <f>E481</f>
+        <v>40</v>
+      </c>
+      <c r="G481">
+        <f t="shared" ref="G481:BR481" si="20">F481</f>
+        <v>40</v>
+      </c>
+      <c r="H481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="I481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="J481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="K481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="L481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="M481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="N481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="O481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="P481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="Q481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="R481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="S481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="T481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="U481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="V481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="W481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="X481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="Y481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="Z481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AA481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AB481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AC481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AD481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AE481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AF481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AG481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AH481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AI481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AJ481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AK481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AL481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AM481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AN481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AO481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AP481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AQ481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AR481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AS481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AT481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AU481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AV481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AW481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AX481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AY481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AZ481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="BA481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="BB481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="BC481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="BD481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="BE481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="BF481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="BG481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="BH481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="BI481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="BJ481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="BK481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="BL481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="BM481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="BN481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="BO481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="BP481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="BQ481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="BR481">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="BS481">
+        <f t="shared" ref="BS481:CX481" si="21">BR481</f>
+        <v>40</v>
+      </c>
+      <c r="BT481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="BU481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="BV481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="BW481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="BX481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="BY481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="BZ481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CA481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CB481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CC481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CD481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CE481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CF481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CG481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CH481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CI481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CJ481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CK481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CL481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CM481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CN481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CO481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CP481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CQ481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CR481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CS481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CT481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CU481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CV481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CW481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="CX481">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="482" spans="1:102" x14ac:dyDescent="0.25">
+      <c r="A482" s="51"/>
+      <c r="B482" t="s">
+        <v>870</v>
+      </c>
+      <c r="C482">
+        <v>1</v>
+      </c>
+      <c r="D482">
+        <v>2</v>
+      </c>
+      <c r="E482" s="9">
+        <v>3</v>
+      </c>
+      <c r="F482">
+        <v>4</v>
+      </c>
+      <c r="G482" s="9">
+        <v>5</v>
+      </c>
+      <c r="H482">
+        <v>6</v>
+      </c>
+      <c r="I482" s="9">
+        <v>7</v>
+      </c>
+      <c r="J482">
+        <v>8</v>
+      </c>
+      <c r="K482" s="9">
+        <v>9</v>
+      </c>
+      <c r="L482">
+        <v>10</v>
+      </c>
+      <c r="M482" s="9">
+        <v>11</v>
+      </c>
+      <c r="N482">
+        <v>12</v>
+      </c>
+      <c r="O482" s="9">
+        <v>13</v>
+      </c>
+      <c r="P482">
+        <v>14</v>
+      </c>
+      <c r="Q482" s="9">
+        <v>15</v>
+      </c>
+      <c r="R482">
+        <v>16</v>
+      </c>
+      <c r="S482" s="9">
+        <v>17</v>
+      </c>
+      <c r="T482">
+        <v>18</v>
+      </c>
+      <c r="U482" s="9">
+        <v>19</v>
+      </c>
+      <c r="V482">
+        <v>20</v>
+      </c>
+      <c r="W482" s="9">
+        <v>21</v>
+      </c>
+      <c r="X482">
+        <v>22</v>
+      </c>
+      <c r="Y482" s="9">
+        <v>23</v>
+      </c>
+      <c r="Z482">
+        <v>24</v>
+      </c>
+      <c r="AA482" s="9">
+        <v>25</v>
+      </c>
+      <c r="AB482">
+        <v>26</v>
+      </c>
+      <c r="AC482" s="9">
+        <v>27</v>
+      </c>
+      <c r="AD482">
+        <v>28</v>
+      </c>
+      <c r="AE482" s="9">
+        <v>29</v>
+      </c>
+      <c r="AF482">
+        <v>30</v>
+      </c>
+      <c r="AG482" s="9">
+        <v>31</v>
+      </c>
+      <c r="AH482">
+        <v>32</v>
+      </c>
+      <c r="AI482" s="9">
+        <v>33</v>
+      </c>
+      <c r="AJ482">
+        <v>34</v>
+      </c>
+      <c r="AK482" s="9">
+        <v>35</v>
+      </c>
+      <c r="AL482">
+        <v>36</v>
+      </c>
+      <c r="AM482" s="9">
+        <v>37</v>
+      </c>
+      <c r="AN482">
+        <v>38</v>
+      </c>
+      <c r="AO482" s="9">
         <v>39</v>
       </c>
-      <c r="C480" t="s">
+      <c r="AP482">
+        <v>40</v>
+      </c>
+      <c r="AQ482" s="9">
+        <v>41</v>
+      </c>
+      <c r="AR482">
+        <v>42</v>
+      </c>
+      <c r="AS482" s="9">
+        <v>43</v>
+      </c>
+      <c r="AT482">
+        <v>44</v>
+      </c>
+      <c r="AU482" s="9">
+        <v>45</v>
+      </c>
+      <c r="AV482">
+        <v>46</v>
+      </c>
+      <c r="AW482" s="9">
+        <v>47</v>
+      </c>
+      <c r="AX482">
+        <v>48</v>
+      </c>
+      <c r="AY482" s="9">
+        <v>49</v>
+      </c>
+      <c r="AZ482">
+        <v>50</v>
+      </c>
+      <c r="BA482" s="9">
+        <v>51</v>
+      </c>
+      <c r="BB482">
+        <v>52</v>
+      </c>
+      <c r="BC482" s="9">
+        <v>53</v>
+      </c>
+      <c r="BD482">
+        <v>54</v>
+      </c>
+      <c r="BE482" s="9">
+        <v>55</v>
+      </c>
+      <c r="BF482">
+        <v>56</v>
+      </c>
+      <c r="BG482" s="9">
+        <v>57</v>
+      </c>
+      <c r="BH482">
+        <v>58</v>
+      </c>
+      <c r="BI482" s="9">
+        <v>59</v>
+      </c>
+      <c r="BJ482">
+        <v>60</v>
+      </c>
+      <c r="BK482" s="9">
+        <v>61</v>
+      </c>
+      <c r="BL482">
+        <v>62</v>
+      </c>
+      <c r="BM482" s="9">
+        <v>63</v>
+      </c>
+      <c r="BN482">
+        <v>64</v>
+      </c>
+      <c r="BO482" s="9">
+        <v>65</v>
+      </c>
+      <c r="BP482">
+        <v>66</v>
+      </c>
+      <c r="BQ482" s="9">
+        <v>67</v>
+      </c>
+      <c r="BR482">
+        <v>68</v>
+      </c>
+      <c r="BS482" s="9">
+        <v>69</v>
+      </c>
+      <c r="BT482">
+        <v>70</v>
+      </c>
+      <c r="BU482" s="9">
+        <v>71</v>
+      </c>
+      <c r="BV482">
+        <v>72</v>
+      </c>
+      <c r="BW482" s="9">
+        <v>73</v>
+      </c>
+      <c r="BX482">
+        <v>74</v>
+      </c>
+      <c r="BY482" s="9">
+        <v>75</v>
+      </c>
+      <c r="BZ482">
+        <v>76</v>
+      </c>
+      <c r="CA482" s="9">
+        <v>77</v>
+      </c>
+      <c r="CB482">
+        <v>78</v>
+      </c>
+      <c r="CC482" s="9">
+        <v>79</v>
+      </c>
+      <c r="CD482">
+        <v>80</v>
+      </c>
+      <c r="CE482" s="9">
+        <v>81</v>
+      </c>
+      <c r="CF482">
+        <v>82</v>
+      </c>
+      <c r="CG482" s="9">
+        <v>83</v>
+      </c>
+      <c r="CH482">
+        <v>84</v>
+      </c>
+      <c r="CI482" s="9">
+        <v>85</v>
+      </c>
+      <c r="CJ482">
+        <v>86</v>
+      </c>
+      <c r="CK482" s="9">
+        <v>87</v>
+      </c>
+      <c r="CL482">
+        <v>88</v>
+      </c>
+      <c r="CM482" s="9">
+        <v>89</v>
+      </c>
+      <c r="CN482">
+        <v>90</v>
+      </c>
+      <c r="CO482" s="9">
+        <v>91</v>
+      </c>
+      <c r="CP482">
+        <v>92</v>
+      </c>
+      <c r="CQ482" s="9">
+        <v>93</v>
+      </c>
+      <c r="CR482">
+        <v>94</v>
+      </c>
+      <c r="CS482" s="9">
+        <v>95</v>
+      </c>
+      <c r="CT482">
+        <v>96</v>
+      </c>
+      <c r="CU482" s="9">
+        <v>97</v>
+      </c>
+      <c r="CV482">
+        <v>98</v>
+      </c>
+      <c r="CW482" s="9">
+        <v>99</v>
+      </c>
+      <c r="CX482">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="483" spans="1:102" x14ac:dyDescent="0.25">
+      <c r="A483" s="51"/>
+      <c r="B483" t="s">
+        <v>871</v>
+      </c>
+      <c r="C483">
+        <f>(C482/50)*C481</f>
+        <v>0.8</v>
+      </c>
+      <c r="D483">
+        <f>(D482/50)*D481</f>
+        <v>1.6</v>
+      </c>
+      <c r="E483">
+        <f t="shared" ref="E483:AZ483" si="22">(E482/50)*E481</f>
+        <v>2.4</v>
+      </c>
+      <c r="F483">
+        <f t="shared" si="22"/>
+        <v>3.2</v>
+      </c>
+      <c r="G483">
+        <f t="shared" si="22"/>
+        <v>4</v>
+      </c>
+      <c r="H483">
+        <f t="shared" si="22"/>
+        <v>4.8</v>
+      </c>
+      <c r="I483">
+        <f t="shared" si="22"/>
+        <v>5.6000000000000005</v>
+      </c>
+      <c r="J483">
+        <f t="shared" si="22"/>
+        <v>6.4</v>
+      </c>
+      <c r="K483">
+        <f t="shared" si="22"/>
+        <v>7.1999999999999993</v>
+      </c>
+      <c r="L483">
+        <f t="shared" si="22"/>
+        <v>8</v>
+      </c>
+      <c r="M483">
+        <f t="shared" si="22"/>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="N483">
+        <f t="shared" si="22"/>
+        <v>9.6</v>
+      </c>
+      <c r="O483">
+        <f t="shared" si="22"/>
+        <v>10.4</v>
+      </c>
+      <c r="P483">
+        <f t="shared" si="22"/>
+        <v>11.200000000000001</v>
+      </c>
+      <c r="Q483">
+        <f t="shared" si="22"/>
+        <v>12</v>
+      </c>
+      <c r="R483">
+        <f t="shared" si="22"/>
+        <v>12.8</v>
+      </c>
+      <c r="S483">
+        <f t="shared" si="22"/>
+        <v>13.600000000000001</v>
+      </c>
+      <c r="T483">
+        <f t="shared" si="22"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="U483">
+        <f t="shared" si="22"/>
+        <v>15.2</v>
+      </c>
+      <c r="V483">
+        <f t="shared" si="22"/>
+        <v>16</v>
+      </c>
+      <c r="W483">
+        <f t="shared" si="22"/>
+        <v>16.8</v>
+      </c>
+      <c r="X483">
+        <f t="shared" si="22"/>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="Y483">
+        <f t="shared" si="22"/>
+        <v>18.400000000000002</v>
+      </c>
+      <c r="Z483">
+        <f t="shared" si="22"/>
+        <v>19.2</v>
+      </c>
+      <c r="AA483">
+        <f t="shared" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="AB483">
+        <f t="shared" si="22"/>
+        <v>20.8</v>
+      </c>
+      <c r="AC483">
+        <f t="shared" si="22"/>
+        <v>21.6</v>
+      </c>
+      <c r="AD483">
+        <f t="shared" si="22"/>
+        <v>22.400000000000002</v>
+      </c>
+      <c r="AE483">
+        <f t="shared" si="22"/>
+        <v>23.2</v>
+      </c>
+      <c r="AF483">
+        <f t="shared" si="22"/>
+        <v>24</v>
+      </c>
+      <c r="AG483">
+        <f t="shared" si="22"/>
+        <v>24.8</v>
+      </c>
+      <c r="AH483">
+        <f t="shared" si="22"/>
+        <v>25.6</v>
+      </c>
+      <c r="AI483">
+        <f t="shared" si="22"/>
+        <v>26.400000000000002</v>
+      </c>
+      <c r="AJ483">
+        <f t="shared" si="22"/>
+        <v>27.200000000000003</v>
+      </c>
+      <c r="AK483">
+        <f t="shared" si="22"/>
+        <v>28</v>
+      </c>
+      <c r="AL483">
+        <f t="shared" si="22"/>
+        <v>28.799999999999997</v>
+      </c>
+      <c r="AM483">
+        <f t="shared" si="22"/>
+        <v>29.6</v>
+      </c>
+      <c r="AN483">
+        <f t="shared" si="22"/>
+        <v>30.4</v>
+      </c>
+      <c r="AO483">
+        <f t="shared" si="22"/>
+        <v>31.200000000000003</v>
+      </c>
+      <c r="AP483">
+        <f t="shared" si="22"/>
+        <v>32</v>
+      </c>
+      <c r="AQ483">
+        <f t="shared" si="22"/>
+        <v>32.799999999999997</v>
+      </c>
+      <c r="AR483">
+        <f t="shared" si="22"/>
+        <v>33.6</v>
+      </c>
+      <c r="AS483">
+        <f t="shared" si="22"/>
+        <v>34.4</v>
+      </c>
+      <c r="AT483">
+        <f t="shared" si="22"/>
+        <v>35.200000000000003</v>
+      </c>
+      <c r="AU483">
+        <f t="shared" si="22"/>
+        <v>36</v>
+      </c>
+      <c r="AV483">
+        <f t="shared" si="22"/>
+        <v>36.800000000000004</v>
+      </c>
+      <c r="AW483">
+        <f t="shared" si="22"/>
+        <v>37.599999999999994</v>
+      </c>
+      <c r="AX483">
+        <f t="shared" si="22"/>
+        <v>38.4</v>
+      </c>
+      <c r="AY483">
+        <f t="shared" si="22"/>
+        <v>39.200000000000003</v>
+      </c>
+      <c r="AZ483">
+        <f t="shared" si="22"/>
+        <v>40</v>
+      </c>
+      <c r="BA483">
+        <f>(((100-BA482)/50)*BA481)</f>
+        <v>39.200000000000003</v>
+      </c>
+      <c r="BB483">
+        <f t="shared" ref="BB483:BD483" si="23">(((100-BB482)/50)*BB481)</f>
+        <v>38.4</v>
+      </c>
+      <c r="BC483">
+        <f t="shared" si="23"/>
+        <v>37.599999999999994</v>
+      </c>
+      <c r="BD483">
+        <f t="shared" si="23"/>
+        <v>36.800000000000004</v>
+      </c>
+      <c r="BE483">
+        <f t="shared" ref="BE483" si="24">(((100-BE482)/50)*BE481)</f>
+        <v>36</v>
+      </c>
+      <c r="BF483">
+        <f t="shared" ref="BF483:BG483" si="25">(((100-BF482)/50)*BF481)</f>
+        <v>35.200000000000003</v>
+      </c>
+      <c r="BG483">
+        <f t="shared" si="25"/>
+        <v>34.4</v>
+      </c>
+      <c r="BH483">
+        <f t="shared" ref="BH483" si="26">(((100-BH482)/50)*BH481)</f>
+        <v>33.6</v>
+      </c>
+      <c r="BI483">
+        <f t="shared" ref="BI483:BJ483" si="27">(((100-BI482)/50)*BI481)</f>
+        <v>32.799999999999997</v>
+      </c>
+      <c r="BJ483">
+        <f t="shared" si="27"/>
+        <v>32</v>
+      </c>
+      <c r="BK483">
+        <f t="shared" ref="BK483" si="28">(((100-BK482)/50)*BK481)</f>
+        <v>31.200000000000003</v>
+      </c>
+      <c r="BL483">
+        <f t="shared" ref="BL483:BM483" si="29">(((100-BL482)/50)*BL481)</f>
+        <v>30.4</v>
+      </c>
+      <c r="BM483">
+        <f t="shared" si="29"/>
+        <v>29.6</v>
+      </c>
+      <c r="BN483">
+        <f t="shared" ref="BN483" si="30">(((100-BN482)/50)*BN481)</f>
+        <v>28.799999999999997</v>
+      </c>
+      <c r="BO483">
+        <f t="shared" ref="BO483:BP483" si="31">(((100-BO482)/50)*BO481)</f>
+        <v>28</v>
+      </c>
+      <c r="BP483">
+        <f t="shared" si="31"/>
+        <v>27.200000000000003</v>
+      </c>
+      <c r="BQ483">
+        <f t="shared" ref="BQ483" si="32">(((100-BQ482)/50)*BQ481)</f>
+        <v>26.400000000000002</v>
+      </c>
+      <c r="BR483">
+        <f t="shared" ref="BR483:BS483" si="33">(((100-BR482)/50)*BR481)</f>
+        <v>25.6</v>
+      </c>
+      <c r="BS483">
+        <f t="shared" si="33"/>
+        <v>24.8</v>
+      </c>
+      <c r="BT483">
+        <f t="shared" ref="BT483" si="34">(((100-BT482)/50)*BT481)</f>
+        <v>24</v>
+      </c>
+      <c r="BU483">
+        <f t="shared" ref="BU483:BV483" si="35">(((100-BU482)/50)*BU481)</f>
+        <v>23.2</v>
+      </c>
+      <c r="BV483">
+        <f t="shared" si="35"/>
+        <v>22.400000000000002</v>
+      </c>
+      <c r="BW483">
+        <f t="shared" ref="BW483" si="36">(((100-BW482)/50)*BW481)</f>
+        <v>21.6</v>
+      </c>
+      <c r="BX483">
+        <f t="shared" ref="BX483:BY483" si="37">(((100-BX482)/50)*BX481)</f>
+        <v>20.8</v>
+      </c>
+      <c r="BY483">
+        <f t="shared" si="37"/>
+        <v>20</v>
+      </c>
+      <c r="BZ483">
+        <f t="shared" ref="BZ483" si="38">(((100-BZ482)/50)*BZ481)</f>
+        <v>19.2</v>
+      </c>
+      <c r="CA483">
+        <f t="shared" ref="CA483:CB483" si="39">(((100-CA482)/50)*CA481)</f>
+        <v>18.400000000000002</v>
+      </c>
+      <c r="CB483">
+        <f t="shared" si="39"/>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="CC483">
+        <f t="shared" ref="CC483" si="40">(((100-CC482)/50)*CC481)</f>
+        <v>16.8</v>
+      </c>
+      <c r="CD483">
+        <f t="shared" ref="CD483:CE483" si="41">(((100-CD482)/50)*CD481)</f>
+        <v>16</v>
+      </c>
+      <c r="CE483">
+        <f t="shared" si="41"/>
+        <v>15.2</v>
+      </c>
+      <c r="CF483">
+        <f t="shared" ref="CF483" si="42">(((100-CF482)/50)*CF481)</f>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="CG483">
+        <f t="shared" ref="CG483:CH483" si="43">(((100-CG482)/50)*CG481)</f>
+        <v>13.600000000000001</v>
+      </c>
+      <c r="CH483">
+        <f t="shared" si="43"/>
+        <v>12.8</v>
+      </c>
+      <c r="CI483">
+        <f t="shared" ref="CI483" si="44">(((100-CI482)/50)*CI481)</f>
+        <v>12</v>
+      </c>
+      <c r="CJ483">
+        <f t="shared" ref="CJ483:CK483" si="45">(((100-CJ482)/50)*CJ481)</f>
+        <v>11.200000000000001</v>
+      </c>
+      <c r="CK483">
+        <f t="shared" si="45"/>
+        <v>10.4</v>
+      </c>
+      <c r="CL483">
+        <f t="shared" ref="CL483" si="46">(((100-CL482)/50)*CL481)</f>
+        <v>9.6</v>
+      </c>
+      <c r="CM483">
+        <f t="shared" ref="CM483:CN483" si="47">(((100-CM482)/50)*CM481)</f>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="CN483">
+        <f t="shared" si="47"/>
+        <v>8</v>
+      </c>
+      <c r="CO483">
+        <f t="shared" ref="CO483" si="48">(((100-CO482)/50)*CO481)</f>
+        <v>7.1999999999999993</v>
+      </c>
+      <c r="CP483">
+        <f t="shared" ref="CP483:CQ483" si="49">(((100-CP482)/50)*CP481)</f>
+        <v>6.4</v>
+      </c>
+      <c r="CQ483">
+        <f t="shared" si="49"/>
+        <v>5.6000000000000005</v>
+      </c>
+      <c r="CR483">
+        <f t="shared" ref="CR483" si="50">(((100-CR482)/50)*CR481)</f>
+        <v>4.8</v>
+      </c>
+      <c r="CS483">
+        <f t="shared" ref="CS483:CT483" si="51">(((100-CS482)/50)*CS481)</f>
+        <v>4</v>
+      </c>
+      <c r="CT483">
+        <f t="shared" si="51"/>
+        <v>3.2</v>
+      </c>
+      <c r="CU483">
+        <f t="shared" ref="CU483" si="52">(((100-CU482)/50)*CU481)</f>
+        <v>2.4</v>
+      </c>
+      <c r="CV483">
+        <f t="shared" ref="CV483:CW483" si="53">(((100-CV482)/50)*CV481)</f>
+        <v>1.6</v>
+      </c>
+      <c r="CW483">
+        <f t="shared" si="53"/>
+        <v>0.8</v>
+      </c>
+      <c r="CX483">
+        <f t="shared" ref="CX483" si="54">(((100-CX482)/50)*CX481)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="1:102" x14ac:dyDescent="0.25">
+      <c r="A484" s="51"/>
+      <c r="B484" t="s">
+        <v>873</v>
+      </c>
+      <c r="C484">
+        <f>C483/$D$454</f>
+        <v>5.333333333333334E-3</v>
+      </c>
+      <c r="D484">
+        <f t="shared" ref="D484:BO484" si="55">D483/$D$454</f>
+        <v>1.0666666666666668E-2</v>
+      </c>
+      <c r="E484">
+        <f t="shared" si="55"/>
+        <v>1.6E-2</v>
+      </c>
+      <c r="F484">
+        <f t="shared" si="55"/>
+        <v>2.1333333333333336E-2</v>
+      </c>
+      <c r="G484">
+        <f t="shared" si="55"/>
+        <v>2.6666666666666668E-2</v>
+      </c>
+      <c r="H484">
+        <f t="shared" si="55"/>
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="I484">
+        <f t="shared" si="55"/>
+        <v>3.7333333333333336E-2</v>
+      </c>
+      <c r="J484">
+        <f t="shared" si="55"/>
+        <v>4.2666666666666672E-2</v>
+      </c>
+      <c r="K484">
+        <f t="shared" si="55"/>
+        <v>4.7999999999999994E-2</v>
+      </c>
+      <c r="L484">
+        <f t="shared" si="55"/>
+        <v>5.3333333333333337E-2</v>
+      </c>
+      <c r="M484">
+        <f t="shared" si="55"/>
+        <v>5.8666666666666673E-2</v>
+      </c>
+      <c r="N484">
+        <f t="shared" si="55"/>
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="O484">
+        <f t="shared" si="55"/>
+        <v>6.933333333333333E-2</v>
+      </c>
+      <c r="P484">
+        <f t="shared" si="55"/>
+        <v>7.4666666666666673E-2</v>
+      </c>
+      <c r="Q484">
+        <f t="shared" si="55"/>
+        <v>0.08</v>
+      </c>
+      <c r="R484">
+        <f t="shared" si="55"/>
+        <v>8.5333333333333344E-2</v>
+      </c>
+      <c r="S484">
+        <f t="shared" si="55"/>
+        <v>9.0666666666666673E-2</v>
+      </c>
+      <c r="T484">
+        <f t="shared" si="55"/>
+        <v>9.5999999999999988E-2</v>
+      </c>
+      <c r="U484">
+        <f t="shared" si="55"/>
+        <v>0.10133333333333333</v>
+      </c>
+      <c r="V484">
+        <f t="shared" si="55"/>
+        <v>0.10666666666666667</v>
+      </c>
+      <c r="W484">
+        <f t="shared" si="55"/>
+        <v>0.112</v>
+      </c>
+      <c r="X484">
+        <f t="shared" si="55"/>
+        <v>0.11733333333333335</v>
+      </c>
+      <c r="Y484">
+        <f t="shared" si="55"/>
+        <v>0.12266666666666669</v>
+      </c>
+      <c r="Z484">
+        <f t="shared" si="55"/>
+        <v>0.128</v>
+      </c>
+      <c r="AA484">
+        <f t="shared" si="55"/>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="AB484">
+        <f t="shared" si="55"/>
+        <v>0.13866666666666666</v>
+      </c>
+      <c r="AC484">
+        <f t="shared" si="55"/>
+        <v>0.14400000000000002</v>
+      </c>
+      <c r="AD484">
+        <f t="shared" si="55"/>
+        <v>0.14933333333333335</v>
+      </c>
+      <c r="AE484">
+        <f t="shared" si="55"/>
+        <v>0.15466666666666667</v>
+      </c>
+      <c r="AF484">
+        <f t="shared" si="55"/>
+        <v>0.16</v>
+      </c>
+      <c r="AG484">
+        <f t="shared" si="55"/>
+        <v>0.16533333333333333</v>
+      </c>
+      <c r="AH484">
+        <f t="shared" si="55"/>
+        <v>0.17066666666666669</v>
+      </c>
+      <c r="AI484">
+        <f t="shared" si="55"/>
+        <v>0.17600000000000002</v>
+      </c>
+      <c r="AJ484">
+        <f t="shared" si="55"/>
+        <v>0.18133333333333335</v>
+      </c>
+      <c r="AK484">
+        <f t="shared" si="55"/>
+        <v>0.18666666666666668</v>
+      </c>
+      <c r="AL484">
+        <f t="shared" si="55"/>
+        <v>0.19199999999999998</v>
+      </c>
+      <c r="AM484">
+        <f t="shared" si="55"/>
+        <v>0.19733333333333333</v>
+      </c>
+      <c r="AN484">
+        <f t="shared" si="55"/>
+        <v>0.20266666666666666</v>
+      </c>
+      <c r="AO484">
+        <f t="shared" si="55"/>
+        <v>0.20800000000000002</v>
+      </c>
+      <c r="AP484">
+        <f t="shared" si="55"/>
+        <v>0.21333333333333335</v>
+      </c>
+      <c r="AQ484">
+        <f t="shared" si="55"/>
+        <v>0.21866666666666665</v>
+      </c>
+      <c r="AR484">
+        <f t="shared" si="55"/>
+        <v>0.224</v>
+      </c>
+      <c r="AS484">
+        <f t="shared" si="55"/>
+        <v>0.22933333333333333</v>
+      </c>
+      <c r="AT484">
+        <f t="shared" si="55"/>
+        <v>0.23466666666666669</v>
+      </c>
+      <c r="AU484">
+        <f t="shared" si="55"/>
+        <v>0.24</v>
+      </c>
+      <c r="AV484">
+        <f t="shared" si="55"/>
+        <v>0.24533333333333338</v>
+      </c>
+      <c r="AW484">
+        <f t="shared" si="55"/>
+        <v>0.25066666666666665</v>
+      </c>
+      <c r="AX484">
+        <f t="shared" si="55"/>
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="AY484">
+        <f t="shared" si="55"/>
+        <v>0.26133333333333336</v>
+      </c>
+      <c r="AZ484">
+        <f t="shared" si="55"/>
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="BA484">
+        <f t="shared" si="55"/>
+        <v>0.26133333333333336</v>
+      </c>
+      <c r="BB484">
+        <f t="shared" si="55"/>
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="BC484">
+        <f t="shared" si="55"/>
+        <v>0.25066666666666665</v>
+      </c>
+      <c r="BD484">
+        <f t="shared" si="55"/>
+        <v>0.24533333333333338</v>
+      </c>
+      <c r="BE484">
+        <f t="shared" si="55"/>
+        <v>0.24</v>
+      </c>
+      <c r="BF484">
+        <f t="shared" si="55"/>
+        <v>0.23466666666666669</v>
+      </c>
+      <c r="BG484">
+        <f t="shared" si="55"/>
+        <v>0.22933333333333333</v>
+      </c>
+      <c r="BH484">
+        <f t="shared" si="55"/>
+        <v>0.224</v>
+      </c>
+      <c r="BI484">
+        <f t="shared" si="55"/>
+        <v>0.21866666666666665</v>
+      </c>
+      <c r="BJ484">
+        <f t="shared" si="55"/>
+        <v>0.21333333333333335</v>
+      </c>
+      <c r="BK484">
+        <f t="shared" si="55"/>
+        <v>0.20800000000000002</v>
+      </c>
+      <c r="BL484">
+        <f t="shared" si="55"/>
+        <v>0.20266666666666666</v>
+      </c>
+      <c r="BM484">
+        <f t="shared" si="55"/>
+        <v>0.19733333333333333</v>
+      </c>
+      <c r="BN484">
+        <f t="shared" si="55"/>
+        <v>0.19199999999999998</v>
+      </c>
+      <c r="BO484">
+        <f t="shared" si="55"/>
+        <v>0.18666666666666668</v>
+      </c>
+      <c r="BP484">
+        <f t="shared" ref="BP484:CX484" si="56">BP483/$D$454</f>
+        <v>0.18133333333333335</v>
+      </c>
+      <c r="BQ484">
+        <f t="shared" si="56"/>
+        <v>0.17600000000000002</v>
+      </c>
+      <c r="BR484">
+        <f t="shared" si="56"/>
+        <v>0.17066666666666669</v>
+      </c>
+      <c r="BS484">
+        <f t="shared" si="56"/>
+        <v>0.16533333333333333</v>
+      </c>
+      <c r="BT484">
+        <f t="shared" si="56"/>
+        <v>0.16</v>
+      </c>
+      <c r="BU484">
+        <f t="shared" si="56"/>
+        <v>0.15466666666666667</v>
+      </c>
+      <c r="BV484">
+        <f t="shared" si="56"/>
+        <v>0.14933333333333335</v>
+      </c>
+      <c r="BW484">
+        <f t="shared" si="56"/>
+        <v>0.14400000000000002</v>
+      </c>
+      <c r="BX484">
+        <f t="shared" si="56"/>
+        <v>0.13866666666666666</v>
+      </c>
+      <c r="BY484">
+        <f t="shared" si="56"/>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="BZ484">
+        <f t="shared" si="56"/>
+        <v>0.128</v>
+      </c>
+      <c r="CA484">
+        <f t="shared" si="56"/>
+        <v>0.12266666666666669</v>
+      </c>
+      <c r="CB484">
+        <f t="shared" si="56"/>
+        <v>0.11733333333333335</v>
+      </c>
+      <c r="CC484">
+        <f t="shared" si="56"/>
+        <v>0.112</v>
+      </c>
+      <c r="CD484">
+        <f t="shared" si="56"/>
+        <v>0.10666666666666667</v>
+      </c>
+      <c r="CE484">
+        <f t="shared" si="56"/>
+        <v>0.10133333333333333</v>
+      </c>
+      <c r="CF484">
+        <f t="shared" si="56"/>
+        <v>9.5999999999999988E-2</v>
+      </c>
+      <c r="CG484">
+        <f t="shared" si="56"/>
+        <v>9.0666666666666673E-2</v>
+      </c>
+      <c r="CH484">
+        <f t="shared" si="56"/>
+        <v>8.5333333333333344E-2</v>
+      </c>
+      <c r="CI484">
+        <f t="shared" si="56"/>
+        <v>0.08</v>
+      </c>
+      <c r="CJ484">
+        <f t="shared" si="56"/>
+        <v>7.4666666666666673E-2</v>
+      </c>
+      <c r="CK484">
+        <f t="shared" si="56"/>
+        <v>6.933333333333333E-2</v>
+      </c>
+      <c r="CL484">
+        <f t="shared" si="56"/>
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="CM484">
+        <f t="shared" si="56"/>
+        <v>5.8666666666666673E-2</v>
+      </c>
+      <c r="CN484">
+        <f t="shared" si="56"/>
+        <v>5.3333333333333337E-2</v>
+      </c>
+      <c r="CO484">
+        <f t="shared" si="56"/>
+        <v>4.7999999999999994E-2</v>
+      </c>
+      <c r="CP484">
+        <f t="shared" si="56"/>
+        <v>4.2666666666666672E-2</v>
+      </c>
+      <c r="CQ484">
+        <f t="shared" si="56"/>
+        <v>3.7333333333333336E-2</v>
+      </c>
+      <c r="CR484">
+        <f t="shared" si="56"/>
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="CS484">
+        <f t="shared" si="56"/>
+        <v>2.6666666666666668E-2</v>
+      </c>
+      <c r="CT484">
+        <f t="shared" si="56"/>
+        <v>2.1333333333333336E-2</v>
+      </c>
+      <c r="CU484">
+        <f t="shared" si="56"/>
+        <v>1.6E-2</v>
+      </c>
+      <c r="CV484">
+        <f t="shared" si="56"/>
+        <v>1.0666666666666668E-2</v>
+      </c>
+      <c r="CW484">
+        <f t="shared" si="56"/>
+        <v>5.333333333333334E-3</v>
+      </c>
+      <c r="CX484">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="1:102" x14ac:dyDescent="0.25">
+      <c r="A485" s="51"/>
+      <c r="B485" t="s">
+        <v>874</v>
+      </c>
+      <c r="C485">
+        <f>(($D$460*2)+(C484*($D$462+$D$464)))*$D$480</f>
+        <v>3.9166666666666675E-7</v>
+      </c>
+      <c r="D485">
+        <f>(($D$460*2)+(D484*($D$462+$D$464)))*$D$480</f>
+        <v>4.0833333333333338E-7</v>
+      </c>
+      <c r="E485">
+        <f t="shared" ref="E485:BP485" si="57">(($D$460*2)+(E484*($D$462+$D$464)))*$D$480</f>
+        <v>4.2500000000000001E-7</v>
+      </c>
+      <c r="F485">
+        <f t="shared" si="57"/>
+        <v>4.4166666666666669E-7</v>
+      </c>
+      <c r="G485">
+        <f t="shared" si="57"/>
+        <v>4.5833333333333332E-7</v>
+      </c>
+      <c r="H485">
+        <f t="shared" si="57"/>
+        <v>4.7500000000000006E-7</v>
+      </c>
+      <c r="I485">
+        <f t="shared" si="57"/>
+        <v>4.9166666666666669E-7</v>
+      </c>
+      <c r="J485">
+        <f t="shared" si="57"/>
+        <v>5.0833333333333337E-7</v>
+      </c>
+      <c r="K485">
+        <f t="shared" si="57"/>
+        <v>5.2500000000000006E-7</v>
+      </c>
+      <c r="L485">
+        <f t="shared" si="57"/>
+        <v>5.4166666666666674E-7</v>
+      </c>
+      <c r="M485">
+        <f t="shared" si="57"/>
+        <v>5.5833333333333332E-7</v>
+      </c>
+      <c r="N485">
+        <f t="shared" si="57"/>
+        <v>5.75E-7</v>
+      </c>
+      <c r="O485">
+        <f t="shared" si="57"/>
+        <v>5.9166666666666668E-7</v>
+      </c>
+      <c r="P485">
+        <f t="shared" si="57"/>
+        <v>6.0833333333333337E-7</v>
+      </c>
+      <c r="Q485">
+        <f t="shared" si="57"/>
+        <v>6.2500000000000005E-7</v>
+      </c>
+      <c r="R485">
+        <f t="shared" si="57"/>
+        <v>6.4166666666666684E-7</v>
+      </c>
+      <c r="S485">
+        <f t="shared" si="57"/>
+        <v>6.5833333333333331E-7</v>
+      </c>
+      <c r="T485">
+        <f t="shared" si="57"/>
+        <v>6.75E-7</v>
+      </c>
+      <c r="U485">
+        <f t="shared" si="57"/>
+        <v>6.9166666666666657E-7</v>
+      </c>
+      <c r="V485">
+        <f t="shared" si="57"/>
+        <v>7.0833333333333336E-7</v>
+      </c>
+      <c r="W485">
+        <f t="shared" si="57"/>
+        <v>7.2500000000000015E-7</v>
+      </c>
+      <c r="X485">
+        <f t="shared" si="57"/>
+        <v>7.4166666666666662E-7</v>
+      </c>
+      <c r="Y485">
+        <f t="shared" si="57"/>
+        <v>7.5833333333333341E-7</v>
+      </c>
+      <c r="Z485">
+        <f t="shared" si="57"/>
+        <v>7.750000000000001E-7</v>
+      </c>
+      <c r="AA485">
+        <f t="shared" si="57"/>
+        <v>7.9166666666666667E-7</v>
+      </c>
+      <c r="AB485">
+        <f t="shared" si="57"/>
+        <v>8.0833333333333346E-7</v>
+      </c>
+      <c r="AC485">
+        <f t="shared" si="57"/>
+        <v>8.2500000000000015E-7</v>
+      </c>
+      <c r="AD485">
+        <f t="shared" si="57"/>
+        <v>8.4166666666666673E-7</v>
+      </c>
+      <c r="AE485">
+        <f t="shared" si="57"/>
+        <v>8.5833333333333352E-7</v>
+      </c>
+      <c r="AF485">
+        <f t="shared" si="57"/>
+        <v>8.7499999999999999E-7</v>
+      </c>
+      <c r="AG485">
+        <f t="shared" si="57"/>
+        <v>8.9166666666666678E-7</v>
+      </c>
+      <c r="AH485">
+        <f t="shared" si="57"/>
+        <v>9.0833333333333357E-7</v>
+      </c>
+      <c r="AI485">
+        <f t="shared" si="57"/>
+        <v>9.2500000000000004E-7</v>
+      </c>
+      <c r="AJ485">
+        <f t="shared" si="57"/>
+        <v>9.4166666666666683E-7</v>
+      </c>
+      <c r="AK485">
+        <f t="shared" si="57"/>
+        <v>9.583333333333334E-7</v>
+      </c>
+      <c r="AL485">
+        <f t="shared" si="57"/>
+        <v>9.7499999999999998E-7</v>
+      </c>
+      <c r="AM485">
+        <f t="shared" si="57"/>
+        <v>9.9166666666666677E-7</v>
+      </c>
+      <c r="AN485">
+        <f t="shared" si="57"/>
+        <v>1.0083333333333333E-6</v>
+      </c>
+      <c r="AO485">
+        <f t="shared" si="57"/>
+        <v>1.0250000000000001E-6</v>
+      </c>
+      <c r="AP485">
+        <f t="shared" si="57"/>
+        <v>1.0416666666666667E-6</v>
+      </c>
+      <c r="AQ485">
+        <f t="shared" si="57"/>
+        <v>1.0583333333333335E-6</v>
+      </c>
+      <c r="AR485">
+        <f t="shared" si="57"/>
+        <v>1.0750000000000003E-6</v>
+      </c>
+      <c r="AS485">
+        <f t="shared" si="57"/>
+        <v>1.0916666666666667E-6</v>
+      </c>
+      <c r="AT485">
+        <f t="shared" si="57"/>
+        <v>1.1083333333333335E-6</v>
+      </c>
+      <c r="AU485">
+        <f t="shared" si="57"/>
+        <v>1.125E-6</v>
+      </c>
+      <c r="AV485">
+        <f t="shared" si="57"/>
+        <v>1.1416666666666668E-6</v>
+      </c>
+      <c r="AW485">
+        <f t="shared" si="57"/>
+        <v>1.1583333333333332E-6</v>
+      </c>
+      <c r="AX485">
+        <f t="shared" si="57"/>
+        <v>1.175E-6</v>
+      </c>
+      <c r="AY485">
+        <f t="shared" si="57"/>
+        <v>1.1916666666666668E-6</v>
+      </c>
+      <c r="AZ485">
+        <f t="shared" si="57"/>
+        <v>1.2083333333333333E-6</v>
+      </c>
+      <c r="BA485">
+        <f t="shared" si="57"/>
+        <v>1.1916666666666668E-6</v>
+      </c>
+      <c r="BB485">
+        <f t="shared" si="57"/>
+        <v>1.175E-6</v>
+      </c>
+      <c r="BC485">
+        <f t="shared" si="57"/>
+        <v>1.1583333333333332E-6</v>
+      </c>
+      <c r="BD485">
+        <f t="shared" si="57"/>
+        <v>1.1416666666666668E-6</v>
+      </c>
+      <c r="BE485">
+        <f t="shared" si="57"/>
+        <v>1.125E-6</v>
+      </c>
+      <c r="BF485">
+        <f t="shared" si="57"/>
+        <v>1.1083333333333335E-6</v>
+      </c>
+      <c r="BG485">
+        <f t="shared" si="57"/>
+        <v>1.0916666666666667E-6</v>
+      </c>
+      <c r="BH485">
+        <f t="shared" si="57"/>
+        <v>1.0750000000000003E-6</v>
+      </c>
+      <c r="BI485">
+        <f t="shared" si="57"/>
+        <v>1.0583333333333335E-6</v>
+      </c>
+      <c r="BJ485">
+        <f t="shared" si="57"/>
+        <v>1.0416666666666667E-6</v>
+      </c>
+      <c r="BK485">
+        <f t="shared" si="57"/>
+        <v>1.0250000000000001E-6</v>
+      </c>
+      <c r="BL485">
+        <f t="shared" si="57"/>
+        <v>1.0083333333333333E-6</v>
+      </c>
+      <c r="BM485">
+        <f t="shared" si="57"/>
+        <v>9.9166666666666677E-7</v>
+      </c>
+      <c r="BN485">
+        <f t="shared" si="57"/>
+        <v>9.7499999999999998E-7</v>
+      </c>
+      <c r="BO485">
+        <f t="shared" si="57"/>
+        <v>9.583333333333334E-7</v>
+      </c>
+      <c r="BP485">
+        <f t="shared" si="57"/>
+        <v>9.4166666666666683E-7</v>
+      </c>
+      <c r="BQ485">
+        <f t="shared" ref="BQ485:CX485" si="58">(($D$460*2)+(BQ484*($D$462+$D$464)))*$D$480</f>
+        <v>9.2500000000000004E-7</v>
+      </c>
+      <c r="BR485">
+        <f t="shared" si="58"/>
+        <v>9.0833333333333357E-7</v>
+      </c>
+      <c r="BS485">
+        <f t="shared" si="58"/>
+        <v>8.9166666666666678E-7</v>
+      </c>
+      <c r="BT485">
+        <f t="shared" si="58"/>
+        <v>8.7499999999999999E-7</v>
+      </c>
+      <c r="BU485">
+        <f t="shared" si="58"/>
+        <v>8.5833333333333352E-7</v>
+      </c>
+      <c r="BV485">
+        <f t="shared" si="58"/>
+        <v>8.4166666666666673E-7</v>
+      </c>
+      <c r="BW485">
+        <f t="shared" si="58"/>
+        <v>8.2500000000000015E-7</v>
+      </c>
+      <c r="BX485">
+        <f t="shared" si="58"/>
+        <v>8.0833333333333346E-7</v>
+      </c>
+      <c r="BY485">
+        <f t="shared" si="58"/>
+        <v>7.9166666666666667E-7</v>
+      </c>
+      <c r="BZ485">
+        <f t="shared" si="58"/>
+        <v>7.750000000000001E-7</v>
+      </c>
+      <c r="CA485">
+        <f t="shared" si="58"/>
+        <v>7.5833333333333341E-7</v>
+      </c>
+      <c r="CB485">
+        <f t="shared" si="58"/>
+        <v>7.4166666666666662E-7</v>
+      </c>
+      <c r="CC485">
+        <f t="shared" si="58"/>
+        <v>7.2500000000000015E-7</v>
+      </c>
+      <c r="CD485">
+        <f t="shared" si="58"/>
+        <v>7.0833333333333336E-7</v>
+      </c>
+      <c r="CE485">
+        <f t="shared" si="58"/>
+        <v>6.9166666666666657E-7</v>
+      </c>
+      <c r="CF485">
+        <f t="shared" si="58"/>
+        <v>6.75E-7</v>
+      </c>
+      <c r="CG485">
+        <f t="shared" si="58"/>
+        <v>6.5833333333333331E-7</v>
+      </c>
+      <c r="CH485">
+        <f t="shared" si="58"/>
+        <v>6.4166666666666684E-7</v>
+      </c>
+      <c r="CI485">
+        <f t="shared" si="58"/>
+        <v>6.2500000000000005E-7</v>
+      </c>
+      <c r="CJ485">
+        <f t="shared" si="58"/>
+        <v>6.0833333333333337E-7</v>
+      </c>
+      <c r="CK485">
+        <f t="shared" si="58"/>
+        <v>5.9166666666666668E-7</v>
+      </c>
+      <c r="CL485">
+        <f t="shared" si="58"/>
+        <v>5.75E-7</v>
+      </c>
+      <c r="CM485">
+        <f t="shared" si="58"/>
+        <v>5.5833333333333332E-7</v>
+      </c>
+      <c r="CN485">
+        <f t="shared" si="58"/>
+        <v>5.4166666666666674E-7</v>
+      </c>
+      <c r="CO485">
+        <f t="shared" si="58"/>
+        <v>5.2500000000000006E-7</v>
+      </c>
+      <c r="CP485">
+        <f t="shared" si="58"/>
+        <v>5.0833333333333337E-7</v>
+      </c>
+      <c r="CQ485">
+        <f t="shared" si="58"/>
+        <v>4.9166666666666669E-7</v>
+      </c>
+      <c r="CR485">
+        <f t="shared" si="58"/>
+        <v>4.7500000000000006E-7</v>
+      </c>
+      <c r="CS485">
+        <f t="shared" si="58"/>
+        <v>4.5833333333333332E-7</v>
+      </c>
+      <c r="CT485">
+        <f t="shared" si="58"/>
+        <v>4.4166666666666669E-7</v>
+      </c>
+      <c r="CU485">
+        <f t="shared" si="58"/>
+        <v>4.2500000000000001E-7</v>
+      </c>
+      <c r="CV485">
+        <f t="shared" si="58"/>
+        <v>4.0833333333333338E-7</v>
+      </c>
+      <c r="CW485">
+        <f t="shared" si="58"/>
+        <v>3.9166666666666675E-7</v>
+      </c>
+      <c r="CX485">
+        <f t="shared" si="58"/>
+        <v>3.7500000000000001E-7</v>
+      </c>
+    </row>
+    <row r="486" spans="1:102" x14ac:dyDescent="0.25">
+      <c r="A486" s="51"/>
+      <c r="B486" t="s">
+        <v>875</v>
+      </c>
+      <c r="C486">
+        <f>SUM(C485:CX485)</f>
+        <v>7.9166666666666676E-5</v>
+      </c>
+    </row>
+    <row r="487" spans="1:102" x14ac:dyDescent="0.25">
+      <c r="A487" s="51"/>
+      <c r="B487" t="s">
+        <v>876</v>
+      </c>
+      <c r="C487">
+        <f>381/1000000</f>
+        <v>3.8099999999999999E-4</v>
+      </c>
+    </row>
+    <row r="488" spans="1:102" x14ac:dyDescent="0.25">
+      <c r="A488" s="51"/>
+      <c r="C488" t="s">
+        <v>877</v>
+      </c>
+      <c r="D488" t="b">
+        <f>C486&lt;=C487</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="489" spans="1:102" x14ac:dyDescent="0.25">
+      <c r="A489" s="51"/>
+    </row>
+    <row r="490" spans="1:102" x14ac:dyDescent="0.25">
+      <c r="A490" s="51"/>
+      <c r="E490" s="9"/>
+    </row>
+    <row r="491" spans="1:102" x14ac:dyDescent="0.25">
+      <c r="A491" s="54" t="s">
+        <v>451</v>
+      </c>
+      <c r="B491" t="s">
+        <v>48</v>
+      </c>
+      <c r="C491" t="s">
+        <v>47</v>
+      </c>
+      <c r="D491">
+        <f>D3</f>
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="492" spans="1:102" x14ac:dyDescent="0.25">
+      <c r="A492" s="54"/>
+      <c r="B492" t="s">
+        <v>41</v>
+      </c>
+      <c r="C492" t="s">
+        <v>434</v>
+      </c>
+      <c r="D492">
+        <f>D105</f>
+        <v>22.598870056497173</v>
+      </c>
+    </row>
+    <row r="493" spans="1:102" x14ac:dyDescent="0.25">
+      <c r="A493" s="54"/>
+      <c r="B493" t="s">
+        <v>39</v>
+      </c>
+      <c r="C493" t="s">
         <v>435</v>
       </c>
-      <c r="D480">
+      <c r="D493">
         <f>D103</f>
         <v>0.5</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A481" s="51"/>
-      <c r="B481" t="s">
+    <row r="494" spans="1:102" x14ac:dyDescent="0.25">
+      <c r="A494" s="54"/>
+      <c r="B494" t="s">
         <v>432</v>
       </c>
-      <c r="C481" t="s">
+      <c r="C494" t="s">
         <v>433</v>
       </c>
-      <c r="D481">
-        <f>0.5*D479/D478</f>
+      <c r="D494">
+        <f>0.5*D492/D491</f>
         <v>7.0621468926553661E-4</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A482" s="51"/>
-      <c r="B482" t="s">
+    <row r="495" spans="1:102" x14ac:dyDescent="0.25">
+      <c r="A495" s="54"/>
+      <c r="B495" t="s">
         <v>436</v>
       </c>
-      <c r="D482">
+      <c r="D495">
         <v>0.5</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A483" s="51"/>
-      <c r="B483" t="s">
+    <row r="496" spans="1:102" x14ac:dyDescent="0.25">
+      <c r="A496" s="54"/>
+      <c r="B496" t="s">
         <v>442</v>
       </c>
-      <c r="D483">
-        <f>D481/D482</f>
+      <c r="D496">
+        <f>D494/D495</f>
         <v>1.4124293785310732E-3</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A484" s="51"/>
-      <c r="C484" t="s">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A497" s="54"/>
+      <c r="C497" t="s">
         <v>437</v>
       </c>
-      <c r="D484">
+      <c r="D497">
         <v>10</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A485" s="51"/>
-      <c r="B485" t="s">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A498" s="54"/>
+      <c r="B498" t="s">
         <v>441</v>
       </c>
-      <c r="D485">
-        <f>D484*D483</f>
+      <c r="D498">
+        <f>D497*D496</f>
         <v>1.4124293785310733E-2</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A486" s="51"/>
-      <c r="B486" t="s">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A499" s="54"/>
+      <c r="B499" t="s">
         <v>466</v>
       </c>
-      <c r="C486" t="s">
+      <c r="C499" t="s">
         <v>467</v>
       </c>
-      <c r="D486">
-        <f>3*D508</f>
+      <c r="D499">
+        <f>3*D521</f>
         <v>132.30000000000001</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A487" s="51"/>
-      <c r="B487" t="s">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A500" s="54"/>
+      <c r="B500" t="s">
         <v>468</v>
       </c>
-      <c r="D487" s="1">
+      <c r="D500" s="1">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A488" s="51"/>
-      <c r="B488" t="s">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A501" s="54"/>
+      <c r="B501" t="s">
         <v>469</v>
       </c>
-      <c r="D488">
+      <c r="D501">
         <v>20</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A489" s="51"/>
-      <c r="B489" t="s">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A502" s="54"/>
+      <c r="B502" t="s">
         <v>472</v>
       </c>
-      <c r="C489" t="s">
+      <c r="C502" t="s">
         <v>473</v>
       </c>
-      <c r="D489" s="30">
+      <c r="D502" s="30">
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A490" s="51"/>
-      <c r="B490" t="s">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A503" s="54"/>
+      <c r="B503" t="s">
         <v>474</v>
       </c>
-      <c r="D490">
-        <f>D489/D488</f>
+      <c r="D503">
+        <f>D502/D501</f>
         <v>8.5000000000000006E-4</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A491" s="51"/>
-      <c r="B491" t="s">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A504" s="54"/>
+      <c r="B504" t="s">
         <v>447</v>
       </c>
-      <c r="C491" t="s">
+      <c r="C504" t="s">
         <v>448</v>
       </c>
-      <c r="D491" s="1">
-        <f>D487*D488</f>
+      <c r="D504" s="1">
+        <f>D500*D501</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A492" s="51"/>
-      <c r="C492" t="s">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A505" s="54"/>
+      <c r="C505" t="s">
         <v>470</v>
       </c>
-      <c r="D492" s="1">
+      <c r="D505" s="1">
         <f>0.2</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A493" s="51"/>
-      <c r="B493" t="s">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A506" s="54"/>
+      <c r="B506" t="s">
         <v>471</v>
       </c>
-      <c r="D493" s="1">
-        <f>D491*(1-D492)</f>
+      <c r="D506" s="1">
+        <f>D504*(1-D505)</f>
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A494" s="51"/>
-      <c r="B494" t="s">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A507" s="54"/>
+      <c r="B507" t="s">
         <v>507</v>
       </c>
-      <c r="D494" s="1">
-        <f>D490*D479</f>
+      <c r="D507" s="1">
+        <f>D503*D492</f>
         <v>1.9209039548022597E-2</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A495" s="51"/>
-      <c r="B495" t="s">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A508" s="54"/>
+      <c r="B508" t="s">
         <v>508</v>
       </c>
-      <c r="D495" s="1">
-        <f>D481/D491</f>
+      <c r="D508" s="1">
+        <f>D494/D504</f>
         <v>3.531073446327683E-2</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A496" s="51"/>
-      <c r="B496" t="s">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A509" s="54"/>
+      <c r="B509" t="s">
         <v>509</v>
       </c>
-      <c r="D496" s="1">
-        <f>D494+D495</f>
+      <c r="D509" s="1">
+        <f>D507+D508</f>
         <v>5.4519774011299427E-2</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A497" s="51"/>
-      <c r="B497" t="s">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A510" s="54"/>
+      <c r="B510" t="s">
         <v>475</v>
       </c>
-      <c r="D497" s="1">
-        <f>POWER(D494, 2)/D490</f>
+      <c r="D510" s="1">
+        <f>POWER(D507, 2)/D503</f>
         <v>0.43410258865587781</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A498" s="51"/>
-      <c r="B498" t="s">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A511" s="54"/>
+      <c r="B511" t="s">
         <v>476</v>
       </c>
-      <c r="D498" s="1">
-        <f>D497/D488</f>
+      <c r="D511" s="1">
+        <f>D510/D501</f>
         <v>2.1705129432793891E-2</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A499" s="51"/>
-      <c r="B499" t="s">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A512" s="54"/>
+      <c r="B512" t="s">
         <v>445</v>
       </c>
-      <c r="C499" t="s">
+      <c r="C512" t="s">
         <v>439</v>
       </c>
-      <c r="D499">
+      <c r="D512">
         <v>500</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A500" s="51"/>
-      <c r="B500" t="s">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A513" s="54"/>
+      <c r="B513" t="s">
         <v>443</v>
       </c>
-      <c r="C500" t="s">
+      <c r="C513" t="s">
         <v>444</v>
       </c>
-      <c r="D500">
-        <f>1/(POWER(2*PI()*D499, 2)*D485)</f>
+      <c r="D513">
+        <f>1/(POWER(2*PI()*D512, 2)*D498)</f>
         <v>7.1735398018775158E-6</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A501" s="51"/>
-      <c r="B501" t="s">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A514" s="54"/>
+      <c r="B514" t="s">
         <v>440</v>
       </c>
-      <c r="C501" t="s">
+      <c r="C514" t="s">
         <v>477</v>
       </c>
-      <c r="D501" s="1">
+      <c r="D514" s="1">
         <v>2.1999999999999999E-5</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A502" s="51"/>
-      <c r="B502" t="s">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A515" s="54"/>
+      <c r="B515" t="s">
         <v>478</v>
       </c>
-      <c r="D502" s="1">
+      <c r="D515" s="1">
         <f>D2*2/D5</f>
         <v>11.299435028248586</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A503" s="51"/>
-      <c r="B503" t="s">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A516" s="54"/>
+      <c r="B516" t="s">
         <v>479</v>
       </c>
-      <c r="D503" s="1">
-        <f>2*D502</f>
+      <c r="D516" s="1">
+        <f>2*D515</f>
         <v>22.598870056497173</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A504" s="51"/>
-      <c r="B504" t="s">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A517" s="54"/>
+      <c r="B517" t="s">
         <v>438</v>
       </c>
-      <c r="C504" t="s">
+      <c r="C517" t="s">
         <v>446</v>
       </c>
-      <c r="D504" s="1">
-        <f>1/(2*PI()*POWER(D491*D501, 0.5))</f>
+      <c r="D517" s="1">
+        <f>1/(2*PI()*POWER(D504*D514, 0.5))</f>
         <v>239.93510443917407</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A505" s="51"/>
-      <c r="B505" t="s">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A518" s="54"/>
+      <c r="B518" t="s">
         <v>449</v>
       </c>
-      <c r="D505" s="1">
-        <f>40*LOG10(D478/D504)</f>
+      <c r="D518" s="1">
+        <f>40*LOG10(D491/D517)</f>
         <v>72.961047570285331</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A506" s="51"/>
-      <c r="C506" t="s">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A519" s="54"/>
+      <c r="C519" t="s">
         <v>450</v>
       </c>
-      <c r="D506">
-        <f>POWER(D7, 2)*0.5*D491</f>
+      <c r="D519">
+        <f>POWER(D7, 2)*0.5*D504</f>
         <v>19.448100000000004</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A507" s="51"/>
-      <c r="B507" t="s">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A520" s="54"/>
+      <c r="B520" t="s">
         <v>452</v>
       </c>
-      <c r="C507" t="s">
+      <c r="C520" t="s">
         <v>453</v>
       </c>
-      <c r="D507">
+      <c r="D520">
         <v>33</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A508" s="51"/>
-      <c r="B508" t="s">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A521" s="54"/>
+      <c r="B521" t="s">
         <v>38</v>
       </c>
-      <c r="D508">
+      <c r="D521">
         <f>D7</f>
         <v>44.1</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A509" s="51"/>
-    </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A510" s="51"/>
-      <c r="B510" t="s">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A522" s="54"/>
+    </row>
+    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A523" s="54"/>
+      <c r="B523" t="s">
         <v>455</v>
       </c>
-      <c r="D510" s="1">
-        <f>((-D507)+POWER(POWER(D507, 2)-(4*D501/D491), 0.5))/(2*D501)</f>
+      <c r="D523" s="1">
+        <f>((-D520)+POWER(POWER(D520, 2)-(4*D514/D504), 0.5))/(2*D514)</f>
         <v>-1.5151530456139737</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A511" s="51"/>
-      <c r="B511" t="s">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A524" s="54"/>
+      <c r="B524" t="s">
         <v>456</v>
       </c>
-      <c r="D511" s="1">
-        <f>((-D507)-POWER(POWER(D507, 2)-(4*D501/D491), 0.5))/(2*D501)</f>
+      <c r="D524" s="1">
+        <f>((-D520)-POWER(POWER(D520, 2)-(4*D514/D504), 0.5))/(2*D514)</f>
         <v>-1499998.4848469547</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A512" s="51"/>
-      <c r="B512" t="s">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A525" s="54"/>
+      <c r="B525" t="s">
         <v>457</v>
       </c>
-      <c r="D512" s="1">
-        <f>LN(D511/D510)/(D510-D511)</f>
+      <c r="D525" s="1">
+        <f>LN(D524/D523)/(D523-D524)</f>
         <v>9.2036573945350537E-6</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A513" s="51"/>
-      <c r="B513" t="s">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A526" s="54"/>
+      <c r="B526" t="s">
         <v>240</v>
       </c>
-      <c r="D513" s="1">
-        <f>(D508/(D501*(D510-D511)))*(EXP(D510*D512)-EXP(D511*D512))</f>
+      <c r="D526" s="1">
+        <f>(D521/(D514*(D523-D524)))*(EXP(D523*D525)-EXP(D524*D525))</f>
         <v>1.3363463508162678</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A514" s="51"/>
-      <c r="B514" t="s">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A527" s="54"/>
+      <c r="B527" t="s">
         <v>458</v>
       </c>
-      <c r="D514" s="1">
-        <f>D507*POWER(D513, 2)</f>
+      <c r="D527" s="1">
+        <f>D520*POWER(D526, 2)</f>
         <v>58.932111788218542</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A515" s="51"/>
-      <c r="C515" t="s">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A528" s="54"/>
+      <c r="C528" t="s">
         <v>454</v>
       </c>
-      <c r="D515" s="1">
-        <f>D514*D4</f>
+      <c r="D528" s="1">
+        <f>D527*D4</f>
         <v>70.71853414586225</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A516" s="51"/>
-      <c r="B516" t="s">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A529" s="54"/>
+      <c r="B529" t="s">
         <v>460</v>
       </c>
-      <c r="C516" t="s">
+      <c r="C529" t="s">
         <v>459</v>
       </c>
-      <c r="D516" t="b">
-        <f>(POWER(D507, 2)/(4*POWER(D501, 2)))&lt;(1/(D501*D491))</f>
+      <c r="D529" t="b">
+        <f>(POWER(D520, 2)/(4*POWER(D514, 2)))&lt;(1/(D514*D504))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A517" s="51"/>
-      <c r="B517" t="s">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A530" s="54"/>
+      <c r="B530" t="s">
         <v>461</v>
       </c>
-      <c r="D517" s="1">
-        <f>D507/(2*D501)</f>
+      <c r="D530" s="1">
+        <f>D520/(2*D514)</f>
         <v>750000</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A518" s="51"/>
-      <c r="B518" t="s">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A531" s="54"/>
+      <c r="B531" t="s">
         <v>462</v>
       </c>
-      <c r="D518" s="1">
-        <f>1/POWER(D501*D491, 0.5)</f>
+      <c r="D531" s="1">
+        <f>1/POWER(D514*D504, 0.5)</f>
         <v>1507.5567228888181</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A519" s="51"/>
-      <c r="B519" t="s">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A532" s="54"/>
+      <c r="B532" t="s">
         <v>463</v>
       </c>
-      <c r="D519" t="str">
-        <f>IF(D516, POWER(POWER(D518, 2)-POWER(D517, 2), 0.5),"NA")</f>
+      <c r="D532" t="str">
+        <f>IF(D529, POWER(POWER(D531, 2)-POWER(D530, 2), 0.5),"NA")</f>
         <v>NA</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A520" s="51"/>
-      <c r="C520" t="s">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A533" s="54"/>
+      <c r="C533" t="s">
         <v>464</v>
       </c>
-      <c r="D520" s="1" t="str">
-        <f>IF(D516, 100*EXP(-PI()*D517/D519), "Not Under-damped")</f>
+      <c r="D533" s="1" t="str">
+        <f>IF(D529, 100*EXP(-PI()*D530/D532), "Not Under-damped")</f>
         <v>Not Under-damped</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A521" s="51"/>
-      <c r="B521" t="s">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A534" s="54"/>
+      <c r="B534" t="s">
         <v>465</v>
       </c>
-      <c r="D521" s="1">
-        <f>5/MIN(ABS(D510), ABS(D511))</f>
+      <c r="D534" s="1">
+        <f>5/MIN(ABS(D523), ABS(D524))</f>
         <v>3.2999966666561322</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A522" s="51"/>
-      <c r="B522" t="s">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A535" s="54"/>
+      <c r="B535" t="s">
         <v>483</v>
       </c>
-      <c r="C522" t="s">
+      <c r="C535" t="s">
         <v>480</v>
       </c>
-      <c r="D522">
+      <c r="D535">
         <v>1600</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A523" s="51"/>
-      <c r="C523" t="s">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A536" s="54"/>
+      <c r="C536" t="s">
         <v>481</v>
       </c>
-      <c r="D523">
+      <c r="D536">
         <v>0.1</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A524" s="51"/>
-      <c r="B524" t="s">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A537" s="54"/>
+      <c r="B537" t="s">
         <v>482</v>
       </c>
-      <c r="D524">
-        <f>D522*(1-D523)</f>
+      <c r="D537">
+        <f>D535*(1-D536)</f>
         <v>1440</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A525" s="51"/>
-      <c r="B525" t="s">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A538" s="54"/>
+      <c r="B538" t="s">
         <v>484</v>
       </c>
-      <c r="D525">
-        <f>D522*(1+D523)</f>
+      <c r="D538">
+        <f>D535*(1+D536)</f>
         <v>1760.0000000000002</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A526" s="51"/>
-      <c r="B526" t="s">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A539" s="54"/>
+      <c r="B539" t="s">
         <v>485</v>
       </c>
-      <c r="D526">
+      <c r="D539">
         <v>24</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A527" s="51"/>
-      <c r="B527" t="s">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A540" s="54"/>
+      <c r="B540" t="s">
         <v>486</v>
       </c>
-      <c r="D527">
+      <c r="D540">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A528" s="51"/>
-      <c r="C528" t="s">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A541" s="54"/>
+      <c r="C541" t="s">
         <v>487</v>
       </c>
-      <c r="D528" t="b">
-        <f>(D526/D522)=D527</f>
+      <c r="D541" t="b">
+        <f>(D539/D535)=D540</f>
         <v>1</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A529" s="51"/>
-      <c r="B529" t="s">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A542" s="54"/>
+      <c r="B542" t="s">
         <v>488</v>
       </c>
-      <c r="C529" t="s">
+      <c r="C542" t="s">
         <v>489</v>
       </c>
-      <c r="D529">
-        <f>1.3*D526</f>
+      <c r="D542">
+        <f>1.3*D539</f>
         <v>31.200000000000003</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A530" s="51"/>
-      <c r="B530" t="s">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A543" s="54"/>
+      <c r="B543" t="s">
         <v>490</v>
       </c>
-      <c r="C530" t="s">
+      <c r="C543" t="s">
         <v>491</v>
       </c>
-      <c r="D530">
-        <f>0.75*D526</f>
+      <c r="D543">
+        <f>0.75*D539</f>
         <v>18</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A531" s="51"/>
-      <c r="B531" t="s">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A544" s="54"/>
+      <c r="B544" t="s">
         <v>492</v>
       </c>
-      <c r="D531">
-        <f>D530/D525</f>
+      <c r="D544">
+        <f>D543/D538</f>
         <v>1.0227272727272725E-2</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A532" s="51"/>
-      <c r="B532" t="s">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A545" s="54"/>
+      <c r="B545" t="s">
         <v>493</v>
       </c>
-      <c r="D532">
-        <f>D529/D525</f>
+      <c r="D545">
+        <f>D542/D538</f>
         <v>1.7727272727272727E-2</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A533" s="51"/>
-      <c r="B533" t="s">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A546" s="54"/>
+      <c r="B546" t="s">
         <v>499</v>
       </c>
-      <c r="D533">
+      <c r="D546">
         <v>1330</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A534" s="51"/>
-      <c r="C534" t="s">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A547" s="54"/>
+      <c r="C547" t="s">
         <v>503</v>
       </c>
-      <c r="D534">
+      <c r="D547">
         <v>0.05</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A535" s="51"/>
-      <c r="B535" t="s">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A548" s="54"/>
+      <c r="B548" t="s">
         <v>504</v>
       </c>
-      <c r="D535">
-        <f>D533*(1-D534)</f>
+      <c r="D548">
+        <f>D546*(1-D547)</f>
         <v>1263.5</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A536" s="51"/>
-      <c r="B536" t="s">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A549" s="54"/>
+      <c r="B549" t="s">
         <v>505</v>
       </c>
-      <c r="D536">
-        <f>D533*(1+D534)</f>
+      <c r="D549">
+        <f>D546*(1+D547)</f>
         <v>1396.5</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A537" s="51"/>
-      <c r="C537" t="s">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A550" s="54"/>
+      <c r="C550" t="s">
         <v>496</v>
       </c>
-      <c r="D537">
-        <f>D6/(D522+D533)</f>
+      <c r="D550">
+        <f>D6/(D535+D546)</f>
         <v>1.3003412969283274E-2</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A538" s="51"/>
-      <c r="C538" t="s">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A551" s="54"/>
+      <c r="C551" t="s">
         <v>497</v>
       </c>
-      <c r="D538">
-        <f>D5/(D524+D536)</f>
+      <c r="D551">
+        <f>D5/(D537+D549)</f>
         <v>1.2480169222633529E-2</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A539" s="51"/>
-      <c r="C539" t="s">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A552" s="54"/>
+      <c r="C552" t="s">
         <v>498</v>
       </c>
-      <c r="D539">
-        <f>D7/(D524+D535)</f>
+      <c r="D552">
+        <f>D7/(D537+D548)</f>
         <v>1.6312187904568152E-2</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A540" s="51"/>
-      <c r="C540" t="s">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A553" s="54"/>
+      <c r="C553" t="s">
         <v>500</v>
       </c>
-      <c r="D540" t="b">
-        <f>AND((D537&gt;D531), (D539&lt;D532))</f>
+      <c r="D553" t="b">
+        <f>AND((D550&gt;D544), (D552&lt;D545))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A541" s="51"/>
-    </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A542" s="51"/>
-      <c r="B542" t="s">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A554" s="54"/>
+    </row>
+    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A555" s="54"/>
+      <c r="B555" t="s">
         <v>501</v>
       </c>
-      <c r="D542">
-        <f xml:space="preserve"> POWER(D539, 2)*D533</f>
+      <c r="D555">
+        <f xml:space="preserve"> POWER(D552, 2)*D546</f>
         <v>0.35389634073113957</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A543" s="51"/>
-      <c r="B543" t="s">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A556" s="54"/>
+      <c r="B556" t="s">
         <v>506</v>
       </c>
-      <c r="D543">
-        <f>POWER(D537, 2)*D522</f>
+      <c r="D556">
+        <f>POWER(D550, 2)*D535</f>
         <v>0.27054199815955915</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A544" s="51"/>
-      <c r="B544" t="s">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A557" s="54"/>
+      <c r="B557" t="s">
         <v>502</v>
       </c>
-      <c r="D544">
-        <f>POWER(D538, 2)*D525</f>
+      <c r="D557">
+        <f>POWER(D551, 2)*D538</f>
         <v>0.27412813793300184</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A545" s="51"/>
-      <c r="C545" t="s">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A558" s="54"/>
+      <c r="C558" t="s">
         <v>626</v>
       </c>
-      <c r="D545" s="1">
-        <f>0.5*D501*POWER(D546, 2)</f>
+      <c r="D558" s="1">
+        <f>0.5*D514*POWER(D559, 2)</f>
         <v>3.0311171733454588E-4</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A546" s="51"/>
-      <c r="C546" t="s">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A559" s="54"/>
+      <c r="C559" t="s">
         <v>627</v>
       </c>
-      <c r="D546">
+      <c r="D559">
         <f>D2/D6</f>
         <v>5.2493438320209984</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A547" s="51"/>
-      <c r="C547" t="s">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A560" s="54"/>
+      <c r="C560" t="s">
         <v>628</v>
       </c>
-      <c r="D547">
+      <c r="D560">
         <f>D6</f>
         <v>38.099999999999994</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A548" s="51"/>
-      <c r="C548" t="s">
+    <row r="561" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A561" s="54"/>
+      <c r="C561" t="s">
         <v>629</v>
       </c>
-      <c r="D548">
-        <f>POWER(((0.5*D491*POWER(D547, 2))+D545)*2/D491, 0.5)</f>
+      <c r="D561">
+        <f>POWER(((0.5*D504*POWER(D560, 2))+D558)*2/D504, 0.5)</f>
         <v>38.100397782329424</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A549" s="51"/>
-      <c r="B549" t="s">
+    <row r="562" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A562" s="54"/>
+      <c r="B562" t="s">
         <v>739</v>
       </c>
-      <c r="C549" t="s">
+      <c r="C562" t="s">
         <v>738</v>
       </c>
-      <c r="D549" s="1">
-        <f>0.5*D491*POWER(D7, 2)</f>
+      <c r="D562" s="1">
+        <f>0.5*D504*POWER(D7, 2)</f>
         <v>19.448100000000004</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A550" t="s">
+    <row r="563" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A563" t="s">
         <v>737</v>
       </c>
-      <c r="B550" t="s">
+      <c r="B563" t="s">
         <v>740</v>
       </c>
-      <c r="C550" t="s">
+      <c r="C563" t="s">
         <v>741</v>
       </c>
-      <c r="D550">
+      <c r="D563">
         <f>(0.06*0.022*0.0018)+(2*(0.06*0.0129*0.001))+(0.06*0.0091*0.0018)</f>
         <v>4.9067999999999993E-6</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B551" t="s">
+    <row r="564" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B564" t="s">
         <v>742</v>
       </c>
-      <c r="C551" t="s">
+      <c r="C564" t="s">
         <v>743</v>
       </c>
-      <c r="D551">
+      <c r="D564">
         <v>850</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B552" t="s">
+    <row r="565" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B565" t="s">
         <v>744</v>
       </c>
-      <c r="C552" t="s">
+      <c r="C565" t="s">
         <v>745</v>
       </c>
-      <c r="D552">
+      <c r="D565">
         <v>2700</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B553" t="s">
+    <row r="566" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B566" t="s">
         <v>713</v>
       </c>
-      <c r="D553">
-        <f>D549/(D552*D550*D551)</f>
+      <c r="D566">
+        <f>D562/(D565*D563*D564)</f>
         <v>1.7270150907024588</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B554" t="s">
+    <row r="567" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B567" t="s">
         <v>746</v>
       </c>
-      <c r="C554" t="s">
+      <c r="C567" t="s">
         <v>753</v>
       </c>
-      <c r="D554">
+      <c r="D567">
         <v>0.2</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B555" t="s">
+    <row r="568" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B568" t="s">
         <v>751</v>
       </c>
-      <c r="C555" t="s">
+      <c r="C568" t="s">
         <v>750</v>
       </c>
-      <c r="D555">
-        <f>D551*D550*D552</f>
+      <c r="D568">
+        <f>D564*D563*D565</f>
         <v>11.261106</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B556" t="s">
+    <row r="569" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B569" t="s">
         <v>757</v>
       </c>
-      <c r="C556" t="s">
+      <c r="C569" t="s">
         <v>756</v>
       </c>
-      <c r="D556">
+      <c r="D569">
         <f>0.022*0.06</f>
         <v>1.3199999999999998E-3</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B557" t="s">
+    <row r="570" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B570" t="s">
         <v>758</v>
       </c>
-      <c r="C557" t="s">
+      <c r="C570" t="s">
         <v>759</v>
       </c>
-      <c r="D557">
+      <c r="D570">
         <f>0.002</f>
         <v>2E-3</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B558" t="s">
+    <row r="571" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B571" t="s">
         <v>747</v>
       </c>
-      <c r="C558" t="s">
+      <c r="C571" t="s">
         <v>748</v>
       </c>
-      <c r="D558">
+      <c r="D571">
         <v>0.5</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B559" t="s">
+    <row r="572" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B572" t="s">
         <v>752</v>
       </c>
-      <c r="C559" t="s">
+      <c r="C572" t="s">
         <v>749</v>
       </c>
-      <c r="D559">
-        <f>4.605*D555/D558</f>
+      <c r="D572">
+        <f>4.605*D568/D571</f>
         <v>103.71478626000001</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B560" t="s">
+    <row r="573" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B573" t="s">
         <v>754</v>
       </c>
-      <c r="C560" t="s">
+      <c r="C573" t="s">
         <v>755</v>
       </c>
-      <c r="D560">
-        <f>D557/(D554*D556)</f>
+      <c r="D573">
+        <f>D570/(D567*D569)</f>
         <v>7.575757575757577</v>
       </c>
     </row>
-    <row r="561" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B561" t="s">
+    <row r="574" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B574" t="s">
         <v>760</v>
       </c>
-      <c r="D561">
-        <f>D555*D553/D559</f>
+      <c r="D574">
+        <f>D568*D566/D572</f>
         <v>0.18751521071687935</v>
       </c>
     </row>
-    <row r="562" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B562" t="s">
+    <row r="575" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B575" t="s">
         <v>761</v>
       </c>
-      <c r="D562">
-        <f>D561*D560</f>
+      <c r="D575">
+        <f>D574*D573</f>
         <v>1.4205697781581772</v>
       </c>
     </row>
-    <row r="563" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A563" s="42"/>
-      <c r="C563" t="s">
+    <row r="576" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A576" s="42"/>
+      <c r="C576" t="s">
         <v>634</v>
       </c>
-      <c r="D563" t="s">
+      <c r="D576" t="s">
         <v>635</v>
       </c>
-      <c r="E563" t="s">
+      <c r="E576" t="s">
         <v>637</v>
       </c>
-      <c r="F563" t="s">
+      <c r="F576" t="s">
         <v>636</v>
       </c>
-      <c r="G563" t="s">
+      <c r="G576" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="564" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A564" s="51" t="s">
+    <row r="577" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A577" s="54" t="s">
         <v>630</v>
       </c>
-      <c r="C564" t="s">
+      <c r="C577" t="s">
         <v>631</v>
       </c>
-      <c r="D564">
+      <c r="D577">
         <f>D2/D5</f>
         <v>5.6497175141242932</v>
       </c>
-      <c r="E564">
+      <c r="E577">
         <f>11*0.01</f>
         <v>0.11</v>
       </c>
-      <c r="F564">
+      <c r="F577">
         <v>1</v>
       </c>
-      <c r="G564">
+      <c r="G577">
         <v>22</v>
       </c>
-      <c r="H564">
+      <c r="H577">
         <v>10</v>
       </c>
-      <c r="I564">
+      <c r="I577">
         <v>10</v>
       </c>
-      <c r="J564">
+      <c r="J577">
         <v>10</v>
       </c>
     </row>
-    <row r="565" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A565" s="51"/>
-      <c r="C565" t="s">
+    <row r="578" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A578" s="54"/>
+      <c r="C578" t="s">
         <v>632</v>
       </c>
-      <c r="D565">
+      <c r="D578">
         <v>2</v>
       </c>
-      <c r="E565">
+      <c r="E578">
         <v>2</v>
       </c>
-      <c r="F565">
+      <c r="F578">
         <v>2</v>
       </c>
-      <c r="G565">
+      <c r="G578">
         <v>2</v>
       </c>
-      <c r="H565">
+      <c r="H578">
         <v>2</v>
       </c>
-      <c r="I565">
+      <c r="I578">
         <v>2</v>
       </c>
-      <c r="J565">
+      <c r="J578">
         <v>2</v>
       </c>
     </row>
-    <row r="566" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A566" s="51"/>
-      <c r="C566" t="s">
+    <row r="579" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A579" s="54"/>
+      <c r="C579" t="s">
         <v>633</v>
       </c>
-      <c r="D566">
+      <c r="D579">
         <v>5</v>
       </c>
-      <c r="E566">
+      <c r="E579">
         <v>5</v>
       </c>
-      <c r="F566">
+      <c r="F579">
         <v>5</v>
       </c>
-      <c r="G566">
+      <c r="G579">
         <v>5</v>
       </c>
-      <c r="H566">
+      <c r="H579">
         <v>5</v>
       </c>
-      <c r="I566">
+      <c r="I579">
         <v>5</v>
       </c>
-      <c r="J566">
+      <c r="J579">
         <v>5</v>
       </c>
     </row>
-    <row r="567" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A567" s="51"/>
-      <c r="C567" t="s">
+    <row r="580" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A580" s="54"/>
+      <c r="C580" t="s">
         <v>641</v>
       </c>
-      <c r="D567">
-        <f>0.0254*POWER(D564/(0.048*POWER(D566, 0.44)), 1/0.725)/(D565*1.378)</f>
+      <c r="D580">
+        <f>0.0254*POWER(D577/(0.048*POWER(D579, 0.44)), 1/0.725)/(D578*1.378)</f>
         <v>2.4923433704232472</v>
       </c>
-      <c r="E567">
-        <f t="shared" ref="E567:G567" si="20">0.0254*POWER(E564/(0.048*POWER(E566, 0.44)), 1/0.725)/(E565*1.378)</f>
+      <c r="E580">
+        <f t="shared" ref="E580:G580" si="59">0.0254*POWER(E577/(0.048*POWER(E579, 0.44)), 1/0.725)/(E578*1.378)</f>
         <v>1.0892125473680554E-2</v>
       </c>
-      <c r="F567">
-        <f t="shared" si="20"/>
+      <c r="F580">
+        <f t="shared" si="59"/>
         <v>0.22873341897835012</v>
       </c>
-      <c r="G567">
-        <f t="shared" si="20"/>
+      <c r="G580">
+        <f t="shared" si="59"/>
         <v>16.253508114154439</v>
       </c>
-      <c r="H567">
-        <f t="shared" ref="H567" si="21">0.0254*POWER(H564/(0.048*POWER(H566, 0.44)), 1/0.725)/(H565*1.378)</f>
+      <c r="H580">
+        <f t="shared" ref="H580" si="60">0.0254*POWER(H577/(0.048*POWER(H579, 0.44)), 1/0.725)/(H578*1.378)</f>
         <v>5.4782262733389961</v>
       </c>
-      <c r="I567">
-        <f t="shared" ref="I567:J567" si="22">0.0254*POWER(I564/(0.048*POWER(I566, 0.44)), 1/0.725)/(I565*1.378)</f>
+      <c r="I580">
+        <f t="shared" ref="I580:J580" si="61">0.0254*POWER(I577/(0.048*POWER(I579, 0.44)), 1/0.725)/(I578*1.378)</f>
         <v>5.4782262733389961</v>
       </c>
-      <c r="J567">
-        <f t="shared" si="22"/>
+      <c r="J580">
+        <f t="shared" si="61"/>
         <v>5.4782262733389961</v>
       </c>
     </row>
-    <row r="568" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A568" s="51"/>
-      <c r="C568" t="s">
+    <row r="581" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A581" s="54"/>
+      <c r="C581" t="s">
         <v>642</v>
       </c>
-      <c r="D568">
-        <f>0.0254*POWER(D564/(0.024*POWER(D566, 0.44)), 1/0.725)/(D565*1.378)</f>
+      <c r="D581">
+        <f>0.0254*POWER(D577/(0.024*POWER(D579, 0.44)), 1/0.725)/(D578*1.378)</f>
         <v>6.4836813405534928</v>
       </c>
-      <c r="E568">
-        <f t="shared" ref="E568:I568" si="23">0.0254*POWER(E564/(0.024*POWER(E566, 0.44)), 1/0.725)/(E565*1.378)</f>
+      <c r="E581">
+        <f t="shared" ref="E581:I581" si="62">0.0254*POWER(E577/(0.024*POWER(E579, 0.44)), 1/0.725)/(E578*1.378)</f>
         <v>2.8335209157266786E-2</v>
       </c>
-      <c r="F568">
-        <f t="shared" si="23"/>
+      <c r="F581">
+        <f t="shared" si="62"/>
         <v>0.59503622903255293</v>
       </c>
-      <c r="G568">
-        <f t="shared" si="23"/>
+      <c r="G581">
+        <f t="shared" si="62"/>
         <v>42.282523559497292</v>
       </c>
-      <c r="H568">
-        <f t="shared" si="23"/>
+      <c r="H581">
+        <f t="shared" si="62"/>
         <v>14.251276083899347</v>
       </c>
-      <c r="I568">
-        <f t="shared" si="23"/>
+      <c r="I581">
+        <f t="shared" si="62"/>
         <v>14.251276083899347</v>
       </c>
     </row>
-    <row r="569" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A569" s="51"/>
-      <c r="C569" t="s">
+    <row r="582" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A582" s="54"/>
+      <c r="C582" t="s">
         <v>640</v>
       </c>
-      <c r="D569">
+      <c r="D582">
         <v>8</v>
       </c>
-      <c r="E569">
+      <c r="E582">
         <v>1</v>
       </c>
-      <c r="F569">
+      <c r="F582">
         <v>1</v>
       </c>
-      <c r="G569">
+      <c r="G582">
         <v>8</v>
       </c>
-      <c r="H569">
+      <c r="H582">
         <v>8</v>
       </c>
     </row>
-    <row r="570" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A570" s="51"/>
-      <c r="C570" t="s">
+    <row r="583" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A583" s="54"/>
+      <c r="C583" t="s">
         <v>645</v>
       </c>
-      <c r="D570">
-        <f>POWER(D564/POWER(D569*(D565*1.378)/0.0254, 0.725)/0.048, 1/0.44)</f>
+      <c r="D583">
+        <f>POWER(D577/POWER(D582*(D578*1.378)/0.0254, 0.725)/0.048, 1/0.44)</f>
         <v>0.7318559619713908</v>
       </c>
-      <c r="E570">
-        <f t="shared" ref="E570:H570" si="24">POWER(E564/POWER(E569*(E565*1.378)/0.0254, 0.725)/0.048, 1/0.44)</f>
+      <c r="E583">
+        <f t="shared" ref="E583:H583" si="63">POWER(E577/POWER(E582*(E578*1.378)/0.0254, 0.725)/0.048, 1/0.44)</f>
         <v>2.9151906392472556E-3</v>
       </c>
-      <c r="F570">
-        <f t="shared" si="24"/>
+      <c r="F583">
+        <f t="shared" si="63"/>
         <v>0.43986554940209394</v>
       </c>
-      <c r="G570">
-        <f t="shared" si="24"/>
+      <c r="G583">
+        <f t="shared" si="63"/>
         <v>16.078094835159579</v>
       </c>
-      <c r="H570">
-        <f t="shared" si="24"/>
+      <c r="H583">
+        <f t="shared" si="63"/>
         <v>2.6791758539545092</v>
       </c>
     </row>
-    <row r="571" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A571" s="51"/>
-      <c r="C571" t="s">
+    <row r="584" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A584" s="54"/>
+      <c r="C584" t="s">
         <v>644</v>
       </c>
-      <c r="D571">
-        <f>POWER(D564/POWER(D569*(D565*1.378)/0.0254, 0.725)/0.024, 1/0.44)</f>
+      <c r="D584">
+        <f>POWER(D577/POWER(D582*(D578*1.378)/0.0254, 0.725)/0.024, 1/0.44)</f>
         <v>3.5365898499283999</v>
       </c>
-      <c r="E571">
-        <f t="shared" ref="E571:H571" si="25">POWER(E564/POWER(E569*(E565*1.378)/0.0254, 0.725)/0.024, 1/0.44)</f>
+      <c r="E584">
+        <f t="shared" ref="E584:H584" si="64">POWER(E577/POWER(E582*(E578*1.378)/0.0254, 0.725)/0.024, 1/0.44)</f>
         <v>1.4087244158805046E-2</v>
       </c>
-      <c r="F571">
-        <f t="shared" si="25"/>
+      <c r="F584">
+        <f t="shared" si="64"/>
         <v>2.1255877087593311</v>
       </c>
-      <c r="G571">
-        <f t="shared" si="25"/>
+      <c r="G584">
+        <f t="shared" si="64"/>
         <v>77.695106625959824</v>
       </c>
-      <c r="H571">
-        <f t="shared" si="25"/>
+      <c r="H584">
+        <f t="shared" si="64"/>
         <v>12.946736275462857</v>
       </c>
     </row>
-    <row r="572" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A572" s="51"/>
-      <c r="C572" t="s">
+    <row r="585" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A585" s="54"/>
+      <c r="C585" t="s">
         <v>639</v>
       </c>
-      <c r="D572">
+      <c r="D585">
         <v>100</v>
       </c>
-      <c r="E572">
+      <c r="E585">
         <v>200</v>
       </c>
-      <c r="F572">
+      <c r="F585">
         <v>120</v>
       </c>
-      <c r="G572">
+      <c r="G585">
         <v>100</v>
       </c>
-      <c r="H572">
+      <c r="H585">
         <v>100</v>
       </c>
     </row>
-    <row r="573" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A573" s="51"/>
-      <c r="C573" t="s">
+    <row r="586" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A586" s="54"/>
+      <c r="C586" t="s">
         <v>200</v>
       </c>
-      <c r="D573">
-        <f>(0.0000000168)*(D572/1000)/((D569/1000)*0.0000348*D565)</f>
+      <c r="D586">
+        <f>(0.0000000168)*(D585/1000)/((D582/1000)*0.0000348*D578)</f>
         <v>3.0172413793103452E-3</v>
       </c>
-      <c r="E573">
-        <f>(0.0000000168)*(E572/1000)/((E569/1000)*0.0000348*E565)</f>
+      <c r="E586">
+        <f>(0.0000000168)*(E585/1000)/((E582/1000)*0.0000348*E578)</f>
         <v>4.8275862068965524E-2</v>
       </c>
-      <c r="F573">
-        <f>(0.0000000168)*(F572/1000)/((F569/1000)*0.0000348*F565)</f>
+      <c r="F586">
+        <f>(0.0000000168)*(F585/1000)/((F582/1000)*0.0000348*F578)</f>
         <v>2.8965517241379312E-2</v>
       </c>
-      <c r="G573">
-        <f>(0.0000000168)*(G572/1000)/((G569/1000)*0.0000348*G565)</f>
+      <c r="G586">
+        <f>(0.0000000168)*(G585/1000)/((G582/1000)*0.0000348*G578)</f>
         <v>3.0172413793103452E-3</v>
       </c>
-      <c r="H573">
-        <f>(0.0000000168)*(H572/1000)/((H569/1000)*0.0000348*H565)</f>
+      <c r="H586">
+        <f>(0.0000000168)*(H585/1000)/((H582/1000)*0.0000348*H578)</f>
         <v>3.0172413793103452E-3</v>
       </c>
     </row>
-    <row r="574" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A574" s="51"/>
-      <c r="C574" t="s">
+    <row r="587" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A587" s="54"/>
+      <c r="C587" t="s">
         <v>643</v>
       </c>
-      <c r="D574">
-        <f>POWER(D564, 2)*D573</f>
+      <c r="D587">
+        <f>POWER(D577, 2)*D586</f>
         <v>9.6308256864577377E-2</v>
       </c>
-      <c r="E574">
-        <f>POWER(E564, 2)*E573</f>
+      <c r="E587">
+        <f>POWER(E577, 2)*E586</f>
         <v>5.8413793103448278E-4</v>
       </c>
-      <c r="F574">
-        <f>POWER(F564, 2)*F573</f>
+      <c r="F587">
+        <f>POWER(F577, 2)*F586</f>
         <v>2.8965517241379312E-2</v>
       </c>
-      <c r="G574">
-        <f>POWER(G564, 2)*G573</f>
+      <c r="G587">
+        <f>POWER(G577, 2)*G586</f>
         <v>1.460344827586207</v>
       </c>
-      <c r="H574">
-        <f>POWER(H564, 2)*H573</f>
+      <c r="H587">
+        <f>POWER(H577, 2)*H586</f>
         <v>0.30172413793103453</v>
       </c>
     </row>
-    <row r="575" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A575" s="51"/>
-      <c r="C575" t="s">
+    <row r="588" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A588" s="54"/>
+      <c r="C588" t="s">
         <v>646</v>
       </c>
-      <c r="D575">
-        <f>D564*D573</f>
+      <c r="D588">
+        <f>D577*D586</f>
         <v>1.7046561465030197E-2</v>
       </c>
-      <c r="E575">
-        <f t="shared" ref="E575:H575" si="26">E564*E573</f>
+      <c r="E588">
+        <f t="shared" ref="E588:H588" si="65">E577*E586</f>
         <v>5.3103448275862077E-3</v>
       </c>
-      <c r="F575">
-        <f t="shared" si="26"/>
+      <c r="F588">
+        <f t="shared" si="65"/>
         <v>2.8965517241379312E-2</v>
       </c>
-      <c r="G575">
-        <f t="shared" si="26"/>
+      <c r="G588">
+        <f t="shared" si="65"/>
         <v>6.6379310344827594E-2</v>
       </c>
-      <c r="H575">
-        <f t="shared" si="26"/>
+      <c r="H588">
+        <f t="shared" si="65"/>
         <v>3.0172413793103453E-2</v>
       </c>
     </row>
-    <row r="576" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A576" s="51"/>
-    </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A577" s="42"/>
-    </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A578" s="42"/>
-    </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A583" s="52" t="s">
+    <row r="589" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A589" s="54"/>
+    </row>
+    <row r="590" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A590" s="42"/>
+    </row>
+    <row r="591" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A591" s="42"/>
+    </row>
+    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A596" s="53" t="s">
         <v>719</v>
       </c>
-      <c r="C583" t="s">
+      <c r="C596" t="s">
         <v>720</v>
       </c>
-      <c r="D583" s="1">
+      <c r="D596" s="1">
         <v>1000000000</v>
       </c>
     </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A584" s="52"/>
-      <c r="C584" t="s">
+    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A597" s="53"/>
+      <c r="C597" t="s">
         <v>721</v>
       </c>
-      <c r="D584">
+      <c r="D597">
         <v>14</v>
       </c>
     </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A585" s="52"/>
-      <c r="C585" t="s">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A598" s="53"/>
+      <c r="C598" t="s">
         <v>219</v>
       </c>
-      <c r="D585" s="1">
-        <f>D583*D584</f>
+      <c r="D598" s="1">
+        <f>D596*D597</f>
         <v>14000000000</v>
       </c>
     </row>
-    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A586" s="52"/>
-      <c r="C586" t="s">
+    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A599" s="53"/>
+      <c r="C599" t="s">
         <v>722</v>
       </c>
-      <c r="D586">
+      <c r="D599">
         <f>2.5</f>
         <v>2.5</v>
       </c>
     </row>
-    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A587" s="52"/>
-      <c r="C587" t="s">
-        <v>723</v>
-      </c>
-      <c r="D587">
-        <f>D8/D586</f>
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A588" s="52"/>
-      <c r="C588" t="s">
-        <v>724</v>
-      </c>
-      <c r="D588">
-        <f>D585/D587</f>
-        <v>437500</v>
-      </c>
-    </row>
-    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A589" s="52"/>
-      <c r="C589" t="s">
-        <v>762</v>
-      </c>
-      <c r="D589" s="1">
-        <v>130000</v>
-      </c>
-    </row>
-    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A590" s="52"/>
-      <c r="C590" t="s">
-        <v>725</v>
-      </c>
-      <c r="D590" s="1">
-        <f>D8/D585</f>
-        <v>5.7142857142857145E-6</v>
-      </c>
-    </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A591" s="52"/>
-      <c r="C591" t="s">
-        <v>726</v>
-      </c>
-      <c r="D591" s="1">
-        <f>D590*D590*D583</f>
-        <v>3.2653061224489799E-2</v>
-      </c>
-    </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A592" s="52"/>
-      <c r="C592" t="s">
-        <v>727</v>
-      </c>
-      <c r="D592" s="1">
-        <f>D591*D584</f>
-        <v>0.45714285714285718</v>
-      </c>
-    </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A593" s="52"/>
-      <c r="C593" t="s">
-        <v>728</v>
-      </c>
-      <c r="D593" s="1">
-        <f>POWER(D590, 2)*D589</f>
-        <v>4.2448979591836746E-6</v>
-      </c>
-    </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A594" s="52"/>
-    </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C596" t="s">
-        <v>720</v>
-      </c>
-      <c r="D596" s="1">
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A597" s="52" t="s">
-        <v>729</v>
-      </c>
-      <c r="C597" t="s">
-        <v>721</v>
-      </c>
-      <c r="D597">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A598" s="52"/>
-      <c r="C598" t="s">
-        <v>219</v>
-      </c>
-      <c r="D598" s="1">
-        <f>D596*D597</f>
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A599" s="52"/>
-      <c r="C599" t="s">
-        <v>722</v>
-      </c>
-      <c r="D599">
-        <v>2.5</v>
-      </c>
-    </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A600" s="52"/>
+      <c r="A600" s="53"/>
       <c r="C600" t="s">
         <v>723</v>
       </c>
       <c r="D600">
-        <f>D12/D599</f>
-        <v>5600</v>
+        <f>D8/D599</f>
+        <v>32000</v>
       </c>
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A601" s="52"/>
+      <c r="A601" s="53"/>
       <c r="C601" t="s">
         <v>724</v>
       </c>
       <c r="D601">
         <f>D598/D600</f>
-        <v>17857.142857142859</v>
+        <v>437500</v>
       </c>
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A602" s="52"/>
+      <c r="A602" s="53"/>
       <c r="C602" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D602" s="1">
-        <v>20000</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A603" s="52"/>
+      <c r="A603" s="53"/>
       <c r="C603" t="s">
         <v>725</v>
       </c>
       <c r="D603" s="1">
-        <f>D12/D598</f>
-        <v>1.3999999999999999E-4</v>
+        <f>D8/D598</f>
+        <v>5.7142857142857145E-6</v>
       </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A604" s="52"/>
+      <c r="A604" s="53"/>
       <c r="C604" t="s">
         <v>726</v>
       </c>
       <c r="D604" s="1">
         <f>D603*D603*D596</f>
-        <v>1.9599999999999997</v>
+        <v>3.2653061224489799E-2</v>
       </c>
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A605" s="52"/>
+      <c r="A605" s="53"/>
       <c r="C605" t="s">
         <v>727</v>
       </c>
       <c r="D605" s="1">
         <f>D604*D597</f>
-        <v>1.9599999999999997</v>
+        <v>0.45714285714285718</v>
       </c>
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A606" s="52"/>
+      <c r="A606" s="53"/>
       <c r="C606" t="s">
         <v>728</v>
       </c>
       <c r="D606" s="1">
         <f>POWER(D603, 2)*D602</f>
+        <v>4.2448979591836746E-6</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A607" s="53"/>
+    </row>
+    <row r="609" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C609" t="s">
+        <v>720</v>
+      </c>
+      <c r="D609" s="1">
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="610" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A610" s="53" t="s">
+        <v>729</v>
+      </c>
+      <c r="C610" t="s">
+        <v>721</v>
+      </c>
+      <c r="D610">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="611" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A611" s="53"/>
+      <c r="C611" t="s">
+        <v>219</v>
+      </c>
+      <c r="D611" s="1">
+        <f>D609*D610</f>
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="612" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A612" s="53"/>
+      <c r="C612" t="s">
+        <v>722</v>
+      </c>
+      <c r="D612">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="613" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A613" s="53"/>
+      <c r="C613" t="s">
+        <v>723</v>
+      </c>
+      <c r="D613">
+        <f>D12/D612</f>
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="614" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A614" s="53"/>
+      <c r="C614" t="s">
+        <v>724</v>
+      </c>
+      <c r="D614">
+        <f>D611/D613</f>
+        <v>17857.142857142859</v>
+      </c>
+    </row>
+    <row r="615" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A615" s="53"/>
+      <c r="C615" t="s">
+        <v>763</v>
+      </c>
+      <c r="D615" s="1">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="616" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A616" s="53"/>
+      <c r="C616" t="s">
+        <v>725</v>
+      </c>
+      <c r="D616" s="1">
+        <f>D12/D611</f>
+        <v>1.3999999999999999E-4</v>
+      </c>
+    </row>
+    <row r="617" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A617" s="53"/>
+      <c r="C617" t="s">
+        <v>726</v>
+      </c>
+      <c r="D617" s="1">
+        <f>D616*D616*D609</f>
+        <v>1.9599999999999997</v>
+      </c>
+    </row>
+    <row r="618" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A618" s="53"/>
+      <c r="C618" t="s">
+        <v>727</v>
+      </c>
+      <c r="D618" s="1">
+        <f>D617*D610</f>
+        <v>1.9599999999999997</v>
+      </c>
+    </row>
+    <row r="619" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A619" s="53"/>
+      <c r="C619" t="s">
+        <v>728</v>
+      </c>
+      <c r="D619" s="1">
+        <f>POWER(D616, 2)*D615</f>
         <v>3.9199999999999993E-4</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C608" t="s">
+    <row r="621" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C621" t="s">
         <v>731</v>
       </c>
-      <c r="D608">
+      <c r="D621">
         <v>3</v>
       </c>
     </row>
-    <row r="609" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A609" s="51" t="s">
+    <row r="622" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A622" s="54" t="s">
         <v>730</v>
       </c>
-      <c r="C609" t="s">
+      <c r="C622" t="s">
         <v>732</v>
       </c>
-      <c r="D609">
+      <c r="D622">
         <v>550</v>
       </c>
-      <c r="E609" t="s">
+      <c r="E622" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="610" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A610" s="51"/>
-      <c r="C610" t="s">
+    <row r="623" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A623" s="54"/>
+      <c r="C623" t="s">
         <v>733</v>
       </c>
-      <c r="D610">
+      <c r="D623">
         <f>25.4*41.9*0.000001</f>
         <v>1.06426E-3</v>
       </c>
     </row>
-    <row r="611" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A611" s="51"/>
-      <c r="C611" t="s">
+    <row r="624" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A624" s="54"/>
+      <c r="C624" t="s">
         <v>735</v>
       </c>
-      <c r="D611">
-        <f>D610*D609*0.3048</f>
+      <c r="D624">
+        <f>D623*D622*0.3048</f>
         <v>0.17841254640000004</v>
       </c>
-      <c r="E611" t="s">
+      <c r="E624" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="612" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A612" s="51"/>
-      <c r="C612" t="s">
+    <row r="625" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A625" s="54"/>
+      <c r="C625" t="s">
         <v>736</v>
       </c>
-      <c r="D612">
-        <f>D611*50</f>
+      <c r="D625">
+        <f>D624*50</f>
         <v>8.9206273200000012</v>
       </c>
     </row>
-    <row r="613" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A613" s="51"/>
-    </row>
-    <row r="614" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A614" s="51"/>
-    </row>
-    <row r="615" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A615" s="51"/>
-    </row>
-    <row r="616" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A616" s="51"/>
-    </row>
-    <row r="617" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A617" s="51"/>
-    </row>
-    <row r="618" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A618" s="51"/>
-    </row>
-    <row r="619" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A619" s="51"/>
-    </row>
-    <row r="620" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A620" s="51"/>
-    </row>
-    <row r="621" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A621" s="51"/>
-    </row>
-    <row r="622" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C622" t="s">
+    <row r="626" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A626" s="54"/>
+    </row>
+    <row r="627" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A627" s="54"/>
+    </row>
+    <row r="628" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A628" s="54"/>
+    </row>
+    <row r="629" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A629" s="54"/>
+    </row>
+    <row r="630" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A630" s="54"/>
+    </row>
+    <row r="631" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A631" s="54"/>
+    </row>
+    <row r="632" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A632" s="54"/>
+    </row>
+    <row r="633" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A633" s="54"/>
+    </row>
+    <row r="634" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A634" s="54"/>
+    </row>
+    <row r="635" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C635" t="s">
         <v>765</v>
       </c>
-      <c r="E622" s="1">
+      <c r="E635" s="1">
         <f>D67</f>
         <v>0.15679999999999999</v>
       </c>
     </row>
-    <row r="623" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A623" s="51" t="s">
+    <row r="636" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A636" s="54" t="s">
         <v>764</v>
       </c>
-      <c r="C623" t="s">
+      <c r="C636" t="s">
         <v>766</v>
       </c>
-      <c r="E623">
+      <c r="E636">
         <f>D27</f>
         <v>0.7</v>
       </c>
     </row>
-    <row r="624" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A624" s="51"/>
-      <c r="C624" t="s">
+    <row r="637" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A637" s="54"/>
+      <c r="C637" t="s">
         <v>767</v>
       </c>
-      <c r="E624" s="1">
+      <c r="E637" s="1">
         <f>D163+D164</f>
         <v>3.2288346657248184</v>
       </c>
     </row>
-    <row r="625" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A625" s="51"/>
-      <c r="C625" t="s">
+    <row r="638" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A638" s="54"/>
+      <c r="C638" t="s">
         <v>768</v>
       </c>
-      <c r="E625" s="1">
-        <f>E622+E623+E624</f>
+      <c r="E638" s="1">
+        <f>E635+E636+E637</f>
         <v>4.0856346657248181</v>
       </c>
     </row>
-    <row r="626" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A626" s="51"/>
-    </row>
-    <row r="627" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A627" s="51"/>
-    </row>
-    <row r="628" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A628" s="51"/>
-      <c r="C628" t="s">
+    <row r="639" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A639" s="54"/>
+    </row>
+    <row r="640" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A640" s="54"/>
+    </row>
+    <row r="641" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A641" s="54"/>
+      <c r="C641" t="s">
         <v>4</v>
       </c>
-      <c r="E628">
+      <c r="E641">
         <v>2</v>
       </c>
     </row>
-    <row r="629" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A629" s="51"/>
-      <c r="C629" t="s">
+    <row r="642" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A642" s="54"/>
+      <c r="C642" t="s">
         <v>649</v>
       </c>
-      <c r="D629" t="s">
+      <c r="D642" t="s">
         <v>212</v>
       </c>
-      <c r="E629">
+      <c r="E642">
         <v>0.17399999999999999</v>
       </c>
     </row>
-    <row r="630" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A630" s="51"/>
-      <c r="C630" t="s">
+    <row r="643" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A643" s="54"/>
+      <c r="C643" t="s">
         <v>650</v>
       </c>
-      <c r="D630" t="s">
+      <c r="D643" t="s">
         <v>212</v>
       </c>
-      <c r="E630">
+      <c r="E643">
         <v>0.5</v>
       </c>
     </row>
-    <row r="631" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A631" s="51"/>
-      <c r="C631" t="s">
+    <row r="644" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A644" s="54"/>
+      <c r="C644" t="s">
         <v>647</v>
       </c>
-      <c r="D631" t="s">
+      <c r="D644" t="s">
         <v>658</v>
       </c>
-      <c r="E631">
-        <f>POWER(E629/2, 2)*PI()*E630</f>
+      <c r="E644">
+        <f>POWER(E642/2, 2)*PI()*E643</f>
         <v>1.1889357397510571E-2</v>
       </c>
     </row>
-    <row r="632" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A632" s="51"/>
-      <c r="C632" t="s">
+    <row r="645" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A645" s="54"/>
+      <c r="C645" t="s">
         <v>651</v>
       </c>
-      <c r="E632" s="1">
-        <f>E625</f>
+      <c r="E645" s="1">
+        <f>E638</f>
         <v>4.0856346657248181</v>
       </c>
     </row>
-    <row r="633" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A633" s="51"/>
-      <c r="C633" t="s">
+    <row r="646" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A646" s="54"/>
+      <c r="C646" t="s">
         <v>656</v>
       </c>
-      <c r="D633" t="s">
+      <c r="D646" t="s">
         <v>652</v>
       </c>
-      <c r="E633">
+      <c r="E646">
         <v>2300</v>
       </c>
     </row>
-    <row r="634" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A634" s="51"/>
-      <c r="C634" t="s">
+    <row r="647" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A647" s="54"/>
+      <c r="C647" t="s">
         <v>653</v>
       </c>
-      <c r="D634" t="s">
+      <c r="D647" t="s">
         <v>654</v>
       </c>
-      <c r="E634">
+      <c r="E647">
         <v>20</v>
       </c>
     </row>
-    <row r="635" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A635" s="51"/>
-      <c r="C635" t="s">
+    <row r="648" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A648" s="54"/>
+      <c r="C648" t="s">
         <v>655</v>
       </c>
-      <c r="D635" t="s">
+      <c r="D648" t="s">
         <v>657</v>
       </c>
-      <c r="E635">
+      <c r="E648">
         <v>800</v>
       </c>
     </row>
-    <row r="636" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A636" s="51"/>
-      <c r="C636" t="s">
+    <row r="649" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A649" s="54"/>
+      <c r="C649" t="s">
         <v>659</v>
       </c>
-      <c r="D636" t="s">
+      <c r="D649" t="s">
         <v>660</v>
       </c>
-      <c r="E636">
-        <f>E635*E631</f>
+      <c r="E649">
+        <f>E648*E644</f>
         <v>9.5114859180084572</v>
       </c>
     </row>
-    <row r="637" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A637" s="51"/>
-      <c r="C637" t="s">
+    <row r="650" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A650" s="54"/>
+      <c r="C650" t="s">
         <v>661</v>
       </c>
-      <c r="D637" t="s">
+      <c r="D650" t="s">
         <v>662</v>
       </c>
-      <c r="E637">
-        <f>E633*E636*E634</f>
+      <c r="E650">
+        <f>E646*E649*E647</f>
         <v>437528.35222838906</v>
       </c>
     </row>
-    <row r="638" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A638" s="51"/>
-      <c r="C638" t="s">
+    <row r="651" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A651" s="54"/>
+      <c r="C651" t="s">
         <v>663</v>
       </c>
-      <c r="D638" t="s">
+      <c r="D651" t="s">
         <v>342</v>
       </c>
-      <c r="E638">
-        <f>E637/E632</f>
+      <c r="E651">
+        <f>E650/E645</f>
         <v>107089.44583295695</v>
       </c>
     </row>
-    <row r="639" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A639" s="51"/>
-      <c r="C639" t="s">
+    <row r="652" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A652" s="54"/>
+      <c r="C652" t="s">
         <v>664</v>
       </c>
-      <c r="D639" t="s">
+      <c r="D652" t="s">
         <v>342</v>
       </c>
-      <c r="E639">
-        <f>E638/E628</f>
+      <c r="E652">
+        <f>E651/E641</f>
         <v>53544.722916478473</v>
       </c>
     </row>
-    <row r="640" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A640" s="51"/>
-      <c r="C640" t="s">
+    <row r="653" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A653" s="54"/>
+      <c r="C653" t="s">
         <v>665</v>
       </c>
-      <c r="D640" t="s">
+      <c r="D653" t="s">
         <v>666</v>
       </c>
-      <c r="E640">
-        <f>E631/E639</f>
+      <c r="E653">
+        <f>E644/E652</f>
         <v>2.2204536226765314E-7</v>
       </c>
     </row>
-    <row r="641" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A641" s="51"/>
-      <c r="C641" t="s">
+    <row r="654" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A654" s="54"/>
+      <c r="C654" t="s">
         <v>665</v>
       </c>
-      <c r="D641" t="s">
+      <c r="D654" t="s">
         <v>667</v>
       </c>
-      <c r="E641">
-        <f>(1000000)*E640</f>
+      <c r="E654">
+        <f>(1000000)*E653</f>
         <v>0.22204536226765315</v>
       </c>
     </row>
-    <row r="642" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A642" s="51"/>
-      <c r="C642" t="s">
+    <row r="655" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A655" s="54"/>
+      <c r="C655" t="s">
         <v>668</v>
       </c>
-      <c r="D642" t="s">
+      <c r="D655" t="s">
         <v>669</v>
       </c>
-      <c r="E642">
+      <c r="E655">
         <v>0.1</v>
       </c>
     </row>
-    <row r="643" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A643" s="51"/>
-      <c r="C643" t="s">
+    <row r="656" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A656" s="54"/>
+      <c r="C656" t="s">
         <v>670</v>
       </c>
-      <c r="D643" t="s">
+      <c r="D656" t="s">
         <v>213</v>
       </c>
-      <c r="E643">
-        <f>E640/E642</f>
+      <c r="E656">
+        <f>E653/E655</f>
         <v>2.2204536226765314E-6</v>
       </c>
     </row>
-    <row r="644" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A644" s="51"/>
-      <c r="C644" t="s">
+    <row r="657" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A657" s="54"/>
+      <c r="C657" t="s">
         <v>671</v>
       </c>
-      <c r="D644" t="s">
+      <c r="D657" t="s">
         <v>212</v>
       </c>
-      <c r="E644">
-        <f>2*POWER(E643/PI(), 0.5)</f>
+      <c r="E657">
+        <f>2*POWER(E656/PI(), 0.5)</f>
         <v>1.681418853124411E-3</v>
       </c>
     </row>
-    <row r="645" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A645" s="51"/>
-      <c r="C645" t="s">
+    <row r="658" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A658" s="54"/>
+      <c r="C658" t="s">
         <v>673</v>
       </c>
-      <c r="D645" t="s">
+      <c r="D658" t="s">
         <v>212</v>
       </c>
-      <c r="E645">
-        <f>CEILING(E644, 0.001)</f>
+      <c r="E658">
+        <f>CEILING(E657, 0.001)</f>
         <v>2E-3</v>
       </c>
     </row>
-    <row r="646" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A646" s="51"/>
-      <c r="C646" t="s">
+    <row r="659" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A659" s="54"/>
+      <c r="C659" t="s">
         <v>672</v>
       </c>
-      <c r="D646" t="s">
+      <c r="D659" t="s">
         <v>139</v>
       </c>
-      <c r="E646">
-        <f>E645*1000</f>
+      <c r="E659">
+        <f>E658*1000</f>
         <v>2</v>
       </c>
     </row>
-    <row r="647" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A647" s="51"/>
-      <c r="C647" t="s">
+    <row r="660" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A660" s="54"/>
+      <c r="C660" t="s">
         <v>678</v>
       </c>
-      <c r="D647" t="s">
+      <c r="D660" t="s">
         <v>139</v>
       </c>
-      <c r="E647">
+      <c r="E660">
         <v>9</v>
       </c>
     </row>
-    <row r="648" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A648" s="51"/>
-      <c r="C648" t="s">
+    <row r="661" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A661" s="54"/>
+      <c r="C661" t="s">
         <v>679</v>
       </c>
-      <c r="E648">
-        <f>E647/1000</f>
+      <c r="E661">
+        <f>E660/1000</f>
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="649" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C649" t="s">
+    <row r="662" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C662" t="s">
         <v>676</v>
       </c>
-      <c r="E649">
+      <c r="E662">
         <f>0.00604</f>
         <v>6.0400000000000002E-3</v>
       </c>
     </row>
-    <row r="650" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C650" t="s">
+    <row r="663" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C663" t="s">
         <v>675</v>
       </c>
-      <c r="E650">
-        <f>E649/E635</f>
+      <c r="E663">
+        <f>E662/E648</f>
         <v>7.5500000000000006E-6</v>
       </c>
     </row>
-    <row r="651" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C651" t="s">
+    <row r="664" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C664" t="s">
         <v>674</v>
       </c>
-      <c r="E651">
+      <c r="E664">
         <v>2300</v>
       </c>
     </row>
-    <row r="652" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C652" t="s">
+    <row r="665" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C665" t="s">
         <v>677</v>
       </c>
-      <c r="E652">
-        <f>E635*E642*E648/E649</f>
+      <c r="E665">
+        <f>E648*E655*E661/E662</f>
         <v>119.20529801324503</v>
       </c>
     </row>
-    <row r="653" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C653" t="s">
+    <row r="666" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C666" t="s">
         <v>680</v>
       </c>
-      <c r="E653" t="b">
-        <f>E652&lt;E651</f>
+      <c r="E666" t="b">
+        <f>E665&lt;E664</f>
         <v>1</v>
       </c>
     </row>
-    <row r="656" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B656" t="s">
+    <row r="669" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B669" t="s">
         <v>37</v>
       </c>
-      <c r="C656" t="s">
+      <c r="C669" t="s">
         <v>44</v>
       </c>
-      <c r="D656" t="s">
+      <c r="D669" t="s">
         <v>21</v>
       </c>
-      <c r="E656">
+      <c r="E669">
         <f>D5</f>
         <v>35.400000000000006</v>
       </c>
     </row>
-    <row r="657" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A657" s="51" t="s">
+    <row r="670" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A670" s="54" t="s">
         <v>785</v>
       </c>
-      <c r="B657" t="s">
+      <c r="B670" t="s">
         <v>494</v>
       </c>
-      <c r="C657" t="s">
+      <c r="C670" t="s">
         <v>495</v>
       </c>
-      <c r="D657" t="s">
+      <c r="D670" t="s">
         <v>21</v>
       </c>
-      <c r="E657">
+      <c r="E670">
         <f>D6</f>
         <v>38.099999999999994</v>
       </c>
     </row>
-    <row r="658" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A658" s="51"/>
-      <c r="B658" t="s">
+    <row r="671" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A671" s="54"/>
+      <c r="B671" t="s">
         <v>38</v>
       </c>
-      <c r="C658" t="s">
+      <c r="C671" t="s">
         <v>43</v>
       </c>
-      <c r="D658" t="s">
+      <c r="D671" t="s">
         <v>21</v>
       </c>
-      <c r="E658">
+      <c r="E671">
         <f>D7</f>
         <v>44.1</v>
       </c>
     </row>
-    <row r="659" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A659" s="51"/>
-      <c r="C659" t="s">
+    <row r="672" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A672" s="54"/>
+      <c r="C672" t="s">
         <v>786</v>
       </c>
-      <c r="D659" t="s">
+      <c r="D672" t="s">
         <v>20</v>
       </c>
-      <c r="E659">
+      <c r="E672">
         <v>3</v>
       </c>
     </row>
-    <row r="660" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A660" s="51"/>
-      <c r="C660" t="s">
+    <row r="673" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A673" s="54"/>
+      <c r="C673" t="s">
         <v>787</v>
       </c>
-      <c r="E660">
-        <f>(E658/E659)</f>
+      <c r="E673">
+        <f>(E671/E672)</f>
         <v>14.700000000000001</v>
       </c>
     </row>
-    <row r="661" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A661" s="51"/>
-      <c r="C661" t="s">
+    <row r="674" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A674" s="54"/>
+      <c r="C674" t="s">
         <v>788</v>
       </c>
-      <c r="E661">
-        <f>E656/E659</f>
+      <c r="E674">
+        <f>E669/E672</f>
         <v>11.800000000000002</v>
       </c>
     </row>
-    <row r="662" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A662" s="51"/>
-      <c r="C662" t="s">
+    <row r="675" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A675" s="54"/>
+      <c r="C675" t="s">
         <v>789</v>
       </c>
-      <c r="E662">
-        <f>E657/E659</f>
+      <c r="E675">
+        <f>E670/E672</f>
         <v>12.699999999999998</v>
       </c>
     </row>
-    <row r="663" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A663" s="51"/>
-      <c r="C663" t="s">
+    <row r="676" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A676" s="54"/>
+      <c r="C676" t="s">
         <v>790</v>
       </c>
-      <c r="E663">
+      <c r="E676">
         <f>12</f>
         <v>12</v>
       </c>
     </row>
-    <row r="664" spans="1:15" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A664" s="51"/>
-      <c r="C664" t="s">
+    <row r="677" spans="1:15" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A677" s="54"/>
+      <c r="C677" t="s">
         <v>791</v>
       </c>
-      <c r="E664">
-        <f>E658*E658/E663</f>
+      <c r="E677">
+        <f>E671*E671/E676</f>
         <v>162.06750000000002</v>
       </c>
-      <c r="G664" s="18" t="s">
+      <c r="G677" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="H664" s="48" t="s">
+      <c r="H677" s="48" t="s">
         <v>797</v>
       </c>
-      <c r="I664" s="48" t="s">
+      <c r="I677" s="48" t="s">
         <v>800</v>
       </c>
-      <c r="J664" s="48" t="s">
+      <c r="J677" s="48" t="s">
         <v>799</v>
       </c>
-      <c r="K664" s="48" t="s">
+      <c r="K677" s="48" t="s">
         <v>798</v>
       </c>
-      <c r="L664" s="48" t="s">
+      <c r="L677" s="48" t="s">
         <v>801</v>
       </c>
-      <c r="M664" s="48" t="s">
+      <c r="M677" s="48" t="s">
         <v>802</v>
       </c>
-      <c r="N664" s="48" t="s">
+      <c r="N677" s="48" t="s">
         <v>804</v>
       </c>
-      <c r="O664" s="47"/>
-    </row>
-    <row r="665" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A665" s="51"/>
-      <c r="C665" t="s">
+      <c r="O677" s="47"/>
+    </row>
+    <row r="678" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A678" s="54"/>
+      <c r="C678" t="s">
         <v>792</v>
       </c>
-      <c r="E665">
+      <c r="E678">
         <f>6</f>
         <v>6</v>
       </c>
-      <c r="G665" s="18">
+      <c r="G678" s="18">
         <v>1</v>
       </c>
-      <c r="H665" s="18">
-        <f>E658/G665</f>
+      <c r="H678" s="18">
+        <f>E671/G678</f>
         <v>44.1</v>
       </c>
-      <c r="I665" s="18">
-        <f>H665*H665*G665</f>
+      <c r="I678" s="18">
+        <f>H678*H678*G678</f>
         <v>1944.8100000000002</v>
       </c>
-      <c r="J665" s="18">
-        <f>I665/2</f>
+      <c r="J678" s="18">
+        <f>I678/2</f>
         <v>972.40500000000009</v>
       </c>
-      <c r="K665" s="18">
-        <f>E656/G665</f>
+      <c r="K678" s="18">
+        <f>E669/G678</f>
         <v>35.400000000000006</v>
       </c>
-      <c r="L665" s="18">
-        <f>E656*E656/G665</f>
+      <c r="L678" s="18">
+        <f>E669*E669/G678</f>
         <v>1253.1600000000003</v>
       </c>
-      <c r="M665" s="18">
-        <f>L665/2</f>
+      <c r="M678" s="18">
+        <f>L678/2</f>
         <v>626.58000000000015</v>
       </c>
-      <c r="N665" s="47"/>
-    </row>
-    <row r="666" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A666" s="51"/>
-      <c r="C666" t="s">
+      <c r="N678" s="47"/>
+    </row>
+    <row r="679" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A679" s="54"/>
+      <c r="C679" t="s">
         <v>793</v>
       </c>
-      <c r="E666">
+      <c r="E679">
         <v>2</v>
       </c>
-      <c r="G666" s="18">
+      <c r="G679" s="18">
         <v>2</v>
       </c>
-      <c r="H666" s="18">
-        <f>E658/G666</f>
+      <c r="H679" s="18">
+        <f>E671/G679</f>
         <v>22.05</v>
       </c>
-      <c r="I666" s="18">
-        <f t="shared" ref="I666:I678" si="27">H666*H666*G666</f>
+      <c r="I679" s="18">
+        <f t="shared" ref="I679:I691" si="66">H679*H679*G679</f>
         <v>972.40500000000009</v>
       </c>
-      <c r="J666" s="18">
-        <f>I666/2</f>
+      <c r="J679" s="18">
+        <f>I679/2</f>
         <v>486.20250000000004</v>
       </c>
-      <c r="K666" s="18">
-        <f>E656/G666</f>
+      <c r="K679" s="18">
+        <f>E669/G679</f>
         <v>17.700000000000003</v>
       </c>
-      <c r="L666" s="18">
-        <f>E656*E656/G666</f>
+      <c r="L679" s="18">
+        <f>E669*E669/G679</f>
         <v>626.58000000000015</v>
       </c>
-      <c r="M666" s="18">
-        <f>L666/2</f>
+      <c r="M679" s="18">
+        <f>L679/2</f>
         <v>313.29000000000008</v>
       </c>
-      <c r="N666" s="47"/>
-    </row>
-    <row r="667" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A667" s="51"/>
-      <c r="C667" t="s">
+      <c r="N679" s="47"/>
+    </row>
+    <row r="680" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A680" s="54"/>
+      <c r="C680" t="s">
         <v>794</v>
       </c>
-      <c r="E667">
-        <f xml:space="preserve"> E665*E666</f>
+      <c r="E680">
+        <f xml:space="preserve"> E678*E679</f>
         <v>12</v>
       </c>
-      <c r="G667" s="18">
+      <c r="G680" s="18">
         <v>3</v>
       </c>
-      <c r="H667" s="18">
-        <f>E658/G667</f>
+      <c r="H680" s="18">
+        <f>E671/G680</f>
         <v>14.700000000000001</v>
       </c>
-      <c r="I667" s="18">
-        <f t="shared" si="27"/>
+      <c r="I680" s="18">
+        <f t="shared" si="66"/>
         <v>648.2700000000001</v>
       </c>
-      <c r="J667" s="18">
-        <f>I667/2</f>
+      <c r="J680" s="18">
+        <f>I680/2</f>
         <v>324.13500000000005</v>
       </c>
-      <c r="K667" s="18">
-        <f>E656/G667</f>
+      <c r="K680" s="18">
+        <f>E669/G680</f>
         <v>11.800000000000002</v>
       </c>
-      <c r="L667" s="18">
-        <f>E656*E656/G667</f>
+      <c r="L680" s="18">
+        <f>E669*E669/G680</f>
         <v>417.72000000000008</v>
       </c>
-      <c r="M667" s="18">
-        <f>L667/2</f>
+      <c r="M680" s="18">
+        <f>L680/2</f>
         <v>208.86000000000004</v>
       </c>
     </row>
-    <row r="668" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A668" s="51"/>
-      <c r="G668" s="18">
+    <row r="681" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A681" s="54"/>
+      <c r="G681" s="18">
         <v>4</v>
       </c>
-      <c r="H668" s="18">
-        <f>E658/G668</f>
+      <c r="H681" s="18">
+        <f>E671/G681</f>
         <v>11.025</v>
       </c>
-      <c r="I668" s="18">
-        <f t="shared" si="27"/>
+      <c r="I681" s="18">
+        <f t="shared" si="66"/>
         <v>486.20250000000004</v>
       </c>
-      <c r="J668" s="18">
-        <f t="shared" ref="J668:J678" si="28">I668/2</f>
+      <c r="J681" s="18">
+        <f t="shared" ref="J681:J691" si="67">I681/2</f>
         <v>243.10125000000002</v>
       </c>
-      <c r="K668" s="18">
-        <f>E656/G668</f>
+      <c r="K681" s="18">
+        <f>E669/G681</f>
         <v>8.8500000000000014</v>
       </c>
-      <c r="L668" s="18">
-        <f>E656*E656/G668</f>
+      <c r="L681" s="18">
+        <f>E669*E669/G681</f>
         <v>313.29000000000008</v>
       </c>
-      <c r="M668" s="18">
-        <f t="shared" ref="M668:M678" si="29">L668/2</f>
+      <c r="M681" s="18">
+        <f t="shared" ref="M681:M691" si="68">L681/2</f>
         <v>156.64500000000004</v>
       </c>
     </row>
-    <row r="669" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A669" s="51"/>
-      <c r="C669" t="s">
+    <row r="682" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A682" s="54"/>
+      <c r="C682" t="s">
         <v>795</v>
       </c>
-      <c r="E669">
-        <f>(POWER(E658,2))/(200*2)</f>
+      <c r="E682">
+        <f>(POWER(E671,2))/(200*2)</f>
         <v>4.862025</v>
       </c>
-      <c r="G669" s="18">
+      <c r="G682" s="18">
         <v>5</v>
       </c>
-      <c r="H669" s="18">
-        <f>E658/G669</f>
+      <c r="H682" s="18">
+        <f>E671/G682</f>
         <v>8.82</v>
       </c>
-      <c r="I669" s="18">
-        <f t="shared" si="27"/>
+      <c r="I682" s="18">
+        <f t="shared" si="66"/>
         <v>388.96199999999999</v>
       </c>
-      <c r="J669" s="18">
-        <f t="shared" si="28"/>
+      <c r="J682" s="18">
+        <f t="shared" si="67"/>
         <v>194.48099999999999</v>
       </c>
-      <c r="K669" s="18">
-        <f>E656/G669</f>
+      <c r="K682" s="18">
+        <f>E669/G682</f>
         <v>7.080000000000001</v>
       </c>
-      <c r="L669" s="18">
-        <f>E656*E656/G669</f>
+      <c r="L682" s="18">
+        <f>E669*E669/G682</f>
         <v>250.63200000000006</v>
       </c>
-      <c r="M669" s="18">
-        <f t="shared" si="29"/>
+      <c r="M682" s="18">
+        <f t="shared" si="68"/>
         <v>125.31600000000003</v>
       </c>
-      <c r="N669" t="s">
+      <c r="N682" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="670" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A670" s="51"/>
-      <c r="C670" t="s">
+    <row r="683" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A683" s="54"/>
+      <c r="C683" t="s">
         <v>796</v>
       </c>
-      <c r="E670">
-        <f>E658/E669</f>
+      <c r="E683">
+        <f>E671/E682</f>
         <v>9.0702947845804989</v>
       </c>
-      <c r="G670" s="18">
+      <c r="G683" s="18">
         <v>6</v>
       </c>
-      <c r="H670" s="18">
-        <f>E658/G670</f>
+      <c r="H683" s="18">
+        <f>E671/G683</f>
         <v>7.3500000000000005</v>
       </c>
-      <c r="I670" s="18">
-        <f t="shared" si="27"/>
+      <c r="I683" s="18">
+        <f t="shared" si="66"/>
         <v>324.13500000000005</v>
       </c>
-      <c r="J670" s="18">
-        <f t="shared" si="28"/>
+      <c r="J683" s="18">
+        <f t="shared" si="67"/>
         <v>162.06750000000002</v>
       </c>
-      <c r="K670" s="18">
-        <f>E656/G670</f>
+      <c r="K683" s="18">
+        <f>E669/G683</f>
         <v>5.9000000000000012</v>
       </c>
-      <c r="L670" s="18">
-        <f>E656*E656/G670</f>
+      <c r="L683" s="18">
+        <f>E669*E669/G683</f>
         <v>208.86000000000004</v>
       </c>
-      <c r="M670" s="18">
-        <f t="shared" si="29"/>
+      <c r="M683" s="18">
+        <f t="shared" si="68"/>
         <v>104.43000000000002</v>
       </c>
-      <c r="N670" t="s">
+      <c r="N683" t="s">
         <v>805</v>
       </c>
     </row>
-    <row r="671" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A671" s="51"/>
-      <c r="G671" s="18">
+    <row r="684" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A684" s="54"/>
+      <c r="G684" s="18">
         <v>7</v>
       </c>
-      <c r="H671" s="18">
-        <f>E658/G671</f>
+      <c r="H684" s="18">
+        <f>E671/G684</f>
         <v>6.3</v>
       </c>
-      <c r="I671" s="18">
-        <f t="shared" si="27"/>
+      <c r="I684" s="18">
+        <f t="shared" si="66"/>
         <v>277.83</v>
       </c>
-      <c r="J671" s="18">
-        <f t="shared" si="28"/>
+      <c r="J684" s="18">
+        <f t="shared" si="67"/>
         <v>138.91499999999999</v>
       </c>
-      <c r="K671" s="18">
-        <f>E656/G671</f>
+      <c r="K684" s="18">
+        <f>E669/G684</f>
         <v>5.0571428571428578</v>
       </c>
-      <c r="L671" s="18">
-        <f>E656*E656/G671</f>
+      <c r="L684" s="18">
+        <f>E669*E669/G684</f>
         <v>179.02285714285719</v>
       </c>
-      <c r="M671" s="18">
-        <f t="shared" si="29"/>
+      <c r="M684" s="18">
+        <f t="shared" si="68"/>
         <v>89.511428571428596</v>
       </c>
-      <c r="N671" t="s">
+      <c r="N684" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="672" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G672" s="18">
+    <row r="685" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G685" s="18">
         <v>8</v>
       </c>
-      <c r="H672" s="18">
-        <f>E658/G672</f>
+      <c r="H685" s="18">
+        <f>E671/G685</f>
         <v>5.5125000000000002</v>
       </c>
-      <c r="I672" s="18">
-        <f t="shared" si="27"/>
+      <c r="I685" s="18">
+        <f t="shared" si="66"/>
         <v>243.10125000000002</v>
       </c>
-      <c r="J672" s="18">
-        <f t="shared" si="28"/>
+      <c r="J685" s="18">
+        <f t="shared" si="67"/>
         <v>121.55062500000001</v>
       </c>
-      <c r="K672" s="18">
-        <f>E656/G672</f>
+      <c r="K685" s="18">
+        <f>E669/G685</f>
         <v>4.4250000000000007</v>
       </c>
-      <c r="L672" s="18">
-        <f>E656*E656/G672</f>
+      <c r="L685" s="18">
+        <f>E669*E669/G685</f>
         <v>156.64500000000004</v>
       </c>
-      <c r="M672" s="18">
-        <f t="shared" si="29"/>
+      <c r="M685" s="18">
+        <f t="shared" si="68"/>
         <v>78.322500000000019</v>
       </c>
-      <c r="N672" t="s">
+      <c r="N685" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="673" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G673" s="18">
+    <row r="686" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G686" s="18">
         <v>9</v>
       </c>
-      <c r="H673" s="18">
-        <f>E658/G673</f>
+      <c r="H686" s="18">
+        <f>E671/G686</f>
         <v>4.9000000000000004</v>
       </c>
-      <c r="I673" s="18">
-        <f t="shared" si="27"/>
+      <c r="I686" s="18">
+        <f t="shared" si="66"/>
         <v>216.09000000000003</v>
       </c>
-      <c r="J673" s="18">
-        <f t="shared" si="28"/>
+      <c r="J686" s="18">
+        <f t="shared" si="67"/>
         <v>108.04500000000002</v>
       </c>
-      <c r="K673" s="18">
-        <f>E656/G673</f>
+      <c r="K686" s="18">
+        <f>E669/G686</f>
         <v>3.933333333333334</v>
       </c>
-      <c r="L673" s="18">
-        <f>E656*E656/G673</f>
+      <c r="L686" s="18">
+        <f>E669*E669/G686</f>
         <v>139.24000000000004</v>
       </c>
-      <c r="M673" s="18">
-        <f t="shared" si="29"/>
+      <c r="M686" s="18">
+        <f t="shared" si="68"/>
         <v>69.620000000000019</v>
       </c>
-      <c r="N673" t="s">
+      <c r="N686" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="674" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G674" s="18">
+    <row r="687" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G687" s="18">
         <v>10</v>
       </c>
-      <c r="H674" s="18">
-        <f>E658/G674</f>
+      <c r="H687" s="18">
+        <f>E671/G687</f>
         <v>4.41</v>
       </c>
-      <c r="I674" s="18">
-        <f t="shared" si="27"/>
+      <c r="I687" s="18">
+        <f t="shared" si="66"/>
         <v>194.48099999999999</v>
       </c>
-      <c r="J674" s="18">
-        <f t="shared" si="28"/>
+      <c r="J687" s="18">
+        <f t="shared" si="67"/>
         <v>97.240499999999997</v>
       </c>
-      <c r="K674" s="18">
-        <f>E656/G674</f>
+      <c r="K687" s="18">
+        <f>E669/G687</f>
         <v>3.5400000000000005</v>
       </c>
-      <c r="L674" s="18">
-        <f>E656*E656/G674</f>
+      <c r="L687" s="18">
+        <f>E669*E669/G687</f>
         <v>125.31600000000003</v>
       </c>
-      <c r="M674" s="18">
-        <f t="shared" si="29"/>
+      <c r="M687" s="18">
+        <f t="shared" si="68"/>
         <v>62.658000000000015</v>
       </c>
-      <c r="N674" t="s">
+      <c r="N687" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="675" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G675" s="18">
+    <row r="688" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G688" s="18">
         <v>11</v>
       </c>
-      <c r="H675" s="18">
-        <f>E658/G675</f>
+      <c r="H688" s="18">
+        <f>E671/G688</f>
         <v>4.0090909090909088</v>
       </c>
-      <c r="I675" s="18">
-        <f t="shared" si="27"/>
+      <c r="I688" s="18">
+        <f t="shared" si="66"/>
         <v>176.80090909090904</v>
       </c>
-      <c r="J675" s="18">
-        <f t="shared" si="28"/>
+      <c r="J688" s="18">
+        <f t="shared" si="67"/>
         <v>88.400454545454522</v>
       </c>
-      <c r="K675" s="18">
-        <f>E656/G675</f>
+      <c r="K688" s="18">
+        <f>E669/G688</f>
         <v>3.2181818181818187</v>
       </c>
-      <c r="L675" s="18">
-        <f>E656*E656/G675</f>
+      <c r="L688" s="18">
+        <f>E669*E669/G688</f>
         <v>113.92363636363639</v>
       </c>
-      <c r="M675" s="18">
-        <f t="shared" si="29"/>
+      <c r="M688" s="18">
+        <f t="shared" si="68"/>
         <v>56.961818181818195</v>
       </c>
-      <c r="N675" t="s">
+      <c r="N688" t="s">
         <v>810</v>
       </c>
     </row>
-    <row r="676" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G676" s="18">
+    <row r="689" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G689" s="18">
         <v>12</v>
       </c>
-      <c r="H676" s="18">
-        <f>E658/G676</f>
+      <c r="H689" s="18">
+        <f>E671/G689</f>
         <v>3.6750000000000003</v>
       </c>
-      <c r="I676" s="18">
-        <f t="shared" si="27"/>
+      <c r="I689" s="18">
+        <f t="shared" si="66"/>
         <v>162.06750000000002</v>
       </c>
-      <c r="J676" s="18">
-        <f t="shared" si="28"/>
+      <c r="J689" s="18">
+        <f t="shared" si="67"/>
         <v>81.033750000000012</v>
       </c>
-      <c r="K676" s="18">
-        <f>E656/G676</f>
+      <c r="K689" s="18">
+        <f>E669/G689</f>
         <v>2.9500000000000006</v>
       </c>
-      <c r="L676" s="18">
-        <f>E656*E656/G676</f>
+      <c r="L689" s="18">
+        <f>E669*E669/G689</f>
         <v>104.43000000000002</v>
       </c>
-      <c r="M676" s="18">
-        <f t="shared" si="29"/>
+      <c r="M689" s="18">
+        <f t="shared" si="68"/>
         <v>52.215000000000011</v>
       </c>
-      <c r="N676" t="s">
+      <c r="N689" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="677" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G677" s="18">
+    <row r="690" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G690" s="18">
         <v>13</v>
       </c>
-      <c r="H677" s="18">
-        <f>E658/G677</f>
+      <c r="H690" s="18">
+        <f>E671/G690</f>
         <v>3.3923076923076922</v>
       </c>
-      <c r="I677" s="18">
-        <f t="shared" si="27"/>
+      <c r="I690" s="18">
+        <f t="shared" si="66"/>
         <v>149.60076923076923</v>
       </c>
-      <c r="J677" s="18">
-        <f t="shared" si="28"/>
+      <c r="J690" s="18">
+        <f t="shared" si="67"/>
         <v>74.800384615384615</v>
       </c>
-      <c r="K677" s="18">
-        <f>E656/G677</f>
+      <c r="K690" s="18">
+        <f>E669/G690</f>
         <v>2.7230769230769236</v>
       </c>
-      <c r="L677" s="18">
-        <f>E656*E656/G677</f>
+      <c r="L690" s="18">
+        <f>E669*E669/G690</f>
         <v>96.396923076923102</v>
       </c>
-      <c r="M677" s="18">
-        <f t="shared" si="29"/>
+      <c r="M690" s="18">
+        <f t="shared" si="68"/>
         <v>48.198461538461551</v>
       </c>
-      <c r="N677" t="s">
+      <c r="N690" t="s">
         <v>811</v>
       </c>
     </row>
-    <row r="678" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G678" s="18">
+    <row r="691" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="G691" s="18">
         <v>14</v>
       </c>
-      <c r="H678" s="18">
-        <f>E658/G678</f>
+      <c r="H691" s="18">
+        <f>E671/G691</f>
         <v>3.15</v>
       </c>
-      <c r="I678" s="18">
-        <f t="shared" si="27"/>
+      <c r="I691" s="18">
+        <f t="shared" si="66"/>
         <v>138.91499999999999</v>
       </c>
-      <c r="J678" s="18">
-        <f t="shared" si="28"/>
+      <c r="J691" s="18">
+        <f t="shared" si="67"/>
         <v>69.457499999999996</v>
       </c>
-      <c r="K678" s="18">
-        <f>E656/G678</f>
+      <c r="K691" s="18">
+        <f>E669/G691</f>
         <v>2.5285714285714289</v>
       </c>
-      <c r="L678" s="18">
-        <f>E656*E656/G678</f>
+      <c r="L691" s="18">
+        <f>E669*E669/G691</f>
         <v>89.511428571428596</v>
       </c>
-      <c r="M678" s="18">
-        <f t="shared" si="29"/>
+      <c r="M691" s="18">
+        <f t="shared" si="68"/>
         <v>44.755714285714298</v>
       </c>
-      <c r="N678" t="s">
+      <c r="N691" t="s">
         <v>813</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A670:A684"/>
+    <mergeCell ref="A364:A376"/>
+    <mergeCell ref="A377:A380"/>
+    <mergeCell ref="A596:A607"/>
+    <mergeCell ref="A610:A619"/>
+    <mergeCell ref="A577:A589"/>
+    <mergeCell ref="A491:A562"/>
     <mergeCell ref="A31:A59"/>
-    <mergeCell ref="A623:A648"/>
+    <mergeCell ref="A636:A661"/>
     <mergeCell ref="A228:A279"/>
     <mergeCell ref="G19:J22"/>
     <mergeCell ref="G29:K34"/>
@@ -12895,14 +14947,7 @@
     <mergeCell ref="A98:A169"/>
     <mergeCell ref="A171:A226"/>
     <mergeCell ref="A303:A315"/>
-    <mergeCell ref="A609:A621"/>
-    <mergeCell ref="A657:A671"/>
-    <mergeCell ref="A364:A376"/>
-    <mergeCell ref="A377:A380"/>
-    <mergeCell ref="A583:A594"/>
-    <mergeCell ref="A597:A606"/>
-    <mergeCell ref="A479:A549"/>
-    <mergeCell ref="A564:A576"/>
+    <mergeCell ref="A622:A634"/>
   </mergeCells>
   <conditionalFormatting sqref="D110">
     <cfRule type="cellIs" dxfId="9" priority="9" operator="notEqual">
@@ -12912,7 +14957,7 @@
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E653">
+  <conditionalFormatting sqref="E666">
     <cfRule type="cellIs" dxfId="7" priority="7" operator="notEqual">
       <formula>TRUE</formula>
     </cfRule>
@@ -13196,17 +15241,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="57" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="55"/>
+      <c r="B1" s="57"/>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C18" s="56" t="s">
+      <c r="C18" s="58" t="s">
         <v>167</v>
       </c>
-      <c r="D18" s="57"/>
-      <c r="E18" s="58"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="60"/>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C19" s="18" t="s">
@@ -13400,17 +15445,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="57" t="s">
         <v>166</v>
       </c>
-      <c r="B1" s="55"/>
+      <c r="B1" s="57"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="58" t="s">
         <v>167</v>
       </c>
-      <c r="C17" s="57"/>
-      <c r="D17" s="58"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="60"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B18" s="18" t="s">
@@ -13663,17 +15708,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="55"/>
+      <c r="B1" s="57"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="58" t="s">
         <v>167</v>
       </c>
-      <c r="C17" s="57"/>
-      <c r="D17" s="58"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="60"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B18" s="18" t="s">

--- a/Spreadsheets/BasicCalculations.xlsx
+++ b/Spreadsheets/BasicCalculations.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="899">
   <si>
     <t>N stages required</t>
   </si>
@@ -2680,6 +2680,69 @@
   </si>
   <si>
     <t>Vs acceptible</t>
+  </si>
+  <si>
+    <t>Desired output voltage</t>
+  </si>
+  <si>
+    <t>Vout</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>Do not change</t>
+  </si>
+  <si>
+    <t>Required R2 value</t>
+  </si>
+  <si>
+    <t>Minimum desired output voltage</t>
+  </si>
+  <si>
+    <t>Vout_min</t>
+  </si>
+  <si>
+    <t>Vout_max</t>
+  </si>
+  <si>
+    <t>Maximum desired output voltage</t>
+  </si>
+  <si>
+    <t>Required R2 value for minimum output voltage</t>
+  </si>
+  <si>
+    <t>Requried R2 value for maximum output voltage</t>
+  </si>
+  <si>
+    <t>R2_max</t>
+  </si>
+  <si>
+    <t>R2_min</t>
+  </si>
+  <si>
+    <t>Cff</t>
+  </si>
+  <si>
+    <t>LM2956HV-adj for 3.3v</t>
+  </si>
+  <si>
+    <t>LM2956HV-adj for 5v</t>
+  </si>
+  <si>
+    <t>LM2956HV-adj for 2-30v</t>
+  </si>
+  <si>
+    <t>LM2956HV-adj for 9-15v</t>
+  </si>
+  <si>
+    <t>LM2956HV-adj for 10v</t>
+  </si>
+  <si>
+    <t>Feedforward capacitor given by equations on https://e2e.ti.com/support/power-management-group/power-management/f/power-management-forum/898296/lm2596-feedforward-capacitor-selection#:~:text=Andy%20Chen%20over%206%20years,performance%20in%20the%20actual%20application.</t>
   </si>
 </sst>
 </file>
@@ -2884,7 +2947,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2973,10 +3036,13 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -4373,7 +4439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CX691"/>
+  <dimension ref="A1:CX715"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" customWidth="1"/>
@@ -4620,15 +4686,15 @@
       <c r="C19" s="8"/>
       <c r="D19" s="13"/>
       <c r="E19" s="8"/>
-      <c r="G19" s="55" t="s">
+      <c r="G19" s="56" t="s">
         <v>589</v>
       </c>
-      <c r="H19" s="55"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="55"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="56"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="53" t="s">
+      <c r="A20" s="55" t="s">
         <v>103</v>
       </c>
       <c r="B20" t="s">
@@ -4643,13 +4709,13 @@
       <c r="E20" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="55"/>
-      <c r="H20" s="55"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="55"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="56"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="53"/>
+      <c r="A21" s="55"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6" t="s">
         <v>3</v>
@@ -4661,13 +4727,13 @@
       <c r="E21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G21" s="55"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="55"/>
-      <c r="J21" s="55"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="56"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="53"/>
+      <c r="A22" s="55"/>
       <c r="B22" t="s">
         <v>67</v>
       </c>
@@ -4677,13 +4743,13 @@
       <c r="D22">
         <v>0.1</v>
       </c>
-      <c r="G22" s="55"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="55"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="56"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="53"/>
+      <c r="A23" s="55"/>
       <c r="B23" s="6"/>
       <c r="C23" s="12" t="s">
         <v>72</v>
@@ -4695,7 +4761,7 @@
       <c r="E23" s="6"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="53"/>
+      <c r="A24" s="55"/>
       <c r="C24" t="s">
         <v>7</v>
       </c>
@@ -4704,7 +4770,7 @@
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="53"/>
+      <c r="A25" s="55"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6" t="s">
         <v>28</v>
@@ -4713,7 +4779,7 @@
       <c r="E25" s="6"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="53"/>
+      <c r="A26" s="55"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
         <v>12</v>
@@ -4727,7 +4793,7 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="53"/>
+      <c r="A27" s="55"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6" t="s">
         <v>11</v>
@@ -4741,7 +4807,7 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="53"/>
+      <c r="A28" s="55"/>
       <c r="C28" t="s">
         <v>8</v>
       </c>
@@ -4753,7 +4819,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="53"/>
+      <c r="A29" s="55"/>
       <c r="C29" t="s">
         <v>10</v>
       </c>
@@ -4764,41 +4830,41 @@
       <c r="E29" t="s">
         <v>25</v>
       </c>
-      <c r="G29" s="55" t="s">
+      <c r="G29" s="56" t="s">
         <v>590</v>
       </c>
-      <c r="H29" s="56"/>
-      <c r="I29" s="56"/>
-      <c r="J29" s="56"/>
-      <c r="K29" s="56"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B30" s="8"/>
       <c r="C30" s="10"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="56"/>
-      <c r="J30" s="56"/>
-      <c r="K30" s="56"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="53" t="s">
+      <c r="A31" s="55" t="s">
         <v>132</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="7"/>
-      <c r="G31" s="56"/>
-      <c r="H31" s="56"/>
-      <c r="I31" s="56"/>
-      <c r="J31" s="56"/>
-      <c r="K31" s="56"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="57"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="53"/>
+      <c r="A32" s="55"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6" t="s">
         <v>126</v>
@@ -4810,14 +4876,14 @@
       <c r="E32" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G32" s="56"/>
-      <c r="H32" s="56"/>
-      <c r="I32" s="56"/>
-      <c r="J32" s="56"/>
-      <c r="K32" s="56"/>
+      <c r="G32" s="57"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="57"/>
+      <c r="J32" s="57"/>
+      <c r="K32" s="57"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="53"/>
+      <c r="A33" s="55"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8" t="s">
         <v>127</v>
@@ -4828,14 +4894,14 @@
       <c r="E33" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G33" s="56"/>
-      <c r="H33" s="56"/>
-      <c r="I33" s="56"/>
-      <c r="J33" s="56"/>
-      <c r="K33" s="56"/>
+      <c r="G33" s="57"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="57"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="53"/>
+      <c r="A34" s="55"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8" t="s">
         <v>128</v>
@@ -4844,14 +4910,14 @@
         <v>5</v>
       </c>
       <c r="E34" s="9"/>
-      <c r="G34" s="56"/>
-      <c r="H34" s="56"/>
-      <c r="I34" s="56"/>
-      <c r="J34" s="56"/>
-      <c r="K34" s="56"/>
+      <c r="G34" s="57"/>
+      <c r="H34" s="57"/>
+      <c r="I34" s="57"/>
+      <c r="J34" s="57"/>
+      <c r="K34" s="57"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="53"/>
+      <c r="A35" s="55"/>
       <c r="C35" t="s">
         <v>133</v>
       </c>
@@ -4861,7 +4927,7 @@
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="53"/>
+      <c r="A36" s="55"/>
       <c r="C36" t="s">
         <v>136</v>
       </c>
@@ -4873,7 +4939,7 @@
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="53"/>
+      <c r="A37" s="55"/>
       <c r="C37" t="s">
         <v>169</v>
       </c>
@@ -4883,7 +4949,7 @@
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="53"/>
+      <c r="A38" s="55"/>
       <c r="C38" t="s">
         <v>170</v>
       </c>
@@ -4893,7 +4959,7 @@
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="53"/>
+      <c r="A39" s="55"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6" t="s">
         <v>9</v>
@@ -4907,7 +4973,7 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="53"/>
+      <c r="A40" s="55"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6" t="s">
         <v>772</v>
@@ -4921,7 +4987,7 @@
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="53"/>
+      <c r="A41" s="55"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6" t="s">
         <v>171</v>
@@ -4933,7 +4999,7 @@
       <c r="E41" s="6"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="53"/>
+      <c r="A42" s="55"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6" t="s">
         <v>172</v>
@@ -4945,7 +5011,7 @@
       <c r="E42" s="6"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="53"/>
+      <c r="A43" s="55"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6" t="s">
         <v>773</v>
@@ -4959,7 +5025,7 @@
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="53"/>
+      <c r="A44" s="55"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6" t="s">
         <v>27</v>
@@ -4973,7 +5039,7 @@
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="53"/>
+      <c r="A45" s="55"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6" t="s">
         <v>770</v>
@@ -4986,7 +5052,7 @@
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="53"/>
+      <c r="A46" s="55"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6" t="s">
         <v>771</v>
@@ -4998,7 +5064,7 @@
       <c r="E46" s="6"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="53"/>
+      <c r="A47" s="55"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6" t="s">
         <v>774</v>
@@ -5010,14 +5076,14 @@
       <c r="E47" s="6"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="53"/>
+      <c r="A48" s="55"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
       <c r="D48" s="11"/>
       <c r="E48" s="6"/>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A49" s="53"/>
+      <c r="A49" s="55"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8" t="s">
         <v>776</v>
@@ -5029,7 +5095,7 @@
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A50" s="53"/>
+      <c r="A50" s="55"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8" t="s">
         <v>682</v>
@@ -5040,7 +5106,7 @@
       <c r="E50" s="8"/>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A51" s="53"/>
+      <c r="A51" s="55"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8" t="s">
         <v>683</v>
@@ -5051,7 +5117,7 @@
       <c r="E51" s="8"/>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A52" s="53"/>
+      <c r="A52" s="55"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8" t="s">
         <v>777</v>
@@ -5063,7 +5129,7 @@
       <c r="E52" s="8"/>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A53" s="53"/>
+      <c r="A53" s="55"/>
       <c r="B53" s="44"/>
       <c r="C53" s="44" t="s">
         <v>200</v>
@@ -5075,7 +5141,7 @@
       <c r="E53" s="44"/>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A54" s="53"/>
+      <c r="A54" s="55"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6" t="s">
         <v>779</v>
@@ -5087,7 +5153,7 @@
       <c r="E54" s="6"/>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A55" s="53"/>
+      <c r="A55" s="55"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6" t="s">
         <v>780</v>
@@ -5100,7 +5166,7 @@
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A56" s="53"/>
+      <c r="A56" s="55"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6" t="s">
         <v>782</v>
@@ -5111,7 +5177,7 @@
       <c r="E56" s="6"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A57" s="53"/>
+      <c r="A57" s="55"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6" t="s">
         <v>778</v>
@@ -5123,7 +5189,7 @@
       <c r="E57" s="6"/>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A58" s="53"/>
+      <c r="A58" s="55"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6" t="s">
         <v>783</v>
@@ -5135,7 +5201,7 @@
       <c r="E58" s="6"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A59" s="53"/>
+      <c r="A59" s="55"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6" t="s">
         <v>784</v>
@@ -5159,7 +5225,7 @@
       </c>
     </row>
     <row r="61" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="53" t="s">
+      <c r="A61" s="55" t="s">
         <v>30</v>
       </c>
       <c r="C61" s="8" t="s">
@@ -5183,7 +5249,7 @@
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A62" s="53"/>
+      <c r="A62" s="55"/>
       <c r="C62" s="8" t="s">
         <v>26</v>
       </c>
@@ -5205,7 +5271,7 @@
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A63" s="53"/>
+      <c r="A63" s="55"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6" t="s">
         <v>13</v>
@@ -5229,7 +5295,7 @@
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A64" s="53"/>
+      <c r="A64" s="55"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6" t="s">
         <v>14</v>
@@ -5250,7 +5316,7 @@
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A65" s="53"/>
+      <c r="A65" s="55"/>
       <c r="C65" s="8" t="s">
         <v>16</v>
       </c>
@@ -5273,7 +5339,7 @@
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A66" s="53"/>
+      <c r="A66" s="55"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6" t="s">
         <v>107</v>
@@ -5294,7 +5360,7 @@
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A67" s="53"/>
+      <c r="A67" s="55"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6" t="s">
         <v>15</v>
@@ -5315,7 +5381,7 @@
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A68" s="53"/>
+      <c r="A68" s="55"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6" t="s">
         <v>32</v>
@@ -5327,7 +5393,7 @@
       <c r="E68" s="6"/>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A69" s="53"/>
+      <c r="A69" s="55"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6" t="s">
         <v>108</v>
@@ -5645,7 +5711,7 @@
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="53" t="s">
+      <c r="A98" s="55" t="s">
         <v>125</v>
       </c>
       <c r="B98" s="6" t="s">
@@ -5661,7 +5727,7 @@
       <c r="E98" s="2"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="53"/>
+      <c r="A99" s="55"/>
       <c r="B99" t="s">
         <v>58</v>
       </c>
@@ -5673,7 +5739,7 @@
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="53"/>
+      <c r="A100" s="55"/>
       <c r="B100" t="s">
         <v>57</v>
       </c>
@@ -5682,7 +5748,7 @@
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="53"/>
+      <c r="A101" s="55"/>
       <c r="B101" t="s">
         <v>51</v>
       </c>
@@ -5694,7 +5760,7 @@
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="53"/>
+      <c r="A102" s="55"/>
       <c r="C102" t="s">
         <v>36</v>
       </c>
@@ -5703,7 +5769,7 @@
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="53"/>
+      <c r="A103" s="55"/>
       <c r="B103" t="s">
         <v>39</v>
       </c>
@@ -5715,7 +5781,7 @@
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="53"/>
+      <c r="A104" s="55"/>
       <c r="B104" t="s">
         <v>578</v>
       </c>
@@ -5728,7 +5794,7 @@
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="53"/>
+      <c r="A105" s="55"/>
       <c r="B105" t="s">
         <v>41</v>
       </c>
@@ -5741,7 +5807,7 @@
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="53"/>
+      <c r="A106" s="55"/>
       <c r="C106" t="s">
         <v>40</v>
       </c>
@@ -5751,7 +5817,7 @@
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="53"/>
+      <c r="A107" s="55"/>
       <c r="B107" t="s">
         <v>45</v>
       </c>
@@ -5764,7 +5830,7 @@
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="53"/>
+      <c r="A108" s="55"/>
       <c r="B108" t="s">
         <v>53</v>
       </c>
@@ -5777,7 +5843,7 @@
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="53"/>
+      <c r="A109" s="55"/>
       <c r="B109" t="s">
         <v>55</v>
       </c>
@@ -5790,7 +5856,7 @@
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="53"/>
+      <c r="A110" s="55"/>
       <c r="C110" t="s">
         <v>60</v>
       </c>
@@ -5800,7 +5866,7 @@
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="53"/>
+      <c r="A111" s="55"/>
       <c r="B111" t="s">
         <v>580</v>
       </c>
@@ -5813,7 +5879,7 @@
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="53"/>
+      <c r="A112" s="55"/>
       <c r="B112" t="s">
         <v>581</v>
       </c>
@@ -5829,7 +5895,7 @@
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="53"/>
+      <c r="A113" s="55"/>
       <c r="B113" t="s">
         <v>64</v>
       </c>
@@ -5842,7 +5908,7 @@
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="53"/>
+      <c r="A114" s="55"/>
       <c r="C114" t="s">
         <v>66</v>
       </c>
@@ -5852,7 +5918,7 @@
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="53"/>
+      <c r="A115" s="55"/>
       <c r="B115" t="s">
         <v>68</v>
       </c>
@@ -5868,7 +5934,7 @@
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="53"/>
+      <c r="A116" s="55"/>
       <c r="B116" t="s">
         <v>815</v>
       </c>
@@ -5884,7 +5950,7 @@
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="53"/>
+      <c r="A117" s="55"/>
       <c r="B117" t="s">
         <v>174</v>
       </c>
@@ -5897,7 +5963,7 @@
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="53"/>
+      <c r="A118" s="55"/>
       <c r="C118" t="s">
         <v>176</v>
       </c>
@@ -5906,7 +5972,7 @@
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="53"/>
+      <c r="A119" s="55"/>
       <c r="C119" t="s">
         <v>227</v>
       </c>
@@ -5916,7 +5982,7 @@
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="53"/>
+      <c r="A120" s="55"/>
       <c r="C120" t="s">
         <v>187</v>
       </c>
@@ -5928,7 +5994,7 @@
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="53"/>
+      <c r="A121" s="55"/>
       <c r="C121" t="s">
         <v>185</v>
       </c>
@@ -5940,7 +6006,7 @@
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="53"/>
+      <c r="A122" s="55"/>
       <c r="C122" t="s">
         <v>184</v>
       </c>
@@ -5949,7 +6015,7 @@
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="53"/>
+      <c r="A123" s="55"/>
       <c r="C123" t="s">
         <v>178</v>
       </c>
@@ -5962,7 +6028,7 @@
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="53"/>
+      <c r="A124" s="55"/>
       <c r="C124" t="s">
         <v>179</v>
       </c>
@@ -5975,7 +6041,7 @@
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="53"/>
+      <c r="A125" s="55"/>
       <c r="C125" t="s">
         <v>180</v>
       </c>
@@ -5987,7 +6053,7 @@
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="53"/>
+      <c r="A126" s="55"/>
       <c r="C126" t="s">
         <v>189</v>
       </c>
@@ -6000,7 +6066,7 @@
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="53"/>
+      <c r="A127" s="55"/>
       <c r="C127" t="s">
         <v>181</v>
       </c>
@@ -6010,7 +6076,7 @@
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="53"/>
+      <c r="A128" s="55"/>
       <c r="C128" t="s">
         <v>182</v>
       </c>
@@ -6020,7 +6086,7 @@
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="53"/>
+      <c r="A129" s="55"/>
       <c r="C129" t="s">
         <v>177</v>
       </c>
@@ -6030,7 +6096,7 @@
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="53"/>
+      <c r="A130" s="55"/>
       <c r="C130" t="s">
         <v>183</v>
       </c>
@@ -6040,7 +6106,7 @@
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="53"/>
+      <c r="A131" s="55"/>
       <c r="C131" t="s">
         <v>195</v>
       </c>
@@ -6050,7 +6116,7 @@
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="53"/>
+      <c r="A132" s="55"/>
       <c r="C132" t="s">
         <v>194</v>
       </c>
@@ -6063,7 +6129,7 @@
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="53"/>
+      <c r="A133" s="55"/>
       <c r="C133" t="s">
         <v>186</v>
       </c>
@@ -6073,7 +6139,7 @@
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" s="53"/>
+      <c r="A134" s="55"/>
       <c r="C134" t="s">
         <v>188</v>
       </c>
@@ -6083,7 +6149,7 @@
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" s="53"/>
+      <c r="A135" s="55"/>
       <c r="C135" t="s">
         <v>189</v>
       </c>
@@ -6093,7 +6159,7 @@
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="53"/>
+      <c r="A136" s="55"/>
       <c r="C136" t="s">
         <v>190</v>
       </c>
@@ -6106,7 +6172,7 @@
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" s="53"/>
+      <c r="A137" s="55"/>
       <c r="C137" t="s">
         <v>191</v>
       </c>
@@ -6115,7 +6181,7 @@
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" s="53"/>
+      <c r="A138" s="55"/>
       <c r="C138" t="s">
         <v>193</v>
       </c>
@@ -6125,7 +6191,7 @@
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" s="53"/>
+      <c r="A139" s="55"/>
       <c r="C139" t="s">
         <v>225</v>
       </c>
@@ -6135,7 +6201,7 @@
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" s="53"/>
+      <c r="A140" s="55"/>
       <c r="C140" t="s">
         <v>201</v>
       </c>
@@ -6144,7 +6210,7 @@
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A141" s="53"/>
+      <c r="A141" s="55"/>
       <c r="C141" t="s">
         <v>200</v>
       </c>
@@ -6154,7 +6220,7 @@
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" s="53"/>
+      <c r="A142" s="55"/>
       <c r="C142" t="s">
         <v>202</v>
       </c>
@@ -6167,19 +6233,19 @@
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143" s="53"/>
+      <c r="A143" s="55"/>
       <c r="C143" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A144" s="53"/>
+      <c r="A144" s="55"/>
       <c r="C144" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" s="53"/>
+      <c r="A145" s="55"/>
       <c r="C145" t="s">
         <v>199</v>
       </c>
@@ -6191,7 +6257,7 @@
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A146" s="53"/>
+      <c r="A146" s="55"/>
       <c r="C146" t="s">
         <v>209</v>
       </c>
@@ -6201,7 +6267,7 @@
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" s="53"/>
+      <c r="A147" s="55"/>
       <c r="C147" t="s">
         <v>198</v>
       </c>
@@ -6210,7 +6276,7 @@
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" s="53"/>
+      <c r="A148" s="55"/>
       <c r="C148" t="s">
         <v>203</v>
       </c>
@@ -6219,7 +6285,7 @@
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149" s="53"/>
+      <c r="A149" s="55"/>
       <c r="C149" t="s">
         <v>204</v>
       </c>
@@ -6229,7 +6295,7 @@
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A150" s="53"/>
+      <c r="A150" s="55"/>
       <c r="C150" t="s">
         <v>189</v>
       </c>
@@ -6239,7 +6305,7 @@
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151" s="53"/>
+      <c r="A151" s="55"/>
       <c r="C151" t="s">
         <v>190</v>
       </c>
@@ -6249,7 +6315,7 @@
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A152" s="53"/>
+      <c r="A152" s="55"/>
       <c r="C152" t="s">
         <v>206</v>
       </c>
@@ -6262,7 +6328,7 @@
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153" s="53"/>
+      <c r="A153" s="55"/>
       <c r="C153" t="s">
         <v>207</v>
       </c>
@@ -6275,7 +6341,7 @@
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A154" s="53"/>
+      <c r="A154" s="55"/>
       <c r="C154" t="s">
         <v>208</v>
       </c>
@@ -6288,7 +6354,7 @@
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" s="53"/>
+      <c r="A155" s="55"/>
       <c r="C155" t="s">
         <v>210</v>
       </c>
@@ -6301,7 +6367,7 @@
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" s="53"/>
+      <c r="A156" s="55"/>
       <c r="C156" t="s">
         <v>211</v>
       </c>
@@ -6314,7 +6380,7 @@
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A157" s="53"/>
+      <c r="A157" s="55"/>
       <c r="C157" t="s">
         <v>201</v>
       </c>
@@ -6323,7 +6389,7 @@
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A158" s="53"/>
+      <c r="A158" s="55"/>
       <c r="C158" t="s">
         <v>215</v>
       </c>
@@ -6333,7 +6399,7 @@
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159" s="53"/>
+      <c r="A159" s="55"/>
       <c r="C159" t="s">
         <v>216</v>
       </c>
@@ -6343,7 +6409,7 @@
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A160" s="53"/>
+      <c r="A160" s="55"/>
       <c r="C160" t="s">
         <v>217</v>
       </c>
@@ -6356,7 +6422,7 @@
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A161" s="53"/>
+      <c r="A161" s="55"/>
       <c r="C161" t="s">
         <v>218</v>
       </c>
@@ -6366,7 +6432,7 @@
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A162" s="53"/>
+      <c r="A162" s="55"/>
       <c r="C162" t="s">
         <v>219</v>
       </c>
@@ -6376,7 +6442,7 @@
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A163" s="53"/>
+      <c r="A163" s="55"/>
       <c r="C163" t="s">
         <v>220</v>
       </c>
@@ -6386,7 +6452,7 @@
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A164" s="53"/>
+      <c r="A164" s="55"/>
       <c r="C164" t="s">
         <v>221</v>
       </c>
@@ -6396,7 +6462,7 @@
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A165" s="53"/>
+      <c r="A165" s="55"/>
       <c r="C165" t="s">
         <v>222</v>
       </c>
@@ -6406,7 +6472,7 @@
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A166" s="53"/>
+      <c r="A166" s="55"/>
       <c r="C166" t="s">
         <v>223</v>
       </c>
@@ -6419,7 +6485,7 @@
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A167" s="53"/>
+      <c r="A167" s="55"/>
       <c r="C167" t="s">
         <v>295</v>
       </c>
@@ -6428,7 +6494,7 @@
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A168" s="53"/>
+      <c r="A168" s="55"/>
       <c r="C168" t="s">
         <v>814</v>
       </c>
@@ -6438,7 +6504,7 @@
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A169" s="53"/>
+      <c r="A169" s="55"/>
       <c r="C169" t="s">
         <v>231</v>
       </c>
@@ -8401,7 +8467,7 @@
       <c r="A302" s="54"/>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A303" s="53" t="s">
+      <c r="A303" s="55" t="s">
         <v>607</v>
       </c>
       <c r="B303" t="s">
@@ -8413,7 +8479,7 @@
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A304" s="53"/>
+      <c r="A304" s="55"/>
       <c r="B304" t="s">
         <v>609</v>
       </c>
@@ -8422,7 +8488,7 @@
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A305" s="53"/>
+      <c r="A305" s="55"/>
       <c r="B305" t="s">
         <v>610</v>
       </c>
@@ -8431,7 +8497,7 @@
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A306" s="53"/>
+      <c r="A306" s="55"/>
       <c r="B306" t="s">
         <v>611</v>
       </c>
@@ -8441,7 +8507,7 @@
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A307" s="53"/>
+      <c r="A307" s="55"/>
       <c r="B307" t="s">
         <v>615</v>
       </c>
@@ -8451,7 +8517,7 @@
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A308" s="53"/>
+      <c r="A308" s="55"/>
       <c r="B308" t="s">
         <v>613</v>
       </c>
@@ -8461,7 +8527,7 @@
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A309" s="53"/>
+      <c r="A309" s="55"/>
       <c r="B309" t="s">
         <v>614</v>
       </c>
@@ -8471,7 +8537,7 @@
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A310" s="53"/>
+      <c r="A310" s="55"/>
       <c r="B310" t="s">
         <v>616</v>
       </c>
@@ -8481,7 +8547,7 @@
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A311" s="53"/>
+      <c r="A311" s="55"/>
       <c r="C311" t="s">
         <v>617</v>
       </c>
@@ -8490,7 +8556,7 @@
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A312" s="53"/>
+      <c r="A312" s="55"/>
       <c r="C312" t="s">
         <v>618</v>
       </c>
@@ -8500,7 +8566,7 @@
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A313" s="53"/>
+      <c r="A313" s="55"/>
       <c r="C313" t="s">
         <v>619</v>
       </c>
@@ -8510,7 +8576,7 @@
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A314" s="53"/>
+      <c r="A314" s="55"/>
       <c r="C314" t="s">
         <v>620</v>
       </c>
@@ -8520,10 +8586,10 @@
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A315" s="53"/>
+      <c r="A315" s="55"/>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A316" s="53" t="s">
+      <c r="A316" s="55" t="s">
         <v>584</v>
       </c>
       <c r="C316" t="s">
@@ -8534,7 +8600,7 @@
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A317" s="53"/>
+      <c r="A317" s="55"/>
       <c r="B317" t="s">
         <v>38</v>
       </c>
@@ -8544,7 +8610,7 @@
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A318" s="53"/>
+      <c r="A318" s="55"/>
       <c r="B318" t="s">
         <v>286</v>
       </c>
@@ -8556,7 +8622,7 @@
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A319" s="53"/>
+      <c r="A319" s="55"/>
       <c r="C319" t="s">
         <v>289</v>
       </c>
@@ -8566,7 +8632,7 @@
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A320" s="53"/>
+      <c r="A320" s="55"/>
       <c r="B320" t="s">
         <v>290</v>
       </c>
@@ -8579,7 +8645,7 @@
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A321" s="53"/>
+      <c r="A321" s="55"/>
       <c r="C321" t="s">
         <v>288</v>
       </c>
@@ -8588,7 +8654,7 @@
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A322" s="53"/>
+      <c r="A322" s="55"/>
       <c r="B322" t="s">
         <v>287</v>
       </c>
@@ -8597,7 +8663,7 @@
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A323" s="53"/>
+      <c r="A323" s="55"/>
       <c r="B323" t="s">
         <v>291</v>
       </c>
@@ -8609,7 +8675,7 @@
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A324" s="53"/>
+      <c r="A324" s="55"/>
       <c r="B324" t="s">
         <v>292</v>
       </c>
@@ -8622,7 +8688,7 @@
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A325" s="53"/>
+      <c r="A325" s="55"/>
       <c r="B325" t="s">
         <v>349</v>
       </c>
@@ -9102,7 +9168,7 @@
       <c r="A363" s="38"/>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A364" s="53" t="s">
+      <c r="A364" s="55" t="s">
         <v>700</v>
       </c>
       <c r="B364" t="s">
@@ -9117,7 +9183,7 @@
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A365" s="53"/>
+      <c r="A365" s="55"/>
       <c r="C365" t="s">
         <v>701</v>
       </c>
@@ -9129,7 +9195,7 @@
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A366" s="53"/>
+      <c r="A366" s="55"/>
       <c r="C366" t="s">
         <v>703</v>
       </c>
@@ -9141,7 +9207,7 @@
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A367" s="53"/>
+      <c r="A367" s="55"/>
       <c r="C367" t="s">
         <v>704</v>
       </c>
@@ -9153,7 +9219,7 @@
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A368" s="53"/>
+      <c r="A368" s="55"/>
       <c r="B368" t="s">
         <v>706</v>
       </c>
@@ -9167,7 +9233,7 @@
       <c r="E368" s="40"/>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A369" s="53"/>
+      <c r="A369" s="55"/>
       <c r="B369" t="s">
         <v>708</v>
       </c>
@@ -9181,7 +9247,7 @@
       <c r="E369" s="40"/>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A370" s="53"/>
+      <c r="A370" s="55"/>
       <c r="B370" t="s">
         <v>710</v>
       </c>
@@ -9194,7 +9260,7 @@
       <c r="E370" s="39"/>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A371" s="53"/>
+      <c r="A371" s="55"/>
       <c r="C371" t="s">
         <v>705</v>
       </c>
@@ -9205,7 +9271,7 @@
       <c r="E371" s="39"/>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A372" s="53"/>
+      <c r="A372" s="55"/>
       <c r="B372" t="s">
         <v>713</v>
       </c>
@@ -9219,7 +9285,7 @@
       <c r="E372" s="39"/>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A373" s="53"/>
+      <c r="A373" s="55"/>
       <c r="C373" t="s">
         <v>714</v>
       </c>
@@ -9229,7 +9295,7 @@
       <c r="E373" s="39"/>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A374" s="53"/>
+      <c r="A374" s="55"/>
       <c r="C374" t="s">
         <v>715</v>
       </c>
@@ -9240,7 +9306,7 @@
       <c r="E374" s="39"/>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A375" s="53"/>
+      <c r="A375" s="55"/>
       <c r="C375" t="s">
         <v>716</v>
       </c>
@@ -9250,7 +9316,7 @@
       <c r="E375" s="39"/>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A376" s="53"/>
+      <c r="A376" s="55"/>
       <c r="C376" t="s">
         <v>717</v>
       </c>
@@ -9260,18 +9326,18 @@
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A377" s="53" t="s">
+      <c r="A377" s="55" t="s">
         <v>718</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A378" s="53"/>
+      <c r="A378" s="55"/>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A379" s="53"/>
+      <c r="A379" s="55"/>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A380" s="53"/>
+      <c r="A380" s="55"/>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" s="54" t="s">
@@ -10104,7 +10170,7 @@
         <v>820</v>
       </c>
       <c r="D454" s="8">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="455" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
@@ -10114,7 +10180,7 @@
       </c>
       <c r="D455" s="8">
         <f>D449/D454</f>
-        <v>0.15065913370998116</v>
+        <v>0.11299435028248586</v>
       </c>
       <c r="E455" t="s">
         <v>20</v>
@@ -10127,7 +10193,7 @@
       </c>
       <c r="D456" s="8">
         <f>D451/D454</f>
-        <v>0.26666666666666666</v>
+        <v>0.2</v>
       </c>
       <c r="E456" t="s">
         <v>20</v>
@@ -10140,7 +10206,7 @@
       </c>
       <c r="D457" s="8">
         <f>D450/D454</f>
-        <v>8.6983091403333448E-2</v>
+        <v>6.523731855250009E-2</v>
       </c>
       <c r="E457" t="s">
         <v>20</v>
@@ -10153,7 +10219,7 @@
       </c>
       <c r="D458" s="8">
         <f>D452/D454</f>
-        <v>0.15396007178390023</v>
+        <v>0.11547005383792516</v>
       </c>
       <c r="E458" t="s">
         <v>20</v>
@@ -10168,7 +10234,7 @@
         <v>835</v>
       </c>
       <c r="D459" s="8">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="E459" t="s">
         <v>21</v>
@@ -10183,7 +10249,7 @@
         <v>823</v>
       </c>
       <c r="D460">
-        <v>0.6</v>
+        <v>1.05</v>
       </c>
       <c r="E460" t="s">
         <v>21</v>
@@ -10199,7 +10265,7 @@
       </c>
       <c r="D461">
         <f>(D459)/D456</f>
-        <v>10.125</v>
+        <v>10</v>
       </c>
       <c r="E461" s="9" t="s">
         <v>24</v>
@@ -10230,7 +10296,7 @@
       </c>
       <c r="D463">
         <f xml:space="preserve"> D456*D462</f>
-        <v>2.6666666666666665</v>
+        <v>2</v>
       </c>
       <c r="E463" t="s">
         <v>21</v>
@@ -10249,7 +10315,7 @@
       </c>
       <c r="D465">
         <f xml:space="preserve"> POWER(D456, 2)*D462</f>
-        <v>0.71111111111111114</v>
+        <v>0.40000000000000008</v>
       </c>
       <c r="E465" t="s">
         <v>22</v>
@@ -10265,7 +10331,7 @@
       </c>
       <c r="D466">
         <f>POWER(D458, 2)*D462</f>
-        <v>0.2370370370370371</v>
+        <v>0.13333333333333336</v>
       </c>
       <c r="E466" t="s">
         <v>22</v>
@@ -10281,7 +10347,7 @@
       </c>
       <c r="D467">
         <f>POWER(D455, 2)*D462</f>
-        <v>0.2269817457024198</v>
+        <v>0.12767723195761113</v>
       </c>
       <c r="E467" t="s">
         <v>22</v>
@@ -10297,7 +10363,7 @@
       </c>
       <c r="D468">
         <f>POWER(D457, 2)*D462</f>
-        <v>7.5660581900806614E-2</v>
+        <v>4.255907731920372E-2</v>
       </c>
       <c r="E468" t="s">
         <v>22</v>
@@ -10313,7 +10379,7 @@
       </c>
       <c r="D469">
         <f>D460*D456</f>
-        <v>0.16</v>
+        <v>0.21000000000000002</v>
       </c>
       <c r="E469" t="s">
         <v>22</v>
@@ -10329,7 +10395,7 @@
       </c>
       <c r="D470">
         <f>D460*D455</f>
-        <v>9.0395480225988686E-2</v>
+        <v>0.11864406779661016</v>
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
@@ -10345,7 +10411,7 @@
       </c>
       <c r="D472">
         <f>D462+(2*(D460/D456))</f>
-        <v>14.5</v>
+        <v>20.5</v>
       </c>
       <c r="E472" s="9" t="s">
         <v>24</v>
@@ -10361,7 +10427,7 @@
       </c>
       <c r="D473">
         <f>D455*D462</f>
-        <v>1.5065913370998116</v>
+        <v>1.1299435028248586</v>
       </c>
       <c r="E473" t="s">
         <v>21</v>
@@ -10377,7 +10443,7 @@
       </c>
       <c r="D474">
         <f>D456</f>
-        <v>0.26666666666666666</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
@@ -11579,399 +11645,399 @@
       </c>
       <c r="C484">
         <f>C483/$D$454</f>
-        <v>5.333333333333334E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D484">
         <f t="shared" ref="D484:BO484" si="55">D483/$D$454</f>
-        <v>1.0666666666666668E-2</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="E484">
         <f t="shared" si="55"/>
-        <v>1.6E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="F484">
         <f t="shared" si="55"/>
-        <v>2.1333333333333336E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="G484">
         <f t="shared" si="55"/>
-        <v>2.6666666666666668E-2</v>
+        <v>0.02</v>
       </c>
       <c r="H484">
         <f t="shared" si="55"/>
-        <v>3.2000000000000001E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="I484">
         <f t="shared" si="55"/>
-        <v>3.7333333333333336E-2</v>
+        <v>2.8000000000000004E-2</v>
       </c>
       <c r="J484">
         <f t="shared" si="55"/>
-        <v>4.2666666666666672E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="K484">
         <f t="shared" si="55"/>
-        <v>4.7999999999999994E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="L484">
         <f t="shared" si="55"/>
-        <v>5.3333333333333337E-2</v>
+        <v>0.04</v>
       </c>
       <c r="M484">
         <f t="shared" si="55"/>
-        <v>5.8666666666666673E-2</v>
+        <v>4.4000000000000004E-2</v>
       </c>
       <c r="N484">
         <f t="shared" si="55"/>
-        <v>6.4000000000000001E-2</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="O484">
         <f t="shared" si="55"/>
-        <v>6.933333333333333E-2</v>
+        <v>5.2000000000000005E-2</v>
       </c>
       <c r="P484">
         <f t="shared" si="55"/>
-        <v>7.4666666666666673E-2</v>
+        <v>5.6000000000000008E-2</v>
       </c>
       <c r="Q484">
         <f t="shared" si="55"/>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="R484">
         <f t="shared" si="55"/>
-        <v>8.5333333333333344E-2</v>
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="S484">
         <f t="shared" si="55"/>
-        <v>9.0666666666666673E-2</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="T484">
         <f t="shared" si="55"/>
-        <v>9.5999999999999988E-2</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="U484">
         <f t="shared" si="55"/>
-        <v>0.10133333333333333</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="V484">
         <f t="shared" si="55"/>
-        <v>0.10666666666666667</v>
+        <v>0.08</v>
       </c>
       <c r="W484">
         <f t="shared" si="55"/>
-        <v>0.112</v>
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="X484">
         <f t="shared" si="55"/>
-        <v>0.11733333333333335</v>
+        <v>8.8000000000000009E-2</v>
       </c>
       <c r="Y484">
         <f t="shared" si="55"/>
-        <v>0.12266666666666669</v>
+        <v>9.2000000000000012E-2</v>
       </c>
       <c r="Z484">
         <f t="shared" si="55"/>
-        <v>0.128</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="AA484">
         <f t="shared" si="55"/>
-        <v>0.13333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="AB484">
         <f t="shared" si="55"/>
-        <v>0.13866666666666666</v>
+        <v>0.10400000000000001</v>
       </c>
       <c r="AC484">
         <f t="shared" si="55"/>
-        <v>0.14400000000000002</v>
+        <v>0.10800000000000001</v>
       </c>
       <c r="AD484">
         <f t="shared" si="55"/>
-        <v>0.14933333333333335</v>
+        <v>0.11200000000000002</v>
       </c>
       <c r="AE484">
         <f t="shared" si="55"/>
-        <v>0.15466666666666667</v>
+        <v>0.11599999999999999</v>
       </c>
       <c r="AF484">
         <f t="shared" si="55"/>
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="AG484">
         <f t="shared" si="55"/>
-        <v>0.16533333333333333</v>
+        <v>0.124</v>
       </c>
       <c r="AH484">
         <f t="shared" si="55"/>
-        <v>0.17066666666666669</v>
+        <v>0.128</v>
       </c>
       <c r="AI484">
         <f t="shared" si="55"/>
-        <v>0.17600000000000002</v>
+        <v>0.13200000000000001</v>
       </c>
       <c r="AJ484">
         <f t="shared" si="55"/>
-        <v>0.18133333333333335</v>
+        <v>0.13600000000000001</v>
       </c>
       <c r="AK484">
         <f t="shared" si="55"/>
-        <v>0.18666666666666668</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AL484">
         <f t="shared" si="55"/>
-        <v>0.19199999999999998</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="AM484">
         <f t="shared" si="55"/>
-        <v>0.19733333333333333</v>
+        <v>0.14800000000000002</v>
       </c>
       <c r="AN484">
         <f t="shared" si="55"/>
-        <v>0.20266666666666666</v>
+        <v>0.152</v>
       </c>
       <c r="AO484">
         <f t="shared" si="55"/>
-        <v>0.20800000000000002</v>
+        <v>0.15600000000000003</v>
       </c>
       <c r="AP484">
         <f t="shared" si="55"/>
-        <v>0.21333333333333335</v>
+        <v>0.16</v>
       </c>
       <c r="AQ484">
         <f t="shared" si="55"/>
-        <v>0.21866666666666665</v>
+        <v>0.16399999999999998</v>
       </c>
       <c r="AR484">
         <f t="shared" si="55"/>
-        <v>0.224</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="AS484">
         <f t="shared" si="55"/>
-        <v>0.22933333333333333</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="AT484">
         <f t="shared" si="55"/>
-        <v>0.23466666666666669</v>
+        <v>0.17600000000000002</v>
       </c>
       <c r="AU484">
         <f t="shared" si="55"/>
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="AV484">
         <f t="shared" si="55"/>
-        <v>0.24533333333333338</v>
+        <v>0.18400000000000002</v>
       </c>
       <c r="AW484">
         <f t="shared" si="55"/>
-        <v>0.25066666666666665</v>
+        <v>0.18799999999999997</v>
       </c>
       <c r="AX484">
         <f t="shared" si="55"/>
-        <v>0.25600000000000001</v>
+        <v>0.192</v>
       </c>
       <c r="AY484">
         <f t="shared" si="55"/>
-        <v>0.26133333333333336</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="AZ484">
         <f t="shared" si="55"/>
-        <v>0.26666666666666666</v>
+        <v>0.2</v>
       </c>
       <c r="BA484">
         <f t="shared" si="55"/>
-        <v>0.26133333333333336</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="BB484">
         <f t="shared" si="55"/>
-        <v>0.25600000000000001</v>
+        <v>0.192</v>
       </c>
       <c r="BC484">
         <f t="shared" si="55"/>
-        <v>0.25066666666666665</v>
+        <v>0.18799999999999997</v>
       </c>
       <c r="BD484">
         <f t="shared" si="55"/>
-        <v>0.24533333333333338</v>
+        <v>0.18400000000000002</v>
       </c>
       <c r="BE484">
         <f t="shared" si="55"/>
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="BF484">
         <f t="shared" si="55"/>
-        <v>0.23466666666666669</v>
+        <v>0.17600000000000002</v>
       </c>
       <c r="BG484">
         <f t="shared" si="55"/>
-        <v>0.22933333333333333</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="BH484">
         <f t="shared" si="55"/>
-        <v>0.224</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="BI484">
         <f t="shared" si="55"/>
-        <v>0.21866666666666665</v>
+        <v>0.16399999999999998</v>
       </c>
       <c r="BJ484">
         <f t="shared" si="55"/>
-        <v>0.21333333333333335</v>
+        <v>0.16</v>
       </c>
       <c r="BK484">
         <f t="shared" si="55"/>
-        <v>0.20800000000000002</v>
+        <v>0.15600000000000003</v>
       </c>
       <c r="BL484">
         <f t="shared" si="55"/>
-        <v>0.20266666666666666</v>
+        <v>0.152</v>
       </c>
       <c r="BM484">
         <f t="shared" si="55"/>
-        <v>0.19733333333333333</v>
+        <v>0.14800000000000002</v>
       </c>
       <c r="BN484">
         <f t="shared" si="55"/>
-        <v>0.19199999999999998</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="BO484">
         <f t="shared" si="55"/>
-        <v>0.18666666666666668</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="BP484">
         <f t="shared" ref="BP484:CX484" si="56">BP483/$D$454</f>
-        <v>0.18133333333333335</v>
+        <v>0.13600000000000001</v>
       </c>
       <c r="BQ484">
         <f t="shared" si="56"/>
-        <v>0.17600000000000002</v>
+        <v>0.13200000000000001</v>
       </c>
       <c r="BR484">
         <f t="shared" si="56"/>
-        <v>0.17066666666666669</v>
+        <v>0.128</v>
       </c>
       <c r="BS484">
         <f t="shared" si="56"/>
-        <v>0.16533333333333333</v>
+        <v>0.124</v>
       </c>
       <c r="BT484">
         <f t="shared" si="56"/>
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="BU484">
         <f t="shared" si="56"/>
-        <v>0.15466666666666667</v>
+        <v>0.11599999999999999</v>
       </c>
       <c r="BV484">
         <f t="shared" si="56"/>
-        <v>0.14933333333333335</v>
+        <v>0.11200000000000002</v>
       </c>
       <c r="BW484">
         <f t="shared" si="56"/>
-        <v>0.14400000000000002</v>
+        <v>0.10800000000000001</v>
       </c>
       <c r="BX484">
         <f t="shared" si="56"/>
-        <v>0.13866666666666666</v>
+        <v>0.10400000000000001</v>
       </c>
       <c r="BY484">
         <f t="shared" si="56"/>
-        <v>0.13333333333333333</v>
+        <v>0.1</v>
       </c>
       <c r="BZ484">
         <f t="shared" si="56"/>
-        <v>0.128</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="CA484">
         <f t="shared" si="56"/>
-        <v>0.12266666666666669</v>
+        <v>9.2000000000000012E-2</v>
       </c>
       <c r="CB484">
         <f t="shared" si="56"/>
-        <v>0.11733333333333335</v>
+        <v>8.8000000000000009E-2</v>
       </c>
       <c r="CC484">
         <f t="shared" si="56"/>
-        <v>0.112</v>
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="CD484">
         <f t="shared" si="56"/>
-        <v>0.10666666666666667</v>
+        <v>0.08</v>
       </c>
       <c r="CE484">
         <f t="shared" si="56"/>
-        <v>0.10133333333333333</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="CF484">
         <f t="shared" si="56"/>
-        <v>9.5999999999999988E-2</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="CG484">
         <f t="shared" si="56"/>
-        <v>9.0666666666666673E-2</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="CH484">
         <f t="shared" si="56"/>
-        <v>8.5333333333333344E-2</v>
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="CI484">
         <f t="shared" si="56"/>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="CJ484">
         <f t="shared" si="56"/>
-        <v>7.4666666666666673E-2</v>
+        <v>5.6000000000000008E-2</v>
       </c>
       <c r="CK484">
         <f t="shared" si="56"/>
-        <v>6.933333333333333E-2</v>
+        <v>5.2000000000000005E-2</v>
       </c>
       <c r="CL484">
         <f t="shared" si="56"/>
-        <v>6.4000000000000001E-2</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="CM484">
         <f t="shared" si="56"/>
-        <v>5.8666666666666673E-2</v>
+        <v>4.4000000000000004E-2</v>
       </c>
       <c r="CN484">
         <f t="shared" si="56"/>
-        <v>5.3333333333333337E-2</v>
+        <v>0.04</v>
       </c>
       <c r="CO484">
         <f t="shared" si="56"/>
-        <v>4.7999999999999994E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="CP484">
         <f t="shared" si="56"/>
-        <v>4.2666666666666672E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="CQ484">
         <f t="shared" si="56"/>
-        <v>3.7333333333333336E-2</v>
+        <v>2.8000000000000004E-2</v>
       </c>
       <c r="CR484">
         <f t="shared" si="56"/>
-        <v>3.2000000000000001E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="CS484">
         <f t="shared" si="56"/>
-        <v>2.6666666666666668E-2</v>
+        <v>0.02</v>
       </c>
       <c r="CT484">
         <f t="shared" si="56"/>
-        <v>2.1333333333333336E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="CU484">
         <f t="shared" si="56"/>
-        <v>1.6E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="CV484">
         <f t="shared" si="56"/>
-        <v>1.0666666666666668E-2</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="CW484">
         <f t="shared" si="56"/>
-        <v>5.333333333333334E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="CX484">
         <f t="shared" si="56"/>
@@ -11985,403 +12051,403 @@
       </c>
       <c r="C485">
         <f>(($D$460*2)+(C484*($D$462+$D$464)))*$D$480</f>
-        <v>3.9166666666666675E-7</v>
+        <v>6.6875000000000006E-7</v>
       </c>
       <c r="D485">
         <f>(($D$460*2)+(D484*($D$462+$D$464)))*$D$480</f>
-        <v>4.0833333333333338E-7</v>
+        <v>6.8125000000000015E-7</v>
       </c>
       <c r="E485">
         <f t="shared" ref="E485:BP485" si="57">(($D$460*2)+(E484*($D$462+$D$464)))*$D$480</f>
-        <v>4.2500000000000001E-7</v>
+        <v>6.9375000000000013E-7</v>
       </c>
       <c r="F485">
         <f t="shared" si="57"/>
-        <v>4.4166666666666669E-7</v>
+        <v>7.0625000000000012E-7</v>
       </c>
       <c r="G485">
         <f t="shared" si="57"/>
-        <v>4.5833333333333332E-7</v>
+        <v>7.1875000000000011E-7</v>
       </c>
       <c r="H485">
         <f t="shared" si="57"/>
-        <v>4.7500000000000006E-7</v>
+        <v>7.3124999999999999E-7</v>
       </c>
       <c r="I485">
         <f t="shared" si="57"/>
-        <v>4.9166666666666669E-7</v>
+        <v>7.4375000000000008E-7</v>
       </c>
       <c r="J485">
         <f t="shared" si="57"/>
-        <v>5.0833333333333337E-7</v>
+        <v>7.5625000000000007E-7</v>
       </c>
       <c r="K485">
         <f t="shared" si="57"/>
-        <v>5.2500000000000006E-7</v>
+        <v>7.6875000000000005E-7</v>
       </c>
       <c r="L485">
         <f t="shared" si="57"/>
-        <v>5.4166666666666674E-7</v>
+        <v>7.8125000000000004E-7</v>
       </c>
       <c r="M485">
         <f t="shared" si="57"/>
-        <v>5.5833333333333332E-7</v>
+        <v>7.9375000000000002E-7</v>
       </c>
       <c r="N485">
         <f t="shared" si="57"/>
-        <v>5.75E-7</v>
+        <v>8.0625000000000012E-7</v>
       </c>
       <c r="O485">
         <f t="shared" si="57"/>
-        <v>5.9166666666666668E-7</v>
+        <v>8.187500000000001E-7</v>
       </c>
       <c r="P485">
         <f t="shared" si="57"/>
-        <v>6.0833333333333337E-7</v>
+        <v>8.3125000000000009E-7</v>
       </c>
       <c r="Q485">
         <f t="shared" si="57"/>
-        <v>6.2500000000000005E-7</v>
+        <v>8.4375000000000007E-7</v>
       </c>
       <c r="R485">
         <f t="shared" si="57"/>
-        <v>6.4166666666666684E-7</v>
+        <v>8.5625000000000017E-7</v>
       </c>
       <c r="S485">
         <f t="shared" si="57"/>
-        <v>6.5833333333333331E-7</v>
+        <v>8.6875000000000015E-7</v>
       </c>
       <c r="T485">
         <f t="shared" si="57"/>
-        <v>6.75E-7</v>
+        <v>8.8125000000000014E-7</v>
       </c>
       <c r="U485">
         <f t="shared" si="57"/>
-        <v>6.9166666666666657E-7</v>
+        <v>8.9375000000000012E-7</v>
       </c>
       <c r="V485">
         <f t="shared" si="57"/>
-        <v>7.0833333333333336E-7</v>
+        <v>9.0625000000000022E-7</v>
       </c>
       <c r="W485">
         <f t="shared" si="57"/>
-        <v>7.2500000000000015E-7</v>
+        <v>9.187500000000002E-7</v>
       </c>
       <c r="X485">
         <f t="shared" si="57"/>
-        <v>7.4166666666666662E-7</v>
+        <v>9.3125000000000019E-7</v>
       </c>
       <c r="Y485">
         <f t="shared" si="57"/>
-        <v>7.5833333333333341E-7</v>
+        <v>9.4375000000000018E-7</v>
       </c>
       <c r="Z485">
         <f t="shared" si="57"/>
-        <v>7.750000000000001E-7</v>
+        <v>9.5625000000000016E-7</v>
       </c>
       <c r="AA485">
         <f t="shared" si="57"/>
-        <v>7.9166666666666667E-7</v>
+        <v>9.6875000000000004E-7</v>
       </c>
       <c r="AB485">
         <f t="shared" si="57"/>
-        <v>8.0833333333333346E-7</v>
+        <v>9.8125000000000013E-7</v>
       </c>
       <c r="AC485">
         <f t="shared" si="57"/>
-        <v>8.2500000000000015E-7</v>
+        <v>9.9375000000000023E-7</v>
       </c>
       <c r="AD485">
         <f t="shared" si="57"/>
-        <v>8.4166666666666673E-7</v>
+        <v>1.0062500000000001E-6</v>
       </c>
       <c r="AE485">
         <f t="shared" si="57"/>
-        <v>8.5833333333333352E-7</v>
+        <v>1.01875E-6</v>
       </c>
       <c r="AF485">
         <f t="shared" si="57"/>
-        <v>8.7499999999999999E-7</v>
+        <v>1.0312500000000001E-6</v>
       </c>
       <c r="AG485">
         <f t="shared" si="57"/>
-        <v>8.9166666666666678E-7</v>
+        <v>1.04375E-6</v>
       </c>
       <c r="AH485">
         <f t="shared" si="57"/>
-        <v>9.0833333333333357E-7</v>
+        <v>1.0562500000000001E-6</v>
       </c>
       <c r="AI485">
         <f t="shared" si="57"/>
-        <v>9.2500000000000004E-7</v>
+        <v>1.0687500000000001E-6</v>
       </c>
       <c r="AJ485">
         <f t="shared" si="57"/>
-        <v>9.4166666666666683E-7</v>
+        <v>1.08125E-6</v>
       </c>
       <c r="AK485">
         <f t="shared" si="57"/>
-        <v>9.583333333333334E-7</v>
+        <v>1.0937500000000001E-6</v>
       </c>
       <c r="AL485">
         <f t="shared" si="57"/>
-        <v>9.7499999999999998E-7</v>
+        <v>1.10625E-6</v>
       </c>
       <c r="AM485">
         <f t="shared" si="57"/>
-        <v>9.9166666666666677E-7</v>
+        <v>1.1187500000000001E-6</v>
       </c>
       <c r="AN485">
         <f t="shared" si="57"/>
-        <v>1.0083333333333333E-6</v>
+        <v>1.1312500000000002E-6</v>
       </c>
       <c r="AO485">
         <f t="shared" si="57"/>
-        <v>1.0250000000000001E-6</v>
+        <v>1.1437500000000001E-6</v>
       </c>
       <c r="AP485">
         <f t="shared" si="57"/>
-        <v>1.0416666666666667E-6</v>
+        <v>1.1562500000000002E-6</v>
       </c>
       <c r="AQ485">
         <f t="shared" si="57"/>
-        <v>1.0583333333333335E-6</v>
+        <v>1.16875E-6</v>
       </c>
       <c r="AR485">
         <f t="shared" si="57"/>
-        <v>1.0750000000000003E-6</v>
+        <v>1.1812500000000001E-6</v>
       </c>
       <c r="AS485">
         <f t="shared" si="57"/>
-        <v>1.0916666666666667E-6</v>
+        <v>1.19375E-6</v>
       </c>
       <c r="AT485">
         <f t="shared" si="57"/>
-        <v>1.1083333333333335E-6</v>
+        <v>1.2062500000000001E-6</v>
       </c>
       <c r="AU485">
         <f t="shared" si="57"/>
-        <v>1.125E-6</v>
+        <v>1.21875E-6</v>
       </c>
       <c r="AV485">
         <f t="shared" si="57"/>
-        <v>1.1416666666666668E-6</v>
+        <v>1.2312500000000003E-6</v>
       </c>
       <c r="AW485">
         <f t="shared" si="57"/>
-        <v>1.1583333333333332E-6</v>
+        <v>1.24375E-6</v>
       </c>
       <c r="AX485">
         <f t="shared" si="57"/>
-        <v>1.175E-6</v>
+        <v>1.25625E-6</v>
       </c>
       <c r="AY485">
         <f t="shared" si="57"/>
-        <v>1.1916666666666668E-6</v>
+        <v>1.2687500000000003E-6</v>
       </c>
       <c r="AZ485">
         <f t="shared" si="57"/>
-        <v>1.2083333333333333E-6</v>
+        <v>1.28125E-6</v>
       </c>
       <c r="BA485">
         <f t="shared" si="57"/>
-        <v>1.1916666666666668E-6</v>
+        <v>1.2687500000000003E-6</v>
       </c>
       <c r="BB485">
         <f t="shared" si="57"/>
-        <v>1.175E-6</v>
+        <v>1.25625E-6</v>
       </c>
       <c r="BC485">
         <f t="shared" si="57"/>
-        <v>1.1583333333333332E-6</v>
+        <v>1.24375E-6</v>
       </c>
       <c r="BD485">
         <f t="shared" si="57"/>
-        <v>1.1416666666666668E-6</v>
+        <v>1.2312500000000003E-6</v>
       </c>
       <c r="BE485">
         <f t="shared" si="57"/>
-        <v>1.125E-6</v>
+        <v>1.21875E-6</v>
       </c>
       <c r="BF485">
         <f t="shared" si="57"/>
-        <v>1.1083333333333335E-6</v>
+        <v>1.2062500000000001E-6</v>
       </c>
       <c r="BG485">
         <f t="shared" si="57"/>
-        <v>1.0916666666666667E-6</v>
+        <v>1.19375E-6</v>
       </c>
       <c r="BH485">
         <f t="shared" si="57"/>
-        <v>1.0750000000000003E-6</v>
+        <v>1.1812500000000001E-6</v>
       </c>
       <c r="BI485">
         <f t="shared" si="57"/>
-        <v>1.0583333333333335E-6</v>
+        <v>1.16875E-6</v>
       </c>
       <c r="BJ485">
         <f t="shared" si="57"/>
-        <v>1.0416666666666667E-6</v>
+        <v>1.1562500000000002E-6</v>
       </c>
       <c r="BK485">
         <f t="shared" si="57"/>
-        <v>1.0250000000000001E-6</v>
+        <v>1.1437500000000001E-6</v>
       </c>
       <c r="BL485">
         <f t="shared" si="57"/>
-        <v>1.0083333333333333E-6</v>
+        <v>1.1312500000000002E-6</v>
       </c>
       <c r="BM485">
         <f t="shared" si="57"/>
-        <v>9.9166666666666677E-7</v>
+        <v>1.1187500000000001E-6</v>
       </c>
       <c r="BN485">
         <f t="shared" si="57"/>
-        <v>9.7499999999999998E-7</v>
+        <v>1.10625E-6</v>
       </c>
       <c r="BO485">
         <f t="shared" si="57"/>
-        <v>9.583333333333334E-7</v>
+        <v>1.0937500000000001E-6</v>
       </c>
       <c r="BP485">
         <f t="shared" si="57"/>
-        <v>9.4166666666666683E-7</v>
+        <v>1.08125E-6</v>
       </c>
       <c r="BQ485">
         <f t="shared" ref="BQ485:CX485" si="58">(($D$460*2)+(BQ484*($D$462+$D$464)))*$D$480</f>
-        <v>9.2500000000000004E-7</v>
+        <v>1.0687500000000001E-6</v>
       </c>
       <c r="BR485">
         <f t="shared" si="58"/>
-        <v>9.0833333333333357E-7</v>
+        <v>1.0562500000000001E-6</v>
       </c>
       <c r="BS485">
         <f t="shared" si="58"/>
-        <v>8.9166666666666678E-7</v>
+        <v>1.04375E-6</v>
       </c>
       <c r="BT485">
         <f t="shared" si="58"/>
-        <v>8.7499999999999999E-7</v>
+        <v>1.0312500000000001E-6</v>
       </c>
       <c r="BU485">
         <f t="shared" si="58"/>
-        <v>8.5833333333333352E-7</v>
+        <v>1.01875E-6</v>
       </c>
       <c r="BV485">
         <f t="shared" si="58"/>
-        <v>8.4166666666666673E-7</v>
+        <v>1.0062500000000001E-6</v>
       </c>
       <c r="BW485">
         <f t="shared" si="58"/>
-        <v>8.2500000000000015E-7</v>
+        <v>9.9375000000000023E-7</v>
       </c>
       <c r="BX485">
         <f t="shared" si="58"/>
-        <v>8.0833333333333346E-7</v>
+        <v>9.8125000000000013E-7</v>
       </c>
       <c r="BY485">
         <f t="shared" si="58"/>
-        <v>7.9166666666666667E-7</v>
+        <v>9.6875000000000004E-7</v>
       </c>
       <c r="BZ485">
         <f t="shared" si="58"/>
-        <v>7.750000000000001E-7</v>
+        <v>9.5625000000000016E-7</v>
       </c>
       <c r="CA485">
         <f t="shared" si="58"/>
-        <v>7.5833333333333341E-7</v>
+        <v>9.4375000000000018E-7</v>
       </c>
       <c r="CB485">
         <f t="shared" si="58"/>
-        <v>7.4166666666666662E-7</v>
+        <v>9.3125000000000019E-7</v>
       </c>
       <c r="CC485">
         <f t="shared" si="58"/>
-        <v>7.2500000000000015E-7</v>
+        <v>9.187500000000002E-7</v>
       </c>
       <c r="CD485">
         <f t="shared" si="58"/>
-        <v>7.0833333333333336E-7</v>
+        <v>9.0625000000000022E-7</v>
       </c>
       <c r="CE485">
         <f t="shared" si="58"/>
-        <v>6.9166666666666657E-7</v>
+        <v>8.9375000000000012E-7</v>
       </c>
       <c r="CF485">
         <f t="shared" si="58"/>
-        <v>6.75E-7</v>
+        <v>8.8125000000000014E-7</v>
       </c>
       <c r="CG485">
         <f t="shared" si="58"/>
-        <v>6.5833333333333331E-7</v>
+        <v>8.6875000000000015E-7</v>
       </c>
       <c r="CH485">
         <f t="shared" si="58"/>
-        <v>6.4166666666666684E-7</v>
+        <v>8.5625000000000017E-7</v>
       </c>
       <c r="CI485">
         <f t="shared" si="58"/>
-        <v>6.2500000000000005E-7</v>
+        <v>8.4375000000000007E-7</v>
       </c>
       <c r="CJ485">
         <f t="shared" si="58"/>
-        <v>6.0833333333333337E-7</v>
+        <v>8.3125000000000009E-7</v>
       </c>
       <c r="CK485">
         <f t="shared" si="58"/>
-        <v>5.9166666666666668E-7</v>
+        <v>8.187500000000001E-7</v>
       </c>
       <c r="CL485">
         <f t="shared" si="58"/>
-        <v>5.75E-7</v>
+        <v>8.0625000000000012E-7</v>
       </c>
       <c r="CM485">
         <f t="shared" si="58"/>
-        <v>5.5833333333333332E-7</v>
+        <v>7.9375000000000002E-7</v>
       </c>
       <c r="CN485">
         <f t="shared" si="58"/>
-        <v>5.4166666666666674E-7</v>
+        <v>7.8125000000000004E-7</v>
       </c>
       <c r="CO485">
         <f t="shared" si="58"/>
-        <v>5.2500000000000006E-7</v>
+        <v>7.6875000000000005E-7</v>
       </c>
       <c r="CP485">
         <f t="shared" si="58"/>
-        <v>5.0833333333333337E-7</v>
+        <v>7.5625000000000007E-7</v>
       </c>
       <c r="CQ485">
         <f t="shared" si="58"/>
-        <v>4.9166666666666669E-7</v>
+        <v>7.4375000000000008E-7</v>
       </c>
       <c r="CR485">
         <f t="shared" si="58"/>
-        <v>4.7500000000000006E-7</v>
+        <v>7.3124999999999999E-7</v>
       </c>
       <c r="CS485">
         <f t="shared" si="58"/>
-        <v>4.5833333333333332E-7</v>
+        <v>7.1875000000000011E-7</v>
       </c>
       <c r="CT485">
         <f t="shared" si="58"/>
-        <v>4.4166666666666669E-7</v>
+        <v>7.0625000000000012E-7</v>
       </c>
       <c r="CU485">
         <f t="shared" si="58"/>
-        <v>4.2500000000000001E-7</v>
+        <v>6.9375000000000013E-7</v>
       </c>
       <c r="CV485">
         <f t="shared" si="58"/>
-        <v>4.0833333333333338E-7</v>
+        <v>6.8125000000000015E-7</v>
       </c>
       <c r="CW485">
         <f t="shared" si="58"/>
-        <v>3.9166666666666675E-7</v>
+        <v>6.6875000000000006E-7</v>
       </c>
       <c r="CX485">
         <f t="shared" si="58"/>
-        <v>3.7500000000000001E-7</v>
+        <v>6.5625000000000007E-7</v>
       </c>
     </row>
     <row r="486" spans="1:102" x14ac:dyDescent="0.25">
@@ -12391,7 +12457,7 @@
       </c>
       <c r="C486">
         <f>SUM(C485:CX485)</f>
-        <v>7.9166666666666676E-5</v>
+        <v>9.6874999999999969E-5</v>
       </c>
     </row>
     <row r="487" spans="1:102" x14ac:dyDescent="0.25">
@@ -12400,8 +12466,8 @@
         <v>876</v>
       </c>
       <c r="C487">
-        <f>381/1000000</f>
-        <v>3.8099999999999999E-4</v>
+        <f>791/1000000</f>
+        <v>7.9100000000000004E-4</v>
       </c>
     </row>
     <row r="488" spans="1:102" x14ac:dyDescent="0.25">
@@ -13661,7 +13727,7 @@
       <c r="A591" s="42"/>
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A596" s="53" t="s">
+      <c r="A596" s="55" t="s">
         <v>719</v>
       </c>
       <c r="C596" t="s">
@@ -13672,7 +13738,7 @@
       </c>
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A597" s="53"/>
+      <c r="A597" s="55"/>
       <c r="C597" t="s">
         <v>721</v>
       </c>
@@ -13681,7 +13747,7 @@
       </c>
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A598" s="53"/>
+      <c r="A598" s="55"/>
       <c r="C598" t="s">
         <v>219</v>
       </c>
@@ -13691,7 +13757,7 @@
       </c>
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A599" s="53"/>
+      <c r="A599" s="55"/>
       <c r="C599" t="s">
         <v>722</v>
       </c>
@@ -13701,7 +13767,7 @@
       </c>
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A600" s="53"/>
+      <c r="A600" s="55"/>
       <c r="C600" t="s">
         <v>723</v>
       </c>
@@ -13711,7 +13777,7 @@
       </c>
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A601" s="53"/>
+      <c r="A601" s="55"/>
       <c r="C601" t="s">
         <v>724</v>
       </c>
@@ -13721,7 +13787,7 @@
       </c>
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A602" s="53"/>
+      <c r="A602" s="55"/>
       <c r="C602" t="s">
         <v>762</v>
       </c>
@@ -13730,7 +13796,7 @@
       </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A603" s="53"/>
+      <c r="A603" s="55"/>
       <c r="C603" t="s">
         <v>725</v>
       </c>
@@ -13740,7 +13806,7 @@
       </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A604" s="53"/>
+      <c r="A604" s="55"/>
       <c r="C604" t="s">
         <v>726</v>
       </c>
@@ -13750,7 +13816,7 @@
       </c>
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A605" s="53"/>
+      <c r="A605" s="55"/>
       <c r="C605" t="s">
         <v>727</v>
       </c>
@@ -13760,7 +13826,7 @@
       </c>
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A606" s="53"/>
+      <c r="A606" s="55"/>
       <c r="C606" t="s">
         <v>728</v>
       </c>
@@ -13770,7 +13836,7 @@
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A607" s="53"/>
+      <c r="A607" s="55"/>
     </row>
     <row r="609" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C609" t="s">
@@ -13781,7 +13847,7 @@
       </c>
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A610" s="53" t="s">
+      <c r="A610" s="55" t="s">
         <v>729</v>
       </c>
       <c r="C610" t="s">
@@ -13792,7 +13858,7 @@
       </c>
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A611" s="53"/>
+      <c r="A611" s="55"/>
       <c r="C611" t="s">
         <v>219</v>
       </c>
@@ -13802,7 +13868,7 @@
       </c>
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A612" s="53"/>
+      <c r="A612" s="55"/>
       <c r="C612" t="s">
         <v>722</v>
       </c>
@@ -13811,7 +13877,7 @@
       </c>
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A613" s="53"/>
+      <c r="A613" s="55"/>
       <c r="C613" t="s">
         <v>723</v>
       </c>
@@ -13821,7 +13887,7 @@
       </c>
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A614" s="53"/>
+      <c r="A614" s="55"/>
       <c r="C614" t="s">
         <v>724</v>
       </c>
@@ -13831,7 +13897,7 @@
       </c>
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A615" s="53"/>
+      <c r="A615" s="55"/>
       <c r="C615" t="s">
         <v>763</v>
       </c>
@@ -13840,7 +13906,7 @@
       </c>
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A616" s="53"/>
+      <c r="A616" s="55"/>
       <c r="C616" t="s">
         <v>725</v>
       </c>
@@ -13850,7 +13916,7 @@
       </c>
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A617" s="53"/>
+      <c r="A617" s="55"/>
       <c r="C617" t="s">
         <v>726</v>
       </c>
@@ -13860,7 +13926,7 @@
       </c>
     </row>
     <row r="618" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A618" s="53"/>
+      <c r="A618" s="55"/>
       <c r="C618" t="s">
         <v>727</v>
       </c>
@@ -13870,7 +13936,7 @@
       </c>
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A619" s="53"/>
+      <c r="A619" s="55"/>
       <c r="C619" t="s">
         <v>728</v>
       </c>
@@ -14498,7 +14564,7 @@
         <v>22.05</v>
       </c>
       <c r="I679" s="18">
-        <f t="shared" ref="I679:I691" si="66">H679*H679*G679</f>
+        <f t="shared" ref="I679:I692" si="66">H679*H679*G679</f>
         <v>972.40500000000009</v>
       </c>
       <c r="J679" s="18">
@@ -14570,7 +14636,7 @@
         <v>486.20250000000004</v>
       </c>
       <c r="J681" s="18">
-        <f t="shared" ref="J681:J691" si="67">I681/2</f>
+        <f t="shared" ref="J681:J692" si="67">I681/2</f>
         <v>243.10125000000002</v>
       </c>
       <c r="K681" s="18">
@@ -14582,7 +14648,7 @@
         <v>313.29000000000008</v>
       </c>
       <c r="M681" s="18">
-        <f t="shared" ref="M681:M691" si="68">L681/2</f>
+        <f t="shared" ref="M681:M692" si="68">L681/2</f>
         <v>156.64500000000004</v>
       </c>
     </row>
@@ -14796,6 +14862,21 @@
       </c>
     </row>
     <row r="688" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A688" s="54" t="s">
+        <v>893</v>
+      </c>
+      <c r="B688" t="s">
+        <v>879</v>
+      </c>
+      <c r="C688" t="s">
+        <v>878</v>
+      </c>
+      <c r="E688">
+        <v>5</v>
+      </c>
+      <c r="F688" s="9" t="s">
+        <v>21</v>
+      </c>
       <c r="G688" s="18">
         <v>11</v>
       </c>
@@ -14827,7 +14908,21 @@
         <v>810</v>
       </c>
     </row>
-    <row r="689" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A689" s="54"/>
+      <c r="B689" t="s">
+        <v>881</v>
+      </c>
+      <c r="C689" t="s">
+        <v>882</v>
+      </c>
+      <c r="E689">
+        <f>2000</f>
+        <v>2000</v>
+      </c>
+      <c r="F689" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="G689" s="18">
         <v>12</v>
       </c>
@@ -14859,7 +14954,21 @@
         <v>812</v>
       </c>
     </row>
-    <row r="690" spans="7:14" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A690" s="54"/>
+      <c r="B690" t="s">
+        <v>880</v>
+      </c>
+      <c r="C690" t="s">
+        <v>883</v>
+      </c>
+      <c r="E690">
+        <f>((E688/1.23)-1)*E689</f>
+        <v>6130.081300813009</v>
+      </c>
+      <c r="F690" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="G690" s="18">
         <v>13</v>
       </c>
@@ -14891,47 +15000,388 @@
         <v>811</v>
       </c>
     </row>
-    <row r="691" spans="7:14" x14ac:dyDescent="0.25">
-      <c r="G691" s="18">
+    <row r="691" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A691" s="53"/>
+      <c r="B691" t="s">
+        <v>892</v>
+      </c>
+      <c r="C691" t="s">
+        <v>898</v>
+      </c>
+      <c r="E691">
+        <f>1/(31000*E690)</f>
+        <v>5.26225720886455E-9</v>
+      </c>
+      <c r="F691" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G691" s="18"/>
+      <c r="H691" s="18"/>
+      <c r="I691" s="18"/>
+      <c r="J691" s="18"/>
+      <c r="K691" s="18"/>
+      <c r="L691" s="18"/>
+      <c r="M691" s="18"/>
+    </row>
+    <row r="692" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G692" s="18">
         <v>14</v>
       </c>
-      <c r="H691" s="18">
-        <f>E671/G691</f>
+      <c r="H692" s="18">
+        <f>E671/G692</f>
         <v>3.15</v>
       </c>
-      <c r="I691" s="18">
+      <c r="I692" s="18">
         <f t="shared" si="66"/>
         <v>138.91499999999999</v>
       </c>
-      <c r="J691" s="18">
+      <c r="J692" s="18">
         <f t="shared" si="67"/>
         <v>69.457499999999996</v>
       </c>
-      <c r="K691" s="18">
-        <f>E669/G691</f>
+      <c r="K692" s="18">
+        <f>E669/G692</f>
         <v>2.5285714285714289</v>
       </c>
-      <c r="L691" s="18">
-        <f>E669*E669/G691</f>
+      <c r="L692" s="18">
+        <f>E669*E669/G692</f>
         <v>89.511428571428596</v>
       </c>
-      <c r="M691" s="18">
+      <c r="M692" s="18">
         <f t="shared" si="68"/>
         <v>44.755714285714298</v>
       </c>
-      <c r="N691" t="s">
+      <c r="N692" t="s">
         <v>813</v>
       </c>
     </row>
+    <row r="693" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A693" s="54" t="s">
+        <v>894</v>
+      </c>
+      <c r="B693" t="s">
+        <v>879</v>
+      </c>
+      <c r="C693" t="s">
+        <v>878</v>
+      </c>
+      <c r="E693">
+        <v>3.3</v>
+      </c>
+      <c r="F693" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="694" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A694" s="54"/>
+      <c r="B694" t="s">
+        <v>881</v>
+      </c>
+      <c r="C694" t="s">
+        <v>882</v>
+      </c>
+      <c r="E694">
+        <f>2000</f>
+        <v>2000</v>
+      </c>
+      <c r="F694" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="695" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A695" s="54"/>
+      <c r="B695" t="s">
+        <v>880</v>
+      </c>
+      <c r="C695" t="s">
+        <v>883</v>
+      </c>
+      <c r="E695">
+        <f>((E693/1.23)-1)*E694</f>
+        <v>3365.8536585365846</v>
+      </c>
+      <c r="F695" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="696" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B696" t="s">
+        <v>892</v>
+      </c>
+      <c r="C696" t="s">
+        <v>898</v>
+      </c>
+      <c r="E696">
+        <f>1/(31000*E695)</f>
+        <v>9.583917718560077E-9</v>
+      </c>
+      <c r="F696" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="698" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A698" s="54" t="s">
+        <v>897</v>
+      </c>
+      <c r="B698" t="s">
+        <v>879</v>
+      </c>
+      <c r="C698" t="s">
+        <v>878</v>
+      </c>
+      <c r="E698">
+        <v>10</v>
+      </c>
+      <c r="F698" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="699" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A699" s="54"/>
+      <c r="B699" t="s">
+        <v>881</v>
+      </c>
+      <c r="C699" t="s">
+        <v>882</v>
+      </c>
+      <c r="E699">
+        <f>2000</f>
+        <v>2000</v>
+      </c>
+      <c r="F699" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="700" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A700" s="54"/>
+      <c r="B700" t="s">
+        <v>880</v>
+      </c>
+      <c r="C700" t="s">
+        <v>883</v>
+      </c>
+      <c r="E700">
+        <f>((E698/1.23)-1)*E699</f>
+        <v>14260.162601626018</v>
+      </c>
+      <c r="F700" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="701" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B701" t="s">
+        <v>892</v>
+      </c>
+      <c r="C701" t="s">
+        <v>898</v>
+      </c>
+      <c r="E701">
+        <f>1/(31000*E700)</f>
+        <v>2.2621105675506673E-9</v>
+      </c>
+      <c r="F701" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="703" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A703" s="54" t="s">
+        <v>895</v>
+      </c>
+      <c r="B703" t="s">
+        <v>885</v>
+      </c>
+      <c r="C703" t="s">
+        <v>884</v>
+      </c>
+      <c r="E703">
+        <v>2</v>
+      </c>
+      <c r="F703" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="704" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A704" s="54"/>
+      <c r="B704" t="s">
+        <v>886</v>
+      </c>
+      <c r="C704" t="s">
+        <v>887</v>
+      </c>
+      <c r="E704">
+        <v>30</v>
+      </c>
+      <c r="F704" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="705" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A705" s="54"/>
+      <c r="B705" t="s">
+        <v>881</v>
+      </c>
+      <c r="C705" t="s">
+        <v>882</v>
+      </c>
+      <c r="E705">
+        <f>2000</f>
+        <v>2000</v>
+      </c>
+      <c r="F705" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="706" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A706" s="54"/>
+      <c r="B706" t="s">
+        <v>891</v>
+      </c>
+      <c r="C706" t="s">
+        <v>888</v>
+      </c>
+      <c r="E706">
+        <f>((E703/1.23)-1)*E705</f>
+        <v>1252.0325203252032</v>
+      </c>
+      <c r="F706" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="707" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A707" s="54"/>
+      <c r="B707" t="s">
+        <v>890</v>
+      </c>
+      <c r="C707" t="s">
+        <v>889</v>
+      </c>
+      <c r="E707">
+        <f>((E704/1.23)-1)*E705</f>
+        <v>46780.487804878052</v>
+      </c>
+      <c r="F707" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="708" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A708" s="54"/>
+      <c r="B708" t="s">
+        <v>892</v>
+      </c>
+      <c r="C708" t="s">
+        <v>898</v>
+      </c>
+      <c r="E708">
+        <f>1/(31000*E706)</f>
+        <v>2.5764558022622537E-8</v>
+      </c>
+      <c r="F708" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="710" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A710" s="54" t="s">
+        <v>896</v>
+      </c>
+      <c r="B710" t="s">
+        <v>885</v>
+      </c>
+      <c r="C710" t="s">
+        <v>884</v>
+      </c>
+      <c r="E710">
+        <v>9</v>
+      </c>
+      <c r="F710" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="711" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A711" s="54"/>
+      <c r="B711" t="s">
+        <v>886</v>
+      </c>
+      <c r="C711" t="s">
+        <v>887</v>
+      </c>
+      <c r="E711">
+        <v>14</v>
+      </c>
+      <c r="F711" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="712" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A712" s="54"/>
+      <c r="B712" t="s">
+        <v>881</v>
+      </c>
+      <c r="C712" t="s">
+        <v>882</v>
+      </c>
+      <c r="E712">
+        <f>2000</f>
+        <v>2000</v>
+      </c>
+      <c r="F712" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="713" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A713" s="54"/>
+      <c r="B713" t="s">
+        <v>891</v>
+      </c>
+      <c r="C713" t="s">
+        <v>888</v>
+      </c>
+      <c r="E713">
+        <f>((E710/1.23)-1)*E712</f>
+        <v>12634.146341463415</v>
+      </c>
+      <c r="F713" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="714" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A714" s="54"/>
+      <c r="B714" t="s">
+        <v>890</v>
+      </c>
+      <c r="C714" t="s">
+        <v>889</v>
+      </c>
+      <c r="E714">
+        <f>((E711/1.23)-1)*E712</f>
+        <v>20764.227642276423</v>
+      </c>
+      <c r="F714" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="715" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A715" s="54"/>
+      <c r="B715" t="s">
+        <v>892</v>
+      </c>
+      <c r="C715" t="s">
+        <v>898</v>
+      </c>
+      <c r="E715">
+        <f>1/(31000*E713)</f>
+        <v>2.5532444887283596E-9</v>
+      </c>
+      <c r="F715" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="A670:A684"/>
-    <mergeCell ref="A364:A376"/>
-    <mergeCell ref="A377:A380"/>
-    <mergeCell ref="A596:A607"/>
-    <mergeCell ref="A610:A619"/>
-    <mergeCell ref="A577:A589"/>
-    <mergeCell ref="A491:A562"/>
+  <mergeCells count="28">
+    <mergeCell ref="A688:A690"/>
+    <mergeCell ref="A693:A695"/>
+    <mergeCell ref="A698:A700"/>
+    <mergeCell ref="A703:A708"/>
+    <mergeCell ref="A710:A715"/>
     <mergeCell ref="A31:A59"/>
     <mergeCell ref="A636:A661"/>
     <mergeCell ref="A228:A279"/>
@@ -14948,6 +15398,13 @@
     <mergeCell ref="A171:A226"/>
     <mergeCell ref="A303:A315"/>
     <mergeCell ref="A622:A634"/>
+    <mergeCell ref="A670:A684"/>
+    <mergeCell ref="A364:A376"/>
+    <mergeCell ref="A377:A380"/>
+    <mergeCell ref="A596:A607"/>
+    <mergeCell ref="A610:A619"/>
+    <mergeCell ref="A577:A589"/>
+    <mergeCell ref="A491:A562"/>
   </mergeCells>
   <conditionalFormatting sqref="D110">
     <cfRule type="cellIs" dxfId="9" priority="9" operator="notEqual">
@@ -15241,17 +15698,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="58" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="57"/>
+      <c r="B1" s="58"/>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C18" s="58" t="s">
+      <c r="C18" s="59" t="s">
         <v>167</v>
       </c>
-      <c r="D18" s="59"/>
-      <c r="E18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="61"/>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C19" s="18" t="s">
@@ -15445,17 +15902,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="58" t="s">
         <v>166</v>
       </c>
-      <c r="B1" s="57"/>
+      <c r="B1" s="58"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="58" t="s">
+      <c r="B17" s="59" t="s">
         <v>167</v>
       </c>
-      <c r="C17" s="59"/>
-      <c r="D17" s="60"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="61"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B18" s="18" t="s">
@@ -15708,17 +16165,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="58" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="57"/>
+      <c r="B1" s="58"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="58" t="s">
+      <c r="B17" s="59" t="s">
         <v>167</v>
       </c>
-      <c r="C17" s="59"/>
-      <c r="D17" s="60"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="61"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B18" s="18" t="s">

--- a/Spreadsheets/BasicCalculations.xlsx
+++ b/Spreadsheets/BasicCalculations.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="1135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="1138">
   <si>
     <t>N stages required</t>
   </si>
@@ -3309,21 +3309,12 @@
     <t>μ0</t>
   </si>
   <si>
-    <t>Edge-to-edge spacing (m)</t>
-  </si>
-  <si>
-    <t>Parallel length (m)</t>
-  </si>
-  <si>
     <t>𝑙</t>
   </si>
   <si>
     <t>w</t>
   </si>
   <si>
-    <t>Width of the victim trace (m)</t>
-  </si>
-  <si>
     <t>M</t>
   </si>
   <si>
@@ -3451,6 +3442,24 @@
   </si>
   <si>
     <t>L_total</t>
+  </si>
+  <si>
+    <t>Trace Separation (m)</t>
+  </si>
+  <si>
+    <t>Parallel Trace Length (m)</t>
+  </si>
+  <si>
+    <t>2l/d</t>
+  </si>
+  <si>
+    <t>d/(2l)</t>
+  </si>
+  <si>
+    <t>(2l/d)^2</t>
+  </si>
+  <si>
+    <t>(d/(2l))^2</t>
   </si>
 </sst>
 </file>
@@ -4729,19 +4738,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>4493559</xdr:colOff>
-      <xdr:row>940</xdr:row>
-      <xdr:rowOff>89647</xdr:rowOff>
+      <xdr:colOff>3038475</xdr:colOff>
+      <xdr:row>950</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>32822</xdr:colOff>
-      <xdr:row>943</xdr:row>
-      <xdr:rowOff>22413</xdr:rowOff>
+      <xdr:colOff>628954</xdr:colOff>
+      <xdr:row>954</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Picture 16"/>
+        <xdr:cNvPr id="21" name="Picture 20"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -4754,8 +4763,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8079441" y="176369382"/>
-          <a:ext cx="1635263" cy="504266"/>
+          <a:off x="6619875" y="181575075"/>
+          <a:ext cx="3686479" cy="638175"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5656,7 +5665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CX964"/>
+  <dimension ref="A1:CX968"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" customWidth="1"/>
@@ -12668,10 +12677,10 @@
     <row r="487" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A487" s="75"/>
       <c r="B487" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="C487" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="D487" s="54">
         <v>1.9</v>
@@ -12683,10 +12692,10 @@
     <row r="488" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A488" s="75"/>
       <c r="B488" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="C488" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="D488" s="54">
         <v>4.7</v>
@@ -12698,7 +12707,7 @@
     <row r="489" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A489" s="75"/>
       <c r="C489" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="D489" s="54">
         <v>0.5</v>
@@ -12710,10 +12719,10 @@
     <row r="490" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A490" s="75"/>
       <c r="B490" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="C490" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="D490" s="51">
         <f>D488*(100-D489)/100</f>
@@ -12724,10 +12733,10 @@
     <row r="491" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A491" s="75"/>
       <c r="B491" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="C491" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="D491" s="51">
         <v>0</v>
@@ -12751,10 +12760,10 @@
     <row r="493" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A493" s="75"/>
       <c r="B493" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="C493" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="D493" s="51">
         <f>D485/D490</f>
@@ -12766,10 +12775,10 @@
     <row r="494" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A494" s="75"/>
       <c r="B494" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="C494" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="D494" s="27">
         <f>D485/D492</f>
@@ -12783,7 +12792,7 @@
     <row r="495" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A495" s="75"/>
       <c r="C495" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="D495" s="51"/>
       <c r="H495" s="52"/>
@@ -12822,7 +12831,7 @@
     <row r="499" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A499" s="75"/>
       <c r="C499" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="D499" s="27" t="b">
         <f>AND(D493&lt;D497, D494&lt;=D498)</f>
@@ -13593,10 +13602,10 @@
     <row r="560" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="75"/>
       <c r="B560" s="35" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="C560" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="D560" s="51">
         <f>D492</f>
@@ -13606,10 +13615,10 @@
     <row r="561" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="75"/>
       <c r="B561" s="35" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="C561" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="D561" s="54">
         <f>0.00000000361</f>
@@ -13619,23 +13628,23 @@
     <row r="562" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="75"/>
       <c r="B562" s="35" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="C562" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="D562" s="51">
-        <f>E953</f>
+        <f>E957</f>
         <v>2.2741325637156556E-10</v>
       </c>
     </row>
     <row r="563" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="75"/>
       <c r="B563" s="35" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="C563" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="D563" s="51">
         <v>2.0000000000000001E-9</v>
@@ -13644,7 +13653,7 @@
     <row r="564" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="75"/>
       <c r="B564" s="35" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="D564" s="51">
         <f>D562+D563</f>
@@ -13654,7 +13663,7 @@
     <row r="565" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="75"/>
       <c r="B565" s="35" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="D565" s="51">
         <f>D560*0.5*SQRT(D561/D564)</f>
@@ -20085,13 +20094,13 @@
         <v>1085</v>
       </c>
       <c r="C940" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="E940" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="G940" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="941" spans="1:14" x14ac:dyDescent="0.25">
@@ -20142,13 +20151,13 @@
     <row r="942" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A942" s="75"/>
       <c r="B942" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="C942" t="s">
-        <v>1088</v>
+        <v>1133</v>
       </c>
       <c r="E942">
-        <v>0.01</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="F942" s="8" t="s">
         <v>206</v>
@@ -20160,10 +20169,10 @@
         <v>135</v>
       </c>
       <c r="C943" t="s">
-        <v>1087</v>
+        <v>1132</v>
       </c>
       <c r="E943">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F943" s="8" t="s">
         <v>206</v>
@@ -20171,239 +20180,263 @@
     </row>
     <row r="944" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A944" s="75"/>
-      <c r="B944" t="s">
-        <v>1090</v>
-      </c>
       <c r="C944" t="s">
-        <v>1091</v>
+        <v>1134</v>
       </c>
       <c r="E944">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="F944" s="8" t="s">
-        <v>206</v>
-      </c>
+        <f>2*E942/E943</f>
+        <v>0.3</v>
+      </c>
+      <c r="F944" s="8"/>
     </row>
     <row r="945" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A945" s="75"/>
-      <c r="B945" t="s">
-        <v>1092</v>
-      </c>
       <c r="C945" t="s">
-        <v>1093</v>
+        <v>1135</v>
       </c>
       <c r="E945">
-        <f>(E941*E942/(2*PI()))*LN((E943+SQRT(POWER(E943, 2)+POWER(E944, 2)))/E944)</f>
-        <v>8.7643656961309974E-9</v>
-      </c>
-      <c r="F945" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="G945" t="e">
-        <f t="shared" ref="G945:N945" si="86">(G941*G942/(2*PI()))*LN((G943+SQRT(POWER(G943, 2)+POWER(G944, 2)))/G944)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H945" t="e">
-        <f t="shared" si="86"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I945" t="e">
-        <f t="shared" si="86"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J945" t="e">
-        <f t="shared" si="86"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K945" t="e">
-        <f t="shared" si="86"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L945" t="e">
-        <f t="shared" si="86"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M945" t="e">
-        <f t="shared" si="86"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N945" t="e">
-        <f t="shared" si="86"/>
-        <v>#DIV/0!</v>
-      </c>
+        <f>1/E944</f>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="F945" s="8"/>
     </row>
     <row r="946" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A946" s="75"/>
-      <c r="B946" t="s">
-        <v>1094</v>
-      </c>
       <c r="C946" t="s">
-        <v>1095</v>
+        <v>1136</v>
       </c>
       <c r="E946">
+        <f>POWER(E944, 2)</f>
+        <v>0.09</v>
+      </c>
+      <c r="F946" s="8"/>
+    </row>
+    <row r="947" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A947" s="75"/>
+      <c r="C947" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E947">
+        <f>1/E946</f>
+        <v>11.111111111111111</v>
+      </c>
+      <c r="F947" s="8"/>
+    </row>
+    <row r="948" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A948" s="75"/>
+      <c r="F948" s="8"/>
+    </row>
+    <row r="949" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A949" s="75"/>
+      <c r="B949" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C949" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E949">
+        <f>(E941/(4*PI()))*(LN(E944+SQRT(1+E946)) - SQRT(1+E947)+E945)</f>
+        <v>1.4890421125990595E-8</v>
+      </c>
+      <c r="F949" t="s">
+        <v>154</v>
+      </c>
+      <c r="G949">
+        <f t="shared" ref="F949:N949" si="86">(G941/(4*PI()))*(LN(G944+SQRT(1+G946)) - SQRT(1+G947)+G945)</f>
+        <v>-1.0000000000000001E-7</v>
+      </c>
+      <c r="H949">
+        <f t="shared" si="86"/>
+        <v>-1.0000000000000001E-7</v>
+      </c>
+      <c r="I949">
+        <f t="shared" si="86"/>
+        <v>-1.0000000000000001E-7</v>
+      </c>
+      <c r="J949">
+        <f t="shared" si="86"/>
+        <v>-1.0000000000000001E-7</v>
+      </c>
+      <c r="K949">
+        <f t="shared" si="86"/>
+        <v>-1.0000000000000001E-7</v>
+      </c>
+      <c r="L949">
+        <f t="shared" si="86"/>
+        <v>-1.0000000000000001E-7</v>
+      </c>
+      <c r="M949">
+        <f t="shared" si="86"/>
+        <v>-1.0000000000000001E-7</v>
+      </c>
+      <c r="N949">
+        <f t="shared" si="86"/>
+        <v>-1.0000000000000001E-7</v>
+      </c>
+    </row>
+    <row r="950" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A950" s="75"/>
+      <c r="B950" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C950" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E950">
         <f>22*16000*4</f>
         <v>1408000</v>
       </c>
     </row>
-    <row r="947" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A947" s="75"/>
-      <c r="B947" s="84" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C947" t="s">
-        <v>1099</v>
-      </c>
-      <c r="E947">
-        <v>0</v>
-      </c>
-      <c r="F947">
-        <v>0</v>
-      </c>
-      <c r="G947">
-        <v>0</v>
-      </c>
-      <c r="H947">
-        <v>0</v>
-      </c>
-      <c r="I947">
-        <v>0</v>
-      </c>
-      <c r="J947">
-        <v>0</v>
-      </c>
-      <c r="K947">
-        <v>0</v>
-      </c>
-      <c r="L947">
-        <v>0</v>
-      </c>
-      <c r="M947">
-        <v>0</v>
-      </c>
-      <c r="N947">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="948" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A948" s="75"/>
-      <c r="B948" t="s">
-        <v>1097</v>
-      </c>
-      <c r="C948" t="s">
-        <v>1096</v>
-      </c>
-      <c r="E948">
-        <f>E946*COS(E947)*E945</f>
-        <v>1.2340226900152445E-2</v>
-      </c>
-      <c r="F948" t="e">
-        <f t="shared" ref="F948:N948" si="87">F946*COS(F947)*F945</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G948" t="e">
-        <f t="shared" si="87"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H948" t="e">
-        <f t="shared" si="87"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I948" t="e">
-        <f t="shared" si="87"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J948" t="e">
-        <f t="shared" si="87"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K948" t="e">
-        <f t="shared" si="87"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L948" t="e">
-        <f t="shared" si="87"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M948" t="e">
-        <f t="shared" si="87"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N948" t="e">
-        <f t="shared" si="87"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="949" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A949" s="37"/>
-    </row>
-    <row r="950" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A950" s="75" t="s">
-        <v>1110</v>
-      </c>
-      <c r="B950" t="s">
-        <v>1111</v>
-      </c>
-      <c r="C950" t="s">
-        <v>1112</v>
-      </c>
-      <c r="E950">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="F950" t="s">
-        <v>206</v>
-      </c>
-    </row>
     <row r="951" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A951" s="75"/>
-      <c r="B951" t="s">
-        <v>1090</v>
+      <c r="B951" s="84" t="s">
+        <v>1095</v>
       </c>
       <c r="C951" t="s">
-        <v>1113</v>
+        <v>1096</v>
       </c>
       <c r="E951">
-        <v>1E-3</v>
-      </c>
-      <c r="F951" t="s">
-        <v>206</v>
+        <v>0</v>
+      </c>
+      <c r="F951">
+        <v>0</v>
+      </c>
+      <c r="G951">
+        <v>0</v>
+      </c>
+      <c r="H951">
+        <v>0</v>
+      </c>
+      <c r="I951">
+        <v>0</v>
+      </c>
+      <c r="J951">
+        <v>0</v>
+      </c>
+      <c r="K951">
+        <v>0</v>
+      </c>
+      <c r="L951">
+        <v>0</v>
+      </c>
+      <c r="M951">
+        <v>0</v>
+      </c>
+      <c r="N951">
+        <v>0</v>
       </c>
     </row>
     <row r="952" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A952" s="75"/>
       <c r="B952" t="s">
-        <v>1114</v>
+        <v>1094</v>
       </c>
       <c r="C952" t="s">
-        <v>1115</v>
+        <v>1093</v>
       </c>
       <c r="E952">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="F952" t="s">
+        <f>E950*COS(E951)*E949</f>
+        <v>2.096571294539476E-2</v>
+      </c>
+      <c r="F952" t="e">
+        <f t="shared" ref="F952:N952" si="87">F950*COS(F951)*F949</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G952">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="H952">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="I952">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="J952">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="K952">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="L952">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="M952">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="N952">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="953" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A953" s="37"/>
+    </row>
+    <row r="954" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A954" s="75" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B954" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C954" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E954">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F954" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="953" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A953" s="75"/>
-      <c r="B953" t="s">
-        <v>1116</v>
-      </c>
-      <c r="E953">
-        <f>0.00000000508*E950*(LN(2*E950/(E951+E952))+0.5+(0.2235*(E951+E952)/E950))</f>
-        <v>2.2741325637156556E-10</v>
-      </c>
-      <c r="F953" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="954" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A954" s="75"/>
     </row>
     <row r="955" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A955" s="75"/>
+      <c r="B955" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C955" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E955">
+        <v>1E-3</v>
+      </c>
+      <c r="F955" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="956" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A956" s="75"/>
+      <c r="B956" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C956" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E956">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="F956" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="957" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A957" s="75"/>
+      <c r="B957" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E957">
+        <f>0.00000000508*E954*(LN(2*E954/(E955+E956))+0.5+(0.2235*(E955+E956)/E954))</f>
+        <v>2.2741325637156556E-10</v>
+      </c>
+      <c r="F957" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="958" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A958" s="75"/>
@@ -20414,9 +20447,6 @@
     <row r="960" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A960" s="75"/>
     </row>
-    <row r="961" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A961" s="75"/>
-    </row>
     <row r="962" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A962" s="75"/>
     </row>
@@ -20426,11 +20456,23 @@
     <row r="964" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A964" s="75"/>
     </row>
+    <row r="965" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A965" s="75"/>
+    </row>
+    <row r="966" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A966" s="75"/>
+    </row>
+    <row r="967" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A967" s="75"/>
+    </row>
+    <row r="968" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A968" s="75"/>
+    </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A940:A948"/>
-    <mergeCell ref="A950:A956"/>
-    <mergeCell ref="A958:A964"/>
+    <mergeCell ref="A940:A952"/>
+    <mergeCell ref="A954:A960"/>
+    <mergeCell ref="A962:A968"/>
     <mergeCell ref="A892:A906"/>
     <mergeCell ref="A568:A580"/>
     <mergeCell ref="A581:A584"/>

--- a/Spreadsheets/BasicCalculations.xlsx
+++ b/Spreadsheets/BasicCalculations.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="1138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="1147">
   <si>
     <t>N stages required</t>
   </si>
@@ -3460,6 +3460,33 @@
   </si>
   <si>
     <t>(d/(2l))^2</t>
+  </si>
+  <si>
+    <t>IPC-2221 Track Thickness Calculation</t>
+  </si>
+  <si>
+    <t>Internal else External</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>Allowable rise in temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross-Sectional Area </t>
+  </si>
+  <si>
+    <t>mil^2</t>
+  </si>
+  <si>
+    <t>Thickness</t>
+  </si>
+  <si>
+    <t>RMS Current</t>
+  </si>
+  <si>
+    <t>Width</t>
   </si>
 </sst>
 </file>
@@ -3854,7 +3881,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3871,6 +3898,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3882,9 +3912,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4738,15 +4765,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>3038475</xdr:colOff>
-      <xdr:row>950</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:colOff>2514600</xdr:colOff>
+      <xdr:row>945</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>628954</xdr:colOff>
-      <xdr:row>954</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>105079</xdr:colOff>
+      <xdr:row>949</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4763,8 +4790,84 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6619875" y="181575075"/>
+          <a:off x="6096000" y="181403625"/>
           <a:ext cx="3686479" cy="638175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>3829050</xdr:colOff>
+      <xdr:row>960</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1505260</xdr:colOff>
+      <xdr:row>966</xdr:row>
+      <xdr:rowOff>136</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Picture 16"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7410450" y="184251600"/>
+          <a:ext cx="2219635" cy="971686"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>3800475</xdr:colOff>
+      <xdr:row>966</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>676473</xdr:colOff>
+      <xdr:row>970</xdr:row>
+      <xdr:rowOff>95363</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Picture 19"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7381875" y="185270775"/>
+          <a:ext cx="1419423" cy="809738"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7130,13 +7233,13 @@
       <c r="E111" t="s">
         <v>25</v>
       </c>
-      <c r="G111" s="74" t="s">
+      <c r="G111" s="80" t="s">
         <v>1013</v>
       </c>
-      <c r="H111" s="74"/>
-      <c r="I111" s="74"/>
-      <c r="J111" s="74"/>
-      <c r="K111" s="74"/>
+      <c r="H111" s="80"/>
+      <c r="I111" s="80"/>
+      <c r="J111" s="80"/>
+      <c r="K111" s="80"/>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="75"/>
@@ -20116,35 +20219,35 @@
         <v>206</v>
       </c>
       <c r="G941">
-        <f>$E941</f>
+        <f t="shared" ref="G941:N941" si="86">$E941</f>
         <v>1.2566370614359173E-6</v>
       </c>
       <c r="H941">
-        <f>$E941</f>
+        <f t="shared" si="86"/>
         <v>1.2566370614359173E-6</v>
       </c>
       <c r="I941">
-        <f>$E941</f>
+        <f t="shared" si="86"/>
         <v>1.2566370614359173E-6</v>
       </c>
       <c r="J941">
-        <f>$E941</f>
+        <f t="shared" si="86"/>
         <v>1.2566370614359173E-6</v>
       </c>
       <c r="K941">
-        <f>$E941</f>
+        <f t="shared" si="86"/>
         <v>1.2566370614359173E-6</v>
       </c>
       <c r="L941">
-        <f>$E941</f>
+        <f t="shared" si="86"/>
         <v>1.2566370614359173E-6</v>
       </c>
       <c r="M941">
-        <f>$E941</f>
+        <f t="shared" si="86"/>
         <v>1.2566370614359173E-6</v>
       </c>
       <c r="N941">
-        <f>$E941</f>
+        <f t="shared" si="86"/>
         <v>1.2566370614359173E-6</v>
       </c>
     </row>
@@ -20242,35 +20345,35 @@
         <v>154</v>
       </c>
       <c r="G949">
-        <f t="shared" ref="F949:N949" si="86">(G941/(4*PI()))*(LN(G944+SQRT(1+G946)) - SQRT(1+G947)+G945)</f>
+        <f t="shared" ref="G949:N949" si="87">(G941/(4*PI()))*(LN(G944+SQRT(1+G946)) - SQRT(1+G947)+G945)</f>
         <v>-1.0000000000000001E-7</v>
       </c>
       <c r="H949">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>-1.0000000000000001E-7</v>
       </c>
       <c r="I949">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>-1.0000000000000001E-7</v>
       </c>
       <c r="J949">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>-1.0000000000000001E-7</v>
       </c>
       <c r="K949">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>-1.0000000000000001E-7</v>
       </c>
       <c r="L949">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>-1.0000000000000001E-7</v>
       </c>
       <c r="M949">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>-1.0000000000000001E-7</v>
       </c>
       <c r="N949">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>-1.0000000000000001E-7</v>
       </c>
     </row>
@@ -20289,7 +20392,7 @@
     </row>
     <row r="951" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A951" s="75"/>
-      <c r="B951" s="84" t="s">
+      <c r="B951" s="74" t="s">
         <v>1095</v>
       </c>
       <c r="C951" t="s">
@@ -20339,39 +20442,39 @@
         <v>2.096571294539476E-2</v>
       </c>
       <c r="F952" t="e">
-        <f t="shared" ref="F952:N952" si="87">F950*COS(F951)*F949</f>
+        <f t="shared" ref="F952:N952" si="88">F950*COS(F951)*F949</f>
         <v>#VALUE!</v>
       </c>
       <c r="G952">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="H952">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="I952">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="J952">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="K952">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="L952">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="M952">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="N952">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
     </row>
@@ -20447,40 +20550,106 @@
     <row r="960" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A960" s="75"/>
     </row>
-    <row r="962" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A962" s="75"/>
-    </row>
-    <row r="963" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A962" s="75" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B962" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C962" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E962" s="52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="963" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A963" s="75"/>
-    </row>
-    <row r="964" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B963" t="s">
+        <v>511</v>
+      </c>
+      <c r="E963" s="27">
+        <f>IF(E962, 0.024, 0.048)</f>
+        <v>4.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="964" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A964" s="75"/>
-    </row>
-    <row r="965" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B964" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C964" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E964" s="52">
+        <f>22/SQRT(3)</f>
+        <v>12.701705922171767</v>
+      </c>
+      <c r="F964" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="965" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A965" s="75"/>
-    </row>
-    <row r="966" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B965" s="74" t="s">
+        <v>693</v>
+      </c>
+      <c r="C965" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E965">
+        <v>10</v>
+      </c>
+      <c r="F965" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="966" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A966" s="75"/>
-    </row>
-    <row r="967" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C966" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E966">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="967" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A967" s="75"/>
-    </row>
-    <row r="968" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B967" t="s">
+        <v>20</v>
+      </c>
+      <c r="C967" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E967">
+        <f>POWER(E964/(E963*POWER(E965, 0.44)), (1/0.725))</f>
+        <v>542.8119517712156</v>
+      </c>
+      <c r="F967" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="968" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A968" s="75"/>
+      <c r="C968" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E968">
+        <f>E967/(E966*1.378*39.37)</f>
+        <v>5.0027036102653044</v>
+      </c>
+      <c r="F968" t="s">
+        <v>133</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A940:A952"/>
-    <mergeCell ref="A954:A960"/>
-    <mergeCell ref="A962:A968"/>
-    <mergeCell ref="A892:A906"/>
-    <mergeCell ref="A568:A580"/>
-    <mergeCell ref="A581:A584"/>
-    <mergeCell ref="A781:A793"/>
-    <mergeCell ref="A695:A766"/>
-    <mergeCell ref="A653:A692"/>
-    <mergeCell ref="A799:A819"/>
-    <mergeCell ref="A821:A841"/>
+    <mergeCell ref="G111:K111"/>
+    <mergeCell ref="A99:A136"/>
+    <mergeCell ref="A196:A220"/>
+    <mergeCell ref="A167:A193"/>
+    <mergeCell ref="A138:A164"/>
     <mergeCell ref="A31:A59"/>
     <mergeCell ref="A858:A883"/>
     <mergeCell ref="A286:A337"/>
@@ -20497,16 +20666,22 @@
     <mergeCell ref="A844:A856"/>
     <mergeCell ref="A414:A454"/>
     <mergeCell ref="A456:A566"/>
+    <mergeCell ref="A940:A952"/>
+    <mergeCell ref="A954:A960"/>
+    <mergeCell ref="A962:A968"/>
+    <mergeCell ref="A892:A906"/>
+    <mergeCell ref="A568:A580"/>
+    <mergeCell ref="A581:A584"/>
+    <mergeCell ref="A781:A793"/>
+    <mergeCell ref="A695:A766"/>
+    <mergeCell ref="A653:A692"/>
+    <mergeCell ref="A799:A819"/>
+    <mergeCell ref="A821:A841"/>
     <mergeCell ref="A910:A912"/>
     <mergeCell ref="A915:A917"/>
     <mergeCell ref="A920:A922"/>
     <mergeCell ref="A925:A930"/>
     <mergeCell ref="A932:A937"/>
-    <mergeCell ref="G111:K111"/>
-    <mergeCell ref="A99:A136"/>
-    <mergeCell ref="A196:A220"/>
-    <mergeCell ref="A167:A193"/>
-    <mergeCell ref="A138:A164"/>
   </mergeCells>
   <conditionalFormatting sqref="D120">
     <cfRule type="cellIs" dxfId="11" priority="11" operator="notEqual">
@@ -20809,17 +20984,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="81" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="80"/>
+      <c r="B1" s="81"/>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C18" s="81" t="s">
+      <c r="C18" s="82" t="s">
         <v>161</v>
       </c>
-      <c r="D18" s="82"/>
-      <c r="E18" s="83"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="84"/>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C19" s="17" t="s">
@@ -21013,17 +21188,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="81" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="80"/>
+      <c r="B1" s="81"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="81" t="s">
+      <c r="B17" s="82" t="s">
         <v>161</v>
       </c>
-      <c r="C17" s="82"/>
-      <c r="D17" s="83"/>
+      <c r="C17" s="83"/>
+      <c r="D17" s="84"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B18" s="17" t="s">
@@ -21276,17 +21451,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="81" t="s">
         <v>167</v>
       </c>
-      <c r="B1" s="80"/>
+      <c r="B1" s="81"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="81" t="s">
+      <c r="B17" s="82" t="s">
         <v>161</v>
       </c>
-      <c r="C17" s="82"/>
-      <c r="D17" s="83"/>
+      <c r="C17" s="83"/>
+      <c r="D17" s="84"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B18" s="17" t="s">

--- a/Spreadsheets/BasicCalculations.xlsx
+++ b/Spreadsheets/BasicCalculations.xlsx
@@ -3884,6 +3884,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3897,9 +3900,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4067,7 +4067,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>709268</xdr:colOff>
+      <xdr:colOff>743904</xdr:colOff>
       <xdr:row>285</xdr:row>
       <xdr:rowOff>23213</xdr:rowOff>
     </xdr:to>
@@ -4105,7 +4105,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>512266</xdr:colOff>
+      <xdr:colOff>481958</xdr:colOff>
       <xdr:row>376</xdr:row>
       <xdr:rowOff>46128</xdr:rowOff>
     </xdr:to>
@@ -4143,7 +4143,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>322861</xdr:colOff>
+      <xdr:colOff>374815</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>121227</xdr:rowOff>
     </xdr:to>
@@ -4181,7 +4181,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>415638</xdr:colOff>
+      <xdr:colOff>480582</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>177458</xdr:rowOff>
     </xdr:to>
@@ -4345,7 +4345,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>13820</xdr:colOff>
+      <xdr:colOff>35466</xdr:colOff>
       <xdr:row>322</xdr:row>
       <xdr:rowOff>65731</xdr:rowOff>
     </xdr:to>
@@ -4383,7 +4383,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1282200</xdr:colOff>
+      <xdr:colOff>1286530</xdr:colOff>
       <xdr:row>831</xdr:row>
       <xdr:rowOff>101281</xdr:rowOff>
     </xdr:to>
@@ -4505,7 +4505,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>293081</xdr:colOff>
+      <xdr:colOff>319057</xdr:colOff>
       <xdr:row>551</xdr:row>
       <xdr:rowOff>112978</xdr:rowOff>
     </xdr:to>
@@ -4543,7 +4543,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>228966</xdr:colOff>
+      <xdr:colOff>263602</xdr:colOff>
       <xdr:row>555</xdr:row>
       <xdr:rowOff>72209</xdr:rowOff>
     </xdr:to>
@@ -4581,7 +4581,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>286453</xdr:colOff>
+      <xdr:colOff>338407</xdr:colOff>
       <xdr:row>526</xdr:row>
       <xdr:rowOff>53235</xdr:rowOff>
     </xdr:to>
@@ -4619,7 +4619,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>458947</xdr:colOff>
+      <xdr:colOff>484923</xdr:colOff>
       <xdr:row>534</xdr:row>
       <xdr:rowOff>15171</xdr:rowOff>
     </xdr:to>
@@ -4657,7 +4657,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1407499</xdr:colOff>
+      <xdr:colOff>1433475</xdr:colOff>
       <xdr:row>555</xdr:row>
       <xdr:rowOff>84877</xdr:rowOff>
     </xdr:to>
@@ -4695,7 +4695,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>557086</xdr:colOff>
+      <xdr:colOff>483482</xdr:colOff>
       <xdr:row>555</xdr:row>
       <xdr:rowOff>65826</xdr:rowOff>
     </xdr:to>
@@ -4733,7 +4733,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>975913</xdr:colOff>
+      <xdr:colOff>1010549</xdr:colOff>
       <xdr:row>503</xdr:row>
       <xdr:rowOff>147056</xdr:rowOff>
     </xdr:to>
@@ -4766,13 +4766,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2514600</xdr:colOff>
-      <xdr:row>945</xdr:row>
+      <xdr:row>951</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>105079</xdr:colOff>
-      <xdr:row>949</xdr:row>
+      <xdr:row>955</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4804,13 +4804,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3829050</xdr:colOff>
-      <xdr:row>960</xdr:row>
+      <xdr:row>966</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1505260</xdr:colOff>
-      <xdr:row>966</xdr:row>
+      <xdr:colOff>1483610</xdr:colOff>
+      <xdr:row>972</xdr:row>
       <xdr:rowOff>136</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4842,13 +4842,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3800475</xdr:colOff>
-      <xdr:row>966</xdr:row>
+      <xdr:row>972</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>676473</xdr:colOff>
-      <xdr:row>970</xdr:row>
+      <xdr:colOff>654823</xdr:colOff>
+      <xdr:row>976</xdr:row>
       <xdr:rowOff>95363</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5768,7 +5768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CX968"/>
+  <dimension ref="A1:CX974"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" customWidth="1"/>
@@ -6019,15 +6019,15 @@
       <c r="C19" s="7"/>
       <c r="D19" s="12"/>
       <c r="E19" s="7"/>
-      <c r="G19" s="77" t="s">
+      <c r="G19" s="78" t="s">
         <v>569</v>
       </c>
-      <c r="H19" s="77"/>
-      <c r="I19" s="77"/>
-      <c r="J19" s="77"/>
+      <c r="H19" s="78"/>
+      <c r="I19" s="78"/>
+      <c r="J19" s="78"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="75" t="s">
+      <c r="A20" s="76" t="s">
         <v>98</v>
       </c>
       <c r="B20" t="s">
@@ -6042,13 +6042,13 @@
       <c r="E20" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="77"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="77"/>
-      <c r="J20" s="77"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="78"/>
+      <c r="I20" s="78"/>
+      <c r="J20" s="78"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="75"/>
+      <c r="A21" s="76"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5" t="s">
         <v>3</v>
@@ -6060,13 +6060,13 @@
       <c r="E21" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G21" s="77"/>
-      <c r="H21" s="77"/>
-      <c r="I21" s="77"/>
-      <c r="J21" s="77"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="78"/>
+      <c r="I21" s="78"/>
+      <c r="J21" s="78"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="75"/>
+      <c r="A22" s="76"/>
       <c r="B22" t="s">
         <v>64</v>
       </c>
@@ -6076,13 +6076,13 @@
       <c r="D22">
         <v>0.1</v>
       </c>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
-      <c r="J22" s="77"/>
+      <c r="G22" s="78"/>
+      <c r="H22" s="78"/>
+      <c r="I22" s="78"/>
+      <c r="J22" s="78"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="75"/>
+      <c r="A23" s="76"/>
       <c r="B23" s="5"/>
       <c r="C23" s="11" t="s">
         <v>67</v>
@@ -6094,7 +6094,7 @@
       <c r="E23" s="5"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="75"/>
+      <c r="A24" s="76"/>
       <c r="C24" t="s">
         <v>7</v>
       </c>
@@ -6103,7 +6103,7 @@
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="75"/>
+      <c r="A25" s="76"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5" t="s">
         <v>28</v>
@@ -6112,7 +6112,7 @@
       <c r="E25" s="5"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="75"/>
+      <c r="A26" s="76"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5" t="s">
         <v>12</v>
@@ -6126,7 +6126,7 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="75"/>
+      <c r="A27" s="76"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5" t="s">
         <v>11</v>
@@ -6140,7 +6140,7 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="75"/>
+      <c r="A28" s="76"/>
       <c r="C28" t="s">
         <v>8</v>
       </c>
@@ -6152,7 +6152,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="75"/>
+      <c r="A29" s="76"/>
       <c r="C29" t="s">
         <v>10</v>
       </c>
@@ -6163,41 +6163,41 @@
       <c r="E29" t="s">
         <v>25</v>
       </c>
-      <c r="G29" s="77" t="s">
+      <c r="G29" s="78" t="s">
         <v>570</v>
       </c>
-      <c r="H29" s="78"/>
-      <c r="I29" s="78"/>
-      <c r="J29" s="78"/>
-      <c r="K29" s="78"/>
+      <c r="H29" s="79"/>
+      <c r="I29" s="79"/>
+      <c r="J29" s="79"/>
+      <c r="K29" s="79"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B30" s="7"/>
       <c r="C30" s="9"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
-      <c r="G30" s="78"/>
-      <c r="H30" s="78"/>
-      <c r="I30" s="78"/>
-      <c r="J30" s="78"/>
-      <c r="K30" s="78"/>
+      <c r="G30" s="79"/>
+      <c r="H30" s="79"/>
+      <c r="I30" s="79"/>
+      <c r="J30" s="79"/>
+      <c r="K30" s="79"/>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="75" t="s">
+      <c r="A31" s="76" t="s">
         <v>126</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="6"/>
-      <c r="G31" s="78"/>
-      <c r="H31" s="78"/>
-      <c r="I31" s="78"/>
-      <c r="J31" s="78"/>
-      <c r="K31" s="78"/>
+      <c r="G31" s="79"/>
+      <c r="H31" s="79"/>
+      <c r="I31" s="79"/>
+      <c r="J31" s="79"/>
+      <c r="K31" s="79"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="75"/>
+      <c r="A32" s="76"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5" t="s">
         <v>120</v>
@@ -6209,14 +6209,14 @@
       <c r="E32" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G32" s="78"/>
-      <c r="H32" s="78"/>
-      <c r="I32" s="78"/>
-      <c r="J32" s="78"/>
-      <c r="K32" s="78"/>
+      <c r="G32" s="79"/>
+      <c r="H32" s="79"/>
+      <c r="I32" s="79"/>
+      <c r="J32" s="79"/>
+      <c r="K32" s="79"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="75"/>
+      <c r="A33" s="76"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7" t="s">
         <v>121</v>
@@ -6227,14 +6227,14 @@
       <c r="E33" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="G33" s="78"/>
-      <c r="H33" s="78"/>
-      <c r="I33" s="78"/>
-      <c r="J33" s="78"/>
-      <c r="K33" s="78"/>
+      <c r="G33" s="79"/>
+      <c r="H33" s="79"/>
+      <c r="I33" s="79"/>
+      <c r="J33" s="79"/>
+      <c r="K33" s="79"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="75"/>
+      <c r="A34" s="76"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7" t="s">
         <v>122</v>
@@ -6243,14 +6243,14 @@
         <v>5</v>
       </c>
       <c r="E34" s="8"/>
-      <c r="G34" s="78"/>
-      <c r="H34" s="78"/>
-      <c r="I34" s="78"/>
-      <c r="J34" s="78"/>
-      <c r="K34" s="78"/>
+      <c r="G34" s="79"/>
+      <c r="H34" s="79"/>
+      <c r="I34" s="79"/>
+      <c r="J34" s="79"/>
+      <c r="K34" s="79"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="75"/>
+      <c r="A35" s="76"/>
       <c r="C35" t="s">
         <v>127</v>
       </c>
@@ -6260,7 +6260,7 @@
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="75"/>
+      <c r="A36" s="76"/>
       <c r="C36" t="s">
         <v>130</v>
       </c>
@@ -6272,7 +6272,7 @@
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="75"/>
+      <c r="A37" s="76"/>
       <c r="C37" t="s">
         <v>163</v>
       </c>
@@ -6282,7 +6282,7 @@
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="75"/>
+      <c r="A38" s="76"/>
       <c r="C38" t="s">
         <v>164</v>
       </c>
@@ -6292,7 +6292,7 @@
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="75"/>
+      <c r="A39" s="76"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5" t="s">
         <v>9</v>
@@ -6306,7 +6306,7 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="75"/>
+      <c r="A40" s="76"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5" t="s">
         <v>748</v>
@@ -6320,7 +6320,7 @@
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="75"/>
+      <c r="A41" s="76"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
         <v>165</v>
@@ -6332,7 +6332,7 @@
       <c r="E41" s="5"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="75"/>
+      <c r="A42" s="76"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5" t="s">
         <v>166</v>
@@ -6344,7 +6344,7 @@
       <c r="E42" s="5"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="75"/>
+      <c r="A43" s="76"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5" t="s">
         <v>749</v>
@@ -6358,7 +6358,7 @@
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="75"/>
+      <c r="A44" s="76"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5" t="s">
         <v>27</v>
@@ -6372,7 +6372,7 @@
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="75"/>
+      <c r="A45" s="76"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5" t="s">
         <v>746</v>
@@ -6385,7 +6385,7 @@
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="75"/>
+      <c r="A46" s="76"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5" t="s">
         <v>747</v>
@@ -6397,7 +6397,7 @@
       <c r="E46" s="5"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="75"/>
+      <c r="A47" s="76"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5" t="s">
         <v>750</v>
@@ -6409,14 +6409,14 @@
       <c r="E47" s="5"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="75"/>
+      <c r="A48" s="76"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
       <c r="D48" s="10"/>
       <c r="E48" s="5"/>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A49" s="75"/>
+      <c r="A49" s="76"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7" t="s">
         <v>752</v>
@@ -6428,7 +6428,7 @@
       <c r="E49" s="7"/>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A50" s="75"/>
+      <c r="A50" s="76"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7" t="s">
         <v>662</v>
@@ -6439,7 +6439,7 @@
       <c r="E50" s="7"/>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A51" s="75"/>
+      <c r="A51" s="76"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7" t="s">
         <v>663</v>
@@ -6450,7 +6450,7 @@
       <c r="E51" s="7"/>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A52" s="75"/>
+      <c r="A52" s="76"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7" t="s">
         <v>753</v>
@@ -6462,7 +6462,7 @@
       <c r="E52" s="7"/>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A53" s="75"/>
+      <c r="A53" s="76"/>
       <c r="B53" s="39"/>
       <c r="C53" s="39" t="s">
         <v>194</v>
@@ -6474,7 +6474,7 @@
       <c r="E53" s="39"/>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A54" s="75"/>
+      <c r="A54" s="76"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5" t="s">
         <v>755</v>
@@ -6486,7 +6486,7 @@
       <c r="E54" s="5"/>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A55" s="75"/>
+      <c r="A55" s="76"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5" t="s">
         <v>756</v>
@@ -6499,7 +6499,7 @@
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A56" s="75"/>
+      <c r="A56" s="76"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5" t="s">
         <v>758</v>
@@ -6510,7 +6510,7 @@
       <c r="E56" s="5"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A57" s="75"/>
+      <c r="A57" s="76"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5" t="s">
         <v>754</v>
@@ -6522,7 +6522,7 @@
       <c r="E57" s="5"/>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A58" s="75"/>
+      <c r="A58" s="76"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5" t="s">
         <v>759</v>
@@ -6534,7 +6534,7 @@
       <c r="E58" s="5"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A59" s="75"/>
+      <c r="A59" s="76"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5" t="s">
         <v>760</v>
@@ -6558,7 +6558,7 @@
       </c>
     </row>
     <row r="61" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="75" t="s">
+      <c r="A61" s="76" t="s">
         <v>30</v>
       </c>
       <c r="C61" s="7" t="s">
@@ -6582,7 +6582,7 @@
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A62" s="75"/>
+      <c r="A62" s="76"/>
       <c r="C62" s="7" t="s">
         <v>26</v>
       </c>
@@ -6604,7 +6604,7 @@
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A63" s="75"/>
+      <c r="A63" s="76"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5" t="s">
         <v>13</v>
@@ -6628,7 +6628,7 @@
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A64" s="75"/>
+      <c r="A64" s="76"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5" t="s">
         <v>14</v>
@@ -6649,7 +6649,7 @@
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A65" s="75"/>
+      <c r="A65" s="76"/>
       <c r="C65" s="7" t="s">
         <v>16</v>
       </c>
@@ -6672,7 +6672,7 @@
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A66" s="75"/>
+      <c r="A66" s="76"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5" t="s">
         <v>102</v>
@@ -6693,7 +6693,7 @@
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A67" s="75"/>
+      <c r="A67" s="76"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5" t="s">
         <v>15</v>
@@ -6714,7 +6714,7 @@
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A68" s="75"/>
+      <c r="A68" s="76"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5" t="s">
         <v>32</v>
@@ -6726,7 +6726,7 @@
       <c r="E68" s="5"/>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A69" s="75"/>
+      <c r="A69" s="76"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5" t="s">
         <v>103</v>
@@ -6745,7 +6745,7 @@
       <c r="E70" s="7"/>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A71" s="76" t="s">
+      <c r="A71" s="77" t="s">
         <v>104</v>
       </c>
       <c r="C71" s="5"/>
@@ -6753,7 +6753,7 @@
       <c r="E71" s="5"/>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A72" s="76"/>
+      <c r="A72" s="77"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5" t="s">
         <v>85</v>
@@ -6765,7 +6765,7 @@
       <c r="E72" s="5"/>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A73" s="76"/>
+      <c r="A73" s="77"/>
       <c r="B73" s="5" t="s">
         <v>119</v>
       </c>
@@ -6781,7 +6781,7 @@
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A74" s="76"/>
+      <c r="A74" s="77"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5" t="s">
         <v>129</v>
@@ -6793,7 +6793,7 @@
       <c r="E74" s="5"/>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A75" s="76"/>
+      <c r="A75" s="77"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5" t="s">
         <v>86</v>
@@ -6806,7 +6806,7 @@
       <c r="R75" s="1"/>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A76" s="76"/>
+      <c r="A76" s="77"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5" t="s">
         <v>87</v>
@@ -6818,7 +6818,7 @@
       <c r="E76" s="5"/>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A77" s="76"/>
+      <c r="A77" s="77"/>
       <c r="B77" s="5" t="s">
         <v>118</v>
       </c>
@@ -6832,7 +6832,7 @@
       <c r="E77" s="5"/>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A78" s="76"/>
+      <c r="A78" s="77"/>
       <c r="B78" s="5" t="s">
         <v>114</v>
       </c>
@@ -6846,7 +6846,7 @@
       <c r="E78" s="5"/>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A79" s="76"/>
+      <c r="A79" s="77"/>
       <c r="B79" s="5" t="s">
         <v>117</v>
       </c>
@@ -6860,7 +6860,7 @@
       <c r="E79" s="5"/>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A80" s="76"/>
+      <c r="A80" s="77"/>
       <c r="C80" t="s">
         <v>89</v>
       </c>
@@ -6869,7 +6869,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="76"/>
+      <c r="A81" s="77"/>
       <c r="C81" t="s">
         <v>90</v>
       </c>
@@ -6878,7 +6878,7 @@
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="76"/>
+      <c r="A82" s="77"/>
       <c r="C82" t="s">
         <v>91</v>
       </c>
@@ -6893,7 +6893,7 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="76"/>
+      <c r="A83" s="77"/>
       <c r="C83" t="s">
         <v>92</v>
       </c>
@@ -6903,7 +6903,7 @@
       <c r="G83" s="4"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="76"/>
+      <c r="A84" s="77"/>
       <c r="C84" t="s">
         <v>93</v>
       </c>
@@ -6912,7 +6912,7 @@
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="76"/>
+      <c r="A85" s="77"/>
       <c r="C85" t="s">
         <v>94</v>
       </c>
@@ -6921,7 +6921,7 @@
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="76"/>
+      <c r="A86" s="77"/>
       <c r="C86" t="s">
         <v>95</v>
       </c>
@@ -6930,7 +6930,7 @@
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="76"/>
+      <c r="A87" s="77"/>
       <c r="C87" t="s">
         <v>108</v>
       </c>
@@ -6939,7 +6939,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="76"/>
+      <c r="A88" s="77"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5" t="s">
         <v>105</v>
@@ -6951,7 +6951,7 @@
       <c r="E88" s="5"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="76"/>
+      <c r="A89" s="77"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5" t="s">
         <v>106</v>
@@ -6963,7 +6963,7 @@
       <c r="E89" s="5"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="76"/>
+      <c r="A90" s="77"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5" t="s">
         <v>107</v>
@@ -6975,7 +6975,7 @@
       <c r="E90" s="5"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="76"/>
+      <c r="A91" s="77"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5" t="s">
         <v>109</v>
@@ -6987,7 +6987,7 @@
       <c r="E91" s="5"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="76"/>
+      <c r="A92" s="77"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5" t="s">
         <v>110</v>
@@ -6999,7 +6999,7 @@
       <c r="E92" s="5"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="76"/>
+      <c r="A93" s="77"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5" t="s">
         <v>111</v>
@@ -7011,7 +7011,7 @@
       <c r="E93" s="5"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="76"/>
+      <c r="A94" s="77"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5" t="s">
         <v>112</v>
@@ -7023,7 +7023,7 @@
       <c r="E94" s="5"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="76"/>
+      <c r="A95" s="77"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5" t="s">
         <v>113</v>
@@ -7044,7 +7044,7 @@
       </c>
     </row>
     <row r="99" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="75" t="s">
+      <c r="A99" s="76" t="s">
         <v>1014</v>
       </c>
       <c r="B99" s="7" t="s">
@@ -7062,7 +7062,7 @@
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100" s="75"/>
+      <c r="A100" s="76"/>
       <c r="B100" s="7" t="s">
         <v>994</v>
       </c>
@@ -7078,7 +7078,7 @@
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" s="75"/>
+      <c r="A101" s="76"/>
       <c r="B101" s="7" t="s">
         <v>47</v>
       </c>
@@ -7094,7 +7094,7 @@
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" s="75"/>
+      <c r="A102" s="76"/>
       <c r="B102" t="s">
         <v>986</v>
       </c>
@@ -7110,7 +7110,7 @@
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" s="75"/>
+      <c r="A103" s="76"/>
       <c r="B103" t="s">
         <v>37</v>
       </c>
@@ -7126,7 +7126,7 @@
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104" s="75"/>
+      <c r="A104" s="76"/>
       <c r="B104" t="s">
         <v>38</v>
       </c>
@@ -7139,7 +7139,7 @@
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A105" s="75"/>
+      <c r="A105" s="76"/>
       <c r="B105" s="7" t="s">
         <v>60</v>
       </c>
@@ -7155,7 +7155,7 @@
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A106" s="75"/>
+      <c r="A106" s="76"/>
       <c r="B106" t="s">
         <v>56</v>
       </c>
@@ -7170,7 +7170,7 @@
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107" s="75"/>
+      <c r="A107" s="76"/>
       <c r="B107" t="s">
         <v>55</v>
       </c>
@@ -7182,7 +7182,7 @@
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" s="75"/>
+      <c r="A108" s="76"/>
       <c r="B108" t="s">
         <v>49</v>
       </c>
@@ -7198,7 +7198,7 @@
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A109" s="75"/>
+      <c r="A109" s="76"/>
       <c r="C109" t="s">
         <v>36</v>
       </c>
@@ -7207,7 +7207,7 @@
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A110" s="75"/>
+      <c r="A110" s="76"/>
       <c r="B110" t="s">
         <v>39</v>
       </c>
@@ -7219,7 +7219,7 @@
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A111" s="75"/>
+      <c r="A111" s="76"/>
       <c r="B111" t="s">
         <v>558</v>
       </c>
@@ -7233,16 +7233,16 @@
       <c r="E111" t="s">
         <v>25</v>
       </c>
-      <c r="G111" s="80" t="s">
+      <c r="G111" s="75" t="s">
         <v>1013</v>
       </c>
-      <c r="H111" s="80"/>
-      <c r="I111" s="80"/>
-      <c r="J111" s="80"/>
-      <c r="K111" s="80"/>
+      <c r="H111" s="75"/>
+      <c r="I111" s="75"/>
+      <c r="J111" s="75"/>
+      <c r="K111" s="75"/>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A112" s="75"/>
+      <c r="A112" s="76"/>
       <c r="B112" t="s">
         <v>1029</v>
       </c>
@@ -7260,7 +7260,7 @@
       <c r="K112" s="68"/>
     </row>
     <row r="113" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A113" s="75"/>
+      <c r="A113" s="76"/>
       <c r="B113" t="s">
         <v>1030</v>
       </c>
@@ -7291,7 +7291,7 @@
       </c>
     </row>
     <row r="114" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A114" s="75"/>
+      <c r="A114" s="76"/>
       <c r="B114" t="s">
         <v>40</v>
       </c>
@@ -7325,7 +7325,7 @@
       </c>
     </row>
     <row r="115" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A115" s="75"/>
+      <c r="A115" s="76"/>
       <c r="C115" s="57" t="s">
         <v>1032</v>
       </c>
@@ -7335,7 +7335,7 @@
       </c>
     </row>
     <row r="116" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A116" s="75"/>
+      <c r="A116" s="76"/>
       <c r="C116" s="57" t="s">
         <v>1033</v>
       </c>
@@ -7345,7 +7345,7 @@
       </c>
     </row>
     <row r="117" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A117" s="75"/>
+      <c r="A117" s="76"/>
       <c r="B117" t="s">
         <v>62</v>
       </c>
@@ -7373,7 +7373,7 @@
       </c>
     </row>
     <row r="118" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A118" s="75"/>
+      <c r="A118" s="76"/>
       <c r="B118" t="s">
         <v>51</v>
       </c>
@@ -7461,7 +7461,7 @@
       </c>
     </row>
     <row r="119" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A119" s="75"/>
+      <c r="A119" s="76"/>
       <c r="B119" t="s">
         <v>53</v>
       </c>
@@ -7477,7 +7477,7 @@
       </c>
     </row>
     <row r="120" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A120" s="75"/>
+      <c r="A120" s="76"/>
       <c r="C120" t="s">
         <v>58</v>
       </c>
@@ -7487,7 +7487,7 @@
       </c>
     </row>
     <row r="121" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A121" s="75"/>
+      <c r="A121" s="76"/>
       <c r="B121" t="s">
         <v>1021</v>
       </c>
@@ -7500,7 +7500,7 @@
       </c>
     </row>
     <row r="122" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A122" s="75"/>
+      <c r="A122" s="76"/>
       <c r="B122" t="s">
         <v>1024</v>
       </c>
@@ -7513,7 +7513,7 @@
       </c>
     </row>
     <row r="123" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A123" s="75"/>
+      <c r="A123" s="76"/>
       <c r="B123" t="s">
         <v>1023</v>
       </c>
@@ -7526,7 +7526,7 @@
       </c>
     </row>
     <row r="124" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A124" s="75"/>
+      <c r="A124" s="76"/>
       <c r="B124" t="s">
         <v>1027</v>
       </c>
@@ -7539,7 +7539,7 @@
       </c>
     </row>
     <row r="125" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A125" s="75"/>
+      <c r="A125" s="76"/>
       <c r="B125" t="s">
         <v>1037</v>
       </c>
@@ -7552,7 +7552,7 @@
       </c>
     </row>
     <row r="126" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A126" s="75"/>
+      <c r="A126" s="76"/>
       <c r="C126" t="s">
         <v>1031</v>
       </c>
@@ -7562,7 +7562,7 @@
       </c>
     </row>
     <row r="127" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A127" s="75"/>
+      <c r="A127" s="76"/>
       <c r="C127" t="s">
         <v>1034</v>
       </c>
@@ -7572,7 +7572,7 @@
       </c>
     </row>
     <row r="128" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A128" s="75"/>
+      <c r="A128" s="76"/>
       <c r="C128" t="s">
         <v>1035</v>
       </c>
@@ -7582,7 +7582,7 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" s="75"/>
+      <c r="A129" s="76"/>
       <c r="C129" t="s">
         <v>1036</v>
       </c>
@@ -7592,18 +7592,18 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" s="75"/>
+      <c r="A130" s="76"/>
       <c r="D130" s="27" t="str">
         <f>IF(D129, "Demagnetisation may not complete with 0.5 duty cycle", "Demagnetisation should complete for 0.5 duty cycle")</f>
         <v>Demagnetisation may not complete with 0.5 duty cycle</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" s="75"/>
+      <c r="A131" s="76"/>
       <c r="D131" s="27"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" s="75"/>
+      <c r="A132" s="76"/>
       <c r="C132" t="s">
         <v>63</v>
       </c>
@@ -7613,7 +7613,7 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" s="75"/>
+      <c r="A133" s="76"/>
       <c r="B133" s="58" t="s">
         <v>988</v>
       </c>
@@ -7632,7 +7632,7 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="75"/>
+      <c r="A134" s="76"/>
       <c r="B134" s="70" t="s">
         <v>989</v>
       </c>
@@ -7646,7 +7646,7 @@
       <c r="E134" s="70"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" s="75"/>
+      <c r="A135" s="76"/>
       <c r="B135" s="70" t="s">
         <v>791</v>
       </c>
@@ -7665,7 +7665,7 @@
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="75"/>
+      <c r="A136" s="76"/>
       <c r="B136" t="s">
         <v>168</v>
       </c>
@@ -7682,7 +7682,7 @@
       <c r="D137" s="27"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="75" t="s">
+      <c r="A138" s="76" t="s">
         <v>1015</v>
       </c>
       <c r="B138" s="7" t="s">
@@ -7696,7 +7696,7 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="75"/>
+      <c r="A139" s="76"/>
       <c r="B139" s="7" t="s">
         <v>993</v>
       </c>
@@ -7712,7 +7712,7 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="75"/>
+      <c r="A140" s="76"/>
       <c r="B140" s="7" t="s">
         <v>994</v>
       </c>
@@ -7727,7 +7727,7 @@
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" s="75"/>
+      <c r="A141" s="76"/>
       <c r="B141" s="7" t="s">
         <v>47</v>
       </c>
@@ -7743,7 +7743,7 @@
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" s="75"/>
+      <c r="A142" s="76"/>
       <c r="B142" t="s">
         <v>986</v>
       </c>
@@ -7759,7 +7759,7 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" s="75"/>
+      <c r="A143" s="76"/>
       <c r="B143" t="s">
         <v>38</v>
       </c>
@@ -7775,7 +7775,7 @@
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" s="75"/>
+      <c r="A144" s="76"/>
       <c r="B144" s="7" t="s">
         <v>1016</v>
       </c>
@@ -7791,7 +7791,7 @@
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" s="75"/>
+      <c r="A145" s="76"/>
       <c r="B145" t="s">
         <v>56</v>
       </c>
@@ -7806,7 +7806,7 @@
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A146" s="75"/>
+      <c r="A146" s="76"/>
       <c r="B146" t="s">
         <v>55</v>
       </c>
@@ -7818,7 +7818,7 @@
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" s="75"/>
+      <c r="A147" s="76"/>
       <c r="B147" t="s">
         <v>49</v>
       </c>
@@ -7834,7 +7834,7 @@
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" s="75"/>
+      <c r="A148" s="76"/>
       <c r="C148" t="s">
         <v>36</v>
       </c>
@@ -7843,7 +7843,7 @@
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149" s="75"/>
+      <c r="A149" s="76"/>
       <c r="B149" t="s">
         <v>137</v>
       </c>
@@ -7855,7 +7855,7 @@
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A150" s="75"/>
+      <c r="A150" s="76"/>
       <c r="B150" t="s">
         <v>558</v>
       </c>
@@ -7871,7 +7871,7 @@
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151" s="75"/>
+      <c r="A151" s="76"/>
       <c r="B151" t="s">
         <v>44</v>
       </c>
@@ -7887,7 +7887,7 @@
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A152" s="75"/>
+      <c r="A152" s="76"/>
       <c r="B152" t="s">
         <v>40</v>
       </c>
@@ -7903,7 +7903,7 @@
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153" s="75"/>
+      <c r="A153" s="76"/>
       <c r="B153" t="s">
         <v>62</v>
       </c>
@@ -7913,7 +7913,7 @@
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A154" s="75"/>
+      <c r="A154" s="76"/>
       <c r="B154" t="s">
         <v>51</v>
       </c>
@@ -7926,7 +7926,7 @@
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" s="75"/>
+      <c r="A155" s="76"/>
       <c r="B155" t="s">
         <v>53</v>
       </c>
@@ -7942,7 +7942,7 @@
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" s="75"/>
+      <c r="A156" s="76"/>
       <c r="C156" t="s">
         <v>58</v>
       </c>
@@ -7952,7 +7952,7 @@
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A157" s="75"/>
+      <c r="A157" s="76"/>
       <c r="B157" t="s">
         <v>560</v>
       </c>
@@ -7965,7 +7965,7 @@
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A158" s="75"/>
+      <c r="A158" s="76"/>
       <c r="B158" t="s">
         <v>561</v>
       </c>
@@ -7978,10 +7978,10 @@
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159" s="75"/>
+      <c r="A159" s="76"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A160" s="75"/>
+      <c r="A160" s="76"/>
       <c r="C160" t="s">
         <v>63</v>
       </c>
@@ -7991,7 +7991,7 @@
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A161" s="75"/>
+      <c r="A161" s="76"/>
       <c r="B161" s="58" t="s">
         <v>988</v>
       </c>
@@ -8007,7 +8007,7 @@
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A162" s="75"/>
+      <c r="A162" s="76"/>
       <c r="B162" t="s">
         <v>989</v>
       </c>
@@ -8020,7 +8020,7 @@
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A163" s="75"/>
+      <c r="A163" s="76"/>
       <c r="B163" t="s">
         <v>791</v>
       </c>
@@ -8036,7 +8036,7 @@
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A164" s="75"/>
+      <c r="A164" s="76"/>
       <c r="B164" t="s">
         <v>168</v>
       </c>
@@ -8057,7 +8057,7 @@
       <c r="D166" s="27"/>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A167" s="75" t="s">
+      <c r="A167" s="76" t="s">
         <v>1005</v>
       </c>
       <c r="B167" t="s">
@@ -8069,7 +8069,7 @@
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A168" s="75"/>
+      <c r="A168" s="76"/>
       <c r="B168" t="s">
         <v>168</v>
       </c>
@@ -8082,7 +8082,7 @@
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A169" s="75"/>
+      <c r="A169" s="76"/>
       <c r="B169" t="s">
         <v>1001</v>
       </c>
@@ -8094,7 +8094,7 @@
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A170" s="75"/>
+      <c r="A170" s="76"/>
       <c r="B170" t="s">
         <v>1002</v>
       </c>
@@ -8107,7 +8107,7 @@
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A171" s="75"/>
+      <c r="A171" s="76"/>
       <c r="C171" t="s">
         <v>181</v>
       </c>
@@ -8119,7 +8119,7 @@
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A172" s="75"/>
+      <c r="A172" s="76"/>
       <c r="C172" t="s">
         <v>179</v>
       </c>
@@ -8131,7 +8131,7 @@
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A173" s="75"/>
+      <c r="A173" s="76"/>
       <c r="C173" t="s">
         <v>178</v>
       </c>
@@ -8140,7 +8140,7 @@
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A174" s="75"/>
+      <c r="A174" s="76"/>
       <c r="C174" t="s">
         <v>172</v>
       </c>
@@ -8153,7 +8153,7 @@
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A175" s="75"/>
+      <c r="A175" s="76"/>
       <c r="C175" t="s">
         <v>173</v>
       </c>
@@ -8166,7 +8166,7 @@
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A176" s="75"/>
+      <c r="A176" s="76"/>
       <c r="C176" t="s">
         <v>174</v>
       </c>
@@ -8178,7 +8178,7 @@
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A177" s="75"/>
+      <c r="A177" s="76"/>
       <c r="C177" t="s">
         <v>183</v>
       </c>
@@ -8191,7 +8191,7 @@
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A178" s="75"/>
+      <c r="A178" s="76"/>
       <c r="C178" t="s">
         <v>175</v>
       </c>
@@ -8204,7 +8204,7 @@
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A179" s="75"/>
+      <c r="A179" s="76"/>
       <c r="C179" t="s">
         <v>176</v>
       </c>
@@ -8214,7 +8214,7 @@
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A180" s="75"/>
+      <c r="A180" s="76"/>
       <c r="C180" t="s">
         <v>171</v>
       </c>
@@ -8224,7 +8224,7 @@
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A181" s="75"/>
+      <c r="A181" s="76"/>
       <c r="C181" t="s">
         <v>177</v>
       </c>
@@ -8234,7 +8234,7 @@
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A182" s="75"/>
+      <c r="A182" s="76"/>
       <c r="C182" t="s">
         <v>189</v>
       </c>
@@ -8244,7 +8244,7 @@
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A183" s="75"/>
+      <c r="A183" s="76"/>
       <c r="C183" t="s">
         <v>188</v>
       </c>
@@ -8257,7 +8257,7 @@
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A184" s="75"/>
+      <c r="A184" s="76"/>
       <c r="C184" t="s">
         <v>180</v>
       </c>
@@ -8270,7 +8270,7 @@
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A185" s="75"/>
+      <c r="A185" s="76"/>
       <c r="C185" t="s">
         <v>182</v>
       </c>
@@ -8283,7 +8283,7 @@
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A186" s="75"/>
+      <c r="A186" s="76"/>
       <c r="C186" t="s">
         <v>183</v>
       </c>
@@ -8296,7 +8296,7 @@
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A187" s="75"/>
+      <c r="A187" s="76"/>
       <c r="C187" t="s">
         <v>184</v>
       </c>
@@ -8306,7 +8306,7 @@
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A188" s="75"/>
+      <c r="A188" s="76"/>
       <c r="C188" t="s">
         <v>185</v>
       </c>
@@ -8318,7 +8318,7 @@
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A189" s="75"/>
+      <c r="A189" s="76"/>
       <c r="C189" t="s">
         <v>187</v>
       </c>
@@ -8331,7 +8331,7 @@
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A190" s="75"/>
+      <c r="A190" s="76"/>
       <c r="C190" t="s">
         <v>216</v>
       </c>
@@ -8341,7 +8341,7 @@
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A191" s="75"/>
+      <c r="A191" s="76"/>
       <c r="C191" t="s">
         <v>195</v>
       </c>
@@ -8353,7 +8353,7 @@
       </c>
     </row>
     <row r="192" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A192" s="75"/>
+      <c r="A192" s="76"/>
       <c r="C192" t="s">
         <v>194</v>
       </c>
@@ -8366,7 +8366,7 @@
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A193" s="75"/>
+      <c r="A193" s="76"/>
       <c r="B193" t="s">
         <v>1003</v>
       </c>
@@ -8394,7 +8394,7 @@
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A196" s="75" t="s">
+      <c r="A196" s="76" t="s">
         <v>1004</v>
       </c>
       <c r="C196" t="s">
@@ -8408,7 +8408,7 @@
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A197" s="75"/>
+      <c r="A197" s="76"/>
       <c r="C197" t="s">
         <v>192</v>
       </c>
@@ -8420,7 +8420,7 @@
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A198" s="75"/>
+      <c r="A198" s="76"/>
       <c r="C198" t="s">
         <v>197</v>
       </c>
@@ -8432,7 +8432,7 @@
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A199" s="75"/>
+      <c r="A199" s="76"/>
       <c r="B199" t="s">
         <v>999</v>
       </c>
@@ -8445,7 +8445,7 @@
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A200" s="75"/>
+      <c r="A200" s="76"/>
       <c r="B200" s="7" t="s">
         <v>47</v>
       </c>
@@ -8461,7 +8461,7 @@
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A201" s="75"/>
+      <c r="A201" s="76"/>
       <c r="B201" t="s">
         <v>40</v>
       </c>
@@ -8477,7 +8477,7 @@
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A202" s="75"/>
+      <c r="A202" s="76"/>
       <c r="C202" t="s">
         <v>203</v>
       </c>
@@ -8490,7 +8490,7 @@
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A203" s="75"/>
+      <c r="A203" s="76"/>
       <c r="C203" t="s">
         <v>198</v>
       </c>
@@ -8503,7 +8503,7 @@
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A204" s="75"/>
+      <c r="A204" s="76"/>
       <c r="C204" t="s">
         <v>183</v>
       </c>
@@ -8516,7 +8516,7 @@
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A205" s="75"/>
+      <c r="A205" s="76"/>
       <c r="C205" t="s">
         <v>184</v>
       </c>
@@ -8529,7 +8529,7 @@
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A206" s="75"/>
+      <c r="A206" s="76"/>
       <c r="C206" t="s">
         <v>200</v>
       </c>
@@ -8542,7 +8542,7 @@
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A207" s="75"/>
+      <c r="A207" s="76"/>
       <c r="C207" t="s">
         <v>201</v>
       </c>
@@ -8555,7 +8555,7 @@
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A208" s="75"/>
+      <c r="A208" s="76"/>
       <c r="C208" t="s">
         <v>202</v>
       </c>
@@ -8568,7 +8568,7 @@
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A209" s="75"/>
+      <c r="A209" s="76"/>
       <c r="C209" t="s">
         <v>204</v>
       </c>
@@ -8581,7 +8581,7 @@
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A210" s="75"/>
+      <c r="A210" s="76"/>
       <c r="C210" t="s">
         <v>205</v>
       </c>
@@ -8594,7 +8594,7 @@
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A211" s="75"/>
+      <c r="A211" s="76"/>
       <c r="C211" t="s">
         <v>195</v>
       </c>
@@ -8606,7 +8606,7 @@
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A212" s="75"/>
+      <c r="A212" s="76"/>
       <c r="C212" t="s">
         <v>208</v>
       </c>
@@ -8619,7 +8619,7 @@
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A213" s="75"/>
+      <c r="A213" s="76"/>
       <c r="C213" t="s">
         <v>209</v>
       </c>
@@ -8632,7 +8632,7 @@
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A214" s="75"/>
+      <c r="A214" s="76"/>
       <c r="C214" t="s">
         <v>210</v>
       </c>
@@ -8645,7 +8645,7 @@
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A215" s="75"/>
+      <c r="A215" s="76"/>
       <c r="C215" t="s">
         <v>211</v>
       </c>
@@ -8658,7 +8658,7 @@
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A216" s="75"/>
+      <c r="A216" s="76"/>
       <c r="C216" t="s">
         <v>212</v>
       </c>
@@ -8671,7 +8671,7 @@
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A217" s="75"/>
+      <c r="A217" s="76"/>
       <c r="C217" t="s">
         <v>1000</v>
       </c>
@@ -8684,7 +8684,7 @@
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A218" s="75"/>
+      <c r="A218" s="76"/>
       <c r="C218" t="s">
         <v>213</v>
       </c>
@@ -8697,7 +8697,7 @@
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A219" s="75"/>
+      <c r="A219" s="76"/>
       <c r="C219" t="s">
         <v>214</v>
       </c>
@@ -8710,7 +8710,7 @@
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A220" s="75"/>
+      <c r="A220" s="76"/>
       <c r="C220" t="s">
         <v>215</v>
       </c>
@@ -8777,7 +8777,7 @@
       <c r="A228" s="23"/>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A229" s="79" t="s">
+      <c r="A229" s="80" t="s">
         <v>517</v>
       </c>
       <c r="B229" s="61" t="s">
@@ -8800,7 +8800,7 @@
       <c r="N229" s="61"/>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A230" s="79"/>
+      <c r="A230" s="80"/>
       <c r="B230" s="61" t="s">
         <v>48</v>
       </c>
@@ -8823,7 +8823,7 @@
       <c r="N230" s="61"/>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A231" s="79"/>
+      <c r="A231" s="80"/>
       <c r="B231" s="61" t="s">
         <v>47</v>
       </c>
@@ -8844,7 +8844,7 @@
       <c r="N231" s="61"/>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A232" s="79"/>
+      <c r="A232" s="80"/>
       <c r="B232" s="61" t="s">
         <v>71</v>
       </c>
@@ -8865,7 +8865,7 @@
       <c r="N232" s="61"/>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A233" s="79"/>
+      <c r="A233" s="80"/>
       <c r="B233" s="61" t="s">
         <v>511</v>
       </c>
@@ -8887,7 +8887,7 @@
       <c r="N233" s="61"/>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A234" s="79"/>
+      <c r="A234" s="80"/>
       <c r="B234" s="61" t="s">
         <v>231</v>
       </c>
@@ -8908,7 +8908,7 @@
       <c r="N234" s="61"/>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A235" s="79"/>
+      <c r="A235" s="80"/>
       <c r="B235" s="61" t="s">
         <v>232</v>
       </c>
@@ -8929,7 +8929,7 @@
       <c r="N235" s="61"/>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A236" s="79"/>
+      <c r="A236" s="80"/>
       <c r="B236" s="61" t="s">
         <v>516</v>
       </c>
@@ -8950,7 +8950,7 @@
       <c r="N236" s="61"/>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A237" s="79"/>
+      <c r="A237" s="80"/>
       <c r="B237" s="61" t="s">
         <v>229</v>
       </c>
@@ -8970,7 +8970,7 @@
       <c r="N237" s="61"/>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A238" s="79"/>
+      <c r="A238" s="80"/>
       <c r="B238" s="61" t="s">
         <v>219</v>
       </c>
@@ -8993,7 +8993,7 @@
       <c r="N238" s="61"/>
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A239" s="79"/>
+      <c r="A239" s="80"/>
       <c r="B239" s="61" t="s">
         <v>39</v>
       </c>
@@ -9014,7 +9014,7 @@
       <c r="N239" s="61"/>
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A240" s="79"/>
+      <c r="A240" s="80"/>
       <c r="B240" s="61" t="s">
         <v>284</v>
       </c>
@@ -9035,7 +9035,7 @@
       <c r="N240" s="61"/>
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A241" s="79"/>
+      <c r="A241" s="80"/>
       <c r="B241" s="61" t="s">
         <v>220</v>
       </c>
@@ -9056,7 +9056,7 @@
       <c r="N241" s="61"/>
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A242" s="79"/>
+      <c r="A242" s="80"/>
       <c r="B242" s="61" t="s">
         <v>221</v>
       </c>
@@ -9077,7 +9077,7 @@
       <c r="N242" s="61"/>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A243" s="79"/>
+      <c r="A243" s="80"/>
       <c r="B243" s="61" t="s">
         <v>233</v>
       </c>
@@ -9098,7 +9098,7 @@
       <c r="N243" s="61"/>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A244" s="79"/>
+      <c r="A244" s="80"/>
       <c r="B244" s="61" t="s">
         <v>226</v>
       </c>
@@ -9119,7 +9119,7 @@
       <c r="N244" s="61"/>
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A245" s="79"/>
+      <c r="A245" s="80"/>
       <c r="B245" s="61" t="s">
         <v>224</v>
       </c>
@@ -9139,7 +9139,7 @@
       <c r="N245" s="61"/>
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A246" s="79"/>
+      <c r="A246" s="80"/>
       <c r="B246" s="61" t="s">
         <v>513</v>
       </c>
@@ -9160,7 +9160,7 @@
       <c r="N246" s="61"/>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A247" s="79"/>
+      <c r="A247" s="80"/>
       <c r="B247" s="61" t="s">
         <v>515</v>
       </c>
@@ -9181,7 +9181,7 @@
       <c r="N247" s="61"/>
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A248" s="79"/>
+      <c r="A248" s="80"/>
       <c r="B248" s="61" t="s">
         <v>234</v>
       </c>
@@ -9204,7 +9204,7 @@
       <c r="N248" s="61"/>
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A249" s="79"/>
+      <c r="A249" s="80"/>
       <c r="B249" s="61" t="s">
         <v>223</v>
       </c>
@@ -9226,7 +9226,7 @@
       <c r="N249" s="61"/>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A250" s="79"/>
+      <c r="A250" s="80"/>
       <c r="B250" s="61" t="s">
         <v>225</v>
       </c>
@@ -9247,7 +9247,7 @@
       <c r="N250" s="61"/>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A251" s="79"/>
+      <c r="A251" s="80"/>
       <c r="B251" s="61" t="s">
         <v>277</v>
       </c>
@@ -9269,7 +9269,7 @@
       <c r="N251" s="61"/>
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A252" s="79"/>
+      <c r="A252" s="80"/>
       <c r="B252" s="61" t="s">
         <v>514</v>
       </c>
@@ -9289,7 +9289,7 @@
       <c r="N252" s="61"/>
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A253" s="79"/>
+      <c r="A253" s="80"/>
       <c r="B253" s="61" t="s">
         <v>490</v>
       </c>
@@ -9309,7 +9309,7 @@
       <c r="N253" s="61"/>
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A254" s="79"/>
+      <c r="A254" s="80"/>
       <c r="B254" s="61" t="s">
         <v>227</v>
       </c>
@@ -9330,7 +9330,7 @@
       <c r="N254" s="61"/>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A255" s="79"/>
+      <c r="A255" s="80"/>
       <c r="B255" s="61" t="s">
         <v>491</v>
       </c>
@@ -9351,7 +9351,7 @@
       <c r="N255" s="61"/>
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A256" s="79"/>
+      <c r="A256" s="80"/>
       <c r="B256" s="61" t="s">
         <v>495</v>
       </c>
@@ -9388,7 +9388,7 @@
       </c>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A257" s="79"/>
+      <c r="A257" s="80"/>
       <c r="B257" s="61" t="s">
         <v>496</v>
       </c>
@@ -9430,7 +9430,7 @@
       </c>
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A258" s="79"/>
+      <c r="A258" s="80"/>
       <c r="B258" s="61" t="s">
         <v>494</v>
       </c>
@@ -9470,7 +9470,7 @@
       </c>
     </row>
     <row r="259" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="79"/>
+      <c r="A259" s="80"/>
       <c r="B259" s="61" t="s">
         <v>492</v>
       </c>
@@ -9510,7 +9510,7 @@
       </c>
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A260" s="79"/>
+      <c r="A260" s="80"/>
       <c r="B260" s="61" t="s">
         <v>493</v>
       </c>
@@ -9550,7 +9550,7 @@
       </c>
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A261" s="79"/>
+      <c r="A261" s="80"/>
       <c r="B261" s="61" t="s">
         <v>280</v>
       </c>
@@ -9589,7 +9589,7 @@
       </c>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A262" s="79"/>
+      <c r="A262" s="80"/>
       <c r="B262" s="61" t="s">
         <v>281</v>
       </c>
@@ -9628,7 +9628,7 @@
       </c>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A263" s="79"/>
+      <c r="A263" s="80"/>
       <c r="B263" s="61" t="s">
         <v>282</v>
       </c>
@@ -9665,7 +9665,7 @@
       </c>
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A264" s="79"/>
+      <c r="A264" s="80"/>
       <c r="B264" s="61" t="s">
         <v>283</v>
       </c>
@@ -9686,7 +9686,7 @@
       <c r="N264" s="61"/>
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A265" s="79"/>
+      <c r="A265" s="80"/>
       <c r="B265" s="61" t="s">
         <v>284</v>
       </c>
@@ -9707,7 +9707,7 @@
       <c r="N265" s="61"/>
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A266" s="79"/>
+      <c r="A266" s="80"/>
       <c r="B266" s="61" t="s">
         <v>285</v>
       </c>
@@ -9725,7 +9725,7 @@
       <c r="N266" s="61"/>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A267" s="79"/>
+      <c r="A267" s="80"/>
       <c r="B267" s="61" t="s">
         <v>286</v>
       </c>
@@ -9746,7 +9746,7 @@
       <c r="N267" s="61"/>
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A268" s="79"/>
+      <c r="A268" s="80"/>
       <c r="B268" s="61" t="s">
         <v>238</v>
       </c>
@@ -9766,7 +9766,7 @@
       <c r="N268" s="61"/>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A269" s="79"/>
+      <c r="A269" s="80"/>
       <c r="B269" s="61"/>
       <c r="C269" s="61" t="s">
         <v>239</v>
@@ -9786,7 +9786,7 @@
       <c r="N269" s="61"/>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A270" s="79"/>
+      <c r="A270" s="80"/>
       <c r="B270" s="61"/>
       <c r="C270" s="61" t="s">
         <v>240</v>
@@ -9807,7 +9807,7 @@
       <c r="N270" s="61"/>
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A271" s="79"/>
+      <c r="A271" s="80"/>
       <c r="B271" s="61"/>
       <c r="C271" s="61" t="s">
         <v>241</v>
@@ -9827,7 +9827,7 @@
       <c r="N271" s="61"/>
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A272" s="79"/>
+      <c r="A272" s="80"/>
       <c r="B272" s="61"/>
       <c r="C272" s="61"/>
       <c r="D272" s="61"/>
@@ -9843,7 +9843,7 @@
       <c r="N272" s="61"/>
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A273" s="79"/>
+      <c r="A273" s="80"/>
       <c r="B273" s="61" t="s">
         <v>243</v>
       </c>
@@ -9863,7 +9863,7 @@
       <c r="N273" s="61"/>
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A274" s="79"/>
+      <c r="A274" s="80"/>
       <c r="B274" s="61" t="s">
         <v>267</v>
       </c>
@@ -9884,7 +9884,7 @@
       <c r="N274" s="61"/>
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A275" s="79"/>
+      <c r="A275" s="80"/>
       <c r="B275" s="61" t="s">
         <v>244</v>
       </c>
@@ -9904,7 +9904,7 @@
       <c r="N275" s="61"/>
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A276" s="79"/>
+      <c r="A276" s="80"/>
       <c r="B276" s="61" t="s">
         <v>245</v>
       </c>
@@ -9925,7 +9925,7 @@
       <c r="N276" s="61"/>
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A277" s="79"/>
+      <c r="A277" s="80"/>
       <c r="B277" s="61" t="s">
         <v>246</v>
       </c>
@@ -9948,7 +9948,7 @@
       <c r="N277" s="61"/>
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A278" s="79"/>
+      <c r="A278" s="80"/>
       <c r="B278" s="61" t="s">
         <v>247</v>
       </c>
@@ -9971,7 +9971,7 @@
       <c r="N278" s="61"/>
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A279" s="79"/>
+      <c r="A279" s="80"/>
       <c r="B279" s="61" t="s">
         <v>248</v>
       </c>
@@ -9994,7 +9994,7 @@
       <c r="N279" s="61"/>
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A280" s="79"/>
+      <c r="A280" s="80"/>
       <c r="B280" s="61" t="s">
         <v>249</v>
       </c>
@@ -10019,7 +10019,7 @@
       <c r="N280" s="61"/>
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A281" s="79"/>
+      <c r="A281" s="80"/>
       <c r="B281" s="61" t="s">
         <v>250</v>
       </c>
@@ -10040,7 +10040,7 @@
       <c r="N281" s="61"/>
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A282" s="79"/>
+      <c r="A282" s="80"/>
       <c r="B282" s="61"/>
       <c r="C282" s="61" t="s">
         <v>251</v>
@@ -10061,7 +10061,7 @@
       <c r="N282" s="61"/>
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A283" s="79"/>
+      <c r="A283" s="80"/>
       <c r="B283" s="61"/>
       <c r="C283" s="61" t="s">
         <v>252</v>
@@ -10082,7 +10082,7 @@
       <c r="N283" s="61"/>
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A284" s="79"/>
+      <c r="A284" s="80"/>
       <c r="B284" s="61"/>
       <c r="C284" s="61" t="s">
         <v>253</v>
@@ -10108,12 +10108,12 @@
       <c r="A285" s="28"/>
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A286" s="76" t="s">
+      <c r="A286" s="77" t="s">
         <v>751</v>
       </c>
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A287" s="76"/>
+      <c r="A287" s="77"/>
       <c r="B287" t="s">
         <v>556</v>
       </c>
@@ -10122,10 +10122,10 @@
       </c>
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A288" s="76"/>
+      <c r="A288" s="77"/>
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A289" s="76"/>
+      <c r="A289" s="77"/>
       <c r="B289" t="s">
         <v>512</v>
       </c>
@@ -10134,7 +10134,7 @@
       </c>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A290" s="76"/>
+      <c r="A290" s="77"/>
       <c r="B290" t="s">
         <v>527</v>
       </c>
@@ -10173,7 +10173,7 @@
       </c>
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A291" s="76"/>
+      <c r="A291" s="77"/>
       <c r="B291" t="s">
         <v>541</v>
       </c>
@@ -10212,7 +10212,7 @@
       </c>
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A292" s="76"/>
+      <c r="A292" s="77"/>
       <c r="B292" t="s">
         <v>528</v>
       </c>
@@ -10251,7 +10251,7 @@
       </c>
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A293" s="76"/>
+      <c r="A293" s="77"/>
       <c r="B293" t="s">
         <v>309</v>
       </c>
@@ -10292,7 +10292,7 @@
       </c>
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A294" s="76"/>
+      <c r="A294" s="77"/>
       <c r="B294" t="s">
         <v>529</v>
       </c>
@@ -10333,7 +10333,7 @@
       </c>
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A295" s="76"/>
+      <c r="A295" s="77"/>
       <c r="B295" t="s">
         <v>531</v>
       </c>
@@ -10371,7 +10371,7 @@
       </c>
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A296" s="76"/>
+      <c r="A296" s="77"/>
       <c r="B296" t="s">
         <v>533</v>
       </c>
@@ -10410,7 +10410,7 @@
       </c>
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A297" s="76"/>
+      <c r="A297" s="77"/>
       <c r="B297" t="s">
         <v>47</v>
       </c>
@@ -10448,7 +10448,7 @@
       </c>
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A298" s="76"/>
+      <c r="A298" s="77"/>
       <c r="B298" t="s">
         <v>39</v>
       </c>
@@ -10486,11 +10486,11 @@
       </c>
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A299" s="76"/>
+      <c r="A299" s="77"/>
       <c r="C299" s="31"/>
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A300" s="76"/>
+      <c r="A300" s="77"/>
       <c r="B300" t="s">
         <v>538</v>
       </c>
@@ -10527,7 +10527,7 @@
       </c>
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A301" s="76"/>
+      <c r="A301" s="77"/>
       <c r="B301" t="s">
         <v>547</v>
       </c>
@@ -10540,7 +10540,7 @@
       </c>
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A302" s="76"/>
+      <c r="A302" s="77"/>
       <c r="B302" t="s">
         <v>526</v>
       </c>
@@ -10582,7 +10582,7 @@
       <c r="L302" s="1"/>
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A303" s="76"/>
+      <c r="A303" s="77"/>
       <c r="B303" t="s">
         <v>534</v>
       </c>
@@ -10623,7 +10623,7 @@
       </c>
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A304" s="76"/>
+      <c r="A304" s="77"/>
       <c r="B304" t="s">
         <v>536</v>
       </c>
@@ -10664,7 +10664,7 @@
       </c>
     </row>
     <row r="305" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A305" s="76"/>
+      <c r="A305" s="77"/>
       <c r="B305" t="s">
         <v>540</v>
       </c>
@@ -10704,7 +10704,7 @@
       </c>
     </row>
     <row r="306" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A306" s="76"/>
+      <c r="A306" s="77"/>
       <c r="B306" t="s">
         <v>543</v>
       </c>
@@ -10745,7 +10745,7 @@
       </c>
     </row>
     <row r="307" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A307" s="76"/>
+      <c r="A307" s="77"/>
       <c r="B307" t="s">
         <v>566</v>
       </c>
@@ -10754,7 +10754,7 @@
       </c>
     </row>
     <row r="308" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A308" s="76"/>
+      <c r="A308" s="77"/>
       <c r="B308" t="s">
         <v>284</v>
       </c>
@@ -10764,7 +10764,7 @@
       </c>
     </row>
     <row r="309" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A309" s="76"/>
+      <c r="A309" s="77"/>
       <c r="B309" t="s">
         <v>565</v>
       </c>
@@ -10777,7 +10777,7 @@
       </c>
     </row>
     <row r="310" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A310" s="76"/>
+      <c r="A310" s="77"/>
       <c r="B310" t="s">
         <v>572</v>
       </c>
@@ -10808,7 +10808,7 @@
       </c>
     </row>
     <row r="311" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A311" s="76"/>
+      <c r="A311" s="77"/>
       <c r="B311" s="32" t="s">
         <v>571</v>
       </c>
@@ -10845,7 +10845,7 @@
       </c>
     </row>
     <row r="312" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A312" s="76"/>
+      <c r="A312" s="77"/>
       <c r="B312" t="s">
         <v>574</v>
       </c>
@@ -10855,7 +10855,7 @@
       </c>
     </row>
     <row r="313" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A313" s="76"/>
+      <c r="A313" s="77"/>
       <c r="B313" t="s">
         <v>575</v>
       </c>
@@ -10865,7 +10865,7 @@
       </c>
     </row>
     <row r="314" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A314" s="76"/>
+      <c r="A314" s="77"/>
       <c r="B314" t="s">
         <v>573</v>
       </c>
@@ -10875,7 +10875,7 @@
       </c>
     </row>
     <row r="315" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A315" s="76"/>
+      <c r="A315" s="77"/>
       <c r="B315" t="s">
         <v>576</v>
       </c>
@@ -10885,7 +10885,7 @@
       </c>
     </row>
     <row r="316" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A316" s="76"/>
+      <c r="A316" s="77"/>
       <c r="B316" t="s">
         <v>577</v>
       </c>
@@ -10895,7 +10895,7 @@
       </c>
     </row>
     <row r="317" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A317" s="76"/>
+      <c r="A317" s="77"/>
       <c r="B317" t="s">
         <v>580</v>
       </c>
@@ -10905,7 +10905,7 @@
       </c>
     </row>
     <row r="318" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A318" s="76"/>
+      <c r="A318" s="77"/>
       <c r="B318" t="s">
         <v>578</v>
       </c>
@@ -10915,7 +10915,7 @@
       </c>
     </row>
     <row r="319" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A319" s="76"/>
+      <c r="A319" s="77"/>
       <c r="B319" t="s">
         <v>578</v>
       </c>
@@ -10925,7 +10925,7 @@
       </c>
     </row>
     <row r="320" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A320" s="76"/>
+      <c r="A320" s="77"/>
       <c r="B320" t="s">
         <v>582</v>
       </c>
@@ -10935,7 +10935,7 @@
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A321" s="76"/>
+      <c r="A321" s="77"/>
       <c r="B321" t="s">
         <v>581</v>
       </c>
@@ -10945,7 +10945,7 @@
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A322" s="76"/>
+      <c r="A322" s="77"/>
       <c r="B322" t="s">
         <v>579</v>
       </c>
@@ -10955,7 +10955,7 @@
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A323" s="76"/>
+      <c r="A323" s="77"/>
       <c r="B323" t="s">
         <v>603</v>
       </c>
@@ -10964,7 +10964,7 @@
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A324" s="76"/>
+      <c r="A324" s="77"/>
       <c r="B324" t="s">
         <v>604</v>
       </c>
@@ -10974,7 +10974,7 @@
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A325" s="76"/>
+      <c r="A325" s="77"/>
       <c r="B325" t="s">
         <v>601</v>
       </c>
@@ -10987,7 +10987,7 @@
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A326" s="76"/>
+      <c r="A326" s="77"/>
       <c r="B326" t="s">
         <v>602</v>
       </c>
@@ -11000,7 +11000,7 @@
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A327" s="76"/>
+      <c r="A327" s="77"/>
       <c r="B327" t="s">
         <v>583</v>
       </c>
@@ -11015,7 +11015,7 @@
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A328" s="76"/>
+      <c r="A328" s="77"/>
       <c r="B328" s="38" t="s">
         <v>585</v>
       </c>
@@ -11028,45 +11028,45 @@
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A329" s="76"/>
+      <c r="A329" s="77"/>
       <c r="C329" s="31"/>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A330" s="76"/>
+      <c r="A330" s="77"/>
       <c r="C330" s="31"/>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A331" s="76"/>
+      <c r="A331" s="77"/>
       <c r="C331" s="31"/>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A332" s="76"/>
+      <c r="A332" s="77"/>
       <c r="C332" s="31"/>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A333" s="76"/>
+      <c r="A333" s="77"/>
       <c r="C333" s="31"/>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A334" s="76"/>
+      <c r="A334" s="77"/>
       <c r="C334" s="31"/>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A335" s="76"/>
+      <c r="A335" s="77"/>
       <c r="C335" s="31"/>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A336" s="76"/>
+      <c r="A336" s="77"/>
       <c r="C336" s="31"/>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A337" s="76"/>
+      <c r="A337" s="77"/>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" s="33"/>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A339" s="76" t="s">
+      <c r="A339" s="77" t="s">
         <v>588</v>
       </c>
       <c r="C339" t="s">
@@ -11078,7 +11078,7 @@
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A340" s="76"/>
+      <c r="A340" s="77"/>
       <c r="C340" t="s">
         <v>255</v>
       </c>
@@ -11088,7 +11088,7 @@
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A341" s="76"/>
+      <c r="A341" s="77"/>
       <c r="C341" t="s">
         <v>256</v>
       </c>
@@ -11098,7 +11098,7 @@
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A342" s="76"/>
+      <c r="A342" s="77"/>
       <c r="C342" t="s">
         <v>257</v>
       </c>
@@ -11108,7 +11108,7 @@
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A343" s="76"/>
+      <c r="A343" s="77"/>
       <c r="C343" t="s">
         <v>258</v>
       </c>
@@ -11118,7 +11118,7 @@
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A344" s="76"/>
+      <c r="A344" s="77"/>
       <c r="C344" t="s">
         <v>259</v>
       </c>
@@ -11128,7 +11128,7 @@
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A345" s="76"/>
+      <c r="A345" s="77"/>
       <c r="C345" t="s">
         <v>260</v>
       </c>
@@ -11138,7 +11138,7 @@
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A346" s="76"/>
+      <c r="A346" s="77"/>
       <c r="C346" t="s">
         <v>261</v>
       </c>
@@ -11148,7 +11148,7 @@
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A347" s="76"/>
+      <c r="A347" s="77"/>
       <c r="B347" t="s">
         <v>262</v>
       </c>
@@ -11157,7 +11157,7 @@
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A348" s="76"/>
+      <c r="A348" s="77"/>
       <c r="B348" t="s">
         <v>264</v>
       </c>
@@ -11167,7 +11167,7 @@
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A349" s="76"/>
+      <c r="A349" s="77"/>
       <c r="C349" t="s">
         <v>265</v>
       </c>
@@ -11177,10 +11177,10 @@
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A350" s="76"/>
+      <c r="A350" s="77"/>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A351" s="76"/>
+      <c r="A351" s="77"/>
       <c r="B351" t="s">
         <v>266</v>
       </c>
@@ -11190,7 +11190,7 @@
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A352" s="76"/>
+      <c r="A352" s="77"/>
       <c r="B352" t="s">
         <v>329</v>
       </c>
@@ -11200,7 +11200,7 @@
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A353" s="76"/>
+      <c r="A353" s="77"/>
       <c r="B353" t="s">
         <v>274</v>
       </c>
@@ -11210,7 +11210,7 @@
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A354" s="76"/>
+      <c r="A354" s="77"/>
       <c r="B354" t="s">
         <v>273</v>
       </c>
@@ -11219,10 +11219,10 @@
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A355" s="76"/>
+      <c r="A355" s="77"/>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A356" s="76"/>
+      <c r="A356" s="77"/>
       <c r="B356" t="s">
         <v>271</v>
       </c>
@@ -11232,7 +11232,7 @@
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A357" s="76"/>
+      <c r="A357" s="77"/>
       <c r="B357" t="s">
         <v>270</v>
       </c>
@@ -11244,7 +11244,7 @@
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A358" s="76"/>
+      <c r="A358" s="77"/>
       <c r="C358" t="s">
         <v>268</v>
       </c>
@@ -11254,7 +11254,7 @@
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A359" s="76"/>
+      <c r="A359" s="77"/>
       <c r="C359" t="s">
         <v>272</v>
       </c>
@@ -11264,13 +11264,13 @@
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A360" s="76"/>
+      <c r="A360" s="77"/>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" s="49"/>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A362" s="75" t="s">
+      <c r="A362" s="76" t="s">
         <v>587</v>
       </c>
       <c r="B362" t="s">
@@ -11282,7 +11282,7 @@
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A363" s="75"/>
+      <c r="A363" s="76"/>
       <c r="B363" t="s">
         <v>589</v>
       </c>
@@ -11291,7 +11291,7 @@
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A364" s="75"/>
+      <c r="A364" s="76"/>
       <c r="B364" t="s">
         <v>590</v>
       </c>
@@ -11300,7 +11300,7 @@
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A365" s="75"/>
+      <c r="A365" s="76"/>
       <c r="B365" t="s">
         <v>591</v>
       </c>
@@ -11310,7 +11310,7 @@
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A366" s="75"/>
+      <c r="A366" s="76"/>
       <c r="B366" t="s">
         <v>595</v>
       </c>
@@ -11320,7 +11320,7 @@
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A367" s="75"/>
+      <c r="A367" s="76"/>
       <c r="B367" t="s">
         <v>593</v>
       </c>
@@ -11330,7 +11330,7 @@
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A368" s="75"/>
+      <c r="A368" s="76"/>
       <c r="B368" t="s">
         <v>594</v>
       </c>
@@ -11340,7 +11340,7 @@
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A369" s="75"/>
+      <c r="A369" s="76"/>
       <c r="B369" t="s">
         <v>596</v>
       </c>
@@ -11350,7 +11350,7 @@
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A370" s="75"/>
+      <c r="A370" s="76"/>
       <c r="C370" t="s">
         <v>597</v>
       </c>
@@ -11359,7 +11359,7 @@
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A371" s="75"/>
+      <c r="A371" s="76"/>
       <c r="C371" t="s">
         <v>598</v>
       </c>
@@ -11369,7 +11369,7 @@
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A372" s="75"/>
+      <c r="A372" s="76"/>
       <c r="C372" t="s">
         <v>599</v>
       </c>
@@ -11379,7 +11379,7 @@
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A373" s="75"/>
+      <c r="A373" s="76"/>
       <c r="C373" t="s">
         <v>600</v>
       </c>
@@ -11389,13 +11389,13 @@
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A374" s="75"/>
+      <c r="A374" s="76"/>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" s="50"/>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A376" s="75" t="s">
+      <c r="A376" s="76" t="s">
         <v>564</v>
       </c>
       <c r="C376" t="s">
@@ -11403,7 +11403,7 @@
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A377" s="75"/>
+      <c r="A377" s="76"/>
       <c r="B377" t="s">
         <v>38</v>
       </c>
@@ -11416,7 +11416,7 @@
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A378" s="75"/>
+      <c r="A378" s="76"/>
       <c r="B378" t="s">
         <v>37</v>
       </c>
@@ -11429,7 +11429,7 @@
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A379" s="75"/>
+      <c r="A379" s="76"/>
       <c r="B379" t="s">
         <v>1040</v>
       </c>
@@ -11441,7 +11441,7 @@
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A380" s="75"/>
+      <c r="A380" s="76"/>
       <c r="C380" t="s">
         <v>1039</v>
       </c>
@@ -11451,7 +11451,7 @@
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A381" s="75"/>
+      <c r="A381" s="76"/>
       <c r="B381" t="s">
         <v>1041</v>
       </c>
@@ -11464,7 +11464,7 @@
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A382" s="75"/>
+      <c r="A382" s="76"/>
       <c r="C382" t="s">
         <v>276</v>
       </c>
@@ -11476,7 +11476,7 @@
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A383" s="75"/>
+      <c r="A383" s="76"/>
       <c r="B383" t="s">
         <v>1042</v>
       </c>
@@ -11488,7 +11488,7 @@
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A384" s="75"/>
+      <c r="A384" s="76"/>
       <c r="C384" t="s">
         <v>1051</v>
       </c>
@@ -11500,7 +11500,7 @@
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A385" s="75"/>
+      <c r="A385" s="76"/>
       <c r="B385" t="s">
         <v>520</v>
       </c>
@@ -11513,7 +11513,7 @@
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A386" s="75"/>
+      <c r="A386" s="76"/>
       <c r="B386" t="s">
         <v>1049</v>
       </c>
@@ -11526,7 +11526,7 @@
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A387" s="75"/>
+      <c r="A387" s="76"/>
       <c r="B387" t="s">
         <v>1050</v>
       </c>
@@ -11539,7 +11539,7 @@
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A388" s="75"/>
+      <c r="A388" s="76"/>
       <c r="B388" t="s">
         <v>157</v>
       </c>
@@ -11552,7 +11552,7 @@
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A389" s="75"/>
+      <c r="A389" s="76"/>
       <c r="B389" t="s">
         <v>324</v>
       </c>
@@ -11564,7 +11564,7 @@
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A390" s="75"/>
+      <c r="A390" s="76"/>
       <c r="B390" t="s">
         <v>1043</v>
       </c>
@@ -11577,7 +11577,7 @@
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A391" s="75"/>
+      <c r="A391" s="76"/>
       <c r="B391" t="s">
         <v>1062</v>
       </c>
@@ -11593,7 +11593,7 @@
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A392" s="75"/>
+      <c r="A392" s="76"/>
       <c r="B392" t="s">
         <v>1064</v>
       </c>
@@ -11606,7 +11606,7 @@
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A393" s="75"/>
+      <c r="A393" s="76"/>
       <c r="B393" t="s">
         <v>1038</v>
       </c>
@@ -11618,7 +11618,7 @@
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A394" s="75"/>
+      <c r="A394" s="76"/>
       <c r="C394" t="s">
         <v>1044</v>
       </c>
@@ -11631,7 +11631,7 @@
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A395" s="75"/>
+      <c r="A395" s="76"/>
       <c r="C395" t="s">
         <v>1045</v>
       </c>
@@ -11644,7 +11644,7 @@
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A396" s="75"/>
+      <c r="A396" s="76"/>
       <c r="C396" t="s">
         <v>1047</v>
       </c>
@@ -11657,7 +11657,7 @@
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A397" s="75"/>
+      <c r="A397" s="76"/>
       <c r="C397" t="s">
         <v>1046</v>
       </c>
@@ -11670,7 +11670,7 @@
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A398" s="75"/>
+      <c r="A398" s="76"/>
       <c r="B398" t="s">
         <v>1067</v>
       </c>
@@ -11686,7 +11686,7 @@
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A399" s="75"/>
+      <c r="A399" s="76"/>
       <c r="B399" t="s">
         <v>1067</v>
       </c>
@@ -11702,7 +11702,7 @@
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A400" s="75"/>
+      <c r="A400" s="76"/>
       <c r="C400" t="s">
         <v>1048</v>
       </c>
@@ -11715,7 +11715,7 @@
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A401" s="75"/>
+      <c r="A401" s="76"/>
       <c r="C401" t="s">
         <v>1052</v>
       </c>
@@ -11728,7 +11728,7 @@
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A402" s="75"/>
+      <c r="A402" s="76"/>
       <c r="C402" t="s">
         <v>1065</v>
       </c>
@@ -11739,7 +11739,7 @@
       <c r="E402" s="8"/>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A403" s="75"/>
+      <c r="A403" s="76"/>
       <c r="C403" t="s">
         <v>1054</v>
       </c>
@@ -11750,7 +11750,7 @@
       <c r="E403" s="8"/>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A404" s="75"/>
+      <c r="A404" s="76"/>
       <c r="C404" t="s">
         <v>1053</v>
       </c>
@@ -11761,7 +11761,7 @@
       <c r="E404" s="8"/>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A405" s="75"/>
+      <c r="A405" s="76"/>
       <c r="C405" t="s">
         <v>1055</v>
       </c>
@@ -11772,7 +11772,7 @@
       <c r="E405" s="8"/>
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A406" s="75"/>
+      <c r="A406" s="76"/>
       <c r="C406" t="s">
         <v>1056</v>
       </c>
@@ -11783,7 +11783,7 @@
       <c r="E406" s="8"/>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A407" s="75"/>
+      <c r="A407" s="76"/>
       <c r="C407" t="s">
         <v>1057</v>
       </c>
@@ -11794,7 +11794,7 @@
       <c r="E407" s="8"/>
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A408" s="75"/>
+      <c r="A408" s="76"/>
       <c r="C408" t="s">
         <v>1058</v>
       </c>
@@ -11807,7 +11807,7 @@
       </c>
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A409" s="75"/>
+      <c r="A409" s="76"/>
       <c r="C409" t="s">
         <v>1059</v>
       </c>
@@ -11820,7 +11820,7 @@
       </c>
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A410" s="75"/>
+      <c r="A410" s="76"/>
       <c r="C410" t="s">
         <v>1060</v>
       </c>
@@ -11833,7 +11833,7 @@
       </c>
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A411" s="75"/>
+      <c r="A411" s="76"/>
       <c r="C411" t="s">
         <v>1061</v>
       </c>
@@ -11846,7 +11846,7 @@
       </c>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A412" s="75"/>
+      <c r="A412" s="76"/>
       <c r="E412" s="8"/>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
@@ -11854,7 +11854,7 @@
       <c r="E413" s="8"/>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A414" s="75" t="s">
+      <c r="A414" s="76" t="s">
         <v>883</v>
       </c>
       <c r="C414" t="s">
@@ -11867,7 +11867,7 @@
       <c r="E414" s="8"/>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A415" s="75"/>
+      <c r="A415" s="76"/>
       <c r="B415" t="s">
         <v>47</v>
       </c>
@@ -11880,7 +11880,7 @@
       </c>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A416" s="75"/>
+      <c r="A416" s="76"/>
       <c r="B416" t="s">
         <v>877</v>
       </c>
@@ -11893,7 +11893,7 @@
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A417" s="75"/>
+      <c r="A417" s="76"/>
       <c r="B417" t="s">
         <v>40</v>
       </c>
@@ -11906,7 +11906,7 @@
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A418" s="75"/>
+      <c r="A418" s="76"/>
       <c r="B418" t="s">
         <v>875</v>
       </c>
@@ -11919,7 +11919,7 @@
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A419" s="75"/>
+      <c r="A419" s="76"/>
       <c r="B419" t="s">
         <v>39</v>
       </c>
@@ -11928,7 +11928,7 @@
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A420" s="75"/>
+      <c r="A420" s="76"/>
       <c r="B420" t="s">
         <v>288</v>
       </c>
@@ -11940,7 +11940,7 @@
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A421" s="75"/>
+      <c r="A421" s="76"/>
       <c r="B421" t="s">
         <v>906</v>
       </c>
@@ -11956,11 +11956,11 @@
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A422" s="75"/>
+      <c r="A422" s="76"/>
       <c r="E422" s="8"/>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A423" s="75"/>
+      <c r="A423" s="76"/>
       <c r="B423" t="s">
         <v>287</v>
       </c>
@@ -11970,7 +11970,7 @@
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A424" s="75"/>
+      <c r="A424" s="76"/>
       <c r="B424" t="s">
         <v>290</v>
       </c>
@@ -11983,7 +11983,7 @@
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A425" s="75"/>
+      <c r="A425" s="76"/>
       <c r="B425" t="s">
         <v>291</v>
       </c>
@@ -11996,7 +11996,7 @@
       </c>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A426" s="75"/>
+      <c r="A426" s="76"/>
       <c r="B426" t="s">
         <v>308</v>
       </c>
@@ -12008,7 +12008,7 @@
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A427" s="75"/>
+      <c r="A427" s="76"/>
       <c r="C427" t="s">
         <v>325</v>
       </c>
@@ -12018,7 +12018,7 @@
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A428" s="75"/>
+      <c r="A428" s="76"/>
       <c r="B428" t="s">
         <v>292</v>
       </c>
@@ -12028,7 +12028,7 @@
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A429" s="75"/>
+      <c r="A429" s="76"/>
       <c r="B429" t="s">
         <v>293</v>
       </c>
@@ -12038,7 +12038,7 @@
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A430" s="75"/>
+      <c r="A430" s="76"/>
       <c r="B430" t="s">
         <v>294</v>
       </c>
@@ -12053,7 +12053,7 @@
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A431" s="75"/>
+      <c r="A431" s="76"/>
       <c r="B431" t="s">
         <v>296</v>
       </c>
@@ -12066,7 +12066,7 @@
       </c>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A432" s="75"/>
+      <c r="A432" s="76"/>
       <c r="B432" t="s">
         <v>298</v>
       </c>
@@ -12081,7 +12081,7 @@
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A433" s="75"/>
+      <c r="A433" s="76"/>
       <c r="B433" t="s">
         <v>299</v>
       </c>
@@ -12093,7 +12093,7 @@
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A434" s="75"/>
+      <c r="A434" s="76"/>
       <c r="B434" t="s">
         <v>220</v>
       </c>
@@ -12109,7 +12109,7 @@
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A435" s="75"/>
+      <c r="A435" s="76"/>
       <c r="B435" t="s">
         <v>304</v>
       </c>
@@ -12125,7 +12125,7 @@
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A436" s="75"/>
+      <c r="A436" s="76"/>
       <c r="B436" t="s">
         <v>305</v>
       </c>
@@ -12141,7 +12141,7 @@
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A437" s="75"/>
+      <c r="A437" s="76"/>
       <c r="C437" t="s">
         <v>300</v>
       </c>
@@ -12154,7 +12154,7 @@
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A438" s="75"/>
+      <c r="A438" s="76"/>
       <c r="C438" t="s">
         <v>302</v>
       </c>
@@ -12166,7 +12166,7 @@
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A439" s="75"/>
+      <c r="A439" s="76"/>
       <c r="C439" t="s">
         <v>303</v>
       </c>
@@ -12179,7 +12179,7 @@
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A440" s="75"/>
+      <c r="A440" s="76"/>
       <c r="C440" t="s">
         <v>301</v>
       </c>
@@ -12189,7 +12189,7 @@
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A441" s="75"/>
+      <c r="A441" s="76"/>
       <c r="B441" t="s">
         <v>327</v>
       </c>
@@ -12205,7 +12205,7 @@
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A442" s="75"/>
+      <c r="A442" s="76"/>
       <c r="B442" t="s">
         <v>880</v>
       </c>
@@ -12221,7 +12221,7 @@
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A443" s="75"/>
+      <c r="A443" s="76"/>
       <c r="B443" t="s">
         <v>879</v>
       </c>
@@ -12234,7 +12234,7 @@
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A444" s="75"/>
+      <c r="A444" s="76"/>
       <c r="B444" t="s">
         <v>882</v>
       </c>
@@ -12247,7 +12247,7 @@
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A445" s="75"/>
+      <c r="A445" s="76"/>
       <c r="B445" t="s">
         <v>322</v>
       </c>
@@ -12260,7 +12260,7 @@
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A446" s="75"/>
+      <c r="A446" s="76"/>
       <c r="B446" t="s">
         <v>311</v>
       </c>
@@ -12272,7 +12272,7 @@
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A447" s="75"/>
+      <c r="A447" s="76"/>
       <c r="B447" t="s">
         <v>314</v>
       </c>
@@ -12284,7 +12284,7 @@
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A448" s="75"/>
+      <c r="A448" s="76"/>
       <c r="B448" t="s">
         <v>315</v>
       </c>
@@ -12299,7 +12299,7 @@
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A449" s="75"/>
+      <c r="A449" s="76"/>
       <c r="B449" t="s">
         <v>312</v>
       </c>
@@ -12315,7 +12315,7 @@
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A450" s="75"/>
+      <c r="A450" s="76"/>
       <c r="C450" t="s">
         <v>326</v>
       </c>
@@ -12328,7 +12328,7 @@
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A451" s="75"/>
+      <c r="A451" s="76"/>
       <c r="B451" t="s">
         <v>317</v>
       </c>
@@ -12340,7 +12340,7 @@
       </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A452" s="75"/>
+      <c r="A452" s="76"/>
       <c r="C452" t="s">
         <v>319</v>
       </c>
@@ -12350,7 +12350,7 @@
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A453" s="75"/>
+      <c r="A453" s="76"/>
       <c r="C453" t="s">
         <v>318</v>
       </c>
@@ -12360,7 +12360,7 @@
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A454" s="75"/>
+      <c r="A454" s="76"/>
       <c r="B454" t="s">
         <v>320</v>
       </c>
@@ -12380,7 +12380,7 @@
       <c r="D455" s="27"/>
     </row>
     <row r="456" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A456" s="75" t="s">
+      <c r="A456" s="76" t="s">
         <v>974</v>
       </c>
       <c r="C456" t="s">
@@ -12393,7 +12393,7 @@
       <c r="E456" s="8"/>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A457" s="75"/>
+      <c r="A457" s="76"/>
       <c r="B457" t="s">
         <v>47</v>
       </c>
@@ -12406,7 +12406,7 @@
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A458" s="75"/>
+      <c r="A458" s="76"/>
       <c r="B458" t="s">
         <v>877</v>
       </c>
@@ -12419,7 +12419,7 @@
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A459" s="75"/>
+      <c r="A459" s="76"/>
       <c r="B459" t="s">
         <v>40</v>
       </c>
@@ -12432,11 +12432,11 @@
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A460" s="75"/>
+      <c r="A460" s="76"/>
       <c r="D460" s="53"/>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A461" s="75"/>
+      <c r="A461" s="76"/>
       <c r="B461" t="s">
         <v>39</v>
       </c>
@@ -12445,7 +12445,7 @@
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A462" s="75"/>
+      <c r="A462" s="76"/>
       <c r="B462" t="s">
         <v>288</v>
       </c>
@@ -12457,7 +12457,7 @@
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A463" s="75"/>
+      <c r="A463" s="76"/>
       <c r="B463" t="s">
         <v>906</v>
       </c>
@@ -12473,12 +12473,12 @@
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A464" s="75"/>
+      <c r="A464" s="76"/>
       <c r="D464" s="53"/>
       <c r="E464" s="8"/>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A465" s="75"/>
+      <c r="A465" s="76"/>
       <c r="B465" t="s">
         <v>287</v>
       </c>
@@ -12488,7 +12488,7 @@
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A466" s="75"/>
+      <c r="A466" s="76"/>
       <c r="B466" t="s">
         <v>290</v>
       </c>
@@ -12501,7 +12501,7 @@
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A467" s="75"/>
+      <c r="A467" s="76"/>
       <c r="B467" t="s">
         <v>971</v>
       </c>
@@ -12511,7 +12511,7 @@
       <c r="D467" s="51"/>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A468" s="75"/>
+      <c r="A468" s="76"/>
       <c r="C468" t="s">
         <v>972</v>
       </c>
@@ -12521,7 +12521,7 @@
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A469" s="75"/>
+      <c r="A469" s="76"/>
       <c r="B469" t="s">
         <v>291</v>
       </c>
@@ -12534,7 +12534,7 @@
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A470" s="75"/>
+      <c r="A470" s="76"/>
       <c r="B470" t="s">
         <v>308</v>
       </c>
@@ -12546,7 +12546,7 @@
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A471" s="75"/>
+      <c r="A471" s="76"/>
       <c r="C471" t="s">
         <v>325</v>
       </c>
@@ -12556,7 +12556,7 @@
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A472" s="75"/>
+      <c r="A472" s="76"/>
       <c r="B472" t="s">
         <v>292</v>
       </c>
@@ -12566,7 +12566,7 @@
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A473" s="75"/>
+      <c r="A473" s="76"/>
       <c r="B473" t="s">
         <v>293</v>
       </c>
@@ -12576,7 +12576,7 @@
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A474" s="75"/>
+      <c r="A474" s="76"/>
       <c r="B474" t="s">
         <v>294</v>
       </c>
@@ -12591,7 +12591,7 @@
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A475" s="75"/>
+      <c r="A475" s="76"/>
       <c r="B475" t="s">
         <v>296</v>
       </c>
@@ -12604,7 +12604,7 @@
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A476" s="75"/>
+      <c r="A476" s="76"/>
       <c r="B476" t="s">
         <v>922</v>
       </c>
@@ -12616,7 +12616,7 @@
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A477" s="75"/>
+      <c r="A477" s="76"/>
       <c r="B477" s="35" t="s">
         <v>909</v>
       </c>
@@ -12631,7 +12631,7 @@
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A478" s="75"/>
+      <c r="A478" s="76"/>
       <c r="B478" s="35" t="s">
         <v>911</v>
       </c>
@@ -12647,7 +12647,7 @@
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A479" s="75"/>
+      <c r="A479" s="76"/>
       <c r="B479" s="35" t="s">
         <v>910</v>
       </c>
@@ -12666,7 +12666,7 @@
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A480" s="75"/>
+      <c r="A480" s="76"/>
       <c r="B480" s="35" t="s">
         <v>912</v>
       </c>
@@ -12682,7 +12682,7 @@
       </c>
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A481" s="75"/>
+      <c r="A481" s="76"/>
       <c r="B481" s="35"/>
       <c r="C481" t="s">
         <v>924</v>
@@ -12693,7 +12693,7 @@
       </c>
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A482" s="75"/>
+      <c r="A482" s="76"/>
       <c r="B482" s="35" t="s">
         <v>935</v>
       </c>
@@ -12709,7 +12709,7 @@
       </c>
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A483" s="75"/>
+      <c r="A483" s="76"/>
       <c r="B483" s="35" t="s">
         <v>937</v>
       </c>
@@ -12725,7 +12725,7 @@
       </c>
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A484" s="75"/>
+      <c r="A484" s="76"/>
       <c r="B484" s="35" t="s">
         <v>919</v>
       </c>
@@ -12746,7 +12746,7 @@
       </c>
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A485" s="75"/>
+      <c r="A485" s="76"/>
       <c r="B485" t="s">
         <v>886</v>
       </c>
@@ -12762,7 +12762,7 @@
       </c>
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A486" s="75"/>
+      <c r="A486" s="76"/>
       <c r="B486" t="s">
         <v>921</v>
       </c>
@@ -12778,7 +12778,7 @@
       </c>
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A487" s="75"/>
+      <c r="A487" s="76"/>
       <c r="B487" t="s">
         <v>1114</v>
       </c>
@@ -12793,7 +12793,7 @@
       </c>
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A488" s="75"/>
+      <c r="A488" s="76"/>
       <c r="B488" t="s">
         <v>1116</v>
       </c>
@@ -12808,7 +12808,7 @@
       </c>
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A489" s="75"/>
+      <c r="A489" s="76"/>
       <c r="C489" t="s">
         <v>1125</v>
       </c>
@@ -12820,7 +12820,7 @@
       </c>
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A490" s="75"/>
+      <c r="A490" s="76"/>
       <c r="B490" t="s">
         <v>1126</v>
       </c>
@@ -12834,7 +12834,7 @@
       <c r="E490" s="8"/>
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A491" s="75"/>
+      <c r="A491" s="76"/>
       <c r="B491" t="s">
         <v>1118</v>
       </c>
@@ -12847,7 +12847,7 @@
       <c r="E491" s="8"/>
     </row>
     <row r="492" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A492" s="75"/>
+      <c r="A492" s="76"/>
       <c r="B492" t="s">
         <v>299</v>
       </c>
@@ -12861,7 +12861,7 @@
       <c r="H492" s="52"/>
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A493" s="75"/>
+      <c r="A493" s="76"/>
       <c r="B493" t="s">
         <v>1122</v>
       </c>
@@ -12876,7 +12876,7 @@
       <c r="H493" s="52"/>
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A494" s="75"/>
+      <c r="A494" s="76"/>
       <c r="B494" t="s">
         <v>1120</v>
       </c>
@@ -12893,7 +12893,7 @@
       <c r="H494" s="52"/>
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A495" s="75"/>
+      <c r="A495" s="76"/>
       <c r="C495" t="s">
         <v>1124</v>
       </c>
@@ -12901,11 +12901,11 @@
       <c r="H495" s="52"/>
     </row>
     <row r="496" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A496" s="75"/>
+      <c r="A496" s="76"/>
       <c r="H496" s="52"/>
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A497" s="75"/>
+      <c r="A497" s="76"/>
       <c r="C497" t="s">
         <v>302</v>
       </c>
@@ -12918,7 +12918,7 @@
       <c r="H497" s="52"/>
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A498" s="75"/>
+      <c r="A498" s="76"/>
       <c r="C498" t="s">
         <v>303</v>
       </c>
@@ -12932,7 +12932,7 @@
       <c r="H498" s="52"/>
     </row>
     <row r="499" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A499" s="75"/>
+      <c r="A499" s="76"/>
       <c r="C499" t="s">
         <v>1128</v>
       </c>
@@ -12943,7 +12943,7 @@
       <c r="H499" s="52"/>
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A500" s="75"/>
+      <c r="A500" s="76"/>
       <c r="B500" t="s">
         <v>941</v>
       </c>
@@ -12955,7 +12955,7 @@
       </c>
     </row>
     <row r="501" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A501" s="75"/>
+      <c r="A501" s="76"/>
       <c r="B501" t="s">
         <v>950</v>
       </c>
@@ -12970,7 +12970,7 @@
       </c>
     </row>
     <row r="502" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A502" s="75"/>
+      <c r="A502" s="76"/>
       <c r="B502" t="s">
         <v>1080</v>
       </c>
@@ -12988,7 +12988,7 @@
       </c>
     </row>
     <row r="503" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A503" s="75"/>
+      <c r="A503" s="76"/>
       <c r="B503" t="s">
         <v>940</v>
       </c>
@@ -13004,7 +13004,7 @@
       </c>
     </row>
     <row r="504" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A504" s="75"/>
+      <c r="A504" s="76"/>
       <c r="B504" t="s">
         <v>1082</v>
       </c>
@@ -13015,7 +13015,7 @@
       <c r="E504" s="8"/>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A505" s="75"/>
+      <c r="A505" s="76"/>
       <c r="B505" t="s">
         <v>1083</v>
       </c>
@@ -13026,7 +13026,7 @@
       <c r="E505" s="8"/>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A506" s="75"/>
+      <c r="A506" s="76"/>
       <c r="C506" t="s">
         <v>1084</v>
       </c>
@@ -13037,7 +13037,7 @@
       <c r="E506" s="8"/>
     </row>
     <row r="507" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A507" s="75"/>
+      <c r="A507" s="76"/>
       <c r="B507" t="s">
         <v>943</v>
       </c>
@@ -13052,7 +13052,7 @@
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A508" s="75"/>
+      <c r="A508" s="76"/>
       <c r="B508" t="s">
         <v>946</v>
       </c>
@@ -13068,7 +13068,7 @@
       </c>
     </row>
     <row r="509" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A509" s="75"/>
+      <c r="A509" s="76"/>
       <c r="B509" t="s">
         <v>947</v>
       </c>
@@ -13081,7 +13081,7 @@
       </c>
     </row>
     <row r="510" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A510" s="75"/>
+      <c r="A510" s="76"/>
       <c r="B510" t="s">
         <v>949</v>
       </c>
@@ -13093,7 +13093,7 @@
       </c>
     </row>
     <row r="511" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A511" s="75"/>
+      <c r="A511" s="76"/>
       <c r="C511" t="s">
         <v>945</v>
       </c>
@@ -13104,7 +13104,7 @@
       <c r="E511" s="8"/>
     </row>
     <row r="512" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A512" s="75"/>
+      <c r="A512" s="76"/>
       <c r="B512" t="s">
         <v>948</v>
       </c>
@@ -13116,7 +13116,7 @@
       </c>
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A513" s="75"/>
+      <c r="A513" s="76"/>
       <c r="C513" t="s">
         <v>951</v>
       </c>
@@ -13127,7 +13127,7 @@
       <c r="E513" s="8"/>
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A514" s="75"/>
+      <c r="A514" s="76"/>
       <c r="B514" t="s">
         <v>889</v>
       </c>
@@ -13143,7 +13143,7 @@
       </c>
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A515" s="75"/>
+      <c r="A515" s="76"/>
       <c r="B515" t="s">
         <v>890</v>
       </c>
@@ -13159,7 +13159,7 @@
       </c>
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A516" s="75"/>
+      <c r="A516" s="76"/>
       <c r="B516" t="s">
         <v>891</v>
       </c>
@@ -13175,7 +13175,7 @@
       </c>
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A517" s="75"/>
+      <c r="A517" s="76"/>
       <c r="B517" t="s">
         <v>892</v>
       </c>
@@ -13191,7 +13191,7 @@
       </c>
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A518" s="75"/>
+      <c r="A518" s="76"/>
       <c r="B518" t="s">
         <v>893</v>
       </c>
@@ -13207,7 +13207,7 @@
       </c>
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A519" s="75"/>
+      <c r="A519" s="76"/>
       <c r="B519" t="s">
         <v>894</v>
       </c>
@@ -13223,19 +13223,19 @@
       </c>
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A520" s="75"/>
+      <c r="A520" s="76"/>
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A521" s="75"/>
+      <c r="A521" s="76"/>
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A522" s="75"/>
+      <c r="A522" s="76"/>
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A523" s="75"/>
+      <c r="A523" s="76"/>
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A524" s="75"/>
+      <c r="A524" s="76"/>
       <c r="B524" t="s">
         <v>953</v>
       </c>
@@ -13248,7 +13248,7 @@
       </c>
     </row>
     <row r="525" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A525" s="75"/>
+      <c r="A525" s="76"/>
       <c r="B525" t="s">
         <v>954</v>
       </c>
@@ -13266,7 +13266,7 @@
       </c>
     </row>
     <row r="526" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A526" s="75"/>
+      <c r="A526" s="76"/>
       <c r="B526" t="s">
         <v>955</v>
       </c>
@@ -13281,7 +13281,7 @@
       </c>
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A527" s="75"/>
+      <c r="A527" s="76"/>
       <c r="B527" t="s">
         <v>968</v>
       </c>
@@ -13297,7 +13297,7 @@
       </c>
     </row>
     <row r="528" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A528" s="75"/>
+      <c r="A528" s="76"/>
       <c r="B528" t="s">
         <v>900</v>
       </c>
@@ -13313,14 +13313,14 @@
       </c>
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A529" s="75"/>
+      <c r="A529" s="76"/>
       <c r="D529" s="54"/>
       <c r="E529" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A530" s="75"/>
+      <c r="A530" s="76"/>
       <c r="B530" t="s">
         <v>960</v>
       </c>
@@ -13338,7 +13338,7 @@
       </c>
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A531" s="75"/>
+      <c r="A531" s="76"/>
       <c r="B531" t="s">
         <v>959</v>
       </c>
@@ -13353,7 +13353,7 @@
       </c>
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A532" s="75"/>
+      <c r="A532" s="76"/>
       <c r="B532" t="s">
         <v>965</v>
       </c>
@@ -13369,7 +13369,7 @@
       </c>
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A533" s="75"/>
+      <c r="A533" s="76"/>
       <c r="B533" t="s">
         <v>969</v>
       </c>
@@ -13384,7 +13384,7 @@
       </c>
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A534" s="75"/>
+      <c r="A534" s="76"/>
       <c r="B534" t="s">
         <v>963</v>
       </c>
@@ -13399,7 +13399,7 @@
       </c>
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A535" s="75"/>
+      <c r="A535" s="76"/>
       <c r="B535" t="s">
         <v>970</v>
       </c>
@@ -13409,7 +13409,7 @@
       </c>
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A536" s="75"/>
+      <c r="A536" s="76"/>
       <c r="B536" t="s">
         <v>964</v>
       </c>
@@ -13419,7 +13419,7 @@
       </c>
     </row>
     <row r="537" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A537" s="75"/>
+      <c r="A537" s="76"/>
       <c r="B537" t="s">
         <v>880</v>
       </c>
@@ -13432,7 +13432,7 @@
       </c>
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A538" s="75"/>
+      <c r="A538" s="76"/>
       <c r="B538" t="s">
         <v>879</v>
       </c>
@@ -13445,7 +13445,7 @@
       </c>
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A539" s="75"/>
+      <c r="A539" s="76"/>
       <c r="B539" t="s">
         <v>899</v>
       </c>
@@ -13458,7 +13458,7 @@
       </c>
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A540" s="75"/>
+      <c r="A540" s="76"/>
       <c r="B540" t="s">
         <v>901</v>
       </c>
@@ -13474,7 +13474,7 @@
       </c>
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A541" s="75"/>
+      <c r="A541" s="76"/>
       <c r="B541" t="s">
         <v>903</v>
       </c>
@@ -13490,7 +13490,7 @@
       </c>
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A542" s="75"/>
+      <c r="A542" s="76"/>
       <c r="B542" t="s">
         <v>311</v>
       </c>
@@ -13502,7 +13502,7 @@
       </c>
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A543" s="75"/>
+      <c r="A543" s="76"/>
       <c r="B543" t="s">
         <v>314</v>
       </c>
@@ -13514,7 +13514,7 @@
       </c>
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A544" s="75"/>
+      <c r="A544" s="76"/>
       <c r="B544" t="s">
         <v>315</v>
       </c>
@@ -13529,7 +13529,7 @@
       </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A545" s="75"/>
+      <c r="A545" s="76"/>
       <c r="B545" t="s">
         <v>312</v>
       </c>
@@ -13545,7 +13545,7 @@
       </c>
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A546" s="75"/>
+      <c r="A546" s="76"/>
       <c r="C546" t="s">
         <v>326</v>
       </c>
@@ -13558,7 +13558,7 @@
       </c>
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A547" s="75"/>
+      <c r="A547" s="76"/>
       <c r="B547" t="s">
         <v>317</v>
       </c>
@@ -13570,7 +13570,7 @@
       </c>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A548" s="75"/>
+      <c r="A548" s="76"/>
       <c r="C548" t="s">
         <v>319</v>
       </c>
@@ -13580,7 +13580,7 @@
       </c>
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A549" s="75"/>
+      <c r="A549" s="76"/>
       <c r="C549" t="s">
         <v>318</v>
       </c>
@@ -13590,7 +13590,7 @@
       </c>
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A550" s="75"/>
+      <c r="A550" s="76"/>
       <c r="B550" t="s">
         <v>320</v>
       </c>
@@ -13606,7 +13606,7 @@
       </c>
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A551" s="75"/>
+      <c r="A551" s="76"/>
       <c r="B551" s="35" t="s">
         <v>916</v>
       </c>
@@ -13618,7 +13618,7 @@
       </c>
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A552" s="75"/>
+      <c r="A552" s="76"/>
       <c r="B552" s="35" t="s">
         <v>930</v>
       </c>
@@ -13631,7 +13631,7 @@
       </c>
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A553" s="75"/>
+      <c r="A553" s="76"/>
       <c r="B553" t="s">
         <v>925</v>
       </c>
@@ -13643,7 +13643,7 @@
       </c>
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A554" s="75"/>
+      <c r="A554" s="76"/>
       <c r="B554" s="35"/>
       <c r="C554" t="s">
         <v>933</v>
@@ -13654,7 +13654,7 @@
       </c>
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A555" s="75"/>
+      <c r="A555" s="76"/>
       <c r="B555" t="s">
         <v>929</v>
       </c>
@@ -13663,7 +13663,7 @@
       </c>
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A556" s="75"/>
+      <c r="A556" s="76"/>
       <c r="B556" t="s">
         <v>927</v>
       </c>
@@ -13676,7 +13676,7 @@
       </c>
     </row>
     <row r="557" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A557" s="75"/>
+      <c r="A557" s="76"/>
       <c r="B557" s="35" t="s">
         <v>931</v>
       </c>
@@ -13689,7 +13689,7 @@
       </c>
     </row>
     <row r="558" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A558" s="75"/>
+      <c r="A558" s="76"/>
       <c r="C558" t="s">
         <v>934</v>
       </c>
@@ -13699,11 +13699,11 @@
       </c>
     </row>
     <row r="559" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A559" s="75"/>
+      <c r="A559" s="76"/>
       <c r="D559" s="51"/>
     </row>
     <row r="560" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A560" s="75"/>
+      <c r="A560" s="76"/>
       <c r="B560" s="35" t="s">
         <v>1101</v>
       </c>
@@ -13716,7 +13716,7 @@
       </c>
     </row>
     <row r="561" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A561" s="75"/>
+      <c r="A561" s="76"/>
       <c r="B561" s="35" t="s">
         <v>1103</v>
       </c>
@@ -13729,7 +13729,7 @@
       </c>
     </row>
     <row r="562" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A562" s="75"/>
+      <c r="A562" s="76"/>
       <c r="B562" s="35" t="s">
         <v>1105</v>
       </c>
@@ -13737,12 +13737,12 @@
         <v>1106</v>
       </c>
       <c r="D562" s="51">
-        <f>E957</f>
+        <f>E963</f>
         <v>2.2741325637156556E-10</v>
       </c>
     </row>
     <row r="563" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A563" s="75"/>
+      <c r="A563" s="76"/>
       <c r="B563" s="35" t="s">
         <v>1130</v>
       </c>
@@ -13754,7 +13754,7 @@
       </c>
     </row>
     <row r="564" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A564" s="75"/>
+      <c r="A564" s="76"/>
       <c r="B564" s="35" t="s">
         <v>1131</v>
       </c>
@@ -13764,7 +13764,7 @@
       </c>
     </row>
     <row r="565" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A565" s="75"/>
+      <c r="A565" s="76"/>
       <c r="B565" s="35" t="s">
         <v>1100</v>
       </c>
@@ -13774,14 +13774,14 @@
       </c>
     </row>
     <row r="566" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A566" s="75"/>
+      <c r="A566" s="76"/>
     </row>
     <row r="567" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="48"/>
       <c r="D567" s="27"/>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A568" s="75" t="s">
+      <c r="A568" s="76" t="s">
         <v>680</v>
       </c>
       <c r="B568" t="s">
@@ -13796,7 +13796,7 @@
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A569" s="75"/>
+      <c r="A569" s="76"/>
       <c r="C569" t="s">
         <v>681</v>
       </c>
@@ -13808,7 +13808,7 @@
       </c>
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A570" s="75"/>
+      <c r="A570" s="76"/>
       <c r="C570" t="s">
         <v>683</v>
       </c>
@@ -13820,7 +13820,7 @@
       </c>
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A571" s="75"/>
+      <c r="A571" s="76"/>
       <c r="C571" t="s">
         <v>684</v>
       </c>
@@ -13832,7 +13832,7 @@
       </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A572" s="75"/>
+      <c r="A572" s="76"/>
       <c r="B572" t="s">
         <v>686</v>
       </c>
@@ -13846,7 +13846,7 @@
       <c r="E572" s="35"/>
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A573" s="75"/>
+      <c r="A573" s="76"/>
       <c r="B573" t="s">
         <v>688</v>
       </c>
@@ -13860,7 +13860,7 @@
       <c r="E573" s="35"/>
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A574" s="75"/>
+      <c r="A574" s="76"/>
       <c r="B574" t="s">
         <v>690</v>
       </c>
@@ -13873,7 +13873,7 @@
       <c r="E574" s="34"/>
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A575" s="75"/>
+      <c r="A575" s="76"/>
       <c r="C575" t="s">
         <v>685</v>
       </c>
@@ -13884,7 +13884,7 @@
       <c r="E575" s="34"/>
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A576" s="75"/>
+      <c r="A576" s="76"/>
       <c r="B576" t="s">
         <v>693</v>
       </c>
@@ -13898,7 +13898,7 @@
       <c r="E576" s="34"/>
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A577" s="75"/>
+      <c r="A577" s="76"/>
       <c r="C577" t="s">
         <v>694</v>
       </c>
@@ -13908,7 +13908,7 @@
       <c r="E577" s="34"/>
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A578" s="75"/>
+      <c r="A578" s="76"/>
       <c r="C578" t="s">
         <v>695</v>
       </c>
@@ -13919,7 +13919,7 @@
       <c r="E578" s="34"/>
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A579" s="75"/>
+      <c r="A579" s="76"/>
       <c r="C579" t="s">
         <v>696</v>
       </c>
@@ -13929,7 +13929,7 @@
       <c r="E579" s="34"/>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A580" s="75"/>
+      <c r="A580" s="76"/>
       <c r="C580" t="s">
         <v>697</v>
       </c>
@@ -13939,21 +13939,21 @@
       </c>
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A581" s="75" t="s">
+      <c r="A581" s="76" t="s">
         <v>698</v>
       </c>
     </row>
     <row r="582" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A582" s="75"/>
+      <c r="A582" s="76"/>
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A583" s="75"/>
+      <c r="A583" s="76"/>
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A584" s="75"/>
+      <c r="A584" s="76"/>
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A585" s="76" t="s">
+      <c r="A585" s="77" t="s">
         <v>330</v>
       </c>
       <c r="B585" t="s">
@@ -13968,7 +13968,7 @@
       </c>
     </row>
     <row r="586" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A586" s="76"/>
+      <c r="A586" s="77"/>
       <c r="B586" t="s">
         <v>47</v>
       </c>
@@ -13978,7 +13978,7 @@
       </c>
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A587" s="76"/>
+      <c r="A587" s="77"/>
       <c r="B587" t="s">
         <v>231</v>
       </c>
@@ -13988,7 +13988,7 @@
       </c>
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A588" s="76"/>
+      <c r="A588" s="77"/>
       <c r="C588" t="s">
         <v>334</v>
       </c>
@@ -13997,7 +13997,7 @@
       </c>
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A589" s="76"/>
+      <c r="A589" s="77"/>
       <c r="C589" t="s">
         <v>336</v>
       </c>
@@ -14007,7 +14007,7 @@
       </c>
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A590" s="76"/>
+      <c r="A590" s="77"/>
       <c r="B590" t="s">
         <v>331</v>
       </c>
@@ -14019,7 +14019,7 @@
       </c>
     </row>
     <row r="591" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A591" s="76"/>
+      <c r="A591" s="77"/>
       <c r="B591" t="s">
         <v>333</v>
       </c>
@@ -14032,7 +14032,7 @@
       </c>
     </row>
     <row r="592" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A592" s="76"/>
+      <c r="A592" s="77"/>
       <c r="B592" t="s">
         <v>383</v>
       </c>
@@ -14045,7 +14045,7 @@
       </c>
     </row>
     <row r="593" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A593" s="76"/>
+      <c r="A593" s="77"/>
       <c r="B593" t="s">
         <v>338</v>
       </c>
@@ -14058,7 +14058,7 @@
       </c>
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A594" s="76"/>
+      <c r="A594" s="77"/>
       <c r="B594" t="s">
         <v>339</v>
       </c>
@@ -14071,7 +14071,7 @@
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A595" s="76"/>
+      <c r="A595" s="77"/>
       <c r="B595" t="s">
         <v>340</v>
       </c>
@@ -14084,7 +14084,7 @@
       </c>
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A596" s="76"/>
+      <c r="A596" s="77"/>
       <c r="C596" t="s">
         <v>342</v>
       </c>
@@ -14094,7 +14094,7 @@
       </c>
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A597" s="76"/>
+      <c r="A597" s="77"/>
       <c r="B597" t="s">
         <v>373</v>
       </c>
@@ -14106,7 +14106,7 @@
       </c>
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A598" s="76"/>
+      <c r="A598" s="77"/>
       <c r="B598" t="s">
         <v>347</v>
       </c>
@@ -14118,7 +14118,7 @@
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A599" s="76"/>
+      <c r="A599" s="77"/>
       <c r="B599" t="s">
         <v>348</v>
       </c>
@@ -14130,7 +14130,7 @@
       </c>
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A600" s="76"/>
+      <c r="A600" s="77"/>
       <c r="B600" t="s">
         <v>351</v>
       </c>
@@ -14145,7 +14145,7 @@
       </c>
     </row>
     <row r="601" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A601" s="76"/>
+      <c r="A601" s="77"/>
       <c r="B601" t="s">
         <v>352</v>
       </c>
@@ -14160,7 +14160,7 @@
       </c>
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A602" s="76"/>
+      <c r="A602" s="77"/>
       <c r="B602" t="s">
         <v>354</v>
       </c>
@@ -14176,7 +14176,7 @@
       </c>
     </row>
     <row r="603" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A603" s="76"/>
+      <c r="A603" s="77"/>
       <c r="B603" s="26" t="s">
         <v>358</v>
       </c>
@@ -14191,7 +14191,7 @@
       </c>
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A604" s="76"/>
+      <c r="A604" s="77"/>
       <c r="C604" t="s">
         <v>361</v>
       </c>
@@ -14201,7 +14201,7 @@
       </c>
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A605" s="76"/>
+      <c r="A605" s="77"/>
       <c r="B605" t="s">
         <v>376</v>
       </c>
@@ -14214,7 +14214,7 @@
       </c>
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A606" s="76"/>
+      <c r="A606" s="77"/>
       <c r="B606" t="s">
         <v>377</v>
       </c>
@@ -14224,7 +14224,7 @@
       </c>
     </row>
     <row r="607" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A607" s="76"/>
+      <c r="A607" s="77"/>
       <c r="B607" t="s">
         <v>343</v>
       </c>
@@ -14233,7 +14233,7 @@
       </c>
     </row>
     <row r="608" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A608" s="76"/>
+      <c r="A608" s="77"/>
       <c r="B608" t="s">
         <v>345</v>
       </c>
@@ -14243,7 +14243,7 @@
       </c>
     </row>
     <row r="609" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A609" s="76"/>
+      <c r="A609" s="77"/>
       <c r="B609" t="s">
         <v>344</v>
       </c>
@@ -14255,7 +14255,7 @@
       </c>
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A610" s="76"/>
+      <c r="A610" s="77"/>
       <c r="B610" t="s">
         <v>378</v>
       </c>
@@ -14268,7 +14268,7 @@
       </c>
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A611" s="76"/>
+      <c r="A611" s="77"/>
       <c r="C611" t="s">
         <v>394</v>
       </c>
@@ -14277,7 +14277,7 @@
       </c>
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A612" s="76"/>
+      <c r="A612" s="77"/>
       <c r="B612" t="s">
         <v>395</v>
       </c>
@@ -14287,7 +14287,7 @@
       </c>
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A613" s="76"/>
+      <c r="A613" s="77"/>
       <c r="B613" t="s">
         <v>396</v>
       </c>
@@ -14297,7 +14297,7 @@
       </c>
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A614" s="76"/>
+      <c r="A614" s="77"/>
       <c r="B614" t="s">
         <v>397</v>
       </c>
@@ -14307,7 +14307,7 @@
       </c>
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A615" s="76"/>
+      <c r="A615" s="77"/>
       <c r="B615" t="s">
         <v>398</v>
       </c>
@@ -14317,7 +14317,7 @@
       </c>
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A616" s="76"/>
+      <c r="A616" s="77"/>
       <c r="B616" t="s">
         <v>392</v>
       </c>
@@ -14330,7 +14330,7 @@
       </c>
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A617" s="76"/>
+      <c r="A617" s="77"/>
       <c r="B617" t="s">
         <v>399</v>
       </c>
@@ -14343,7 +14343,7 @@
       </c>
     </row>
     <row r="618" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A618" s="76"/>
+      <c r="A618" s="77"/>
       <c r="C618" t="s">
         <v>400</v>
       </c>
@@ -14353,7 +14353,7 @@
       </c>
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A619" s="76"/>
+      <c r="A619" s="77"/>
       <c r="C619" t="s">
         <v>401</v>
       </c>
@@ -14366,7 +14366,7 @@
       </c>
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A620" s="76"/>
+      <c r="A620" s="77"/>
       <c r="B620" t="s">
         <v>379</v>
       </c>
@@ -14376,7 +14376,7 @@
       </c>
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A621" s="76"/>
+      <c r="A621" s="77"/>
       <c r="C621" t="s">
         <v>368</v>
       </c>
@@ -14386,7 +14386,7 @@
       </c>
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A622" s="76"/>
+      <c r="A622" s="77"/>
       <c r="C622" t="s">
         <v>380</v>
       </c>
@@ -14396,7 +14396,7 @@
       </c>
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A623" s="76"/>
+      <c r="A623" s="77"/>
       <c r="B623" t="s">
         <v>366</v>
       </c>
@@ -14409,7 +14409,7 @@
       </c>
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A624" s="76"/>
+      <c r="A624" s="77"/>
       <c r="C624" t="s">
         <v>381</v>
       </c>
@@ -14419,7 +14419,7 @@
       </c>
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A625" s="76"/>
+      <c r="A625" s="77"/>
       <c r="C625" t="s">
         <v>382</v>
       </c>
@@ -14429,7 +14429,7 @@
       </c>
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A626" s="76"/>
+      <c r="A626" s="77"/>
       <c r="B626" t="s">
         <v>367</v>
       </c>
@@ -14439,7 +14439,7 @@
       </c>
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A627" s="76"/>
+      <c r="A627" s="77"/>
       <c r="C627" t="s">
         <v>372</v>
       </c>
@@ -14449,7 +14449,7 @@
       </c>
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A628" s="76"/>
+      <c r="A628" s="77"/>
       <c r="C628" t="s">
         <v>369</v>
       </c>
@@ -14459,10 +14459,10 @@
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A629" s="76"/>
+      <c r="A629" s="77"/>
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A630" s="76"/>
+      <c r="A630" s="77"/>
       <c r="C630" t="s">
         <v>370</v>
       </c>
@@ -14475,7 +14475,7 @@
       </c>
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A631" s="76"/>
+      <c r="A631" s="77"/>
       <c r="C631" t="s">
         <v>370</v>
       </c>
@@ -14488,7 +14488,7 @@
       </c>
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A632" s="76"/>
+      <c r="A632" s="77"/>
       <c r="C632" t="s">
         <v>371</v>
       </c>
@@ -14498,7 +14498,7 @@
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A633" s="76"/>
+      <c r="A633" s="77"/>
       <c r="B633" t="s">
         <v>385</v>
       </c>
@@ -14508,7 +14508,7 @@
       </c>
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A634" s="76"/>
+      <c r="A634" s="77"/>
       <c r="B634" t="s">
         <v>386</v>
       </c>
@@ -14518,13 +14518,13 @@
       </c>
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A635" s="76"/>
+      <c r="A635" s="77"/>
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A636" s="76"/>
+      <c r="A636" s="77"/>
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A637" s="76"/>
+      <c r="A637" s="77"/>
       <c r="B637" t="s">
         <v>388</v>
       </c>
@@ -14540,7 +14540,7 @@
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A638" s="76"/>
+      <c r="A638" s="77"/>
       <c r="B638" t="s">
         <v>389</v>
       </c>
@@ -14553,7 +14553,7 @@
       </c>
     </row>
     <row r="639" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A639" s="76"/>
+      <c r="A639" s="77"/>
       <c r="B639" t="s">
         <v>391</v>
       </c>
@@ -14563,7 +14563,7 @@
       </c>
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A640" s="76"/>
+      <c r="A640" s="77"/>
       <c r="B640" t="s">
         <v>402</v>
       </c>
@@ -14576,7 +14576,7 @@
       </c>
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A641" s="76"/>
+      <c r="A641" s="77"/>
       <c r="B641" t="s">
         <v>404</v>
       </c>
@@ -14586,7 +14586,7 @@
       </c>
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A642" s="76"/>
+      <c r="A642" s="77"/>
       <c r="B642" t="s">
         <v>405</v>
       </c>
@@ -14596,7 +14596,7 @@
       </c>
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A643" s="76"/>
+      <c r="A643" s="77"/>
       <c r="B643" t="s">
         <v>406</v>
       </c>
@@ -14606,7 +14606,7 @@
       </c>
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A644" s="76"/>
+      <c r="A644" s="77"/>
       <c r="B644" t="s">
         <v>407</v>
       </c>
@@ -14616,7 +14616,7 @@
       </c>
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A645" s="76"/>
+      <c r="A645" s="77"/>
       <c r="C645" t="s">
         <v>408</v>
       </c>
@@ -14626,7 +14626,7 @@
       </c>
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A646" s="76"/>
+      <c r="A646" s="77"/>
       <c r="B646" t="s">
         <v>409</v>
       </c>
@@ -14636,7 +14636,7 @@
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A647" s="76"/>
+      <c r="A647" s="77"/>
       <c r="B647" t="s">
         <v>410</v>
       </c>
@@ -14646,7 +14646,7 @@
       </c>
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A648" s="76"/>
+      <c r="A648" s="77"/>
       <c r="B648" t="s">
         <v>411</v>
       </c>
@@ -14656,7 +14656,7 @@
       </c>
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A649" s="76"/>
+      <c r="A649" s="77"/>
       <c r="B649" t="s">
         <v>409</v>
       </c>
@@ -14669,7 +14669,7 @@
       </c>
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A650" s="76"/>
+      <c r="A650" s="77"/>
       <c r="B650" t="s">
         <v>410</v>
       </c>
@@ -14682,7 +14682,7 @@
       </c>
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A651" s="76"/>
+      <c r="A651" s="77"/>
       <c r="B651" t="s">
         <v>411</v>
       </c>
@@ -14698,7 +14698,7 @@
       <c r="A652" s="44"/>
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A653" s="75" t="s">
+      <c r="A653" s="76" t="s">
         <v>1007</v>
       </c>
       <c r="B653" t="s">
@@ -14716,7 +14716,7 @@
       </c>
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A654" s="75"/>
+      <c r="A654" s="76"/>
       <c r="B654" t="s">
         <v>830</v>
       </c>
@@ -14729,7 +14729,7 @@
       </c>
     </row>
     <row r="655" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A655" s="75"/>
+      <c r="A655" s="76"/>
       <c r="B655" s="46" t="s">
         <v>806</v>
       </c>
@@ -14745,7 +14745,7 @@
       </c>
     </row>
     <row r="656" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A656" s="75"/>
+      <c r="A656" s="76"/>
       <c r="B656" s="46" t="s">
         <v>808</v>
       </c>
@@ -14761,7 +14761,7 @@
       </c>
     </row>
     <row r="657" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A657" s="75"/>
+      <c r="A657" s="76"/>
       <c r="B657" s="46" t="s">
         <v>793</v>
       </c>
@@ -14777,7 +14777,7 @@
       </c>
     </row>
     <row r="658" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A658" s="75"/>
+      <c r="A658" s="76"/>
       <c r="B658" s="46" t="s">
         <v>795</v>
       </c>
@@ -14789,7 +14789,7 @@
       </c>
     </row>
     <row r="659" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A659" s="75"/>
+      <c r="A659" s="76"/>
       <c r="B659" s="46" t="s">
         <v>820</v>
       </c>
@@ -14802,7 +14802,7 @@
       </c>
     </row>
     <row r="660" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A660" s="75"/>
+      <c r="A660" s="76"/>
       <c r="B660" t="s">
         <v>809</v>
       </c>
@@ -14815,7 +14815,7 @@
       </c>
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A661" s="75"/>
+      <c r="A661" s="76"/>
       <c r="B661" t="s">
         <v>829</v>
       </c>
@@ -14828,7 +14828,7 @@
       </c>
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A662" s="75"/>
+      <c r="A662" s="76"/>
       <c r="B662" t="s">
         <v>810</v>
       </c>
@@ -14841,7 +14841,7 @@
       </c>
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A663" s="75"/>
+      <c r="A663" s="76"/>
       <c r="B663" t="s">
         <v>797</v>
       </c>
@@ -14856,7 +14856,7 @@
       </c>
     </row>
     <row r="664" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A664" s="75"/>
+      <c r="A664" s="76"/>
       <c r="B664" t="s">
         <v>798</v>
       </c>
@@ -14871,7 +14871,7 @@
       </c>
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A665" s="75"/>
+      <c r="A665" s="76"/>
       <c r="B665" t="s">
         <v>801</v>
       </c>
@@ -14887,7 +14887,7 @@
       </c>
     </row>
     <row r="666" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A666" s="75"/>
+      <c r="A666" s="76"/>
       <c r="B666" t="s">
         <v>802</v>
       </c>
@@ -14903,7 +14903,7 @@
       </c>
     </row>
     <row r="667" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A667" s="75"/>
+      <c r="A667" s="76"/>
       <c r="B667" t="s">
         <v>815</v>
       </c>
@@ -14919,10 +14919,10 @@
       </c>
     </row>
     <row r="668" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A668" s="75"/>
+      <c r="A668" s="76"/>
     </row>
     <row r="669" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A669" s="75"/>
+      <c r="A669" s="76"/>
       <c r="B669" t="s">
         <v>817</v>
       </c>
@@ -14938,7 +14938,7 @@
       </c>
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A670" s="75"/>
+      <c r="A670" s="76"/>
       <c r="B670" t="s">
         <v>825</v>
       </c>
@@ -14954,7 +14954,7 @@
       </c>
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A671" s="75"/>
+      <c r="A671" s="76"/>
       <c r="B671" t="s">
         <v>819</v>
       </c>
@@ -14970,7 +14970,7 @@
       </c>
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A672" s="75"/>
+      <c r="A672" s="76"/>
       <c r="B672" t="s">
         <v>826</v>
       </c>
@@ -14986,7 +14986,7 @@
       </c>
     </row>
     <row r="673" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A673" s="75"/>
+      <c r="A673" s="76"/>
       <c r="B673" t="s">
         <v>816</v>
       </c>
@@ -15002,7 +15002,7 @@
       </c>
     </row>
     <row r="674" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A674" s="75"/>
+      <c r="A674" s="76"/>
       <c r="B674" t="s">
         <v>821</v>
       </c>
@@ -15015,11 +15015,11 @@
       </c>
     </row>
     <row r="675" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A675" s="75"/>
+      <c r="A675" s="76"/>
       <c r="D675" s="27"/>
     </row>
     <row r="676" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A676" s="75"/>
+      <c r="A676" s="76"/>
       <c r="B676" t="s">
         <v>832</v>
       </c>
@@ -15035,7 +15035,7 @@
       </c>
     </row>
     <row r="677" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A677" s="75"/>
+      <c r="A677" s="76"/>
       <c r="B677" t="s">
         <v>823</v>
       </c>
@@ -15051,7 +15051,7 @@
       </c>
     </row>
     <row r="678" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A678" s="75"/>
+      <c r="A678" s="76"/>
       <c r="B678" t="s">
         <v>834</v>
       </c>
@@ -15064,7 +15064,7 @@
       </c>
     </row>
     <row r="679" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A679" s="75"/>
+      <c r="A679" s="76"/>
       <c r="B679" t="s">
         <v>836</v>
       </c>
@@ -15076,7 +15076,7 @@
       </c>
     </row>
     <row r="680" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A680" s="75"/>
+      <c r="A680" s="76"/>
       <c r="B680" t="s">
         <v>838</v>
       </c>
@@ -15085,7 +15085,7 @@
       </c>
     </row>
     <row r="681" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A681" s="75"/>
+      <c r="A681" s="76"/>
       <c r="B681" t="s">
         <v>840</v>
       </c>
@@ -15100,7 +15100,7 @@
       </c>
     </row>
     <row r="682" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A682" s="75"/>
+      <c r="A682" s="76"/>
       <c r="B682" t="s">
         <v>842</v>
       </c>
@@ -15111,7 +15111,7 @@
       <c r="E682" s="8"/>
     </row>
     <row r="683" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A683" s="75"/>
+      <c r="A683" s="76"/>
       <c r="B683" t="s">
         <v>843</v>
       </c>
@@ -15124,7 +15124,7 @@
       <c r="E683" s="8"/>
     </row>
     <row r="684" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A684" s="75"/>
+      <c r="A684" s="76"/>
       <c r="B684" t="s">
         <v>693</v>
       </c>
@@ -15138,7 +15138,7 @@
       <c r="E684" s="8"/>
     </row>
     <row r="685" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A685" s="75"/>
+      <c r="A685" s="76"/>
       <c r="B685" t="s">
         <v>848</v>
       </c>
@@ -15544,7 +15544,7 @@
       </c>
     </row>
     <row r="686" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A686" s="75"/>
+      <c r="A686" s="76"/>
       <c r="B686" t="s">
         <v>846</v>
       </c>
@@ -15850,7 +15850,7 @@
       </c>
     </row>
     <row r="687" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A687" s="75"/>
+      <c r="A687" s="76"/>
       <c r="B687" t="s">
         <v>847</v>
       </c>
@@ -16256,7 +16256,7 @@
       </c>
     </row>
     <row r="688" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A688" s="75"/>
+      <c r="A688" s="76"/>
       <c r="B688" t="s">
         <v>849</v>
       </c>
@@ -16662,7 +16662,7 @@
       </c>
     </row>
     <row r="689" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A689" s="75"/>
+      <c r="A689" s="76"/>
       <c r="B689" t="s">
         <v>850</v>
       </c>
@@ -17068,7 +17068,7 @@
       </c>
     </row>
     <row r="690" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A690" s="75"/>
+      <c r="A690" s="76"/>
       <c r="B690" t="s">
         <v>851</v>
       </c>
@@ -17078,7 +17078,7 @@
       </c>
     </row>
     <row r="691" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A691" s="75"/>
+      <c r="A691" s="76"/>
       <c r="B691" t="s">
         <v>852</v>
       </c>
@@ -17088,7 +17088,7 @@
       </c>
     </row>
     <row r="692" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A692" s="75"/>
+      <c r="A692" s="76"/>
       <c r="C692" t="s">
         <v>853</v>
       </c>
@@ -17105,7 +17105,7 @@
       <c r="E694" s="8"/>
     </row>
     <row r="695" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A695" s="76" t="s">
+      <c r="A695" s="77" t="s">
         <v>431</v>
       </c>
       <c r="B695" t="s">
@@ -17120,7 +17120,7 @@
       </c>
     </row>
     <row r="696" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A696" s="76"/>
+      <c r="A696" s="77"/>
       <c r="B696" t="s">
         <v>40</v>
       </c>
@@ -17133,7 +17133,7 @@
       </c>
     </row>
     <row r="697" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A697" s="76"/>
+      <c r="A697" s="77"/>
       <c r="B697" t="s">
         <v>39</v>
       </c>
@@ -17146,7 +17146,7 @@
       </c>
     </row>
     <row r="698" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A698" s="76"/>
+      <c r="A698" s="77"/>
       <c r="B698" t="s">
         <v>412</v>
       </c>
@@ -17159,7 +17159,7 @@
       </c>
     </row>
     <row r="699" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A699" s="76"/>
+      <c r="A699" s="77"/>
       <c r="B699" t="s">
         <v>416</v>
       </c>
@@ -17168,7 +17168,7 @@
       </c>
     </row>
     <row r="700" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A700" s="76"/>
+      <c r="A700" s="77"/>
       <c r="B700" t="s">
         <v>422</v>
       </c>
@@ -17178,7 +17178,7 @@
       </c>
     </row>
     <row r="701" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A701" s="76"/>
+      <c r="A701" s="77"/>
       <c r="C701" t="s">
         <v>417</v>
       </c>
@@ -17187,7 +17187,7 @@
       </c>
     </row>
     <row r="702" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A702" s="76"/>
+      <c r="A702" s="77"/>
       <c r="B702" t="s">
         <v>421</v>
       </c>
@@ -17197,7 +17197,7 @@
       </c>
     </row>
     <row r="703" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A703" s="76"/>
+      <c r="A703" s="77"/>
       <c r="B703" t="s">
         <v>446</v>
       </c>
@@ -17210,7 +17210,7 @@
       </c>
     </row>
     <row r="704" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A704" s="76"/>
+      <c r="A704" s="77"/>
       <c r="B704" t="s">
         <v>448</v>
       </c>
@@ -17219,7 +17219,7 @@
       </c>
     </row>
     <row r="705" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A705" s="76"/>
+      <c r="A705" s="77"/>
       <c r="B705" t="s">
         <v>449</v>
       </c>
@@ -17228,7 +17228,7 @@
       </c>
     </row>
     <row r="706" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A706" s="76"/>
+      <c r="A706" s="77"/>
       <c r="B706" t="s">
         <v>452</v>
       </c>
@@ -17240,7 +17240,7 @@
       </c>
     </row>
     <row r="707" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A707" s="76"/>
+      <c r="A707" s="77"/>
       <c r="B707" t="s">
         <v>454</v>
       </c>
@@ -17250,7 +17250,7 @@
       </c>
     </row>
     <row r="708" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A708" s="76"/>
+      <c r="A708" s="77"/>
       <c r="B708" t="s">
         <v>427</v>
       </c>
@@ -17263,7 +17263,7 @@
       </c>
     </row>
     <row r="709" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A709" s="76"/>
+      <c r="A709" s="77"/>
       <c r="C709" t="s">
         <v>450</v>
       </c>
@@ -17273,7 +17273,7 @@
       </c>
     </row>
     <row r="710" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A710" s="76"/>
+      <c r="A710" s="77"/>
       <c r="B710" t="s">
         <v>451</v>
       </c>
@@ -17283,7 +17283,7 @@
       </c>
     </row>
     <row r="711" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A711" s="76"/>
+      <c r="A711" s="77"/>
       <c r="B711" t="s">
         <v>487</v>
       </c>
@@ -17293,7 +17293,7 @@
       </c>
     </row>
     <row r="712" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A712" s="76"/>
+      <c r="A712" s="77"/>
       <c r="B712" t="s">
         <v>488</v>
       </c>
@@ -17303,7 +17303,7 @@
       </c>
     </row>
     <row r="713" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A713" s="76"/>
+      <c r="A713" s="77"/>
       <c r="B713" t="s">
         <v>489</v>
       </c>
@@ -17313,7 +17313,7 @@
       </c>
     </row>
     <row r="714" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A714" s="76"/>
+      <c r="A714" s="77"/>
       <c r="B714" t="s">
         <v>455</v>
       </c>
@@ -17323,7 +17323,7 @@
       </c>
     </row>
     <row r="715" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A715" s="76"/>
+      <c r="A715" s="77"/>
       <c r="B715" t="s">
         <v>456</v>
       </c>
@@ -17333,7 +17333,7 @@
       </c>
     </row>
     <row r="716" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A716" s="76"/>
+      <c r="A716" s="77"/>
       <c r="B716" t="s">
         <v>425</v>
       </c>
@@ -17345,7 +17345,7 @@
       </c>
     </row>
     <row r="717" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A717" s="76"/>
+      <c r="A717" s="77"/>
       <c r="B717" t="s">
         <v>423</v>
       </c>
@@ -17358,7 +17358,7 @@
       </c>
     </row>
     <row r="718" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A718" s="76"/>
+      <c r="A718" s="77"/>
       <c r="B718" t="s">
         <v>420</v>
       </c>
@@ -17370,7 +17370,7 @@
       </c>
     </row>
     <row r="719" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A719" s="76"/>
+      <c r="A719" s="77"/>
       <c r="B719" t="s">
         <v>458</v>
       </c>
@@ -17380,7 +17380,7 @@
       </c>
     </row>
     <row r="720" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A720" s="76"/>
+      <c r="A720" s="77"/>
       <c r="B720" t="s">
         <v>459</v>
       </c>
@@ -17390,7 +17390,7 @@
       </c>
     </row>
     <row r="721" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A721" s="76"/>
+      <c r="A721" s="77"/>
       <c r="B721" t="s">
         <v>418</v>
       </c>
@@ -17403,7 +17403,7 @@
       </c>
     </row>
     <row r="722" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A722" s="76"/>
+      <c r="A722" s="77"/>
       <c r="B722" t="s">
         <v>429</v>
       </c>
@@ -17413,7 +17413,7 @@
       </c>
     </row>
     <row r="723" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A723" s="76"/>
+      <c r="A723" s="77"/>
       <c r="C723" t="s">
         <v>430</v>
       </c>
@@ -17423,7 +17423,7 @@
       </c>
     </row>
     <row r="724" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A724" s="76"/>
+      <c r="A724" s="77"/>
       <c r="B724" t="s">
         <v>432</v>
       </c>
@@ -17435,7 +17435,7 @@
       </c>
     </row>
     <row r="725" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A725" s="76"/>
+      <c r="A725" s="77"/>
       <c r="B725" t="s">
         <v>38</v>
       </c>
@@ -17445,10 +17445,10 @@
       </c>
     </row>
     <row r="726" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A726" s="76"/>
+      <c r="A726" s="77"/>
     </row>
     <row r="727" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A727" s="76"/>
+      <c r="A727" s="77"/>
       <c r="B727" t="s">
         <v>435</v>
       </c>
@@ -17458,7 +17458,7 @@
       </c>
     </row>
     <row r="728" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A728" s="76"/>
+      <c r="A728" s="77"/>
       <c r="B728" t="s">
         <v>436</v>
       </c>
@@ -17468,7 +17468,7 @@
       </c>
     </row>
     <row r="729" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A729" s="76"/>
+      <c r="A729" s="77"/>
       <c r="B729" t="s">
         <v>437</v>
       </c>
@@ -17478,7 +17478,7 @@
       </c>
     </row>
     <row r="730" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A730" s="76"/>
+      <c r="A730" s="77"/>
       <c r="B730" t="s">
         <v>231</v>
       </c>
@@ -17488,7 +17488,7 @@
       </c>
     </row>
     <row r="731" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A731" s="76"/>
+      <c r="A731" s="77"/>
       <c r="B731" t="s">
         <v>438</v>
       </c>
@@ -17498,7 +17498,7 @@
       </c>
     </row>
     <row r="732" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A732" s="76"/>
+      <c r="A732" s="77"/>
       <c r="C732" t="s">
         <v>434</v>
       </c>
@@ -17508,7 +17508,7 @@
       </c>
     </row>
     <row r="733" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A733" s="76"/>
+      <c r="A733" s="77"/>
       <c r="B733" t="s">
         <v>440</v>
       </c>
@@ -17521,7 +17521,7 @@
       </c>
     </row>
     <row r="734" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A734" s="76"/>
+      <c r="A734" s="77"/>
       <c r="B734" t="s">
         <v>441</v>
       </c>
@@ -17531,7 +17531,7 @@
       </c>
     </row>
     <row r="735" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A735" s="76"/>
+      <c r="A735" s="77"/>
       <c r="B735" t="s">
         <v>442</v>
       </c>
@@ -17541,7 +17541,7 @@
       </c>
     </row>
     <row r="736" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A736" s="76"/>
+      <c r="A736" s="77"/>
       <c r="B736" t="s">
         <v>443</v>
       </c>
@@ -17551,7 +17551,7 @@
       </c>
     </row>
     <row r="737" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A737" s="76"/>
+      <c r="A737" s="77"/>
       <c r="C737" t="s">
         <v>444</v>
       </c>
@@ -17561,7 +17561,7 @@
       </c>
     </row>
     <row r="738" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A738" s="76"/>
+      <c r="A738" s="77"/>
       <c r="B738" t="s">
         <v>445</v>
       </c>
@@ -17571,7 +17571,7 @@
       </c>
     </row>
     <row r="739" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A739" s="76"/>
+      <c r="A739" s="77"/>
       <c r="B739" t="s">
         <v>463</v>
       </c>
@@ -17583,7 +17583,7 @@
       </c>
     </row>
     <row r="740" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A740" s="76"/>
+      <c r="A740" s="77"/>
       <c r="C740" t="s">
         <v>461</v>
       </c>
@@ -17592,7 +17592,7 @@
       </c>
     </row>
     <row r="741" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A741" s="76"/>
+      <c r="A741" s="77"/>
       <c r="B741" t="s">
         <v>462</v>
       </c>
@@ -17602,7 +17602,7 @@
       </c>
     </row>
     <row r="742" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A742" s="76"/>
+      <c r="A742" s="77"/>
       <c r="B742" t="s">
         <v>464</v>
       </c>
@@ -17612,7 +17612,7 @@
       </c>
     </row>
     <row r="743" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A743" s="76"/>
+      <c r="A743" s="77"/>
       <c r="B743" t="s">
         <v>465</v>
       </c>
@@ -17621,7 +17621,7 @@
       </c>
     </row>
     <row r="744" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A744" s="76"/>
+      <c r="A744" s="77"/>
       <c r="B744" t="s">
         <v>466</v>
       </c>
@@ -17630,7 +17630,7 @@
       </c>
     </row>
     <row r="745" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A745" s="76"/>
+      <c r="A745" s="77"/>
       <c r="C745" t="s">
         <v>467</v>
       </c>
@@ -17640,7 +17640,7 @@
       </c>
     </row>
     <row r="746" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A746" s="76"/>
+      <c r="A746" s="77"/>
       <c r="B746" t="s">
         <v>468</v>
       </c>
@@ -17653,7 +17653,7 @@
       </c>
     </row>
     <row r="747" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A747" s="76"/>
+      <c r="A747" s="77"/>
       <c r="B747" t="s">
         <v>470</v>
       </c>
@@ -17666,7 +17666,7 @@
       </c>
     </row>
     <row r="748" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A748" s="76"/>
+      <c r="A748" s="77"/>
       <c r="B748" t="s">
         <v>472</v>
       </c>
@@ -17676,7 +17676,7 @@
       </c>
     </row>
     <row r="749" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A749" s="76"/>
+      <c r="A749" s="77"/>
       <c r="B749" t="s">
         <v>473</v>
       </c>
@@ -17686,7 +17686,7 @@
       </c>
     </row>
     <row r="750" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A750" s="76"/>
+      <c r="A750" s="77"/>
       <c r="B750" t="s">
         <v>479</v>
       </c>
@@ -17695,7 +17695,7 @@
       </c>
     </row>
     <row r="751" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A751" s="76"/>
+      <c r="A751" s="77"/>
       <c r="C751" t="s">
         <v>483</v>
       </c>
@@ -17704,7 +17704,7 @@
       </c>
     </row>
     <row r="752" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A752" s="76"/>
+      <c r="A752" s="77"/>
       <c r="B752" t="s">
         <v>484</v>
       </c>
@@ -17714,7 +17714,7 @@
       </c>
     </row>
     <row r="753" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A753" s="76"/>
+      <c r="A753" s="77"/>
       <c r="B753" t="s">
         <v>485</v>
       </c>
@@ -17724,7 +17724,7 @@
       </c>
     </row>
     <row r="754" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A754" s="76"/>
+      <c r="A754" s="77"/>
       <c r="C754" t="s">
         <v>476</v>
       </c>
@@ -17734,7 +17734,7 @@
       </c>
     </row>
     <row r="755" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A755" s="76"/>
+      <c r="A755" s="77"/>
       <c r="C755" t="s">
         <v>477</v>
       </c>
@@ -17744,7 +17744,7 @@
       </c>
     </row>
     <row r="756" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A756" s="76"/>
+      <c r="A756" s="77"/>
       <c r="C756" t="s">
         <v>478</v>
       </c>
@@ -17754,7 +17754,7 @@
       </c>
     </row>
     <row r="757" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A757" s="76"/>
+      <c r="A757" s="77"/>
       <c r="C757" t="s">
         <v>480</v>
       </c>
@@ -17764,10 +17764,10 @@
       </c>
     </row>
     <row r="758" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A758" s="76"/>
+      <c r="A758" s="77"/>
     </row>
     <row r="759" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A759" s="76"/>
+      <c r="A759" s="77"/>
       <c r="B759" t="s">
         <v>481</v>
       </c>
@@ -17777,7 +17777,7 @@
       </c>
     </row>
     <row r="760" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A760" s="76"/>
+      <c r="A760" s="77"/>
       <c r="B760" t="s">
         <v>486</v>
       </c>
@@ -17787,7 +17787,7 @@
       </c>
     </row>
     <row r="761" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A761" s="76"/>
+      <c r="A761" s="77"/>
       <c r="B761" t="s">
         <v>482</v>
       </c>
@@ -17797,7 +17797,7 @@
       </c>
     </row>
     <row r="762" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A762" s="76"/>
+      <c r="A762" s="77"/>
       <c r="C762" t="s">
         <v>606</v>
       </c>
@@ -17807,7 +17807,7 @@
       </c>
     </row>
     <row r="763" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A763" s="76"/>
+      <c r="A763" s="77"/>
       <c r="C763" t="s">
         <v>607</v>
       </c>
@@ -17817,7 +17817,7 @@
       </c>
     </row>
     <row r="764" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A764" s="76"/>
+      <c r="A764" s="77"/>
       <c r="C764" t="s">
         <v>608</v>
       </c>
@@ -17827,7 +17827,7 @@
       </c>
     </row>
     <row r="765" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A765" s="76"/>
+      <c r="A765" s="77"/>
       <c r="C765" t="s">
         <v>609</v>
       </c>
@@ -17837,7 +17837,7 @@
       </c>
     </row>
     <row r="766" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A766" s="76"/>
+      <c r="A766" s="77"/>
       <c r="B766" t="s">
         <v>716</v>
       </c>
@@ -18014,7 +18014,7 @@
       </c>
     </row>
     <row r="781" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A781" s="76" t="s">
+      <c r="A781" s="77" t="s">
         <v>610</v>
       </c>
       <c r="C781" t="s">
@@ -18045,7 +18045,7 @@
       </c>
     </row>
     <row r="782" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A782" s="76"/>
+      <c r="A782" s="77"/>
       <c r="C782" t="s">
         <v>612</v>
       </c>
@@ -18072,7 +18072,7 @@
       </c>
     </row>
     <row r="783" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A783" s="76"/>
+      <c r="A783" s="77"/>
       <c r="C783" t="s">
         <v>613</v>
       </c>
@@ -18099,7 +18099,7 @@
       </c>
     </row>
     <row r="784" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A784" s="76"/>
+      <c r="A784" s="77"/>
       <c r="C784" t="s">
         <v>621</v>
       </c>
@@ -18133,7 +18133,7 @@
       </c>
     </row>
     <row r="785" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A785" s="76"/>
+      <c r="A785" s="77"/>
       <c r="C785" t="s">
         <v>622</v>
       </c>
@@ -18163,7 +18163,7 @@
       </c>
     </row>
     <row r="786" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A786" s="76"/>
+      <c r="A786" s="77"/>
       <c r="C786" t="s">
         <v>620</v>
       </c>
@@ -18184,7 +18184,7 @@
       </c>
     </row>
     <row r="787" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A787" s="76"/>
+      <c r="A787" s="77"/>
       <c r="C787" t="s">
         <v>625</v>
       </c>
@@ -18210,7 +18210,7 @@
       </c>
     </row>
     <row r="788" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A788" s="76"/>
+      <c r="A788" s="77"/>
       <c r="C788" t="s">
         <v>624</v>
       </c>
@@ -18236,7 +18236,7 @@
       </c>
     </row>
     <row r="789" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A789" s="76"/>
+      <c r="A789" s="77"/>
       <c r="C789" t="s">
         <v>619</v>
       </c>
@@ -18257,7 +18257,7 @@
       </c>
     </row>
     <row r="790" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A790" s="76"/>
+      <c r="A790" s="77"/>
       <c r="C790" t="s">
         <v>194</v>
       </c>
@@ -18283,7 +18283,7 @@
       </c>
     </row>
     <row r="791" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A791" s="76"/>
+      <c r="A791" s="77"/>
       <c r="C791" t="s">
         <v>623</v>
       </c>
@@ -18309,7 +18309,7 @@
       </c>
     </row>
     <row r="792" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A792" s="76"/>
+      <c r="A792" s="77"/>
       <c r="C792" t="s">
         <v>626</v>
       </c>
@@ -18335,7 +18335,7 @@
       </c>
     </row>
     <row r="793" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A793" s="76"/>
+      <c r="A793" s="77"/>
     </row>
     <row r="794" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A794" s="37"/>
@@ -18344,7 +18344,7 @@
       <c r="A795" s="37"/>
     </row>
     <row r="799" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A799" s="75" t="s">
+      <c r="A799" s="76" t="s">
         <v>699</v>
       </c>
       <c r="C799" t="s">
@@ -18355,7 +18355,7 @@
       </c>
     </row>
     <row r="800" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A800" s="75"/>
+      <c r="A800" s="76"/>
       <c r="C800" t="s">
         <v>1069</v>
       </c>
@@ -18364,7 +18364,7 @@
       </c>
     </row>
     <row r="801" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A801" s="75"/>
+      <c r="A801" s="76"/>
       <c r="C801" t="s">
         <v>1070</v>
       </c>
@@ -18374,7 +18374,7 @@
       </c>
     </row>
     <row r="802" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A802" s="75"/>
+      <c r="A802" s="76"/>
       <c r="C802" t="s">
         <v>1072</v>
       </c>
@@ -18383,7 +18383,7 @@
       </c>
     </row>
     <row r="803" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A803" s="75"/>
+      <c r="A803" s="76"/>
       <c r="C803" t="s">
         <v>1071</v>
       </c>
@@ -18392,7 +18392,7 @@
       </c>
     </row>
     <row r="804" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A804" s="75"/>
+      <c r="A804" s="76"/>
       <c r="C804" t="s">
         <v>1074</v>
       </c>
@@ -18401,7 +18401,7 @@
       </c>
     </row>
     <row r="805" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A805" s="75"/>
+      <c r="A805" s="76"/>
       <c r="C805" t="s">
         <v>1076</v>
       </c>
@@ -18411,7 +18411,7 @@
       </c>
     </row>
     <row r="806" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A806" s="75"/>
+      <c r="A806" s="76"/>
       <c r="C806" t="s">
         <v>1075</v>
       </c>
@@ -18421,7 +18421,7 @@
       </c>
     </row>
     <row r="807" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A807" s="75"/>
+      <c r="A807" s="76"/>
       <c r="C807" t="s">
         <v>1073</v>
       </c>
@@ -18431,7 +18431,7 @@
       </c>
     </row>
     <row r="808" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A808" s="75"/>
+      <c r="A808" s="76"/>
       <c r="C808" t="s">
         <v>700</v>
       </c>
@@ -18440,7 +18440,7 @@
       </c>
     </row>
     <row r="809" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A809" s="75"/>
+      <c r="A809" s="76"/>
       <c r="C809" t="s">
         <v>1079</v>
       </c>
@@ -18450,7 +18450,7 @@
       </c>
     </row>
     <row r="810" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A810" s="75"/>
+      <c r="A810" s="76"/>
       <c r="C810" t="s">
         <v>212</v>
       </c>
@@ -18460,7 +18460,7 @@
       </c>
     </row>
     <row r="811" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A811" s="75"/>
+      <c r="A811" s="76"/>
       <c r="C811" t="s">
         <v>701</v>
       </c>
@@ -18470,7 +18470,7 @@
       </c>
     </row>
     <row r="812" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A812" s="75"/>
+      <c r="A812" s="76"/>
       <c r="C812" t="s">
         <v>702</v>
       </c>
@@ -18480,7 +18480,7 @@
       </c>
     </row>
     <row r="813" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A813" s="75"/>
+      <c r="A813" s="76"/>
       <c r="C813" t="s">
         <v>739</v>
       </c>
@@ -18490,7 +18490,7 @@
       </c>
     </row>
     <row r="814" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A814" s="75"/>
+      <c r="A814" s="76"/>
       <c r="C814" t="s">
         <v>703</v>
       </c>
@@ -18503,7 +18503,7 @@
       </c>
     </row>
     <row r="815" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A815" s="75"/>
+      <c r="A815" s="76"/>
       <c r="C815" t="s">
         <v>704</v>
       </c>
@@ -18513,7 +18513,7 @@
       </c>
     </row>
     <row r="816" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A816" s="75"/>
+      <c r="A816" s="76"/>
       <c r="C816" t="s">
         <v>1078</v>
       </c>
@@ -18523,7 +18523,7 @@
       </c>
     </row>
     <row r="817" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A817" s="75"/>
+      <c r="A817" s="76"/>
       <c r="C817" t="s">
         <v>1077</v>
       </c>
@@ -18533,7 +18533,7 @@
       </c>
     </row>
     <row r="818" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A818" s="75"/>
+      <c r="A818" s="76"/>
       <c r="C818" t="s">
         <v>705</v>
       </c>
@@ -18543,7 +18543,7 @@
       </c>
     </row>
     <row r="819" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A819" s="75"/>
+      <c r="A819" s="76"/>
       <c r="C819" t="s">
         <v>706</v>
       </c>
@@ -18553,7 +18553,7 @@
       </c>
     </row>
     <row r="821" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A821" s="75" t="s">
+      <c r="A821" s="76" t="s">
         <v>699</v>
       </c>
       <c r="C821" t="s">
@@ -18564,7 +18564,7 @@
       </c>
     </row>
     <row r="822" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A822" s="75"/>
+      <c r="A822" s="76"/>
       <c r="C822" t="s">
         <v>1069</v>
       </c>
@@ -18573,7 +18573,7 @@
       </c>
     </row>
     <row r="823" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A823" s="75"/>
+      <c r="A823" s="76"/>
       <c r="C823" t="s">
         <v>1070</v>
       </c>
@@ -18583,7 +18583,7 @@
       </c>
     </row>
     <row r="824" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A824" s="75"/>
+      <c r="A824" s="76"/>
       <c r="C824" t="s">
         <v>1072</v>
       </c>
@@ -18592,7 +18592,7 @@
       </c>
     </row>
     <row r="825" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A825" s="75"/>
+      <c r="A825" s="76"/>
       <c r="C825" t="s">
         <v>1071</v>
       </c>
@@ -18601,7 +18601,7 @@
       </c>
     </row>
     <row r="826" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A826" s="75"/>
+      <c r="A826" s="76"/>
       <c r="C826" t="s">
         <v>1074</v>
       </c>
@@ -18610,7 +18610,7 @@
       </c>
     </row>
     <row r="827" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A827" s="75"/>
+      <c r="A827" s="76"/>
       <c r="C827" t="s">
         <v>1076</v>
       </c>
@@ -18620,7 +18620,7 @@
       </c>
     </row>
     <row r="828" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A828" s="75"/>
+      <c r="A828" s="76"/>
       <c r="C828" t="s">
         <v>1075</v>
       </c>
@@ -18630,7 +18630,7 @@
       </c>
     </row>
     <row r="829" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A829" s="75"/>
+      <c r="A829" s="76"/>
       <c r="C829" t="s">
         <v>1073</v>
       </c>
@@ -18640,7 +18640,7 @@
       </c>
     </row>
     <row r="830" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A830" s="75"/>
+      <c r="A830" s="76"/>
       <c r="C830" t="s">
         <v>700</v>
       </c>
@@ -18649,7 +18649,7 @@
       </c>
     </row>
     <row r="831" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A831" s="75"/>
+      <c r="A831" s="76"/>
       <c r="C831" t="s">
         <v>1079</v>
       </c>
@@ -18659,7 +18659,7 @@
       </c>
     </row>
     <row r="832" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A832" s="75"/>
+      <c r="A832" s="76"/>
       <c r="C832" t="s">
         <v>212</v>
       </c>
@@ -18669,7 +18669,7 @@
       </c>
     </row>
     <row r="833" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A833" s="75"/>
+      <c r="A833" s="76"/>
       <c r="C833" t="s">
         <v>701</v>
       </c>
@@ -18679,7 +18679,7 @@
       </c>
     </row>
     <row r="834" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A834" s="75"/>
+      <c r="A834" s="76"/>
       <c r="C834" t="s">
         <v>702</v>
       </c>
@@ -18689,7 +18689,7 @@
       </c>
     </row>
     <row r="835" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A835" s="75"/>
+      <c r="A835" s="76"/>
       <c r="C835" t="s">
         <v>739</v>
       </c>
@@ -18699,7 +18699,7 @@
       </c>
     </row>
     <row r="836" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A836" s="75"/>
+      <c r="A836" s="76"/>
       <c r="C836" t="s">
         <v>703</v>
       </c>
@@ -18709,7 +18709,7 @@
       </c>
     </row>
     <row r="837" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A837" s="75"/>
+      <c r="A837" s="76"/>
       <c r="C837" t="s">
         <v>704</v>
       </c>
@@ -18719,7 +18719,7 @@
       </c>
     </row>
     <row r="838" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A838" s="75"/>
+      <c r="A838" s="76"/>
       <c r="C838" t="s">
         <v>1078</v>
       </c>
@@ -18729,7 +18729,7 @@
       </c>
     </row>
     <row r="839" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A839" s="75"/>
+      <c r="A839" s="76"/>
       <c r="C839" t="s">
         <v>1077</v>
       </c>
@@ -18739,7 +18739,7 @@
       </c>
     </row>
     <row r="840" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A840" s="75"/>
+      <c r="A840" s="76"/>
       <c r="C840" t="s">
         <v>705</v>
       </c>
@@ -18749,7 +18749,7 @@
       </c>
     </row>
     <row r="841" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A841" s="75"/>
+      <c r="A841" s="76"/>
       <c r="C841" t="s">
         <v>706</v>
       </c>
@@ -18771,7 +18771,7 @@
       </c>
     </row>
     <row r="844" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A844" s="76" t="s">
+      <c r="A844" s="77" t="s">
         <v>707</v>
       </c>
       <c r="C844" t="s">
@@ -18785,7 +18785,7 @@
       </c>
     </row>
     <row r="845" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A845" s="76"/>
+      <c r="A845" s="77"/>
       <c r="C845" t="s">
         <v>710</v>
       </c>
@@ -18795,7 +18795,7 @@
       </c>
     </row>
     <row r="846" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A846" s="76"/>
+      <c r="A846" s="77"/>
       <c r="C846" t="s">
         <v>712</v>
       </c>
@@ -18808,7 +18808,7 @@
       </c>
     </row>
     <row r="847" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A847" s="76"/>
+      <c r="A847" s="77"/>
       <c r="C847" t="s">
         <v>713</v>
       </c>
@@ -18818,31 +18818,31 @@
       </c>
     </row>
     <row r="848" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A848" s="76"/>
+      <c r="A848" s="77"/>
     </row>
     <row r="849" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A849" s="76"/>
+      <c r="A849" s="77"/>
     </row>
     <row r="850" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A850" s="76"/>
+      <c r="A850" s="77"/>
     </row>
     <row r="851" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A851" s="76"/>
+      <c r="A851" s="77"/>
     </row>
     <row r="852" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A852" s="76"/>
+      <c r="A852" s="77"/>
     </row>
     <row r="853" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A853" s="76"/>
+      <c r="A853" s="77"/>
     </row>
     <row r="854" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A854" s="76"/>
+      <c r="A854" s="77"/>
     </row>
     <row r="855" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A855" s="76"/>
+      <c r="A855" s="77"/>
     </row>
     <row r="856" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A856" s="76"/>
+      <c r="A856" s="77"/>
     </row>
     <row r="857" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C857" t="s">
@@ -18854,7 +18854,7 @@
       </c>
     </row>
     <row r="858" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A858" s="76" t="s">
+      <c r="A858" s="77" t="s">
         <v>740</v>
       </c>
       <c r="C858" t="s">
@@ -18866,7 +18866,7 @@
       </c>
     </row>
     <row r="859" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A859" s="76"/>
+      <c r="A859" s="77"/>
       <c r="C859" t="s">
         <v>743</v>
       </c>
@@ -18876,7 +18876,7 @@
       </c>
     </row>
     <row r="860" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A860" s="76"/>
+      <c r="A860" s="77"/>
       <c r="C860" t="s">
         <v>744</v>
       </c>
@@ -18886,13 +18886,13 @@
       </c>
     </row>
     <row r="861" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A861" s="76"/>
+      <c r="A861" s="77"/>
     </row>
     <row r="862" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A862" s="76"/>
+      <c r="A862" s="77"/>
     </row>
     <row r="863" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A863" s="76"/>
+      <c r="A863" s="77"/>
       <c r="C863" t="s">
         <v>4</v>
       </c>
@@ -18901,7 +18901,7 @@
       </c>
     </row>
     <row r="864" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A864" s="76"/>
+      <c r="A864" s="77"/>
       <c r="C864" t="s">
         <v>629</v>
       </c>
@@ -18913,7 +18913,7 @@
       </c>
     </row>
     <row r="865" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A865" s="76"/>
+      <c r="A865" s="77"/>
       <c r="C865" t="s">
         <v>630</v>
       </c>
@@ -18925,7 +18925,7 @@
       </c>
     </row>
     <row r="866" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A866" s="76"/>
+      <c r="A866" s="77"/>
       <c r="C866" t="s">
         <v>627</v>
       </c>
@@ -18938,7 +18938,7 @@
       </c>
     </row>
     <row r="867" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A867" s="76"/>
+      <c r="A867" s="77"/>
       <c r="C867" t="s">
         <v>631</v>
       </c>
@@ -18948,7 +18948,7 @@
       </c>
     </row>
     <row r="868" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A868" s="76"/>
+      <c r="A868" s="77"/>
       <c r="C868" t="s">
         <v>636</v>
       </c>
@@ -18960,7 +18960,7 @@
       </c>
     </row>
     <row r="869" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A869" s="76"/>
+      <c r="A869" s="77"/>
       <c r="C869" t="s">
         <v>633</v>
       </c>
@@ -18972,7 +18972,7 @@
       </c>
     </row>
     <row r="870" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A870" s="76"/>
+      <c r="A870" s="77"/>
       <c r="C870" t="s">
         <v>635</v>
       </c>
@@ -18984,7 +18984,7 @@
       </c>
     </row>
     <row r="871" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A871" s="76"/>
+      <c r="A871" s="77"/>
       <c r="C871" t="s">
         <v>639</v>
       </c>
@@ -18997,7 +18997,7 @@
       </c>
     </row>
     <row r="872" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A872" s="76"/>
+      <c r="A872" s="77"/>
       <c r="C872" t="s">
         <v>641</v>
       </c>
@@ -19010,7 +19010,7 @@
       </c>
     </row>
     <row r="873" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A873" s="76"/>
+      <c r="A873" s="77"/>
       <c r="C873" t="s">
         <v>643</v>
       </c>
@@ -19023,7 +19023,7 @@
       </c>
     </row>
     <row r="874" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A874" s="76"/>
+      <c r="A874" s="77"/>
       <c r="C874" t="s">
         <v>644</v>
       </c>
@@ -19036,7 +19036,7 @@
       </c>
     </row>
     <row r="875" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A875" s="76"/>
+      <c r="A875" s="77"/>
       <c r="C875" t="s">
         <v>645</v>
       </c>
@@ -19049,7 +19049,7 @@
       </c>
     </row>
     <row r="876" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A876" s="76"/>
+      <c r="A876" s="77"/>
       <c r="C876" t="s">
         <v>645</v>
       </c>
@@ -19062,7 +19062,7 @@
       </c>
     </row>
     <row r="877" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A877" s="76"/>
+      <c r="A877" s="77"/>
       <c r="C877" t="s">
         <v>648</v>
       </c>
@@ -19074,7 +19074,7 @@
       </c>
     </row>
     <row r="878" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A878" s="76"/>
+      <c r="A878" s="77"/>
       <c r="C878" t="s">
         <v>650</v>
       </c>
@@ -19087,7 +19087,7 @@
       </c>
     </row>
     <row r="879" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A879" s="76"/>
+      <c r="A879" s="77"/>
       <c r="C879" t="s">
         <v>651</v>
       </c>
@@ -19100,7 +19100,7 @@
       </c>
     </row>
     <row r="880" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A880" s="76"/>
+      <c r="A880" s="77"/>
       <c r="C880" t="s">
         <v>653</v>
       </c>
@@ -19113,7 +19113,7 @@
       </c>
     </row>
     <row r="881" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A881" s="76"/>
+      <c r="A881" s="77"/>
       <c r="C881" t="s">
         <v>652</v>
       </c>
@@ -19126,7 +19126,7 @@
       </c>
     </row>
     <row r="882" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A882" s="76"/>
+      <c r="A882" s="77"/>
       <c r="C882" t="s">
         <v>658</v>
       </c>
@@ -19138,7 +19138,7 @@
       </c>
     </row>
     <row r="883" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A883" s="76"/>
+      <c r="A883" s="77"/>
       <c r="C883" t="s">
         <v>659</v>
       </c>
@@ -19207,7 +19207,7 @@
       </c>
     </row>
     <row r="892" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A892" s="76" t="s">
+      <c r="A892" s="77" t="s">
         <v>761</v>
       </c>
       <c r="B892" t="s">
@@ -19225,7 +19225,7 @@
       </c>
     </row>
     <row r="893" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A893" s="76"/>
+      <c r="A893" s="77"/>
       <c r="B893" t="s">
         <v>38</v>
       </c>
@@ -19241,7 +19241,7 @@
       </c>
     </row>
     <row r="894" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A894" s="76"/>
+      <c r="A894" s="77"/>
       <c r="C894" t="s">
         <v>762</v>
       </c>
@@ -19253,7 +19253,7 @@
       </c>
     </row>
     <row r="895" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A895" s="76"/>
+      <c r="A895" s="77"/>
       <c r="C895" t="s">
         <v>763</v>
       </c>
@@ -19263,7 +19263,7 @@
       </c>
     </row>
     <row r="896" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A896" s="76"/>
+      <c r="A896" s="77"/>
       <c r="C896" t="s">
         <v>764</v>
       </c>
@@ -19273,7 +19273,7 @@
       </c>
     </row>
     <row r="897" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A897" s="76"/>
+      <c r="A897" s="77"/>
       <c r="C897" t="s">
         <v>765</v>
       </c>
@@ -19283,7 +19283,7 @@
       </c>
     </row>
     <row r="898" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A898" s="76"/>
+      <c r="A898" s="77"/>
       <c r="C898" t="s">
         <v>766</v>
       </c>
@@ -19293,7 +19293,7 @@
       </c>
     </row>
     <row r="899" spans="1:15" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A899" s="76"/>
+      <c r="A899" s="77"/>
       <c r="C899" t="s">
         <v>767</v>
       </c>
@@ -19328,7 +19328,7 @@
       <c r="O899" s="42"/>
     </row>
     <row r="900" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A900" s="76"/>
+      <c r="A900" s="77"/>
       <c r="C900" t="s">
         <v>768</v>
       </c>
@@ -19366,7 +19366,7 @@
       <c r="N900" s="42"/>
     </row>
     <row r="901" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A901" s="76"/>
+      <c r="A901" s="77"/>
       <c r="C901" t="s">
         <v>769</v>
       </c>
@@ -19403,7 +19403,7 @@
       <c r="N901" s="42"/>
     </row>
     <row r="902" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A902" s="76"/>
+      <c r="A902" s="77"/>
       <c r="C902" t="s">
         <v>770</v>
       </c>
@@ -19440,7 +19440,7 @@
       </c>
     </row>
     <row r="903" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A903" s="76"/>
+      <c r="A903" s="77"/>
       <c r="G903" s="17">
         <v>4</v>
       </c>
@@ -19470,7 +19470,7 @@
       </c>
     </row>
     <row r="904" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A904" s="76"/>
+      <c r="A904" s="77"/>
       <c r="C904" t="s">
         <v>771</v>
       </c>
@@ -19510,7 +19510,7 @@
       </c>
     </row>
     <row r="905" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A905" s="76"/>
+      <c r="A905" s="77"/>
       <c r="C905" t="s">
         <v>772</v>
       </c>
@@ -19550,7 +19550,7 @@
       </c>
     </row>
     <row r="906" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A906" s="76"/>
+      <c r="A906" s="77"/>
       <c r="G906" s="17">
         <v>7</v>
       </c>
@@ -19679,7 +19679,7 @@
       </c>
     </row>
     <row r="910" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A910" s="76" t="s">
+      <c r="A910" s="77" t="s">
         <v>869</v>
       </c>
       <c r="B910" t="s">
@@ -19726,7 +19726,7 @@
       </c>
     </row>
     <row r="911" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A911" s="76"/>
+      <c r="A911" s="77"/>
       <c r="B911" t="s">
         <v>857</v>
       </c>
@@ -19772,7 +19772,7 @@
       </c>
     </row>
     <row r="912" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A912" s="76"/>
+      <c r="A912" s="77"/>
       <c r="B912" t="s">
         <v>856</v>
       </c>
@@ -19873,7 +19873,7 @@
       </c>
     </row>
     <row r="915" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A915" s="76" t="s">
+      <c r="A915" s="77" t="s">
         <v>870</v>
       </c>
       <c r="B915" t="s">
@@ -19890,7 +19890,7 @@
       </c>
     </row>
     <row r="916" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A916" s="76"/>
+      <c r="A916" s="77"/>
       <c r="B916" t="s">
         <v>857</v>
       </c>
@@ -19906,7 +19906,7 @@
       </c>
     </row>
     <row r="917" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A917" s="76"/>
+      <c r="A917" s="77"/>
       <c r="B917" t="s">
         <v>856</v>
       </c>
@@ -19937,7 +19937,7 @@
       </c>
     </row>
     <row r="920" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A920" s="76" t="s">
+      <c r="A920" s="77" t="s">
         <v>873</v>
       </c>
       <c r="B920" t="s">
@@ -19954,7 +19954,7 @@
       </c>
     </row>
     <row r="921" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A921" s="76"/>
+      <c r="A921" s="77"/>
       <c r="B921" t="s">
         <v>857</v>
       </c>
@@ -19970,7 +19970,7 @@
       </c>
     </row>
     <row r="922" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A922" s="76"/>
+      <c r="A922" s="77"/>
       <c r="B922" t="s">
         <v>856</v>
       </c>
@@ -20001,7 +20001,7 @@
       </c>
     </row>
     <row r="925" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A925" s="76" t="s">
+      <c r="A925" s="77" t="s">
         <v>871</v>
       </c>
       <c r="B925" t="s">
@@ -20018,7 +20018,7 @@
       </c>
     </row>
     <row r="926" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A926" s="76"/>
+      <c r="A926" s="77"/>
       <c r="B926" t="s">
         <v>862</v>
       </c>
@@ -20033,7 +20033,7 @@
       </c>
     </row>
     <row r="927" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A927" s="76"/>
+      <c r="A927" s="77"/>
       <c r="B927" t="s">
         <v>857</v>
       </c>
@@ -20049,7 +20049,7 @@
       </c>
     </row>
     <row r="928" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A928" s="76"/>
+      <c r="A928" s="77"/>
       <c r="B928" t="s">
         <v>867</v>
       </c>
@@ -20064,8 +20064,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="929" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A929" s="76"/>
+    <row r="929" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A929" s="77"/>
       <c r="B929" t="s">
         <v>866</v>
       </c>
@@ -20080,8 +20080,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="930" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A930" s="76"/>
+    <row r="930" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A930" s="77"/>
       <c r="B930" t="s">
         <v>868</v>
       </c>
@@ -20096,8 +20096,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="932" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A932" s="76" t="s">
+    <row r="932" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A932" s="77" t="s">
         <v>872</v>
       </c>
       <c r="B932" t="s">
@@ -20113,8 +20113,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="933" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A933" s="76"/>
+    <row r="933" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A933" s="77"/>
       <c r="B933" t="s">
         <v>862</v>
       </c>
@@ -20128,8 +20128,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="934" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A934" s="76"/>
+    <row r="934" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A934" s="77"/>
       <c r="B934" t="s">
         <v>857</v>
       </c>
@@ -20144,8 +20144,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="935" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A935" s="76"/>
+    <row r="935" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A935" s="77"/>
       <c r="B935" t="s">
         <v>867</v>
       </c>
@@ -20160,8 +20160,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="936" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A936" s="76"/>
+    <row r="936" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A936" s="77"/>
       <c r="B936" t="s">
         <v>866</v>
       </c>
@@ -20176,8 +20176,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="937" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A937" s="76"/>
+    <row r="937" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A937" s="77"/>
       <c r="B937" t="s">
         <v>868</v>
       </c>
@@ -20192,464 +20192,475 @@
         <v>23</v>
       </c>
     </row>
-    <row r="940" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A940" s="75" t="s">
+    <row r="946" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A946" s="76" t="s">
         <v>1085</v>
       </c>
-      <c r="C940" t="s">
+      <c r="C946" t="s">
         <v>1097</v>
       </c>
-      <c r="E940" t="s">
+      <c r="E946" t="s">
         <v>1098</v>
       </c>
-      <c r="G940" t="s">
+      <c r="G946" t="s">
         <v>1099</v>
       </c>
     </row>
-    <row r="941" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A941" s="75"/>
-      <c r="B941" t="s">
+    <row r="947" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A947" s="76"/>
+      <c r="B947" t="s">
         <v>1086</v>
       </c>
-      <c r="E941">
+      <c r="E947">
         <f>PI()*0.0000004</f>
         <v>1.2566370614359173E-6</v>
       </c>
-      <c r="F941" s="8" t="s">
+      <c r="F947" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="G941">
-        <f t="shared" ref="G941:N941" si="86">$E941</f>
+      <c r="G947">
+        <f t="shared" ref="G947:N947" si="86">$E947</f>
         <v>1.2566370614359173E-6</v>
       </c>
-      <c r="H941">
+      <c r="H947">
         <f t="shared" si="86"/>
         <v>1.2566370614359173E-6</v>
       </c>
-      <c r="I941">
+      <c r="I947">
         <f t="shared" si="86"/>
         <v>1.2566370614359173E-6</v>
       </c>
-      <c r="J941">
+      <c r="J947">
         <f t="shared" si="86"/>
         <v>1.2566370614359173E-6</v>
       </c>
-      <c r="K941">
+      <c r="K947">
         <f t="shared" si="86"/>
         <v>1.2566370614359173E-6</v>
       </c>
-      <c r="L941">
+      <c r="L947">
         <f t="shared" si="86"/>
         <v>1.2566370614359173E-6</v>
       </c>
-      <c r="M941">
+      <c r="M947">
         <f t="shared" si="86"/>
         <v>1.2566370614359173E-6</v>
       </c>
-      <c r="N941">
+      <c r="N947">
         <f t="shared" si="86"/>
         <v>1.2566370614359173E-6</v>
       </c>
     </row>
-    <row r="942" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A942" s="75"/>
-      <c r="B942" t="s">
+    <row r="948" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A948" s="76"/>
+      <c r="B948" t="s">
         <v>1087</v>
       </c>
-      <c r="C942" t="s">
+      <c r="C948" t="s">
         <v>1133</v>
       </c>
-      <c r="E942">
+      <c r="E948">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="F942" s="8" t="s">
+      <c r="F948" s="8" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="943" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A943" s="75"/>
-      <c r="B943" t="s">
+    <row r="949" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A949" s="76"/>
+      <c r="B949" t="s">
         <v>135</v>
       </c>
-      <c r="C943" t="s">
+      <c r="C949" t="s">
         <v>1132</v>
       </c>
-      <c r="E943">
+      <c r="E949">
         <v>0.04</v>
       </c>
-      <c r="F943" s="8" t="s">
+      <c r="F949" s="8" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="944" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A944" s="75"/>
-      <c r="C944" t="s">
+    <row r="950" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A950" s="76"/>
+      <c r="C950" t="s">
         <v>1134</v>
       </c>
-      <c r="E944">
-        <f>2*E942/E943</f>
+      <c r="E950">
+        <f>2*E948/E949</f>
         <v>0.3</v>
       </c>
-      <c r="F944" s="8"/>
-    </row>
-    <row r="945" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A945" s="75"/>
-      <c r="C945" t="s">
+      <c r="F950" s="8"/>
+    </row>
+    <row r="951" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A951" s="76"/>
+      <c r="C951" t="s">
         <v>1135</v>
       </c>
-      <c r="E945">
-        <f>1/E944</f>
+      <c r="E951">
+        <f>1/E950</f>
         <v>3.3333333333333335</v>
       </c>
-      <c r="F945" s="8"/>
-    </row>
-    <row r="946" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A946" s="75"/>
-      <c r="C946" t="s">
+      <c r="F951" s="8"/>
+    </row>
+    <row r="952" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A952" s="76"/>
+      <c r="C952" t="s">
         <v>1136</v>
       </c>
-      <c r="E946">
-        <f>POWER(E944, 2)</f>
+      <c r="E952">
+        <f>POWER(E950, 2)</f>
         <v>0.09</v>
       </c>
-      <c r="F946" s="8"/>
-    </row>
-    <row r="947" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A947" s="75"/>
-      <c r="C947" t="s">
+      <c r="F952" s="8"/>
+    </row>
+    <row r="953" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A953" s="76"/>
+      <c r="C953" t="s">
         <v>1137</v>
       </c>
-      <c r="E947">
-        <f>1/E946</f>
+      <c r="E953">
+        <f>1/E952</f>
         <v>11.111111111111111</v>
       </c>
-      <c r="F947" s="8"/>
-    </row>
-    <row r="948" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A948" s="75"/>
-      <c r="F948" s="8"/>
-    </row>
-    <row r="949" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A949" s="75"/>
-      <c r="B949" t="s">
+      <c r="F953" s="8"/>
+    </row>
+    <row r="954" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A954" s="76"/>
+      <c r="F954" s="8"/>
+    </row>
+    <row r="955" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A955" s="76"/>
+      <c r="B955" t="s">
         <v>1089</v>
       </c>
-      <c r="C949" t="s">
+      <c r="C955" t="s">
         <v>1090</v>
       </c>
-      <c r="E949">
-        <f>(E941/(4*PI()))*(LN(E944+SQRT(1+E946)) - SQRT(1+E947)+E945)</f>
+      <c r="E955">
+        <f>(E947/(4*PI()))*(LN(E950+SQRT(1+E952)) - SQRT(1+E953)+E951)</f>
         <v>1.4890421125990595E-8</v>
       </c>
-      <c r="F949" t="s">
+      <c r="F955" t="s">
         <v>154</v>
       </c>
-      <c r="G949">
-        <f t="shared" ref="G949:N949" si="87">(G941/(4*PI()))*(LN(G944+SQRT(1+G946)) - SQRT(1+G947)+G945)</f>
+      <c r="G955">
+        <f t="shared" ref="G955:N955" si="87">(G947/(4*PI()))*(LN(G950+SQRT(1+G952)) - SQRT(1+G953)+G951)</f>
         <v>-1.0000000000000001E-7</v>
       </c>
-      <c r="H949">
+      <c r="H955">
         <f t="shared" si="87"/>
         <v>-1.0000000000000001E-7</v>
       </c>
-      <c r="I949">
+      <c r="I955">
         <f t="shared" si="87"/>
         <v>-1.0000000000000001E-7</v>
       </c>
-      <c r="J949">
+      <c r="J955">
         <f t="shared" si="87"/>
         <v>-1.0000000000000001E-7</v>
       </c>
-      <c r="K949">
+      <c r="K955">
         <f t="shared" si="87"/>
         <v>-1.0000000000000001E-7</v>
       </c>
-      <c r="L949">
+      <c r="L955">
         <f t="shared" si="87"/>
         <v>-1.0000000000000001E-7</v>
       </c>
-      <c r="M949">
+      <c r="M955">
         <f t="shared" si="87"/>
         <v>-1.0000000000000001E-7</v>
       </c>
-      <c r="N949">
+      <c r="N955">
         <f t="shared" si="87"/>
         <v>-1.0000000000000001E-7</v>
       </c>
     </row>
-    <row r="950" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A950" s="75"/>
-      <c r="B950" t="s">
+    <row r="956" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A956" s="76"/>
+      <c r="B956" t="s">
         <v>1091</v>
       </c>
-      <c r="C950" t="s">
+      <c r="C956" t="s">
         <v>1092</v>
       </c>
-      <c r="E950">
+      <c r="E956">
         <f>22*16000*4</f>
         <v>1408000</v>
       </c>
     </row>
-    <row r="951" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A951" s="75"/>
-      <c r="B951" s="74" t="s">
+    <row r="957" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A957" s="76"/>
+      <c r="B957" s="74" t="s">
         <v>1095</v>
       </c>
-      <c r="C951" t="s">
+      <c r="C957" t="s">
         <v>1096</v>
       </c>
-      <c r="E951">
+      <c r="E957">
         <v>0</v>
       </c>
-      <c r="F951">
+      <c r="F957">
         <v>0</v>
       </c>
-      <c r="G951">
+      <c r="G957">
         <v>0</v>
       </c>
-      <c r="H951">
+      <c r="H957">
         <v>0</v>
       </c>
-      <c r="I951">
+      <c r="I957">
         <v>0</v>
       </c>
-      <c r="J951">
+      <c r="J957">
         <v>0</v>
       </c>
-      <c r="K951">
+      <c r="K957">
         <v>0</v>
       </c>
-      <c r="L951">
+      <c r="L957">
         <v>0</v>
       </c>
-      <c r="M951">
+      <c r="M957">
         <v>0</v>
       </c>
-      <c r="N951">
+      <c r="N957">
         <v>0</v>
       </c>
     </row>
-    <row r="952" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A952" s="75"/>
-      <c r="B952" t="s">
+    <row r="958" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A958" s="76"/>
+      <c r="B958" t="s">
         <v>1094</v>
       </c>
-      <c r="C952" t="s">
+      <c r="C958" t="s">
         <v>1093</v>
       </c>
-      <c r="E952">
-        <f>E950*COS(E951)*E949</f>
+      <c r="E958">
+        <f>E956*COS(E957)*E955</f>
         <v>2.096571294539476E-2</v>
       </c>
-      <c r="F952" t="e">
-        <f t="shared" ref="F952:N952" si="88">F950*COS(F951)*F949</f>
+      <c r="F958" t="e">
+        <f t="shared" ref="F958:N958" si="88">F956*COS(F957)*F955</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G952">
+      <c r="G958">
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
-      <c r="H952">
+      <c r="H958">
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
-      <c r="I952">
+      <c r="I958">
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
-      <c r="J952">
+      <c r="J958">
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
-      <c r="K952">
+      <c r="K958">
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
-      <c r="L952">
+      <c r="L958">
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
-      <c r="M952">
+      <c r="M958">
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
-      <c r="N952">
+      <c r="N958">
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
     </row>
-    <row r="953" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A953" s="37"/>
-    </row>
-    <row r="954" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A954" s="75" t="s">
+    <row r="959" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A959" s="37"/>
+    </row>
+    <row r="960" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A960" s="76" t="s">
         <v>1107</v>
       </c>
-      <c r="B954" t="s">
+      <c r="B960" t="s">
         <v>1108</v>
       </c>
-      <c r="C954" t="s">
+      <c r="C960" t="s">
         <v>1109</v>
       </c>
-      <c r="E954">
+      <c r="E960">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="F954" t="s">
+      <c r="F960" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="955" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A955" s="75"/>
-      <c r="B955" t="s">
+    <row r="961" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A961" s="76"/>
+      <c r="B961" t="s">
         <v>1088</v>
       </c>
-      <c r="C955" t="s">
+      <c r="C961" t="s">
         <v>1110</v>
       </c>
-      <c r="E955">
+      <c r="E961">
         <v>1E-3</v>
       </c>
-      <c r="F955" t="s">
+      <c r="F961" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="956" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A956" s="75"/>
-      <c r="B956" t="s">
+    <row r="962" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A962" s="76"/>
+      <c r="B962" t="s">
         <v>1111</v>
       </c>
-      <c r="C956" t="s">
+      <c r="C962" t="s">
         <v>1112</v>
       </c>
-      <c r="E956">
+      <c r="E962">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="F956" t="s">
+      <c r="F962" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="957" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A957" s="75"/>
-      <c r="B957" t="s">
+    <row r="963" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A963" s="76"/>
+      <c r="B963" t="s">
         <v>1113</v>
       </c>
-      <c r="E957">
-        <f>0.00000000508*E954*(LN(2*E954/(E955+E956))+0.5+(0.2235*(E955+E956)/E954))</f>
+      <c r="E963">
+        <f>0.00000000508*E960*(LN(2*E960/(E961+E962))+0.5+(0.2235*(E961+E962)/E960))</f>
         <v>2.2741325637156556E-10</v>
       </c>
-      <c r="F957" t="s">
+      <c r="F963" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="958" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A958" s="75"/>
-    </row>
-    <row r="959" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A959" s="75"/>
-    </row>
-    <row r="960" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A960" s="75"/>
-    </row>
-    <row r="962" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A962" s="75" t="s">
+    <row r="964" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A964" s="76"/>
+    </row>
+    <row r="965" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A965" s="76"/>
+    </row>
+    <row r="966" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A966" s="76"/>
+    </row>
+    <row r="968" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A968" s="76" t="s">
         <v>1138</v>
       </c>
-      <c r="B962" t="s">
+      <c r="B968" t="s">
         <v>1139</v>
       </c>
-      <c r="C962" t="s">
+      <c r="C968" t="s">
         <v>1139</v>
       </c>
-      <c r="E962" s="52" t="b">
+      <c r="E968" s="52" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="963" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A963" s="75"/>
-      <c r="B963" t="s">
+    <row r="969" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A969" s="76"/>
+      <c r="B969" t="s">
         <v>511</v>
       </c>
-      <c r="E963" s="27">
-        <f>IF(E962, 0.024, 0.048)</f>
+      <c r="E969" s="27">
+        <f>IF(E968, 0.024, 0.048)</f>
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="964" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A964" s="75"/>
-      <c r="B964" t="s">
+    <row r="970" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A970" s="76"/>
+      <c r="B970" t="s">
         <v>1140</v>
       </c>
-      <c r="C964" t="s">
+      <c r="C970" t="s">
         <v>1145</v>
       </c>
-      <c r="E964" s="52">
+      <c r="E970" s="52">
         <f>22/SQRT(3)</f>
         <v>12.701705922171767</v>
       </c>
-      <c r="F964" t="s">
+      <c r="F970" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="965" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A965" s="75"/>
-      <c r="B965" s="74" t="s">
+    <row r="971" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A971" s="76"/>
+      <c r="B971" s="74" t="s">
         <v>693</v>
       </c>
-      <c r="C965" t="s">
+      <c r="C971" t="s">
         <v>1141</v>
       </c>
-      <c r="E965">
+      <c r="E971">
         <v>10</v>
       </c>
-      <c r="F965" t="s">
+      <c r="F971" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="966" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A966" s="75"/>
-      <c r="C966" t="s">
+    <row r="972" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A972" s="76"/>
+      <c r="C972" t="s">
         <v>1144</v>
       </c>
-      <c r="E966">
+      <c r="E972">
         <v>2</v>
       </c>
     </row>
-    <row r="967" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A967" s="75"/>
-      <c r="B967" t="s">
+    <row r="973" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A973" s="76"/>
+      <c r="B973" t="s">
         <v>20</v>
       </c>
-      <c r="C967" t="s">
+      <c r="C973" t="s">
         <v>1142</v>
       </c>
-      <c r="E967">
-        <f>POWER(E964/(E963*POWER(E965, 0.44)), (1/0.725))</f>
+      <c r="E973">
+        <f>POWER(E970/(E969*POWER(E971, 0.44)), (1/0.725))</f>
         <v>542.8119517712156</v>
       </c>
-      <c r="F967" t="s">
+      <c r="F973" t="s">
         <v>1143</v>
       </c>
     </row>
-    <row r="968" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A968" s="75"/>
-      <c r="C968" t="s">
+    <row r="974" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A974" s="76"/>
+      <c r="C974" t="s">
         <v>1146</v>
       </c>
-      <c r="E968">
-        <f>E967/(E966*1.378*39.37)</f>
+      <c r="E974">
+        <f>E973/(E972*1.378*39.37)</f>
         <v>5.0027036102653044</v>
       </c>
-      <c r="F968" t="s">
+      <c r="F974" t="s">
         <v>133</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="G111:K111"/>
-    <mergeCell ref="A99:A136"/>
-    <mergeCell ref="A196:A220"/>
-    <mergeCell ref="A167:A193"/>
-    <mergeCell ref="A138:A164"/>
+    <mergeCell ref="A946:A958"/>
+    <mergeCell ref="A960:A966"/>
+    <mergeCell ref="A968:A974"/>
+    <mergeCell ref="A892:A906"/>
+    <mergeCell ref="A568:A580"/>
+    <mergeCell ref="A581:A584"/>
+    <mergeCell ref="A781:A793"/>
+    <mergeCell ref="A695:A766"/>
+    <mergeCell ref="A653:A692"/>
+    <mergeCell ref="A799:A819"/>
+    <mergeCell ref="A821:A841"/>
+    <mergeCell ref="A910:A912"/>
+    <mergeCell ref="A915:A917"/>
+    <mergeCell ref="A920:A922"/>
+    <mergeCell ref="A925:A930"/>
+    <mergeCell ref="A932:A937"/>
     <mergeCell ref="A31:A59"/>
     <mergeCell ref="A858:A883"/>
     <mergeCell ref="A286:A337"/>
@@ -20666,22 +20677,11 @@
     <mergeCell ref="A844:A856"/>
     <mergeCell ref="A414:A454"/>
     <mergeCell ref="A456:A566"/>
-    <mergeCell ref="A940:A952"/>
-    <mergeCell ref="A954:A960"/>
-    <mergeCell ref="A962:A968"/>
-    <mergeCell ref="A892:A906"/>
-    <mergeCell ref="A568:A580"/>
-    <mergeCell ref="A581:A584"/>
-    <mergeCell ref="A781:A793"/>
-    <mergeCell ref="A695:A766"/>
-    <mergeCell ref="A653:A692"/>
-    <mergeCell ref="A799:A819"/>
-    <mergeCell ref="A821:A841"/>
-    <mergeCell ref="A910:A912"/>
-    <mergeCell ref="A915:A917"/>
-    <mergeCell ref="A920:A922"/>
-    <mergeCell ref="A925:A930"/>
-    <mergeCell ref="A932:A937"/>
+    <mergeCell ref="G111:K111"/>
+    <mergeCell ref="A99:A136"/>
+    <mergeCell ref="A196:A220"/>
+    <mergeCell ref="A167:A193"/>
+    <mergeCell ref="A138:A164"/>
   </mergeCells>
   <conditionalFormatting sqref="D120">
     <cfRule type="cellIs" dxfId="11" priority="11" operator="notEqual">

--- a/Spreadsheets/BasicCalculations.xlsx
+++ b/Spreadsheets/BasicCalculations.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="1147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="1148">
   <si>
     <t>N stages required</t>
   </si>
@@ -3487,6 +3487,9 @@
   </si>
   <si>
     <t>Width</t>
+  </si>
+  <si>
+    <t>Actual ratio</t>
   </si>
 </sst>
 </file>
@@ -3884,9 +3887,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3900,6 +3900,9 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4766,13 +4769,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2514600</xdr:colOff>
-      <xdr:row>951</xdr:row>
+      <xdr:row>952</xdr:row>
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>105079</xdr:colOff>
-      <xdr:row>955</xdr:row>
+      <xdr:row>956</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4804,13 +4807,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3829050</xdr:colOff>
-      <xdr:row>966</xdr:row>
+      <xdr:row>967</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1483610</xdr:colOff>
-      <xdr:row>972</xdr:row>
+      <xdr:row>973</xdr:row>
       <xdr:rowOff>136</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4842,13 +4845,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>3800475</xdr:colOff>
-      <xdr:row>972</xdr:row>
+      <xdr:row>973</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>654823</xdr:colOff>
-      <xdr:row>976</xdr:row>
+      <xdr:row>977</xdr:row>
       <xdr:rowOff>95363</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5768,7 +5771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:CX974"/>
+  <dimension ref="A1:CX975"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" customWidth="1"/>
@@ -6019,15 +6022,15 @@
       <c r="C19" s="7"/>
       <c r="D19" s="12"/>
       <c r="E19" s="7"/>
-      <c r="G19" s="78" t="s">
+      <c r="G19" s="77" t="s">
         <v>569</v>
       </c>
-      <c r="H19" s="78"/>
-      <c r="I19" s="78"/>
-      <c r="J19" s="78"/>
+      <c r="H19" s="77"/>
+      <c r="I19" s="77"/>
+      <c r="J19" s="77"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="76" t="s">
+      <c r="A20" s="75" t="s">
         <v>98</v>
       </c>
       <c r="B20" t="s">
@@ -6042,13 +6045,13 @@
       <c r="E20" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="78"/>
-      <c r="H20" s="78"/>
-      <c r="I20" s="78"/>
-      <c r="J20" s="78"/>
+      <c r="G20" s="77"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="77"/>
+      <c r="J20" s="77"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="76"/>
+      <c r="A21" s="75"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5" t="s">
         <v>3</v>
@@ -6060,13 +6063,13 @@
       <c r="E21" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G21" s="78"/>
-      <c r="H21" s="78"/>
-      <c r="I21" s="78"/>
-      <c r="J21" s="78"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="77"/>
+      <c r="I21" s="77"/>
+      <c r="J21" s="77"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="76"/>
+      <c r="A22" s="75"/>
       <c r="B22" t="s">
         <v>64</v>
       </c>
@@ -6076,13 +6079,13 @@
       <c r="D22">
         <v>0.1</v>
       </c>
-      <c r="G22" s="78"/>
-      <c r="H22" s="78"/>
-      <c r="I22" s="78"/>
-      <c r="J22" s="78"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
+      <c r="J22" s="77"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="76"/>
+      <c r="A23" s="75"/>
       <c r="B23" s="5"/>
       <c r="C23" s="11" t="s">
         <v>67</v>
@@ -6094,7 +6097,7 @@
       <c r="E23" s="5"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="76"/>
+      <c r="A24" s="75"/>
       <c r="C24" t="s">
         <v>7</v>
       </c>
@@ -6103,7 +6106,7 @@
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="76"/>
+      <c r="A25" s="75"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5" t="s">
         <v>28</v>
@@ -6112,7 +6115,7 @@
       <c r="E25" s="5"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="76"/>
+      <c r="A26" s="75"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5" t="s">
         <v>12</v>
@@ -6126,7 +6129,7 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="76"/>
+      <c r="A27" s="75"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5" t="s">
         <v>11</v>
@@ -6140,7 +6143,7 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="76"/>
+      <c r="A28" s="75"/>
       <c r="C28" t="s">
         <v>8</v>
       </c>
@@ -6152,7 +6155,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="76"/>
+      <c r="A29" s="75"/>
       <c r="C29" t="s">
         <v>10</v>
       </c>
@@ -6163,41 +6166,41 @@
       <c r="E29" t="s">
         <v>25</v>
       </c>
-      <c r="G29" s="78" t="s">
+      <c r="G29" s="77" t="s">
         <v>570</v>
       </c>
-      <c r="H29" s="79"/>
-      <c r="I29" s="79"/>
-      <c r="J29" s="79"/>
-      <c r="K29" s="79"/>
+      <c r="H29" s="78"/>
+      <c r="I29" s="78"/>
+      <c r="J29" s="78"/>
+      <c r="K29" s="78"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B30" s="7"/>
       <c r="C30" s="9"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
-      <c r="G30" s="79"/>
-      <c r="H30" s="79"/>
-      <c r="I30" s="79"/>
-      <c r="J30" s="79"/>
-      <c r="K30" s="79"/>
+      <c r="G30" s="78"/>
+      <c r="H30" s="78"/>
+      <c r="I30" s="78"/>
+      <c r="J30" s="78"/>
+      <c r="K30" s="78"/>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="76" t="s">
+      <c r="A31" s="75" t="s">
         <v>126</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="6"/>
-      <c r="G31" s="79"/>
-      <c r="H31" s="79"/>
-      <c r="I31" s="79"/>
-      <c r="J31" s="79"/>
-      <c r="K31" s="79"/>
+      <c r="G31" s="78"/>
+      <c r="H31" s="78"/>
+      <c r="I31" s="78"/>
+      <c r="J31" s="78"/>
+      <c r="K31" s="78"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="76"/>
+      <c r="A32" s="75"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5" t="s">
         <v>120</v>
@@ -6209,14 +6212,14 @@
       <c r="E32" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G32" s="79"/>
-      <c r="H32" s="79"/>
-      <c r="I32" s="79"/>
-      <c r="J32" s="79"/>
-      <c r="K32" s="79"/>
+      <c r="G32" s="78"/>
+      <c r="H32" s="78"/>
+      <c r="I32" s="78"/>
+      <c r="J32" s="78"/>
+      <c r="K32" s="78"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="76"/>
+      <c r="A33" s="75"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7" t="s">
         <v>121</v>
@@ -6227,14 +6230,14 @@
       <c r="E33" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="G33" s="79"/>
-      <c r="H33" s="79"/>
-      <c r="I33" s="79"/>
-      <c r="J33" s="79"/>
-      <c r="K33" s="79"/>
+      <c r="G33" s="78"/>
+      <c r="H33" s="78"/>
+      <c r="I33" s="78"/>
+      <c r="J33" s="78"/>
+      <c r="K33" s="78"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="76"/>
+      <c r="A34" s="75"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7" t="s">
         <v>122</v>
@@ -6243,14 +6246,14 @@
         <v>5</v>
       </c>
       <c r="E34" s="8"/>
-      <c r="G34" s="79"/>
-      <c r="H34" s="79"/>
-      <c r="I34" s="79"/>
-      <c r="J34" s="79"/>
-      <c r="K34" s="79"/>
+      <c r="G34" s="78"/>
+      <c r="H34" s="78"/>
+      <c r="I34" s="78"/>
+      <c r="J34" s="78"/>
+      <c r="K34" s="78"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="76"/>
+      <c r="A35" s="75"/>
       <c r="C35" t="s">
         <v>127</v>
       </c>
@@ -6260,7 +6263,7 @@
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="76"/>
+      <c r="A36" s="75"/>
       <c r="C36" t="s">
         <v>130</v>
       </c>
@@ -6272,7 +6275,7 @@
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="76"/>
+      <c r="A37" s="75"/>
       <c r="C37" t="s">
         <v>163</v>
       </c>
@@ -6282,7 +6285,7 @@
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="76"/>
+      <c r="A38" s="75"/>
       <c r="C38" t="s">
         <v>164</v>
       </c>
@@ -6292,7 +6295,7 @@
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="76"/>
+      <c r="A39" s="75"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5" t="s">
         <v>9</v>
@@ -6306,7 +6309,7 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="76"/>
+      <c r="A40" s="75"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5" t="s">
         <v>748</v>
@@ -6320,7 +6323,7 @@
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="76"/>
+      <c r="A41" s="75"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
         <v>165</v>
@@ -6332,7 +6335,7 @@
       <c r="E41" s="5"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="76"/>
+      <c r="A42" s="75"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5" t="s">
         <v>166</v>
@@ -6344,7 +6347,7 @@
       <c r="E42" s="5"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="76"/>
+      <c r="A43" s="75"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5" t="s">
         <v>749</v>
@@ -6358,7 +6361,7 @@
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="76"/>
+      <c r="A44" s="75"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5" t="s">
         <v>27</v>
@@ -6372,7 +6375,7 @@
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="76"/>
+      <c r="A45" s="75"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5" t="s">
         <v>746</v>
@@ -6385,7 +6388,7 @@
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="76"/>
+      <c r="A46" s="75"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5" t="s">
         <v>747</v>
@@ -6397,7 +6400,7 @@
       <c r="E46" s="5"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="76"/>
+      <c r="A47" s="75"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5" t="s">
         <v>750</v>
@@ -6409,14 +6412,14 @@
       <c r="E47" s="5"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="76"/>
+      <c r="A48" s="75"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
       <c r="D48" s="10"/>
       <c r="E48" s="5"/>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A49" s="76"/>
+      <c r="A49" s="75"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7" t="s">
         <v>752</v>
@@ -6428,7 +6431,7 @@
       <c r="E49" s="7"/>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A50" s="76"/>
+      <c r="A50" s="75"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7" t="s">
         <v>662</v>
@@ -6439,7 +6442,7 @@
       <c r="E50" s="7"/>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A51" s="76"/>
+      <c r="A51" s="75"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7" t="s">
         <v>663</v>
@@ -6450,7 +6453,7 @@
       <c r="E51" s="7"/>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A52" s="76"/>
+      <c r="A52" s="75"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7" t="s">
         <v>753</v>
@@ -6462,7 +6465,7 @@
       <c r="E52" s="7"/>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A53" s="76"/>
+      <c r="A53" s="75"/>
       <c r="B53" s="39"/>
       <c r="C53" s="39" t="s">
         <v>194</v>
@@ -6474,7 +6477,7 @@
       <c r="E53" s="39"/>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A54" s="76"/>
+      <c r="A54" s="75"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5" t="s">
         <v>755</v>
@@ -6486,7 +6489,7 @@
       <c r="E54" s="5"/>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A55" s="76"/>
+      <c r="A55" s="75"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5" t="s">
         <v>756</v>
@@ -6499,7 +6502,7 @@
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A56" s="76"/>
+      <c r="A56" s="75"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5" t="s">
         <v>758</v>
@@ -6510,7 +6513,7 @@
       <c r="E56" s="5"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A57" s="76"/>
+      <c r="A57" s="75"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5" t="s">
         <v>754</v>
@@ -6522,7 +6525,7 @@
       <c r="E57" s="5"/>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A58" s="76"/>
+      <c r="A58" s="75"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5" t="s">
         <v>759</v>
@@ -6534,7 +6537,7 @@
       <c r="E58" s="5"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A59" s="76"/>
+      <c r="A59" s="75"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5" t="s">
         <v>760</v>
@@ -6558,7 +6561,7 @@
       </c>
     </row>
     <row r="61" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="76" t="s">
+      <c r="A61" s="75" t="s">
         <v>30</v>
       </c>
       <c r="C61" s="7" t="s">
@@ -6582,7 +6585,7 @@
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A62" s="76"/>
+      <c r="A62" s="75"/>
       <c r="C62" s="7" t="s">
         <v>26</v>
       </c>
@@ -6604,7 +6607,7 @@
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A63" s="76"/>
+      <c r="A63" s="75"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5" t="s">
         <v>13</v>
@@ -6628,7 +6631,7 @@
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A64" s="76"/>
+      <c r="A64" s="75"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5" t="s">
         <v>14</v>
@@ -6649,7 +6652,7 @@
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A65" s="76"/>
+      <c r="A65" s="75"/>
       <c r="C65" s="7" t="s">
         <v>16</v>
       </c>
@@ -6672,7 +6675,7 @@
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A66" s="76"/>
+      <c r="A66" s="75"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5" t="s">
         <v>102</v>
@@ -6693,7 +6696,7 @@
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A67" s="76"/>
+      <c r="A67" s="75"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5" t="s">
         <v>15</v>
@@ -6714,7 +6717,7 @@
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A68" s="76"/>
+      <c r="A68" s="75"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5" t="s">
         <v>32</v>
@@ -6726,7 +6729,7 @@
       <c r="E68" s="5"/>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A69" s="76"/>
+      <c r="A69" s="75"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5" t="s">
         <v>103</v>
@@ -6745,7 +6748,7 @@
       <c r="E70" s="7"/>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A71" s="77" t="s">
+      <c r="A71" s="76" t="s">
         <v>104</v>
       </c>
       <c r="C71" s="5"/>
@@ -6753,7 +6756,7 @@
       <c r="E71" s="5"/>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A72" s="77"/>
+      <c r="A72" s="76"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5" t="s">
         <v>85</v>
@@ -6765,7 +6768,7 @@
       <c r="E72" s="5"/>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A73" s="77"/>
+      <c r="A73" s="76"/>
       <c r="B73" s="5" t="s">
         <v>119</v>
       </c>
@@ -6781,7 +6784,7 @@
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A74" s="77"/>
+      <c r="A74" s="76"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5" t="s">
         <v>129</v>
@@ -6793,7 +6796,7 @@
       <c r="E74" s="5"/>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A75" s="77"/>
+      <c r="A75" s="76"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5" t="s">
         <v>86</v>
@@ -6806,7 +6809,7 @@
       <c r="R75" s="1"/>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A76" s="77"/>
+      <c r="A76" s="76"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5" t="s">
         <v>87</v>
@@ -6818,7 +6821,7 @@
       <c r="E76" s="5"/>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A77" s="77"/>
+      <c r="A77" s="76"/>
       <c r="B77" s="5" t="s">
         <v>118</v>
       </c>
@@ -6832,7 +6835,7 @@
       <c r="E77" s="5"/>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A78" s="77"/>
+      <c r="A78" s="76"/>
       <c r="B78" s="5" t="s">
         <v>114</v>
       </c>
@@ -6846,7 +6849,7 @@
       <c r="E78" s="5"/>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A79" s="77"/>
+      <c r="A79" s="76"/>
       <c r="B79" s="5" t="s">
         <v>117</v>
       </c>
@@ -6860,7 +6863,7 @@
       <c r="E79" s="5"/>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A80" s="77"/>
+      <c r="A80" s="76"/>
       <c r="C80" t="s">
         <v>89</v>
       </c>
@@ -6869,7 +6872,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="77"/>
+      <c r="A81" s="76"/>
       <c r="C81" t="s">
         <v>90</v>
       </c>
@@ -6878,7 +6881,7 @@
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="77"/>
+      <c r="A82" s="76"/>
       <c r="C82" t="s">
         <v>91</v>
       </c>
@@ -6893,7 +6896,7 @@
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="77"/>
+      <c r="A83" s="76"/>
       <c r="C83" t="s">
         <v>92</v>
       </c>
@@ -6903,7 +6906,7 @@
       <c r="G83" s="4"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="77"/>
+      <c r="A84" s="76"/>
       <c r="C84" t="s">
         <v>93</v>
       </c>
@@ -6912,7 +6915,7 @@
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="77"/>
+      <c r="A85" s="76"/>
       <c r="C85" t="s">
         <v>94</v>
       </c>
@@ -6921,7 +6924,7 @@
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="77"/>
+      <c r="A86" s="76"/>
       <c r="C86" t="s">
         <v>95</v>
       </c>
@@ -6930,7 +6933,7 @@
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="77"/>
+      <c r="A87" s="76"/>
       <c r="C87" t="s">
         <v>108</v>
       </c>
@@ -6939,7 +6942,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="77"/>
+      <c r="A88" s="76"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5" t="s">
         <v>105</v>
@@ -6951,7 +6954,7 @@
       <c r="E88" s="5"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="77"/>
+      <c r="A89" s="76"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5" t="s">
         <v>106</v>
@@ -6963,7 +6966,7 @@
       <c r="E89" s="5"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="77"/>
+      <c r="A90" s="76"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5" t="s">
         <v>107</v>
@@ -6975,7 +6978,7 @@
       <c r="E90" s="5"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="77"/>
+      <c r="A91" s="76"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5" t="s">
         <v>109</v>
@@ -6987,7 +6990,7 @@
       <c r="E91" s="5"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="77"/>
+      <c r="A92" s="76"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5" t="s">
         <v>110</v>
@@ -6999,7 +7002,7 @@
       <c r="E92" s="5"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="77"/>
+      <c r="A93" s="76"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5" t="s">
         <v>111</v>
@@ -7011,7 +7014,7 @@
       <c r="E93" s="5"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="77"/>
+      <c r="A94" s="76"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5" t="s">
         <v>112</v>
@@ -7023,7 +7026,7 @@
       <c r="E94" s="5"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="77"/>
+      <c r="A95" s="76"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5" t="s">
         <v>113</v>
@@ -7044,7 +7047,7 @@
       </c>
     </row>
     <row r="99" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="76" t="s">
+      <c r="A99" s="75" t="s">
         <v>1014</v>
       </c>
       <c r="B99" s="7" t="s">
@@ -7062,7 +7065,7 @@
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100" s="76"/>
+      <c r="A100" s="75"/>
       <c r="B100" s="7" t="s">
         <v>994</v>
       </c>
@@ -7078,7 +7081,7 @@
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" s="76"/>
+      <c r="A101" s="75"/>
       <c r="B101" s="7" t="s">
         <v>47</v>
       </c>
@@ -7094,7 +7097,7 @@
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" s="76"/>
+      <c r="A102" s="75"/>
       <c r="B102" t="s">
         <v>986</v>
       </c>
@@ -7110,7 +7113,7 @@
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" s="76"/>
+      <c r="A103" s="75"/>
       <c r="B103" t="s">
         <v>37</v>
       </c>
@@ -7126,7 +7129,7 @@
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104" s="76"/>
+      <c r="A104" s="75"/>
       <c r="B104" t="s">
         <v>38</v>
       </c>
@@ -7139,7 +7142,7 @@
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A105" s="76"/>
+      <c r="A105" s="75"/>
       <c r="B105" s="7" t="s">
         <v>60</v>
       </c>
@@ -7155,7 +7158,7 @@
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A106" s="76"/>
+      <c r="A106" s="75"/>
       <c r="B106" t="s">
         <v>56</v>
       </c>
@@ -7170,7 +7173,7 @@
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107" s="76"/>
+      <c r="A107" s="75"/>
       <c r="B107" t="s">
         <v>55</v>
       </c>
@@ -7182,7 +7185,7 @@
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" s="76"/>
+      <c r="A108" s="75"/>
       <c r="B108" t="s">
         <v>49</v>
       </c>
@@ -7198,7 +7201,7 @@
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A109" s="76"/>
+      <c r="A109" s="75"/>
       <c r="C109" t="s">
         <v>36</v>
       </c>
@@ -7207,7 +7210,7 @@
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A110" s="76"/>
+      <c r="A110" s="75"/>
       <c r="B110" t="s">
         <v>39</v>
       </c>
@@ -7219,7 +7222,7 @@
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A111" s="76"/>
+      <c r="A111" s="75"/>
       <c r="B111" t="s">
         <v>558</v>
       </c>
@@ -7233,16 +7236,16 @@
       <c r="E111" t="s">
         <v>25</v>
       </c>
-      <c r="G111" s="75" t="s">
+      <c r="G111" s="80" t="s">
         <v>1013</v>
       </c>
-      <c r="H111" s="75"/>
-      <c r="I111" s="75"/>
-      <c r="J111" s="75"/>
-      <c r="K111" s="75"/>
+      <c r="H111" s="80"/>
+      <c r="I111" s="80"/>
+      <c r="J111" s="80"/>
+      <c r="K111" s="80"/>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A112" s="76"/>
+      <c r="A112" s="75"/>
       <c r="B112" t="s">
         <v>1029</v>
       </c>
@@ -7260,7 +7263,7 @@
       <c r="K112" s="68"/>
     </row>
     <row r="113" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A113" s="76"/>
+      <c r="A113" s="75"/>
       <c r="B113" t="s">
         <v>1030</v>
       </c>
@@ -7291,7 +7294,7 @@
       </c>
     </row>
     <row r="114" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A114" s="76"/>
+      <c r="A114" s="75"/>
       <c r="B114" t="s">
         <v>40</v>
       </c>
@@ -7325,7 +7328,7 @@
       </c>
     </row>
     <row r="115" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A115" s="76"/>
+      <c r="A115" s="75"/>
       <c r="C115" s="57" t="s">
         <v>1032</v>
       </c>
@@ -7335,7 +7338,7 @@
       </c>
     </row>
     <row r="116" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A116" s="76"/>
+      <c r="A116" s="75"/>
       <c r="C116" s="57" t="s">
         <v>1033</v>
       </c>
@@ -7345,7 +7348,7 @@
       </c>
     </row>
     <row r="117" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A117" s="76"/>
+      <c r="A117" s="75"/>
       <c r="B117" t="s">
         <v>62</v>
       </c>
@@ -7373,7 +7376,7 @@
       </c>
     </row>
     <row r="118" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A118" s="76"/>
+      <c r="A118" s="75"/>
       <c r="B118" t="s">
         <v>51</v>
       </c>
@@ -7461,7 +7464,7 @@
       </c>
     </row>
     <row r="119" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A119" s="76"/>
+      <c r="A119" s="75"/>
       <c r="B119" t="s">
         <v>53</v>
       </c>
@@ -7477,7 +7480,7 @@
       </c>
     </row>
     <row r="120" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A120" s="76"/>
+      <c r="A120" s="75"/>
       <c r="C120" t="s">
         <v>58</v>
       </c>
@@ -7487,7 +7490,7 @@
       </c>
     </row>
     <row r="121" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A121" s="76"/>
+      <c r="A121" s="75"/>
       <c r="B121" t="s">
         <v>1021</v>
       </c>
@@ -7500,7 +7503,7 @@
       </c>
     </row>
     <row r="122" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A122" s="76"/>
+      <c r="A122" s="75"/>
       <c r="B122" t="s">
         <v>1024</v>
       </c>
@@ -7513,7 +7516,7 @@
       </c>
     </row>
     <row r="123" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A123" s="76"/>
+      <c r="A123" s="75"/>
       <c r="B123" t="s">
         <v>1023</v>
       </c>
@@ -7526,7 +7529,7 @@
       </c>
     </row>
     <row r="124" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A124" s="76"/>
+      <c r="A124" s="75"/>
       <c r="B124" t="s">
         <v>1027</v>
       </c>
@@ -7539,7 +7542,7 @@
       </c>
     </row>
     <row r="125" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A125" s="76"/>
+      <c r="A125" s="75"/>
       <c r="B125" t="s">
         <v>1037</v>
       </c>
@@ -7552,7 +7555,7 @@
       </c>
     </row>
     <row r="126" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A126" s="76"/>
+      <c r="A126" s="75"/>
       <c r="C126" t="s">
         <v>1031</v>
       </c>
@@ -7562,7 +7565,7 @@
       </c>
     </row>
     <row r="127" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A127" s="76"/>
+      <c r="A127" s="75"/>
       <c r="C127" t="s">
         <v>1034</v>
       </c>
@@ -7572,7 +7575,7 @@
       </c>
     </row>
     <row r="128" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A128" s="76"/>
+      <c r="A128" s="75"/>
       <c r="C128" t="s">
         <v>1035</v>
       </c>
@@ -7582,7 +7585,7 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" s="76"/>
+      <c r="A129" s="75"/>
       <c r="C129" t="s">
         <v>1036</v>
       </c>
@@ -7592,18 +7595,18 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" s="76"/>
+      <c r="A130" s="75"/>
       <c r="D130" s="27" t="str">
         <f>IF(D129, "Demagnetisation may not complete with 0.5 duty cycle", "Demagnetisation should complete for 0.5 duty cycle")</f>
         <v>Demagnetisation may not complete with 0.5 duty cycle</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" s="76"/>
+      <c r="A131" s="75"/>
       <c r="D131" s="27"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" s="76"/>
+      <c r="A132" s="75"/>
       <c r="C132" t="s">
         <v>63</v>
       </c>
@@ -7613,7 +7616,7 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" s="76"/>
+      <c r="A133" s="75"/>
       <c r="B133" s="58" t="s">
         <v>988</v>
       </c>
@@ -7632,7 +7635,7 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="76"/>
+      <c r="A134" s="75"/>
       <c r="B134" s="70" t="s">
         <v>989</v>
       </c>
@@ -7646,7 +7649,7 @@
       <c r="E134" s="70"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" s="76"/>
+      <c r="A135" s="75"/>
       <c r="B135" s="70" t="s">
         <v>791</v>
       </c>
@@ -7665,7 +7668,7 @@
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="76"/>
+      <c r="A136" s="75"/>
       <c r="B136" t="s">
         <v>168</v>
       </c>
@@ -7682,7 +7685,7 @@
       <c r="D137" s="27"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="76" t="s">
+      <c r="A138" s="75" t="s">
         <v>1015</v>
       </c>
       <c r="B138" s="7" t="s">
@@ -7696,7 +7699,7 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="76"/>
+      <c r="A139" s="75"/>
       <c r="B139" s="7" t="s">
         <v>993</v>
       </c>
@@ -7712,7 +7715,7 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="76"/>
+      <c r="A140" s="75"/>
       <c r="B140" s="7" t="s">
         <v>994</v>
       </c>
@@ -7727,7 +7730,7 @@
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" s="76"/>
+      <c r="A141" s="75"/>
       <c r="B141" s="7" t="s">
         <v>47</v>
       </c>
@@ -7743,7 +7746,7 @@
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" s="76"/>
+      <c r="A142" s="75"/>
       <c r="B142" t="s">
         <v>986</v>
       </c>
@@ -7759,7 +7762,7 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" s="76"/>
+      <c r="A143" s="75"/>
       <c r="B143" t="s">
         <v>38</v>
       </c>
@@ -7775,7 +7778,7 @@
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" s="76"/>
+      <c r="A144" s="75"/>
       <c r="B144" s="7" t="s">
         <v>1016</v>
       </c>
@@ -7791,7 +7794,7 @@
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" s="76"/>
+      <c r="A145" s="75"/>
       <c r="B145" t="s">
         <v>56</v>
       </c>
@@ -7806,7 +7809,7 @@
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A146" s="76"/>
+      <c r="A146" s="75"/>
       <c r="B146" t="s">
         <v>55</v>
       </c>
@@ -7818,7 +7821,7 @@
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" s="76"/>
+      <c r="A147" s="75"/>
       <c r="B147" t="s">
         <v>49</v>
       </c>
@@ -7834,7 +7837,7 @@
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" s="76"/>
+      <c r="A148" s="75"/>
       <c r="C148" t="s">
         <v>36</v>
       </c>
@@ -7843,7 +7846,7 @@
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149" s="76"/>
+      <c r="A149" s="75"/>
       <c r="B149" t="s">
         <v>137</v>
       </c>
@@ -7855,7 +7858,7 @@
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A150" s="76"/>
+      <c r="A150" s="75"/>
       <c r="B150" t="s">
         <v>558</v>
       </c>
@@ -7871,7 +7874,7 @@
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151" s="76"/>
+      <c r="A151" s="75"/>
       <c r="B151" t="s">
         <v>44</v>
       </c>
@@ -7887,7 +7890,7 @@
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A152" s="76"/>
+      <c r="A152" s="75"/>
       <c r="B152" t="s">
         <v>40</v>
       </c>
@@ -7903,7 +7906,7 @@
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153" s="76"/>
+      <c r="A153" s="75"/>
       <c r="B153" t="s">
         <v>62</v>
       </c>
@@ -7913,7 +7916,7 @@
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A154" s="76"/>
+      <c r="A154" s="75"/>
       <c r="B154" t="s">
         <v>51</v>
       </c>
@@ -7926,7 +7929,7 @@
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" s="76"/>
+      <c r="A155" s="75"/>
       <c r="B155" t="s">
         <v>53</v>
       </c>
@@ -7942,7 +7945,7 @@
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" s="76"/>
+      <c r="A156" s="75"/>
       <c r="C156" t="s">
         <v>58</v>
       </c>
@@ -7952,7 +7955,7 @@
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A157" s="76"/>
+      <c r="A157" s="75"/>
       <c r="B157" t="s">
         <v>560</v>
       </c>
@@ -7965,7 +7968,7 @@
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A158" s="76"/>
+      <c r="A158" s="75"/>
       <c r="B158" t="s">
         <v>561</v>
       </c>
@@ -7978,10 +7981,10 @@
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159" s="76"/>
+      <c r="A159" s="75"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A160" s="76"/>
+      <c r="A160" s="75"/>
       <c r="C160" t="s">
         <v>63</v>
       </c>
@@ -7991,7 +7994,7 @@
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A161" s="76"/>
+      <c r="A161" s="75"/>
       <c r="B161" s="58" t="s">
         <v>988</v>
       </c>
@@ -8007,7 +8010,7 @@
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A162" s="76"/>
+      <c r="A162" s="75"/>
       <c r="B162" t="s">
         <v>989</v>
       </c>
@@ -8020,7 +8023,7 @@
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A163" s="76"/>
+      <c r="A163" s="75"/>
       <c r="B163" t="s">
         <v>791</v>
       </c>
@@ -8036,7 +8039,7 @@
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A164" s="76"/>
+      <c r="A164" s="75"/>
       <c r="B164" t="s">
         <v>168</v>
       </c>
@@ -8057,7 +8060,7 @@
       <c r="D166" s="27"/>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A167" s="76" t="s">
+      <c r="A167" s="75" t="s">
         <v>1005</v>
       </c>
       <c r="B167" t="s">
@@ -8069,7 +8072,7 @@
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A168" s="76"/>
+      <c r="A168" s="75"/>
       <c r="B168" t="s">
         <v>168</v>
       </c>
@@ -8082,7 +8085,7 @@
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A169" s="76"/>
+      <c r="A169" s="75"/>
       <c r="B169" t="s">
         <v>1001</v>
       </c>
@@ -8094,7 +8097,7 @@
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A170" s="76"/>
+      <c r="A170" s="75"/>
       <c r="B170" t="s">
         <v>1002</v>
       </c>
@@ -8107,7 +8110,7 @@
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A171" s="76"/>
+      <c r="A171" s="75"/>
       <c r="C171" t="s">
         <v>181</v>
       </c>
@@ -8119,7 +8122,7 @@
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A172" s="76"/>
+      <c r="A172" s="75"/>
       <c r="C172" t="s">
         <v>179</v>
       </c>
@@ -8131,7 +8134,7 @@
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A173" s="76"/>
+      <c r="A173" s="75"/>
       <c r="C173" t="s">
         <v>178</v>
       </c>
@@ -8140,7 +8143,7 @@
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A174" s="76"/>
+      <c r="A174" s="75"/>
       <c r="C174" t="s">
         <v>172</v>
       </c>
@@ -8153,7 +8156,7 @@
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A175" s="76"/>
+      <c r="A175" s="75"/>
       <c r="C175" t="s">
         <v>173</v>
       </c>
@@ -8166,7 +8169,7 @@
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A176" s="76"/>
+      <c r="A176" s="75"/>
       <c r="C176" t="s">
         <v>174</v>
       </c>
@@ -8178,7 +8181,7 @@
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A177" s="76"/>
+      <c r="A177" s="75"/>
       <c r="C177" t="s">
         <v>183</v>
       </c>
@@ -8191,7 +8194,7 @@
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A178" s="76"/>
+      <c r="A178" s="75"/>
       <c r="C178" t="s">
         <v>175</v>
       </c>
@@ -8204,7 +8207,7 @@
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A179" s="76"/>
+      <c r="A179" s="75"/>
       <c r="C179" t="s">
         <v>176</v>
       </c>
@@ -8214,7 +8217,7 @@
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A180" s="76"/>
+      <c r="A180" s="75"/>
       <c r="C180" t="s">
         <v>171</v>
       </c>
@@ -8224,7 +8227,7 @@
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A181" s="76"/>
+      <c r="A181" s="75"/>
       <c r="C181" t="s">
         <v>177</v>
       </c>
@@ -8234,7 +8237,7 @@
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A182" s="76"/>
+      <c r="A182" s="75"/>
       <c r="C182" t="s">
         <v>189</v>
       </c>
@@ -8244,7 +8247,7 @@
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A183" s="76"/>
+      <c r="A183" s="75"/>
       <c r="C183" t="s">
         <v>188</v>
       </c>
@@ -8257,7 +8260,7 @@
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A184" s="76"/>
+      <c r="A184" s="75"/>
       <c r="C184" t="s">
         <v>180</v>
       </c>
@@ -8270,7 +8273,7 @@
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A185" s="76"/>
+      <c r="A185" s="75"/>
       <c r="C185" t="s">
         <v>182</v>
       </c>
@@ -8283,7 +8286,7 @@
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A186" s="76"/>
+      <c r="A186" s="75"/>
       <c r="C186" t="s">
         <v>183</v>
       </c>
@@ -8296,7 +8299,7 @@
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A187" s="76"/>
+      <c r="A187" s="75"/>
       <c r="C187" t="s">
         <v>184</v>
       </c>
@@ -8306,7 +8309,7 @@
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A188" s="76"/>
+      <c r="A188" s="75"/>
       <c r="C188" t="s">
         <v>185</v>
       </c>
@@ -8318,7 +8321,7 @@
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A189" s="76"/>
+      <c r="A189" s="75"/>
       <c r="C189" t="s">
         <v>187</v>
       </c>
@@ -8331,7 +8334,7 @@
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A190" s="76"/>
+      <c r="A190" s="75"/>
       <c r="C190" t="s">
         <v>216</v>
       </c>
@@ -8341,7 +8344,7 @@
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A191" s="76"/>
+      <c r="A191" s="75"/>
       <c r="C191" t="s">
         <v>195</v>
       </c>
@@ -8353,7 +8356,7 @@
       </c>
     </row>
     <row r="192" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A192" s="76"/>
+      <c r="A192" s="75"/>
       <c r="C192" t="s">
         <v>194</v>
       </c>
@@ -8366,7 +8369,7 @@
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A193" s="76"/>
+      <c r="A193" s="75"/>
       <c r="B193" t="s">
         <v>1003</v>
       </c>
@@ -8394,7 +8397,7 @@
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A196" s="76" t="s">
+      <c r="A196" s="75" t="s">
         <v>1004</v>
       </c>
       <c r="C196" t="s">
@@ -8408,7 +8411,7 @@
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A197" s="76"/>
+      <c r="A197" s="75"/>
       <c r="C197" t="s">
         <v>192</v>
       </c>
@@ -8420,7 +8423,7 @@
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A198" s="76"/>
+      <c r="A198" s="75"/>
       <c r="C198" t="s">
         <v>197</v>
       </c>
@@ -8432,7 +8435,7 @@
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A199" s="76"/>
+      <c r="A199" s="75"/>
       <c r="B199" t="s">
         <v>999</v>
       </c>
@@ -8445,7 +8448,7 @@
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A200" s="76"/>
+      <c r="A200" s="75"/>
       <c r="B200" s="7" t="s">
         <v>47</v>
       </c>
@@ -8461,7 +8464,7 @@
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A201" s="76"/>
+      <c r="A201" s="75"/>
       <c r="B201" t="s">
         <v>40</v>
       </c>
@@ -8477,7 +8480,7 @@
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A202" s="76"/>
+      <c r="A202" s="75"/>
       <c r="C202" t="s">
         <v>203</v>
       </c>
@@ -8490,7 +8493,7 @@
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A203" s="76"/>
+      <c r="A203" s="75"/>
       <c r="C203" t="s">
         <v>198</v>
       </c>
@@ -8503,7 +8506,7 @@
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A204" s="76"/>
+      <c r="A204" s="75"/>
       <c r="C204" t="s">
         <v>183</v>
       </c>
@@ -8516,7 +8519,7 @@
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A205" s="76"/>
+      <c r="A205" s="75"/>
       <c r="C205" t="s">
         <v>184</v>
       </c>
@@ -8529,7 +8532,7 @@
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A206" s="76"/>
+      <c r="A206" s="75"/>
       <c r="C206" t="s">
         <v>200</v>
       </c>
@@ -8542,7 +8545,7 @@
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A207" s="76"/>
+      <c r="A207" s="75"/>
       <c r="C207" t="s">
         <v>201</v>
       </c>
@@ -8555,7 +8558,7 @@
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A208" s="76"/>
+      <c r="A208" s="75"/>
       <c r="C208" t="s">
         <v>202</v>
       </c>
@@ -8568,7 +8571,7 @@
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A209" s="76"/>
+      <c r="A209" s="75"/>
       <c r="C209" t="s">
         <v>204</v>
       </c>
@@ -8581,7 +8584,7 @@
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A210" s="76"/>
+      <c r="A210" s="75"/>
       <c r="C210" t="s">
         <v>205</v>
       </c>
@@ -8594,7 +8597,7 @@
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A211" s="76"/>
+      <c r="A211" s="75"/>
       <c r="C211" t="s">
         <v>195</v>
       </c>
@@ -8606,7 +8609,7 @@
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A212" s="76"/>
+      <c r="A212" s="75"/>
       <c r="C212" t="s">
         <v>208</v>
       </c>
@@ -8619,7 +8622,7 @@
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A213" s="76"/>
+      <c r="A213" s="75"/>
       <c r="C213" t="s">
         <v>209</v>
       </c>
@@ -8632,7 +8635,7 @@
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A214" s="76"/>
+      <c r="A214" s="75"/>
       <c r="C214" t="s">
         <v>210</v>
       </c>
@@ -8645,7 +8648,7 @@
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A215" s="76"/>
+      <c r="A215" s="75"/>
       <c r="C215" t="s">
         <v>211</v>
       </c>
@@ -8658,7 +8661,7 @@
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A216" s="76"/>
+      <c r="A216" s="75"/>
       <c r="C216" t="s">
         <v>212</v>
       </c>
@@ -8671,7 +8674,7 @@
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A217" s="76"/>
+      <c r="A217" s="75"/>
       <c r="C217" t="s">
         <v>1000</v>
       </c>
@@ -8684,7 +8687,7 @@
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A218" s="76"/>
+      <c r="A218" s="75"/>
       <c r="C218" t="s">
         <v>213</v>
       </c>
@@ -8697,7 +8700,7 @@
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A219" s="76"/>
+      <c r="A219" s="75"/>
       <c r="C219" t="s">
         <v>214</v>
       </c>
@@ -8710,7 +8713,7 @@
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A220" s="76"/>
+      <c r="A220" s="75"/>
       <c r="C220" t="s">
         <v>215</v>
       </c>
@@ -8777,7 +8780,7 @@
       <c r="A228" s="23"/>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A229" s="80" t="s">
+      <c r="A229" s="79" t="s">
         <v>517</v>
       </c>
       <c r="B229" s="61" t="s">
@@ -8800,7 +8803,7 @@
       <c r="N229" s="61"/>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A230" s="80"/>
+      <c r="A230" s="79"/>
       <c r="B230" s="61" t="s">
         <v>48</v>
       </c>
@@ -8823,7 +8826,7 @@
       <c r="N230" s="61"/>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A231" s="80"/>
+      <c r="A231" s="79"/>
       <c r="B231" s="61" t="s">
         <v>47</v>
       </c>
@@ -8844,7 +8847,7 @@
       <c r="N231" s="61"/>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A232" s="80"/>
+      <c r="A232" s="79"/>
       <c r="B232" s="61" t="s">
         <v>71</v>
       </c>
@@ -8865,7 +8868,7 @@
       <c r="N232" s="61"/>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A233" s="80"/>
+      <c r="A233" s="79"/>
       <c r="B233" s="61" t="s">
         <v>511</v>
       </c>
@@ -8887,7 +8890,7 @@
       <c r="N233" s="61"/>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A234" s="80"/>
+      <c r="A234" s="79"/>
       <c r="B234" s="61" t="s">
         <v>231</v>
       </c>
@@ -8908,7 +8911,7 @@
       <c r="N234" s="61"/>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A235" s="80"/>
+      <c r="A235" s="79"/>
       <c r="B235" s="61" t="s">
         <v>232</v>
       </c>
@@ -8929,7 +8932,7 @@
       <c r="N235" s="61"/>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A236" s="80"/>
+      <c r="A236" s="79"/>
       <c r="B236" s="61" t="s">
         <v>516</v>
       </c>
@@ -8950,7 +8953,7 @@
       <c r="N236" s="61"/>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A237" s="80"/>
+      <c r="A237" s="79"/>
       <c r="B237" s="61" t="s">
         <v>229</v>
       </c>
@@ -8970,7 +8973,7 @@
       <c r="N237" s="61"/>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A238" s="80"/>
+      <c r="A238" s="79"/>
       <c r="B238" s="61" t="s">
         <v>219</v>
       </c>
@@ -8993,7 +8996,7 @@
       <c r="N238" s="61"/>
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A239" s="80"/>
+      <c r="A239" s="79"/>
       <c r="B239" s="61" t="s">
         <v>39</v>
       </c>
@@ -9014,7 +9017,7 @@
       <c r="N239" s="61"/>
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A240" s="80"/>
+      <c r="A240" s="79"/>
       <c r="B240" s="61" t="s">
         <v>284</v>
       </c>
@@ -9035,7 +9038,7 @@
       <c r="N240" s="61"/>
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A241" s="80"/>
+      <c r="A241" s="79"/>
       <c r="B241" s="61" t="s">
         <v>220</v>
       </c>
@@ -9056,7 +9059,7 @@
       <c r="N241" s="61"/>
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A242" s="80"/>
+      <c r="A242" s="79"/>
       <c r="B242" s="61" t="s">
         <v>221</v>
       </c>
@@ -9077,7 +9080,7 @@
       <c r="N242" s="61"/>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A243" s="80"/>
+      <c r="A243" s="79"/>
       <c r="B243" s="61" t="s">
         <v>233</v>
       </c>
@@ -9098,7 +9101,7 @@
       <c r="N243" s="61"/>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A244" s="80"/>
+      <c r="A244" s="79"/>
       <c r="B244" s="61" t="s">
         <v>226</v>
       </c>
@@ -9119,7 +9122,7 @@
       <c r="N244" s="61"/>
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A245" s="80"/>
+      <c r="A245" s="79"/>
       <c r="B245" s="61" t="s">
         <v>224</v>
       </c>
@@ -9139,7 +9142,7 @@
       <c r="N245" s="61"/>
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A246" s="80"/>
+      <c r="A246" s="79"/>
       <c r="B246" s="61" t="s">
         <v>513</v>
       </c>
@@ -9160,7 +9163,7 @@
       <c r="N246" s="61"/>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A247" s="80"/>
+      <c r="A247" s="79"/>
       <c r="B247" s="61" t="s">
         <v>515</v>
       </c>
@@ -9181,7 +9184,7 @@
       <c r="N247" s="61"/>
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A248" s="80"/>
+      <c r="A248" s="79"/>
       <c r="B248" s="61" t="s">
         <v>234</v>
       </c>
@@ -9204,7 +9207,7 @@
       <c r="N248" s="61"/>
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A249" s="80"/>
+      <c r="A249" s="79"/>
       <c r="B249" s="61" t="s">
         <v>223</v>
       </c>
@@ -9226,7 +9229,7 @@
       <c r="N249" s="61"/>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A250" s="80"/>
+      <c r="A250" s="79"/>
       <c r="B250" s="61" t="s">
         <v>225</v>
       </c>
@@ -9247,7 +9250,7 @@
       <c r="N250" s="61"/>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A251" s="80"/>
+      <c r="A251" s="79"/>
       <c r="B251" s="61" t="s">
         <v>277</v>
       </c>
@@ -9269,7 +9272,7 @@
       <c r="N251" s="61"/>
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A252" s="80"/>
+      <c r="A252" s="79"/>
       <c r="B252" s="61" t="s">
         <v>514</v>
       </c>
@@ -9289,7 +9292,7 @@
       <c r="N252" s="61"/>
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A253" s="80"/>
+      <c r="A253" s="79"/>
       <c r="B253" s="61" t="s">
         <v>490</v>
       </c>
@@ -9309,7 +9312,7 @@
       <c r="N253" s="61"/>
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A254" s="80"/>
+      <c r="A254" s="79"/>
       <c r="B254" s="61" t="s">
         <v>227</v>
       </c>
@@ -9330,7 +9333,7 @@
       <c r="N254" s="61"/>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A255" s="80"/>
+      <c r="A255" s="79"/>
       <c r="B255" s="61" t="s">
         <v>491</v>
       </c>
@@ -9351,7 +9354,7 @@
       <c r="N255" s="61"/>
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A256" s="80"/>
+      <c r="A256" s="79"/>
       <c r="B256" s="61" t="s">
         <v>495</v>
       </c>
@@ -9388,7 +9391,7 @@
       </c>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A257" s="80"/>
+      <c r="A257" s="79"/>
       <c r="B257" s="61" t="s">
         <v>496</v>
       </c>
@@ -9430,7 +9433,7 @@
       </c>
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A258" s="80"/>
+      <c r="A258" s="79"/>
       <c r="B258" s="61" t="s">
         <v>494</v>
       </c>
@@ -9470,7 +9473,7 @@
       </c>
     </row>
     <row r="259" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="80"/>
+      <c r="A259" s="79"/>
       <c r="B259" s="61" t="s">
         <v>492</v>
       </c>
@@ -9510,7 +9513,7 @@
       </c>
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A260" s="80"/>
+      <c r="A260" s="79"/>
       <c r="B260" s="61" t="s">
         <v>493</v>
       </c>
@@ -9550,7 +9553,7 @@
       </c>
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A261" s="80"/>
+      <c r="A261" s="79"/>
       <c r="B261" s="61" t="s">
         <v>280</v>
       </c>
@@ -9589,7 +9592,7 @@
       </c>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A262" s="80"/>
+      <c r="A262" s="79"/>
       <c r="B262" s="61" t="s">
         <v>281</v>
       </c>
@@ -9628,7 +9631,7 @@
       </c>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A263" s="80"/>
+      <c r="A263" s="79"/>
       <c r="B263" s="61" t="s">
         <v>282</v>
       </c>
@@ -9665,7 +9668,7 @@
       </c>
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A264" s="80"/>
+      <c r="A264" s="79"/>
       <c r="B264" s="61" t="s">
         <v>283</v>
       </c>
@@ -9686,7 +9689,7 @@
       <c r="N264" s="61"/>
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A265" s="80"/>
+      <c r="A265" s="79"/>
       <c r="B265" s="61" t="s">
         <v>284</v>
       </c>
@@ -9707,7 +9710,7 @@
       <c r="N265" s="61"/>
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A266" s="80"/>
+      <c r="A266" s="79"/>
       <c r="B266" s="61" t="s">
         <v>285</v>
       </c>
@@ -9725,7 +9728,7 @@
       <c r="N266" s="61"/>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A267" s="80"/>
+      <c r="A267" s="79"/>
       <c r="B267" s="61" t="s">
         <v>286</v>
       </c>
@@ -9746,7 +9749,7 @@
       <c r="N267" s="61"/>
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A268" s="80"/>
+      <c r="A268" s="79"/>
       <c r="B268" s="61" t="s">
         <v>238</v>
       </c>
@@ -9766,7 +9769,7 @@
       <c r="N268" s="61"/>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A269" s="80"/>
+      <c r="A269" s="79"/>
       <c r="B269" s="61"/>
       <c r="C269" s="61" t="s">
         <v>239</v>
@@ -9786,7 +9789,7 @@
       <c r="N269" s="61"/>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A270" s="80"/>
+      <c r="A270" s="79"/>
       <c r="B270" s="61"/>
       <c r="C270" s="61" t="s">
         <v>240</v>
@@ -9807,7 +9810,7 @@
       <c r="N270" s="61"/>
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A271" s="80"/>
+      <c r="A271" s="79"/>
       <c r="B271" s="61"/>
       <c r="C271" s="61" t="s">
         <v>241</v>
@@ -9827,7 +9830,7 @@
       <c r="N271" s="61"/>
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A272" s="80"/>
+      <c r="A272" s="79"/>
       <c r="B272" s="61"/>
       <c r="C272" s="61"/>
       <c r="D272" s="61"/>
@@ -9843,7 +9846,7 @@
       <c r="N272" s="61"/>
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A273" s="80"/>
+      <c r="A273" s="79"/>
       <c r="B273" s="61" t="s">
         <v>243</v>
       </c>
@@ -9863,7 +9866,7 @@
       <c r="N273" s="61"/>
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A274" s="80"/>
+      <c r="A274" s="79"/>
       <c r="B274" s="61" t="s">
         <v>267</v>
       </c>
@@ -9884,7 +9887,7 @@
       <c r="N274" s="61"/>
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A275" s="80"/>
+      <c r="A275" s="79"/>
       <c r="B275" s="61" t="s">
         <v>244</v>
       </c>
@@ -9904,7 +9907,7 @@
       <c r="N275" s="61"/>
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A276" s="80"/>
+      <c r="A276" s="79"/>
       <c r="B276" s="61" t="s">
         <v>245</v>
       </c>
@@ -9925,7 +9928,7 @@
       <c r="N276" s="61"/>
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A277" s="80"/>
+      <c r="A277" s="79"/>
       <c r="B277" s="61" t="s">
         <v>246</v>
       </c>
@@ -9948,7 +9951,7 @@
       <c r="N277" s="61"/>
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A278" s="80"/>
+      <c r="A278" s="79"/>
       <c r="B278" s="61" t="s">
         <v>247</v>
       </c>
@@ -9971,7 +9974,7 @@
       <c r="N278" s="61"/>
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A279" s="80"/>
+      <c r="A279" s="79"/>
       <c r="B279" s="61" t="s">
         <v>248</v>
       </c>
@@ -9994,7 +9997,7 @@
       <c r="N279" s="61"/>
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A280" s="80"/>
+      <c r="A280" s="79"/>
       <c r="B280" s="61" t="s">
         <v>249</v>
       </c>
@@ -10019,7 +10022,7 @@
       <c r="N280" s="61"/>
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A281" s="80"/>
+      <c r="A281" s="79"/>
       <c r="B281" s="61" t="s">
         <v>250</v>
       </c>
@@ -10040,7 +10043,7 @@
       <c r="N281" s="61"/>
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A282" s="80"/>
+      <c r="A282" s="79"/>
       <c r="B282" s="61"/>
       <c r="C282" s="61" t="s">
         <v>251</v>
@@ -10061,7 +10064,7 @@
       <c r="N282" s="61"/>
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A283" s="80"/>
+      <c r="A283" s="79"/>
       <c r="B283" s="61"/>
       <c r="C283" s="61" t="s">
         <v>252</v>
@@ -10082,7 +10085,7 @@
       <c r="N283" s="61"/>
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A284" s="80"/>
+      <c r="A284" s="79"/>
       <c r="B284" s="61"/>
       <c r="C284" s="61" t="s">
         <v>253</v>
@@ -10108,12 +10111,12 @@
       <c r="A285" s="28"/>
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A286" s="77" t="s">
+      <c r="A286" s="76" t="s">
         <v>751</v>
       </c>
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A287" s="77"/>
+      <c r="A287" s="76"/>
       <c r="B287" t="s">
         <v>556</v>
       </c>
@@ -10122,10 +10125,10 @@
       </c>
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A288" s="77"/>
+      <c r="A288" s="76"/>
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A289" s="77"/>
+      <c r="A289" s="76"/>
       <c r="B289" t="s">
         <v>512</v>
       </c>
@@ -10134,7 +10137,7 @@
       </c>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A290" s="77"/>
+      <c r="A290" s="76"/>
       <c r="B290" t="s">
         <v>527</v>
       </c>
@@ -10173,7 +10176,7 @@
       </c>
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A291" s="77"/>
+      <c r="A291" s="76"/>
       <c r="B291" t="s">
         <v>541</v>
       </c>
@@ -10212,7 +10215,7 @@
       </c>
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A292" s="77"/>
+      <c r="A292" s="76"/>
       <c r="B292" t="s">
         <v>528</v>
       </c>
@@ -10251,7 +10254,7 @@
       </c>
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A293" s="77"/>
+      <c r="A293" s="76"/>
       <c r="B293" t="s">
         <v>309</v>
       </c>
@@ -10292,7 +10295,7 @@
       </c>
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A294" s="77"/>
+      <c r="A294" s="76"/>
       <c r="B294" t="s">
         <v>529</v>
       </c>
@@ -10333,7 +10336,7 @@
       </c>
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A295" s="77"/>
+      <c r="A295" s="76"/>
       <c r="B295" t="s">
         <v>531</v>
       </c>
@@ -10371,7 +10374,7 @@
       </c>
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A296" s="77"/>
+      <c r="A296" s="76"/>
       <c r="B296" t="s">
         <v>533</v>
       </c>
@@ -10410,7 +10413,7 @@
       </c>
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A297" s="77"/>
+      <c r="A297" s="76"/>
       <c r="B297" t="s">
         <v>47</v>
       </c>
@@ -10448,7 +10451,7 @@
       </c>
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A298" s="77"/>
+      <c r="A298" s="76"/>
       <c r="B298" t="s">
         <v>39</v>
       </c>
@@ -10486,11 +10489,11 @@
       </c>
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A299" s="77"/>
+      <c r="A299" s="76"/>
       <c r="C299" s="31"/>
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A300" s="77"/>
+      <c r="A300" s="76"/>
       <c r="B300" t="s">
         <v>538</v>
       </c>
@@ -10527,7 +10530,7 @@
       </c>
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A301" s="77"/>
+      <c r="A301" s="76"/>
       <c r="B301" t="s">
         <v>547</v>
       </c>
@@ -10540,7 +10543,7 @@
       </c>
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A302" s="77"/>
+      <c r="A302" s="76"/>
       <c r="B302" t="s">
         <v>526</v>
       </c>
@@ -10582,7 +10585,7 @@
       <c r="L302" s="1"/>
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A303" s="77"/>
+      <c r="A303" s="76"/>
       <c r="B303" t="s">
         <v>534</v>
       </c>
@@ -10623,7 +10626,7 @@
       </c>
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A304" s="77"/>
+      <c r="A304" s="76"/>
       <c r="B304" t="s">
         <v>536</v>
       </c>
@@ -10664,7 +10667,7 @@
       </c>
     </row>
     <row r="305" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A305" s="77"/>
+      <c r="A305" s="76"/>
       <c r="B305" t="s">
         <v>540</v>
       </c>
@@ -10704,7 +10707,7 @@
       </c>
     </row>
     <row r="306" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A306" s="77"/>
+      <c r="A306" s="76"/>
       <c r="B306" t="s">
         <v>543</v>
       </c>
@@ -10745,7 +10748,7 @@
       </c>
     </row>
     <row r="307" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A307" s="77"/>
+      <c r="A307" s="76"/>
       <c r="B307" t="s">
         <v>566</v>
       </c>
@@ -10754,7 +10757,7 @@
       </c>
     </row>
     <row r="308" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A308" s="77"/>
+      <c r="A308" s="76"/>
       <c r="B308" t="s">
         <v>284</v>
       </c>
@@ -10764,7 +10767,7 @@
       </c>
     </row>
     <row r="309" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A309" s="77"/>
+      <c r="A309" s="76"/>
       <c r="B309" t="s">
         <v>565</v>
       </c>
@@ -10777,7 +10780,7 @@
       </c>
     </row>
     <row r="310" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A310" s="77"/>
+      <c r="A310" s="76"/>
       <c r="B310" t="s">
         <v>572</v>
       </c>
@@ -10808,7 +10811,7 @@
       </c>
     </row>
     <row r="311" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A311" s="77"/>
+      <c r="A311" s="76"/>
       <c r="B311" s="32" t="s">
         <v>571</v>
       </c>
@@ -10845,7 +10848,7 @@
       </c>
     </row>
     <row r="312" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A312" s="77"/>
+      <c r="A312" s="76"/>
       <c r="B312" t="s">
         <v>574</v>
       </c>
@@ -10855,7 +10858,7 @@
       </c>
     </row>
     <row r="313" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A313" s="77"/>
+      <c r="A313" s="76"/>
       <c r="B313" t="s">
         <v>575</v>
       </c>
@@ -10865,7 +10868,7 @@
       </c>
     </row>
     <row r="314" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A314" s="77"/>
+      <c r="A314" s="76"/>
       <c r="B314" t="s">
         <v>573</v>
       </c>
@@ -10875,7 +10878,7 @@
       </c>
     </row>
     <row r="315" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A315" s="77"/>
+      <c r="A315" s="76"/>
       <c r="B315" t="s">
         <v>576</v>
       </c>
@@ -10885,7 +10888,7 @@
       </c>
     </row>
     <row r="316" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A316" s="77"/>
+      <c r="A316" s="76"/>
       <c r="B316" t="s">
         <v>577</v>
       </c>
@@ -10895,7 +10898,7 @@
       </c>
     </row>
     <row r="317" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A317" s="77"/>
+      <c r="A317" s="76"/>
       <c r="B317" t="s">
         <v>580</v>
       </c>
@@ -10905,7 +10908,7 @@
       </c>
     </row>
     <row r="318" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A318" s="77"/>
+      <c r="A318" s="76"/>
       <c r="B318" t="s">
         <v>578</v>
       </c>
@@ -10915,7 +10918,7 @@
       </c>
     </row>
     <row r="319" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A319" s="77"/>
+      <c r="A319" s="76"/>
       <c r="B319" t="s">
         <v>578</v>
       </c>
@@ -10925,7 +10928,7 @@
       </c>
     </row>
     <row r="320" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A320" s="77"/>
+      <c r="A320" s="76"/>
       <c r="B320" t="s">
         <v>582</v>
       </c>
@@ -10935,7 +10938,7 @@
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A321" s="77"/>
+      <c r="A321" s="76"/>
       <c r="B321" t="s">
         <v>581</v>
       </c>
@@ -10945,7 +10948,7 @@
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A322" s="77"/>
+      <c r="A322" s="76"/>
       <c r="B322" t="s">
         <v>579</v>
       </c>
@@ -10955,7 +10958,7 @@
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A323" s="77"/>
+      <c r="A323" s="76"/>
       <c r="B323" t="s">
         <v>603</v>
       </c>
@@ -10964,7 +10967,7 @@
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A324" s="77"/>
+      <c r="A324" s="76"/>
       <c r="B324" t="s">
         <v>604</v>
       </c>
@@ -10974,7 +10977,7 @@
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A325" s="77"/>
+      <c r="A325" s="76"/>
       <c r="B325" t="s">
         <v>601</v>
       </c>
@@ -10987,7 +10990,7 @@
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A326" s="77"/>
+      <c r="A326" s="76"/>
       <c r="B326" t="s">
         <v>602</v>
       </c>
@@ -11000,7 +11003,7 @@
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A327" s="77"/>
+      <c r="A327" s="76"/>
       <c r="B327" t="s">
         <v>583</v>
       </c>
@@ -11015,7 +11018,7 @@
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A328" s="77"/>
+      <c r="A328" s="76"/>
       <c r="B328" s="38" t="s">
         <v>585</v>
       </c>
@@ -11028,45 +11031,45 @@
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A329" s="77"/>
+      <c r="A329" s="76"/>
       <c r="C329" s="31"/>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A330" s="77"/>
+      <c r="A330" s="76"/>
       <c r="C330" s="31"/>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A331" s="77"/>
+      <c r="A331" s="76"/>
       <c r="C331" s="31"/>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A332" s="77"/>
+      <c r="A332" s="76"/>
       <c r="C332" s="31"/>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A333" s="77"/>
+      <c r="A333" s="76"/>
       <c r="C333" s="31"/>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A334" s="77"/>
+      <c r="A334" s="76"/>
       <c r="C334" s="31"/>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A335" s="77"/>
+      <c r="A335" s="76"/>
       <c r="C335" s="31"/>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A336" s="77"/>
+      <c r="A336" s="76"/>
       <c r="C336" s="31"/>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A337" s="77"/>
+      <c r="A337" s="76"/>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" s="33"/>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A339" s="77" t="s">
+      <c r="A339" s="76" t="s">
         <v>588</v>
       </c>
       <c r="C339" t="s">
@@ -11078,7 +11081,7 @@
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A340" s="77"/>
+      <c r="A340" s="76"/>
       <c r="C340" t="s">
         <v>255</v>
       </c>
@@ -11088,7 +11091,7 @@
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A341" s="77"/>
+      <c r="A341" s="76"/>
       <c r="C341" t="s">
         <v>256</v>
       </c>
@@ -11098,7 +11101,7 @@
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A342" s="77"/>
+      <c r="A342" s="76"/>
       <c r="C342" t="s">
         <v>257</v>
       </c>
@@ -11108,7 +11111,7 @@
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A343" s="77"/>
+      <c r="A343" s="76"/>
       <c r="C343" t="s">
         <v>258</v>
       </c>
@@ -11118,7 +11121,7 @@
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A344" s="77"/>
+      <c r="A344" s="76"/>
       <c r="C344" t="s">
         <v>259</v>
       </c>
@@ -11128,7 +11131,7 @@
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A345" s="77"/>
+      <c r="A345" s="76"/>
       <c r="C345" t="s">
         <v>260</v>
       </c>
@@ -11138,7 +11141,7 @@
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A346" s="77"/>
+      <c r="A346" s="76"/>
       <c r="C346" t="s">
         <v>261</v>
       </c>
@@ -11148,7 +11151,7 @@
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A347" s="77"/>
+      <c r="A347" s="76"/>
       <c r="B347" t="s">
         <v>262</v>
       </c>
@@ -11157,7 +11160,7 @@
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A348" s="77"/>
+      <c r="A348" s="76"/>
       <c r="B348" t="s">
         <v>264</v>
       </c>
@@ -11167,7 +11170,7 @@
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A349" s="77"/>
+      <c r="A349" s="76"/>
       <c r="C349" t="s">
         <v>265</v>
       </c>
@@ -11177,10 +11180,10 @@
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A350" s="77"/>
+      <c r="A350" s="76"/>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A351" s="77"/>
+      <c r="A351" s="76"/>
       <c r="B351" t="s">
         <v>266</v>
       </c>
@@ -11190,7 +11193,7 @@
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A352" s="77"/>
+      <c r="A352" s="76"/>
       <c r="B352" t="s">
         <v>329</v>
       </c>
@@ -11200,7 +11203,7 @@
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A353" s="77"/>
+      <c r="A353" s="76"/>
       <c r="B353" t="s">
         <v>274</v>
       </c>
@@ -11210,7 +11213,7 @@
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A354" s="77"/>
+      <c r="A354" s="76"/>
       <c r="B354" t="s">
         <v>273</v>
       </c>
@@ -11219,10 +11222,10 @@
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A355" s="77"/>
+      <c r="A355" s="76"/>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A356" s="77"/>
+      <c r="A356" s="76"/>
       <c r="B356" t="s">
         <v>271</v>
       </c>
@@ -11232,7 +11235,7 @@
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A357" s="77"/>
+      <c r="A357" s="76"/>
       <c r="B357" t="s">
         <v>270</v>
       </c>
@@ -11244,7 +11247,7 @@
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A358" s="77"/>
+      <c r="A358" s="76"/>
       <c r="C358" t="s">
         <v>268</v>
       </c>
@@ -11254,7 +11257,7 @@
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A359" s="77"/>
+      <c r="A359" s="76"/>
       <c r="C359" t="s">
         <v>272</v>
       </c>
@@ -11264,13 +11267,13 @@
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A360" s="77"/>
+      <c r="A360" s="76"/>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" s="49"/>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A362" s="76" t="s">
+      <c r="A362" s="75" t="s">
         <v>587</v>
       </c>
       <c r="B362" t="s">
@@ -11282,7 +11285,7 @@
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A363" s="76"/>
+      <c r="A363" s="75"/>
       <c r="B363" t="s">
         <v>589</v>
       </c>
@@ -11291,7 +11294,7 @@
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A364" s="76"/>
+      <c r="A364" s="75"/>
       <c r="B364" t="s">
         <v>590</v>
       </c>
@@ -11300,7 +11303,7 @@
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A365" s="76"/>
+      <c r="A365" s="75"/>
       <c r="B365" t="s">
         <v>591</v>
       </c>
@@ -11310,7 +11313,7 @@
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A366" s="76"/>
+      <c r="A366" s="75"/>
       <c r="B366" t="s">
         <v>595</v>
       </c>
@@ -11320,7 +11323,7 @@
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A367" s="76"/>
+      <c r="A367" s="75"/>
       <c r="B367" t="s">
         <v>593</v>
       </c>
@@ -11330,7 +11333,7 @@
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A368" s="76"/>
+      <c r="A368" s="75"/>
       <c r="B368" t="s">
         <v>594</v>
       </c>
@@ -11340,7 +11343,7 @@
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A369" s="76"/>
+      <c r="A369" s="75"/>
       <c r="B369" t="s">
         <v>596</v>
       </c>
@@ -11350,7 +11353,7 @@
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A370" s="76"/>
+      <c r="A370" s="75"/>
       <c r="C370" t="s">
         <v>597</v>
       </c>
@@ -11359,7 +11362,7 @@
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A371" s="76"/>
+      <c r="A371" s="75"/>
       <c r="C371" t="s">
         <v>598</v>
       </c>
@@ -11369,7 +11372,7 @@
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A372" s="76"/>
+      <c r="A372" s="75"/>
       <c r="C372" t="s">
         <v>599</v>
       </c>
@@ -11379,7 +11382,7 @@
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A373" s="76"/>
+      <c r="A373" s="75"/>
       <c r="C373" t="s">
         <v>600</v>
       </c>
@@ -11389,13 +11392,13 @@
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A374" s="76"/>
+      <c r="A374" s="75"/>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" s="50"/>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A376" s="76" t="s">
+      <c r="A376" s="75" t="s">
         <v>564</v>
       </c>
       <c r="C376" t="s">
@@ -11403,7 +11406,7 @@
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A377" s="76"/>
+      <c r="A377" s="75"/>
       <c r="B377" t="s">
         <v>38</v>
       </c>
@@ -11416,7 +11419,7 @@
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A378" s="76"/>
+      <c r="A378" s="75"/>
       <c r="B378" t="s">
         <v>37</v>
       </c>
@@ -11429,7 +11432,7 @@
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A379" s="76"/>
+      <c r="A379" s="75"/>
       <c r="B379" t="s">
         <v>1040</v>
       </c>
@@ -11441,7 +11444,7 @@
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A380" s="76"/>
+      <c r="A380" s="75"/>
       <c r="C380" t="s">
         <v>1039</v>
       </c>
@@ -11451,7 +11454,7 @@
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A381" s="76"/>
+      <c r="A381" s="75"/>
       <c r="B381" t="s">
         <v>1041</v>
       </c>
@@ -11464,7 +11467,7 @@
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A382" s="76"/>
+      <c r="A382" s="75"/>
       <c r="C382" t="s">
         <v>276</v>
       </c>
@@ -11476,7 +11479,7 @@
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A383" s="76"/>
+      <c r="A383" s="75"/>
       <c r="B383" t="s">
         <v>1042</v>
       </c>
@@ -11488,7 +11491,7 @@
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A384" s="76"/>
+      <c r="A384" s="75"/>
       <c r="C384" t="s">
         <v>1051</v>
       </c>
@@ -11500,7 +11503,7 @@
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A385" s="76"/>
+      <c r="A385" s="75"/>
       <c r="B385" t="s">
         <v>520</v>
       </c>
@@ -11513,7 +11516,7 @@
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A386" s="76"/>
+      <c r="A386" s="75"/>
       <c r="B386" t="s">
         <v>1049</v>
       </c>
@@ -11526,7 +11529,7 @@
       </c>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A387" s="76"/>
+      <c r="A387" s="75"/>
       <c r="B387" t="s">
         <v>1050</v>
       </c>
@@ -11539,7 +11542,7 @@
       </c>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A388" s="76"/>
+      <c r="A388" s="75"/>
       <c r="B388" t="s">
         <v>157</v>
       </c>
@@ -11552,7 +11555,7 @@
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A389" s="76"/>
+      <c r="A389" s="75"/>
       <c r="B389" t="s">
         <v>324</v>
       </c>
@@ -11564,7 +11567,7 @@
       </c>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A390" s="76"/>
+      <c r="A390" s="75"/>
       <c r="B390" t="s">
         <v>1043</v>
       </c>
@@ -11577,7 +11580,7 @@
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A391" s="76"/>
+      <c r="A391" s="75"/>
       <c r="B391" t="s">
         <v>1062</v>
       </c>
@@ -11593,7 +11596,7 @@
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A392" s="76"/>
+      <c r="A392" s="75"/>
       <c r="B392" t="s">
         <v>1064</v>
       </c>
@@ -11606,7 +11609,7 @@
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A393" s="76"/>
+      <c r="A393" s="75"/>
       <c r="B393" t="s">
         <v>1038</v>
       </c>
@@ -11618,7 +11621,7 @@
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A394" s="76"/>
+      <c r="A394" s="75"/>
       <c r="C394" t="s">
         <v>1044</v>
       </c>
@@ -11631,7 +11634,7 @@
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A395" s="76"/>
+      <c r="A395" s="75"/>
       <c r="C395" t="s">
         <v>1045</v>
       </c>
@@ -11644,7 +11647,7 @@
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A396" s="76"/>
+      <c r="A396" s="75"/>
       <c r="C396" t="s">
         <v>1047</v>
       </c>
@@ -11657,7 +11660,7 @@
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A397" s="76"/>
+      <c r="A397" s="75"/>
       <c r="C397" t="s">
         <v>1046</v>
       </c>
@@ -11670,7 +11673,7 @@
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A398" s="76"/>
+      <c r="A398" s="75"/>
       <c r="B398" t="s">
         <v>1067</v>
       </c>
@@ -11686,7 +11689,7 @@
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A399" s="76"/>
+      <c r="A399" s="75"/>
       <c r="B399" t="s">
         <v>1067</v>
       </c>
@@ -11702,7 +11705,7 @@
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A400" s="76"/>
+      <c r="A400" s="75"/>
       <c r="C400" t="s">
         <v>1048</v>
       </c>
@@ -11715,7 +11718,7 @@
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A401" s="76"/>
+      <c r="A401" s="75"/>
       <c r="C401" t="s">
         <v>1052</v>
       </c>
@@ -11728,7 +11731,7 @@
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A402" s="76"/>
+      <c r="A402" s="75"/>
       <c r="C402" t="s">
         <v>1065</v>
       </c>
@@ -11739,7 +11742,7 @@
       <c r="E402" s="8"/>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A403" s="76"/>
+      <c r="A403" s="75"/>
       <c r="C403" t="s">
         <v>1054</v>
       </c>
@@ -11750,7 +11753,7 @@
       <c r="E403" s="8"/>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A404" s="76"/>
+      <c r="A404" s="75"/>
       <c r="C404" t="s">
         <v>1053</v>
       </c>
@@ -11761,7 +11764,7 @@
       <c r="E404" s="8"/>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A405" s="76"/>
+      <c r="A405" s="75"/>
       <c r="C405" t="s">
         <v>1055</v>
       </c>
@@ -11772,7 +11775,7 @@
       <c r="E405" s="8"/>
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A406" s="76"/>
+      <c r="A406" s="75"/>
       <c r="C406" t="s">
         <v>1056</v>
       </c>
@@ -11783,7 +11786,7 @@
       <c r="E406" s="8"/>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A407" s="76"/>
+      <c r="A407" s="75"/>
       <c r="C407" t="s">
         <v>1057</v>
       </c>
@@ -11794,7 +11797,7 @@
       <c r="E407" s="8"/>
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A408" s="76"/>
+      <c r="A408" s="75"/>
       <c r="C408" t="s">
         <v>1058</v>
       </c>
@@ -11807,7 +11810,7 @@
       </c>
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A409" s="76"/>
+      <c r="A409" s="75"/>
       <c r="C409" t="s">
         <v>1059</v>
       </c>
@@ -11820,7 +11823,7 @@
       </c>
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A410" s="76"/>
+      <c r="A410" s="75"/>
       <c r="C410" t="s">
         <v>1060</v>
       </c>
@@ -11833,7 +11836,7 @@
       </c>
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A411" s="76"/>
+      <c r="A411" s="75"/>
       <c r="C411" t="s">
         <v>1061</v>
       </c>
@@ -11846,7 +11849,7 @@
       </c>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A412" s="76"/>
+      <c r="A412" s="75"/>
       <c r="E412" s="8"/>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
@@ -11854,7 +11857,7 @@
       <c r="E413" s="8"/>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A414" s="76" t="s">
+      <c r="A414" s="75" t="s">
         <v>883</v>
       </c>
       <c r="C414" t="s">
@@ -11867,7 +11870,7 @@
       <c r="E414" s="8"/>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A415" s="76"/>
+      <c r="A415" s="75"/>
       <c r="B415" t="s">
         <v>47</v>
       </c>
@@ -11880,7 +11883,7 @@
       </c>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A416" s="76"/>
+      <c r="A416" s="75"/>
       <c r="B416" t="s">
         <v>877</v>
       </c>
@@ -11893,7 +11896,7 @@
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A417" s="76"/>
+      <c r="A417" s="75"/>
       <c r="B417" t="s">
         <v>40</v>
       </c>
@@ -11906,7 +11909,7 @@
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A418" s="76"/>
+      <c r="A418" s="75"/>
       <c r="B418" t="s">
         <v>875</v>
       </c>
@@ -11919,7 +11922,7 @@
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A419" s="76"/>
+      <c r="A419" s="75"/>
       <c r="B419" t="s">
         <v>39</v>
       </c>
@@ -11928,7 +11931,7 @@
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A420" s="76"/>
+      <c r="A420" s="75"/>
       <c r="B420" t="s">
         <v>288</v>
       </c>
@@ -11940,7 +11943,7 @@
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A421" s="76"/>
+      <c r="A421" s="75"/>
       <c r="B421" t="s">
         <v>906</v>
       </c>
@@ -11956,11 +11959,11 @@
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A422" s="76"/>
+      <c r="A422" s="75"/>
       <c r="E422" s="8"/>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A423" s="76"/>
+      <c r="A423" s="75"/>
       <c r="B423" t="s">
         <v>287</v>
       </c>
@@ -11970,7 +11973,7 @@
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A424" s="76"/>
+      <c r="A424" s="75"/>
       <c r="B424" t="s">
         <v>290</v>
       </c>
@@ -11983,7 +11986,7 @@
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A425" s="76"/>
+      <c r="A425" s="75"/>
       <c r="B425" t="s">
         <v>291</v>
       </c>
@@ -11996,7 +11999,7 @@
       </c>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A426" s="76"/>
+      <c r="A426" s="75"/>
       <c r="B426" t="s">
         <v>308</v>
       </c>
@@ -12008,7 +12011,7 @@
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A427" s="76"/>
+      <c r="A427" s="75"/>
       <c r="C427" t="s">
         <v>325</v>
       </c>
@@ -12018,7 +12021,7 @@
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A428" s="76"/>
+      <c r="A428" s="75"/>
       <c r="B428" t="s">
         <v>292</v>
       </c>
@@ -12028,7 +12031,7 @@
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A429" s="76"/>
+      <c r="A429" s="75"/>
       <c r="B429" t="s">
         <v>293</v>
       </c>
@@ -12038,7 +12041,7 @@
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A430" s="76"/>
+      <c r="A430" s="75"/>
       <c r="B430" t="s">
         <v>294</v>
       </c>
@@ -12053,7 +12056,7 @@
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A431" s="76"/>
+      <c r="A431" s="75"/>
       <c r="B431" t="s">
         <v>296</v>
       </c>
@@ -12066,7 +12069,7 @@
       </c>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A432" s="76"/>
+      <c r="A432" s="75"/>
       <c r="B432" t="s">
         <v>298</v>
       </c>
@@ -12081,7 +12084,7 @@
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A433" s="76"/>
+      <c r="A433" s="75"/>
       <c r="B433" t="s">
         <v>299</v>
       </c>
@@ -12093,7 +12096,7 @@
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A434" s="76"/>
+      <c r="A434" s="75"/>
       <c r="B434" t="s">
         <v>220</v>
       </c>
@@ -12109,7 +12112,7 @@
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A435" s="76"/>
+      <c r="A435" s="75"/>
       <c r="B435" t="s">
         <v>304</v>
       </c>
@@ -12125,7 +12128,7 @@
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A436" s="76"/>
+      <c r="A436" s="75"/>
       <c r="B436" t="s">
         <v>305</v>
       </c>
@@ -12141,7 +12144,7 @@
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A437" s="76"/>
+      <c r="A437" s="75"/>
       <c r="C437" t="s">
         <v>300</v>
       </c>
@@ -12154,7 +12157,7 @@
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A438" s="76"/>
+      <c r="A438" s="75"/>
       <c r="C438" t="s">
         <v>302</v>
       </c>
@@ -12166,7 +12169,7 @@
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A439" s="76"/>
+      <c r="A439" s="75"/>
       <c r="C439" t="s">
         <v>303</v>
       </c>
@@ -12179,7 +12182,7 @@
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A440" s="76"/>
+      <c r="A440" s="75"/>
       <c r="C440" t="s">
         <v>301</v>
       </c>
@@ -12189,7 +12192,7 @@
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A441" s="76"/>
+      <c r="A441" s="75"/>
       <c r="B441" t="s">
         <v>327</v>
       </c>
@@ -12205,7 +12208,7 @@
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A442" s="76"/>
+      <c r="A442" s="75"/>
       <c r="B442" t="s">
         <v>880</v>
       </c>
@@ -12221,7 +12224,7 @@
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A443" s="76"/>
+      <c r="A443" s="75"/>
       <c r="B443" t="s">
         <v>879</v>
       </c>
@@ -12234,7 +12237,7 @@
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A444" s="76"/>
+      <c r="A444" s="75"/>
       <c r="B444" t="s">
         <v>882</v>
       </c>
@@ -12247,7 +12250,7 @@
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A445" s="76"/>
+      <c r="A445" s="75"/>
       <c r="B445" t="s">
         <v>322</v>
       </c>
@@ -12260,7 +12263,7 @@
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A446" s="76"/>
+      <c r="A446" s="75"/>
       <c r="B446" t="s">
         <v>311</v>
       </c>
@@ -12272,7 +12275,7 @@
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A447" s="76"/>
+      <c r="A447" s="75"/>
       <c r="B447" t="s">
         <v>314</v>
       </c>
@@ -12284,7 +12287,7 @@
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A448" s="76"/>
+      <c r="A448" s="75"/>
       <c r="B448" t="s">
         <v>315</v>
       </c>
@@ -12299,7 +12302,7 @@
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A449" s="76"/>
+      <c r="A449" s="75"/>
       <c r="B449" t="s">
         <v>312</v>
       </c>
@@ -12315,7 +12318,7 @@
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A450" s="76"/>
+      <c r="A450" s="75"/>
       <c r="C450" t="s">
         <v>326</v>
       </c>
@@ -12328,7 +12331,7 @@
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A451" s="76"/>
+      <c r="A451" s="75"/>
       <c r="B451" t="s">
         <v>317</v>
       </c>
@@ -12340,7 +12343,7 @@
       </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A452" s="76"/>
+      <c r="A452" s="75"/>
       <c r="C452" t="s">
         <v>319</v>
       </c>
@@ -12350,7 +12353,7 @@
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A453" s="76"/>
+      <c r="A453" s="75"/>
       <c r="C453" t="s">
         <v>318</v>
       </c>
@@ -12360,7 +12363,7 @@
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A454" s="76"/>
+      <c r="A454" s="75"/>
       <c r="B454" t="s">
         <v>320</v>
       </c>
@@ -12380,7 +12383,7 @@
       <c r="D455" s="27"/>
     </row>
     <row r="456" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A456" s="76" t="s">
+      <c r="A456" s="75" t="s">
         <v>974</v>
       </c>
       <c r="C456" t="s">
@@ -12393,7 +12396,7 @@
       <c r="E456" s="8"/>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A457" s="76"/>
+      <c r="A457" s="75"/>
       <c r="B457" t="s">
         <v>47</v>
       </c>
@@ -12406,7 +12409,7 @@
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A458" s="76"/>
+      <c r="A458" s="75"/>
       <c r="B458" t="s">
         <v>877</v>
       </c>
@@ -12419,7 +12422,7 @@
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A459" s="76"/>
+      <c r="A459" s="75"/>
       <c r="B459" t="s">
         <v>40</v>
       </c>
@@ -12432,11 +12435,11 @@
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A460" s="76"/>
+      <c r="A460" s="75"/>
       <c r="D460" s="53"/>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A461" s="76"/>
+      <c r="A461" s="75"/>
       <c r="B461" t="s">
         <v>39</v>
       </c>
@@ -12445,7 +12448,7 @@
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A462" s="76"/>
+      <c r="A462" s="75"/>
       <c r="B462" t="s">
         <v>288</v>
       </c>
@@ -12457,7 +12460,7 @@
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A463" s="76"/>
+      <c r="A463" s="75"/>
       <c r="B463" t="s">
         <v>906</v>
       </c>
@@ -12473,12 +12476,12 @@
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A464" s="76"/>
+      <c r="A464" s="75"/>
       <c r="D464" s="53"/>
       <c r="E464" s="8"/>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A465" s="76"/>
+      <c r="A465" s="75"/>
       <c r="B465" t="s">
         <v>287</v>
       </c>
@@ -12488,7 +12491,7 @@
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A466" s="76"/>
+      <c r="A466" s="75"/>
       <c r="B466" t="s">
         <v>290</v>
       </c>
@@ -12501,7 +12504,7 @@
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A467" s="76"/>
+      <c r="A467" s="75"/>
       <c r="B467" t="s">
         <v>971</v>
       </c>
@@ -12511,7 +12514,7 @@
       <c r="D467" s="51"/>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A468" s="76"/>
+      <c r="A468" s="75"/>
       <c r="C468" t="s">
         <v>972</v>
       </c>
@@ -12521,7 +12524,7 @@
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A469" s="76"/>
+      <c r="A469" s="75"/>
       <c r="B469" t="s">
         <v>291</v>
       </c>
@@ -12534,7 +12537,7 @@
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A470" s="76"/>
+      <c r="A470" s="75"/>
       <c r="B470" t="s">
         <v>308</v>
       </c>
@@ -12546,7 +12549,7 @@
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A471" s="76"/>
+      <c r="A471" s="75"/>
       <c r="C471" t="s">
         <v>325</v>
       </c>
@@ -12556,7 +12559,7 @@
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A472" s="76"/>
+      <c r="A472" s="75"/>
       <c r="B472" t="s">
         <v>292</v>
       </c>
@@ -12566,7 +12569,7 @@
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A473" s="76"/>
+      <c r="A473" s="75"/>
       <c r="B473" t="s">
         <v>293</v>
       </c>
@@ -12576,7 +12579,7 @@
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A474" s="76"/>
+      <c r="A474" s="75"/>
       <c r="B474" t="s">
         <v>294</v>
       </c>
@@ -12591,7 +12594,7 @@
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A475" s="76"/>
+      <c r="A475" s="75"/>
       <c r="B475" t="s">
         <v>296</v>
       </c>
@@ -12604,7 +12607,7 @@
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A476" s="76"/>
+      <c r="A476" s="75"/>
       <c r="B476" t="s">
         <v>922</v>
       </c>
@@ -12616,7 +12619,7 @@
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A477" s="76"/>
+      <c r="A477" s="75"/>
       <c r="B477" s="35" t="s">
         <v>909</v>
       </c>
@@ -12631,7 +12634,7 @@
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A478" s="76"/>
+      <c r="A478" s="75"/>
       <c r="B478" s="35" t="s">
         <v>911</v>
       </c>
@@ -12647,7 +12650,7 @@
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A479" s="76"/>
+      <c r="A479" s="75"/>
       <c r="B479" s="35" t="s">
         <v>910</v>
       </c>
@@ -12666,7 +12669,7 @@
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A480" s="76"/>
+      <c r="A480" s="75"/>
       <c r="B480" s="35" t="s">
         <v>912</v>
       </c>
@@ -12682,7 +12685,7 @@
       </c>
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A481" s="76"/>
+      <c r="A481" s="75"/>
       <c r="B481" s="35"/>
       <c r="C481" t="s">
         <v>924</v>
@@ -12693,7 +12696,7 @@
       </c>
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A482" s="76"/>
+      <c r="A482" s="75"/>
       <c r="B482" s="35" t="s">
         <v>935</v>
       </c>
@@ -12709,7 +12712,7 @@
       </c>
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A483" s="76"/>
+      <c r="A483" s="75"/>
       <c r="B483" s="35" t="s">
         <v>937</v>
       </c>
@@ -12725,7 +12728,7 @@
       </c>
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A484" s="76"/>
+      <c r="A484" s="75"/>
       <c r="B484" s="35" t="s">
         <v>919</v>
       </c>
@@ -12746,7 +12749,7 @@
       </c>
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A485" s="76"/>
+      <c r="A485" s="75"/>
       <c r="B485" t="s">
         <v>886</v>
       </c>
@@ -12762,7 +12765,7 @@
       </c>
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A486" s="76"/>
+      <c r="A486" s="75"/>
       <c r="B486" t="s">
         <v>921</v>
       </c>
@@ -12778,7 +12781,7 @@
       </c>
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A487" s="76"/>
+      <c r="A487" s="75"/>
       <c r="B487" t="s">
         <v>1114</v>
       </c>
@@ -12793,7 +12796,7 @@
       </c>
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A488" s="76"/>
+      <c r="A488" s="75"/>
       <c r="B488" t="s">
         <v>1116</v>
       </c>
@@ -12808,7 +12811,7 @@
       </c>
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A489" s="76"/>
+      <c r="A489" s="75"/>
       <c r="C489" t="s">
         <v>1125</v>
       </c>
@@ -12820,7 +12823,7 @@
       </c>
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A490" s="76"/>
+      <c r="A490" s="75"/>
       <c r="B490" t="s">
         <v>1126</v>
       </c>
@@ -12834,7 +12837,7 @@
       <c r="E490" s="8"/>
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A491" s="76"/>
+      <c r="A491" s="75"/>
       <c r="B491" t="s">
         <v>1118</v>
       </c>
@@ -12847,7 +12850,7 @@
       <c r="E491" s="8"/>
     </row>
     <row r="492" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A492" s="76"/>
+      <c r="A492" s="75"/>
       <c r="B492" t="s">
         <v>299</v>
       </c>
@@ -12861,7 +12864,7 @@
       <c r="H492" s="52"/>
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A493" s="76"/>
+      <c r="A493" s="75"/>
       <c r="B493" t="s">
         <v>1122</v>
       </c>
@@ -12876,7 +12879,7 @@
       <c r="H493" s="52"/>
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A494" s="76"/>
+      <c r="A494" s="75"/>
       <c r="B494" t="s">
         <v>1120</v>
       </c>
@@ -12893,7 +12896,7 @@
       <c r="H494" s="52"/>
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A495" s="76"/>
+      <c r="A495" s="75"/>
       <c r="C495" t="s">
         <v>1124</v>
       </c>
@@ -12901,11 +12904,11 @@
       <c r="H495" s="52"/>
     </row>
     <row r="496" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A496" s="76"/>
+      <c r="A496" s="75"/>
       <c r="H496" s="52"/>
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A497" s="76"/>
+      <c r="A497" s="75"/>
       <c r="C497" t="s">
         <v>302</v>
       </c>
@@ -12918,7 +12921,7 @@
       <c r="H497" s="52"/>
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A498" s="76"/>
+      <c r="A498" s="75"/>
       <c r="C498" t="s">
         <v>303</v>
       </c>
@@ -12932,7 +12935,7 @@
       <c r="H498" s="52"/>
     </row>
     <row r="499" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A499" s="76"/>
+      <c r="A499" s="75"/>
       <c r="C499" t="s">
         <v>1128</v>
       </c>
@@ -12943,7 +12946,7 @@
       <c r="H499" s="52"/>
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A500" s="76"/>
+      <c r="A500" s="75"/>
       <c r="B500" t="s">
         <v>941</v>
       </c>
@@ -12955,7 +12958,7 @@
       </c>
     </row>
     <row r="501" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A501" s="76"/>
+      <c r="A501" s="75"/>
       <c r="B501" t="s">
         <v>950</v>
       </c>
@@ -12970,7 +12973,7 @@
       </c>
     </row>
     <row r="502" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A502" s="76"/>
+      <c r="A502" s="75"/>
       <c r="B502" t="s">
         <v>1080</v>
       </c>
@@ -12988,7 +12991,7 @@
       </c>
     </row>
     <row r="503" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A503" s="76"/>
+      <c r="A503" s="75"/>
       <c r="B503" t="s">
         <v>940</v>
       </c>
@@ -13004,7 +13007,7 @@
       </c>
     </row>
     <row r="504" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A504" s="76"/>
+      <c r="A504" s="75"/>
       <c r="B504" t="s">
         <v>1082</v>
       </c>
@@ -13015,7 +13018,7 @@
       <c r="E504" s="8"/>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A505" s="76"/>
+      <c r="A505" s="75"/>
       <c r="B505" t="s">
         <v>1083</v>
       </c>
@@ -13026,7 +13029,7 @@
       <c r="E505" s="8"/>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A506" s="76"/>
+      <c r="A506" s="75"/>
       <c r="C506" t="s">
         <v>1084</v>
       </c>
@@ -13037,7 +13040,7 @@
       <c r="E506" s="8"/>
     </row>
     <row r="507" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A507" s="76"/>
+      <c r="A507" s="75"/>
       <c r="B507" t="s">
         <v>943</v>
       </c>
@@ -13052,7 +13055,7 @@
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A508" s="76"/>
+      <c r="A508" s="75"/>
       <c r="B508" t="s">
         <v>946</v>
       </c>
@@ -13068,7 +13071,7 @@
       </c>
     </row>
     <row r="509" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A509" s="76"/>
+      <c r="A509" s="75"/>
       <c r="B509" t="s">
         <v>947</v>
       </c>
@@ -13081,7 +13084,7 @@
       </c>
     </row>
     <row r="510" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A510" s="76"/>
+      <c r="A510" s="75"/>
       <c r="B510" t="s">
         <v>949</v>
       </c>
@@ -13093,7 +13096,7 @@
       </c>
     </row>
     <row r="511" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A511" s="76"/>
+      <c r="A511" s="75"/>
       <c r="C511" t="s">
         <v>945</v>
       </c>
@@ -13104,7 +13107,7 @@
       <c r="E511" s="8"/>
     </row>
     <row r="512" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A512" s="76"/>
+      <c r="A512" s="75"/>
       <c r="B512" t="s">
         <v>948</v>
       </c>
@@ -13116,7 +13119,7 @@
       </c>
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A513" s="76"/>
+      <c r="A513" s="75"/>
       <c r="C513" t="s">
         <v>951</v>
       </c>
@@ -13127,7 +13130,7 @@
       <c r="E513" s="8"/>
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A514" s="76"/>
+      <c r="A514" s="75"/>
       <c r="B514" t="s">
         <v>889</v>
       </c>
@@ -13143,7 +13146,7 @@
       </c>
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A515" s="76"/>
+      <c r="A515" s="75"/>
       <c r="B515" t="s">
         <v>890</v>
       </c>
@@ -13159,7 +13162,7 @@
       </c>
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A516" s="76"/>
+      <c r="A516" s="75"/>
       <c r="B516" t="s">
         <v>891</v>
       </c>
@@ -13175,7 +13178,7 @@
       </c>
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A517" s="76"/>
+      <c r="A517" s="75"/>
       <c r="B517" t="s">
         <v>892</v>
       </c>
@@ -13191,7 +13194,7 @@
       </c>
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A518" s="76"/>
+      <c r="A518" s="75"/>
       <c r="B518" t="s">
         <v>893</v>
       </c>
@@ -13207,7 +13210,7 @@
       </c>
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A519" s="76"/>
+      <c r="A519" s="75"/>
       <c r="B519" t="s">
         <v>894</v>
       </c>
@@ -13223,19 +13226,19 @@
       </c>
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A520" s="76"/>
+      <c r="A520" s="75"/>
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A521" s="76"/>
+      <c r="A521" s="75"/>
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A522" s="76"/>
+      <c r="A522" s="75"/>
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A523" s="76"/>
+      <c r="A523" s="75"/>
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A524" s="76"/>
+      <c r="A524" s="75"/>
       <c r="B524" t="s">
         <v>953</v>
       </c>
@@ -13248,7 +13251,7 @@
       </c>
     </row>
     <row r="525" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A525" s="76"/>
+      <c r="A525" s="75"/>
       <c r="B525" t="s">
         <v>954</v>
       </c>
@@ -13266,7 +13269,7 @@
       </c>
     </row>
     <row r="526" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A526" s="76"/>
+      <c r="A526" s="75"/>
       <c r="B526" t="s">
         <v>955</v>
       </c>
@@ -13281,7 +13284,7 @@
       </c>
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A527" s="76"/>
+      <c r="A527" s="75"/>
       <c r="B527" t="s">
         <v>968</v>
       </c>
@@ -13297,7 +13300,7 @@
       </c>
     </row>
     <row r="528" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A528" s="76"/>
+      <c r="A528" s="75"/>
       <c r="B528" t="s">
         <v>900</v>
       </c>
@@ -13313,14 +13316,14 @@
       </c>
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A529" s="76"/>
+      <c r="A529" s="75"/>
       <c r="D529" s="54"/>
       <c r="E529" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A530" s="76"/>
+      <c r="A530" s="75"/>
       <c r="B530" t="s">
         <v>960</v>
       </c>
@@ -13338,7 +13341,7 @@
       </c>
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A531" s="76"/>
+      <c r="A531" s="75"/>
       <c r="B531" t="s">
         <v>959</v>
       </c>
@@ -13353,7 +13356,7 @@
       </c>
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A532" s="76"/>
+      <c r="A532" s="75"/>
       <c r="B532" t="s">
         <v>965</v>
       </c>
@@ -13369,7 +13372,7 @@
       </c>
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A533" s="76"/>
+      <c r="A533" s="75"/>
       <c r="B533" t="s">
         <v>969</v>
       </c>
@@ -13384,7 +13387,7 @@
       </c>
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A534" s="76"/>
+      <c r="A534" s="75"/>
       <c r="B534" t="s">
         <v>963</v>
       </c>
@@ -13399,7 +13402,7 @@
       </c>
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A535" s="76"/>
+      <c r="A535" s="75"/>
       <c r="B535" t="s">
         <v>970</v>
       </c>
@@ -13409,7 +13412,7 @@
       </c>
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A536" s="76"/>
+      <c r="A536" s="75"/>
       <c r="B536" t="s">
         <v>964</v>
       </c>
@@ -13419,7 +13422,7 @@
       </c>
     </row>
     <row r="537" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A537" s="76"/>
+      <c r="A537" s="75"/>
       <c r="B537" t="s">
         <v>880</v>
       </c>
@@ -13432,7 +13435,7 @@
       </c>
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A538" s="76"/>
+      <c r="A538" s="75"/>
       <c r="B538" t="s">
         <v>879</v>
       </c>
@@ -13445,7 +13448,7 @@
       </c>
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A539" s="76"/>
+      <c r="A539" s="75"/>
       <c r="B539" t="s">
         <v>899</v>
       </c>
@@ -13458,7 +13461,7 @@
       </c>
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A540" s="76"/>
+      <c r="A540" s="75"/>
       <c r="B540" t="s">
         <v>901</v>
       </c>
@@ -13474,7 +13477,7 @@
       </c>
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A541" s="76"/>
+      <c r="A541" s="75"/>
       <c r="B541" t="s">
         <v>903</v>
       </c>
@@ -13490,7 +13493,7 @@
       </c>
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A542" s="76"/>
+      <c r="A542" s="75"/>
       <c r="B542" t="s">
         <v>311</v>
       </c>
@@ -13502,7 +13505,7 @@
       </c>
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A543" s="76"/>
+      <c r="A543" s="75"/>
       <c r="B543" t="s">
         <v>314</v>
       </c>
@@ -13514,7 +13517,7 @@
       </c>
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A544" s="76"/>
+      <c r="A544" s="75"/>
       <c r="B544" t="s">
         <v>315</v>
       </c>
@@ -13529,7 +13532,7 @@
       </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A545" s="76"/>
+      <c r="A545" s="75"/>
       <c r="B545" t="s">
         <v>312</v>
       </c>
@@ -13545,7 +13548,7 @@
       </c>
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A546" s="76"/>
+      <c r="A546" s="75"/>
       <c r="C546" t="s">
         <v>326</v>
       </c>
@@ -13558,7 +13561,7 @@
       </c>
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A547" s="76"/>
+      <c r="A547" s="75"/>
       <c r="B547" t="s">
         <v>317</v>
       </c>
@@ -13570,7 +13573,7 @@
       </c>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A548" s="76"/>
+      <c r="A548" s="75"/>
       <c r="C548" t="s">
         <v>319</v>
       </c>
@@ -13580,7 +13583,7 @@
       </c>
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A549" s="76"/>
+      <c r="A549" s="75"/>
       <c r="C549" t="s">
         <v>318</v>
       </c>
@@ -13590,7 +13593,7 @@
       </c>
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A550" s="76"/>
+      <c r="A550" s="75"/>
       <c r="B550" t="s">
         <v>320</v>
       </c>
@@ -13606,7 +13609,7 @@
       </c>
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A551" s="76"/>
+      <c r="A551" s="75"/>
       <c r="B551" s="35" t="s">
         <v>916</v>
       </c>
@@ -13618,7 +13621,7 @@
       </c>
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A552" s="76"/>
+      <c r="A552" s="75"/>
       <c r="B552" s="35" t="s">
         <v>930</v>
       </c>
@@ -13631,7 +13634,7 @@
       </c>
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A553" s="76"/>
+      <c r="A553" s="75"/>
       <c r="B553" t="s">
         <v>925</v>
       </c>
@@ -13643,7 +13646,7 @@
       </c>
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A554" s="76"/>
+      <c r="A554" s="75"/>
       <c r="B554" s="35"/>
       <c r="C554" t="s">
         <v>933</v>
@@ -13654,7 +13657,7 @@
       </c>
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A555" s="76"/>
+      <c r="A555" s="75"/>
       <c r="B555" t="s">
         <v>929</v>
       </c>
@@ -13663,7 +13666,7 @@
       </c>
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A556" s="76"/>
+      <c r="A556" s="75"/>
       <c r="B556" t="s">
         <v>927</v>
       </c>
@@ -13676,7 +13679,7 @@
       </c>
     </row>
     <row r="557" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A557" s="76"/>
+      <c r="A557" s="75"/>
       <c r="B557" s="35" t="s">
         <v>931</v>
       </c>
@@ -13689,7 +13692,7 @@
       </c>
     </row>
     <row r="558" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A558" s="76"/>
+      <c r="A558" s="75"/>
       <c r="C558" t="s">
         <v>934</v>
       </c>
@@ -13699,11 +13702,11 @@
       </c>
     </row>
     <row r="559" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A559" s="76"/>
+      <c r="A559" s="75"/>
       <c r="D559" s="51"/>
     </row>
     <row r="560" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A560" s="76"/>
+      <c r="A560" s="75"/>
       <c r="B560" s="35" t="s">
         <v>1101</v>
       </c>
@@ -13716,7 +13719,7 @@
       </c>
     </row>
     <row r="561" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A561" s="76"/>
+      <c r="A561" s="75"/>
       <c r="B561" s="35" t="s">
         <v>1103</v>
       </c>
@@ -13729,7 +13732,7 @@
       </c>
     </row>
     <row r="562" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A562" s="76"/>
+      <c r="A562" s="75"/>
       <c r="B562" s="35" t="s">
         <v>1105</v>
       </c>
@@ -13737,12 +13740,12 @@
         <v>1106</v>
       </c>
       <c r="D562" s="51">
-        <f>E963</f>
+        <f>E964</f>
         <v>2.2741325637156556E-10</v>
       </c>
     </row>
     <row r="563" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A563" s="76"/>
+      <c r="A563" s="75"/>
       <c r="B563" s="35" t="s">
         <v>1130</v>
       </c>
@@ -13754,7 +13757,7 @@
       </c>
     </row>
     <row r="564" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A564" s="76"/>
+      <c r="A564" s="75"/>
       <c r="B564" s="35" t="s">
         <v>1131</v>
       </c>
@@ -13764,7 +13767,7 @@
       </c>
     </row>
     <row r="565" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A565" s="76"/>
+      <c r="A565" s="75"/>
       <c r="B565" s="35" t="s">
         <v>1100</v>
       </c>
@@ -13774,14 +13777,14 @@
       </c>
     </row>
     <row r="566" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A566" s="76"/>
+      <c r="A566" s="75"/>
     </row>
     <row r="567" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="48"/>
       <c r="D567" s="27"/>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A568" s="76" t="s">
+      <c r="A568" s="75" t="s">
         <v>680</v>
       </c>
       <c r="B568" t="s">
@@ -13796,7 +13799,7 @@
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A569" s="76"/>
+      <c r="A569" s="75"/>
       <c r="C569" t="s">
         <v>681</v>
       </c>
@@ -13808,7 +13811,7 @@
       </c>
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A570" s="76"/>
+      <c r="A570" s="75"/>
       <c r="C570" t="s">
         <v>683</v>
       </c>
@@ -13820,7 +13823,7 @@
       </c>
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A571" s="76"/>
+      <c r="A571" s="75"/>
       <c r="C571" t="s">
         <v>684</v>
       </c>
@@ -13832,7 +13835,7 @@
       </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A572" s="76"/>
+      <c r="A572" s="75"/>
       <c r="B572" t="s">
         <v>686</v>
       </c>
@@ -13846,7 +13849,7 @@
       <c r="E572" s="35"/>
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A573" s="76"/>
+      <c r="A573" s="75"/>
       <c r="B573" t="s">
         <v>688</v>
       </c>
@@ -13860,7 +13863,7 @@
       <c r="E573" s="35"/>
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A574" s="76"/>
+      <c r="A574" s="75"/>
       <c r="B574" t="s">
         <v>690</v>
       </c>
@@ -13873,7 +13876,7 @@
       <c r="E574" s="34"/>
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A575" s="76"/>
+      <c r="A575" s="75"/>
       <c r="C575" t="s">
         <v>685</v>
       </c>
@@ -13884,7 +13887,7 @@
       <c r="E575" s="34"/>
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A576" s="76"/>
+      <c r="A576" s="75"/>
       <c r="B576" t="s">
         <v>693</v>
       </c>
@@ -13898,7 +13901,7 @@
       <c r="E576" s="34"/>
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A577" s="76"/>
+      <c r="A577" s="75"/>
       <c r="C577" t="s">
         <v>694</v>
       </c>
@@ -13908,7 +13911,7 @@
       <c r="E577" s="34"/>
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A578" s="76"/>
+      <c r="A578" s="75"/>
       <c r="C578" t="s">
         <v>695</v>
       </c>
@@ -13919,7 +13922,7 @@
       <c r="E578" s="34"/>
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A579" s="76"/>
+      <c r="A579" s="75"/>
       <c r="C579" t="s">
         <v>696</v>
       </c>
@@ -13929,7 +13932,7 @@
       <c r="E579" s="34"/>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A580" s="76"/>
+      <c r="A580" s="75"/>
       <c r="C580" t="s">
         <v>697</v>
       </c>
@@ -13939,21 +13942,21 @@
       </c>
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A581" s="76" t="s">
+      <c r="A581" s="75" t="s">
         <v>698</v>
       </c>
     </row>
     <row r="582" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A582" s="76"/>
+      <c r="A582" s="75"/>
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A583" s="76"/>
+      <c r="A583" s="75"/>
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A584" s="76"/>
+      <c r="A584" s="75"/>
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A585" s="77" t="s">
+      <c r="A585" s="76" t="s">
         <v>330</v>
       </c>
       <c r="B585" t="s">
@@ -13968,7 +13971,7 @@
       </c>
     </row>
     <row r="586" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A586" s="77"/>
+      <c r="A586" s="76"/>
       <c r="B586" t="s">
         <v>47</v>
       </c>
@@ -13978,7 +13981,7 @@
       </c>
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A587" s="77"/>
+      <c r="A587" s="76"/>
       <c r="B587" t="s">
         <v>231</v>
       </c>
@@ -13988,7 +13991,7 @@
       </c>
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A588" s="77"/>
+      <c r="A588" s="76"/>
       <c r="C588" t="s">
         <v>334</v>
       </c>
@@ -13997,7 +14000,7 @@
       </c>
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A589" s="77"/>
+      <c r="A589" s="76"/>
       <c r="C589" t="s">
         <v>336</v>
       </c>
@@ -14007,7 +14010,7 @@
       </c>
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A590" s="77"/>
+      <c r="A590" s="76"/>
       <c r="B590" t="s">
         <v>331</v>
       </c>
@@ -14019,7 +14022,7 @@
       </c>
     </row>
     <row r="591" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A591" s="77"/>
+      <c r="A591" s="76"/>
       <c r="B591" t="s">
         <v>333</v>
       </c>
@@ -14032,7 +14035,7 @@
       </c>
     </row>
     <row r="592" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A592" s="77"/>
+      <c r="A592" s="76"/>
       <c r="B592" t="s">
         <v>383</v>
       </c>
@@ -14045,7 +14048,7 @@
       </c>
     </row>
     <row r="593" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A593" s="77"/>
+      <c r="A593" s="76"/>
       <c r="B593" t="s">
         <v>338</v>
       </c>
@@ -14058,7 +14061,7 @@
       </c>
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A594" s="77"/>
+      <c r="A594" s="76"/>
       <c r="B594" t="s">
         <v>339</v>
       </c>
@@ -14071,7 +14074,7 @@
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A595" s="77"/>
+      <c r="A595" s="76"/>
       <c r="B595" t="s">
         <v>340</v>
       </c>
@@ -14084,7 +14087,7 @@
       </c>
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A596" s="77"/>
+      <c r="A596" s="76"/>
       <c r="C596" t="s">
         <v>342</v>
       </c>
@@ -14094,7 +14097,7 @@
       </c>
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A597" s="77"/>
+      <c r="A597" s="76"/>
       <c r="B597" t="s">
         <v>373</v>
       </c>
@@ -14106,7 +14109,7 @@
       </c>
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A598" s="77"/>
+      <c r="A598" s="76"/>
       <c r="B598" t="s">
         <v>347</v>
       </c>
@@ -14118,7 +14121,7 @@
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A599" s="77"/>
+      <c r="A599" s="76"/>
       <c r="B599" t="s">
         <v>348</v>
       </c>
@@ -14130,7 +14133,7 @@
       </c>
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A600" s="77"/>
+      <c r="A600" s="76"/>
       <c r="B600" t="s">
         <v>351</v>
       </c>
@@ -14145,7 +14148,7 @@
       </c>
     </row>
     <row r="601" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A601" s="77"/>
+      <c r="A601" s="76"/>
       <c r="B601" t="s">
         <v>352</v>
       </c>
@@ -14160,7 +14163,7 @@
       </c>
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A602" s="77"/>
+      <c r="A602" s="76"/>
       <c r="B602" t="s">
         <v>354</v>
       </c>
@@ -14176,7 +14179,7 @@
       </c>
     </row>
     <row r="603" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A603" s="77"/>
+      <c r="A603" s="76"/>
       <c r="B603" s="26" t="s">
         <v>358</v>
       </c>
@@ -14191,7 +14194,7 @@
       </c>
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A604" s="77"/>
+      <c r="A604" s="76"/>
       <c r="C604" t="s">
         <v>361</v>
       </c>
@@ -14201,7 +14204,7 @@
       </c>
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A605" s="77"/>
+      <c r="A605" s="76"/>
       <c r="B605" t="s">
         <v>376</v>
       </c>
@@ -14214,7 +14217,7 @@
       </c>
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A606" s="77"/>
+      <c r="A606" s="76"/>
       <c r="B606" t="s">
         <v>377</v>
       </c>
@@ -14224,7 +14227,7 @@
       </c>
     </row>
     <row r="607" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A607" s="77"/>
+      <c r="A607" s="76"/>
       <c r="B607" t="s">
         <v>343</v>
       </c>
@@ -14233,7 +14236,7 @@
       </c>
     </row>
     <row r="608" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A608" s="77"/>
+      <c r="A608" s="76"/>
       <c r="B608" t="s">
         <v>345</v>
       </c>
@@ -14243,7 +14246,7 @@
       </c>
     </row>
     <row r="609" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A609" s="77"/>
+      <c r="A609" s="76"/>
       <c r="B609" t="s">
         <v>344</v>
       </c>
@@ -14255,7 +14258,7 @@
       </c>
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A610" s="77"/>
+      <c r="A610" s="76"/>
       <c r="B610" t="s">
         <v>378</v>
       </c>
@@ -14268,7 +14271,7 @@
       </c>
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A611" s="77"/>
+      <c r="A611" s="76"/>
       <c r="C611" t="s">
         <v>394</v>
       </c>
@@ -14277,7 +14280,7 @@
       </c>
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A612" s="77"/>
+      <c r="A612" s="76"/>
       <c r="B612" t="s">
         <v>395</v>
       </c>
@@ -14287,7 +14290,7 @@
       </c>
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A613" s="77"/>
+      <c r="A613" s="76"/>
       <c r="B613" t="s">
         <v>396</v>
       </c>
@@ -14297,7 +14300,7 @@
       </c>
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A614" s="77"/>
+      <c r="A614" s="76"/>
       <c r="B614" t="s">
         <v>397</v>
       </c>
@@ -14307,7 +14310,7 @@
       </c>
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A615" s="77"/>
+      <c r="A615" s="76"/>
       <c r="B615" t="s">
         <v>398</v>
       </c>
@@ -14317,7 +14320,7 @@
       </c>
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A616" s="77"/>
+      <c r="A616" s="76"/>
       <c r="B616" t="s">
         <v>392</v>
       </c>
@@ -14330,7 +14333,7 @@
       </c>
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A617" s="77"/>
+      <c r="A617" s="76"/>
       <c r="B617" t="s">
         <v>399</v>
       </c>
@@ -14343,7 +14346,7 @@
       </c>
     </row>
     <row r="618" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A618" s="77"/>
+      <c r="A618" s="76"/>
       <c r="C618" t="s">
         <v>400</v>
       </c>
@@ -14353,7 +14356,7 @@
       </c>
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A619" s="77"/>
+      <c r="A619" s="76"/>
       <c r="C619" t="s">
         <v>401</v>
       </c>
@@ -14366,7 +14369,7 @@
       </c>
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A620" s="77"/>
+      <c r="A620" s="76"/>
       <c r="B620" t="s">
         <v>379</v>
       </c>
@@ -14376,7 +14379,7 @@
       </c>
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A621" s="77"/>
+      <c r="A621" s="76"/>
       <c r="C621" t="s">
         <v>368</v>
       </c>
@@ -14386,7 +14389,7 @@
       </c>
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A622" s="77"/>
+      <c r="A622" s="76"/>
       <c r="C622" t="s">
         <v>380</v>
       </c>
@@ -14396,7 +14399,7 @@
       </c>
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A623" s="77"/>
+      <c r="A623" s="76"/>
       <c r="B623" t="s">
         <v>366</v>
       </c>
@@ -14409,7 +14412,7 @@
       </c>
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A624" s="77"/>
+      <c r="A624" s="76"/>
       <c r="C624" t="s">
         <v>381</v>
       </c>
@@ -14419,7 +14422,7 @@
       </c>
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A625" s="77"/>
+      <c r="A625" s="76"/>
       <c r="C625" t="s">
         <v>382</v>
       </c>
@@ -14429,7 +14432,7 @@
       </c>
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A626" s="77"/>
+      <c r="A626" s="76"/>
       <c r="B626" t="s">
         <v>367</v>
       </c>
@@ -14439,7 +14442,7 @@
       </c>
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A627" s="77"/>
+      <c r="A627" s="76"/>
       <c r="C627" t="s">
         <v>372</v>
       </c>
@@ -14449,7 +14452,7 @@
       </c>
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A628" s="77"/>
+      <c r="A628" s="76"/>
       <c r="C628" t="s">
         <v>369</v>
       </c>
@@ -14459,10 +14462,10 @@
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A629" s="77"/>
+      <c r="A629" s="76"/>
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A630" s="77"/>
+      <c r="A630" s="76"/>
       <c r="C630" t="s">
         <v>370</v>
       </c>
@@ -14475,7 +14478,7 @@
       </c>
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A631" s="77"/>
+      <c r="A631" s="76"/>
       <c r="C631" t="s">
         <v>370</v>
       </c>
@@ -14488,7 +14491,7 @@
       </c>
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A632" s="77"/>
+      <c r="A632" s="76"/>
       <c r="C632" t="s">
         <v>371</v>
       </c>
@@ -14498,7 +14501,7 @@
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A633" s="77"/>
+      <c r="A633" s="76"/>
       <c r="B633" t="s">
         <v>385</v>
       </c>
@@ -14508,7 +14511,7 @@
       </c>
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A634" s="77"/>
+      <c r="A634" s="76"/>
       <c r="B634" t="s">
         <v>386</v>
       </c>
@@ -14518,13 +14521,13 @@
       </c>
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A635" s="77"/>
+      <c r="A635" s="76"/>
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A636" s="77"/>
+      <c r="A636" s="76"/>
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A637" s="77"/>
+      <c r="A637" s="76"/>
       <c r="B637" t="s">
         <v>388</v>
       </c>
@@ -14540,7 +14543,7 @@
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A638" s="77"/>
+      <c r="A638" s="76"/>
       <c r="B638" t="s">
         <v>389</v>
       </c>
@@ -14553,7 +14556,7 @@
       </c>
     </row>
     <row r="639" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A639" s="77"/>
+      <c r="A639" s="76"/>
       <c r="B639" t="s">
         <v>391</v>
       </c>
@@ -14563,7 +14566,7 @@
       </c>
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A640" s="77"/>
+      <c r="A640" s="76"/>
       <c r="B640" t="s">
         <v>402</v>
       </c>
@@ -14576,7 +14579,7 @@
       </c>
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A641" s="77"/>
+      <c r="A641" s="76"/>
       <c r="B641" t="s">
         <v>404</v>
       </c>
@@ -14586,7 +14589,7 @@
       </c>
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A642" s="77"/>
+      <c r="A642" s="76"/>
       <c r="B642" t="s">
         <v>405</v>
       </c>
@@ -14596,7 +14599,7 @@
       </c>
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A643" s="77"/>
+      <c r="A643" s="76"/>
       <c r="B643" t="s">
         <v>406</v>
       </c>
@@ -14606,7 +14609,7 @@
       </c>
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A644" s="77"/>
+      <c r="A644" s="76"/>
       <c r="B644" t="s">
         <v>407</v>
       </c>
@@ -14616,7 +14619,7 @@
       </c>
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A645" s="77"/>
+      <c r="A645" s="76"/>
       <c r="C645" t="s">
         <v>408</v>
       </c>
@@ -14626,7 +14629,7 @@
       </c>
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A646" s="77"/>
+      <c r="A646" s="76"/>
       <c r="B646" t="s">
         <v>409</v>
       </c>
@@ -14636,7 +14639,7 @@
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A647" s="77"/>
+      <c r="A647" s="76"/>
       <c r="B647" t="s">
         <v>410</v>
       </c>
@@ -14646,7 +14649,7 @@
       </c>
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A648" s="77"/>
+      <c r="A648" s="76"/>
       <c r="B648" t="s">
         <v>411</v>
       </c>
@@ -14656,7 +14659,7 @@
       </c>
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A649" s="77"/>
+      <c r="A649" s="76"/>
       <c r="B649" t="s">
         <v>409</v>
       </c>
@@ -14669,7 +14672,7 @@
       </c>
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A650" s="77"/>
+      <c r="A650" s="76"/>
       <c r="B650" t="s">
         <v>410</v>
       </c>
@@ -14682,7 +14685,7 @@
       </c>
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A651" s="77"/>
+      <c r="A651" s="76"/>
       <c r="B651" t="s">
         <v>411</v>
       </c>
@@ -14698,7 +14701,7 @@
       <c r="A652" s="44"/>
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A653" s="76" t="s">
+      <c r="A653" s="75" t="s">
         <v>1007</v>
       </c>
       <c r="B653" t="s">
@@ -14716,7 +14719,7 @@
       </c>
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A654" s="76"/>
+      <c r="A654" s="75"/>
       <c r="B654" t="s">
         <v>830</v>
       </c>
@@ -14729,7 +14732,7 @@
       </c>
     </row>
     <row r="655" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A655" s="76"/>
+      <c r="A655" s="75"/>
       <c r="B655" s="46" t="s">
         <v>806</v>
       </c>
@@ -14745,7 +14748,7 @@
       </c>
     </row>
     <row r="656" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A656" s="76"/>
+      <c r="A656" s="75"/>
       <c r="B656" s="46" t="s">
         <v>808</v>
       </c>
@@ -14761,7 +14764,7 @@
       </c>
     </row>
     <row r="657" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A657" s="76"/>
+      <c r="A657" s="75"/>
       <c r="B657" s="46" t="s">
         <v>793</v>
       </c>
@@ -14777,7 +14780,7 @@
       </c>
     </row>
     <row r="658" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A658" s="76"/>
+      <c r="A658" s="75"/>
       <c r="B658" s="46" t="s">
         <v>795</v>
       </c>
@@ -14789,7 +14792,7 @@
       </c>
     </row>
     <row r="659" spans="1:5" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A659" s="76"/>
+      <c r="A659" s="75"/>
       <c r="B659" s="46" t="s">
         <v>820</v>
       </c>
@@ -14802,7 +14805,7 @@
       </c>
     </row>
     <row r="660" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A660" s="76"/>
+      <c r="A660" s="75"/>
       <c r="B660" t="s">
         <v>809</v>
       </c>
@@ -14815,7 +14818,7 @@
       </c>
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A661" s="76"/>
+      <c r="A661" s="75"/>
       <c r="B661" t="s">
         <v>829</v>
       </c>
@@ -14828,7 +14831,7 @@
       </c>
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A662" s="76"/>
+      <c r="A662" s="75"/>
       <c r="B662" t="s">
         <v>810</v>
       </c>
@@ -14841,7 +14844,7 @@
       </c>
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A663" s="76"/>
+      <c r="A663" s="75"/>
       <c r="B663" t="s">
         <v>797</v>
       </c>
@@ -14856,7 +14859,7 @@
       </c>
     </row>
     <row r="664" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A664" s="76"/>
+      <c r="A664" s="75"/>
       <c r="B664" t="s">
         <v>798</v>
       </c>
@@ -14871,7 +14874,7 @@
       </c>
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A665" s="76"/>
+      <c r="A665" s="75"/>
       <c r="B665" t="s">
         <v>801</v>
       </c>
@@ -14887,7 +14890,7 @@
       </c>
     </row>
     <row r="666" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A666" s="76"/>
+      <c r="A666" s="75"/>
       <c r="B666" t="s">
         <v>802</v>
       </c>
@@ -14903,7 +14906,7 @@
       </c>
     </row>
     <row r="667" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A667" s="76"/>
+      <c r="A667" s="75"/>
       <c r="B667" t="s">
         <v>815</v>
       </c>
@@ -14919,10 +14922,10 @@
       </c>
     </row>
     <row r="668" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A668" s="76"/>
+      <c r="A668" s="75"/>
     </row>
     <row r="669" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A669" s="76"/>
+      <c r="A669" s="75"/>
       <c r="B669" t="s">
         <v>817</v>
       </c>
@@ -14938,7 +14941,7 @@
       </c>
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A670" s="76"/>
+      <c r="A670" s="75"/>
       <c r="B670" t="s">
         <v>825</v>
       </c>
@@ -14954,7 +14957,7 @@
       </c>
     </row>
     <row r="671" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A671" s="76"/>
+      <c r="A671" s="75"/>
       <c r="B671" t="s">
         <v>819</v>
       </c>
@@ -14970,7 +14973,7 @@
       </c>
     </row>
     <row r="672" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A672" s="76"/>
+      <c r="A672" s="75"/>
       <c r="B672" t="s">
         <v>826</v>
       </c>
@@ -14986,7 +14989,7 @@
       </c>
     </row>
     <row r="673" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A673" s="76"/>
+      <c r="A673" s="75"/>
       <c r="B673" t="s">
         <v>816</v>
       </c>
@@ -15002,7 +15005,7 @@
       </c>
     </row>
     <row r="674" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A674" s="76"/>
+      <c r="A674" s="75"/>
       <c r="B674" t="s">
         <v>821</v>
       </c>
@@ -15015,11 +15018,11 @@
       </c>
     </row>
     <row r="675" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A675" s="76"/>
+      <c r="A675" s="75"/>
       <c r="D675" s="27"/>
     </row>
     <row r="676" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A676" s="76"/>
+      <c r="A676" s="75"/>
       <c r="B676" t="s">
         <v>832</v>
       </c>
@@ -15035,7 +15038,7 @@
       </c>
     </row>
     <row r="677" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A677" s="76"/>
+      <c r="A677" s="75"/>
       <c r="B677" t="s">
         <v>823</v>
       </c>
@@ -15051,7 +15054,7 @@
       </c>
     </row>
     <row r="678" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A678" s="76"/>
+      <c r="A678" s="75"/>
       <c r="B678" t="s">
         <v>834</v>
       </c>
@@ -15064,7 +15067,7 @@
       </c>
     </row>
     <row r="679" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A679" s="76"/>
+      <c r="A679" s="75"/>
       <c r="B679" t="s">
         <v>836</v>
       </c>
@@ -15076,7 +15079,7 @@
       </c>
     </row>
     <row r="680" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A680" s="76"/>
+      <c r="A680" s="75"/>
       <c r="B680" t="s">
         <v>838</v>
       </c>
@@ -15085,7 +15088,7 @@
       </c>
     </row>
     <row r="681" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A681" s="76"/>
+      <c r="A681" s="75"/>
       <c r="B681" t="s">
         <v>840</v>
       </c>
@@ -15100,7 +15103,7 @@
       </c>
     </row>
     <row r="682" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A682" s="76"/>
+      <c r="A682" s="75"/>
       <c r="B682" t="s">
         <v>842</v>
       </c>
@@ -15111,7 +15114,7 @@
       <c r="E682" s="8"/>
     </row>
     <row r="683" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A683" s="76"/>
+      <c r="A683" s="75"/>
       <c r="B683" t="s">
         <v>843</v>
       </c>
@@ -15124,7 +15127,7 @@
       <c r="E683" s="8"/>
     </row>
     <row r="684" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A684" s="76"/>
+      <c r="A684" s="75"/>
       <c r="B684" t="s">
         <v>693</v>
       </c>
@@ -15138,7 +15141,7 @@
       <c r="E684" s="8"/>
     </row>
     <row r="685" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A685" s="76"/>
+      <c r="A685" s="75"/>
       <c r="B685" t="s">
         <v>848</v>
       </c>
@@ -15544,7 +15547,7 @@
       </c>
     </row>
     <row r="686" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A686" s="76"/>
+      <c r="A686" s="75"/>
       <c r="B686" t="s">
         <v>846</v>
       </c>
@@ -15850,7 +15853,7 @@
       </c>
     </row>
     <row r="687" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A687" s="76"/>
+      <c r="A687" s="75"/>
       <c r="B687" t="s">
         <v>847</v>
       </c>
@@ -16256,7 +16259,7 @@
       </c>
     </row>
     <row r="688" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A688" s="76"/>
+      <c r="A688" s="75"/>
       <c r="B688" t="s">
         <v>849</v>
       </c>
@@ -16662,7 +16665,7 @@
       </c>
     </row>
     <row r="689" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A689" s="76"/>
+      <c r="A689" s="75"/>
       <c r="B689" t="s">
         <v>850</v>
       </c>
@@ -17068,7 +17071,7 @@
       </c>
     </row>
     <row r="690" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A690" s="76"/>
+      <c r="A690" s="75"/>
       <c r="B690" t="s">
         <v>851</v>
       </c>
@@ -17078,7 +17081,7 @@
       </c>
     </row>
     <row r="691" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A691" s="76"/>
+      <c r="A691" s="75"/>
       <c r="B691" t="s">
         <v>852</v>
       </c>
@@ -17088,7 +17091,7 @@
       </c>
     </row>
     <row r="692" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A692" s="76"/>
+      <c r="A692" s="75"/>
       <c r="C692" t="s">
         <v>853</v>
       </c>
@@ -17105,7 +17108,7 @@
       <c r="E694" s="8"/>
     </row>
     <row r="695" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A695" s="77" t="s">
+      <c r="A695" s="76" t="s">
         <v>431</v>
       </c>
       <c r="B695" t="s">
@@ -17120,7 +17123,7 @@
       </c>
     </row>
     <row r="696" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A696" s="77"/>
+      <c r="A696" s="76"/>
       <c r="B696" t="s">
         <v>40</v>
       </c>
@@ -17133,7 +17136,7 @@
       </c>
     </row>
     <row r="697" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A697" s="77"/>
+      <c r="A697" s="76"/>
       <c r="B697" t="s">
         <v>39</v>
       </c>
@@ -17146,7 +17149,7 @@
       </c>
     </row>
     <row r="698" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A698" s="77"/>
+      <c r="A698" s="76"/>
       <c r="B698" t="s">
         <v>412</v>
       </c>
@@ -17159,7 +17162,7 @@
       </c>
     </row>
     <row r="699" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A699" s="77"/>
+      <c r="A699" s="76"/>
       <c r="B699" t="s">
         <v>416</v>
       </c>
@@ -17168,7 +17171,7 @@
       </c>
     </row>
     <row r="700" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A700" s="77"/>
+      <c r="A700" s="76"/>
       <c r="B700" t="s">
         <v>422</v>
       </c>
@@ -17178,7 +17181,7 @@
       </c>
     </row>
     <row r="701" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A701" s="77"/>
+      <c r="A701" s="76"/>
       <c r="C701" t="s">
         <v>417</v>
       </c>
@@ -17187,7 +17190,7 @@
       </c>
     </row>
     <row r="702" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A702" s="77"/>
+      <c r="A702" s="76"/>
       <c r="B702" t="s">
         <v>421</v>
       </c>
@@ -17197,7 +17200,7 @@
       </c>
     </row>
     <row r="703" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A703" s="77"/>
+      <c r="A703" s="76"/>
       <c r="B703" t="s">
         <v>446</v>
       </c>
@@ -17210,7 +17213,7 @@
       </c>
     </row>
     <row r="704" spans="1:102" x14ac:dyDescent="0.25">
-      <c r="A704" s="77"/>
+      <c r="A704" s="76"/>
       <c r="B704" t="s">
         <v>448</v>
       </c>
@@ -17219,7 +17222,7 @@
       </c>
     </row>
     <row r="705" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A705" s="77"/>
+      <c r="A705" s="76"/>
       <c r="B705" t="s">
         <v>449</v>
       </c>
@@ -17228,7 +17231,7 @@
       </c>
     </row>
     <row r="706" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A706" s="77"/>
+      <c r="A706" s="76"/>
       <c r="B706" t="s">
         <v>452</v>
       </c>
@@ -17240,7 +17243,7 @@
       </c>
     </row>
     <row r="707" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A707" s="77"/>
+      <c r="A707" s="76"/>
       <c r="B707" t="s">
         <v>454</v>
       </c>
@@ -17250,7 +17253,7 @@
       </c>
     </row>
     <row r="708" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A708" s="77"/>
+      <c r="A708" s="76"/>
       <c r="B708" t="s">
         <v>427</v>
       </c>
@@ -17263,7 +17266,7 @@
       </c>
     </row>
     <row r="709" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A709" s="77"/>
+      <c r="A709" s="76"/>
       <c r="C709" t="s">
         <v>450</v>
       </c>
@@ -17273,7 +17276,7 @@
       </c>
     </row>
     <row r="710" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A710" s="77"/>
+      <c r="A710" s="76"/>
       <c r="B710" t="s">
         <v>451</v>
       </c>
@@ -17283,7 +17286,7 @@
       </c>
     </row>
     <row r="711" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A711" s="77"/>
+      <c r="A711" s="76"/>
       <c r="B711" t="s">
         <v>487</v>
       </c>
@@ -17293,7 +17296,7 @@
       </c>
     </row>
     <row r="712" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A712" s="77"/>
+      <c r="A712" s="76"/>
       <c r="B712" t="s">
         <v>488</v>
       </c>
@@ -17303,7 +17306,7 @@
       </c>
     </row>
     <row r="713" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A713" s="77"/>
+      <c r="A713" s="76"/>
       <c r="B713" t="s">
         <v>489</v>
       </c>
@@ -17313,7 +17316,7 @@
       </c>
     </row>
     <row r="714" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A714" s="77"/>
+      <c r="A714" s="76"/>
       <c r="B714" t="s">
         <v>455</v>
       </c>
@@ -17323,7 +17326,7 @@
       </c>
     </row>
     <row r="715" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A715" s="77"/>
+      <c r="A715" s="76"/>
       <c r="B715" t="s">
         <v>456</v>
       </c>
@@ -17333,7 +17336,7 @@
       </c>
     </row>
     <row r="716" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A716" s="77"/>
+      <c r="A716" s="76"/>
       <c r="B716" t="s">
         <v>425</v>
       </c>
@@ -17345,7 +17348,7 @@
       </c>
     </row>
     <row r="717" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A717" s="77"/>
+      <c r="A717" s="76"/>
       <c r="B717" t="s">
         <v>423</v>
       </c>
@@ -17358,7 +17361,7 @@
       </c>
     </row>
     <row r="718" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A718" s="77"/>
+      <c r="A718" s="76"/>
       <c r="B718" t="s">
         <v>420</v>
       </c>
@@ -17370,7 +17373,7 @@
       </c>
     </row>
     <row r="719" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A719" s="77"/>
+      <c r="A719" s="76"/>
       <c r="B719" t="s">
         <v>458</v>
       </c>
@@ -17380,7 +17383,7 @@
       </c>
     </row>
     <row r="720" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A720" s="77"/>
+      <c r="A720" s="76"/>
       <c r="B720" t="s">
         <v>459</v>
       </c>
@@ -17390,7 +17393,7 @@
       </c>
     </row>
     <row r="721" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A721" s="77"/>
+      <c r="A721" s="76"/>
       <c r="B721" t="s">
         <v>418</v>
       </c>
@@ -17403,7 +17406,7 @@
       </c>
     </row>
     <row r="722" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A722" s="77"/>
+      <c r="A722" s="76"/>
       <c r="B722" t="s">
         <v>429</v>
       </c>
@@ -17413,7 +17416,7 @@
       </c>
     </row>
     <row r="723" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A723" s="77"/>
+      <c r="A723" s="76"/>
       <c r="C723" t="s">
         <v>430</v>
       </c>
@@ -17423,7 +17426,7 @@
       </c>
     </row>
     <row r="724" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A724" s="77"/>
+      <c r="A724" s="76"/>
       <c r="B724" t="s">
         <v>432</v>
       </c>
@@ -17435,7 +17438,7 @@
       </c>
     </row>
     <row r="725" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A725" s="77"/>
+      <c r="A725" s="76"/>
       <c r="B725" t="s">
         <v>38</v>
       </c>
@@ -17445,10 +17448,10 @@
       </c>
     </row>
     <row r="726" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A726" s="77"/>
+      <c r="A726" s="76"/>
     </row>
     <row r="727" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A727" s="77"/>
+      <c r="A727" s="76"/>
       <c r="B727" t="s">
         <v>435</v>
       </c>
@@ -17458,7 +17461,7 @@
       </c>
     </row>
     <row r="728" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A728" s="77"/>
+      <c r="A728" s="76"/>
       <c r="B728" t="s">
         <v>436</v>
       </c>
@@ -17468,7 +17471,7 @@
       </c>
     </row>
     <row r="729" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A729" s="77"/>
+      <c r="A729" s="76"/>
       <c r="B729" t="s">
         <v>437</v>
       </c>
@@ -17478,7 +17481,7 @@
       </c>
     </row>
     <row r="730" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A730" s="77"/>
+      <c r="A730" s="76"/>
       <c r="B730" t="s">
         <v>231</v>
       </c>
@@ -17488,7 +17491,7 @@
       </c>
     </row>
     <row r="731" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A731" s="77"/>
+      <c r="A731" s="76"/>
       <c r="B731" t="s">
         <v>438</v>
       </c>
@@ -17498,7 +17501,7 @@
       </c>
     </row>
     <row r="732" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A732" s="77"/>
+      <c r="A732" s="76"/>
       <c r="C732" t="s">
         <v>434</v>
       </c>
@@ -17508,7 +17511,7 @@
       </c>
     </row>
     <row r="733" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A733" s="77"/>
+      <c r="A733" s="76"/>
       <c r="B733" t="s">
         <v>440</v>
       </c>
@@ -17521,7 +17524,7 @@
       </c>
     </row>
     <row r="734" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A734" s="77"/>
+      <c r="A734" s="76"/>
       <c r="B734" t="s">
         <v>441</v>
       </c>
@@ -17531,7 +17534,7 @@
       </c>
     </row>
     <row r="735" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A735" s="77"/>
+      <c r="A735" s="76"/>
       <c r="B735" t="s">
         <v>442</v>
       </c>
@@ -17541,7 +17544,7 @@
       </c>
     </row>
     <row r="736" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A736" s="77"/>
+      <c r="A736" s="76"/>
       <c r="B736" t="s">
         <v>443</v>
       </c>
@@ -17551,7 +17554,7 @@
       </c>
     </row>
     <row r="737" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A737" s="77"/>
+      <c r="A737" s="76"/>
       <c r="C737" t="s">
         <v>444</v>
       </c>
@@ -17561,7 +17564,7 @@
       </c>
     </row>
     <row r="738" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A738" s="77"/>
+      <c r="A738" s="76"/>
       <c r="B738" t="s">
         <v>445</v>
       </c>
@@ -17571,7 +17574,7 @@
       </c>
     </row>
     <row r="739" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A739" s="77"/>
+      <c r="A739" s="76"/>
       <c r="B739" t="s">
         <v>463</v>
       </c>
@@ -17583,7 +17586,7 @@
       </c>
     </row>
     <row r="740" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A740" s="77"/>
+      <c r="A740" s="76"/>
       <c r="C740" t="s">
         <v>461</v>
       </c>
@@ -17592,7 +17595,7 @@
       </c>
     </row>
     <row r="741" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A741" s="77"/>
+      <c r="A741" s="76"/>
       <c r="B741" t="s">
         <v>462</v>
       </c>
@@ -17602,7 +17605,7 @@
       </c>
     </row>
     <row r="742" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A742" s="77"/>
+      <c r="A742" s="76"/>
       <c r="B742" t="s">
         <v>464</v>
       </c>
@@ -17612,7 +17615,7 @@
       </c>
     </row>
     <row r="743" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A743" s="77"/>
+      <c r="A743" s="76"/>
       <c r="B743" t="s">
         <v>465</v>
       </c>
@@ -17621,7 +17624,7 @@
       </c>
     </row>
     <row r="744" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A744" s="77"/>
+      <c r="A744" s="76"/>
       <c r="B744" t="s">
         <v>466</v>
       </c>
@@ -17630,7 +17633,7 @@
       </c>
     </row>
     <row r="745" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A745" s="77"/>
+      <c r="A745" s="76"/>
       <c r="C745" t="s">
         <v>467</v>
       </c>
@@ -17640,7 +17643,7 @@
       </c>
     </row>
     <row r="746" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A746" s="77"/>
+      <c r="A746" s="76"/>
       <c r="B746" t="s">
         <v>468</v>
       </c>
@@ -17653,7 +17656,7 @@
       </c>
     </row>
     <row r="747" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A747" s="77"/>
+      <c r="A747" s="76"/>
       <c r="B747" t="s">
         <v>470</v>
       </c>
@@ -17666,7 +17669,7 @@
       </c>
     </row>
     <row r="748" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A748" s="77"/>
+      <c r="A748" s="76"/>
       <c r="B748" t="s">
         <v>472</v>
       </c>
@@ -17676,7 +17679,7 @@
       </c>
     </row>
     <row r="749" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A749" s="77"/>
+      <c r="A749" s="76"/>
       <c r="B749" t="s">
         <v>473</v>
       </c>
@@ -17686,7 +17689,7 @@
       </c>
     </row>
     <row r="750" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A750" s="77"/>
+      <c r="A750" s="76"/>
       <c r="B750" t="s">
         <v>479</v>
       </c>
@@ -17695,7 +17698,7 @@
       </c>
     </row>
     <row r="751" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A751" s="77"/>
+      <c r="A751" s="76"/>
       <c r="C751" t="s">
         <v>483</v>
       </c>
@@ -17704,7 +17707,7 @@
       </c>
     </row>
     <row r="752" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A752" s="77"/>
+      <c r="A752" s="76"/>
       <c r="B752" t="s">
         <v>484</v>
       </c>
@@ -17714,7 +17717,7 @@
       </c>
     </row>
     <row r="753" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A753" s="77"/>
+      <c r="A753" s="76"/>
       <c r="B753" t="s">
         <v>485</v>
       </c>
@@ -17724,7 +17727,7 @@
       </c>
     </row>
     <row r="754" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A754" s="77"/>
+      <c r="A754" s="76"/>
       <c r="C754" t="s">
         <v>476</v>
       </c>
@@ -17734,7 +17737,7 @@
       </c>
     </row>
     <row r="755" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A755" s="77"/>
+      <c r="A755" s="76"/>
       <c r="C755" t="s">
         <v>477</v>
       </c>
@@ -17744,7 +17747,7 @@
       </c>
     </row>
     <row r="756" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A756" s="77"/>
+      <c r="A756" s="76"/>
       <c r="C756" t="s">
         <v>478</v>
       </c>
@@ -17754,7 +17757,7 @@
       </c>
     </row>
     <row r="757" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A757" s="77"/>
+      <c r="A757" s="76"/>
       <c r="C757" t="s">
         <v>480</v>
       </c>
@@ -17764,10 +17767,10 @@
       </c>
     </row>
     <row r="758" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A758" s="77"/>
+      <c r="A758" s="76"/>
     </row>
     <row r="759" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A759" s="77"/>
+      <c r="A759" s="76"/>
       <c r="B759" t="s">
         <v>481</v>
       </c>
@@ -17777,7 +17780,7 @@
       </c>
     </row>
     <row r="760" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A760" s="77"/>
+      <c r="A760" s="76"/>
       <c r="B760" t="s">
         <v>486</v>
       </c>
@@ -17787,7 +17790,7 @@
       </c>
     </row>
     <row r="761" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A761" s="77"/>
+      <c r="A761" s="76"/>
       <c r="B761" t="s">
         <v>482</v>
       </c>
@@ -17797,7 +17800,7 @@
       </c>
     </row>
     <row r="762" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A762" s="77"/>
+      <c r="A762" s="76"/>
       <c r="C762" t="s">
         <v>606</v>
       </c>
@@ -17807,7 +17810,7 @@
       </c>
     </row>
     <row r="763" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A763" s="77"/>
+      <c r="A763" s="76"/>
       <c r="C763" t="s">
         <v>607</v>
       </c>
@@ -17817,7 +17820,7 @@
       </c>
     </row>
     <row r="764" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A764" s="77"/>
+      <c r="A764" s="76"/>
       <c r="C764" t="s">
         <v>608</v>
       </c>
@@ -17827,7 +17830,7 @@
       </c>
     </row>
     <row r="765" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A765" s="77"/>
+      <c r="A765" s="76"/>
       <c r="C765" t="s">
         <v>609</v>
       </c>
@@ -17837,7 +17840,7 @@
       </c>
     </row>
     <row r="766" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A766" s="77"/>
+      <c r="A766" s="76"/>
       <c r="B766" t="s">
         <v>716</v>
       </c>
@@ -18014,7 +18017,7 @@
       </c>
     </row>
     <row r="781" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A781" s="77" t="s">
+      <c r="A781" s="76" t="s">
         <v>610</v>
       </c>
       <c r="C781" t="s">
@@ -18045,7 +18048,7 @@
       </c>
     </row>
     <row r="782" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A782" s="77"/>
+      <c r="A782" s="76"/>
       <c r="C782" t="s">
         <v>612</v>
       </c>
@@ -18072,7 +18075,7 @@
       </c>
     </row>
     <row r="783" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A783" s="77"/>
+      <c r="A783" s="76"/>
       <c r="C783" t="s">
         <v>613</v>
       </c>
@@ -18099,7 +18102,7 @@
       </c>
     </row>
     <row r="784" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A784" s="77"/>
+      <c r="A784" s="76"/>
       <c r="C784" t="s">
         <v>621</v>
       </c>
@@ -18133,7 +18136,7 @@
       </c>
     </row>
     <row r="785" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A785" s="77"/>
+      <c r="A785" s="76"/>
       <c r="C785" t="s">
         <v>622</v>
       </c>
@@ -18163,7 +18166,7 @@
       </c>
     </row>
     <row r="786" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A786" s="77"/>
+      <c r="A786" s="76"/>
       <c r="C786" t="s">
         <v>620</v>
       </c>
@@ -18184,7 +18187,7 @@
       </c>
     </row>
     <row r="787" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A787" s="77"/>
+      <c r="A787" s="76"/>
       <c r="C787" t="s">
         <v>625</v>
       </c>
@@ -18210,7 +18213,7 @@
       </c>
     </row>
     <row r="788" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A788" s="77"/>
+      <c r="A788" s="76"/>
       <c r="C788" t="s">
         <v>624</v>
       </c>
@@ -18236,7 +18239,7 @@
       </c>
     </row>
     <row r="789" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A789" s="77"/>
+      <c r="A789" s="76"/>
       <c r="C789" t="s">
         <v>619</v>
       </c>
@@ -18257,7 +18260,7 @@
       </c>
     </row>
     <row r="790" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A790" s="77"/>
+      <c r="A790" s="76"/>
       <c r="C790" t="s">
         <v>194</v>
       </c>
@@ -18283,7 +18286,7 @@
       </c>
     </row>
     <row r="791" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A791" s="77"/>
+      <c r="A791" s="76"/>
       <c r="C791" t="s">
         <v>623</v>
       </c>
@@ -18309,7 +18312,7 @@
       </c>
     </row>
     <row r="792" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A792" s="77"/>
+      <c r="A792" s="76"/>
       <c r="C792" t="s">
         <v>626</v>
       </c>
@@ -18335,7 +18338,7 @@
       </c>
     </row>
     <row r="793" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A793" s="77"/>
+      <c r="A793" s="76"/>
     </row>
     <row r="794" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A794" s="37"/>
@@ -18344,7 +18347,7 @@
       <c r="A795" s="37"/>
     </row>
     <row r="799" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A799" s="76" t="s">
+      <c r="A799" s="75" t="s">
         <v>699</v>
       </c>
       <c r="C799" t="s">
@@ -18355,7 +18358,7 @@
       </c>
     </row>
     <row r="800" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A800" s="76"/>
+      <c r="A800" s="75"/>
       <c r="C800" t="s">
         <v>1069</v>
       </c>
@@ -18364,7 +18367,7 @@
       </c>
     </row>
     <row r="801" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A801" s="76"/>
+      <c r="A801" s="75"/>
       <c r="C801" t="s">
         <v>1070</v>
       </c>
@@ -18374,7 +18377,7 @@
       </c>
     </row>
     <row r="802" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A802" s="76"/>
+      <c r="A802" s="75"/>
       <c r="C802" t="s">
         <v>1072</v>
       </c>
@@ -18383,7 +18386,7 @@
       </c>
     </row>
     <row r="803" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A803" s="76"/>
+      <c r="A803" s="75"/>
       <c r="C803" t="s">
         <v>1071</v>
       </c>
@@ -18392,7 +18395,7 @@
       </c>
     </row>
     <row r="804" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A804" s="76"/>
+      <c r="A804" s="75"/>
       <c r="C804" t="s">
         <v>1074</v>
       </c>
@@ -18401,7 +18404,7 @@
       </c>
     </row>
     <row r="805" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A805" s="76"/>
+      <c r="A805" s="75"/>
       <c r="C805" t="s">
         <v>1076</v>
       </c>
@@ -18411,7 +18414,7 @@
       </c>
     </row>
     <row r="806" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A806" s="76"/>
+      <c r="A806" s="75"/>
       <c r="C806" t="s">
         <v>1075</v>
       </c>
@@ -18421,7 +18424,7 @@
       </c>
     </row>
     <row r="807" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A807" s="76"/>
+      <c r="A807" s="75"/>
       <c r="C807" t="s">
         <v>1073</v>
       </c>
@@ -18431,7 +18434,7 @@
       </c>
     </row>
     <row r="808" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A808" s="76"/>
+      <c r="A808" s="75"/>
       <c r="C808" t="s">
         <v>700</v>
       </c>
@@ -18440,7 +18443,7 @@
       </c>
     </row>
     <row r="809" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A809" s="76"/>
+      <c r="A809" s="75"/>
       <c r="C809" t="s">
         <v>1079</v>
       </c>
@@ -18450,7 +18453,7 @@
       </c>
     </row>
     <row r="810" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A810" s="76"/>
+      <c r="A810" s="75"/>
       <c r="C810" t="s">
         <v>212</v>
       </c>
@@ -18460,7 +18463,7 @@
       </c>
     </row>
     <row r="811" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A811" s="76"/>
+      <c r="A811" s="75"/>
       <c r="C811" t="s">
         <v>701</v>
       </c>
@@ -18470,7 +18473,7 @@
       </c>
     </row>
     <row r="812" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A812" s="76"/>
+      <c r="A812" s="75"/>
       <c r="C812" t="s">
         <v>702</v>
       </c>
@@ -18480,7 +18483,7 @@
       </c>
     </row>
     <row r="813" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A813" s="76"/>
+      <c r="A813" s="75"/>
       <c r="C813" t="s">
         <v>739</v>
       </c>
@@ -18490,7 +18493,7 @@
       </c>
     </row>
     <row r="814" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A814" s="76"/>
+      <c r="A814" s="75"/>
       <c r="C814" t="s">
         <v>703</v>
       </c>
@@ -18503,7 +18506,7 @@
       </c>
     </row>
     <row r="815" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A815" s="76"/>
+      <c r="A815" s="75"/>
       <c r="C815" t="s">
         <v>704</v>
       </c>
@@ -18513,7 +18516,7 @@
       </c>
     </row>
     <row r="816" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A816" s="76"/>
+      <c r="A816" s="75"/>
       <c r="C816" t="s">
         <v>1078</v>
       </c>
@@ -18523,7 +18526,7 @@
       </c>
     </row>
     <row r="817" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A817" s="76"/>
+      <c r="A817" s="75"/>
       <c r="C817" t="s">
         <v>1077</v>
       </c>
@@ -18533,7 +18536,7 @@
       </c>
     </row>
     <row r="818" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A818" s="76"/>
+      <c r="A818" s="75"/>
       <c r="C818" t="s">
         <v>705</v>
       </c>
@@ -18543,7 +18546,7 @@
       </c>
     </row>
     <row r="819" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A819" s="76"/>
+      <c r="A819" s="75"/>
       <c r="C819" t="s">
         <v>706</v>
       </c>
@@ -18553,7 +18556,7 @@
       </c>
     </row>
     <row r="821" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A821" s="76" t="s">
+      <c r="A821" s="75" t="s">
         <v>699</v>
       </c>
       <c r="C821" t="s">
@@ -18564,7 +18567,7 @@
       </c>
     </row>
     <row r="822" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A822" s="76"/>
+      <c r="A822" s="75"/>
       <c r="C822" t="s">
         <v>1069</v>
       </c>
@@ -18573,7 +18576,7 @@
       </c>
     </row>
     <row r="823" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A823" s="76"/>
+      <c r="A823" s="75"/>
       <c r="C823" t="s">
         <v>1070</v>
       </c>
@@ -18583,7 +18586,7 @@
       </c>
     </row>
     <row r="824" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A824" s="76"/>
+      <c r="A824" s="75"/>
       <c r="C824" t="s">
         <v>1072</v>
       </c>
@@ -18592,7 +18595,7 @@
       </c>
     </row>
     <row r="825" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A825" s="76"/>
+      <c r="A825" s="75"/>
       <c r="C825" t="s">
         <v>1071</v>
       </c>
@@ -18601,7 +18604,7 @@
       </c>
     </row>
     <row r="826" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A826" s="76"/>
+      <c r="A826" s="75"/>
       <c r="C826" t="s">
         <v>1074</v>
       </c>
@@ -18610,7 +18613,7 @@
       </c>
     </row>
     <row r="827" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A827" s="76"/>
+      <c r="A827" s="75"/>
       <c r="C827" t="s">
         <v>1076</v>
       </c>
@@ -18620,7 +18623,7 @@
       </c>
     </row>
     <row r="828" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A828" s="76"/>
+      <c r="A828" s="75"/>
       <c r="C828" t="s">
         <v>1075</v>
       </c>
@@ -18630,7 +18633,7 @@
       </c>
     </row>
     <row r="829" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A829" s="76"/>
+      <c r="A829" s="75"/>
       <c r="C829" t="s">
         <v>1073</v>
       </c>
@@ -18640,7 +18643,7 @@
       </c>
     </row>
     <row r="830" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A830" s="76"/>
+      <c r="A830" s="75"/>
       <c r="C830" t="s">
         <v>700</v>
       </c>
@@ -18649,7 +18652,7 @@
       </c>
     </row>
     <row r="831" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A831" s="76"/>
+      <c r="A831" s="75"/>
       <c r="C831" t="s">
         <v>1079</v>
       </c>
@@ -18659,7 +18662,7 @@
       </c>
     </row>
     <row r="832" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A832" s="76"/>
+      <c r="A832" s="75"/>
       <c r="C832" t="s">
         <v>212</v>
       </c>
@@ -18669,7 +18672,7 @@
       </c>
     </row>
     <row r="833" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A833" s="76"/>
+      <c r="A833" s="75"/>
       <c r="C833" t="s">
         <v>701</v>
       </c>
@@ -18679,7 +18682,7 @@
       </c>
     </row>
     <row r="834" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A834" s="76"/>
+      <c r="A834" s="75"/>
       <c r="C834" t="s">
         <v>702</v>
       </c>
@@ -18689,7 +18692,7 @@
       </c>
     </row>
     <row r="835" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A835" s="76"/>
+      <c r="A835" s="75"/>
       <c r="C835" t="s">
         <v>739</v>
       </c>
@@ -18699,1970 +18702,1969 @@
       </c>
     </row>
     <row r="836" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A836" s="76"/>
+      <c r="A836" s="75"/>
       <c r="C836" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D836" s="54">
+        <f>(D830*D825)/D835</f>
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="837" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A837" s="75"/>
+      <c r="C837" t="s">
         <v>703</v>
       </c>
-      <c r="D836" s="51">
+      <c r="D837" s="51">
         <f>D823/D832</f>
         <v>8.3999999999999995E-5</v>
       </c>
     </row>
-    <row r="837" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A837" s="76"/>
-      <c r="C837" t="s">
+    <row r="838" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A838" s="75"/>
+      <c r="C838" t="s">
         <v>704</v>
       </c>
-      <c r="D837" s="51">
-        <f>POWER(D836,2)*D825</f>
+      <c r="D838" s="51">
+        <f>POWER(D837,2)*D825</f>
         <v>0.7056</v>
       </c>
     </row>
-    <row r="838" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A838" s="76"/>
-      <c r="C838" t="s">
+    <row r="839" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A839" s="75"/>
+      <c r="C839" t="s">
         <v>1078</v>
       </c>
-      <c r="D838" s="51" t="b">
+      <c r="D839" s="51" t="b">
         <f>D831&lt;=D827</f>
         <v>1</v>
       </c>
     </row>
-    <row r="839" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A839" s="76"/>
-      <c r="C839" t="s">
+    <row r="840" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A840" s="75"/>
+      <c r="C840" t="s">
         <v>1077</v>
       </c>
-      <c r="D839" s="51" t="b">
-        <f>D837&lt;=D828</f>
+      <c r="D840" s="51" t="b">
+        <f>D838&lt;=D828</f>
         <v>1</v>
       </c>
     </row>
-    <row r="840" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A840" s="76"/>
-      <c r="C840" t="s">
+    <row r="841" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A841" s="75"/>
+      <c r="C841" t="s">
         <v>705</v>
       </c>
-      <c r="D840" s="51">
-        <f>D837*D830</f>
+      <c r="D841" s="51">
+        <f>D838*D830</f>
         <v>1.4112</v>
       </c>
     </row>
-    <row r="841" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A841" s="76"/>
-      <c r="C841" t="s">
+    <row r="842" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A842" s="75"/>
+      <c r="C842" t="s">
         <v>706</v>
       </c>
-      <c r="D841" s="51">
-        <f>POWER(D836, 2)*D835</f>
+      <c r="D842" s="51">
+        <f>POWER(D837, 2)*D835</f>
         <v>1.6799999999999999E-4</v>
       </c>
     </row>
-    <row r="842" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A842" s="69"/>
-      <c r="D842" s="51"/>
-    </row>
     <row r="843" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C843" t="s">
+      <c r="A843" s="69"/>
+      <c r="D843" s="51"/>
+    </row>
+    <row r="844" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C844" t="s">
         <v>708</v>
       </c>
-      <c r="D843">
+      <c r="D844">
         <v>3</v>
       </c>
     </row>
-    <row r="844" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A844" s="77" t="s">
+    <row r="845" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A845" s="76" t="s">
         <v>707</v>
       </c>
-      <c r="C844" t="s">
+      <c r="C845" t="s">
         <v>709</v>
       </c>
-      <c r="D844">
+      <c r="D845">
         <v>550</v>
       </c>
-      <c r="E844" t="s">
+      <c r="E845" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="845" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A845" s="77"/>
-      <c r="C845" t="s">
+    <row r="846" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A846" s="76"/>
+      <c r="C846" t="s">
         <v>710</v>
       </c>
-      <c r="D845">
+      <c r="D846">
         <f>25.4*41.9*0.000001</f>
         <v>1.06426E-3</v>
       </c>
     </row>
-    <row r="846" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A846" s="77"/>
-      <c r="C846" t="s">
+    <row r="847" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A847" s="76"/>
+      <c r="C847" t="s">
         <v>712</v>
       </c>
-      <c r="D846">
-        <f>D845*D844*0.3048</f>
+      <c r="D847">
+        <f>D846*D845*0.3048</f>
         <v>0.17841254640000004</v>
       </c>
-      <c r="E846" t="s">
+      <c r="E847" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="847" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A847" s="77"/>
-      <c r="C847" t="s">
+    <row r="848" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A848" s="76"/>
+      <c r="C848" t="s">
         <v>713</v>
       </c>
-      <c r="D847">
-        <f>D846*50</f>
+      <c r="D848">
+        <f>D847*50</f>
         <v>8.9206273200000012</v>
       </c>
     </row>
-    <row r="848" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A848" s="77"/>
-    </row>
     <row r="849" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A849" s="77"/>
+      <c r="A849" s="76"/>
     </row>
     <row r="850" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A850" s="77"/>
+      <c r="A850" s="76"/>
     </row>
     <row r="851" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A851" s="77"/>
+      <c r="A851" s="76"/>
     </row>
     <row r="852" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A852" s="77"/>
+      <c r="A852" s="76"/>
     </row>
     <row r="853" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A853" s="77"/>
+      <c r="A853" s="76"/>
     </row>
     <row r="854" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A854" s="77"/>
+      <c r="A854" s="76"/>
     </row>
     <row r="855" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A855" s="77"/>
+      <c r="A855" s="76"/>
     </row>
     <row r="856" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A856" s="77"/>
+      <c r="A856" s="76"/>
     </row>
     <row r="857" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C857" t="s">
+      <c r="A857" s="76"/>
+    </row>
+    <row r="858" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C858" t="s">
         <v>741</v>
       </c>
-      <c r="E857" s="1">
+      <c r="E858" s="1">
         <f>D67</f>
         <v>0.15679999999999999</v>
       </c>
     </row>
-    <row r="858" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A858" s="77" t="s">
+    <row r="859" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A859" s="76" t="s">
         <v>740</v>
       </c>
-      <c r="C858" t="s">
+      <c r="C859" t="s">
         <v>742</v>
       </c>
-      <c r="E858">
+      <c r="E859">
         <f>D27</f>
         <v>0.7</v>
       </c>
     </row>
-    <row r="859" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A859" s="77"/>
-      <c r="C859" t="s">
+    <row r="860" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A860" s="76"/>
+      <c r="C860" t="s">
         <v>743</v>
       </c>
-      <c r="E859" s="1">
+      <c r="E860" s="1">
         <f>D217+D218</f>
         <v>1.5361505115495317</v>
       </c>
     </row>
-    <row r="860" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A860" s="77"/>
-      <c r="C860" t="s">
+    <row r="861" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A861" s="76"/>
+      <c r="C861" t="s">
         <v>744</v>
       </c>
-      <c r="E860" s="1">
-        <f>E857+E858+E859</f>
+      <c r="E861" s="1">
+        <f>E858+E859+E860</f>
         <v>2.3929505115495315</v>
       </c>
     </row>
-    <row r="861" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A861" s="77"/>
-    </row>
     <row r="862" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A862" s="77"/>
+      <c r="A862" s="76"/>
     </row>
     <row r="863" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A863" s="77"/>
-      <c r="C863" t="s">
+      <c r="A863" s="76"/>
+    </row>
+    <row r="864" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A864" s="76"/>
+      <c r="C864" t="s">
         <v>4</v>
       </c>
-      <c r="E863">
+      <c r="E864">
         <v>2</v>
       </c>
     </row>
-    <row r="864" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A864" s="77"/>
-      <c r="C864" t="s">
+    <row r="865" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A865" s="76"/>
+      <c r="C865" t="s">
         <v>629</v>
-      </c>
-      <c r="D864" t="s">
-        <v>206</v>
-      </c>
-      <c r="E864">
-        <v>0.17399999999999999</v>
-      </c>
-    </row>
-    <row r="865" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A865" s="77"/>
-      <c r="C865" t="s">
-        <v>630</v>
       </c>
       <c r="D865" t="s">
         <v>206</v>
       </c>
       <c r="E865">
+        <v>0.17399999999999999</v>
+      </c>
+    </row>
+    <row r="866" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A866" s="76"/>
+      <c r="C866" t="s">
+        <v>630</v>
+      </c>
+      <c r="D866" t="s">
+        <v>206</v>
+      </c>
+      <c r="E866">
         <v>0.5</v>
       </c>
     </row>
-    <row r="866" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A866" s="77"/>
-      <c r="C866" t="s">
+    <row r="867" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A867" s="76"/>
+      <c r="C867" t="s">
         <v>627</v>
       </c>
-      <c r="D866" t="s">
+      <c r="D867" t="s">
         <v>638</v>
       </c>
-      <c r="E866">
-        <f>POWER(E864/2, 2)*PI()*E865</f>
+      <c r="E867">
+        <f>POWER(E865/2, 2)*PI()*E866</f>
         <v>1.1889357397510571E-2</v>
       </c>
     </row>
-    <row r="867" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A867" s="77"/>
-      <c r="C867" t="s">
+    <row r="868" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A868" s="76"/>
+      <c r="C868" t="s">
         <v>631</v>
       </c>
-      <c r="E867" s="1">
-        <f>E860</f>
+      <c r="E868" s="1">
+        <f>E861</f>
         <v>2.3929505115495315</v>
       </c>
     </row>
-    <row r="868" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A868" s="77"/>
-      <c r="C868" t="s">
+    <row r="869" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A869" s="76"/>
+      <c r="C869" t="s">
         <v>636</v>
       </c>
-      <c r="D868" t="s">
+      <c r="D869" t="s">
         <v>632</v>
       </c>
-      <c r="E868">
+      <c r="E869">
         <v>2300</v>
       </c>
     </row>
-    <row r="869" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A869" s="77"/>
-      <c r="C869" t="s">
+    <row r="870" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A870" s="76"/>
+      <c r="C870" t="s">
         <v>633</v>
       </c>
-      <c r="D869" t="s">
+      <c r="D870" t="s">
         <v>634</v>
       </c>
-      <c r="E869">
+      <c r="E870">
         <v>20</v>
       </c>
     </row>
-    <row r="870" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A870" s="77"/>
-      <c r="C870" t="s">
+    <row r="871" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A871" s="76"/>
+      <c r="C871" t="s">
         <v>635</v>
       </c>
-      <c r="D870" t="s">
+      <c r="D871" t="s">
         <v>637</v>
       </c>
-      <c r="E870">
+      <c r="E871">
         <v>800</v>
       </c>
     </row>
-    <row r="871" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A871" s="77"/>
-      <c r="C871" t="s">
+    <row r="872" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A872" s="76"/>
+      <c r="C872" t="s">
         <v>639</v>
       </c>
-      <c r="D871" t="s">
+      <c r="D872" t="s">
         <v>640</v>
       </c>
-      <c r="E871">
-        <f>E870*E866</f>
+      <c r="E872">
+        <f>E871*E867</f>
         <v>9.5114859180084572</v>
       </c>
     </row>
-    <row r="872" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A872" s="77"/>
-      <c r="C872" t="s">
+    <row r="873" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A873" s="76"/>
+      <c r="C873" t="s">
         <v>641</v>
       </c>
-      <c r="D872" t="s">
+      <c r="D873" t="s">
         <v>642</v>
       </c>
-      <c r="E872">
-        <f>E868*E871*E869</f>
+      <c r="E873">
+        <f>E869*E872*E870</f>
         <v>437528.35222838906</v>
       </c>
     </row>
-    <row r="873" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A873" s="77"/>
-      <c r="C873" t="s">
+    <row r="874" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A874" s="76"/>
+      <c r="C874" t="s">
         <v>643</v>
-      </c>
-      <c r="D873" t="s">
-        <v>323</v>
-      </c>
-      <c r="E873">
-        <f>E872/E867</f>
-        <v>182840.53519563674</v>
-      </c>
-    </row>
-    <row r="874" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A874" s="77"/>
-      <c r="C874" t="s">
-        <v>644</v>
       </c>
       <c r="D874" t="s">
         <v>323</v>
       </c>
       <c r="E874">
-        <f>E873/E863</f>
+        <f>E873/E868</f>
+        <v>182840.53519563674</v>
+      </c>
+    </row>
+    <row r="875" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A875" s="76"/>
+      <c r="C875" t="s">
+        <v>644</v>
+      </c>
+      <c r="D875" t="s">
+        <v>323</v>
+      </c>
+      <c r="E875">
+        <f>E874/E864</f>
         <v>91420.267597818369</v>
       </c>
     </row>
-    <row r="875" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A875" s="77"/>
-      <c r="C875" t="s">
-        <v>645</v>
-      </c>
-      <c r="D875" t="s">
-        <v>646</v>
-      </c>
-      <c r="E875">
-        <f>E866/E874</f>
-        <v>1.3005165823638758E-7</v>
-      </c>
-    </row>
     <row r="876" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A876" s="77"/>
+      <c r="A876" s="76"/>
       <c r="C876" t="s">
         <v>645</v>
       </c>
       <c r="D876" t="s">
+        <v>646</v>
+      </c>
+      <c r="E876">
+        <f>E867/E875</f>
+        <v>1.3005165823638758E-7</v>
+      </c>
+    </row>
+    <row r="877" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A877" s="76"/>
+      <c r="C877" t="s">
+        <v>645</v>
+      </c>
+      <c r="D877" t="s">
         <v>647</v>
       </c>
-      <c r="E876">
-        <f>(1000000)*E875</f>
+      <c r="E877">
+        <f>(1000000)*E876</f>
         <v>0.13005165823638759</v>
       </c>
     </row>
-    <row r="877" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A877" s="77"/>
-      <c r="C877" t="s">
+    <row r="878" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A878" s="76"/>
+      <c r="C878" t="s">
         <v>648</v>
       </c>
-      <c r="D877" t="s">
+      <c r="D878" t="s">
         <v>649</v>
       </c>
-      <c r="E877">
+      <c r="E878">
         <v>0.1</v>
       </c>
     </row>
-    <row r="878" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A878" s="77"/>
-      <c r="C878" t="s">
+    <row r="879" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A879" s="76"/>
+      <c r="C879" t="s">
         <v>650</v>
       </c>
-      <c r="D878" t="s">
+      <c r="D879" t="s">
         <v>207</v>
       </c>
-      <c r="E878">
-        <f>E875/E877</f>
+      <c r="E879">
+        <f>E876/E878</f>
         <v>1.3005165823638757E-6</v>
       </c>
     </row>
-    <row r="879" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A879" s="77"/>
-      <c r="C879" t="s">
+    <row r="880" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A880" s="76"/>
+      <c r="C880" t="s">
         <v>651</v>
-      </c>
-      <c r="D879" t="s">
-        <v>206</v>
-      </c>
-      <c r="E879">
-        <f>2*POWER(E878/PI(), 0.5)</f>
-        <v>1.286805790027971E-3</v>
-      </c>
-    </row>
-    <row r="880" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A880" s="77"/>
-      <c r="C880" t="s">
-        <v>653</v>
       </c>
       <c r="D880" t="s">
         <v>206</v>
       </c>
       <c r="E880">
-        <f>CEILING(E879, 0.001)</f>
+        <f>2*POWER(E879/PI(), 0.5)</f>
+        <v>1.286805790027971E-3</v>
+      </c>
+    </row>
+    <row r="881" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A881" s="76"/>
+      <c r="C881" t="s">
+        <v>653</v>
+      </c>
+      <c r="D881" t="s">
+        <v>206</v>
+      </c>
+      <c r="E881">
+        <f>CEILING(E880, 0.001)</f>
         <v>2E-3</v>
       </c>
     </row>
-    <row r="881" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A881" s="77"/>
-      <c r="C881" t="s">
+    <row r="882" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A882" s="76"/>
+      <c r="C882" t="s">
         <v>652</v>
-      </c>
-      <c r="D881" t="s">
-        <v>133</v>
-      </c>
-      <c r="E881">
-        <f>E880*1000</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="882" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A882" s="77"/>
-      <c r="C882" t="s">
-        <v>658</v>
       </c>
       <c r="D882" t="s">
         <v>133</v>
       </c>
       <c r="E882">
+        <f>E881*1000</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="883" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A883" s="76"/>
+      <c r="C883" t="s">
+        <v>658</v>
+      </c>
+      <c r="D883" t="s">
+        <v>133</v>
+      </c>
+      <c r="E883">
         <v>9</v>
       </c>
     </row>
-    <row r="883" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A883" s="77"/>
-      <c r="C883" t="s">
+    <row r="884" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A884" s="76"/>
+      <c r="C884" t="s">
         <v>659</v>
       </c>
-      <c r="E883">
-        <f>E882/1000</f>
+      <c r="E884">
+        <f>E883/1000</f>
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="884" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C884" t="s">
+    <row r="885" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C885" t="s">
         <v>656</v>
       </c>
-      <c r="E884">
+      <c r="E885">
         <f>0.00604</f>
         <v>6.0400000000000002E-3</v>
       </c>
     </row>
-    <row r="885" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C885" t="s">
-        <v>655</v>
-      </c>
-      <c r="E885">
-        <f>E884/E870</f>
-        <v>7.5500000000000006E-6</v>
-      </c>
-    </row>
     <row r="886" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C886" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E886">
-        <v>2300</v>
+        <f>E885/E871</f>
+        <v>7.5500000000000006E-6</v>
       </c>
     </row>
     <row r="887" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C887" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E887">
-        <f>E870*E877*E883/E884</f>
-        <v>119.20529801324503</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="888" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C888" t="s">
+        <v>657</v>
+      </c>
+      <c r="E888">
+        <f>E871*E878*E884/E885</f>
+        <v>119.20529801324503</v>
+      </c>
+    </row>
+    <row r="889" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C889" t="s">
         <v>660</v>
       </c>
-      <c r="E888" t="b">
-        <f>E887&lt;E886</f>
+      <c r="E889" t="b">
+        <f>E888&lt;E887</f>
         <v>1</v>
       </c>
     </row>
-    <row r="891" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B891" t="s">
+    <row r="892" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B892" t="s">
         <v>37</v>
       </c>
-      <c r="C891" t="s">
+      <c r="C892" t="s">
         <v>43</v>
       </c>
-      <c r="D891" t="s">
+      <c r="D892" t="s">
         <v>21</v>
       </c>
-      <c r="E891">
+      <c r="E892">
         <f>D5</f>
         <v>35.400000000000006</v>
       </c>
     </row>
-    <row r="892" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A892" s="77" t="s">
+    <row r="893" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A893" s="76" t="s">
         <v>761</v>
       </c>
-      <c r="B892" t="s">
+      <c r="B893" t="s">
         <v>474</v>
       </c>
-      <c r="C892" t="s">
+      <c r="C893" t="s">
         <v>475</v>
       </c>
-      <c r="D892" t="s">
+      <c r="D893" t="s">
         <v>21</v>
       </c>
-      <c r="E892">
+      <c r="E893">
         <f>D6</f>
         <v>38.099999999999994</v>
       </c>
     </row>
-    <row r="893" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A893" s="77"/>
-      <c r="B893" t="s">
+    <row r="894" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A894" s="76"/>
+      <c r="B894" t="s">
         <v>38</v>
       </c>
-      <c r="C893" t="s">
+      <c r="C894" t="s">
         <v>42</v>
       </c>
-      <c r="D893" t="s">
+      <c r="D894" t="s">
         <v>21</v>
       </c>
-      <c r="E893">
+      <c r="E894">
         <f>D7</f>
         <v>44.1</v>
       </c>
     </row>
-    <row r="894" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A894" s="77"/>
-      <c r="C894" t="s">
+    <row r="895" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A895" s="76"/>
+      <c r="C895" t="s">
         <v>762</v>
       </c>
-      <c r="D894" t="s">
+      <c r="D895" t="s">
         <v>20</v>
       </c>
-      <c r="E894">
+      <c r="E895">
         <v>3</v>
       </c>
     </row>
-    <row r="895" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A895" s="77"/>
-      <c r="C895" t="s">
+    <row r="896" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A896" s="76"/>
+      <c r="C896" t="s">
         <v>763</v>
       </c>
-      <c r="E895">
-        <f>(E893/E894)</f>
+      <c r="E896">
+        <f>(E894/E895)</f>
         <v>14.700000000000001</v>
       </c>
     </row>
-    <row r="896" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A896" s="77"/>
-      <c r="C896" t="s">
+    <row r="897" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A897" s="76"/>
+      <c r="C897" t="s">
         <v>764</v>
       </c>
-      <c r="E896">
-        <f>E891/E894</f>
+      <c r="E897">
+        <f>E892/E895</f>
         <v>11.800000000000002</v>
       </c>
     </row>
-    <row r="897" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A897" s="77"/>
-      <c r="C897" t="s">
+    <row r="898" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A898" s="76"/>
+      <c r="C898" t="s">
         <v>765</v>
       </c>
-      <c r="E897">
-        <f>E892/E894</f>
+      <c r="E898">
+        <f>E893/E895</f>
         <v>12.699999999999998</v>
       </c>
     </row>
-    <row r="898" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A898" s="77"/>
-      <c r="C898" t="s">
+    <row r="899" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A899" s="76"/>
+      <c r="C899" t="s">
         <v>766</v>
       </c>
-      <c r="E898">
+      <c r="E899">
         <f>12</f>
         <v>12</v>
       </c>
     </row>
-    <row r="899" spans="1:15" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A899" s="77"/>
-      <c r="C899" t="s">
+    <row r="900" spans="1:15" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A900" s="76"/>
+      <c r="C900" t="s">
         <v>767</v>
       </c>
-      <c r="E899">
-        <f>E893*E893/E898</f>
+      <c r="E900">
+        <f>E894*E894/E899</f>
         <v>162.06750000000002</v>
       </c>
-      <c r="G899" s="17" t="s">
+      <c r="G900" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="H899" s="43" t="s">
+      <c r="H900" s="43" t="s">
         <v>773</v>
       </c>
-      <c r="I899" s="43" t="s">
+      <c r="I900" s="43" t="s">
         <v>776</v>
       </c>
-      <c r="J899" s="43" t="s">
+      <c r="J900" s="43" t="s">
         <v>775</v>
       </c>
-      <c r="K899" s="43" t="s">
+      <c r="K900" s="43" t="s">
         <v>774</v>
       </c>
-      <c r="L899" s="43" t="s">
+      <c r="L900" s="43" t="s">
         <v>777</v>
       </c>
-      <c r="M899" s="43" t="s">
+      <c r="M900" s="43" t="s">
         <v>778</v>
       </c>
-      <c r="N899" s="43" t="s">
+      <c r="N900" s="43" t="s">
         <v>780</v>
       </c>
-      <c r="O899" s="42"/>
-    </row>
-    <row r="900" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A900" s="77"/>
-      <c r="C900" t="s">
+      <c r="O900" s="42"/>
+    </row>
+    <row r="901" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A901" s="76"/>
+      <c r="C901" t="s">
         <v>768</v>
       </c>
-      <c r="E900">
+      <c r="E901">
         <f>6</f>
         <v>6</v>
       </c>
-      <c r="G900" s="17">
+      <c r="G901" s="17">
         <v>1</v>
       </c>
-      <c r="H900" s="17">
-        <f>E893/G900</f>
+      <c r="H901" s="17">
+        <f>E894/G901</f>
         <v>44.1</v>
       </c>
-      <c r="I900" s="17">
-        <f>H900*H900*G900</f>
+      <c r="I901" s="17">
+        <f>H901*H901*G901</f>
         <v>1944.8100000000002</v>
-      </c>
-      <c r="J900" s="17">
-        <f>I900/2</f>
-        <v>972.40500000000009</v>
-      </c>
-      <c r="K900" s="17">
-        <f>E891/G900</f>
-        <v>35.400000000000006</v>
-      </c>
-      <c r="L900" s="17">
-        <f>E891*E891/G900</f>
-        <v>1253.1600000000003</v>
-      </c>
-      <c r="M900" s="17">
-        <f>L900/2</f>
-        <v>626.58000000000015</v>
-      </c>
-      <c r="N900" s="42"/>
-    </row>
-    <row r="901" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A901" s="77"/>
-      <c r="C901" t="s">
-        <v>769</v>
-      </c>
-      <c r="E901">
-        <v>2</v>
-      </c>
-      <c r="G901" s="17">
-        <v>2</v>
-      </c>
-      <c r="H901" s="17">
-        <f>E893/G901</f>
-        <v>22.05</v>
-      </c>
-      <c r="I901" s="17">
-        <f t="shared" ref="I901:I914" si="83">H901*H901*G901</f>
-        <v>972.40500000000009</v>
       </c>
       <c r="J901" s="17">
         <f>I901/2</f>
-        <v>486.20250000000004</v>
+        <v>972.40500000000009</v>
       </c>
       <c r="K901" s="17">
-        <f>E891/G901</f>
-        <v>17.700000000000003</v>
+        <f>E892/G901</f>
+        <v>35.400000000000006</v>
       </c>
       <c r="L901" s="17">
-        <f>E891*E891/G901</f>
-        <v>626.58000000000015</v>
+        <f>E892*E892/G901</f>
+        <v>1253.1600000000003</v>
       </c>
       <c r="M901" s="17">
         <f>L901/2</f>
+        <v>626.58000000000015</v>
+      </c>
+      <c r="N901" s="42"/>
+    </row>
+    <row r="902" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A902" s="76"/>
+      <c r="C902" t="s">
+        <v>769</v>
+      </c>
+      <c r="E902">
+        <v>2</v>
+      </c>
+      <c r="G902" s="17">
+        <v>2</v>
+      </c>
+      <c r="H902" s="17">
+        <f>E894/G902</f>
+        <v>22.05</v>
+      </c>
+      <c r="I902" s="17">
+        <f t="shared" ref="I902:I915" si="83">H902*H902*G902</f>
+        <v>972.40500000000009</v>
+      </c>
+      <c r="J902" s="17">
+        <f>I902/2</f>
+        <v>486.20250000000004</v>
+      </c>
+      <c r="K902" s="17">
+        <f>E892/G902</f>
+        <v>17.700000000000003</v>
+      </c>
+      <c r="L902" s="17">
+        <f>E892*E892/G902</f>
+        <v>626.58000000000015</v>
+      </c>
+      <c r="M902" s="17">
+        <f>L902/2</f>
         <v>313.29000000000008</v>
       </c>
-      <c r="N901" s="42"/>
-    </row>
-    <row r="902" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A902" s="77"/>
-      <c r="C902" t="s">
+      <c r="N902" s="42"/>
+    </row>
+    <row r="903" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A903" s="76"/>
+      <c r="C903" t="s">
         <v>770</v>
       </c>
-      <c r="E902">
-        <f xml:space="preserve"> E900*E901</f>
+      <c r="E903">
+        <f xml:space="preserve"> E901*E902</f>
         <v>12</v>
       </c>
-      <c r="G902" s="17">
+      <c r="G903" s="17">
         <v>3</v>
       </c>
-      <c r="H902" s="17">
-        <f>E893/G902</f>
+      <c r="H903" s="17">
+        <f>E894/G903</f>
         <v>14.700000000000001</v>
       </c>
-      <c r="I902" s="17">
+      <c r="I903" s="17">
         <f t="shared" si="83"/>
         <v>648.2700000000001</v>
       </c>
-      <c r="J902" s="17">
-        <f>I902/2</f>
+      <c r="J903" s="17">
+        <f>I903/2</f>
         <v>324.13500000000005</v>
       </c>
-      <c r="K902" s="17">
-        <f>E891/G902</f>
+      <c r="K903" s="17">
+        <f>E892/G903</f>
         <v>11.800000000000002</v>
       </c>
-      <c r="L902" s="17">
-        <f>E891*E891/G902</f>
+      <c r="L903" s="17">
+        <f>E892*E892/G903</f>
         <v>417.72000000000008</v>
       </c>
-      <c r="M902" s="17">
-        <f>L902/2</f>
+      <c r="M903" s="17">
+        <f>L903/2</f>
         <v>208.86000000000004</v>
       </c>
     </row>
-    <row r="903" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A903" s="77"/>
-      <c r="G903" s="17">
+    <row r="904" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A904" s="76"/>
+      <c r="G904" s="17">
         <v>4</v>
       </c>
-      <c r="H903" s="17">
-        <f>E893/G903</f>
+      <c r="H904" s="17">
+        <f>E894/G904</f>
         <v>11.025</v>
       </c>
-      <c r="I903" s="17">
+      <c r="I904" s="17">
         <f t="shared" si="83"/>
         <v>486.20250000000004</v>
       </c>
-      <c r="J903" s="17">
-        <f t="shared" ref="J903:J914" si="84">I903/2</f>
+      <c r="J904" s="17">
+        <f t="shared" ref="J904:J915" si="84">I904/2</f>
         <v>243.10125000000002</v>
       </c>
-      <c r="K903" s="17">
-        <f>E891/G903</f>
+      <c r="K904" s="17">
+        <f>E892/G904</f>
         <v>8.8500000000000014</v>
       </c>
-      <c r="L903" s="17">
-        <f>E891*E891/G903</f>
+      <c r="L904" s="17">
+        <f>E892*E892/G904</f>
         <v>313.29000000000008</v>
       </c>
-      <c r="M903" s="17">
-        <f t="shared" ref="M903:M914" si="85">L903/2</f>
+      <c r="M904" s="17">
+        <f t="shared" ref="M904:M915" si="85">L904/2</f>
         <v>156.64500000000004</v>
       </c>
     </row>
-    <row r="904" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A904" s="77"/>
-      <c r="C904" t="s">
+    <row r="905" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A905" s="76"/>
+      <c r="C905" t="s">
         <v>771</v>
       </c>
-      <c r="E904">
-        <f>(POWER(E893,2))/(200*2)</f>
+      <c r="E905">
+        <f>(POWER(E894,2))/(200*2)</f>
         <v>4.862025</v>
       </c>
-      <c r="G904" s="17">
+      <c r="G905" s="17">
         <v>5</v>
       </c>
-      <c r="H904" s="17">
-        <f>E893/G904</f>
+      <c r="H905" s="17">
+        <f>E894/G905</f>
         <v>8.82</v>
       </c>
-      <c r="I904" s="17">
+      <c r="I905" s="17">
         <f t="shared" si="83"/>
         <v>388.96199999999999</v>
       </c>
-      <c r="J904" s="17">
+      <c r="J905" s="17">
         <f t="shared" si="84"/>
         <v>194.48099999999999</v>
       </c>
-      <c r="K904" s="17">
-        <f>E891/G904</f>
+      <c r="K905" s="17">
+        <f>E892/G905</f>
         <v>7.080000000000001</v>
       </c>
-      <c r="L904" s="17">
-        <f>E891*E891/G904</f>
+      <c r="L905" s="17">
+        <f>E892*E892/G905</f>
         <v>250.63200000000006</v>
       </c>
-      <c r="M904" s="17">
+      <c r="M905" s="17">
         <f t="shared" si="85"/>
         <v>125.31600000000003</v>
       </c>
-      <c r="N904" t="s">
+      <c r="N905" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="905" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A905" s="77"/>
-      <c r="C905" t="s">
+    <row r="906" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A906" s="76"/>
+      <c r="C906" t="s">
         <v>772</v>
       </c>
-      <c r="E905">
-        <f>E893/E904</f>
+      <c r="E906">
+        <f>E894/E905</f>
         <v>9.0702947845804989</v>
       </c>
-      <c r="G905" s="17">
+      <c r="G906" s="17">
         <v>6</v>
       </c>
-      <c r="H905" s="17">
-        <f>E893/G905</f>
+      <c r="H906" s="17">
+        <f>E894/G906</f>
         <v>7.3500000000000005</v>
       </c>
-      <c r="I905" s="17">
+      <c r="I906" s="17">
         <f t="shared" si="83"/>
         <v>324.13500000000005</v>
       </c>
-      <c r="J905" s="17">
+      <c r="J906" s="17">
         <f t="shared" si="84"/>
         <v>162.06750000000002</v>
       </c>
-      <c r="K905" s="17">
-        <f>E891/G905</f>
+      <c r="K906" s="17">
+        <f>E892/G906</f>
         <v>5.9000000000000012</v>
       </c>
-      <c r="L905" s="17">
-        <f>E891*E891/G905</f>
+      <c r="L906" s="17">
+        <f>E892*E892/G906</f>
         <v>208.86000000000004</v>
       </c>
-      <c r="M905" s="17">
+      <c r="M906" s="17">
         <f t="shared" si="85"/>
         <v>104.43000000000002</v>
       </c>
-      <c r="N905" t="s">
+      <c r="N906" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="906" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A906" s="77"/>
-      <c r="G906" s="17">
+    <row r="907" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A907" s="76"/>
+      <c r="G907" s="17">
         <v>7</v>
       </c>
-      <c r="H906" s="17">
-        <f>E893/G906</f>
+      <c r="H907" s="17">
+        <f>E894/G907</f>
         <v>6.3</v>
       </c>
-      <c r="I906" s="17">
+      <c r="I907" s="17">
         <f t="shared" si="83"/>
         <v>277.83</v>
       </c>
-      <c r="J906" s="17">
+      <c r="J907" s="17">
         <f t="shared" si="84"/>
         <v>138.91499999999999</v>
       </c>
-      <c r="K906" s="17">
-        <f>E891/G906</f>
+      <c r="K907" s="17">
+        <f>E892/G907</f>
         <v>5.0571428571428578</v>
       </c>
-      <c r="L906" s="17">
-        <f>E891*E891/G906</f>
+      <c r="L907" s="17">
+        <f>E892*E892/G907</f>
         <v>179.02285714285719</v>
       </c>
-      <c r="M906" s="17">
+      <c r="M907" s="17">
         <f t="shared" si="85"/>
         <v>89.511428571428596</v>
       </c>
-      <c r="N906" t="s">
+      <c r="N907" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="907" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G907" s="17">
+    <row r="908" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G908" s="17">
         <v>8</v>
       </c>
-      <c r="H907" s="17">
-        <f>E893/G907</f>
+      <c r="H908" s="17">
+        <f>E894/G908</f>
         <v>5.5125000000000002</v>
       </c>
-      <c r="I907" s="17">
+      <c r="I908" s="17">
         <f t="shared" si="83"/>
         <v>243.10125000000002</v>
       </c>
-      <c r="J907" s="17">
+      <c r="J908" s="17">
         <f t="shared" si="84"/>
         <v>121.55062500000001</v>
       </c>
-      <c r="K907" s="17">
-        <f>E891/G907</f>
+      <c r="K908" s="17">
+        <f>E892/G908</f>
         <v>4.4250000000000007</v>
       </c>
-      <c r="L907" s="17">
-        <f>E891*E891/G907</f>
+      <c r="L908" s="17">
+        <f>E892*E892/G908</f>
         <v>156.64500000000004</v>
       </c>
-      <c r="M907" s="17">
+      <c r="M908" s="17">
         <f t="shared" si="85"/>
         <v>78.322500000000019</v>
       </c>
-      <c r="N907" t="s">
+      <c r="N908" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="908" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G908" s="17">
+    <row r="909" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G909" s="17">
         <v>9</v>
       </c>
-      <c r="H908" s="17">
-        <f>E893/G908</f>
+      <c r="H909" s="17">
+        <f>E894/G909</f>
         <v>4.9000000000000004</v>
       </c>
-      <c r="I908" s="17">
+      <c r="I909" s="17">
         <f t="shared" si="83"/>
         <v>216.09000000000003</v>
       </c>
-      <c r="J908" s="17">
+      <c r="J909" s="17">
         <f t="shared" si="84"/>
         <v>108.04500000000002</v>
       </c>
-      <c r="K908" s="17">
-        <f>E891/G908</f>
+      <c r="K909" s="17">
+        <f>E892/G909</f>
         <v>3.933333333333334</v>
       </c>
-      <c r="L908" s="17">
-        <f>E891*E891/G908</f>
+      <c r="L909" s="17">
+        <f>E892*E892/G909</f>
         <v>139.24000000000004</v>
       </c>
-      <c r="M908" s="17">
+      <c r="M909" s="17">
         <f t="shared" si="85"/>
         <v>69.620000000000019</v>
       </c>
-      <c r="N908" t="s">
+      <c r="N909" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="909" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G909" s="17">
+    <row r="910" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G910" s="17">
         <v>10</v>
       </c>
-      <c r="H909" s="17">
-        <f>E893/G909</f>
+      <c r="H910" s="17">
+        <f>E894/G910</f>
         <v>4.41</v>
       </c>
-      <c r="I909" s="17">
+      <c r="I910" s="17">
         <f t="shared" si="83"/>
         <v>194.48099999999999</v>
       </c>
-      <c r="J909" s="17">
+      <c r="J910" s="17">
         <f t="shared" si="84"/>
         <v>97.240499999999997</v>
       </c>
-      <c r="K909" s="17">
-        <f>E891/G909</f>
+      <c r="K910" s="17">
+        <f>E892/G910</f>
         <v>3.5400000000000005</v>
       </c>
-      <c r="L909" s="17">
-        <f>E891*E891/G909</f>
+      <c r="L910" s="17">
+        <f>E892*E892/G910</f>
         <v>125.31600000000003</v>
       </c>
-      <c r="M909" s="17">
+      <c r="M910" s="17">
         <f t="shared" si="85"/>
         <v>62.658000000000015</v>
       </c>
-      <c r="N909" t="s">
+      <c r="N910" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="910" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A910" s="77" t="s">
+    <row r="911" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A911" s="76" t="s">
         <v>869</v>
       </c>
-      <c r="B910" t="s">
+      <c r="B911" t="s">
         <v>855</v>
       </c>
-      <c r="C910" t="s">
+      <c r="C911" t="s">
         <v>854</v>
       </c>
-      <c r="E910">
+      <c r="E911">
         <v>5</v>
       </c>
-      <c r="F910" s="8" t="s">
+      <c r="F911" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G910" s="17">
+      <c r="G911" s="17">
         <v>11</v>
       </c>
-      <c r="H910" s="17">
-        <f>E893/G910</f>
+      <c r="H911" s="17">
+        <f>E894/G911</f>
         <v>4.0090909090909088</v>
       </c>
-      <c r="I910" s="17">
+      <c r="I911" s="17">
         <f t="shared" si="83"/>
         <v>176.80090909090904</v>
       </c>
-      <c r="J910" s="17">
+      <c r="J911" s="17">
         <f t="shared" si="84"/>
         <v>88.400454545454522</v>
       </c>
-      <c r="K910" s="17">
-        <f>E891/G910</f>
+      <c r="K911" s="17">
+        <f>E892/G911</f>
         <v>3.2181818181818187</v>
       </c>
-      <c r="L910" s="17">
-        <f>E891*E891/G910</f>
+      <c r="L911" s="17">
+        <f>E892*E892/G911</f>
         <v>113.92363636363639</v>
       </c>
-      <c r="M910" s="17">
+      <c r="M911" s="17">
         <f t="shared" si="85"/>
         <v>56.961818181818195</v>
       </c>
-      <c r="N910" t="s">
+      <c r="N911" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="911" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A911" s="77"/>
-      <c r="B911" t="s">
+    <row r="912" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A912" s="76"/>
+      <c r="B912" t="s">
         <v>857</v>
       </c>
-      <c r="C911" t="s">
+      <c r="C912" t="s">
         <v>858</v>
       </c>
-      <c r="E911">
+      <c r="E912">
         <f>2000</f>
         <v>2000</v>
       </c>
-      <c r="F911" s="8" t="s">
+      <c r="F912" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="G911" s="17">
+      <c r="G912" s="17">
         <v>12</v>
       </c>
-      <c r="H911" s="17">
-        <f>E893/G911</f>
+      <c r="H912" s="17">
+        <f>E894/G912</f>
         <v>3.6750000000000003</v>
       </c>
-      <c r="I911" s="17">
+      <c r="I912" s="17">
         <f t="shared" si="83"/>
         <v>162.06750000000002</v>
       </c>
-      <c r="J911" s="17">
+      <c r="J912" s="17">
         <f t="shared" si="84"/>
         <v>81.033750000000012</v>
       </c>
-      <c r="K911" s="17">
-        <f>E891/G911</f>
+      <c r="K912" s="17">
+        <f>E892/G912</f>
         <v>2.9500000000000006</v>
       </c>
-      <c r="L911" s="17">
-        <f>E891*E891/G911</f>
+      <c r="L912" s="17">
+        <f>E892*E892/G912</f>
         <v>104.43000000000002</v>
       </c>
-      <c r="M911" s="17">
+      <c r="M912" s="17">
         <f t="shared" si="85"/>
         <v>52.215000000000011</v>
       </c>
-      <c r="N911" t="s">
+      <c r="N912" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="912" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A912" s="77"/>
-      <c r="B912" t="s">
+    <row r="913" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A913" s="76"/>
+      <c r="B913" t="s">
         <v>856</v>
       </c>
-      <c r="C912" t="s">
+      <c r="C913" t="s">
         <v>859</v>
       </c>
-      <c r="E912">
-        <f>((E910/1.23)-1)*E911</f>
+      <c r="E913">
+        <f>((E911/1.23)-1)*E912</f>
         <v>6130.081300813009</v>
       </c>
-      <c r="F912" s="8" t="s">
+      <c r="F913" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="G912" s="17">
+      <c r="G913" s="17">
         <v>13</v>
       </c>
-      <c r="H912" s="17">
-        <f>E893/G912</f>
+      <c r="H913" s="17">
+        <f>E894/G913</f>
         <v>3.3923076923076922</v>
       </c>
-      <c r="I912" s="17">
+      <c r="I913" s="17">
         <f t="shared" si="83"/>
         <v>149.60076923076923</v>
       </c>
-      <c r="J912" s="17">
+      <c r="J913" s="17">
         <f t="shared" si="84"/>
         <v>74.800384615384615</v>
       </c>
-      <c r="K912" s="17">
-        <f>E891/G912</f>
+      <c r="K913" s="17">
+        <f>E892/G913</f>
         <v>2.7230769230769236</v>
       </c>
-      <c r="L912" s="17">
-        <f>E891*E891/G912</f>
+      <c r="L913" s="17">
+        <f>E892*E892/G913</f>
         <v>96.396923076923102</v>
       </c>
-      <c r="M912" s="17">
+      <c r="M913" s="17">
         <f t="shared" si="85"/>
         <v>48.198461538461551</v>
       </c>
-      <c r="N912" t="s">
+      <c r="N913" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="913" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A913" s="47"/>
-      <c r="B913" t="s">
+    <row r="914" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A914" s="47"/>
+      <c r="B914" t="s">
         <v>868</v>
       </c>
-      <c r="C913" t="s">
+      <c r="C914" t="s">
         <v>874</v>
       </c>
-      <c r="E913">
-        <f>1/(31000*E912)</f>
+      <c r="E914">
+        <f>1/(31000*E913)</f>
         <v>5.26225720886455E-9</v>
       </c>
-      <c r="F913" s="8" t="s">
+      <c r="F914" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G913" s="17"/>
-      <c r="H913" s="17"/>
-      <c r="I913" s="17"/>
-      <c r="J913" s="17"/>
-      <c r="K913" s="17"/>
-      <c r="L913" s="17"/>
-      <c r="M913" s="17"/>
-    </row>
-    <row r="914" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G914" s="17">
+      <c r="G914" s="17"/>
+      <c r="H914" s="17"/>
+      <c r="I914" s="17"/>
+      <c r="J914" s="17"/>
+      <c r="K914" s="17"/>
+      <c r="L914" s="17"/>
+      <c r="M914" s="17"/>
+    </row>
+    <row r="915" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G915" s="17">
         <v>14</v>
       </c>
-      <c r="H914" s="17">
-        <f>E893/G914</f>
+      <c r="H915" s="17">
+        <f>E894/G915</f>
         <v>3.15</v>
       </c>
-      <c r="I914" s="17">
+      <c r="I915" s="17">
         <f t="shared" si="83"/>
         <v>138.91499999999999</v>
       </c>
-      <c r="J914" s="17">
+      <c r="J915" s="17">
         <f t="shared" si="84"/>
         <v>69.457499999999996</v>
       </c>
-      <c r="K914" s="17">
-        <f>E891/G914</f>
+      <c r="K915" s="17">
+        <f>E892/G915</f>
         <v>2.5285714285714289</v>
       </c>
-      <c r="L914" s="17">
-        <f>E891*E891/G914</f>
+      <c r="L915" s="17">
+        <f>E892*E892/G915</f>
         <v>89.511428571428596</v>
       </c>
-      <c r="M914" s="17">
+      <c r="M915" s="17">
         <f t="shared" si="85"/>
         <v>44.755714285714298</v>
       </c>
-      <c r="N914" t="s">
+      <c r="N915" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="915" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A915" s="77" t="s">
+    <row r="916" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A916" s="76" t="s">
         <v>870</v>
       </c>
-      <c r="B915" t="s">
+      <c r="B916" t="s">
         <v>855</v>
       </c>
-      <c r="C915" t="s">
+      <c r="C916" t="s">
         <v>854</v>
       </c>
-      <c r="E915">
+      <c r="E916">
         <v>3.3</v>
       </c>
-      <c r="F915" s="8" t="s">
+      <c r="F916" s="8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="916" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A916" s="77"/>
-      <c r="B916" t="s">
+    <row r="917" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A917" s="76"/>
+      <c r="B917" t="s">
         <v>857</v>
       </c>
-      <c r="C916" t="s">
+      <c r="C917" t="s">
         <v>858</v>
       </c>
-      <c r="E916">
+      <c r="E917">
         <f>2000</f>
         <v>2000</v>
       </c>
-      <c r="F916" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="917" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A917" s="77"/>
-      <c r="B917" t="s">
-        <v>856</v>
-      </c>
-      <c r="C917" t="s">
-        <v>859</v>
-      </c>
-      <c r="E917">
-        <f>((E915/1.23)-1)*E916</f>
-        <v>3365.8536585365846</v>
-      </c>
       <c r="F917" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="918" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A918" s="76"/>
       <c r="B918" t="s">
+        <v>856</v>
+      </c>
+      <c r="C918" t="s">
+        <v>859</v>
+      </c>
+      <c r="E918">
+        <f>((E916/1.23)-1)*E917</f>
+        <v>3365.8536585365846</v>
+      </c>
+      <c r="F918" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="919" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B919" t="s">
         <v>868</v>
       </c>
-      <c r="C918" t="s">
+      <c r="C919" t="s">
         <v>874</v>
       </c>
-      <c r="E918">
-        <f>1/(31000*E917)</f>
+      <c r="E919">
+        <f>1/(31000*E918)</f>
         <v>9.583917718560077E-9</v>
       </c>
-      <c r="F918" s="8" t="s">
+      <c r="F919" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="920" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A920" s="77" t="s">
+    <row r="921" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A921" s="76" t="s">
         <v>873</v>
       </c>
-      <c r="B920" t="s">
+      <c r="B921" t="s">
         <v>855</v>
       </c>
-      <c r="C920" t="s">
+      <c r="C921" t="s">
         <v>854</v>
       </c>
-      <c r="E920">
+      <c r="E921">
         <v>10</v>
       </c>
-      <c r="F920" s="8" t="s">
+      <c r="F921" s="8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="921" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A921" s="77"/>
-      <c r="B921" t="s">
+    <row r="922" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A922" s="76"/>
+      <c r="B922" t="s">
         <v>857</v>
       </c>
-      <c r="C921" t="s">
+      <c r="C922" t="s">
         <v>858</v>
       </c>
-      <c r="E921">
+      <c r="E922">
         <f>2000</f>
         <v>2000</v>
       </c>
-      <c r="F921" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="922" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A922" s="77"/>
-      <c r="B922" t="s">
-        <v>856</v>
-      </c>
-      <c r="C922" t="s">
-        <v>859</v>
-      </c>
-      <c r="E922">
-        <f>((E920/1.23)-1)*E921</f>
-        <v>14260.162601626018</v>
-      </c>
       <c r="F922" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="923" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A923" s="76"/>
       <c r="B923" t="s">
+        <v>856</v>
+      </c>
+      <c r="C923" t="s">
+        <v>859</v>
+      </c>
+      <c r="E923">
+        <f>((E921/1.23)-1)*E922</f>
+        <v>14260.162601626018</v>
+      </c>
+      <c r="F923" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="924" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B924" t="s">
         <v>868</v>
       </c>
-      <c r="C923" t="s">
+      <c r="C924" t="s">
         <v>874</v>
       </c>
-      <c r="E923">
-        <f>1/(31000*E922)</f>
+      <c r="E924">
+        <f>1/(31000*E923)</f>
         <v>2.2621105675506673E-9</v>
       </c>
-      <c r="F923" s="8" t="s">
+      <c r="F924" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="925" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A925" s="77" t="s">
+    <row r="926" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A926" s="76" t="s">
         <v>871</v>
       </c>
-      <c r="B925" t="s">
+      <c r="B926" t="s">
         <v>861</v>
       </c>
-      <c r="C925" t="s">
+      <c r="C926" t="s">
         <v>860</v>
       </c>
-      <c r="E925">
+      <c r="E926">
         <v>2</v>
-      </c>
-      <c r="F925" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="926" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A926" s="77"/>
-      <c r="B926" t="s">
-        <v>862</v>
-      </c>
-      <c r="C926" t="s">
-        <v>863</v>
-      </c>
-      <c r="E926">
-        <v>30</v>
       </c>
       <c r="F926" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="927" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A927" s="77"/>
+      <c r="A927" s="76"/>
       <c r="B927" t="s">
+        <v>862</v>
+      </c>
+      <c r="C927" t="s">
+        <v>863</v>
+      </c>
+      <c r="E927">
+        <v>30</v>
+      </c>
+      <c r="F927" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="928" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A928" s="76"/>
+      <c r="B928" t="s">
         <v>857</v>
       </c>
-      <c r="C927" t="s">
+      <c r="C928" t="s">
         <v>858</v>
       </c>
-      <c r="E927">
+      <c r="E928">
         <f>2000</f>
         <v>2000</v>
       </c>
-      <c r="F927" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="928" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A928" s="77"/>
-      <c r="B928" t="s">
-        <v>867</v>
-      </c>
-      <c r="C928" t="s">
-        <v>864</v>
-      </c>
-      <c r="E928">
-        <f>((E925/1.23)-1)*E927</f>
-        <v>1252.0325203252032</v>
-      </c>
       <c r="F928" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="929" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A929" s="77"/>
+      <c r="A929" s="76"/>
       <c r="B929" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C929" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E929">
-        <f>((E926/1.23)-1)*E927</f>
-        <v>46780.487804878052</v>
+        <f>((E926/1.23)-1)*E928</f>
+        <v>1252.0325203252032</v>
       </c>
       <c r="F929" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="930" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A930" s="77"/>
+      <c r="A930" s="76"/>
       <c r="B930" t="s">
+        <v>866</v>
+      </c>
+      <c r="C930" t="s">
+        <v>865</v>
+      </c>
+      <c r="E930">
+        <f>((E927/1.23)-1)*E928</f>
+        <v>46780.487804878052</v>
+      </c>
+      <c r="F930" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="931" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A931" s="76"/>
+      <c r="B931" t="s">
         <v>868</v>
       </c>
-      <c r="C930" t="s">
+      <c r="C931" t="s">
         <v>874</v>
       </c>
-      <c r="E930">
-        <f>1/(31000*E928)</f>
+      <c r="E931">
+        <f>1/(31000*E929)</f>
         <v>2.5764558022622537E-8</v>
       </c>
-      <c r="F930" s="8" t="s">
+      <c r="F931" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="932" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A932" s="77" t="s">
+    <row r="933" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A933" s="76" t="s">
         <v>872</v>
       </c>
-      <c r="B932" t="s">
+      <c r="B933" t="s">
         <v>861</v>
       </c>
-      <c r="C932" t="s">
+      <c r="C933" t="s">
         <v>860</v>
       </c>
-      <c r="E932">
+      <c r="E933">
         <v>9</v>
-      </c>
-      <c r="F932" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="933" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A933" s="77"/>
-      <c r="B933" t="s">
-        <v>862</v>
-      </c>
-      <c r="C933" t="s">
-        <v>863</v>
-      </c>
-      <c r="E933">
-        <v>20</v>
       </c>
       <c r="F933" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="934" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A934" s="77"/>
+      <c r="A934" s="76"/>
       <c r="B934" t="s">
+        <v>862</v>
+      </c>
+      <c r="C934" t="s">
+        <v>863</v>
+      </c>
+      <c r="E934">
+        <v>20</v>
+      </c>
+      <c r="F934" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="935" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A935" s="76"/>
+      <c r="B935" t="s">
         <v>857</v>
       </c>
-      <c r="C934" t="s">
+      <c r="C935" t="s">
         <v>858</v>
       </c>
-      <c r="E934">
+      <c r="E935">
         <f>2000</f>
         <v>2000</v>
       </c>
-      <c r="F934" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="935" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A935" s="77"/>
-      <c r="B935" t="s">
-        <v>867</v>
-      </c>
-      <c r="C935" t="s">
-        <v>864</v>
-      </c>
-      <c r="E935">
-        <f>((E932/1.23)-1)*E934</f>
-        <v>12634.146341463415</v>
-      </c>
       <c r="F935" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="936" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A936" s="77"/>
+      <c r="A936" s="76"/>
       <c r="B936" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C936" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E936">
-        <f>((E933/1.23)-1)*E934</f>
-        <v>30520.325203252036</v>
+        <f>((E933/1.23)-1)*E935</f>
+        <v>12634.146341463415</v>
       </c>
       <c r="F936" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="937" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A937" s="77"/>
+      <c r="A937" s="76"/>
       <c r="B937" t="s">
+        <v>866</v>
+      </c>
+      <c r="C937" t="s">
+        <v>865</v>
+      </c>
+      <c r="E937">
+        <f>((E934/1.23)-1)*E935</f>
+        <v>30520.325203252036</v>
+      </c>
+      <c r="F937" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="938" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A938" s="76"/>
+      <c r="B938" t="s">
         <v>868</v>
       </c>
-      <c r="C937" t="s">
+      <c r="C938" t="s">
         <v>874</v>
       </c>
-      <c r="E937">
-        <f>1/(31000*E935)</f>
+      <c r="E938">
+        <f>1/(31000*E936)</f>
         <v>2.5532444887283596E-9</v>
       </c>
-      <c r="F937" s="8" t="s">
+      <c r="F938" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="946" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A946" s="76" t="s">
+    <row r="947" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A947" s="75" t="s">
         <v>1085</v>
       </c>
-      <c r="C946" t="s">
+      <c r="C947" t="s">
         <v>1097</v>
       </c>
-      <c r="E946" t="s">
+      <c r="E947" t="s">
         <v>1098</v>
       </c>
-      <c r="G946" t="s">
+      <c r="G947" t="s">
         <v>1099</v>
       </c>
     </row>
-    <row r="947" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A947" s="76"/>
-      <c r="B947" t="s">
+    <row r="948" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A948" s="75"/>
+      <c r="B948" t="s">
         <v>1086</v>
       </c>
-      <c r="E947">
+      <c r="E948">
         <f>PI()*0.0000004</f>
         <v>1.2566370614359173E-6</v>
       </c>
-      <c r="F947" s="8" t="s">
+      <c r="F948" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="G947">
-        <f t="shared" ref="G947:N947" si="86">$E947</f>
+      <c r="G948">
+        <f t="shared" ref="G948:N948" si="86">$E948</f>
         <v>1.2566370614359173E-6</v>
       </c>
-      <c r="H947">
+      <c r="H948">
         <f t="shared" si="86"/>
         <v>1.2566370614359173E-6</v>
       </c>
-      <c r="I947">
+      <c r="I948">
         <f t="shared" si="86"/>
         <v>1.2566370614359173E-6</v>
       </c>
-      <c r="J947">
+      <c r="J948">
         <f t="shared" si="86"/>
         <v>1.2566370614359173E-6</v>
       </c>
-      <c r="K947">
+      <c r="K948">
         <f t="shared" si="86"/>
         <v>1.2566370614359173E-6</v>
       </c>
-      <c r="L947">
+      <c r="L948">
         <f t="shared" si="86"/>
         <v>1.2566370614359173E-6</v>
       </c>
-      <c r="M947">
+      <c r="M948">
         <f t="shared" si="86"/>
         <v>1.2566370614359173E-6</v>
       </c>
-      <c r="N947">
+      <c r="N948">
         <f t="shared" si="86"/>
         <v>1.2566370614359173E-6</v>
       </c>
     </row>
-    <row r="948" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A948" s="76"/>
-      <c r="B948" t="s">
+    <row r="949" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A949" s="75"/>
+      <c r="B949" t="s">
         <v>1087</v>
       </c>
-      <c r="C948" t="s">
+      <c r="C949" t="s">
         <v>1133</v>
       </c>
-      <c r="E948">
+      <c r="E949">
         <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="F948" s="8" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="949" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A949" s="76"/>
-      <c r="B949" t="s">
-        <v>135</v>
-      </c>
-      <c r="C949" t="s">
-        <v>1132</v>
-      </c>
-      <c r="E949">
-        <v>0.04</v>
       </c>
       <c r="F949" s="8" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="950" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A950" s="76"/>
+      <c r="A950" s="75"/>
+      <c r="B950" t="s">
+        <v>135</v>
+      </c>
       <c r="C950" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E950">
+        <v>0.04</v>
+      </c>
+      <c r="F950" s="8" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="951" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A951" s="75"/>
+      <c r="C951" t="s">
         <v>1134</v>
       </c>
-      <c r="E950">
-        <f>2*E948/E949</f>
+      <c r="E951">
+        <f>2*E949/E950</f>
         <v>0.3</v>
       </c>
-      <c r="F950" s="8"/>
-    </row>
-    <row r="951" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A951" s="76"/>
-      <c r="C951" t="s">
+      <c r="F951" s="8"/>
+    </row>
+    <row r="952" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A952" s="75"/>
+      <c r="C952" t="s">
         <v>1135</v>
       </c>
-      <c r="E951">
-        <f>1/E950</f>
+      <c r="E952">
+        <f>1/E951</f>
         <v>3.3333333333333335</v>
       </c>
-      <c r="F951" s="8"/>
-    </row>
-    <row r="952" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A952" s="76"/>
-      <c r="C952" t="s">
+      <c r="F952" s="8"/>
+    </row>
+    <row r="953" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A953" s="75"/>
+      <c r="C953" t="s">
         <v>1136</v>
       </c>
-      <c r="E952">
-        <f>POWER(E950, 2)</f>
+      <c r="E953">
+        <f>POWER(E951, 2)</f>
         <v>0.09</v>
       </c>
-      <c r="F952" s="8"/>
-    </row>
-    <row r="953" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A953" s="76"/>
-      <c r="C953" t="s">
+      <c r="F953" s="8"/>
+    </row>
+    <row r="954" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A954" s="75"/>
+      <c r="C954" t="s">
         <v>1137</v>
       </c>
-      <c r="E953">
-        <f>1/E952</f>
+      <c r="E954">
+        <f>1/E953</f>
         <v>11.111111111111111</v>
       </c>
-      <c r="F953" s="8"/>
-    </row>
-    <row r="954" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A954" s="76"/>
       <c r="F954" s="8"/>
     </row>
     <row r="955" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A955" s="76"/>
-      <c r="B955" t="s">
+      <c r="A955" s="75"/>
+      <c r="F955" s="8"/>
+    </row>
+    <row r="956" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A956" s="75"/>
+      <c r="B956" t="s">
         <v>1089</v>
       </c>
-      <c r="C955" t="s">
+      <c r="C956" t="s">
         <v>1090</v>
       </c>
-      <c r="E955">
-        <f>(E947/(4*PI()))*(LN(E950+SQRT(1+E952)) - SQRT(1+E953)+E951)</f>
+      <c r="E956">
+        <f>(E948/(4*PI()))*(LN(E951+SQRT(1+E953)) - SQRT(1+E954)+E952)</f>
         <v>1.4890421125990595E-8</v>
       </c>
-      <c r="F955" t="s">
+      <c r="F956" t="s">
         <v>154</v>
       </c>
-      <c r="G955">
-        <f t="shared" ref="G955:N955" si="87">(G947/(4*PI()))*(LN(G950+SQRT(1+G952)) - SQRT(1+G953)+G951)</f>
+      <c r="G956">
+        <f t="shared" ref="G956:N956" si="87">(G948/(4*PI()))*(LN(G951+SQRT(1+G953)) - SQRT(1+G954)+G952)</f>
         <v>-1.0000000000000001E-7</v>
       </c>
-      <c r="H955">
+      <c r="H956">
         <f t="shared" si="87"/>
         <v>-1.0000000000000001E-7</v>
       </c>
-      <c r="I955">
+      <c r="I956">
         <f t="shared" si="87"/>
         <v>-1.0000000000000001E-7</v>
       </c>
-      <c r="J955">
+      <c r="J956">
         <f t="shared" si="87"/>
         <v>-1.0000000000000001E-7</v>
       </c>
-      <c r="K955">
+      <c r="K956">
         <f t="shared" si="87"/>
         <v>-1.0000000000000001E-7</v>
       </c>
-      <c r="L955">
+      <c r="L956">
         <f t="shared" si="87"/>
         <v>-1.0000000000000001E-7</v>
       </c>
-      <c r="M955">
+      <c r="M956">
         <f t="shared" si="87"/>
         <v>-1.0000000000000001E-7</v>
       </c>
-      <c r="N955">
+      <c r="N956">
         <f t="shared" si="87"/>
         <v>-1.0000000000000001E-7</v>
       </c>
     </row>
-    <row r="956" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A956" s="76"/>
-      <c r="B956" t="s">
+    <row r="957" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A957" s="75"/>
+      <c r="B957" t="s">
         <v>1091</v>
       </c>
-      <c r="C956" t="s">
+      <c r="C957" t="s">
         <v>1092</v>
       </c>
-      <c r="E956">
+      <c r="E957">
         <f>22*16000*4</f>
         <v>1408000</v>
       </c>
     </row>
-    <row r="957" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A957" s="76"/>
-      <c r="B957" s="74" t="s">
+    <row r="958" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A958" s="75"/>
+      <c r="B958" s="74" t="s">
         <v>1095</v>
       </c>
-      <c r="C957" t="s">
+      <c r="C958" t="s">
         <v>1096</v>
       </c>
-      <c r="E957">
+      <c r="E958">
         <v>0</v>
       </c>
-      <c r="F957">
+      <c r="F958">
         <v>0</v>
       </c>
-      <c r="G957">
+      <c r="G958">
         <v>0</v>
       </c>
-      <c r="H957">
+      <c r="H958">
         <v>0</v>
       </c>
-      <c r="I957">
+      <c r="I958">
         <v>0</v>
       </c>
-      <c r="J957">
+      <c r="J958">
         <v>0</v>
       </c>
-      <c r="K957">
+      <c r="K958">
         <v>0</v>
       </c>
-      <c r="L957">
+      <c r="L958">
         <v>0</v>
       </c>
-      <c r="M957">
+      <c r="M958">
         <v>0</v>
       </c>
-      <c r="N957">
+      <c r="N958">
         <v>0</v>
       </c>
     </row>
-    <row r="958" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A958" s="76"/>
-      <c r="B958" t="s">
+    <row r="959" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A959" s="75"/>
+      <c r="B959" t="s">
         <v>1094</v>
       </c>
-      <c r="C958" t="s">
+      <c r="C959" t="s">
         <v>1093</v>
       </c>
-      <c r="E958">
-        <f>E956*COS(E957)*E955</f>
+      <c r="E959">
+        <f>E957*COS(E958)*E956</f>
         <v>2.096571294539476E-2</v>
       </c>
-      <c r="F958" t="e">
-        <f t="shared" ref="F958:N958" si="88">F956*COS(F957)*F955</f>
+      <c r="F959" t="e">
+        <f t="shared" ref="F959:N959" si="88">F957*COS(F958)*F956</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G958">
+      <c r="G959">
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
-      <c r="H958">
+      <c r="H959">
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
-      <c r="I958">
+      <c r="I959">
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
-      <c r="J958">
+      <c r="J959">
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
-      <c r="K958">
+      <c r="K959">
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
-      <c r="L958">
+      <c r="L959">
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
-      <c r="M958">
+      <c r="M959">
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
-      <c r="N958">
+      <c r="N959">
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
     </row>
-    <row r="959" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A959" s="37"/>
-    </row>
     <row r="960" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A960" s="76" t="s">
+      <c r="A960" s="37"/>
+    </row>
+    <row r="961" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A961" s="75" t="s">
         <v>1107</v>
       </c>
-      <c r="B960" t="s">
+      <c r="B961" t="s">
         <v>1108</v>
       </c>
-      <c r="C960" t="s">
+      <c r="C961" t="s">
         <v>1109</v>
       </c>
-      <c r="E960">
+      <c r="E961">
         <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="F960" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="961" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A961" s="76"/>
-      <c r="B961" t="s">
-        <v>1088</v>
-      </c>
-      <c r="C961" t="s">
-        <v>1110</v>
-      </c>
-      <c r="E961">
-        <v>1E-3</v>
       </c>
       <c r="F961" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="962" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A962" s="76"/>
+      <c r="A962" s="75"/>
       <c r="B962" t="s">
-        <v>1111</v>
+        <v>1088</v>
       </c>
       <c r="C962" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="E962">
-        <v>1.6000000000000001E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="F962" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="963" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A963" s="76"/>
+      <c r="A963" s="75"/>
       <c r="B963" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C963" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E963">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="F963" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="964" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A964" s="75"/>
+      <c r="B964" t="s">
         <v>1113</v>
       </c>
-      <c r="E963">
-        <f>0.00000000508*E960*(LN(2*E960/(E961+E962))+0.5+(0.2235*(E961+E962)/E960))</f>
+      <c r="E964">
+        <f>0.00000000508*E961*(LN(2*E961/(E962+E963))+0.5+(0.2235*(E962+E963)/E961))</f>
         <v>2.2741325637156556E-10</v>
       </c>
-      <c r="F963" t="s">
+      <c r="F964" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="964" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A964" s="76"/>
-    </row>
     <row r="965" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A965" s="76"/>
+      <c r="A965" s="75"/>
     </row>
     <row r="966" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A966" s="76"/>
-    </row>
-    <row r="968" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A968" s="76" t="s">
+      <c r="A966" s="75"/>
+    </row>
+    <row r="967" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A967" s="75"/>
+    </row>
+    <row r="969" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A969" s="75" t="s">
         <v>1138</v>
       </c>
-      <c r="B968" t="s">
+      <c r="B969" t="s">
         <v>1139</v>
       </c>
-      <c r="C968" t="s">
+      <c r="C969" t="s">
         <v>1139</v>
       </c>
-      <c r="E968" s="52" t="b">
+      <c r="E969" s="52" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="969" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A969" s="76"/>
-      <c r="B969" t="s">
+    <row r="970" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A970" s="75"/>
+      <c r="B970" t="s">
         <v>511</v>
       </c>
-      <c r="E969" s="27">
-        <f>IF(E968, 0.024, 0.048)</f>
+      <c r="E970" s="27">
+        <f>IF(E969, 0.024, 0.048)</f>
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="970" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A970" s="76"/>
-      <c r="B970" t="s">
+    <row r="971" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A971" s="75"/>
+      <c r="B971" t="s">
         <v>1140</v>
       </c>
-      <c r="C970" t="s">
+      <c r="C971" t="s">
         <v>1145</v>
       </c>
-      <c r="E970" s="52">
+      <c r="E971" s="52">
         <f>22/SQRT(3)</f>
         <v>12.701705922171767</v>
       </c>
-      <c r="F970" t="s">
+      <c r="F971" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="971" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A971" s="76"/>
-      <c r="B971" s="74" t="s">
+    <row r="972" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A972" s="75"/>
+      <c r="B972" s="74" t="s">
         <v>693</v>
       </c>
-      <c r="C971" t="s">
+      <c r="C972" t="s">
         <v>1141</v>
       </c>
-      <c r="E971">
+      <c r="E972">
         <v>10</v>
       </c>
-      <c r="F971" t="s">
+      <c r="F972" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="972" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A972" s="76"/>
-      <c r="C972" t="s">
+    <row r="973" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A973" s="75"/>
+      <c r="C973" t="s">
         <v>1144</v>
       </c>
-      <c r="E972">
+      <c r="E973">
         <v>2</v>
       </c>
     </row>
-    <row r="973" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A973" s="76"/>
-      <c r="B973" t="s">
+    <row r="974" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A974" s="75"/>
+      <c r="B974" t="s">
         <v>20</v>
       </c>
-      <c r="C973" t="s">
+      <c r="C974" t="s">
         <v>1142</v>
       </c>
-      <c r="E973">
-        <f>POWER(E970/(E969*POWER(E971, 0.44)), (1/0.725))</f>
+      <c r="E974">
+        <f>POWER(E971/(E970*POWER(E972, 0.44)), (1/0.725))</f>
         <v>542.8119517712156</v>
       </c>
-      <c r="F973" t="s">
+      <c r="F974" t="s">
         <v>1143</v>
       </c>
     </row>
-    <row r="974" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A974" s="76"/>
-      <c r="C974" t="s">
+    <row r="975" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A975" s="75"/>
+      <c r="C975" t="s">
         <v>1146</v>
       </c>
-      <c r="E974">
-        <f>E973/(E972*1.378*39.37)</f>
+      <c r="E975">
+        <f>E974/(E973*1.378*39.37)</f>
         <v>5.0027036102653044</v>
       </c>
-      <c r="F974" t="s">
+      <c r="F975" t="s">
         <v>133</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A946:A958"/>
-    <mergeCell ref="A960:A966"/>
-    <mergeCell ref="A968:A974"/>
-    <mergeCell ref="A892:A906"/>
-    <mergeCell ref="A568:A580"/>
-    <mergeCell ref="A581:A584"/>
-    <mergeCell ref="A781:A793"/>
-    <mergeCell ref="A695:A766"/>
-    <mergeCell ref="A653:A692"/>
-    <mergeCell ref="A799:A819"/>
-    <mergeCell ref="A821:A841"/>
-    <mergeCell ref="A910:A912"/>
-    <mergeCell ref="A915:A917"/>
-    <mergeCell ref="A920:A922"/>
-    <mergeCell ref="A925:A930"/>
-    <mergeCell ref="A932:A937"/>
+    <mergeCell ref="G111:K111"/>
+    <mergeCell ref="A99:A136"/>
+    <mergeCell ref="A196:A220"/>
+    <mergeCell ref="A167:A193"/>
+    <mergeCell ref="A138:A164"/>
     <mergeCell ref="A31:A59"/>
-    <mergeCell ref="A858:A883"/>
+    <mergeCell ref="A859:A884"/>
     <mergeCell ref="A286:A337"/>
     <mergeCell ref="G19:J22"/>
     <mergeCell ref="G29:K34"/>
@@ -20674,14 +20676,25 @@
     <mergeCell ref="A376:A412"/>
     <mergeCell ref="A229:A284"/>
     <mergeCell ref="A362:A374"/>
-    <mergeCell ref="A844:A856"/>
+    <mergeCell ref="A845:A857"/>
     <mergeCell ref="A414:A454"/>
     <mergeCell ref="A456:A566"/>
-    <mergeCell ref="G111:K111"/>
-    <mergeCell ref="A99:A136"/>
-    <mergeCell ref="A196:A220"/>
-    <mergeCell ref="A167:A193"/>
-    <mergeCell ref="A138:A164"/>
+    <mergeCell ref="A947:A959"/>
+    <mergeCell ref="A961:A967"/>
+    <mergeCell ref="A969:A975"/>
+    <mergeCell ref="A893:A907"/>
+    <mergeCell ref="A568:A580"/>
+    <mergeCell ref="A581:A584"/>
+    <mergeCell ref="A781:A793"/>
+    <mergeCell ref="A695:A766"/>
+    <mergeCell ref="A653:A692"/>
+    <mergeCell ref="A799:A819"/>
+    <mergeCell ref="A821:A842"/>
+    <mergeCell ref="A911:A913"/>
+    <mergeCell ref="A916:A918"/>
+    <mergeCell ref="A921:A923"/>
+    <mergeCell ref="A926:A931"/>
+    <mergeCell ref="A933:A938"/>
   </mergeCells>
   <conditionalFormatting sqref="D120">
     <cfRule type="cellIs" dxfId="11" priority="11" operator="notEqual">
@@ -20691,7 +20704,7 @@
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E888">
+  <conditionalFormatting sqref="E889">
     <cfRule type="cellIs" dxfId="9" priority="9" operator="notEqual">
       <formula>TRUE</formula>
     </cfRule>
